--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -1611,7 +1611,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -24310,7 +24310,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.656266+00:00</t>
+          <t>2026-10-17T08:29:31.399153+00:00</t>
         </is>
       </c>
     </row>
@@ -24418,7 +24418,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.657204+00:00</t>
+          <t>2026-10-17T08:29:31.400099+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.657229+00:00</t>
+          <t>2026-10-17T08:29:31.400122+00:00</t>
         </is>
       </c>
     </row>
@@ -24626,7 +24626,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.657525+00:00</t>
+          <t>2026-10-17T08:29:31.400356+00:00</t>
         </is>
       </c>
     </row>
@@ -24734,7 +24734,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.658630+00:00</t>
+          <t>2026-10-17T08:29:31.401443+00:00</t>
         </is>
       </c>
     </row>
@@ -24842,7 +24842,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.659073+00:00</t>
+          <t>2026-10-17T08:29:31.401921+00:00</t>
         </is>
       </c>
     </row>
@@ -24950,7 +24950,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.664282+00:00</t>
+          <t>2026-10-17T08:29:31.408803+00:00</t>
         </is>
       </c>
     </row>
@@ -25058,7 +25058,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.666605+00:00</t>
+          <t>2026-10-17T08:29:31.411250+00:00</t>
         </is>
       </c>
     </row>
@@ -25131,13 +25131,21 @@
           <t>papers/R04092/main/187b868956ed_R04092_2018_Mathematical_modelling_of_in-situ_microaerobic_desulfurization_of_biogas_from.pdf</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R04092_2018_Mathematical_modelling_of_in-situ_microaerobic_desulfurization_of_biogas_from.pdf</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R04092_2018_Mathematical_modelling_of_in-situ_microaerobic_desulfurization_of_biogas_from.pdf</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R04092_2018_Mathematical_modelling_of_in-situ_microaerobic_desulfurization_of_biogas_from.pdf</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -25153,12 +25161,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -25195,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.666633+00:00</t>
+          <t>2026-10-17T08:29:31.412226+00:00</t>
         </is>
       </c>
     </row>
@@ -25231,13 +25239,21 @@
           <t>papers/R04177/main/09b0de58af2f_R04177_2018_Operating_characteristics_of_baffled_reactor_under_microaerobic_conditions.pdf</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R04177_2018_Operating_characteristics_of_baffled_reactor_under_microaerobic_conditions.pdf</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R04177_2018_Operating_characteristics_of_baffled_reactor_under_microaerobic_conditions.pdf</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R04177_2018_Operating_characteristics_of_baffled_reactor_under_microaerobic_conditions.pdf</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -25253,12 +25269,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -25295,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.666639+00:00</t>
+          <t>2026-10-17T08:29:31.412619+00:00</t>
         </is>
       </c>
     </row>
@@ -25366,7 +25382,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -25403,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.667580+00:00</t>
+          <t>2026-10-17T08:29:31.413356+00:00</t>
         </is>
       </c>
     </row>
@@ -25474,7 +25490,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -25511,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.668242+00:00</t>
+          <t>2026-10-17T08:29:31.414019+00:00</t>
         </is>
       </c>
     </row>
@@ -25582,7 +25598,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -25619,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.669224+00:00</t>
+          <t>2026-10-17T08:29:31.414915+00:00</t>
         </is>
       </c>
     </row>
@@ -25655,13 +25671,21 @@
           <t>papers/R06152/main/f0955d9cdc45_R06152_2020_The_Influence_of_Zeolite_Addition_into_Anaerobic_Vinasse_Treatment.pdf</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R06152_2020_The_Influence_of_Zeolite_Addition_into_Anaerobic_Vinasse_Treatment.pdf</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R06152_2020_The_Influence_of_Zeolite_Addition_into_Anaerobic_Vinasse_Treatment.pdf</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R06152_2020_The_Influence_of_Zeolite_Addition_into_Anaerobic_Vinasse_Treatment.pdf</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -25677,12 +25701,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -25719,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.669248+00:00</t>
+          <t>2026-10-17T08:29:31.415144+00:00</t>
         </is>
       </c>
     </row>
@@ -25790,7 +25814,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -25827,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.670247+00:00</t>
+          <t>2026-10-17T08:29:31.415998+00:00</t>
         </is>
       </c>
     </row>
@@ -25898,7 +25922,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -25935,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.678053+00:00</t>
+          <t>2026-10-17T08:29:31.424546+00:00</t>
         </is>
       </c>
     </row>
@@ -26006,7 +26030,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -26043,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.678757+00:00</t>
+          <t>2026-10-17T08:29:31.425262+00:00</t>
         </is>
       </c>
     </row>
@@ -26079,13 +26103,21 @@
           <t>papers/R08552/main/bf6b5c964a64_R08552_2023_ALKALINE_PRETREATMENT_AND_AIR_MIXING_FOR_IMPROVEMENT_OF_METHANE.pdf</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R08552_2023_ALKALINE_PRETREATMENT_AND_AIR_MIXING_FOR_IMPROVEMENT_OF_METHANE.pdf</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R08552_2023_ALKALINE_PRETREATMENT_AND_AIR_MIXING_FOR_IMPROVEMENT_OF_METHANE.pdf</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R08552_2023_ALKALINE_PRETREATMENT_AND_AIR_MIXING_FOR_IMPROVEMENT_OF_METHANE.pdf</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -26101,12 +26133,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -26143,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.678777+00:00</t>
+          <t>2026-10-17T08:29:31.426486+00:00</t>
         </is>
       </c>
     </row>
@@ -26179,13 +26211,21 @@
           <t>papers/R08877/main/1665f472122c_R08877_2023_Effects_of_Low_Oxygen_Dosages_on_an_Anaerobic_Membrane.pdf</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R08877_2023_Effects_of_Low_Oxygen_Dosages_on_an_Anaerobic_Membrane.pdf</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R08877_2023_Effects_of_Low_Oxygen_Dosages_on_an_Anaerobic_Membrane.pdf</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R08877_2023_Effects_of_Low_Oxygen_Dosages_on_an_Anaerobic_Membrane.pdf</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -26201,12 +26241,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -26243,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.678782+00:00</t>
+          <t>2026-10-17T08:29:31.429285+00:00</t>
         </is>
       </c>
     </row>
@@ -26314,7 +26354,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -26351,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.679832+00:00</t>
+          <t>2026-10-17T08:29:31.430444+00:00</t>
         </is>
       </c>
     </row>
@@ -26422,7 +26462,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -26459,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.680986+00:00</t>
+          <t>2026-10-17T08:29:31.431844+00:00</t>
         </is>
       </c>
     </row>
@@ -26530,7 +26570,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -26567,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.685469+00:00</t>
+          <t>2026-10-17T08:29:31.436022+00:00</t>
         </is>
       </c>
     </row>
@@ -26638,7 +26678,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -26675,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.687795+00:00</t>
+          <t>2026-10-17T08:29:31.438310+00:00</t>
         </is>
       </c>
     </row>
@@ -26746,7 +26786,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -26783,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.689633+00:00</t>
+          <t>2026-10-17T08:29:31.440446+00:00</t>
         </is>
       </c>
     </row>
@@ -26883,7 +26923,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.689658+00:00</t>
+          <t>2026-10-17T08:29:31.440476+00:00</t>
         </is>
       </c>
     </row>
@@ -26983,7 +27023,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.689663+00:00</t>
+          <t>2026-10-17T08:29:31.440483+00:00</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27094,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -27091,7 +27131,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.691691+00:00</t>
+          <t>2026-10-17T08:29:31.442628+00:00</t>
         </is>
       </c>
     </row>
@@ -27162,7 +27202,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -27199,7 +27239,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.693024+00:00</t>
+          <t>2026-10-17T08:29:31.443878+00:00</t>
         </is>
       </c>
     </row>
@@ -27270,7 +27310,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -27307,7 +27347,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.695413+00:00</t>
+          <t>2026-10-17T08:29:31.445912+00:00</t>
         </is>
       </c>
     </row>
@@ -27378,7 +27418,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -27415,7 +27455,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.697575+00:00</t>
+          <t>2026-10-17T08:29:31.447862+00:00</t>
         </is>
       </c>
     </row>
@@ -27515,7 +27555,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.697604+00:00</t>
+          <t>2026-10-17T08:29:31.447879+00:00</t>
         </is>
       </c>
     </row>
@@ -27615,7 +27655,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.697609+00:00</t>
+          <t>2026-10-17T08:29:31.447883+00:00</t>
         </is>
       </c>
     </row>
@@ -27686,7 +27726,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -27723,7 +27763,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.699181+00:00</t>
+          <t>2026-10-17T08:29:31.449544+00:00</t>
         </is>
       </c>
     </row>
@@ -27794,7 +27834,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -27831,7 +27871,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.702164+00:00</t>
+          <t>2026-10-17T08:29:31.452406+00:00</t>
         </is>
       </c>
     </row>
@@ -27931,7 +27971,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.702190+00:00</t>
+          <t>2026-10-17T08:29:31.452425+00:00</t>
         </is>
       </c>
     </row>
@@ -28002,7 +28042,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -28039,7 +28079,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.703352+00:00</t>
+          <t>2026-10-17T08:29:31.453644+00:00</t>
         </is>
       </c>
     </row>
@@ -28139,7 +28179,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.703368+00:00</t>
+          <t>2026-10-17T08:29:31.453661+00:00</t>
         </is>
       </c>
     </row>
@@ -28210,7 +28250,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -28247,7 +28287,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.704036+00:00</t>
+          <t>2026-10-17T08:29:31.454380+00:00</t>
         </is>
       </c>
     </row>
@@ -28318,7 +28358,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -28355,7 +28395,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.705599+00:00</t>
+          <t>2026-10-17T08:29:31.455942+00:00</t>
         </is>
       </c>
     </row>
@@ -28426,7 +28466,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -28463,7 +28503,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.705849+00:00</t>
+          <t>2026-10-17T08:29:31.456415+00:00</t>
         </is>
       </c>
     </row>
@@ -28563,7 +28603,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.705862+00:00</t>
+          <t>2026-10-17T08:29:31.456440+00:00</t>
         </is>
       </c>
     </row>
@@ -28634,7 +28674,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -28671,7 +28711,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.708680+00:00</t>
+          <t>2026-10-17T08:29:31.459380+00:00</t>
         </is>
       </c>
     </row>
@@ -28771,7 +28811,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.708703+00:00</t>
+          <t>2026-10-17T08:29:31.459405+00:00</t>
         </is>
       </c>
     </row>
@@ -28842,7 +28882,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -28879,7 +28919,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.709211+00:00</t>
+          <t>2026-10-17T08:29:31.459921+00:00</t>
         </is>
       </c>
     </row>
@@ -28979,7 +29019,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.709226+00:00</t>
+          <t>2026-10-17T08:29:31.459935+00:00</t>
         </is>
       </c>
     </row>
@@ -29079,7 +29119,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.709229+00:00</t>
+          <t>2026-10-17T08:29:31.459940+00:00</t>
         </is>
       </c>
     </row>
@@ -29179,7 +29219,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.709232+00:00</t>
+          <t>2026-10-17T08:29:31.459942+00:00</t>
         </is>
       </c>
     </row>
@@ -29250,7 +29290,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -29287,7 +29327,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.710832+00:00</t>
+          <t>2026-10-17T08:29:31.461544+00:00</t>
         </is>
       </c>
     </row>
@@ -29387,7 +29427,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.710849+00:00</t>
+          <t>2026-10-17T08:29:31.461560+00:00</t>
         </is>
       </c>
     </row>
@@ -29487,7 +29527,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.710853+00:00</t>
+          <t>2026-10-17T08:29:31.461563+00:00</t>
         </is>
       </c>
     </row>
@@ -29558,7 +29598,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -29595,7 +29635,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.711428+00:00</t>
+          <t>2026-10-17T08:29:31.461971+00:00</t>
         </is>
       </c>
     </row>
@@ -29695,7 +29735,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.711454+00:00</t>
+          <t>2026-10-17T08:29:31.461985+00:00</t>
         </is>
       </c>
     </row>
@@ -29766,7 +29806,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -29803,7 +29843,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.712940+00:00</t>
+          <t>2026-10-17T08:29:31.463704+00:00</t>
         </is>
       </c>
     </row>
@@ -29874,7 +29914,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -29911,7 +29951,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.714258+00:00</t>
+          <t>2026-10-17T08:29:31.465195+00:00</t>
         </is>
       </c>
     </row>
@@ -30011,7 +30051,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.714277+00:00</t>
+          <t>2026-10-17T08:29:31.465222+00:00</t>
         </is>
       </c>
     </row>
@@ -30111,7 +30151,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.714281+00:00</t>
+          <t>2026-10-17T08:29:31.465227+00:00</t>
         </is>
       </c>
     </row>
@@ -30211,7 +30251,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.714284+00:00</t>
+          <t>2026-10-17T08:29:31.465230+00:00</t>
         </is>
       </c>
     </row>
@@ -30311,7 +30351,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.714303+00:00</t>
+          <t>2026-10-17T08:29:31.465232+00:00</t>
         </is>
       </c>
     </row>
@@ -30382,7 +30422,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -30419,7 +30459,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.714854+00:00</t>
+          <t>2026-10-17T08:29:31.465855+00:00</t>
         </is>
       </c>
     </row>
@@ -30519,7 +30559,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.714870+00:00</t>
+          <t>2026-10-17T08:29:31.465981+00:00</t>
         </is>
       </c>
     </row>
@@ -30619,7 +30659,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.714873+00:00</t>
+          <t>2026-10-17T08:29:31.465989+00:00</t>
         </is>
       </c>
     </row>
@@ -30719,7 +30759,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.714876+00:00</t>
+          <t>2026-10-17T08:29:31.465994+00:00</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30859,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.714879+00:00</t>
+          <t>2026-10-17T08:29:31.466063+00:00</t>
         </is>
       </c>
     </row>
@@ -30919,7 +30959,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.714882+00:00</t>
+          <t>2026-10-17T08:29:31.466067+00:00</t>
         </is>
       </c>
     </row>
@@ -30990,7 +31030,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -31027,7 +31067,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.715311+00:00</t>
+          <t>2026-10-17T08:29:31.466580+00:00</t>
         </is>
       </c>
     </row>
@@ -31098,7 +31138,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -31135,7 +31175,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.716364+00:00</t>
+          <t>2026-10-17T08:29:31.467708+00:00</t>
         </is>
       </c>
     </row>
@@ -31206,7 +31246,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -31243,7 +31283,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.719502+00:00</t>
+          <t>2026-10-17T08:29:31.470706+00:00</t>
         </is>
       </c>
     </row>
@@ -31343,7 +31383,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.719541+00:00</t>
+          <t>2026-10-17T08:29:31.470725+00:00</t>
         </is>
       </c>
     </row>
@@ -31414,7 +31454,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -31451,7 +31491,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.724815+00:00</t>
+          <t>2026-10-17T08:29:31.474854+00:00</t>
         </is>
       </c>
     </row>
@@ -31551,7 +31591,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.724859+00:00</t>
+          <t>2026-10-17T08:29:31.474874+00:00</t>
         </is>
       </c>
     </row>
@@ -31622,7 +31662,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -31659,7 +31699,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.727107+00:00</t>
+          <t>2026-10-17T08:29:31.476946+00:00</t>
         </is>
       </c>
     </row>
@@ -31730,7 +31770,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -31767,7 +31807,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.729031+00:00</t>
+          <t>2026-10-17T08:29:31.478682+00:00</t>
         </is>
       </c>
     </row>
@@ -31867,7 +31907,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.729059+00:00</t>
+          <t>2026-10-17T08:29:31.478699+00:00</t>
         </is>
       </c>
     </row>
@@ -31967,7 +32007,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.729063+00:00</t>
+          <t>2026-10-17T08:29:31.478703+00:00</t>
         </is>
       </c>
     </row>
@@ -32067,7 +32107,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.729067+00:00</t>
+          <t>2026-10-17T08:29:31.478707+00:00</t>
         </is>
       </c>
     </row>
@@ -32167,7 +32207,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.729071+00:00</t>
+          <t>2026-10-17T08:29:31.478709+00:00</t>
         </is>
       </c>
     </row>
@@ -32238,7 +32278,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -32275,7 +32315,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.730456+00:00</t>
+          <t>2026-10-17T08:29:31.479956+00:00</t>
         </is>
       </c>
     </row>
@@ -32375,7 +32415,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.730486+00:00</t>
+          <t>2026-10-17T08:29:31.479979+00:00</t>
         </is>
       </c>
     </row>
@@ -32475,7 +32515,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.730490+00:00</t>
+          <t>2026-10-17T08:29:31.479983+00:00</t>
         </is>
       </c>
     </row>
@@ -32575,7 +32615,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.730494+00:00</t>
+          <t>2026-10-17T08:29:31.479986+00:00</t>
         </is>
       </c>
     </row>
@@ -32671,7 +32711,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.730497+00:00</t>
+          <t>2026-10-17T08:29:31.479990+00:00</t>
         </is>
       </c>
     </row>
@@ -32767,7 +32807,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.730500+00:00</t>
+          <t>2026-10-17T08:29:31.479993+00:00</t>
         </is>
       </c>
     </row>
@@ -32863,7 +32903,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.730503+00:00</t>
+          <t>2026-10-17T08:29:31.479995+00:00</t>
         </is>
       </c>
     </row>
@@ -32959,7 +32999,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.730506+00:00</t>
+          <t>2026-10-17T08:29:31.479999+00:00</t>
         </is>
       </c>
     </row>
@@ -33055,7 +33095,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.730510+00:00</t>
+          <t>2026-10-17T08:29:31.480001+00:00</t>
         </is>
       </c>
     </row>
@@ -33151,7 +33191,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.730513+00:00</t>
+          <t>2026-10-17T08:29:31.480004+00:00</t>
         </is>
       </c>
     </row>
@@ -33247,7 +33287,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.730517+00:00</t>
+          <t>2026-10-17T08:29:31.480007+00:00</t>
         </is>
       </c>
     </row>
@@ -33318,7 +33358,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -33355,7 +33395,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.731221+00:00</t>
+          <t>2026-10-17T08:29:31.480698+00:00</t>
         </is>
       </c>
     </row>
@@ -33455,7 +33495,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.731245+00:00</t>
+          <t>2026-10-17T08:29:31.480715+00:00</t>
         </is>
       </c>
     </row>
@@ -33526,7 +33566,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -33563,7 +33603,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.731471+00:00</t>
+          <t>2026-10-17T08:29:31.480766+00:00</t>
         </is>
       </c>
     </row>
@@ -33634,7 +33674,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -33671,7 +33711,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.731723+00:00</t>
+          <t>2026-10-17T08:29:31.481177+00:00</t>
         </is>
       </c>
     </row>
@@ -33742,7 +33782,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -33779,7 +33819,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.731845+00:00</t>
+          <t>2026-10-17T08:29:31.481353+00:00</t>
         </is>
       </c>
     </row>
@@ -33850,7 +33890,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -33891,7 +33931,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.731959+00:00</t>
+          <t>2026-10-17T08:29:31.481500+00:00</t>
         </is>
       </c>
     </row>
@@ -33962,7 +34002,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -33999,7 +34039,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.732617+00:00</t>
+          <t>2026-10-17T08:29:31.481870+00:00</t>
         </is>
       </c>
     </row>
@@ -34070,7 +34110,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -34107,7 +34147,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.732834+00:00</t>
+          <t>2026-10-17T08:29:31.482061+00:00</t>
         </is>
       </c>
     </row>
@@ -34178,7 +34218,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -34219,7 +34259,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.732890+00:00</t>
+          <t>2026-10-17T08:29:31.482111+00:00</t>
         </is>
       </c>
     </row>
@@ -34290,7 +34330,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -34331,7 +34371,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.732953+00:00</t>
+          <t>2026-10-17T08:29:31.482170+00:00</t>
         </is>
       </c>
     </row>
@@ -34402,7 +34442,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -34443,7 +34483,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.733205+00:00</t>
+          <t>2026-10-17T08:29:31.482322+00:00</t>
         </is>
       </c>
     </row>
@@ -34514,7 +34554,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -34555,7 +34595,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.733271+00:00</t>
+          <t>2026-10-17T08:29:31.482369+00:00</t>
         </is>
       </c>
     </row>
@@ -34626,7 +34666,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -34663,7 +34703,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.733803+00:00</t>
+          <t>2026-10-17T08:29:31.482814+00:00</t>
         </is>
       </c>
     </row>
@@ -34734,7 +34774,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -34771,7 +34811,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.733863+00:00</t>
+          <t>2026-10-17T08:29:31.482858+00:00</t>
         </is>
       </c>
     </row>
@@ -34871,7 +34911,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.733875+00:00</t>
+          <t>2026-10-17T08:29:31.482868+00:00</t>
         </is>
       </c>
     </row>
@@ -34971,7 +35011,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.733879+00:00</t>
+          <t>2026-10-17T08:29:31.482871+00:00</t>
         </is>
       </c>
     </row>
@@ -35075,7 +35115,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.733882+00:00</t>
+          <t>2026-10-17T08:29:31.482875+00:00</t>
         </is>
       </c>
     </row>
@@ -35175,7 +35215,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.733885+00:00</t>
+          <t>2026-10-17T08:29:31.482878+00:00</t>
         </is>
       </c>
     </row>
@@ -35246,7 +35286,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -35283,7 +35323,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.734469+00:00</t>
+          <t>2026-10-17T08:29:31.483148+00:00</t>
         </is>
       </c>
     </row>
@@ -35354,7 +35394,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>git_remote_verified</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -35391,7 +35431,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.735889+00:00</t>
+          <t>2026-10-17T08:29:31.484210+00:00</t>
         </is>
       </c>
     </row>
@@ -35485,7 +35525,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.735918+00:00</t>
+          <t>2026-10-17T08:29:31.484234+00:00</t>
         </is>
       </c>
     </row>
@@ -35579,7 +35619,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.735924+00:00</t>
+          <t>2026-10-17T08:29:31.484237+00:00</t>
         </is>
       </c>
     </row>
@@ -35673,7 +35713,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.735929+00:00</t>
+          <t>2026-10-17T08:29:31.484240+00:00</t>
         </is>
       </c>
     </row>
@@ -35767,7 +35807,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.735935+00:00</t>
+          <t>2026-10-17T08:29:31.484243+00:00</t>
         </is>
       </c>
     </row>
@@ -35861,7 +35901,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.735993+00:00</t>
+          <t>2026-10-17T08:29:31.484246+00:00</t>
         </is>
       </c>
     </row>
@@ -35955,7 +35995,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.735996+00:00</t>
+          <t>2026-10-17T08:29:31.484248+00:00</t>
         </is>
       </c>
     </row>
@@ -36049,7 +36089,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.735999+00:00</t>
+          <t>2026-10-17T08:29:31.484251+00:00</t>
         </is>
       </c>
     </row>
@@ -36143,7 +36183,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736002+00:00</t>
+          <t>2026-10-17T08:29:31.484259+00:00</t>
         </is>
       </c>
     </row>
@@ -36237,7 +36277,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736005+00:00</t>
+          <t>2026-10-17T08:29:31.484262+00:00</t>
         </is>
       </c>
     </row>
@@ -36331,7 +36371,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736008+00:00</t>
+          <t>2026-10-17T08:29:31.484265+00:00</t>
         </is>
       </c>
     </row>
@@ -36425,7 +36465,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736010+00:00</t>
+          <t>2026-10-17T08:29:31.484269+00:00</t>
         </is>
       </c>
     </row>
@@ -36519,7 +36559,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736013+00:00</t>
+          <t>2026-10-17T08:29:31.484272+00:00</t>
         </is>
       </c>
     </row>
@@ -36613,7 +36653,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736016+00:00</t>
+          <t>2026-10-17T08:29:31.484275+00:00</t>
         </is>
       </c>
     </row>
@@ -36707,7 +36747,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736019+00:00</t>
+          <t>2026-10-17T08:29:31.484277+00:00</t>
         </is>
       </c>
     </row>
@@ -36801,7 +36841,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736023+00:00</t>
+          <t>2026-10-17T08:29:31.484280+00:00</t>
         </is>
       </c>
     </row>
@@ -36895,7 +36935,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736026+00:00</t>
+          <t>2026-10-17T08:29:31.484283+00:00</t>
         </is>
       </c>
     </row>
@@ -36989,7 +37029,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736029+00:00</t>
+          <t>2026-10-17T08:29:31.484285+00:00</t>
         </is>
       </c>
     </row>
@@ -37083,7 +37123,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736032+00:00</t>
+          <t>2026-10-17T08:29:31.484288+00:00</t>
         </is>
       </c>
     </row>
@@ -37177,7 +37217,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736034+00:00</t>
+          <t>2026-10-17T08:29:31.484290+00:00</t>
         </is>
       </c>
     </row>
@@ -37271,7 +37311,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736037+00:00</t>
+          <t>2026-10-17T08:29:31.484292+00:00</t>
         </is>
       </c>
     </row>
@@ -37365,7 +37405,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736040+00:00</t>
+          <t>2026-10-17T08:29:31.484322+00:00</t>
         </is>
       </c>
     </row>
@@ -37459,7 +37499,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736043+00:00</t>
+          <t>2026-10-17T08:29:31.484329+00:00</t>
         </is>
       </c>
     </row>
@@ -37553,7 +37593,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736046+00:00</t>
+          <t>2026-10-17T08:29:31.484333+00:00</t>
         </is>
       </c>
     </row>
@@ -37647,7 +37687,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736049+00:00</t>
+          <t>2026-10-17T08:29:31.484336+00:00</t>
         </is>
       </c>
     </row>
@@ -37741,7 +37781,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736052+00:00</t>
+          <t>2026-10-17T08:29:31.484339+00:00</t>
         </is>
       </c>
     </row>
@@ -37835,7 +37875,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736054+00:00</t>
+          <t>2026-10-17T08:29:31.484342+00:00</t>
         </is>
       </c>
     </row>
@@ -37929,7 +37969,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736057+00:00</t>
+          <t>2026-10-17T08:29:31.484346+00:00</t>
         </is>
       </c>
     </row>
@@ -38029,7 +38069,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T08:28:38.736061+00:00</t>
+          <t>2026-10-17T08:29:31.484349+00:00</t>
         </is>
       </c>
     </row>
@@ -38044,7 +38084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38132,12 +38172,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R04092</t>
+          <t>R13558</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R04092.main.187b868956ed3e07</t>
+          <t>R13558.main.0006612a5b75c131</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -38147,20 +38187,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>187b868956ed3e07456eb08dd523d037ffb342e17033c71274fc2618ce78b4ef</t>
+          <t>0006612a5b75c131170aa335c1e8d9810b41dca937beefac6ea258e1920944ec</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1344658</v>
+        <v>974385</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://europepmc.org/api/getPdf?pmcid=PMC6288047</t>
+          <t>https://www.scielo.br/j/esa/a/DPQswHpgKLty6wPLBbxGcCn/?lang=en&amp;format=pdf</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>R04092_2018_Mathematical_modelling_of_in-situ_microaerobic_desulfurization_of_biogas_from.pdf</t>
+          <t>R13558_2026_Redox_mediators_and_microaeration_overcoming_linear_alkylbenzene_sulfonate_recalcitrance.pdf</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -38172,12 +38212,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R04177</t>
+          <t>R04889</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R04177.main.09b0de58af2ff1e6</t>
+          <t>R04889.main.860a0532503787f8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -38187,20 +38227,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>09b0de58af2ff1e679e24cecf4a4a617fa2a0e539dc66351e2edb4076d2e7b72</t>
+          <t>860a0532503787f8bb84a599bdbf923f690615b05121c8a78c21249f8de911cb</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>446033</v>
+        <v>506684</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.deswater.com/DWT_articles/vol_121_papers/121_2018_191.pdf</t>
+          <t>https://journal.unnes.ac.id/nju/jbat/article/download/16318/9427</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>R04177_2018_Operating_characteristics_of_baffled_reactor_under_microaerobic_conditions.pdf</t>
+          <t>R04889_2019_Inoculum_Selection_and_Micro-Aeration_for_Biogas_Production_in_Two-Stage.pdf</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -38212,12 +38252,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R06152</t>
+          <t>R01212</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R06152.main.f0955d9cdc458c31</t>
+          <t>R01212.main.ef235fcb491d4749</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -38227,20 +38267,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>f0955d9cdc458c312005b1ddcd8310e4b51c593dd6837667f2eba967cafd2e68</t>
+          <t>ef235fcb491d474970838cf59cfd36efaf9a37c84ddd225c06788beb77d497e3</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>309899</v>
+        <v>773976</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://kireka.setiabudi.ac.id/index.php/kireka/article/download/10/8</t>
+          <t>https://www.eeer.org/upload/eer-19-1-59-9.pdf</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>R06152_2020_The_Influence_of_Zeolite_Addition_into_Anaerobic_Vinasse_Treatment.pdf</t>
+          <t>R01212_2014_Effects_of_Pre-aeration_on_the_Anaerobic_Digestion_of_Sewage.pdf</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -38252,12 +38292,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R08552</t>
+          <t>R05542</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R08552.main.bf6b5c964a64fd5b</t>
+          <t>R05542.main.735560cdb2769e25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -38267,20 +38307,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>bf6b5c964a64fd5b21a534be73fb1fe5727ff6d8477e1420c4980b43ca0794e8</t>
+          <t>735560cdb2769e2517355c073dd51a95ac90b015a5b36f90dcc0dff360ae182b</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1839968</v>
+        <v>836053</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://scholarworks.uark.edu/cgi/viewcontent.cgi?params=%2Fcontext%2Fbaegpub%2Farticle%2F1025%2F&amp;path_info=1685095243246_1528824496.pdf</t>
+          <t>https://europepmc.org/api/getPdf?pmcid=PMC9056904</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>R08552_2023_ALKALINE_PRETREATMENT_AND_AIR_MIXING_FOR_IMPROVEMENT_OF_METHANE.pdf</t>
+          <t>R05542_2020_Effect_of_micro-aerobic_process_on_improvement_of_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -38292,12 +38332,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R06611</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R08877.main.1665f472122ce85f</t>
+          <t>R06611.main.b8eb8afdada2a2d0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -38307,20 +38347,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1665f472122ce85f4b06ce2770b29b6eb114e09600163b1776a8b49edc1e26a3</t>
+          <t>b8eb8afdada2a2d0d5151fd81489263cbfd0ccc3bbde8c5ca36a02af52cfa12f</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3855275</v>
+        <v>3320239</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://repository.tudelft.nl/file/File_32773e49-f19e-4eb7-9776-049d9763bc66</t>
+          <t>https://eprints.whiterose.ac.uk/id/eprint/168685/1/A_draft_BITE_paper.pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>R08877_2023_Effects_of_Low_Oxygen_Dosages_on_an_Anaerobic_Membrane.pdf</t>
+          <t>R06611_2021_Effective_pretreatment_of_lignocellulosic_co-substrates_using_barley_straw-adapted_microbial.pdf</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -38332,12 +38372,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R13558</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R13558.main.0006612a5b75c131</t>
+          <t>R07238.main.26c38d1631747ddc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -38347,20 +38387,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0006612a5b75c131170aa335c1e8d9810b41dca937beefac6ea258e1920944ec</t>
+          <t>26c38d1631747ddcb443b8d80d0070145f1968ff0f4b8e86dc2f69cc2bb968d8</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>974385</v>
+        <v>4532295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.scielo.br/j/esa/a/DPQswHpgKLty6wPLBbxGcCn/?lang=en&amp;format=pdf</t>
+          <t>https://europepmc.org/api/getPdf?pmcid=PMC8044681</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>R13558_2026_Redox_mediators_and_microaeration_overcoming_linear_alkylbenzene_sulfonate_recalcitrance.pdf</t>
+          <t>R07238_2021_The_influence_of_combined_low-strength_ultrasonics_and_micro-aerobic_pretreatment.pdf</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -38372,12 +38412,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R04889</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R04889.main.860a0532503787f8</t>
+          <t>R08646.main.7df5523334e7d1bb</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -38387,20 +38427,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>860a0532503787f8bb84a599bdbf923f690615b05121c8a78c21249f8de911cb</t>
+          <t>7df5523334e7d1bb513d2a3deb5b018c0c9b2a3ea9e49b7ff8f09a1fe853cd96</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>506684</v>
+        <v>3009960</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://journal.unnes.ac.id/nju/jbat/article/download/16318/9427</t>
+          <t>https://europepmc.org/api/getPdf?pmcid=PMC10559078</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>R04889_2019_Inoculum_Selection_and_Micro-Aeration_for_Biogas_Production_in_Two-Stage.pdf</t>
+          <t>R08646_2023_Approaches_to_mitigation_of_hydrogen_sulfide_during_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -38412,12 +38452,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R01212</t>
+          <t>R10894</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R01212.main.ef235fcb491d4749</t>
+          <t>R10894.main.f9caf3b730e23f0d</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -38427,20 +38467,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ef235fcb491d474970838cf59cfd36efaf9a37c84ddd225c06788beb77d497e3</t>
+          <t>f9caf3b730e23f0d9d31d71069935c39e162415bbdac53ee97821305a81be9d2</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>773976</v>
+        <v>2030435</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.eeer.org/upload/eer-19-1-59-9.pdf</t>
+          <t>https://europepmc.org/api/getPdf?pmcid=PMC11499478</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>R01212_2014_Effects_of_Pre-aeration_on_the_Anaerobic_Digestion_of_Sewage.pdf</t>
+          <t>R10894_2024_The_effects_of_different_pretreatment_technologies_on_microbial_community.pdf</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -38452,12 +38492,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R05542</t>
+          <t>R06737</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R05542.main.735560cdb2769e25</t>
+          <t>R06737.main.32eabc0a46b31862</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -38467,20 +38507,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>735560cdb2769e2517355c073dd51a95ac90b015a5b36f90dcc0dff360ae182b</t>
+          <t>32eabc0a46b31862fa95a7bcf29fc4e5b154b7ec51c11cd1d4f798bbad95b59a</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>836053</v>
+        <v>4126947</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://europepmc.org/api/getPdf?pmcid=PMC9056904</t>
+          <t>https://ira.lib.polyu.edu.hk/bitstream/10397/97386/1/Zhuang_Genomic_Driven_Factors.pdf</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>R05542_2020_Effect_of_micro-aerobic_process_on_improvement_of_anaerobic_digestion.pdf</t>
+          <t>R06737_2021_Genomic_driven_factors_enhance_biocatalyst-related_cellulolysis_potential_in_anaerobic.pdf</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -38492,12 +38532,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R06611</t>
+          <t>R04119</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R06611.main.b8eb8afdada2a2d0</t>
+          <t>R04119.main.c9b1902447e38978</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -38507,20 +38547,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>b8eb8afdada2a2d0d5151fd81489263cbfd0ccc3bbde8c5ca36a02af52cfa12f</t>
+          <t>c9b1902447e38978d2f6f25327940f80e825baee1ebabba8bd8a860ed1fa254c</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3320239</v>
+        <v>1726821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://eprints.whiterose.ac.uk/id/eprint/168685/1/A_draft_BITE_paper.pdf</t>
+          <t>https://europepmc.org/api/getPdf?pmcid=PMC6197294</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>R06611_2021_Effective_pretreatment_of_lignocellulosic_co-substrates_using_barley_straw-adapted_microbial.pdf</t>
+          <t>R04119_2018_Microbial_pretreatment_of_lignocellulosic_biomass_for_enhanced_biomethanation_and.pdf</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -38532,12 +38572,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R00273</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R07238.main.26c38d1631747ddc</t>
+          <t>R00273.main.2059ae72be92bd0e</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -38547,20 +38587,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>26c38d1631747ddcb443b8d80d0070145f1968ff0f4b8e86dc2f69cc2bb968d8</t>
+          <t>2059ae72be92bd0e0928b31eb73f27d1f92ac15865050966ba9369eae1ac9c0c</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4532295</v>
+        <v>5372083</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://europepmc.org/api/getPdf?pmcid=PMC8044681</t>
+          <t>https://lup.lub.lu.se/luur/download?func=downloadFile&amp;recordOId=5277171&amp;fileOId=5277177</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>R07238_2021_The_influence_of_combined_low-strength_ultrasonics_and_micro-aerobic_pretreatment.pdf</t>
+          <t>R00273_2012_Management_of_hydrogen_sulfide_in_anaerobic_digestion_of_enzyme.pdf</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -38572,12 +38612,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R04700</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R08646.main.7df5523334e7d1bb</t>
+          <t>R04700.main.40ac0de29f75851c</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -38587,20 +38627,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7df5523334e7d1bb513d2a3deb5b018c0c9b2a3ea9e49b7ff8f09a1fe853cd96</t>
+          <t>40ac0de29f75851cab1651e1e339d03329bb7ce0141519329487f0559ebd8297</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3009960</v>
+        <v>2892628</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://europepmc.org/api/getPdf?pmcid=PMC10559078</t>
+          <t>https://repository.tudelft.nl/file/File_d8b73973-6e26-4f66-9162-3212f6b93431</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>R08646_2023_Approaches_to_mitigation_of_hydrogen_sulfide_during_anaerobic_digestion.pdf</t>
+          <t>R04700_2019_Effect_of_aeration_by_micro_-_bubbles_on_methane.pdf</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -38612,12 +38652,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R10894</t>
+          <t>R09568</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R10894.main.f9caf3b730e23f0d</t>
+          <t>R09568.main.393322098ea47587</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -38627,20 +38667,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>f9caf3b730e23f0d9d31d71069935c39e162415bbdac53ee97821305a81be9d2</t>
+          <t>393322098ea4758738b0e338c3e0019bd8618611d25a41cf3535d9542a6c8d16</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2030435</v>
+        <v>1433947</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://europepmc.org/api/getPdf?pmcid=PMC11499478</t>
+          <t>https://repository.tudelft.nl/file/File_b3a1ee42-17d3-4f7d-82dc-616c91a5a6bf</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>R10894_2024_The_effects_of_different_pretreatment_technologies_on_microbial_community.pdf</t>
+          <t>R09568_2023_The_fate_of_sulfamethoxazole_and_trimethoprim_in_a_micro-aerated.pdf</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -38652,12 +38692,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R06737</t>
+          <t>R10290</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R06737.main.32eabc0a46b31862</t>
+          <t>R10290.main.0a63bc6c89e8dff8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -38667,20 +38707,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>32eabc0a46b31862fa95a7bcf29fc4e5b154b7ec51c11cd1d4f798bbad95b59a</t>
+          <t>0a63bc6c89e8dff87ff1b364322ce6738e4fc87f505478ef522e7c73b7db342f</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4126947</v>
+        <v>530753</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://ira.lib.polyu.edu.hk/bitstream/10397/97386/1/Zhuang_Genomic_Driven_Factors.pdf</t>
+          <t>https://office.nbc-journal.org/index.php/NBC/article/download/2100/955</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>R06737_2021_Genomic_driven_factors_enhance_biocatalyst-related_cellulolysis_potential_in_anaerobic.pdf</t>
+          <t>R10290_2024_Gas_nanobubble_technology_in_wastewater_treatment_and_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -38692,12 +38732,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R04119</t>
+          <t>R10724</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R04119.main.c9b1902447e38978</t>
+          <t>R10724.main.cfdc1bcb235acdd7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -38707,20 +38747,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>c9b1902447e38978d2f6f25327940f80e825baee1ebabba8bd8a860ed1fa254c</t>
+          <t>cfdc1bcb235acdd703e58447b30b31cb8c4e8d53d1c86999ee8ecdafbba1e8aa</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1726821</v>
+        <v>2366242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://europepmc.org/api/getPdf?pmcid=PMC6197294</t>
+          <t>https://www.ecoeet.com/pdf-181210-105068?filename=Protection-of-the-Purific.pdf</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>R04119_2018_Microbial_pretreatment_of_lignocellulosic_biomass_for_enhanced_biomethanation_and.pdf</t>
+          <t>R10724_2024_Protection_of_the_Purification_Station_Thermal_Engines_Against_the.pdf</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -38732,12 +38772,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R00273</t>
+          <t>R11658</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R00273.main.2059ae72be92bd0e</t>
+          <t>R11658.main.83a514a4b04c73a0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -38747,20 +38787,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2059ae72be92bd0e0928b31eb73f27d1f92ac15865050966ba9369eae1ac9c0c</t>
+          <t>83a514a4b04c73a09129c21d623d57eb798a3af7c20dc842d47308f889d7695f</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5372083</v>
+        <v>458052</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://lup.lub.lu.se/luur/download?func=downloadFile&amp;recordOId=5277171&amp;fileOId=5277177</t>
+          <t>https://bsuj.bsu.edu.az/readpdf.php?file=236e3d6763a43f726c9814e7b5de8bc1.pdf</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>R00273_2012_Management_of_hydrogen_sulfide_in_anaerobic_digestion_of_enzyme.pdf</t>
+          <t>R11658_2025_IMPACT_OF_MICRO-AERATION_ON_FUNGAL_COMMUNITY_FROM_ANAEROBIC_DIGESTION.pdf</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -38772,12 +38812,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R04700</t>
+          <t>R12483</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R04700.main.40ac0de29f75851c</t>
+          <t>R12483.main.b51428ca89e5bf95</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -38787,20 +38827,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>40ac0de29f75851cab1651e1e339d03329bb7ce0141519329487f0559ebd8297</t>
+          <t>b51428ca89e5bf95c17225fe2e0a08a920379629281ab76f33337561553f3b0f</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2892628</v>
+        <v>1807518</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://repository.tudelft.nl/file/File_d8b73973-6e26-4f66-9162-3212f6b93431</t>
+          <t>https://li01.tci-thaijo.org/index.php/TSAEJ/article/download/269146/181297</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>R04700_2019_Effect_of_aeration_by_micro_-_bubbles_on_methane.pdf</t>
+          <t>R12483_2025_การปรบสภาพชวมวลลกโนเซลลโลสดวยวสดเพาะเหดเหลอทง_แนวทางการเพมมล.pdf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -38812,12 +38852,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R09568</t>
+          <t>R13819</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R09568.main.393322098ea47587</t>
+          <t>R13819.main.431f5e76781d3cef</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -38827,20 +38867,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>393322098ea4758738b0e338c3e0019bd8618611d25a41cf3535d9542a6c8d16</t>
+          <t>431f5e76781d3cef39588c258c5589b1c9cf01db486c503ba29ab166bc73f14a</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1433947</v>
+        <v>2172752</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://repository.tudelft.nl/file/File_b3a1ee42-17d3-4f7d-82dc-616c91a5a6bf</t>
+          <t>https://epublications.marquette.edu/cgi/viewcontent.cgi?article=1131&amp;context=civengin_fac</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>R09568_2023_The_fate_of_sulfamethoxazole_and_trimethoprim_in_a_micro-aerated.pdf</t>
+          <t>R13819_2015_Bioaugmentation_of_overloaded_anaerobic_digesters_restores_function_and_archaeal.pdf</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -38852,12 +38892,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R10290</t>
+          <t>R13833</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R10290.main.0a63bc6c89e8dff8</t>
+          <t>R13833.main.1a4a4d5f8fd45de9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -38867,20 +38907,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0a63bc6c89e8dff87ff1b364322ce6738e4fc87f505478ef522e7c73b7db342f</t>
+          <t>1a4a4d5f8fd45de924c78a7be11e1c032c630bd9341431d1d49135c8351cdaf7</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>530753</v>
+        <v>1463714</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://office.nbc-journal.org/index.php/NBC/article/download/2100/955</t>
+          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/234ac4ff-f996-498f-8853-72ba22cb7700/content</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>R10290_2024_Gas_nanobubble_technology_in_wastewater_treatment_and_anaerobic_digestion.pdf</t>
+          <t>R13833_2018_Insight_into_the_Role_of_Facultative_Bacteria_Stimulated_by.pdf</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -38892,12 +38932,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R10724</t>
+          <t>R13861</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R10724.main.cfdc1bcb235acdd7</t>
+          <t>R13861.main.ba6f44b77d79c4a0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -38907,20 +38947,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>cfdc1bcb235acdd703e58447b30b31cb8c4e8d53d1c86999ee8ecdafbba1e8aa</t>
+          <t>ba6f44b77d79c4a07ba08602860bcf1bdbb36cb47b4527fa9d1f087825e394d8</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2366242</v>
+        <v>433474</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.ecoeet.com/pdf-181210-105068?filename=Protection-of-the-Purific.pdf</t>
+          <t>https://www.scielo.br/j/esa/a/BD6Bc5rMVrTsbkK7CZz6yVd/?format=pdf&amp;lang=en&amp;ilang=pt_BR</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>R10724_2024_Protection_of_the_Purification_Station_Thermal_Engines_Against_the.pdf</t>
+          <t>R13861_2019_Enhanced_removal_of_emerging_micropollutants_by_applying_microaeration_to.pdf</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -38932,12 +38972,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R11658</t>
+          <t>R13871</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R11658.main.83a514a4b04c73a0</t>
+          <t>R13871.main.aeab3126b6e68775</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -38947,20 +38987,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>83a514a4b04c73a09129c21d623d57eb798a3af7c20dc842d47308f889d7695f</t>
+          <t>aeab3126b6e68775b9b316714633bd97c1f184cf9e308d75b404bca6b33be19f</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>458052</v>
+        <v>7983514</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://bsuj.bsu.edu.az/readpdf.php?file=236e3d6763a43f726c9814e7b5de8bc1.pdf</t>
+          <t>https://etheses.whiterose.ac.uk/id/eprint/4094/6/Mahmood_Khazzal_Hummadi_Al-Mashhadani._Reg._No._080243946_%28PhD_thesis%29_2013.pdf</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>R11658_2025_IMPACT_OF_MICRO-AERATION_ON_FUNGAL_COMMUNITY_FROM_ANAEROBIC_DIGESTION.pdf</t>
+          <t>R13871_2013_Application_of_Microbubbles_Generated_by_Fluidic_Oscillation_in_the.pdf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -38972,12 +39012,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R12483</t>
+          <t>R13877</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R12483.main.b51428ca89e5bf95</t>
+          <t>R13877.main.04a76adc76fa9472</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -38987,20 +39027,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>b51428ca89e5bf95c17225fe2e0a08a920379629281ab76f33337561553f3b0f</t>
+          <t>04a76adc76fa947250861c95c93759c590dd3e02d7f80dc23ce0abedccb74510</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1807518</v>
+        <v>522402</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://li01.tci-thaijo.org/index.php/TSAEJ/article/download/269146/181297</t>
+          <t>https://escholarship.org/content/qt5572k7rw/qt5572k7rw.pdf</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>R12483_2025_การปรบสภาพชวมวลลกโนเซลลโลสดวยวสดเพาะเหดเหลอทง_แนวทางการเพมมล.pdf</t>
+          <t>R13877_2018_Microbial_community_response_and_SDS-PAGE_reveal_possible_mechanism_of.pdf</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -39012,12 +39052,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R13819</t>
+          <t>R13862</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R13819.main.431f5e76781d3cef</t>
+          <t>R13862.main.64e03a9beb5813a0</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -39027,20 +39067,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>431f5e76781d3cef39588c258c5589b1c9cf01db486c503ba29ab166bc73f14a</t>
+          <t>64e03a9beb5813a0ce6d94272350217f12dac94293420969e3d2d9d7975e96e3</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2172752</v>
+        <v>833659</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://epublications.marquette.edu/cgi/viewcontent.cgi?article=1131&amp;context=civengin_fac</t>
+          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/eb850f96-0570-4e0d-be55-73fcee5f1364/content</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>R13819_2015_Bioaugmentation_of_overloaded_anaerobic_digesters_restores_function_and_archaeal.pdf</t>
+          <t>R13862_2020_Multiple_and_flexible_roles_of_facultative_anaerobic_bacteria_in.pdf</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -39052,12 +39092,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R13833</t>
+          <t>R13900</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R13833.main.1a4a4d5f8fd45de9</t>
+          <t>R13900.main.b2ba7df8c04ab66c</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -39067,20 +39107,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1a4a4d5f8fd45de924c78a7be11e1c032c630bd9341431d1d49135c8351cdaf7</t>
+          <t>b2ba7df8c04ab66c0e548f778e19c5764802c0da8408a3b8499547b3f6ef51b3</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1463714</v>
+        <v>299244</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/234ac4ff-f996-498f-8853-72ba22cb7700/content</t>
+          <t>https://www.research.unipd.it/bitstream/11577/3261852/1/Front.%20Environ.%20Sci.%20Eng%20Dongbei%202018.pdf</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>R13833_2018_Insight_into_the_Role_of_Facultative_Bacteria_Stimulated_by.pdf</t>
+          <t>R13900_2018_Effectiveness_of_aerobic_pretreatment_of_municipal_solid_waste_for.pdf</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -39092,12 +39132,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>R13861</t>
+          <t>R13903</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R13861.main.ba6f44b77d79c4a0</t>
+          <t>R13903.main.2cd9e7b409250e7b</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -39107,20 +39147,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ba6f44b77d79c4a07ba08602860bcf1bdbb36cb47b4527fa9d1f087825e394d8</t>
+          <t>2cd9e7b409250e7b104f489e139f57d4daa40d97133c6c57c937184c3ec73b71</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>433474</v>
+        <v>1107675</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.scielo.br/j/esa/a/BD6Bc5rMVrTsbkK7CZz6yVd/?format=pdf&amp;lang=en&amp;ilang=pt_BR</t>
+          <t>https://ijabe.org/index.php/ijabe/article/download/7975/pdf</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>R13861_2019_Enhanced_removal_of_emerging_micropollutants_by_applying_microaeration_to.pdf</t>
+          <t>R13903_2023_Effect_of_vacuum_negative_pressure_aerobic_hydrolysis_pretreatment_on.pdf</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -39132,12 +39172,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>R13871</t>
+          <t>R13931</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R13871.main.aeab3126b6e68775</t>
+          <t>R13931.main.6e898a403edac7b3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -39147,20 +39187,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>aeab3126b6e68775b9b316714633bd97c1f184cf9e308d75b404bca6b33be19f</t>
+          <t>6e898a403edac7b3ae15ad88cf75788898cd84ea377b2572f7bab40d9c126f8c</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>7983514</v>
+        <v>1324593</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://etheses.whiterose.ac.uk/id/eprint/4094/6/Mahmood_Khazzal_Hummadi_Al-Mashhadani._Reg._No._080243946_%28PhD_thesis%29_2013.pdf</t>
+          <t>https://www.eeer.org/upload/eer-2020-470.pdf</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>R13871_2013_Application_of_Microbubbles_Generated_by_Fluidic_Oscillation_in_the.pdf</t>
+          <t>R13931_2020_Biogas_recovery_from_fresh_landfill_leachates_by_using_a.pdf</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -39172,12 +39212,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>R13877</t>
+          <t>R13945</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>R13877.main.04a76adc76fa9472</t>
+          <t>R13945.main.67309ea094d2f9bb</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -39187,20 +39227,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>04a76adc76fa947250861c95c93759c590dd3e02d7f80dc23ce0abedccb74510</t>
+          <t>67309ea094d2f9bb088d605746ede869866819a733f53c44dc2d44af934e6be9</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>522402</v>
+        <v>2230958</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://escholarship.org/content/qt5572k7rw/qt5572k7rw.pdf</t>
+          <t>https://epublications.marquette.edu/cgi/viewcontent.cgi?article=1459&amp;context=theses_open</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>R13877_2018_Microbial_community_response_and_SDS-PAGE_reveal_possible_mechanism_of.pdf</t>
+          <t>R13945_2018_Effect_of_Low_Aeration_and_Heat_Drying_on_Anaerobic.pdf</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -39212,12 +39252,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>R13862</t>
+          <t>R13950</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R13862.main.64e03a9beb5813a0</t>
+          <t>R13950.main.2bf9b46c448685b9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -39227,20 +39267,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>64e03a9beb5813a0ce6d94272350217f12dac94293420969e3d2d9d7975e96e3</t>
+          <t>2bf9b46c448685b9e66f4064245c5840dc28ded79ee4d613ddd9efeb4805812e</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>833659</v>
+        <v>3508852</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/eb850f96-0570-4e0d-be55-73fcee5f1364/content</t>
+          <t>https://www.research.unipd.it/bitstream/11577/3425227/1/Thesis_Razieh_Rafieenia.pdf</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>R13862_2020_Multiple_and_flexible_roles_of_facultative_anaerobic_bacteria_in.pdf</t>
+          <t>R13950_2019_Enhancement_of_hydrogen_and_methane_production_through_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -39252,12 +39292,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>R13900</t>
+          <t>R13944</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R13900.main.b2ba7df8c04ab66c</t>
+          <t>R13944.main.7e22fbfd39ddfed0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -39267,20 +39307,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>b2ba7df8c04ab66c0e548f778e19c5764802c0da8408a3b8499547b3f6ef51b3</t>
+          <t>7e22fbfd39ddfed09b9235fea5c6914cfbe5987d12564fc9cb799bf412ae6779</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>299244</v>
+        <v>12042699</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.research.unipd.it/bitstream/11577/3261852/1/Front.%20Environ.%20Sci.%20Eng%20Dongbei%202018.pdf</t>
+          <t>https://scholarspace.manoa.hawaii.edu/server/api/core/bitstreams/60c88164-f37f-492a-97bc-e34a2f2b1698/content</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>R13900_2018_Effectiveness_of_aerobic_pretreatment_of_municipal_solid_waste_for.pdf</t>
+          <t>R13944_2018_Oxidation-Reduction_Potential-Based_Micro-Aeration_Control_System_for_Anaerobic_Digestion.pdf</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -39292,12 +39332,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>R13903</t>
+          <t>R13967</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R13903.main.2cd9e7b409250e7b</t>
+          <t>R13967.main.5e9f84dbaf01dd19</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -39307,20 +39347,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2cd9e7b409250e7b104f489e139f57d4daa40d97133c6c57c937184c3ec73b71</t>
+          <t>5e9f84dbaf01dd19674f09cbce96f338f32fe21a37a883bb9658e49af7072194</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1107675</v>
+        <v>160020</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://ijabe.org/index.php/ijabe/article/download/7975/pdf</t>
+          <t>https://www.aceee.org/wp-content/uploads/proceedings-1980-2020/2012/0193-000342.pdf</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>R13903_2023_Effect_of_vacuum_negative_pressure_aerobic_hydrolysis_pretreatment_on.pdf</t>
+          <t>R13967_2012_An_Improved_Biomass_Waste_Anaerobic_Degradation_Technology_for_Producing.pdf</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -39332,12 +39372,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R13931</t>
+          <t>R13972</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R13931.main.6e898a403edac7b3</t>
+          <t>R13972.main.ff4ee9377a7e227c</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -39347,20 +39387,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6e898a403edac7b3ae15ad88cf75788898cd84ea377b2572f7bab40d9c126f8c</t>
+          <t>ff4ee9377a7e227c48a5bc64d301bfc1a989ee0e709c322eb90f254819d7b391</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1324593</v>
+        <v>1192569</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.eeer.org/upload/eer-2020-470.pdf</t>
+          <t>https://www.osti.gov/servlets/purl/2386939</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>R13931_2020_Biogas_recovery_from_fresh_landfill_leachates_by_using_a.pdf</t>
+          <t>R13972_2022_Enhancing_methane_production_of_anaerobic_digested_sewage_sludge_by.pdf</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -39372,12 +39412,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>R13945</t>
+          <t>R13957</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>R13945.main.67309ea094d2f9bb</t>
+          <t>R13957.main.3db804dcdefb7608</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -39387,20 +39427,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>67309ea094d2f9bb088d605746ede869866819a733f53c44dc2d44af934e6be9</t>
+          <t>3db804dcdefb7608eefc6bf166b0713cbbec8ac027b1c01831aec97b54253b82</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2230958</v>
+        <v>7806265</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://epublications.marquette.edu/cgi/viewcontent.cgi?article=1459&amp;context=theses_open</t>
+          <t>https://backoffice.biblio.ugent.be/download/8530499/8530500</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>R13945_2018_Effect_of_Low_Aeration_and_Heat_Drying_on_Anaerobic.pdf</t>
+          <t>R13957_2017_Microaeration_for_biogas_desulfurization_experimental_and_simulation_study_of.pdf</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -39412,12 +39452,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>R13950</t>
+          <t>R04510</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>R13950.main.2bf9b46c448685b9</t>
+          <t>R04510.main.c4520ca79e301bb6</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -39427,20 +39467,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2bf9b46c448685b9e66f4064245c5840dc28ded79ee4d613ddd9efeb4805812e</t>
+          <t>c4520ca79e301bb606a8ab1fef6cf4af9064c0d85f3c390a4cf31a877238e1c6</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3508852</v>
+        <v>492630</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.research.unipd.it/bitstream/11577/3425227/1/Thesis_Razieh_Rafieenia.pdf</t>
+          <t>https://digital.csic.es/bitstream/10261/196040/5/PostP_2019_JESH_V54_Iss10.pdf</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>R13950_2019_Enhancement_of_hydrogen_and_methane_production_through_anaerobic_digestion.pdf</t>
+          <t>R04510_2019_Anaerobic_digestion_of_wastewater_rich_in_sulfate_and_sulfide_effects_of_metallic_waste_addition_and.pdf</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -39452,12 +39492,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>R13944</t>
+          <t>R13889</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R13944.main.7e22fbfd39ddfed0</t>
+          <t>R13889.main.8db0dcdf434e876e</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -39467,20 +39507,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>7e22fbfd39ddfed09b9235fea5c6914cfbe5987d12564fc9cb799bf412ae6779</t>
+          <t>8db0dcdf434e876e7cbff3cf342105807bdd41a900f74c0028cb14a6c6e56779</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>12042699</v>
+        <v>514378</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://scholarspace.manoa.hawaii.edu/server/api/core/bitstreams/60c88164-f37f-492a-97bc-e34a2f2b1698/content</t>
+          <t>https://digital.csic.es/bitstream/10261/178890/1/PotP_2018_RE_V123_P541.pdf</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>R13944_2018_Oxidation-Reduction_Potential-Based_Micro-Aeration_Control_System_for_Anaerobic_Digestion.pdf</t>
+          <t>R13889_2018_Increase_in_biogas_production_in_anaerobic_sludge_digestion_by_combining_aerobic_hydrolysis_and_addi.pdf</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -39492,12 +39532,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>R13967</t>
+          <t>R02719</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>R13967.main.5e9f84dbaf01dd19</t>
+          <t>R02719.main.4bf5e309b2ef3431</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -39507,20 +39547,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5e9f84dbaf01dd19674f09cbce96f338f32fe21a37a883bb9658e49af7072194</t>
+          <t>4bf5e309b2ef343162a9588383a7ae0254118c33cdf2e96bec1a05459fae1523</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>160020</v>
+        <v>583591</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.aceee.org/wp-content/uploads/proceedings-1980-2020/2012/0193-000342.pdf</t>
+          <t>https://digital.csic.es/bitstream/10261/137944/1/Post_2016_JEnvSciHealth_A_BorjaR.pdf</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>R13967_2012_An_Improved_Biomass_Waste_Anaerobic_Degradation_Technology_for_Producing.pdf</t>
+          <t>R02719_2016_Performance_evaluation_of_micro_aerobic_hydrolysis_of_mixed_sludge_Optimum_aeration_and_effect_on_it.pdf</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -39532,12 +39572,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>R13972</t>
+          <t>R02282</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R13972.main.ff4ee9377a7e227c</t>
+          <t>R02282.main.e709439b748e7938</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -39547,20 +39587,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ff4ee9377a7e227c48a5bc64d301bfc1a989ee0e709c322eb90f254819d7b391</t>
+          <t>e709439b748e793826102646c009aa10e1e9ac30627ac301fac7dd42276a2047</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1192569</v>
+        <v>1067465</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.osti.gov/servlets/purl/2386939</t>
+          <t>https://digital.csic.es/bitstream/10261/130093/1/Postprint_2016_EnviromRev_V24_P84.pdf</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>R13972_2022_Enhancing_methane_production_of_anaerobic_digested_sewage_sludge_by.pdf</t>
+          <t>R02282_2016_Advances_in_the_biological_removal_of_sulphides_from_aqueous_phase_in_anaerobic_processes_A_review.pdf</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -39572,12 +39612,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>R13957</t>
+          <t>R13905</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>R13957.main.3db804dcdefb7608</t>
+          <t>R13905.main.c75b5084c2545bd9</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -39587,20 +39627,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3db804dcdefb7608eefc6bf166b0713cbbec8ac027b1c01831aec97b54253b82</t>
+          <t>c75b5084c2545bd939d3b1928be41fe0072c7302f26c25ba023c4bb6fc8a6970</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>7806265</v>
+        <v>2159708</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://backoffice.biblio.ugent.be/download/8530499/8530500</t>
+          <t>https://ddd.uab.cat/pub/artpub/2017/196242/wasbioval_a2017m7v8n5p1793.pdf</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>R13957_2017_Microaeration_for_biogas_desulfurization_experimental_and_simulation_study_of.pdf</t>
+          <t>R13905_2017_The_Effect_of_a_Short_Term_Aerobic_Pretreatment_Step_on_the_Anaerobic_Co_digestion_of_the_Organic_Fr.pdf</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -39612,12 +39652,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>R04510</t>
+          <t>R13932</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>R04510.main.c4520ca79e301bb6</t>
+          <t>R13932.main.c15f49a3d617e1be</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -39627,20 +39667,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>c4520ca79e301bb606a8ab1fef6cf4af9064c0d85f3c390a4cf31a877238e1c6</t>
+          <t>c15f49a3d617e1be5e21578ebda1c2d855f8d460c1d66f446ad0d02856a40a13</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>492630</v>
+        <v>1258157</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/196040/5/PostP_2019_JESH_V54_Iss10.pdf</t>
+          <t>https://hal.inrae.fr/hal-02620984/document</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>R04510_2019_Anaerobic_digestion_of_wastewater_rich_in_sulfate_and_sulfide_effects_of_metallic_waste_addition_and.pdf</t>
+          <t>R13932_2018_Comparison_of_pre_and_inter_stage_aerobic_treatment_of_wastewater_sludge_Effects_on_biogas_productio.pdf</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -39652,12 +39692,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>R13889</t>
+          <t>R13956</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>R13889.main.8db0dcdf434e876e</t>
+          <t>R13956.main.fedaffcdf5be81e2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -39667,20 +39707,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8db0dcdf434e876e7cbff3cf342105807bdd41a900f74c0028cb14a6c6e56779</t>
+          <t>fedaffcdf5be81e2070b7edb0531c332e423578228eeb8c55a6afc4ba8fe1e18</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>514378</v>
+        <v>421626</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/178890/1/PotP_2018_RE_V123_P541.pdf</t>
+          <t>https://www.banglajol.info/index.php/BJSIR/article/download/25579/17152</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>R13889_2018_Increase_in_biogas_production_in_anaerobic_sludge_digestion_by_combining_aerobic_hydrolysis_and_addi.pdf</t>
+          <t>R13956_2015_Anaerobic_digestion_of_mixed_dried_fallen_leaves_by_mixing_with_cow_dung.pdf</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -39692,12 +39732,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>R02719</t>
+          <t>R13955</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>R02719.main.4bf5e309b2ef3431</t>
+          <t>R13955.main.7549e1025985363e</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -39707,20 +39747,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4bf5e309b2ef343162a9588383a7ae0254118c33cdf2e96bec1a05459fae1523</t>
+          <t>7549e1025985363e89542bbc1af6eaaa1150bbd62ea43bdd03d2c7b764631f9d</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>583591</v>
+        <v>14662438</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/137944/1/Post_2016_JEnvSciHealth_A_BorjaR.pdf</t>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>R02719_2016_Performance_evaluation_of_micro_aerobic_hydrolysis_of_mixed_sludge_Optimum_aeration_and_effect_on_it.pdf</t>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -39732,35 +39772,35 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>R02282</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>R02282.main.e709439b748e7938</t>
+          <t>R07238.supplementary.0b7925ad1ed9c793</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>e709439b748e793826102646c009aa10e1e9ac30627ac301fac7dd42276a2047</t>
+          <t>0b7925ad1ed9c7939a79ba6294d17abc4b23fca77e52ec50df5463d050940d1e</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1067465</v>
+        <v>49526</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/130093/1/Postprint_2016_EnviromRev_V24_P84.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>R02282_2016_Advances_in_the_biological_removal_of_sulphides_from_aqueous_phase_in_anaerobic_processes_A_review.pdf</t>
+          <t>mmc1.docx</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -39772,35 +39812,35 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>R13905</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>R13905.main.c75b5084c2545bd9</t>
+          <t>R07238.supplementary.f346f9bdcc964013</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>c75b5084c2545bd939d3b1928be41fe0072c7302f26c25ba023c4bb6fc8a6970</t>
+          <t>f346f9bdcc964013ecb7c4282d6b30f1ab334e035d98adcc653de1447fbe9a9a</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2159708</v>
+        <v>14286928</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://ddd.uab.cat/pub/artpub/2017/196242/wasbioval_a2017m7v8n5p1793.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>R13905_2017_The_Effect_of_a_Short_Term_Aerobic_Pretreatment_Step_on_the_Anaerobic_Co_digestion_of_the_Organic_Fr.pdf</t>
+          <t>mmc2.zip</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -39812,35 +39852,35 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>R13932</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>R13932.main.c15f49a3d617e1be</t>
+          <t>R07238.derived.49b84e369d4bb31b</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>c15f49a3d617e1be5e21578ebda1c2d855f8d460c1d66f446ad0d02856a40a13</t>
+          <t>49b84e369d4bb31b4ebdcd25265be3174105c3433e6fbb865f34a445775516a1</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1258157</v>
+        <v>34855493</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://hal.inrae.fr/hal-02620984/document</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>R13932_2018_Comparison_of_pre_and_inter_stage_aerobic_treatment_of_wastewater_sludge_Effects_on_biogas_productio.pdf</t>
+          <t>g a.skp</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -39852,35 +39892,35 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>R13956</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>R13956.main.fedaffcdf5be81e2</t>
+          <t>R08646.supplementary.cfda7e29b12b9784</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>fedaffcdf5be81e2070b7edb0531c332e423578228eeb8c55a6afc4ba8fe1e18</t>
+          <t>cfda7e29b12b97846343963f9f3b64e784bc79644fb1ee1ca31170be78d75327</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>421626</v>
+        <v>42279</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.banglajol.info/index.php/BJSIR/article/download/25579/17152</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>R13956_2015_Anaerobic_digestion_of_mixed_dried_fallen_leaves_by_mixing_with_cow_dung.pdf</t>
+          <t>mmc1.docx</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -39892,35 +39932,35 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>R13955</t>
+          <t>R03161</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>R13955.main.7549e1025985363e</t>
+          <t>R03161.evidence_xml.466f3a1e78e8b0f1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>7549e1025985363e89542bbc1af6eaaa1150bbd62ea43bdd03d2c7b764631f9d</t>
+          <t>466f3a1e78e8b0f148b1f28f97b61f7134c61488c837c5c5a26ef7316cebc1e9</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>14662438</v>
+        <v>59018</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/fullTextXML</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
+          <t>PMC5627928_fullText.xml</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -39932,35 +39972,35 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R03161</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>R07238.supplementary.0b7925ad1ed9c793</t>
+          <t>R03161.transport_archive.0ef4d4796c84feff</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0b7925ad1ed9c7939a79ba6294d17abc4b23fca77e52ec50df5463d050940d1e</t>
+          <t>0ef4d4796c84fefff7b8450bc56400f8c59f4bdcf074fc51404edff5e4e217f6</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>49526</v>
+        <v>726772</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/supplementaryFiles</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>mmc1.docx</t>
+          <t>PMC5627928_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -39972,35 +40012,35 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R04092</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>R07238.supplementary.f346f9bdcc964013</t>
+          <t>R04092.evidence_xml.0fb90085e30680fa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>f346f9bdcc964013ecb7c4282d6b30f1ab334e035d98adcc653de1447fbe9a9a</t>
+          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>14286928</v>
+        <v>77995</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>mmc2.zip</t>
+          <t>PMC6288047_fullText.xml</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -40012,35 +40052,35 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R05839</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>R07238.derived.49b84e369d4bb31b</t>
+          <t>R05839.evidence_xml.18ffd43dee955086</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>49b84e369d4bb31b4ebdcd25265be3174105c3433e6fbb865f34a445775516a1</t>
+          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>34855493</v>
+        <v>75205</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>g a.skp</t>
+          <t>PMC7566014_fullText.xml</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -40052,35 +40092,35 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R08877</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>R08646.supplementary.cfda7e29b12b9784</t>
+          <t>R08877.evidence_xml.e8712e4198baab4c</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>cfda7e29b12b97846343963f9f3b64e784bc79644fb1ee1ca31170be78d75327</t>
+          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>42279</v>
+        <v>111864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>mmc1.docx</t>
+          <t>PMC10714394_fullText.xml</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -40092,35 +40132,35 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>R03161</t>
+          <t>R08877</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>R03161.evidence_xml.466f3a1e78e8b0f1</t>
+          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>466f3a1e78e8b0f148b1f28f97b61f7134c61488c837c5c5a26ef7316cebc1e9</t>
+          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>59018</v>
+        <v>704921</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>PMC5627928_fullText.xml</t>
+          <t>PMC10714394_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -40132,35 +40172,35 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>R03161</t>
+          <t>R09236</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>R03161.transport_archive.0ef4d4796c84feff</t>
+          <t>R09236.evidence_xml.72064fe9276d8309</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0ef4d4796c84fefff7b8450bc56400f8c59f4bdcf074fc51404edff5e4e217f6</t>
+          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>726772</v>
+        <v>193052</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>PMC5627928_supplementaryFiles.zip</t>
+          <t>PMC10535533_fullText.xml</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -40172,35 +40212,35 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>R04092</t>
+          <t>R09236</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>R04092.evidence_xml.0fb90085e30680fa</t>
+          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
+          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>77995</v>
+        <v>483405</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>PMC6288047_fullText.xml</t>
+          <t>PMC10535533_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -40212,12 +40252,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>R05839</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>R05839.evidence_xml.18ffd43dee955086</t>
+          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -40227,20 +40267,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
+          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>75205</v>
+        <v>118002</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>PMC7566014_fullText.xml</t>
+          <t>PMC10837232_fullText.xml</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -40252,35 +40292,35 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>R08877.evidence_xml.e8712e4198baab4c</t>
+          <t>R10086.transport_archive.4d9eddf454b786ed</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
+          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>111864</v>
+        <v>641038</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>PMC10714394_fullText.xml</t>
+          <t>PMC10837232_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -40292,35 +40332,35 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
+          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
+          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>704921</v>
+        <v>173586</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>PMC10714394_supplementaryFiles.zip</t>
+          <t>PMC12937426_fullText.xml</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -40332,35 +40372,35 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>R09236.evidence_xml.72064fe9276d8309</t>
+          <t>R12985.transport_archive.418d45f1ca296020</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
+          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>193052</v>
+        <v>672244</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>PMC10535533_fullText.xml</t>
+          <t>PMC12937426_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -40372,35 +40412,35 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R05542</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
+          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
+          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>483405</v>
+        <v>100215</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>PMC10535533_supplementaryFiles.zip</t>
+          <t>PMC9056904_fullText.xml</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -40412,12 +40452,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
+          <t>R06325.evidence_xml.645deb707d3790b5</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -40427,20 +40467,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
+          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>118002</v>
+        <v>160509</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>PMC10837232_fullText.xml</t>
+          <t>PMC8290346_fullText.xml</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -40452,12 +40492,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>R10086.transport_archive.4d9eddf454b786ed</t>
+          <t>R06325.transport_archive.6eb4ef126661714a</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -40467,20 +40507,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
+          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>641038</v>
+        <v>1730580</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>PMC10837232_supplementaryFiles.zip</t>
+          <t>PMC8290346_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -40492,12 +40532,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
+          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -40507,20 +40547,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
+          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>173586</v>
+        <v>151458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>PMC12937426_fullText.xml</t>
+          <t>PMC8044681_fullText.xml</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -40532,12 +40572,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>R12985.transport_archive.418d45f1ca296020</t>
+          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -40547,20 +40587,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
+          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>672244</v>
+        <v>14596266</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>PMC12937426_supplementaryFiles.zip</t>
+          <t>PMC8044681_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -40572,12 +40612,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>R05542</t>
+          <t>R03477</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
+          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -40587,20 +40627,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
+          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100215</v>
+        <v>121650</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>PMC9056904_fullText.xml</t>
+          <t>PMC5371168_fullText.xml</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -40612,12 +40652,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>R06325.evidence_xml.645deb707d3790b5</t>
+          <t>R08646.evidence_xml.c7b723e8020f6582</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -40627,20 +40667,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
+          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>160509</v>
+        <v>304277</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>PMC8290346_fullText.xml</t>
+          <t>PMC10559078_fullText.xml</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -40652,12 +40692,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>R06325.transport_archive.6eb4ef126661714a</t>
+          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -40667,20 +40707,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
+          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1730580</v>
+        <v>1539133</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>PMC8290346_supplementaryFiles.zip</t>
+          <t>PMC10559078_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -40692,12 +40732,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R09804</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
+          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -40707,20 +40747,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
+          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>151458</v>
+        <v>211630</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>PMC8044681_fullText.xml</t>
+          <t>PMC11076452_fullText.xml</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -40732,35 +40772,35 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R11503</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
+          <t>R11503.evidence_xml.4002d57be59c215c</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
+          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>14596266</v>
+        <v>258637</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>PMC8044681_supplementaryFiles.zip</t>
+          <t>PMC12561102_fullText.xml</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -40772,12 +40812,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>R03477</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
+          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -40787,20 +40827,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
+          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>121650</v>
+        <v>256247</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>PMC5371168_fullText.xml</t>
+          <t>PMC12125087_fullText.xml</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -40812,35 +40852,35 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>R08646.evidence_xml.c7b723e8020f6582</t>
+          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
+          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>304277</v>
+        <v>521862</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>PMC10559078_fullText.xml</t>
+          <t>PMC12125087_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -40852,35 +40892,35 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
+          <t>R05213.evidence_xml.17894ab410001846</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
+          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1539133</v>
+        <v>130954</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>PMC10559078_supplementaryFiles.zip</t>
+          <t>PMC6858683_fullText.xml</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -40892,35 +40932,35 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
+          <t>R05213.transport_archive.c61c88cf9fd489be</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
+          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>211630</v>
+        <v>1960371</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>PMC11076452_fullText.xml</t>
+          <t>PMC6858683_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -40932,12 +40972,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>R11503</t>
+          <t>R09585</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>R11503.evidence_xml.4002d57be59c215c</t>
+          <t>R09585.evidence_xml.a3430f38fa1652de</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -40947,20 +40987,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
+          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>258637</v>
+        <v>100534</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>PMC12561102_fullText.xml</t>
+          <t>PMC10609292_fullText.xml</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -40972,238 +41012,38 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R11596</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
+          <t>R11596.main.0b2e2d98dffd5449</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
+          <t>0b2e2d98dffd544958b06cc2229d310e4b7d529bd3914c47f20d6a66789a28be</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>256247</v>
+        <v>1659399</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
+          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/7262c516-6b14-4001-a173-517d1187c8d9/content</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>PMC12125087_fullText.xml</t>
+          <t>R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>R11844</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>transport_archive</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>521862</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>PMC12125087_supplementaryFiles.zip</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>R05213</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>R05213.evidence_xml.17894ab410001846</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>evidence_xml</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>130954</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>PMC6858683_fullText.xml</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>R05213</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>R05213.transport_archive.c61c88cf9fd489be</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>transport_archive</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>1960371</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>PMC6858683_supplementaryFiles.zip</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>R09585</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>R09585.evidence_xml.a3430f38fa1652de</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>evidence_xml</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>100534</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>PMC10609292_fullText.xml</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>R11596</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>R11596.main.0b2e2d98dffd5449</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>0b2e2d98dffd544958b06cc2229d310e4b7d529bd3914c47f20d6a66789a28be</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>1659399</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/7262c516-6b14-4001-a173-517d1187c8d9/content</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
         <is>
           <t>历史已获取，当前原件未恢复</t>
         </is>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -4277,7 +4277,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.399153+00:00</t>
+          <t>2026-10-17T08:30:22.811991+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.400099+00:00</t>
+          <t>2026-10-17T08:30:22.813153+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.400122+00:00</t>
+          <t>2026-10-17T08:30:22.813181+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.400356+00:00</t>
+          <t>2026-10-17T08:30:22.813428+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.401443+00:00</t>
+          <t>2026-10-17T08:30:22.814635+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.401921+00:00</t>
+          <t>2026-10-17T08:30:22.815153+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.408803+00:00</t>
+          <t>2026-10-17T08:30:22.820691+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.411250+00:00</t>
+          <t>2026-10-17T08:30:22.823145+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.412226+00:00</t>
+          <t>2026-10-17T08:30:22.824089+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.412619+00:00</t>
+          <t>2026-10-17T08:30:22.824676+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.413356+00:00</t>
+          <t>2026-10-17T08:30:22.825398+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.414019+00:00</t>
+          <t>2026-10-17T08:30:22.826068+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.414915+00:00</t>
+          <t>2026-10-17T08:30:22.827017+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.415144+00:00</t>
+          <t>2026-10-17T08:30:22.827279+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.415998+00:00</t>
+          <t>2026-10-17T08:30:22.828154+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.424546+00:00</t>
+          <t>2026-10-17T08:30:22.837004+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.425262+00:00</t>
+          <t>2026-10-17T08:30:22.837782+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.426486+00:00</t>
+          <t>2026-10-17T08:30:22.839002+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.429285+00:00</t>
+          <t>2026-10-17T08:30:22.841840+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.430444+00:00</t>
+          <t>2026-10-17T08:30:22.843085+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.431844+00:00</t>
+          <t>2026-10-17T08:30:22.844299+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.436022+00:00</t>
+          <t>2026-10-17T08:30:22.848756+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.438310+00:00</t>
+          <t>2026-10-17T08:30:22.851190+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.440446+00:00</t>
+          <t>2026-10-17T08:30:22.853013+00:00</t>
         </is>
       </c>
     </row>
@@ -26859,13 +26859,21 @@
           <t>papers/R13558/main/0006612a5b75_R13558_2026_Redox_mediators_and_microaeration_overcoming_linear_alkylbenzene_sulfonate_recalcitrance.pdf</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13558_2026_Redox_mediators_and_microaeration_overcoming_linear_alkylbenzene_sulfonate_recalcitrance.pdf</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R13558_2026_Redox_mediators_and_microaeration_overcoming_linear_alkylbenzene_sulfonate_recalcitrance.pdf</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13558_2026_Redox_mediators_and_microaeration_overcoming_linear_alkylbenzene_sulfonate_recalcitrance.pdf</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -26881,12 +26889,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -26923,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.440476+00:00</t>
+          <t>2026-10-17T08:30:22.853701+00:00</t>
         </is>
       </c>
     </row>
@@ -26959,13 +26967,21 @@
           <t>papers/R04889/main/860a05325037_R04889_2019_Inoculum_Selection_and_Micro-Aeration_for_Biogas_Production_in_Two-Stage.pdf</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R04889_2019_Inoculum_Selection_and_Micro-Aeration_for_Biogas_Production_in_Two-Stage.pdf</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R04889_2019_Inoculum_Selection_and_Micro-Aeration_for_Biogas_Production_in_Two-Stage.pdf</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R04889_2019_Inoculum_Selection_and_Micro-Aeration_for_Biogas_Production_in_Two-Stage.pdf</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -26981,12 +26997,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -27023,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.440483+00:00</t>
+          <t>2026-10-17T08:30:22.854077+00:00</t>
         </is>
       </c>
     </row>
@@ -27131,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.442628+00:00</t>
+          <t>2026-10-17T08:30:22.856050+00:00</t>
         </is>
       </c>
     </row>
@@ -27239,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.443878+00:00</t>
+          <t>2026-10-17T08:30:22.857269+00:00</t>
         </is>
       </c>
     </row>
@@ -27347,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.445912+00:00</t>
+          <t>2026-10-17T08:30:22.859717+00:00</t>
         </is>
       </c>
     </row>
@@ -27455,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.447862+00:00</t>
+          <t>2026-10-17T08:30:22.861830+00:00</t>
         </is>
       </c>
     </row>
@@ -27555,7 +27571,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.447879+00:00</t>
+          <t>2026-10-17T08:30:22.861861+00:00</t>
         </is>
       </c>
     </row>
@@ -27591,13 +27607,21 @@
           <t>papers/R05542/main/735560cdb276_R05542_2020_Effect_of_micro-aerobic_process_on_improvement_of_anaerobic_digestion.pdf</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R05542_2020_Effect_of_micro-aerobic_process_on_improvement_of_anaerobic_digestion.pdf</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R05542_2020_Effect_of_micro-aerobic_process_on_improvement_of_anaerobic_digestion.pdf</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R05542_2020_Effect_of_micro-aerobic_process_on_improvement_of_anaerobic_digestion.pdf</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -27613,12 +27637,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -27655,7 +27679,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.447883+00:00</t>
+          <t>2026-10-17T08:30:22.862453+00:00</t>
         </is>
       </c>
     </row>
@@ -27763,7 +27787,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.449544+00:00</t>
+          <t>2026-10-17T08:30:22.864374+00:00</t>
         </is>
       </c>
     </row>
@@ -27871,7 +27895,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.452406+00:00</t>
+          <t>2026-10-17T08:30:22.867680+00:00</t>
         </is>
       </c>
     </row>
@@ -27907,13 +27931,21 @@
           <t>papers/R06611/main/b8eb8afdada2_R06611_2021_Effective_pretreatment_of_lignocellulosic_co-substrates_using_barley_straw-adapted_microbial.pdf</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R06611_2021_Effective_pretreatment_of_lignocellulosic_co-substrates_using_barley_straw-adapted_microbial.pdf</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R06611_2021_Effective_pretreatment_of_lignocellulosic_co-substrates_using_barley_straw-adapted_microbial.pdf</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R06611_2021_Effective_pretreatment_of_lignocellulosic_co-substrates_using_barley_straw-adapted_microbial.pdf</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -27929,12 +27961,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -27971,7 +28003,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.452425+00:00</t>
+          <t>2026-10-17T08:30:22.869860+00:00</t>
         </is>
       </c>
     </row>
@@ -28079,7 +28111,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.453644+00:00</t>
+          <t>2026-10-17T08:30:22.871044+00:00</t>
         </is>
       </c>
     </row>
@@ -28115,13 +28147,21 @@
           <t>papers/R07238/main/26c38d163174_R07238_2021_The_influence_of_combined_low-strength_ultrasonics_and_micro-aerobic_pretreatment.pdf</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R07238_2021_The_influence_of_combined_low-strength_ultrasonics_and_micro-aerobic_pretreatment.pdf</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R07238_2021_The_influence_of_combined_low-strength_ultrasonics_and_micro-aerobic_pretreatment.pdf</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R07238_2021_The_influence_of_combined_low-strength_ultrasonics_and_micro-aerobic_pretreatment.pdf</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -28137,12 +28177,12 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -28179,7 +28219,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.453661+00:00</t>
+          <t>2026-10-17T08:30:22.873865+00:00</t>
         </is>
       </c>
     </row>
@@ -28287,7 +28327,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.454380+00:00</t>
+          <t>2026-10-17T08:30:22.874561+00:00</t>
         </is>
       </c>
     </row>
@@ -28395,7 +28435,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.455942+00:00</t>
+          <t>2026-10-17T08:30:22.876112+00:00</t>
         </is>
       </c>
     </row>
@@ -28503,7 +28543,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.456415+00:00</t>
+          <t>2026-10-17T08:30:22.876382+00:00</t>
         </is>
       </c>
     </row>
@@ -28603,7 +28643,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.456440+00:00</t>
+          <t>2026-10-17T08:30:22.876396+00:00</t>
         </is>
       </c>
     </row>
@@ -28711,7 +28751,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.459380+00:00</t>
+          <t>2026-10-17T08:30:22.879197+00:00</t>
         </is>
       </c>
     </row>
@@ -28811,7 +28851,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.459405+00:00</t>
+          <t>2026-10-17T08:30:22.879216+00:00</t>
         </is>
       </c>
     </row>
@@ -28919,7 +28959,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.459921+00:00</t>
+          <t>2026-10-17T08:30:22.879738+00:00</t>
         </is>
       </c>
     </row>
@@ -29019,7 +29059,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.459935+00:00</t>
+          <t>2026-10-17T08:30:22.879752+00:00</t>
         </is>
       </c>
     </row>
@@ -29119,7 +29159,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.459940+00:00</t>
+          <t>2026-10-17T08:30:22.879756+00:00</t>
         </is>
       </c>
     </row>
@@ -29219,7 +29259,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.459942+00:00</t>
+          <t>2026-10-17T08:30:22.879759+00:00</t>
         </is>
       </c>
     </row>
@@ -29327,7 +29367,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.461544+00:00</t>
+          <t>2026-10-17T08:30:22.881343+00:00</t>
         </is>
       </c>
     </row>
@@ -29427,7 +29467,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.461560+00:00</t>
+          <t>2026-10-17T08:30:22.881357+00:00</t>
         </is>
       </c>
     </row>
@@ -29527,7 +29567,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.461563+00:00</t>
+          <t>2026-10-17T08:30:22.881361+00:00</t>
         </is>
       </c>
     </row>
@@ -29635,7 +29675,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.461971+00:00</t>
+          <t>2026-10-17T08:30:22.881786+00:00</t>
         </is>
       </c>
     </row>
@@ -29735,7 +29775,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.461985+00:00</t>
+          <t>2026-10-17T08:30:22.881799+00:00</t>
         </is>
       </c>
     </row>
@@ -29843,7 +29883,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.463704+00:00</t>
+          <t>2026-10-17T08:30:22.883348+00:00</t>
         </is>
       </c>
     </row>
@@ -29951,7 +29991,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.465195+00:00</t>
+          <t>2026-10-17T08:30:22.884628+00:00</t>
         </is>
       </c>
     </row>
@@ -30051,7 +30091,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.465222+00:00</t>
+          <t>2026-10-17T08:30:22.884643+00:00</t>
         </is>
       </c>
     </row>
@@ -30151,7 +30191,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.465227+00:00</t>
+          <t>2026-10-17T08:30:22.884647+00:00</t>
         </is>
       </c>
     </row>
@@ -30251,7 +30291,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.465230+00:00</t>
+          <t>2026-10-17T08:30:22.884651+00:00</t>
         </is>
       </c>
     </row>
@@ -30351,7 +30391,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.465232+00:00</t>
+          <t>2026-10-17T08:30:22.884653+00:00</t>
         </is>
       </c>
     </row>
@@ -30459,7 +30499,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.465855+00:00</t>
+          <t>2026-10-17T08:30:22.885197+00:00</t>
         </is>
       </c>
     </row>
@@ -30559,7 +30599,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.465981+00:00</t>
+          <t>2026-10-17T08:30:22.885210+00:00</t>
         </is>
       </c>
     </row>
@@ -30659,7 +30699,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.465989+00:00</t>
+          <t>2026-10-17T08:30:22.885214+00:00</t>
         </is>
       </c>
     </row>
@@ -30759,7 +30799,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.465994+00:00</t>
+          <t>2026-10-17T08:30:22.885217+00:00</t>
         </is>
       </c>
     </row>
@@ -30859,7 +30899,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.466063+00:00</t>
+          <t>2026-10-17T08:30:22.885220+00:00</t>
         </is>
       </c>
     </row>
@@ -30959,7 +30999,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.466067+00:00</t>
+          <t>2026-10-17T08:30:22.885223+00:00</t>
         </is>
       </c>
     </row>
@@ -31067,7 +31107,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.466580+00:00</t>
+          <t>2026-10-17T08:30:22.885672+00:00</t>
         </is>
       </c>
     </row>
@@ -31175,7 +31215,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.467708+00:00</t>
+          <t>2026-10-17T08:30:22.886715+00:00</t>
         </is>
       </c>
     </row>
@@ -31283,7 +31323,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.470706+00:00</t>
+          <t>2026-10-17T08:30:22.889652+00:00</t>
         </is>
       </c>
     </row>
@@ -31383,7 +31423,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.470725+00:00</t>
+          <t>2026-10-17T08:30:22.889671+00:00</t>
         </is>
       </c>
     </row>
@@ -31491,7 +31531,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.474854+00:00</t>
+          <t>2026-10-17T08:30:22.893917+00:00</t>
         </is>
       </c>
     </row>
@@ -31591,7 +31631,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.474874+00:00</t>
+          <t>2026-10-17T08:30:22.893952+00:00</t>
         </is>
       </c>
     </row>
@@ -31699,7 +31739,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.476946+00:00</t>
+          <t>2026-10-17T08:30:22.896133+00:00</t>
         </is>
       </c>
     </row>
@@ -31807,7 +31847,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.478682+00:00</t>
+          <t>2026-10-17T08:30:22.897997+00:00</t>
         </is>
       </c>
     </row>
@@ -31907,7 +31947,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.478699+00:00</t>
+          <t>2026-10-17T08:30:22.898030+00:00</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32047,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.478703+00:00</t>
+          <t>2026-10-17T08:30:22.898035+00:00</t>
         </is>
       </c>
     </row>
@@ -32107,7 +32147,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.478707+00:00</t>
+          <t>2026-10-17T08:30:22.898038+00:00</t>
         </is>
       </c>
     </row>
@@ -32207,7 +32247,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.478709+00:00</t>
+          <t>2026-10-17T08:30:22.898041+00:00</t>
         </is>
       </c>
     </row>
@@ -32315,7 +32355,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.479956+00:00</t>
+          <t>2026-10-17T08:30:22.899307+00:00</t>
         </is>
       </c>
     </row>
@@ -32415,7 +32455,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.479979+00:00</t>
+          <t>2026-10-17T08:30:22.899337+00:00</t>
         </is>
       </c>
     </row>
@@ -32515,7 +32555,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.479983+00:00</t>
+          <t>2026-10-17T08:30:22.899343+00:00</t>
         </is>
       </c>
     </row>
@@ -32615,7 +32655,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.479986+00:00</t>
+          <t>2026-10-17T08:30:22.899347+00:00</t>
         </is>
       </c>
     </row>
@@ -32711,7 +32751,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.479990+00:00</t>
+          <t>2026-10-17T08:30:22.899352+00:00</t>
         </is>
       </c>
     </row>
@@ -32807,7 +32847,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.479993+00:00</t>
+          <t>2026-10-17T08:30:22.899356+00:00</t>
         </is>
       </c>
     </row>
@@ -32903,7 +32943,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.479995+00:00</t>
+          <t>2026-10-17T08:30:22.899360+00:00</t>
         </is>
       </c>
     </row>
@@ -32999,7 +33039,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.479999+00:00</t>
+          <t>2026-10-17T08:30:22.899365+00:00</t>
         </is>
       </c>
     </row>
@@ -33095,7 +33135,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.480001+00:00</t>
+          <t>2026-10-17T08:30:22.899368+00:00</t>
         </is>
       </c>
     </row>
@@ -33191,7 +33231,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.480004+00:00</t>
+          <t>2026-10-17T08:30:22.899372+00:00</t>
         </is>
       </c>
     </row>
@@ -33287,7 +33327,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.480007+00:00</t>
+          <t>2026-10-17T08:30:22.899376+00:00</t>
         </is>
       </c>
     </row>
@@ -33395,7 +33435,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.480698+00:00</t>
+          <t>2026-10-17T08:30:22.900155+00:00</t>
         </is>
       </c>
     </row>
@@ -33495,7 +33535,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.480715+00:00</t>
+          <t>2026-10-17T08:30:22.900177+00:00</t>
         </is>
       </c>
     </row>
@@ -33603,7 +33643,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.480766+00:00</t>
+          <t>2026-10-17T08:30:22.900231+00:00</t>
         </is>
       </c>
     </row>
@@ -33711,7 +33751,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.481177+00:00</t>
+          <t>2026-10-17T08:30:22.900571+00:00</t>
         </is>
       </c>
     </row>
@@ -33819,7 +33859,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.481353+00:00</t>
+          <t>2026-10-17T08:30:22.900873+00:00</t>
         </is>
       </c>
     </row>
@@ -33931,7 +33971,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.481500+00:00</t>
+          <t>2026-10-17T08:30:22.901038+00:00</t>
         </is>
       </c>
     </row>
@@ -34039,7 +34079,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.481870+00:00</t>
+          <t>2026-10-17T08:30:22.901461+00:00</t>
         </is>
       </c>
     </row>
@@ -34147,7 +34187,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.482061+00:00</t>
+          <t>2026-10-17T08:30:22.901696+00:00</t>
         </is>
       </c>
     </row>
@@ -34259,7 +34299,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.482111+00:00</t>
+          <t>2026-10-17T08:30:22.901753+00:00</t>
         </is>
       </c>
     </row>
@@ -34371,7 +34411,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.482170+00:00</t>
+          <t>2026-10-17T08:30:22.901818+00:00</t>
         </is>
       </c>
     </row>
@@ -34483,7 +34523,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.482322+00:00</t>
+          <t>2026-10-17T08:30:22.902135+00:00</t>
         </is>
       </c>
     </row>
@@ -34595,7 +34635,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.482369+00:00</t>
+          <t>2026-10-17T08:30:22.902198+00:00</t>
         </is>
       </c>
     </row>
@@ -34703,7 +34743,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.482814+00:00</t>
+          <t>2026-10-17T08:30:22.902780+00:00</t>
         </is>
       </c>
     </row>
@@ -34811,7 +34851,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.482858+00:00</t>
+          <t>2026-10-17T08:30:22.902847+00:00</t>
         </is>
       </c>
     </row>
@@ -34911,7 +34951,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.482868+00:00</t>
+          <t>2026-10-17T08:30:22.902875+00:00</t>
         </is>
       </c>
     </row>
@@ -35011,7 +35051,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.482871+00:00</t>
+          <t>2026-10-17T08:30:22.902880+00:00</t>
         </is>
       </c>
     </row>
@@ -35115,7 +35155,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.482875+00:00</t>
+          <t>2026-10-17T08:30:22.902883+00:00</t>
         </is>
       </c>
     </row>
@@ -35215,7 +35255,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.482878+00:00</t>
+          <t>2026-10-17T08:30:22.902886+00:00</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35363,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.483148+00:00</t>
+          <t>2026-10-17T08:30:22.903118+00:00</t>
         </is>
       </c>
     </row>
@@ -35431,7 +35471,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484210+00:00</t>
+          <t>2026-10-17T08:30:22.904207+00:00</t>
         </is>
       </c>
     </row>
@@ -35525,7 +35565,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484234+00:00</t>
+          <t>2026-10-17T08:30:22.904232+00:00</t>
         </is>
       </c>
     </row>
@@ -35619,7 +35659,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484237+00:00</t>
+          <t>2026-10-17T08:30:22.904237+00:00</t>
         </is>
       </c>
     </row>
@@ -35713,7 +35753,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484240+00:00</t>
+          <t>2026-10-17T08:30:22.904240+00:00</t>
         </is>
       </c>
     </row>
@@ -35807,7 +35847,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484243+00:00</t>
+          <t>2026-10-17T08:30:22.904244+00:00</t>
         </is>
       </c>
     </row>
@@ -35901,7 +35941,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484246+00:00</t>
+          <t>2026-10-17T08:30:22.904246+00:00</t>
         </is>
       </c>
     </row>
@@ -35995,7 +36035,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484248+00:00</t>
+          <t>2026-10-17T08:30:22.904250+00:00</t>
         </is>
       </c>
     </row>
@@ -36089,7 +36129,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484251+00:00</t>
+          <t>2026-10-17T08:30:22.904253+00:00</t>
         </is>
       </c>
     </row>
@@ -36183,7 +36223,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484259+00:00</t>
+          <t>2026-10-17T08:30:22.904255+00:00</t>
         </is>
       </c>
     </row>
@@ -36277,7 +36317,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484262+00:00</t>
+          <t>2026-10-17T08:30:22.904258+00:00</t>
         </is>
       </c>
     </row>
@@ -36371,7 +36411,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484265+00:00</t>
+          <t>2026-10-17T08:30:22.904261+00:00</t>
         </is>
       </c>
     </row>
@@ -36465,7 +36505,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484269+00:00</t>
+          <t>2026-10-17T08:30:22.904264+00:00</t>
         </is>
       </c>
     </row>
@@ -36559,7 +36599,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484272+00:00</t>
+          <t>2026-10-17T08:30:22.904267+00:00</t>
         </is>
       </c>
     </row>
@@ -36653,7 +36693,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484275+00:00</t>
+          <t>2026-10-17T08:30:22.904270+00:00</t>
         </is>
       </c>
     </row>
@@ -36747,7 +36787,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484277+00:00</t>
+          <t>2026-10-17T08:30:22.904273+00:00</t>
         </is>
       </c>
     </row>
@@ -36841,7 +36881,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484280+00:00</t>
+          <t>2026-10-17T08:30:22.904276+00:00</t>
         </is>
       </c>
     </row>
@@ -36935,7 +36975,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484283+00:00</t>
+          <t>2026-10-17T08:30:22.904279+00:00</t>
         </is>
       </c>
     </row>
@@ -37029,7 +37069,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484285+00:00</t>
+          <t>2026-10-17T08:30:22.904425+00:00</t>
         </is>
       </c>
     </row>
@@ -37123,7 +37163,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484288+00:00</t>
+          <t>2026-10-17T08:30:22.904429+00:00</t>
         </is>
       </c>
     </row>
@@ -37217,7 +37257,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484290+00:00</t>
+          <t>2026-10-17T08:30:22.904433+00:00</t>
         </is>
       </c>
     </row>
@@ -37311,7 +37351,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484292+00:00</t>
+          <t>2026-10-17T08:30:22.904435+00:00</t>
         </is>
       </c>
     </row>
@@ -37405,7 +37445,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484322+00:00</t>
+          <t>2026-10-17T08:30:22.904439+00:00</t>
         </is>
       </c>
     </row>
@@ -37499,7 +37539,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484329+00:00</t>
+          <t>2026-10-17T08:30:22.904442+00:00</t>
         </is>
       </c>
     </row>
@@ -37593,7 +37633,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484333+00:00</t>
+          <t>2026-10-17T08:30:22.904445+00:00</t>
         </is>
       </c>
     </row>
@@ -37687,7 +37727,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484336+00:00</t>
+          <t>2026-10-17T08:30:22.904448+00:00</t>
         </is>
       </c>
     </row>
@@ -37781,7 +37821,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484339+00:00</t>
+          <t>2026-10-17T08:30:22.904451+00:00</t>
         </is>
       </c>
     </row>
@@ -37875,7 +37915,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484342+00:00</t>
+          <t>2026-10-17T08:30:22.904454+00:00</t>
         </is>
       </c>
     </row>
@@ -37969,7 +38009,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484346+00:00</t>
+          <t>2026-10-17T08:30:22.904458+00:00</t>
         </is>
       </c>
     </row>
@@ -38069,7 +38109,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T08:29:31.484349+00:00</t>
+          <t>2026-10-17T08:30:22.904461+00:00</t>
         </is>
       </c>
     </row>
@@ -38084,7 +38124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38172,12 +38212,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R13558</t>
+          <t>R01212</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R13558.main.0006612a5b75c131</t>
+          <t>R01212.main.ef235fcb491d4749</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -38187,20 +38227,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0006612a5b75c131170aa335c1e8d9810b41dca937beefac6ea258e1920944ec</t>
+          <t>ef235fcb491d474970838cf59cfd36efaf9a37c84ddd225c06788beb77d497e3</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>974385</v>
+        <v>773976</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.scielo.br/j/esa/a/DPQswHpgKLty6wPLBbxGcCn/?lang=en&amp;format=pdf</t>
+          <t>https://www.eeer.org/upload/eer-19-1-59-9.pdf</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>R13558_2026_Redox_mediators_and_microaeration_overcoming_linear_alkylbenzene_sulfonate_recalcitrance.pdf</t>
+          <t>R01212_2014_Effects_of_Pre-aeration_on_the_Anaerobic_Digestion_of_Sewage.pdf</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -38212,12 +38252,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R04889</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R04889.main.860a0532503787f8</t>
+          <t>R08646.main.7df5523334e7d1bb</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -38227,20 +38267,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>860a0532503787f8bb84a599bdbf923f690615b05121c8a78c21249f8de911cb</t>
+          <t>7df5523334e7d1bb513d2a3deb5b018c0c9b2a3ea9e49b7ff8f09a1fe853cd96</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>506684</v>
+        <v>3009960</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://journal.unnes.ac.id/nju/jbat/article/download/16318/9427</t>
+          <t>https://europepmc.org/api/getPdf?pmcid=PMC10559078</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>R04889_2019_Inoculum_Selection_and_Micro-Aeration_for_Biogas_Production_in_Two-Stage.pdf</t>
+          <t>R08646_2023_Approaches_to_mitigation_of_hydrogen_sulfide_during_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -38252,12 +38292,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R01212</t>
+          <t>R10894</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R01212.main.ef235fcb491d4749</t>
+          <t>R10894.main.f9caf3b730e23f0d</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -38267,20 +38307,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ef235fcb491d474970838cf59cfd36efaf9a37c84ddd225c06788beb77d497e3</t>
+          <t>f9caf3b730e23f0d9d31d71069935c39e162415bbdac53ee97821305a81be9d2</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>773976</v>
+        <v>2030435</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.eeer.org/upload/eer-19-1-59-9.pdf</t>
+          <t>https://europepmc.org/api/getPdf?pmcid=PMC11499478</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>R01212_2014_Effects_of_Pre-aeration_on_the_Anaerobic_Digestion_of_Sewage.pdf</t>
+          <t>R10894_2024_The_effects_of_different_pretreatment_technologies_on_microbial_community.pdf</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -38292,12 +38332,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R05542</t>
+          <t>R06737</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R05542.main.735560cdb2769e25</t>
+          <t>R06737.main.32eabc0a46b31862</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -38307,20 +38347,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>735560cdb2769e2517355c073dd51a95ac90b015a5b36f90dcc0dff360ae182b</t>
+          <t>32eabc0a46b31862fa95a7bcf29fc4e5b154b7ec51c11cd1d4f798bbad95b59a</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>836053</v>
+        <v>4126947</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://europepmc.org/api/getPdf?pmcid=PMC9056904</t>
+          <t>https://ira.lib.polyu.edu.hk/bitstream/10397/97386/1/Zhuang_Genomic_Driven_Factors.pdf</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>R05542_2020_Effect_of_micro-aerobic_process_on_improvement_of_anaerobic_digestion.pdf</t>
+          <t>R06737_2021_Genomic_driven_factors_enhance_biocatalyst-related_cellulolysis_potential_in_anaerobic.pdf</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -38332,12 +38372,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R06611</t>
+          <t>R04119</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R06611.main.b8eb8afdada2a2d0</t>
+          <t>R04119.main.c9b1902447e38978</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -38347,20 +38387,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>b8eb8afdada2a2d0d5151fd81489263cbfd0ccc3bbde8c5ca36a02af52cfa12f</t>
+          <t>c9b1902447e38978d2f6f25327940f80e825baee1ebabba8bd8a860ed1fa254c</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3320239</v>
+        <v>1726821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://eprints.whiterose.ac.uk/id/eprint/168685/1/A_draft_BITE_paper.pdf</t>
+          <t>https://europepmc.org/api/getPdf?pmcid=PMC6197294</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>R06611_2021_Effective_pretreatment_of_lignocellulosic_co-substrates_using_barley_straw-adapted_microbial.pdf</t>
+          <t>R04119_2018_Microbial_pretreatment_of_lignocellulosic_biomass_for_enhanced_biomethanation_and.pdf</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -38372,12 +38412,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R00273</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R07238.main.26c38d1631747ddc</t>
+          <t>R00273.main.2059ae72be92bd0e</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -38387,20 +38427,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>26c38d1631747ddcb443b8d80d0070145f1968ff0f4b8e86dc2f69cc2bb968d8</t>
+          <t>2059ae72be92bd0e0928b31eb73f27d1f92ac15865050966ba9369eae1ac9c0c</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4532295</v>
+        <v>5372083</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://europepmc.org/api/getPdf?pmcid=PMC8044681</t>
+          <t>https://lup.lub.lu.se/luur/download?func=downloadFile&amp;recordOId=5277171&amp;fileOId=5277177</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>R07238_2021_The_influence_of_combined_low-strength_ultrasonics_and_micro-aerobic_pretreatment.pdf</t>
+          <t>R00273_2012_Management_of_hydrogen_sulfide_in_anaerobic_digestion_of_enzyme.pdf</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -38412,12 +38452,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R04700</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R08646.main.7df5523334e7d1bb</t>
+          <t>R04700.main.40ac0de29f75851c</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -38427,20 +38467,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7df5523334e7d1bb513d2a3deb5b018c0c9b2a3ea9e49b7ff8f09a1fe853cd96</t>
+          <t>40ac0de29f75851cab1651e1e339d03329bb7ce0141519329487f0559ebd8297</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3009960</v>
+        <v>2892628</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://europepmc.org/api/getPdf?pmcid=PMC10559078</t>
+          <t>https://repository.tudelft.nl/file/File_d8b73973-6e26-4f66-9162-3212f6b93431</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>R08646_2023_Approaches_to_mitigation_of_hydrogen_sulfide_during_anaerobic_digestion.pdf</t>
+          <t>R04700_2019_Effect_of_aeration_by_micro_-_bubbles_on_methane.pdf</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -38452,12 +38492,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R10894</t>
+          <t>R09568</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R10894.main.f9caf3b730e23f0d</t>
+          <t>R09568.main.393322098ea47587</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -38467,20 +38507,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>f9caf3b730e23f0d9d31d71069935c39e162415bbdac53ee97821305a81be9d2</t>
+          <t>393322098ea4758738b0e338c3e0019bd8618611d25a41cf3535d9542a6c8d16</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2030435</v>
+        <v>1433947</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://europepmc.org/api/getPdf?pmcid=PMC11499478</t>
+          <t>https://repository.tudelft.nl/file/File_b3a1ee42-17d3-4f7d-82dc-616c91a5a6bf</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>R10894_2024_The_effects_of_different_pretreatment_technologies_on_microbial_community.pdf</t>
+          <t>R09568_2023_The_fate_of_sulfamethoxazole_and_trimethoprim_in_a_micro-aerated.pdf</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -38492,12 +38532,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R06737</t>
+          <t>R10290</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R06737.main.32eabc0a46b31862</t>
+          <t>R10290.main.0a63bc6c89e8dff8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -38507,20 +38547,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>32eabc0a46b31862fa95a7bcf29fc4e5b154b7ec51c11cd1d4f798bbad95b59a</t>
+          <t>0a63bc6c89e8dff87ff1b364322ce6738e4fc87f505478ef522e7c73b7db342f</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4126947</v>
+        <v>530753</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://ira.lib.polyu.edu.hk/bitstream/10397/97386/1/Zhuang_Genomic_Driven_Factors.pdf</t>
+          <t>https://office.nbc-journal.org/index.php/NBC/article/download/2100/955</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>R06737_2021_Genomic_driven_factors_enhance_biocatalyst-related_cellulolysis_potential_in_anaerobic.pdf</t>
+          <t>R10290_2024_Gas_nanobubble_technology_in_wastewater_treatment_and_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -38532,12 +38572,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R04119</t>
+          <t>R10724</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R04119.main.c9b1902447e38978</t>
+          <t>R10724.main.cfdc1bcb235acdd7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -38547,20 +38587,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>c9b1902447e38978d2f6f25327940f80e825baee1ebabba8bd8a860ed1fa254c</t>
+          <t>cfdc1bcb235acdd703e58447b30b31cb8c4e8d53d1c86999ee8ecdafbba1e8aa</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1726821</v>
+        <v>2366242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://europepmc.org/api/getPdf?pmcid=PMC6197294</t>
+          <t>https://www.ecoeet.com/pdf-181210-105068?filename=Protection-of-the-Purific.pdf</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>R04119_2018_Microbial_pretreatment_of_lignocellulosic_biomass_for_enhanced_biomethanation_and.pdf</t>
+          <t>R10724_2024_Protection_of_the_Purification_Station_Thermal_Engines_Against_the.pdf</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -38572,12 +38612,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R00273</t>
+          <t>R11658</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R00273.main.2059ae72be92bd0e</t>
+          <t>R11658.main.83a514a4b04c73a0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -38587,20 +38627,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2059ae72be92bd0e0928b31eb73f27d1f92ac15865050966ba9369eae1ac9c0c</t>
+          <t>83a514a4b04c73a09129c21d623d57eb798a3af7c20dc842d47308f889d7695f</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5372083</v>
+        <v>458052</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://lup.lub.lu.se/luur/download?func=downloadFile&amp;recordOId=5277171&amp;fileOId=5277177</t>
+          <t>https://bsuj.bsu.edu.az/readpdf.php?file=236e3d6763a43f726c9814e7b5de8bc1.pdf</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>R00273_2012_Management_of_hydrogen_sulfide_in_anaerobic_digestion_of_enzyme.pdf</t>
+          <t>R11658_2025_IMPACT_OF_MICRO-AERATION_ON_FUNGAL_COMMUNITY_FROM_ANAEROBIC_DIGESTION.pdf</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -38612,12 +38652,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R04700</t>
+          <t>R12483</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R04700.main.40ac0de29f75851c</t>
+          <t>R12483.main.b51428ca89e5bf95</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -38627,20 +38667,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>40ac0de29f75851cab1651e1e339d03329bb7ce0141519329487f0559ebd8297</t>
+          <t>b51428ca89e5bf95c17225fe2e0a08a920379629281ab76f33337561553f3b0f</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2892628</v>
+        <v>1807518</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://repository.tudelft.nl/file/File_d8b73973-6e26-4f66-9162-3212f6b93431</t>
+          <t>https://li01.tci-thaijo.org/index.php/TSAEJ/article/download/269146/181297</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>R04700_2019_Effect_of_aeration_by_micro_-_bubbles_on_methane.pdf</t>
+          <t>R12483_2025_การปรบสภาพชวมวลลกโนเซลลโลสดวยวสดเพาะเหดเหลอทง_แนวทางการเพมมล.pdf</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -38652,12 +38692,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R09568</t>
+          <t>R13819</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R09568.main.393322098ea47587</t>
+          <t>R13819.main.431f5e76781d3cef</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -38667,20 +38707,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>393322098ea4758738b0e338c3e0019bd8618611d25a41cf3535d9542a6c8d16</t>
+          <t>431f5e76781d3cef39588c258c5589b1c9cf01db486c503ba29ab166bc73f14a</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1433947</v>
+        <v>2172752</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://repository.tudelft.nl/file/File_b3a1ee42-17d3-4f7d-82dc-616c91a5a6bf</t>
+          <t>https://epublications.marquette.edu/cgi/viewcontent.cgi?article=1131&amp;context=civengin_fac</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>R09568_2023_The_fate_of_sulfamethoxazole_and_trimethoprim_in_a_micro-aerated.pdf</t>
+          <t>R13819_2015_Bioaugmentation_of_overloaded_anaerobic_digesters_restores_function_and_archaeal.pdf</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -38692,12 +38732,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R10290</t>
+          <t>R13833</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R10290.main.0a63bc6c89e8dff8</t>
+          <t>R13833.main.1a4a4d5f8fd45de9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -38707,20 +38747,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0a63bc6c89e8dff87ff1b364322ce6738e4fc87f505478ef522e7c73b7db342f</t>
+          <t>1a4a4d5f8fd45de924c78a7be11e1c032c630bd9341431d1d49135c8351cdaf7</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>530753</v>
+        <v>1463714</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://office.nbc-journal.org/index.php/NBC/article/download/2100/955</t>
+          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/234ac4ff-f996-498f-8853-72ba22cb7700/content</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>R10290_2024_Gas_nanobubble_technology_in_wastewater_treatment_and_anaerobic_digestion.pdf</t>
+          <t>R13833_2018_Insight_into_the_Role_of_Facultative_Bacteria_Stimulated_by.pdf</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -38732,12 +38772,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R10724</t>
+          <t>R13861</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R10724.main.cfdc1bcb235acdd7</t>
+          <t>R13861.main.ba6f44b77d79c4a0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -38747,20 +38787,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>cfdc1bcb235acdd703e58447b30b31cb8c4e8d53d1c86999ee8ecdafbba1e8aa</t>
+          <t>ba6f44b77d79c4a07ba08602860bcf1bdbb36cb47b4527fa9d1f087825e394d8</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2366242</v>
+        <v>433474</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.ecoeet.com/pdf-181210-105068?filename=Protection-of-the-Purific.pdf</t>
+          <t>https://www.scielo.br/j/esa/a/BD6Bc5rMVrTsbkK7CZz6yVd/?format=pdf&amp;lang=en&amp;ilang=pt_BR</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>R10724_2024_Protection_of_the_Purification_Station_Thermal_Engines_Against_the.pdf</t>
+          <t>R13861_2019_Enhanced_removal_of_emerging_micropollutants_by_applying_microaeration_to.pdf</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -38772,12 +38812,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R11658</t>
+          <t>R13871</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R11658.main.83a514a4b04c73a0</t>
+          <t>R13871.main.aeab3126b6e68775</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -38787,20 +38827,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>83a514a4b04c73a09129c21d623d57eb798a3af7c20dc842d47308f889d7695f</t>
+          <t>aeab3126b6e68775b9b316714633bd97c1f184cf9e308d75b404bca6b33be19f</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>458052</v>
+        <v>7983514</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://bsuj.bsu.edu.az/readpdf.php?file=236e3d6763a43f726c9814e7b5de8bc1.pdf</t>
+          <t>https://etheses.whiterose.ac.uk/id/eprint/4094/6/Mahmood_Khazzal_Hummadi_Al-Mashhadani._Reg._No._080243946_%28PhD_thesis%29_2013.pdf</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>R11658_2025_IMPACT_OF_MICRO-AERATION_ON_FUNGAL_COMMUNITY_FROM_ANAEROBIC_DIGESTION.pdf</t>
+          <t>R13871_2013_Application_of_Microbubbles_Generated_by_Fluidic_Oscillation_in_the.pdf</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -38812,12 +38852,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R12483</t>
+          <t>R13877</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R12483.main.b51428ca89e5bf95</t>
+          <t>R13877.main.04a76adc76fa9472</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -38827,20 +38867,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>b51428ca89e5bf95c17225fe2e0a08a920379629281ab76f33337561553f3b0f</t>
+          <t>04a76adc76fa947250861c95c93759c590dd3e02d7f80dc23ce0abedccb74510</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1807518</v>
+        <v>522402</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://li01.tci-thaijo.org/index.php/TSAEJ/article/download/269146/181297</t>
+          <t>https://escholarship.org/content/qt5572k7rw/qt5572k7rw.pdf</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>R12483_2025_การปรบสภาพชวมวลลกโนเซลลโลสดวยวสดเพาะเหดเหลอทง_แนวทางการเพมมล.pdf</t>
+          <t>R13877_2018_Microbial_community_response_and_SDS-PAGE_reveal_possible_mechanism_of.pdf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -38852,12 +38892,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R13819</t>
+          <t>R13862</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R13819.main.431f5e76781d3cef</t>
+          <t>R13862.main.64e03a9beb5813a0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -38867,20 +38907,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>431f5e76781d3cef39588c258c5589b1c9cf01db486c503ba29ab166bc73f14a</t>
+          <t>64e03a9beb5813a0ce6d94272350217f12dac94293420969e3d2d9d7975e96e3</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2172752</v>
+        <v>833659</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://epublications.marquette.edu/cgi/viewcontent.cgi?article=1131&amp;context=civengin_fac</t>
+          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/eb850f96-0570-4e0d-be55-73fcee5f1364/content</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>R13819_2015_Bioaugmentation_of_overloaded_anaerobic_digesters_restores_function_and_archaeal.pdf</t>
+          <t>R13862_2020_Multiple_and_flexible_roles_of_facultative_anaerobic_bacteria_in.pdf</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -38892,12 +38932,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R13833</t>
+          <t>R13900</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R13833.main.1a4a4d5f8fd45de9</t>
+          <t>R13900.main.b2ba7df8c04ab66c</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -38907,20 +38947,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1a4a4d5f8fd45de924c78a7be11e1c032c630bd9341431d1d49135c8351cdaf7</t>
+          <t>b2ba7df8c04ab66c0e548f778e19c5764802c0da8408a3b8499547b3f6ef51b3</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1463714</v>
+        <v>299244</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/234ac4ff-f996-498f-8853-72ba22cb7700/content</t>
+          <t>https://www.research.unipd.it/bitstream/11577/3261852/1/Front.%20Environ.%20Sci.%20Eng%20Dongbei%202018.pdf</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>R13833_2018_Insight_into_the_Role_of_Facultative_Bacteria_Stimulated_by.pdf</t>
+          <t>R13900_2018_Effectiveness_of_aerobic_pretreatment_of_municipal_solid_waste_for.pdf</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -38932,12 +38972,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R13861</t>
+          <t>R13903</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R13861.main.ba6f44b77d79c4a0</t>
+          <t>R13903.main.2cd9e7b409250e7b</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -38947,20 +38987,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ba6f44b77d79c4a07ba08602860bcf1bdbb36cb47b4527fa9d1f087825e394d8</t>
+          <t>2cd9e7b409250e7b104f489e139f57d4daa40d97133c6c57c937184c3ec73b71</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>433474</v>
+        <v>1107675</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.scielo.br/j/esa/a/BD6Bc5rMVrTsbkK7CZz6yVd/?format=pdf&amp;lang=en&amp;ilang=pt_BR</t>
+          <t>https://ijabe.org/index.php/ijabe/article/download/7975/pdf</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>R13861_2019_Enhanced_removal_of_emerging_micropollutants_by_applying_microaeration_to.pdf</t>
+          <t>R13903_2023_Effect_of_vacuum_negative_pressure_aerobic_hydrolysis_pretreatment_on.pdf</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -38972,12 +39012,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R13871</t>
+          <t>R13931</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R13871.main.aeab3126b6e68775</t>
+          <t>R13931.main.6e898a403edac7b3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -38987,20 +39027,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>aeab3126b6e68775b9b316714633bd97c1f184cf9e308d75b404bca6b33be19f</t>
+          <t>6e898a403edac7b3ae15ad88cf75788898cd84ea377b2572f7bab40d9c126f8c</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>7983514</v>
+        <v>1324593</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://etheses.whiterose.ac.uk/id/eprint/4094/6/Mahmood_Khazzal_Hummadi_Al-Mashhadani._Reg._No._080243946_%28PhD_thesis%29_2013.pdf</t>
+          <t>https://www.eeer.org/upload/eer-2020-470.pdf</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>R13871_2013_Application_of_Microbubbles_Generated_by_Fluidic_Oscillation_in_the.pdf</t>
+          <t>R13931_2020_Biogas_recovery_from_fresh_landfill_leachates_by_using_a.pdf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -39012,12 +39052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R13877</t>
+          <t>R13945</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R13877.main.04a76adc76fa9472</t>
+          <t>R13945.main.67309ea094d2f9bb</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -39027,20 +39067,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>04a76adc76fa947250861c95c93759c590dd3e02d7f80dc23ce0abedccb74510</t>
+          <t>67309ea094d2f9bb088d605746ede869866819a733f53c44dc2d44af934e6be9</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>522402</v>
+        <v>2230958</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://escholarship.org/content/qt5572k7rw/qt5572k7rw.pdf</t>
+          <t>https://epublications.marquette.edu/cgi/viewcontent.cgi?article=1459&amp;context=theses_open</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>R13877_2018_Microbial_community_response_and_SDS-PAGE_reveal_possible_mechanism_of.pdf</t>
+          <t>R13945_2018_Effect_of_Low_Aeration_and_Heat_Drying_on_Anaerobic.pdf</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -39052,12 +39092,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R13862</t>
+          <t>R13950</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R13862.main.64e03a9beb5813a0</t>
+          <t>R13950.main.2bf9b46c448685b9</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -39067,20 +39107,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>64e03a9beb5813a0ce6d94272350217f12dac94293420969e3d2d9d7975e96e3</t>
+          <t>2bf9b46c448685b9e66f4064245c5840dc28ded79ee4d613ddd9efeb4805812e</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>833659</v>
+        <v>3508852</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/eb850f96-0570-4e0d-be55-73fcee5f1364/content</t>
+          <t>https://www.research.unipd.it/bitstream/11577/3425227/1/Thesis_Razieh_Rafieenia.pdf</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>R13862_2020_Multiple_and_flexible_roles_of_facultative_anaerobic_bacteria_in.pdf</t>
+          <t>R13950_2019_Enhancement_of_hydrogen_and_methane_production_through_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -39092,12 +39132,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R13900</t>
+          <t>R13944</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R13900.main.b2ba7df8c04ab66c</t>
+          <t>R13944.main.7e22fbfd39ddfed0</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -39107,20 +39147,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>b2ba7df8c04ab66c0e548f778e19c5764802c0da8408a3b8499547b3f6ef51b3</t>
+          <t>7e22fbfd39ddfed09b9235fea5c6914cfbe5987d12564fc9cb799bf412ae6779</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>299244</v>
+        <v>12042699</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.research.unipd.it/bitstream/11577/3261852/1/Front.%20Environ.%20Sci.%20Eng%20Dongbei%202018.pdf</t>
+          <t>https://scholarspace.manoa.hawaii.edu/server/api/core/bitstreams/60c88164-f37f-492a-97bc-e34a2f2b1698/content</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>R13900_2018_Effectiveness_of_aerobic_pretreatment_of_municipal_solid_waste_for.pdf</t>
+          <t>R13944_2018_Oxidation-Reduction_Potential-Based_Micro-Aeration_Control_System_for_Anaerobic_Digestion.pdf</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -39132,12 +39172,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>R13903</t>
+          <t>R13967</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R13903.main.2cd9e7b409250e7b</t>
+          <t>R13967.main.5e9f84dbaf01dd19</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -39147,20 +39187,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2cd9e7b409250e7b104f489e139f57d4daa40d97133c6c57c937184c3ec73b71</t>
+          <t>5e9f84dbaf01dd19674f09cbce96f338f32fe21a37a883bb9658e49af7072194</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1107675</v>
+        <v>160020</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://ijabe.org/index.php/ijabe/article/download/7975/pdf</t>
+          <t>https://www.aceee.org/wp-content/uploads/proceedings-1980-2020/2012/0193-000342.pdf</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>R13903_2023_Effect_of_vacuum_negative_pressure_aerobic_hydrolysis_pretreatment_on.pdf</t>
+          <t>R13967_2012_An_Improved_Biomass_Waste_Anaerobic_Degradation_Technology_for_Producing.pdf</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -39172,12 +39212,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>R13931</t>
+          <t>R13972</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R13931.main.6e898a403edac7b3</t>
+          <t>R13972.main.ff4ee9377a7e227c</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -39187,20 +39227,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6e898a403edac7b3ae15ad88cf75788898cd84ea377b2572f7bab40d9c126f8c</t>
+          <t>ff4ee9377a7e227c48a5bc64d301bfc1a989ee0e709c322eb90f254819d7b391</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1324593</v>
+        <v>1192569</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.eeer.org/upload/eer-2020-470.pdf</t>
+          <t>https://www.osti.gov/servlets/purl/2386939</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>R13931_2020_Biogas_recovery_from_fresh_landfill_leachates_by_using_a.pdf</t>
+          <t>R13972_2022_Enhancing_methane_production_of_anaerobic_digested_sewage_sludge_by.pdf</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -39212,12 +39252,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>R13945</t>
+          <t>R13957</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>R13945.main.67309ea094d2f9bb</t>
+          <t>R13957.main.3db804dcdefb7608</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -39227,20 +39267,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>67309ea094d2f9bb088d605746ede869866819a733f53c44dc2d44af934e6be9</t>
+          <t>3db804dcdefb7608eefc6bf166b0713cbbec8ac027b1c01831aec97b54253b82</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2230958</v>
+        <v>7806265</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://epublications.marquette.edu/cgi/viewcontent.cgi?article=1459&amp;context=theses_open</t>
+          <t>https://backoffice.biblio.ugent.be/download/8530499/8530500</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>R13945_2018_Effect_of_Low_Aeration_and_Heat_Drying_on_Anaerobic.pdf</t>
+          <t>R13957_2017_Microaeration_for_biogas_desulfurization_experimental_and_simulation_study_of.pdf</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -39252,12 +39292,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>R13950</t>
+          <t>R04510</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R13950.main.2bf9b46c448685b9</t>
+          <t>R04510.main.c4520ca79e301bb6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -39267,20 +39307,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2bf9b46c448685b9e66f4064245c5840dc28ded79ee4d613ddd9efeb4805812e</t>
+          <t>c4520ca79e301bb606a8ab1fef6cf4af9064c0d85f3c390a4cf31a877238e1c6</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3508852</v>
+        <v>492630</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.research.unipd.it/bitstream/11577/3425227/1/Thesis_Razieh_Rafieenia.pdf</t>
+          <t>https://digital.csic.es/bitstream/10261/196040/5/PostP_2019_JESH_V54_Iss10.pdf</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>R13950_2019_Enhancement_of_hydrogen_and_methane_production_through_anaerobic_digestion.pdf</t>
+          <t>R04510_2019_Anaerobic_digestion_of_wastewater_rich_in_sulfate_and_sulfide_effects_of_metallic_waste_addition_and.pdf</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -39292,12 +39332,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>R13944</t>
+          <t>R13889</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R13944.main.7e22fbfd39ddfed0</t>
+          <t>R13889.main.8db0dcdf434e876e</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -39307,20 +39347,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7e22fbfd39ddfed09b9235fea5c6914cfbe5987d12564fc9cb799bf412ae6779</t>
+          <t>8db0dcdf434e876e7cbff3cf342105807bdd41a900f74c0028cb14a6c6e56779</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>12042699</v>
+        <v>514378</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://scholarspace.manoa.hawaii.edu/server/api/core/bitstreams/60c88164-f37f-492a-97bc-e34a2f2b1698/content</t>
+          <t>https://digital.csic.es/bitstream/10261/178890/1/PotP_2018_RE_V123_P541.pdf</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>R13944_2018_Oxidation-Reduction_Potential-Based_Micro-Aeration_Control_System_for_Anaerobic_Digestion.pdf</t>
+          <t>R13889_2018_Increase_in_biogas_production_in_anaerobic_sludge_digestion_by_combining_aerobic_hydrolysis_and_addi.pdf</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -39332,12 +39372,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>R13967</t>
+          <t>R02719</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R13967.main.5e9f84dbaf01dd19</t>
+          <t>R02719.main.4bf5e309b2ef3431</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -39347,20 +39387,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5e9f84dbaf01dd19674f09cbce96f338f32fe21a37a883bb9658e49af7072194</t>
+          <t>4bf5e309b2ef343162a9588383a7ae0254118c33cdf2e96bec1a05459fae1523</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>160020</v>
+        <v>583591</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.aceee.org/wp-content/uploads/proceedings-1980-2020/2012/0193-000342.pdf</t>
+          <t>https://digital.csic.es/bitstream/10261/137944/1/Post_2016_JEnvSciHealth_A_BorjaR.pdf</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>R13967_2012_An_Improved_Biomass_Waste_Anaerobic_Degradation_Technology_for_Producing.pdf</t>
+          <t>R02719_2016_Performance_evaluation_of_micro_aerobic_hydrolysis_of_mixed_sludge_Optimum_aeration_and_effect_on_it.pdf</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -39372,12 +39412,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R13972</t>
+          <t>R02282</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R13972.main.ff4ee9377a7e227c</t>
+          <t>R02282.main.e709439b748e7938</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -39387,20 +39427,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ff4ee9377a7e227c48a5bc64d301bfc1a989ee0e709c322eb90f254819d7b391</t>
+          <t>e709439b748e793826102646c009aa10e1e9ac30627ac301fac7dd42276a2047</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1192569</v>
+        <v>1067465</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.osti.gov/servlets/purl/2386939</t>
+          <t>https://digital.csic.es/bitstream/10261/130093/1/Postprint_2016_EnviromRev_V24_P84.pdf</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>R13972_2022_Enhancing_methane_production_of_anaerobic_digested_sewage_sludge_by.pdf</t>
+          <t>R02282_2016_Advances_in_the_biological_removal_of_sulphides_from_aqueous_phase_in_anaerobic_processes_A_review.pdf</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -39412,12 +39452,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>R13957</t>
+          <t>R13905</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>R13957.main.3db804dcdefb7608</t>
+          <t>R13905.main.c75b5084c2545bd9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -39427,20 +39467,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3db804dcdefb7608eefc6bf166b0713cbbec8ac027b1c01831aec97b54253b82</t>
+          <t>c75b5084c2545bd939d3b1928be41fe0072c7302f26c25ba023c4bb6fc8a6970</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>7806265</v>
+        <v>2159708</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://backoffice.biblio.ugent.be/download/8530499/8530500</t>
+          <t>https://ddd.uab.cat/pub/artpub/2017/196242/wasbioval_a2017m7v8n5p1793.pdf</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>R13957_2017_Microaeration_for_biogas_desulfurization_experimental_and_simulation_study_of.pdf</t>
+          <t>R13905_2017_The_Effect_of_a_Short_Term_Aerobic_Pretreatment_Step_on_the_Anaerobic_Co_digestion_of_the_Organic_Fr.pdf</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -39452,12 +39492,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>R04510</t>
+          <t>R13932</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>R04510.main.c4520ca79e301bb6</t>
+          <t>R13932.main.c15f49a3d617e1be</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -39467,20 +39507,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>c4520ca79e301bb606a8ab1fef6cf4af9064c0d85f3c390a4cf31a877238e1c6</t>
+          <t>c15f49a3d617e1be5e21578ebda1c2d855f8d460c1d66f446ad0d02856a40a13</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>492630</v>
+        <v>1258157</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/196040/5/PostP_2019_JESH_V54_Iss10.pdf</t>
+          <t>https://hal.inrae.fr/hal-02620984/document</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>R04510_2019_Anaerobic_digestion_of_wastewater_rich_in_sulfate_and_sulfide_effects_of_metallic_waste_addition_and.pdf</t>
+          <t>R13932_2018_Comparison_of_pre_and_inter_stage_aerobic_treatment_of_wastewater_sludge_Effects_on_biogas_productio.pdf</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -39492,12 +39532,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>R13889</t>
+          <t>R13956</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R13889.main.8db0dcdf434e876e</t>
+          <t>R13956.main.fedaffcdf5be81e2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -39507,20 +39547,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8db0dcdf434e876e7cbff3cf342105807bdd41a900f74c0028cb14a6c6e56779</t>
+          <t>fedaffcdf5be81e2070b7edb0531c332e423578228eeb8c55a6afc4ba8fe1e18</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>514378</v>
+        <v>421626</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/178890/1/PotP_2018_RE_V123_P541.pdf</t>
+          <t>https://www.banglajol.info/index.php/BJSIR/article/download/25579/17152</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>R13889_2018_Increase_in_biogas_production_in_anaerobic_sludge_digestion_by_combining_aerobic_hydrolysis_and_addi.pdf</t>
+          <t>R13956_2015_Anaerobic_digestion_of_mixed_dried_fallen_leaves_by_mixing_with_cow_dung.pdf</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -39532,12 +39572,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>R02719</t>
+          <t>R13955</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>R02719.main.4bf5e309b2ef3431</t>
+          <t>R13955.main.7549e1025985363e</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -39547,20 +39587,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4bf5e309b2ef343162a9588383a7ae0254118c33cdf2e96bec1a05459fae1523</t>
+          <t>7549e1025985363e89542bbc1af6eaaa1150bbd62ea43bdd03d2c7b764631f9d</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>583591</v>
+        <v>14662438</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/137944/1/Post_2016_JEnvSciHealth_A_BorjaR.pdf</t>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>R02719_2016_Performance_evaluation_of_micro_aerobic_hydrolysis_of_mixed_sludge_Optimum_aeration_and_effect_on_it.pdf</t>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -39572,35 +39612,35 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>R02282</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R02282.main.e709439b748e7938</t>
+          <t>R07238.supplementary.0b7925ad1ed9c793</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>e709439b748e793826102646c009aa10e1e9ac30627ac301fac7dd42276a2047</t>
+          <t>0b7925ad1ed9c7939a79ba6294d17abc4b23fca77e52ec50df5463d050940d1e</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1067465</v>
+        <v>49526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/130093/1/Postprint_2016_EnviromRev_V24_P84.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>R02282_2016_Advances_in_the_biological_removal_of_sulphides_from_aqueous_phase_in_anaerobic_processes_A_review.pdf</t>
+          <t>mmc1.docx</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -39612,35 +39652,35 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>R13905</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>R13905.main.c75b5084c2545bd9</t>
+          <t>R07238.supplementary.f346f9bdcc964013</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>c75b5084c2545bd939d3b1928be41fe0072c7302f26c25ba023c4bb6fc8a6970</t>
+          <t>f346f9bdcc964013ecb7c4282d6b30f1ab334e035d98adcc653de1447fbe9a9a</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2159708</v>
+        <v>14286928</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://ddd.uab.cat/pub/artpub/2017/196242/wasbioval_a2017m7v8n5p1793.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>R13905_2017_The_Effect_of_a_Short_Term_Aerobic_Pretreatment_Step_on_the_Anaerobic_Co_digestion_of_the_Organic_Fr.pdf</t>
+          <t>mmc2.zip</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -39652,35 +39692,35 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>R13932</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>R13932.main.c15f49a3d617e1be</t>
+          <t>R07238.derived.49b84e369d4bb31b</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>c15f49a3d617e1be5e21578ebda1c2d855f8d460c1d66f446ad0d02856a40a13</t>
+          <t>49b84e369d4bb31b4ebdcd25265be3174105c3433e6fbb865f34a445775516a1</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1258157</v>
+        <v>34855493</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://hal.inrae.fr/hal-02620984/document</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>R13932_2018_Comparison_of_pre_and_inter_stage_aerobic_treatment_of_wastewater_sludge_Effects_on_biogas_productio.pdf</t>
+          <t>g a.skp</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -39692,35 +39732,35 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>R13956</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>R13956.main.fedaffcdf5be81e2</t>
+          <t>R08646.supplementary.cfda7e29b12b9784</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>fedaffcdf5be81e2070b7edb0531c332e423578228eeb8c55a6afc4ba8fe1e18</t>
+          <t>cfda7e29b12b97846343963f9f3b64e784bc79644fb1ee1ca31170be78d75327</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>421626</v>
+        <v>42279</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.banglajol.info/index.php/BJSIR/article/download/25579/17152</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>R13956_2015_Anaerobic_digestion_of_mixed_dried_fallen_leaves_by_mixing_with_cow_dung.pdf</t>
+          <t>mmc1.docx</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -39732,35 +39772,35 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>R13955</t>
+          <t>R03161</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>R13955.main.7549e1025985363e</t>
+          <t>R03161.evidence_xml.466f3a1e78e8b0f1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>7549e1025985363e89542bbc1af6eaaa1150bbd62ea43bdd03d2c7b764631f9d</t>
+          <t>466f3a1e78e8b0f148b1f28f97b61f7134c61488c837c5c5a26ef7316cebc1e9</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>14662438</v>
+        <v>59018</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/fullTextXML</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
+          <t>PMC5627928_fullText.xml</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -39772,35 +39812,35 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R03161</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>R07238.supplementary.0b7925ad1ed9c793</t>
+          <t>R03161.transport_archive.0ef4d4796c84feff</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0b7925ad1ed9c7939a79ba6294d17abc4b23fca77e52ec50df5463d050940d1e</t>
+          <t>0ef4d4796c84fefff7b8450bc56400f8c59f4bdcf074fc51404edff5e4e217f6</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>49526</v>
+        <v>726772</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/supplementaryFiles</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>mmc1.docx</t>
+          <t>PMC5627928_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -39812,35 +39852,35 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R04092</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>R07238.supplementary.f346f9bdcc964013</t>
+          <t>R04092.evidence_xml.0fb90085e30680fa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>f346f9bdcc964013ecb7c4282d6b30f1ab334e035d98adcc653de1447fbe9a9a</t>
+          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>14286928</v>
+        <v>77995</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>mmc2.zip</t>
+          <t>PMC6288047_fullText.xml</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -39852,35 +39892,35 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R05839</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>R07238.derived.49b84e369d4bb31b</t>
+          <t>R05839.evidence_xml.18ffd43dee955086</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>49b84e369d4bb31b4ebdcd25265be3174105c3433e6fbb865f34a445775516a1</t>
+          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>34855493</v>
+        <v>75205</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>g a.skp</t>
+          <t>PMC7566014_fullText.xml</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -39892,35 +39932,35 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R08877</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>R08646.supplementary.cfda7e29b12b9784</t>
+          <t>R08877.evidence_xml.e8712e4198baab4c</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>cfda7e29b12b97846343963f9f3b64e784bc79644fb1ee1ca31170be78d75327</t>
+          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>42279</v>
+        <v>111864</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>mmc1.docx</t>
+          <t>PMC10714394_fullText.xml</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -39932,35 +39972,35 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>R03161</t>
+          <t>R08877</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>R03161.evidence_xml.466f3a1e78e8b0f1</t>
+          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>466f3a1e78e8b0f148b1f28f97b61f7134c61488c837c5c5a26ef7316cebc1e9</t>
+          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>59018</v>
+        <v>704921</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>PMC5627928_fullText.xml</t>
+          <t>PMC10714394_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -39972,35 +40012,35 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>R03161</t>
+          <t>R09236</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>R03161.transport_archive.0ef4d4796c84feff</t>
+          <t>R09236.evidence_xml.72064fe9276d8309</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0ef4d4796c84fefff7b8450bc56400f8c59f4bdcf074fc51404edff5e4e217f6</t>
+          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>726772</v>
+        <v>193052</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>PMC5627928_supplementaryFiles.zip</t>
+          <t>PMC10535533_fullText.xml</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -40012,35 +40052,35 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>R04092</t>
+          <t>R09236</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>R04092.evidence_xml.0fb90085e30680fa</t>
+          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
+          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>77995</v>
+        <v>483405</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>PMC6288047_fullText.xml</t>
+          <t>PMC10535533_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -40052,12 +40092,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>R05839</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>R05839.evidence_xml.18ffd43dee955086</t>
+          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -40067,20 +40107,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
+          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>75205</v>
+        <v>118002</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>PMC7566014_fullText.xml</t>
+          <t>PMC10837232_fullText.xml</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -40092,35 +40132,35 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>R08877.evidence_xml.e8712e4198baab4c</t>
+          <t>R10086.transport_archive.4d9eddf454b786ed</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
+          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>111864</v>
+        <v>641038</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>PMC10714394_fullText.xml</t>
+          <t>PMC10837232_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -40132,35 +40172,35 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
+          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
+          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>704921</v>
+        <v>173586</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>PMC10714394_supplementaryFiles.zip</t>
+          <t>PMC12937426_fullText.xml</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -40172,35 +40212,35 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>R09236.evidence_xml.72064fe9276d8309</t>
+          <t>R12985.transport_archive.418d45f1ca296020</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
+          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>193052</v>
+        <v>672244</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>PMC10535533_fullText.xml</t>
+          <t>PMC12937426_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -40212,35 +40252,35 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R05542</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
+          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
+          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>483405</v>
+        <v>100215</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>PMC10535533_supplementaryFiles.zip</t>
+          <t>PMC9056904_fullText.xml</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -40252,12 +40292,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
+          <t>R06325.evidence_xml.645deb707d3790b5</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -40267,20 +40307,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
+          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>118002</v>
+        <v>160509</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>PMC10837232_fullText.xml</t>
+          <t>PMC8290346_fullText.xml</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -40292,12 +40332,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>R10086.transport_archive.4d9eddf454b786ed</t>
+          <t>R06325.transport_archive.6eb4ef126661714a</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -40307,20 +40347,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
+          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>641038</v>
+        <v>1730580</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>PMC10837232_supplementaryFiles.zip</t>
+          <t>PMC8290346_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -40332,12 +40372,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
+          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -40347,20 +40387,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
+          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>173586</v>
+        <v>151458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>PMC12937426_fullText.xml</t>
+          <t>PMC8044681_fullText.xml</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -40372,12 +40412,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>R12985.transport_archive.418d45f1ca296020</t>
+          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -40387,20 +40427,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
+          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>672244</v>
+        <v>14596266</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>PMC12937426_supplementaryFiles.zip</t>
+          <t>PMC8044681_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -40412,12 +40452,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>R05542</t>
+          <t>R03477</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
+          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -40427,20 +40467,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
+          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100215</v>
+        <v>121650</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>PMC9056904_fullText.xml</t>
+          <t>PMC5371168_fullText.xml</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -40452,12 +40492,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>R06325.evidence_xml.645deb707d3790b5</t>
+          <t>R08646.evidence_xml.c7b723e8020f6582</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -40467,20 +40507,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
+          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>160509</v>
+        <v>304277</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>PMC8290346_fullText.xml</t>
+          <t>PMC10559078_fullText.xml</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -40492,12 +40532,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>R06325.transport_archive.6eb4ef126661714a</t>
+          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -40507,20 +40547,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
+          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1730580</v>
+        <v>1539133</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>PMC8290346_supplementaryFiles.zip</t>
+          <t>PMC10559078_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -40532,12 +40572,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R09804</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
+          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -40547,20 +40587,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
+          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>151458</v>
+        <v>211630</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>PMC8044681_fullText.xml</t>
+          <t>PMC11076452_fullText.xml</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -40572,35 +40612,35 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R11503</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
+          <t>R11503.evidence_xml.4002d57be59c215c</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
+          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>14596266</v>
+        <v>258637</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>PMC8044681_supplementaryFiles.zip</t>
+          <t>PMC12561102_fullText.xml</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -40612,12 +40652,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>R03477</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
+          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -40627,20 +40667,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
+          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>121650</v>
+        <v>256247</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>PMC5371168_fullText.xml</t>
+          <t>PMC12125087_fullText.xml</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -40652,35 +40692,35 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>R08646.evidence_xml.c7b723e8020f6582</t>
+          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
+          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>304277</v>
+        <v>521862</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>PMC10559078_fullText.xml</t>
+          <t>PMC12125087_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -40692,35 +40732,35 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
+          <t>R05213.evidence_xml.17894ab410001846</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
+          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1539133</v>
+        <v>130954</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>PMC10559078_supplementaryFiles.zip</t>
+          <t>PMC6858683_fullText.xml</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -40732,35 +40772,35 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
+          <t>R05213.transport_archive.c61c88cf9fd489be</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
+          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>211630</v>
+        <v>1960371</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>PMC11076452_fullText.xml</t>
+          <t>PMC6858683_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -40772,12 +40812,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>R11503</t>
+          <t>R09585</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>R11503.evidence_xml.4002d57be59c215c</t>
+          <t>R09585.evidence_xml.a3430f38fa1652de</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -40787,20 +40827,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
+          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>258637</v>
+        <v>100534</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>PMC12561102_fullText.xml</t>
+          <t>PMC10609292_fullText.xml</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -40812,238 +40852,38 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R11596</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
+          <t>R11596.main.0b2e2d98dffd5449</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
+          <t>0b2e2d98dffd544958b06cc2229d310e4b7d529bd3914c47f20d6a66789a28be</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>256247</v>
+        <v>1659399</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
+          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/7262c516-6b14-4001-a173-517d1187c8d9/content</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>PMC12125087_fullText.xml</t>
+          <t>R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>R11844</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>transport_archive</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>521862</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>PMC12125087_supplementaryFiles.zip</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>R05213</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>R05213.evidence_xml.17894ab410001846</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>evidence_xml</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>130954</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>PMC6858683_fullText.xml</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>R05213</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>R05213.transport_archive.c61c88cf9fd489be</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>transport_archive</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>1960371</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>PMC6858683_supplementaryFiles.zip</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>R09585</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>R09585.evidence_xml.a3430f38fa1652de</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>evidence_xml</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>100534</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>PMC10609292_fullText.xml</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>R11596</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>R11596.main.0b2e2d98dffd5449</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>0b2e2d98dffd544958b06cc2229d310e4b7d529bd3914c47f20d6a66789a28be</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>1659399</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/7262c516-6b14-4001-a173-517d1187c8d9/content</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
         <is>
           <t>历史已获取，当前原件未恢复</t>
         </is>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -6982,7 +6982,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.811991+00:00</t>
+          <t>2026-10-17T08:31:28.993751+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.813153+00:00</t>
+          <t>2026-10-17T08:31:28.994695+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.813181+00:00</t>
+          <t>2026-10-17T08:31:28.994719+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.813428+00:00</t>
+          <t>2026-10-17T08:31:28.994934+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.814635+00:00</t>
+          <t>2026-10-17T08:31:28.996082+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.815153+00:00</t>
+          <t>2026-10-17T08:31:28.996557+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.820691+00:00</t>
+          <t>2026-10-17T08:31:29.002707+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.823145+00:00</t>
+          <t>2026-10-17T08:31:29.005018+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.824089+00:00</t>
+          <t>2026-10-17T08:31:29.005907+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.824676+00:00</t>
+          <t>2026-10-17T08:31:29.006218+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.825398+00:00</t>
+          <t>2026-10-17T08:31:29.006922+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.826068+00:00</t>
+          <t>2026-10-17T08:31:29.007565+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.827017+00:00</t>
+          <t>2026-10-17T08:31:29.008442+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.827279+00:00</t>
+          <t>2026-10-17T08:31:29.008668+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.828154+00:00</t>
+          <t>2026-10-17T08:31:29.009536+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.837004+00:00</t>
+          <t>2026-10-17T08:31:29.017400+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.837782+00:00</t>
+          <t>2026-10-17T08:31:29.018112+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.839002+00:00</t>
+          <t>2026-10-17T08:31:29.019564+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.841840+00:00</t>
+          <t>2026-10-17T08:31:29.022148+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.843085+00:00</t>
+          <t>2026-10-17T08:31:29.023217+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.844299+00:00</t>
+          <t>2026-10-17T08:31:29.024451+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.848756+00:00</t>
+          <t>2026-10-17T08:31:29.028967+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.851190+00:00</t>
+          <t>2026-10-17T08:31:29.031246+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.853013+00:00</t>
+          <t>2026-10-17T08:31:29.033013+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.853701+00:00</t>
+          <t>2026-10-17T08:31:29.033671+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.854077+00:00</t>
+          <t>2026-10-17T08:31:29.034014+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.856050+00:00</t>
+          <t>2026-10-17T08:31:29.035955+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.857269+00:00</t>
+          <t>2026-10-17T08:31:29.037156+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.859717+00:00</t>
+          <t>2026-10-17T08:31:29.039182+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.861830+00:00</t>
+          <t>2026-10-17T08:31:29.041093+00:00</t>
         </is>
       </c>
     </row>
@@ -27571,7 +27571,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.861861+00:00</t>
+          <t>2026-10-17T08:31:29.041109+00:00</t>
         </is>
       </c>
     </row>
@@ -27679,7 +27679,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.862453+00:00</t>
+          <t>2026-10-17T08:31:29.041695+00:00</t>
         </is>
       </c>
     </row>
@@ -27787,7 +27787,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.864374+00:00</t>
+          <t>2026-10-17T08:31:29.043379+00:00</t>
         </is>
       </c>
     </row>
@@ -27895,7 +27895,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.867680+00:00</t>
+          <t>2026-10-17T08:31:29.046370+00:00</t>
         </is>
       </c>
     </row>
@@ -28003,7 +28003,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.869860+00:00</t>
+          <t>2026-10-17T08:31:29.048417+00:00</t>
         </is>
       </c>
     </row>
@@ -28111,7 +28111,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.871044+00:00</t>
+          <t>2026-10-17T08:31:29.049641+00:00</t>
         </is>
       </c>
     </row>
@@ -28219,7 +28219,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.873865+00:00</t>
+          <t>2026-10-17T08:31:29.052641+00:00</t>
         </is>
       </c>
     </row>
@@ -28327,7 +28327,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.874561+00:00</t>
+          <t>2026-10-17T08:31:29.053338+00:00</t>
         </is>
       </c>
     </row>
@@ -28435,7 +28435,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.876112+00:00</t>
+          <t>2026-10-17T08:31:29.054950+00:00</t>
         </is>
       </c>
     </row>
@@ -28543,7 +28543,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.876382+00:00</t>
+          <t>2026-10-17T08:31:29.055196+00:00</t>
         </is>
       </c>
     </row>
@@ -28579,13 +28579,21 @@
           <t>papers/R08646/main/7df5523334e7_R08646_2023_Approaches_to_mitigation_of_hydrogen_sulfide_during_anaerobic_digestion.pdf</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R08646_2023_Approaches_to_mitigation_of_hydrogen_sulfide_during_anaerobic_digestion.pdf</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R08646_2023_Approaches_to_mitigation_of_hydrogen_sulfide_during_anaerobic_digestion.pdf</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R08646_2023_Approaches_to_mitigation_of_hydrogen_sulfide_during_anaerobic_digestion.pdf</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -28601,12 +28609,12 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -28643,7 +28651,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.876396+00:00</t>
+          <t>2026-10-17T08:31:29.057047+00:00</t>
         </is>
       </c>
     </row>
@@ -28751,7 +28759,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.879197+00:00</t>
+          <t>2026-10-17T08:31:29.060164+00:00</t>
         </is>
       </c>
     </row>
@@ -28787,13 +28795,21 @@
           <t>papers/R10894/main/f9caf3b730e2_R10894_2024_The_effects_of_different_pretreatment_technologies_on_microbial_community.pdf</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R10894_2024_The_effects_of_different_pretreatment_technologies_on_microbial_community.pdf</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R10894_2024_The_effects_of_different_pretreatment_technologies_on_microbial_community.pdf</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R10894_2024_The_effects_of_different_pretreatment_technologies_on_microbial_community.pdf</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -28809,12 +28825,12 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -28851,7 +28867,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.879216+00:00</t>
+          <t>2026-10-17T08:31:29.061621+00:00</t>
         </is>
       </c>
     </row>
@@ -28959,7 +28975,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.879738+00:00</t>
+          <t>2026-10-17T08:31:29.062243+00:00</t>
         </is>
       </c>
     </row>
@@ -28995,13 +29011,21 @@
           <t>papers/R06737/main/32eabc0a46b3_R06737_2021_Genomic_driven_factors_enhance_biocatalyst-related_cellulolysis_potential_in_anaerobic.pdf</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R06737_2021_Genomic_driven_factors_enhance_biocatalyst-related_cellulolysis_potential_in_anaerobic.pdf</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R06737_2021_Genomic_driven_factors_enhance_biocatalyst-related_cellulolysis_potential_in_anaerobic.pdf</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R06737_2021_Genomic_driven_factors_enhance_biocatalyst-related_cellulolysis_potential_in_anaerobic.pdf</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -29017,12 +29041,12 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -29059,7 +29083,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.879752+00:00</t>
+          <t>2026-10-17T08:31:29.064870+00:00</t>
         </is>
       </c>
     </row>
@@ -29095,13 +29119,21 @@
           <t>papers/R04119/main/c9b1902447e3_R04119_2018_Microbial_pretreatment_of_lignocellulosic_biomass_for_enhanced_biomethanation_and.pdf</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R04119_2018_Microbial_pretreatment_of_lignocellulosic_biomass_for_enhanced_biomethanation_and.pdf</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R04119_2018_Microbial_pretreatment_of_lignocellulosic_biomass_for_enhanced_biomethanation_and.pdf</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R04119_2018_Microbial_pretreatment_of_lignocellulosic_biomass_for_enhanced_biomethanation_and.pdf</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -29117,12 +29149,12 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -29159,7 +29191,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.879756+00:00</t>
+          <t>2026-10-17T08:31:29.066041+00:00</t>
         </is>
       </c>
     </row>
@@ -29195,13 +29227,21 @@
           <t>papers/R00273/main/2059ae72be92_R00273_2012_Management_of_hydrogen_sulfide_in_anaerobic_digestion_of_enzyme.pdf</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R00273_2012_Management_of_hydrogen_sulfide_in_anaerobic_digestion_of_enzyme.pdf</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R00273_2012_Management_of_hydrogen_sulfide_in_anaerobic_digestion_of_enzyme.pdf</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R00273_2012_Management_of_hydrogen_sulfide_in_anaerobic_digestion_of_enzyme.pdf</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -29217,12 +29257,12 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -29259,7 +29299,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.879759+00:00</t>
+          <t>2026-10-17T08:31:29.069520+00:00</t>
         </is>
       </c>
     </row>
@@ -29367,7 +29407,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.881343+00:00</t>
+          <t>2026-10-17T08:31:29.071134+00:00</t>
         </is>
       </c>
     </row>
@@ -29467,7 +29507,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.881357+00:00</t>
+          <t>2026-10-17T08:31:29.071151+00:00</t>
         </is>
       </c>
     </row>
@@ -29567,7 +29607,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.881361+00:00</t>
+          <t>2026-10-17T08:31:29.071157+00:00</t>
         </is>
       </c>
     </row>
@@ -29675,7 +29715,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.881786+00:00</t>
+          <t>2026-10-17T08:31:29.071586+00:00</t>
         </is>
       </c>
     </row>
@@ -29775,7 +29815,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.881799+00:00</t>
+          <t>2026-10-17T08:31:29.071601+00:00</t>
         </is>
       </c>
     </row>
@@ -29883,7 +29923,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.883348+00:00</t>
+          <t>2026-10-17T08:31:29.073027+00:00</t>
         </is>
       </c>
     </row>
@@ -29991,7 +30031,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.884628+00:00</t>
+          <t>2026-10-17T08:31:29.074308+00:00</t>
         </is>
       </c>
     </row>
@@ -30091,7 +30131,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.884643+00:00</t>
+          <t>2026-10-17T08:31:29.074327+00:00</t>
         </is>
       </c>
     </row>
@@ -30191,7 +30231,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.884647+00:00</t>
+          <t>2026-10-17T08:31:29.074330+00:00</t>
         </is>
       </c>
     </row>
@@ -30291,7 +30331,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.884651+00:00</t>
+          <t>2026-10-17T08:31:29.074334+00:00</t>
         </is>
       </c>
     </row>
@@ -30391,7 +30431,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.884653+00:00</t>
+          <t>2026-10-17T08:31:29.074337+00:00</t>
         </is>
       </c>
     </row>
@@ -30499,7 +30539,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.885197+00:00</t>
+          <t>2026-10-17T08:31:29.074884+00:00</t>
         </is>
       </c>
     </row>
@@ -30599,7 +30639,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.885210+00:00</t>
+          <t>2026-10-17T08:31:29.074898+00:00</t>
         </is>
       </c>
     </row>
@@ -30699,7 +30739,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.885214+00:00</t>
+          <t>2026-10-17T08:31:29.074901+00:00</t>
         </is>
       </c>
     </row>
@@ -30799,7 +30839,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.885217+00:00</t>
+          <t>2026-10-17T08:31:29.074904+00:00</t>
         </is>
       </c>
     </row>
@@ -30899,7 +30939,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.885220+00:00</t>
+          <t>2026-10-17T08:31:29.074907+00:00</t>
         </is>
       </c>
     </row>
@@ -30999,7 +31039,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.885223+00:00</t>
+          <t>2026-10-17T08:31:29.074910+00:00</t>
         </is>
       </c>
     </row>
@@ -31107,7 +31147,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.885672+00:00</t>
+          <t>2026-10-17T08:31:29.075334+00:00</t>
         </is>
       </c>
     </row>
@@ -31215,7 +31255,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.886715+00:00</t>
+          <t>2026-10-17T08:31:29.076367+00:00</t>
         </is>
       </c>
     </row>
@@ -31323,7 +31363,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.889652+00:00</t>
+          <t>2026-10-17T08:31:29.079382+00:00</t>
         </is>
       </c>
     </row>
@@ -31423,7 +31463,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.889671+00:00</t>
+          <t>2026-10-17T08:31:29.079407+00:00</t>
         </is>
       </c>
     </row>
@@ -31531,7 +31571,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.893917+00:00</t>
+          <t>2026-10-17T08:31:29.083652+00:00</t>
         </is>
       </c>
     </row>
@@ -31631,7 +31671,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.893952+00:00</t>
+          <t>2026-10-17T08:31:29.083682+00:00</t>
         </is>
       </c>
     </row>
@@ -31739,7 +31779,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.896133+00:00</t>
+          <t>2026-10-17T08:31:29.086002+00:00</t>
         </is>
       </c>
     </row>
@@ -31847,7 +31887,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.897997+00:00</t>
+          <t>2026-10-17T08:31:29.087801+00:00</t>
         </is>
       </c>
     </row>
@@ -31947,7 +31987,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.898030+00:00</t>
+          <t>2026-10-17T08:31:29.087827+00:00</t>
         </is>
       </c>
     </row>
@@ -32047,7 +32087,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.898035+00:00</t>
+          <t>2026-10-17T08:31:29.087831+00:00</t>
         </is>
       </c>
     </row>
@@ -32147,7 +32187,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.898038+00:00</t>
+          <t>2026-10-17T08:31:29.087834+00:00</t>
         </is>
       </c>
     </row>
@@ -32247,7 +32287,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.898041+00:00</t>
+          <t>2026-10-17T08:31:29.087837+00:00</t>
         </is>
       </c>
     </row>
@@ -32355,7 +32395,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.899307+00:00</t>
+          <t>2026-10-17T08:31:29.089025+00:00</t>
         </is>
       </c>
     </row>
@@ -32455,7 +32495,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.899337+00:00</t>
+          <t>2026-10-17T08:31:29.089045+00:00</t>
         </is>
       </c>
     </row>
@@ -32555,7 +32595,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.899343+00:00</t>
+          <t>2026-10-17T08:31:29.089049+00:00</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32695,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.899347+00:00</t>
+          <t>2026-10-17T08:31:29.089052+00:00</t>
         </is>
       </c>
     </row>
@@ -32751,7 +32791,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.899352+00:00</t>
+          <t>2026-10-17T08:31:29.089055+00:00</t>
         </is>
       </c>
     </row>
@@ -32847,7 +32887,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.899356+00:00</t>
+          <t>2026-10-17T08:31:29.089058+00:00</t>
         </is>
       </c>
     </row>
@@ -32943,7 +32983,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.899360+00:00</t>
+          <t>2026-10-17T08:31:29.089062+00:00</t>
         </is>
       </c>
     </row>
@@ -33039,7 +33079,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.899365+00:00</t>
+          <t>2026-10-17T08:31:29.089065+00:00</t>
         </is>
       </c>
     </row>
@@ -33135,7 +33175,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.899368+00:00</t>
+          <t>2026-10-17T08:31:29.089068+00:00</t>
         </is>
       </c>
     </row>
@@ -33231,7 +33271,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.899372+00:00</t>
+          <t>2026-10-17T08:31:29.089070+00:00</t>
         </is>
       </c>
     </row>
@@ -33327,7 +33367,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.899376+00:00</t>
+          <t>2026-10-17T08:31:29.089073+00:00</t>
         </is>
       </c>
     </row>
@@ -33435,7 +33475,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.900155+00:00</t>
+          <t>2026-10-17T08:31:29.089883+00:00</t>
         </is>
       </c>
     </row>
@@ -33535,7 +33575,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.900177+00:00</t>
+          <t>2026-10-17T08:31:29.089951+00:00</t>
         </is>
       </c>
     </row>
@@ -33643,7 +33683,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.900231+00:00</t>
+          <t>2026-10-17T08:31:29.090007+00:00</t>
         </is>
       </c>
     </row>
@@ -33751,7 +33791,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.900571+00:00</t>
+          <t>2026-10-17T08:31:29.090225+00:00</t>
         </is>
       </c>
     </row>
@@ -33859,7 +33899,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.900873+00:00</t>
+          <t>2026-10-17T08:31:29.090363+00:00</t>
         </is>
       </c>
     </row>
@@ -33971,7 +34011,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.901038+00:00</t>
+          <t>2026-10-17T08:31:29.090484+00:00</t>
         </is>
       </c>
     </row>
@@ -34079,7 +34119,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.901461+00:00</t>
+          <t>2026-10-17T08:31:29.090851+00:00</t>
         </is>
       </c>
     </row>
@@ -34187,7 +34227,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.901696+00:00</t>
+          <t>2026-10-17T08:31:29.091031+00:00</t>
         </is>
       </c>
     </row>
@@ -34299,7 +34339,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.901753+00:00</t>
+          <t>2026-10-17T08:31:29.091083+00:00</t>
         </is>
       </c>
     </row>
@@ -34411,7 +34451,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.901818+00:00</t>
+          <t>2026-10-17T08:31:29.091146+00:00</t>
         </is>
       </c>
     </row>
@@ -34523,7 +34563,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.902135+00:00</t>
+          <t>2026-10-17T08:31:29.091302+00:00</t>
         </is>
       </c>
     </row>
@@ -34635,7 +34675,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.902198+00:00</t>
+          <t>2026-10-17T08:31:29.091348+00:00</t>
         </is>
       </c>
     </row>
@@ -34743,7 +34783,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.902780+00:00</t>
+          <t>2026-10-17T08:31:29.091805+00:00</t>
         </is>
       </c>
     </row>
@@ -34851,7 +34891,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.902847+00:00</t>
+          <t>2026-10-17T08:31:29.091851+00:00</t>
         </is>
       </c>
     </row>
@@ -34951,7 +34991,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.902875+00:00</t>
+          <t>2026-10-17T08:31:29.091862+00:00</t>
         </is>
       </c>
     </row>
@@ -35051,7 +35091,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.902880+00:00</t>
+          <t>2026-10-17T08:31:29.091865+00:00</t>
         </is>
       </c>
     </row>
@@ -35155,7 +35195,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.902883+00:00</t>
+          <t>2026-10-17T08:31:29.091869+00:00</t>
         </is>
       </c>
     </row>
@@ -35255,7 +35295,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.902886+00:00</t>
+          <t>2026-10-17T08:31:29.091871+00:00</t>
         </is>
       </c>
     </row>
@@ -35363,7 +35403,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.903118+00:00</t>
+          <t>2026-10-17T08:31:29.092078+00:00</t>
         </is>
       </c>
     </row>
@@ -35471,7 +35511,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904207+00:00</t>
+          <t>2026-10-17T08:31:29.093035+00:00</t>
         </is>
       </c>
     </row>
@@ -35565,7 +35605,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904232+00:00</t>
+          <t>2026-10-17T08:31:29.093051+00:00</t>
         </is>
       </c>
     </row>
@@ -35659,7 +35699,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904237+00:00</t>
+          <t>2026-10-17T08:31:29.093055+00:00</t>
         </is>
       </c>
     </row>
@@ -35753,7 +35793,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904240+00:00</t>
+          <t>2026-10-17T08:31:29.093058+00:00</t>
         </is>
       </c>
     </row>
@@ -35847,7 +35887,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904244+00:00</t>
+          <t>2026-10-17T08:31:29.093061+00:00</t>
         </is>
       </c>
     </row>
@@ -35941,7 +35981,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904246+00:00</t>
+          <t>2026-10-17T08:31:29.093064+00:00</t>
         </is>
       </c>
     </row>
@@ -36035,7 +36075,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904250+00:00</t>
+          <t>2026-10-17T08:31:29.093068+00:00</t>
         </is>
       </c>
     </row>
@@ -36129,7 +36169,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904253+00:00</t>
+          <t>2026-10-17T08:31:29.093071+00:00</t>
         </is>
       </c>
     </row>
@@ -36223,7 +36263,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904255+00:00</t>
+          <t>2026-10-17T08:31:29.093074+00:00</t>
         </is>
       </c>
     </row>
@@ -36317,7 +36357,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904258+00:00</t>
+          <t>2026-10-17T08:31:29.093077+00:00</t>
         </is>
       </c>
     </row>
@@ -36411,7 +36451,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904261+00:00</t>
+          <t>2026-10-17T08:31:29.093081+00:00</t>
         </is>
       </c>
     </row>
@@ -36505,7 +36545,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904264+00:00</t>
+          <t>2026-10-17T08:31:29.093084+00:00</t>
         </is>
       </c>
     </row>
@@ -36599,7 +36639,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904267+00:00</t>
+          <t>2026-10-17T08:31:29.093087+00:00</t>
         </is>
       </c>
     </row>
@@ -36693,7 +36733,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904270+00:00</t>
+          <t>2026-10-17T08:31:29.093090+00:00</t>
         </is>
       </c>
     </row>
@@ -36787,7 +36827,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904273+00:00</t>
+          <t>2026-10-17T08:31:29.093092+00:00</t>
         </is>
       </c>
     </row>
@@ -36881,7 +36921,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904276+00:00</t>
+          <t>2026-10-17T08:31:29.093095+00:00</t>
         </is>
       </c>
     </row>
@@ -36975,7 +37015,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904279+00:00</t>
+          <t>2026-10-17T08:31:29.093098+00:00</t>
         </is>
       </c>
     </row>
@@ -37069,7 +37109,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904425+00:00</t>
+          <t>2026-10-17T08:31:29.093101+00:00</t>
         </is>
       </c>
     </row>
@@ -37163,7 +37203,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904429+00:00</t>
+          <t>2026-10-17T08:31:29.093104+00:00</t>
         </is>
       </c>
     </row>
@@ -37257,7 +37297,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904433+00:00</t>
+          <t>2026-10-17T08:31:29.093107+00:00</t>
         </is>
       </c>
     </row>
@@ -37351,7 +37391,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904435+00:00</t>
+          <t>2026-10-17T08:31:29.093111+00:00</t>
         </is>
       </c>
     </row>
@@ -37445,7 +37485,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904439+00:00</t>
+          <t>2026-10-17T08:31:29.093114+00:00</t>
         </is>
       </c>
     </row>
@@ -37539,7 +37579,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904442+00:00</t>
+          <t>2026-10-17T08:31:29.093116+00:00</t>
         </is>
       </c>
     </row>
@@ -37633,7 +37673,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904445+00:00</t>
+          <t>2026-10-17T08:31:29.093119+00:00</t>
         </is>
       </c>
     </row>
@@ -37727,7 +37767,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904448+00:00</t>
+          <t>2026-10-17T08:31:29.093122+00:00</t>
         </is>
       </c>
     </row>
@@ -37821,7 +37861,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904451+00:00</t>
+          <t>2026-10-17T08:31:29.093126+00:00</t>
         </is>
       </c>
     </row>
@@ -37915,7 +37955,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904454+00:00</t>
+          <t>2026-10-17T08:31:29.093129+00:00</t>
         </is>
       </c>
     </row>
@@ -38009,7 +38049,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904458+00:00</t>
+          <t>2026-10-17T08:31:29.093132+00:00</t>
         </is>
       </c>
     </row>
@@ -38109,7 +38149,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T08:30:22.904461+00:00</t>
+          <t>2026-10-17T08:31:29.093135+00:00</t>
         </is>
       </c>
     </row>
@@ -38124,7 +38164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38252,12 +38292,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R04700</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R08646.main.7df5523334e7d1bb</t>
+          <t>R04700.main.40ac0de29f75851c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -38267,20 +38307,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7df5523334e7d1bb513d2a3deb5b018c0c9b2a3ea9e49b7ff8f09a1fe853cd96</t>
+          <t>40ac0de29f75851cab1651e1e339d03329bb7ce0141519329487f0559ebd8297</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3009960</v>
+        <v>2892628</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://europepmc.org/api/getPdf?pmcid=PMC10559078</t>
+          <t>https://repository.tudelft.nl/file/File_d8b73973-6e26-4f66-9162-3212f6b93431</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>R08646_2023_Approaches_to_mitigation_of_hydrogen_sulfide_during_anaerobic_digestion.pdf</t>
+          <t>R04700_2019_Effect_of_aeration_by_micro_-_bubbles_on_methane.pdf</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -38292,12 +38332,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R10894</t>
+          <t>R09568</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R10894.main.f9caf3b730e23f0d</t>
+          <t>R09568.main.393322098ea47587</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -38307,20 +38347,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>f9caf3b730e23f0d9d31d71069935c39e162415bbdac53ee97821305a81be9d2</t>
+          <t>393322098ea4758738b0e338c3e0019bd8618611d25a41cf3535d9542a6c8d16</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2030435</v>
+        <v>1433947</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://europepmc.org/api/getPdf?pmcid=PMC11499478</t>
+          <t>https://repository.tudelft.nl/file/File_b3a1ee42-17d3-4f7d-82dc-616c91a5a6bf</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>R10894_2024_The_effects_of_different_pretreatment_technologies_on_microbial_community.pdf</t>
+          <t>R09568_2023_The_fate_of_sulfamethoxazole_and_trimethoprim_in_a_micro-aerated.pdf</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -38332,12 +38372,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R06737</t>
+          <t>R10290</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R06737.main.32eabc0a46b31862</t>
+          <t>R10290.main.0a63bc6c89e8dff8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -38347,20 +38387,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>32eabc0a46b31862fa95a7bcf29fc4e5b154b7ec51c11cd1d4f798bbad95b59a</t>
+          <t>0a63bc6c89e8dff87ff1b364322ce6738e4fc87f505478ef522e7c73b7db342f</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4126947</v>
+        <v>530753</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://ira.lib.polyu.edu.hk/bitstream/10397/97386/1/Zhuang_Genomic_Driven_Factors.pdf</t>
+          <t>https://office.nbc-journal.org/index.php/NBC/article/download/2100/955</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>R06737_2021_Genomic_driven_factors_enhance_biocatalyst-related_cellulolysis_potential_in_anaerobic.pdf</t>
+          <t>R10290_2024_Gas_nanobubble_technology_in_wastewater_treatment_and_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -38372,12 +38412,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R04119</t>
+          <t>R10724</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R04119.main.c9b1902447e38978</t>
+          <t>R10724.main.cfdc1bcb235acdd7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -38387,20 +38427,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>c9b1902447e38978d2f6f25327940f80e825baee1ebabba8bd8a860ed1fa254c</t>
+          <t>cfdc1bcb235acdd703e58447b30b31cb8c4e8d53d1c86999ee8ecdafbba1e8aa</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1726821</v>
+        <v>2366242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://europepmc.org/api/getPdf?pmcid=PMC6197294</t>
+          <t>https://www.ecoeet.com/pdf-181210-105068?filename=Protection-of-the-Purific.pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>R04119_2018_Microbial_pretreatment_of_lignocellulosic_biomass_for_enhanced_biomethanation_and.pdf</t>
+          <t>R10724_2024_Protection_of_the_Purification_Station_Thermal_Engines_Against_the.pdf</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -38412,12 +38452,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R00273</t>
+          <t>R11658</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R00273.main.2059ae72be92bd0e</t>
+          <t>R11658.main.83a514a4b04c73a0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -38427,20 +38467,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2059ae72be92bd0e0928b31eb73f27d1f92ac15865050966ba9369eae1ac9c0c</t>
+          <t>83a514a4b04c73a09129c21d623d57eb798a3af7c20dc842d47308f889d7695f</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5372083</v>
+        <v>458052</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://lup.lub.lu.se/luur/download?func=downloadFile&amp;recordOId=5277171&amp;fileOId=5277177</t>
+          <t>https://bsuj.bsu.edu.az/readpdf.php?file=236e3d6763a43f726c9814e7b5de8bc1.pdf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>R00273_2012_Management_of_hydrogen_sulfide_in_anaerobic_digestion_of_enzyme.pdf</t>
+          <t>R11658_2025_IMPACT_OF_MICRO-AERATION_ON_FUNGAL_COMMUNITY_FROM_ANAEROBIC_DIGESTION.pdf</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -38452,12 +38492,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R04700</t>
+          <t>R12483</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R04700.main.40ac0de29f75851c</t>
+          <t>R12483.main.b51428ca89e5bf95</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -38467,20 +38507,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>40ac0de29f75851cab1651e1e339d03329bb7ce0141519329487f0559ebd8297</t>
+          <t>b51428ca89e5bf95c17225fe2e0a08a920379629281ab76f33337561553f3b0f</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2892628</v>
+        <v>1807518</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://repository.tudelft.nl/file/File_d8b73973-6e26-4f66-9162-3212f6b93431</t>
+          <t>https://li01.tci-thaijo.org/index.php/TSAEJ/article/download/269146/181297</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>R04700_2019_Effect_of_aeration_by_micro_-_bubbles_on_methane.pdf</t>
+          <t>R12483_2025_การปรบสภาพชวมวลลกโนเซลลโลสดวยวสดเพาะเหดเหลอทง_แนวทางการเพมมล.pdf</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -38492,12 +38532,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R09568</t>
+          <t>R13819</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R09568.main.393322098ea47587</t>
+          <t>R13819.main.431f5e76781d3cef</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -38507,20 +38547,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>393322098ea4758738b0e338c3e0019bd8618611d25a41cf3535d9542a6c8d16</t>
+          <t>431f5e76781d3cef39588c258c5589b1c9cf01db486c503ba29ab166bc73f14a</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1433947</v>
+        <v>2172752</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://repository.tudelft.nl/file/File_b3a1ee42-17d3-4f7d-82dc-616c91a5a6bf</t>
+          <t>https://epublications.marquette.edu/cgi/viewcontent.cgi?article=1131&amp;context=civengin_fac</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>R09568_2023_The_fate_of_sulfamethoxazole_and_trimethoprim_in_a_micro-aerated.pdf</t>
+          <t>R13819_2015_Bioaugmentation_of_overloaded_anaerobic_digesters_restores_function_and_archaeal.pdf</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -38532,12 +38572,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R10290</t>
+          <t>R13833</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R10290.main.0a63bc6c89e8dff8</t>
+          <t>R13833.main.1a4a4d5f8fd45de9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -38547,20 +38587,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0a63bc6c89e8dff87ff1b364322ce6738e4fc87f505478ef522e7c73b7db342f</t>
+          <t>1a4a4d5f8fd45de924c78a7be11e1c032c630bd9341431d1d49135c8351cdaf7</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>530753</v>
+        <v>1463714</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://office.nbc-journal.org/index.php/NBC/article/download/2100/955</t>
+          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/234ac4ff-f996-498f-8853-72ba22cb7700/content</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>R10290_2024_Gas_nanobubble_technology_in_wastewater_treatment_and_anaerobic_digestion.pdf</t>
+          <t>R13833_2018_Insight_into_the_Role_of_Facultative_Bacteria_Stimulated_by.pdf</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -38572,12 +38612,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R10724</t>
+          <t>R13861</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R10724.main.cfdc1bcb235acdd7</t>
+          <t>R13861.main.ba6f44b77d79c4a0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -38587,20 +38627,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>cfdc1bcb235acdd703e58447b30b31cb8c4e8d53d1c86999ee8ecdafbba1e8aa</t>
+          <t>ba6f44b77d79c4a07ba08602860bcf1bdbb36cb47b4527fa9d1f087825e394d8</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2366242</v>
+        <v>433474</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.ecoeet.com/pdf-181210-105068?filename=Protection-of-the-Purific.pdf</t>
+          <t>https://www.scielo.br/j/esa/a/BD6Bc5rMVrTsbkK7CZz6yVd/?format=pdf&amp;lang=en&amp;ilang=pt_BR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>R10724_2024_Protection_of_the_Purification_Station_Thermal_Engines_Against_the.pdf</t>
+          <t>R13861_2019_Enhanced_removal_of_emerging_micropollutants_by_applying_microaeration_to.pdf</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -38612,12 +38652,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R11658</t>
+          <t>R13871</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R11658.main.83a514a4b04c73a0</t>
+          <t>R13871.main.aeab3126b6e68775</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -38627,20 +38667,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>83a514a4b04c73a09129c21d623d57eb798a3af7c20dc842d47308f889d7695f</t>
+          <t>aeab3126b6e68775b9b316714633bd97c1f184cf9e308d75b404bca6b33be19f</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>458052</v>
+        <v>7983514</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://bsuj.bsu.edu.az/readpdf.php?file=236e3d6763a43f726c9814e7b5de8bc1.pdf</t>
+          <t>https://etheses.whiterose.ac.uk/id/eprint/4094/6/Mahmood_Khazzal_Hummadi_Al-Mashhadani._Reg._No._080243946_%28PhD_thesis%29_2013.pdf</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>R11658_2025_IMPACT_OF_MICRO-AERATION_ON_FUNGAL_COMMUNITY_FROM_ANAEROBIC_DIGESTION.pdf</t>
+          <t>R13871_2013_Application_of_Microbubbles_Generated_by_Fluidic_Oscillation_in_the.pdf</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -38652,12 +38692,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R12483</t>
+          <t>R13877</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R12483.main.b51428ca89e5bf95</t>
+          <t>R13877.main.04a76adc76fa9472</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -38667,20 +38707,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>b51428ca89e5bf95c17225fe2e0a08a920379629281ab76f33337561553f3b0f</t>
+          <t>04a76adc76fa947250861c95c93759c590dd3e02d7f80dc23ce0abedccb74510</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1807518</v>
+        <v>522402</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://li01.tci-thaijo.org/index.php/TSAEJ/article/download/269146/181297</t>
+          <t>https://escholarship.org/content/qt5572k7rw/qt5572k7rw.pdf</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>R12483_2025_การปรบสภาพชวมวลลกโนเซลลโลสดวยวสดเพาะเหดเหลอทง_แนวทางการเพมมล.pdf</t>
+          <t>R13877_2018_Microbial_community_response_and_SDS-PAGE_reveal_possible_mechanism_of.pdf</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -38692,12 +38732,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R13819</t>
+          <t>R13862</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R13819.main.431f5e76781d3cef</t>
+          <t>R13862.main.64e03a9beb5813a0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -38707,20 +38747,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>431f5e76781d3cef39588c258c5589b1c9cf01db486c503ba29ab166bc73f14a</t>
+          <t>64e03a9beb5813a0ce6d94272350217f12dac94293420969e3d2d9d7975e96e3</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2172752</v>
+        <v>833659</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://epublications.marquette.edu/cgi/viewcontent.cgi?article=1131&amp;context=civengin_fac</t>
+          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/eb850f96-0570-4e0d-be55-73fcee5f1364/content</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>R13819_2015_Bioaugmentation_of_overloaded_anaerobic_digesters_restores_function_and_archaeal.pdf</t>
+          <t>R13862_2020_Multiple_and_flexible_roles_of_facultative_anaerobic_bacteria_in.pdf</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -38732,12 +38772,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R13833</t>
+          <t>R13900</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R13833.main.1a4a4d5f8fd45de9</t>
+          <t>R13900.main.b2ba7df8c04ab66c</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -38747,20 +38787,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1a4a4d5f8fd45de924c78a7be11e1c032c630bd9341431d1d49135c8351cdaf7</t>
+          <t>b2ba7df8c04ab66c0e548f778e19c5764802c0da8408a3b8499547b3f6ef51b3</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1463714</v>
+        <v>299244</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/234ac4ff-f996-498f-8853-72ba22cb7700/content</t>
+          <t>https://www.research.unipd.it/bitstream/11577/3261852/1/Front.%20Environ.%20Sci.%20Eng%20Dongbei%202018.pdf</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>R13833_2018_Insight_into_the_Role_of_Facultative_Bacteria_Stimulated_by.pdf</t>
+          <t>R13900_2018_Effectiveness_of_aerobic_pretreatment_of_municipal_solid_waste_for.pdf</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -38772,12 +38812,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R13861</t>
+          <t>R13903</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R13861.main.ba6f44b77d79c4a0</t>
+          <t>R13903.main.2cd9e7b409250e7b</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -38787,20 +38827,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ba6f44b77d79c4a07ba08602860bcf1bdbb36cb47b4527fa9d1f087825e394d8</t>
+          <t>2cd9e7b409250e7b104f489e139f57d4daa40d97133c6c57c937184c3ec73b71</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>433474</v>
+        <v>1107675</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.scielo.br/j/esa/a/BD6Bc5rMVrTsbkK7CZz6yVd/?format=pdf&amp;lang=en&amp;ilang=pt_BR</t>
+          <t>https://ijabe.org/index.php/ijabe/article/download/7975/pdf</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>R13861_2019_Enhanced_removal_of_emerging_micropollutants_by_applying_microaeration_to.pdf</t>
+          <t>R13903_2023_Effect_of_vacuum_negative_pressure_aerobic_hydrolysis_pretreatment_on.pdf</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -38812,12 +38852,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R13871</t>
+          <t>R13931</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R13871.main.aeab3126b6e68775</t>
+          <t>R13931.main.6e898a403edac7b3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -38827,20 +38867,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>aeab3126b6e68775b9b316714633bd97c1f184cf9e308d75b404bca6b33be19f</t>
+          <t>6e898a403edac7b3ae15ad88cf75788898cd84ea377b2572f7bab40d9c126f8c</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7983514</v>
+        <v>1324593</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://etheses.whiterose.ac.uk/id/eprint/4094/6/Mahmood_Khazzal_Hummadi_Al-Mashhadani._Reg._No._080243946_%28PhD_thesis%29_2013.pdf</t>
+          <t>https://www.eeer.org/upload/eer-2020-470.pdf</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>R13871_2013_Application_of_Microbubbles_Generated_by_Fluidic_Oscillation_in_the.pdf</t>
+          <t>R13931_2020_Biogas_recovery_from_fresh_landfill_leachates_by_using_a.pdf</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -38852,12 +38892,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R13877</t>
+          <t>R13945</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R13877.main.04a76adc76fa9472</t>
+          <t>R13945.main.67309ea094d2f9bb</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -38867,20 +38907,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>04a76adc76fa947250861c95c93759c590dd3e02d7f80dc23ce0abedccb74510</t>
+          <t>67309ea094d2f9bb088d605746ede869866819a733f53c44dc2d44af934e6be9</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>522402</v>
+        <v>2230958</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://escholarship.org/content/qt5572k7rw/qt5572k7rw.pdf</t>
+          <t>https://epublications.marquette.edu/cgi/viewcontent.cgi?article=1459&amp;context=theses_open</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>R13877_2018_Microbial_community_response_and_SDS-PAGE_reveal_possible_mechanism_of.pdf</t>
+          <t>R13945_2018_Effect_of_Low_Aeration_and_Heat_Drying_on_Anaerobic.pdf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -38892,12 +38932,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R13862</t>
+          <t>R13950</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R13862.main.64e03a9beb5813a0</t>
+          <t>R13950.main.2bf9b46c448685b9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -38907,20 +38947,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>64e03a9beb5813a0ce6d94272350217f12dac94293420969e3d2d9d7975e96e3</t>
+          <t>2bf9b46c448685b9e66f4064245c5840dc28ded79ee4d613ddd9efeb4805812e</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>833659</v>
+        <v>3508852</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/eb850f96-0570-4e0d-be55-73fcee5f1364/content</t>
+          <t>https://www.research.unipd.it/bitstream/11577/3425227/1/Thesis_Razieh_Rafieenia.pdf</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>R13862_2020_Multiple_and_flexible_roles_of_facultative_anaerobic_bacteria_in.pdf</t>
+          <t>R13950_2019_Enhancement_of_hydrogen_and_methane_production_through_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -38932,12 +38972,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R13900</t>
+          <t>R13944</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R13900.main.b2ba7df8c04ab66c</t>
+          <t>R13944.main.7e22fbfd39ddfed0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -38947,20 +38987,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>b2ba7df8c04ab66c0e548f778e19c5764802c0da8408a3b8499547b3f6ef51b3</t>
+          <t>7e22fbfd39ddfed09b9235fea5c6914cfbe5987d12564fc9cb799bf412ae6779</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>299244</v>
+        <v>12042699</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.research.unipd.it/bitstream/11577/3261852/1/Front.%20Environ.%20Sci.%20Eng%20Dongbei%202018.pdf</t>
+          <t>https://scholarspace.manoa.hawaii.edu/server/api/core/bitstreams/60c88164-f37f-492a-97bc-e34a2f2b1698/content</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>R13900_2018_Effectiveness_of_aerobic_pretreatment_of_municipal_solid_waste_for.pdf</t>
+          <t>R13944_2018_Oxidation-Reduction_Potential-Based_Micro-Aeration_Control_System_for_Anaerobic_Digestion.pdf</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -38972,12 +39012,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R13903</t>
+          <t>R13967</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R13903.main.2cd9e7b409250e7b</t>
+          <t>R13967.main.5e9f84dbaf01dd19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -38987,20 +39027,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2cd9e7b409250e7b104f489e139f57d4daa40d97133c6c57c937184c3ec73b71</t>
+          <t>5e9f84dbaf01dd19674f09cbce96f338f32fe21a37a883bb9658e49af7072194</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1107675</v>
+        <v>160020</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://ijabe.org/index.php/ijabe/article/download/7975/pdf</t>
+          <t>https://www.aceee.org/wp-content/uploads/proceedings-1980-2020/2012/0193-000342.pdf</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>R13903_2023_Effect_of_vacuum_negative_pressure_aerobic_hydrolysis_pretreatment_on.pdf</t>
+          <t>R13967_2012_An_Improved_Biomass_Waste_Anaerobic_Degradation_Technology_for_Producing.pdf</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -39012,12 +39052,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R13931</t>
+          <t>R13972</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R13931.main.6e898a403edac7b3</t>
+          <t>R13972.main.ff4ee9377a7e227c</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -39027,20 +39067,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6e898a403edac7b3ae15ad88cf75788898cd84ea377b2572f7bab40d9c126f8c</t>
+          <t>ff4ee9377a7e227c48a5bc64d301bfc1a989ee0e709c322eb90f254819d7b391</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1324593</v>
+        <v>1192569</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.eeer.org/upload/eer-2020-470.pdf</t>
+          <t>https://www.osti.gov/servlets/purl/2386939</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>R13931_2020_Biogas_recovery_from_fresh_landfill_leachates_by_using_a.pdf</t>
+          <t>R13972_2022_Enhancing_methane_production_of_anaerobic_digested_sewage_sludge_by.pdf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -39052,12 +39092,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R13945</t>
+          <t>R13957</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R13945.main.67309ea094d2f9bb</t>
+          <t>R13957.main.3db804dcdefb7608</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -39067,20 +39107,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>67309ea094d2f9bb088d605746ede869866819a733f53c44dc2d44af934e6be9</t>
+          <t>3db804dcdefb7608eefc6bf166b0713cbbec8ac027b1c01831aec97b54253b82</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2230958</v>
+        <v>7806265</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://epublications.marquette.edu/cgi/viewcontent.cgi?article=1459&amp;context=theses_open</t>
+          <t>https://backoffice.biblio.ugent.be/download/8530499/8530500</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>R13945_2018_Effect_of_Low_Aeration_and_Heat_Drying_on_Anaerobic.pdf</t>
+          <t>R13957_2017_Microaeration_for_biogas_desulfurization_experimental_and_simulation_study_of.pdf</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -39092,12 +39132,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R13950</t>
+          <t>R04510</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R13950.main.2bf9b46c448685b9</t>
+          <t>R04510.main.c4520ca79e301bb6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -39107,20 +39147,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2bf9b46c448685b9e66f4064245c5840dc28ded79ee4d613ddd9efeb4805812e</t>
+          <t>c4520ca79e301bb606a8ab1fef6cf4af9064c0d85f3c390a4cf31a877238e1c6</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3508852</v>
+        <v>492630</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.research.unipd.it/bitstream/11577/3425227/1/Thesis_Razieh_Rafieenia.pdf</t>
+          <t>https://digital.csic.es/bitstream/10261/196040/5/PostP_2019_JESH_V54_Iss10.pdf</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>R13950_2019_Enhancement_of_hydrogen_and_methane_production_through_anaerobic_digestion.pdf</t>
+          <t>R04510_2019_Anaerobic_digestion_of_wastewater_rich_in_sulfate_and_sulfide_effects_of_metallic_waste_addition_and.pdf</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -39132,12 +39172,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R13944</t>
+          <t>R13889</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R13944.main.7e22fbfd39ddfed0</t>
+          <t>R13889.main.8db0dcdf434e876e</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -39147,20 +39187,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7e22fbfd39ddfed09b9235fea5c6914cfbe5987d12564fc9cb799bf412ae6779</t>
+          <t>8db0dcdf434e876e7cbff3cf342105807bdd41a900f74c0028cb14a6c6e56779</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>12042699</v>
+        <v>514378</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://scholarspace.manoa.hawaii.edu/server/api/core/bitstreams/60c88164-f37f-492a-97bc-e34a2f2b1698/content</t>
+          <t>https://digital.csic.es/bitstream/10261/178890/1/PotP_2018_RE_V123_P541.pdf</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>R13944_2018_Oxidation-Reduction_Potential-Based_Micro-Aeration_Control_System_for_Anaerobic_Digestion.pdf</t>
+          <t>R13889_2018_Increase_in_biogas_production_in_anaerobic_sludge_digestion_by_combining_aerobic_hydrolysis_and_addi.pdf</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -39172,12 +39212,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>R13967</t>
+          <t>R02719</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R13967.main.5e9f84dbaf01dd19</t>
+          <t>R02719.main.4bf5e309b2ef3431</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -39187,20 +39227,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5e9f84dbaf01dd19674f09cbce96f338f32fe21a37a883bb9658e49af7072194</t>
+          <t>4bf5e309b2ef343162a9588383a7ae0254118c33cdf2e96bec1a05459fae1523</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>160020</v>
+        <v>583591</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.aceee.org/wp-content/uploads/proceedings-1980-2020/2012/0193-000342.pdf</t>
+          <t>https://digital.csic.es/bitstream/10261/137944/1/Post_2016_JEnvSciHealth_A_BorjaR.pdf</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>R13967_2012_An_Improved_Biomass_Waste_Anaerobic_Degradation_Technology_for_Producing.pdf</t>
+          <t>R02719_2016_Performance_evaluation_of_micro_aerobic_hydrolysis_of_mixed_sludge_Optimum_aeration_and_effect_on_it.pdf</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -39212,12 +39252,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>R13972</t>
+          <t>R02282</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R13972.main.ff4ee9377a7e227c</t>
+          <t>R02282.main.e709439b748e7938</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -39227,20 +39267,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ff4ee9377a7e227c48a5bc64d301bfc1a989ee0e709c322eb90f254819d7b391</t>
+          <t>e709439b748e793826102646c009aa10e1e9ac30627ac301fac7dd42276a2047</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1192569</v>
+        <v>1067465</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.osti.gov/servlets/purl/2386939</t>
+          <t>https://digital.csic.es/bitstream/10261/130093/1/Postprint_2016_EnviromRev_V24_P84.pdf</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>R13972_2022_Enhancing_methane_production_of_anaerobic_digested_sewage_sludge_by.pdf</t>
+          <t>R02282_2016_Advances_in_the_biological_removal_of_sulphides_from_aqueous_phase_in_anaerobic_processes_A_review.pdf</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -39252,12 +39292,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>R13957</t>
+          <t>R13905</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>R13957.main.3db804dcdefb7608</t>
+          <t>R13905.main.c75b5084c2545bd9</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -39267,20 +39307,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3db804dcdefb7608eefc6bf166b0713cbbec8ac027b1c01831aec97b54253b82</t>
+          <t>c75b5084c2545bd939d3b1928be41fe0072c7302f26c25ba023c4bb6fc8a6970</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>7806265</v>
+        <v>2159708</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://backoffice.biblio.ugent.be/download/8530499/8530500</t>
+          <t>https://ddd.uab.cat/pub/artpub/2017/196242/wasbioval_a2017m7v8n5p1793.pdf</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>R13957_2017_Microaeration_for_biogas_desulfurization_experimental_and_simulation_study_of.pdf</t>
+          <t>R13905_2017_The_Effect_of_a_Short_Term_Aerobic_Pretreatment_Step_on_the_Anaerobic_Co_digestion_of_the_Organic_Fr.pdf</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -39292,12 +39332,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>R04510</t>
+          <t>R13932</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R04510.main.c4520ca79e301bb6</t>
+          <t>R13932.main.c15f49a3d617e1be</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -39307,20 +39347,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>c4520ca79e301bb606a8ab1fef6cf4af9064c0d85f3c390a4cf31a877238e1c6</t>
+          <t>c15f49a3d617e1be5e21578ebda1c2d855f8d460c1d66f446ad0d02856a40a13</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>492630</v>
+        <v>1258157</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/196040/5/PostP_2019_JESH_V54_Iss10.pdf</t>
+          <t>https://hal.inrae.fr/hal-02620984/document</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>R04510_2019_Anaerobic_digestion_of_wastewater_rich_in_sulfate_and_sulfide_effects_of_metallic_waste_addition_and.pdf</t>
+          <t>R13932_2018_Comparison_of_pre_and_inter_stage_aerobic_treatment_of_wastewater_sludge_Effects_on_biogas_productio.pdf</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -39332,12 +39372,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>R13889</t>
+          <t>R13956</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R13889.main.8db0dcdf434e876e</t>
+          <t>R13956.main.fedaffcdf5be81e2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -39347,20 +39387,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8db0dcdf434e876e7cbff3cf342105807bdd41a900f74c0028cb14a6c6e56779</t>
+          <t>fedaffcdf5be81e2070b7edb0531c332e423578228eeb8c55a6afc4ba8fe1e18</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>514378</v>
+        <v>421626</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/178890/1/PotP_2018_RE_V123_P541.pdf</t>
+          <t>https://www.banglajol.info/index.php/BJSIR/article/download/25579/17152</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>R13889_2018_Increase_in_biogas_production_in_anaerobic_sludge_digestion_by_combining_aerobic_hydrolysis_and_addi.pdf</t>
+          <t>R13956_2015_Anaerobic_digestion_of_mixed_dried_fallen_leaves_by_mixing_with_cow_dung.pdf</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -39372,12 +39412,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>R02719</t>
+          <t>R13955</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R02719.main.4bf5e309b2ef3431</t>
+          <t>R13955.main.7549e1025985363e</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -39387,20 +39427,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4bf5e309b2ef343162a9588383a7ae0254118c33cdf2e96bec1a05459fae1523</t>
+          <t>7549e1025985363e89542bbc1af6eaaa1150bbd62ea43bdd03d2c7b764631f9d</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>583591</v>
+        <v>14662438</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/137944/1/Post_2016_JEnvSciHealth_A_BorjaR.pdf</t>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>R02719_2016_Performance_evaluation_of_micro_aerobic_hydrolysis_of_mixed_sludge_Optimum_aeration_and_effect_on_it.pdf</t>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -39412,35 +39452,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R02282</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R02282.main.e709439b748e7938</t>
+          <t>R07238.supplementary.0b7925ad1ed9c793</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>e709439b748e793826102646c009aa10e1e9ac30627ac301fac7dd42276a2047</t>
+          <t>0b7925ad1ed9c7939a79ba6294d17abc4b23fca77e52ec50df5463d050940d1e</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1067465</v>
+        <v>49526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/130093/1/Postprint_2016_EnviromRev_V24_P84.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>R02282_2016_Advances_in_the_biological_removal_of_sulphides_from_aqueous_phase_in_anaerobic_processes_A_review.pdf</t>
+          <t>mmc1.docx</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -39452,35 +39492,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>R13905</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>R13905.main.c75b5084c2545bd9</t>
+          <t>R07238.supplementary.f346f9bdcc964013</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>c75b5084c2545bd939d3b1928be41fe0072c7302f26c25ba023c4bb6fc8a6970</t>
+          <t>f346f9bdcc964013ecb7c4282d6b30f1ab334e035d98adcc653de1447fbe9a9a</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2159708</v>
+        <v>14286928</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://ddd.uab.cat/pub/artpub/2017/196242/wasbioval_a2017m7v8n5p1793.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>R13905_2017_The_Effect_of_a_Short_Term_Aerobic_Pretreatment_Step_on_the_Anaerobic_Co_digestion_of_the_Organic_Fr.pdf</t>
+          <t>mmc2.zip</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -39492,35 +39532,35 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>R13932</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>R13932.main.c15f49a3d617e1be</t>
+          <t>R07238.derived.49b84e369d4bb31b</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>c15f49a3d617e1be5e21578ebda1c2d855f8d460c1d66f446ad0d02856a40a13</t>
+          <t>49b84e369d4bb31b4ebdcd25265be3174105c3433e6fbb865f34a445775516a1</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1258157</v>
+        <v>34855493</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://hal.inrae.fr/hal-02620984/document</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>R13932_2018_Comparison_of_pre_and_inter_stage_aerobic_treatment_of_wastewater_sludge_Effects_on_biogas_productio.pdf</t>
+          <t>g a.skp</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -39532,35 +39572,35 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>R13956</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R13956.main.fedaffcdf5be81e2</t>
+          <t>R08646.supplementary.cfda7e29b12b9784</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>fedaffcdf5be81e2070b7edb0531c332e423578228eeb8c55a6afc4ba8fe1e18</t>
+          <t>cfda7e29b12b97846343963f9f3b64e784bc79644fb1ee1ca31170be78d75327</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>421626</v>
+        <v>42279</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.banglajol.info/index.php/BJSIR/article/download/25579/17152</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>R13956_2015_Anaerobic_digestion_of_mixed_dried_fallen_leaves_by_mixing_with_cow_dung.pdf</t>
+          <t>mmc1.docx</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -39572,35 +39612,35 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>R13955</t>
+          <t>R03161</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>R13955.main.7549e1025985363e</t>
+          <t>R03161.evidence_xml.466f3a1e78e8b0f1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>7549e1025985363e89542bbc1af6eaaa1150bbd62ea43bdd03d2c7b764631f9d</t>
+          <t>466f3a1e78e8b0f148b1f28f97b61f7134c61488c837c5c5a26ef7316cebc1e9</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>14662438</v>
+        <v>59018</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/fullTextXML</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
+          <t>PMC5627928_fullText.xml</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -39612,35 +39652,35 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R03161</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R07238.supplementary.0b7925ad1ed9c793</t>
+          <t>R03161.transport_archive.0ef4d4796c84feff</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0b7925ad1ed9c7939a79ba6294d17abc4b23fca77e52ec50df5463d050940d1e</t>
+          <t>0ef4d4796c84fefff7b8450bc56400f8c59f4bdcf074fc51404edff5e4e217f6</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>49526</v>
+        <v>726772</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/supplementaryFiles</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>mmc1.docx</t>
+          <t>PMC5627928_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -39652,35 +39692,35 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R04092</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>R07238.supplementary.f346f9bdcc964013</t>
+          <t>R04092.evidence_xml.0fb90085e30680fa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>f346f9bdcc964013ecb7c4282d6b30f1ab334e035d98adcc653de1447fbe9a9a</t>
+          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>14286928</v>
+        <v>77995</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>mmc2.zip</t>
+          <t>PMC6288047_fullText.xml</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -39692,35 +39732,35 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R05839</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>R07238.derived.49b84e369d4bb31b</t>
+          <t>R05839.evidence_xml.18ffd43dee955086</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>49b84e369d4bb31b4ebdcd25265be3174105c3433e6fbb865f34a445775516a1</t>
+          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>34855493</v>
+        <v>75205</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>g a.skp</t>
+          <t>PMC7566014_fullText.xml</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -39732,35 +39772,35 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R08877</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>R08646.supplementary.cfda7e29b12b9784</t>
+          <t>R08877.evidence_xml.e8712e4198baab4c</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>cfda7e29b12b97846343963f9f3b64e784bc79644fb1ee1ca31170be78d75327</t>
+          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>42279</v>
+        <v>111864</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>mmc1.docx</t>
+          <t>PMC10714394_fullText.xml</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -39772,35 +39812,35 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>R03161</t>
+          <t>R08877</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>R03161.evidence_xml.466f3a1e78e8b0f1</t>
+          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>466f3a1e78e8b0f148b1f28f97b61f7134c61488c837c5c5a26ef7316cebc1e9</t>
+          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>59018</v>
+        <v>704921</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>PMC5627928_fullText.xml</t>
+          <t>PMC10714394_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -39812,35 +39852,35 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>R03161</t>
+          <t>R09236</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>R03161.transport_archive.0ef4d4796c84feff</t>
+          <t>R09236.evidence_xml.72064fe9276d8309</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0ef4d4796c84fefff7b8450bc56400f8c59f4bdcf074fc51404edff5e4e217f6</t>
+          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>726772</v>
+        <v>193052</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>PMC5627928_supplementaryFiles.zip</t>
+          <t>PMC10535533_fullText.xml</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -39852,35 +39892,35 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>R04092</t>
+          <t>R09236</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>R04092.evidence_xml.0fb90085e30680fa</t>
+          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
+          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>77995</v>
+        <v>483405</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>PMC6288047_fullText.xml</t>
+          <t>PMC10535533_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -39892,12 +39932,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>R05839</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>R05839.evidence_xml.18ffd43dee955086</t>
+          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -39907,20 +39947,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
+          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>75205</v>
+        <v>118002</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>PMC7566014_fullText.xml</t>
+          <t>PMC10837232_fullText.xml</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -39932,35 +39972,35 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>R08877.evidence_xml.e8712e4198baab4c</t>
+          <t>R10086.transport_archive.4d9eddf454b786ed</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
+          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>111864</v>
+        <v>641038</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>PMC10714394_fullText.xml</t>
+          <t>PMC10837232_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -39972,35 +40012,35 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
+          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
+          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>704921</v>
+        <v>173586</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>PMC10714394_supplementaryFiles.zip</t>
+          <t>PMC12937426_fullText.xml</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -40012,35 +40052,35 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>R09236.evidence_xml.72064fe9276d8309</t>
+          <t>R12985.transport_archive.418d45f1ca296020</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
+          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>193052</v>
+        <v>672244</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>PMC10535533_fullText.xml</t>
+          <t>PMC12937426_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -40052,35 +40092,35 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R05542</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
+          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
+          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>483405</v>
+        <v>100215</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>PMC10535533_supplementaryFiles.zip</t>
+          <t>PMC9056904_fullText.xml</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -40092,12 +40132,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
+          <t>R06325.evidence_xml.645deb707d3790b5</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -40107,20 +40147,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
+          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>118002</v>
+        <v>160509</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>PMC10837232_fullText.xml</t>
+          <t>PMC8290346_fullText.xml</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -40132,12 +40172,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>R10086.transport_archive.4d9eddf454b786ed</t>
+          <t>R06325.transport_archive.6eb4ef126661714a</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -40147,20 +40187,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
+          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>641038</v>
+        <v>1730580</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>PMC10837232_supplementaryFiles.zip</t>
+          <t>PMC8290346_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -40172,12 +40212,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
+          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -40187,20 +40227,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
+          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>173586</v>
+        <v>151458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>PMC12937426_fullText.xml</t>
+          <t>PMC8044681_fullText.xml</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -40212,12 +40252,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>R12985.transport_archive.418d45f1ca296020</t>
+          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -40227,20 +40267,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
+          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>672244</v>
+        <v>14596266</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>PMC12937426_supplementaryFiles.zip</t>
+          <t>PMC8044681_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -40252,12 +40292,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>R05542</t>
+          <t>R03477</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
+          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -40267,20 +40307,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
+          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100215</v>
+        <v>121650</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>PMC9056904_fullText.xml</t>
+          <t>PMC5371168_fullText.xml</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -40292,12 +40332,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>R06325.evidence_xml.645deb707d3790b5</t>
+          <t>R08646.evidence_xml.c7b723e8020f6582</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -40307,20 +40347,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
+          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>160509</v>
+        <v>304277</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>PMC8290346_fullText.xml</t>
+          <t>PMC10559078_fullText.xml</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -40332,12 +40372,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>R06325.transport_archive.6eb4ef126661714a</t>
+          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -40347,20 +40387,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
+          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1730580</v>
+        <v>1539133</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>PMC8290346_supplementaryFiles.zip</t>
+          <t>PMC10559078_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -40372,12 +40412,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R09804</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
+          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -40387,20 +40427,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
+          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>151458</v>
+        <v>211630</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>PMC8044681_fullText.xml</t>
+          <t>PMC11076452_fullText.xml</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -40412,35 +40452,35 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R11503</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
+          <t>R11503.evidence_xml.4002d57be59c215c</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
+          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>14596266</v>
+        <v>258637</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>PMC8044681_supplementaryFiles.zip</t>
+          <t>PMC12561102_fullText.xml</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -40452,12 +40492,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>R03477</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
+          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -40467,20 +40507,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
+          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>121650</v>
+        <v>256247</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>PMC5371168_fullText.xml</t>
+          <t>PMC12125087_fullText.xml</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -40492,35 +40532,35 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>R08646.evidence_xml.c7b723e8020f6582</t>
+          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
+          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>304277</v>
+        <v>521862</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>PMC10559078_fullText.xml</t>
+          <t>PMC12125087_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -40532,35 +40572,35 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
+          <t>R05213.evidence_xml.17894ab410001846</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
+          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1539133</v>
+        <v>130954</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>PMC10559078_supplementaryFiles.zip</t>
+          <t>PMC6858683_fullText.xml</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -40572,35 +40612,35 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
+          <t>R05213.transport_archive.c61c88cf9fd489be</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
+          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>211630</v>
+        <v>1960371</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>PMC11076452_fullText.xml</t>
+          <t>PMC6858683_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -40612,12 +40652,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>R11503</t>
+          <t>R09585</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>R11503.evidence_xml.4002d57be59c215c</t>
+          <t>R09585.evidence_xml.a3430f38fa1652de</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -40627,20 +40667,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
+          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>258637</v>
+        <v>100534</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>PMC12561102_fullText.xml</t>
+          <t>PMC10609292_fullText.xml</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -40652,238 +40692,38 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R11596</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
+          <t>R11596.main.0b2e2d98dffd5449</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
+          <t>0b2e2d98dffd544958b06cc2229d310e4b7d529bd3914c47f20d6a66789a28be</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>256247</v>
+        <v>1659399</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
+          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/7262c516-6b14-4001-a173-517d1187c8d9/content</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>PMC12125087_fullText.xml</t>
+          <t>R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>R11844</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>transport_archive</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>521862</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>PMC12125087_supplementaryFiles.zip</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>R05213</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>R05213.evidence_xml.17894ab410001846</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>evidence_xml</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>130954</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>PMC6858683_fullText.xml</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>R05213</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>R05213.transport_archive.c61c88cf9fd489be</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>transport_archive</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>1960371</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>PMC6858683_supplementaryFiles.zip</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>R09585</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>R09585.evidence_xml.a3430f38fa1652de</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>evidence_xml</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>100534</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>PMC10609292_fullText.xml</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>R11596</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>R11596.main.0b2e2d98dffd5449</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>0b2e2d98dffd544958b06cc2229d310e4b7d529bd3914c47f20d6a66789a28be</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>1659399</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/7262c516-6b14-4001-a173-517d1187c8d9/content</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
         <is>
           <t>历史已获取，当前原件未恢复</t>
         </is>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -11034,7 +11034,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -15384,7 +15384,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:28.993751+00:00</t>
+          <t>2026-10-17T08:34:16.423822+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:28.994695+00:00</t>
+          <t>2026-10-17T08:34:16.424797+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:28.994719+00:00</t>
+          <t>2026-10-17T08:34:16.424822+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:28.994934+00:00</t>
+          <t>2026-10-17T08:34:16.425042+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:28.996082+00:00</t>
+          <t>2026-10-17T08:34:16.426274+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:28.996557+00:00</t>
+          <t>2026-10-17T08:34:16.426798+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.002707+00:00</t>
+          <t>2026-10-17T08:34:16.434468+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.005018+00:00</t>
+          <t>2026-10-17T08:34:16.437024+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.005907+00:00</t>
+          <t>2026-10-17T08:34:16.438478+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.006218+00:00</t>
+          <t>2026-10-17T08:34:16.438929+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.006922+00:00</t>
+          <t>2026-10-17T08:34:16.439743+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.007565+00:00</t>
+          <t>2026-10-17T08:34:16.440527+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.008442+00:00</t>
+          <t>2026-10-17T08:34:16.441603+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.008668+00:00</t>
+          <t>2026-10-17T08:34:16.441849+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.009536+00:00</t>
+          <t>2026-10-17T08:34:16.442810+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.017400+00:00</t>
+          <t>2026-10-17T08:34:16.451804+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.018112+00:00</t>
+          <t>2026-10-17T08:34:16.452521+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.019564+00:00</t>
+          <t>2026-10-17T08:34:16.453850+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.022148+00:00</t>
+          <t>2026-10-17T08:34:16.456606+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.023217+00:00</t>
+          <t>2026-10-17T08:34:16.457702+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.024451+00:00</t>
+          <t>2026-10-17T08:34:16.458890+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.028967+00:00</t>
+          <t>2026-10-17T08:34:16.463575+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.031246+00:00</t>
+          <t>2026-10-17T08:34:16.466105+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.033013+00:00</t>
+          <t>2026-10-17T08:34:16.468140+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.033671+00:00</t>
+          <t>2026-10-17T08:34:16.468978+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.034014+00:00</t>
+          <t>2026-10-17T08:34:16.469383+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.035955+00:00</t>
+          <t>2026-10-17T08:34:16.471532+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.037156+00:00</t>
+          <t>2026-10-17T08:34:16.472818+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.039182+00:00</t>
+          <t>2026-10-17T08:34:16.475217+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.041093+00:00</t>
+          <t>2026-10-17T08:34:16.477638+00:00</t>
         </is>
       </c>
     </row>
@@ -27571,7 +27571,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.041109+00:00</t>
+          <t>2026-10-17T08:34:16.477668+00:00</t>
         </is>
       </c>
     </row>
@@ -27679,7 +27679,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.041695+00:00</t>
+          <t>2026-10-17T08:34:16.478252+00:00</t>
         </is>
       </c>
     </row>
@@ -27787,7 +27787,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.043379+00:00</t>
+          <t>2026-10-17T08:34:16.479922+00:00</t>
         </is>
       </c>
     </row>
@@ -27895,7 +27895,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.046370+00:00</t>
+          <t>2026-10-17T08:34:16.484056+00:00</t>
         </is>
       </c>
     </row>
@@ -28003,7 +28003,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.048417+00:00</t>
+          <t>2026-10-17T08:34:16.487095+00:00</t>
         </is>
       </c>
     </row>
@@ -28111,7 +28111,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.049641+00:00</t>
+          <t>2026-10-17T08:34:16.488510+00:00</t>
         </is>
       </c>
     </row>
@@ -28219,7 +28219,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.052641+00:00</t>
+          <t>2026-10-17T08:34:16.491590+00:00</t>
         </is>
       </c>
     </row>
@@ -28327,7 +28327,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.053338+00:00</t>
+          <t>2026-10-17T08:34:16.492331+00:00</t>
         </is>
       </c>
     </row>
@@ -28435,7 +28435,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.054950+00:00</t>
+          <t>2026-10-17T08:34:16.494205+00:00</t>
         </is>
       </c>
     </row>
@@ -28543,7 +28543,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.055196+00:00</t>
+          <t>2026-10-17T08:34:16.494494+00:00</t>
         </is>
       </c>
     </row>
@@ -28651,7 +28651,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.057047+00:00</t>
+          <t>2026-10-17T08:34:16.496589+00:00</t>
         </is>
       </c>
     </row>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.060164+00:00</t>
+          <t>2026-10-17T08:34:16.499723+00:00</t>
         </is>
       </c>
     </row>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.061621+00:00</t>
+          <t>2026-10-17T08:34:16.501245+00:00</t>
         </is>
       </c>
     </row>
@@ -28975,7 +28975,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.062243+00:00</t>
+          <t>2026-10-17T08:34:16.501966+00:00</t>
         </is>
       </c>
     </row>
@@ -29083,7 +29083,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.064870+00:00</t>
+          <t>2026-10-17T08:34:16.504601+00:00</t>
         </is>
       </c>
     </row>
@@ -29191,7 +29191,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.066041+00:00</t>
+          <t>2026-10-17T08:34:16.505918+00:00</t>
         </is>
       </c>
     </row>
@@ -29299,7 +29299,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.069520+00:00</t>
+          <t>2026-10-17T08:34:16.510202+00:00</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.071134+00:00</t>
+          <t>2026-10-17T08:34:16.512151+00:00</t>
         </is>
       </c>
     </row>
@@ -29443,13 +29443,21 @@
           <t>papers/R04700/main/40ac0de29f75_R04700_2019_Effect_of_aeration_by_micro_-_bubbles_on_methane.pdf</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R04700_2019_Effect_of_aeration_by_micro_-_bubbles_on_methane.pdf</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R04700_2019_Effect_of_aeration_by_micro_-_bubbles_on_methane.pdf</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R04700_2019_Effect_of_aeration_by_micro_-_bubbles_on_methane.pdf</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -29465,12 +29473,12 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -29507,7 +29515,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.071151+00:00</t>
+          <t>2026-10-17T08:34:16.514057+00:00</t>
         </is>
       </c>
     </row>
@@ -29543,13 +29551,21 @@
           <t>papers/R09568/main/393322098ea4_R09568_2023_The_fate_of_sulfamethoxazole_and_trimethoprim_in_a_micro-aerated.pdf</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R09568_2023_The_fate_of_sulfamethoxazole_and_trimethoprim_in_a_micro-aerated.pdf</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R09568_2023_The_fate_of_sulfamethoxazole_and_trimethoprim_in_a_micro-aerated.pdf</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R09568_2023_The_fate_of_sulfamethoxazole_and_trimethoprim_in_a_micro-aerated.pdf</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -29565,12 +29581,12 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -29607,7 +29623,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.071157+00:00</t>
+          <t>2026-10-17T08:34:16.515118+00:00</t>
         </is>
       </c>
     </row>
@@ -29715,7 +29731,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.071586+00:00</t>
+          <t>2026-10-17T08:34:16.515655+00:00</t>
         </is>
       </c>
     </row>
@@ -29751,13 +29767,21 @@
           <t>papers/R10290/main/0a63bc6c89e8_R10290_2024_Gas_nanobubble_technology_in_wastewater_treatment_and_anaerobic_digestion.pdf</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R10290_2024_Gas_nanobubble_technology_in_wastewater_treatment_and_anaerobic_digestion.pdf</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R10290_2024_Gas_nanobubble_technology_in_wastewater_treatment_and_anaerobic_digestion.pdf</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R10290_2024_Gas_nanobubble_technology_in_wastewater_treatment_and_anaerobic_digestion.pdf</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -29773,12 +29797,12 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -29815,7 +29839,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.071601+00:00</t>
+          <t>2026-10-17T08:34:16.516035+00:00</t>
         </is>
       </c>
     </row>
@@ -29923,7 +29947,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.073027+00:00</t>
+          <t>2026-10-17T08:34:16.517748+00:00</t>
         </is>
       </c>
     </row>
@@ -30031,7 +30055,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.074308+00:00</t>
+          <t>2026-10-17T08:34:16.519122+00:00</t>
         </is>
       </c>
     </row>
@@ -30067,13 +30091,21 @@
           <t>papers/R10724/main/cfdc1bcb235a_R10724_2024_Protection_of_the_Purification_Station_Thermal_Engines_Against_the.pdf</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R10724_2024_Protection_of_the_Purification_Station_Thermal_Engines_Against_the.pdf</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R10724_2024_Protection_of_the_Purification_Station_Thermal_Engines_Against_the.pdf</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R10724_2024_Protection_of_the_Purification_Station_Thermal_Engines_Against_the.pdf</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -30089,12 +30121,12 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -30131,7 +30163,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.074327+00:00</t>
+          <t>2026-10-17T08:34:16.520704+00:00</t>
         </is>
       </c>
     </row>
@@ -30167,13 +30199,21 @@
           <t>papers/R11658/main/83a514a4b04c_R11658_2025_IMPACT_OF_MICRO-AERATION_ON_FUNGAL_COMMUNITY_FROM_ANAEROBIC_DIGESTION.pdf</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R11658_2025_IMPACT_OF_MICRO-AERATION_ON_FUNGAL_COMMUNITY_FROM_ANAEROBIC_DIGESTION.pdf</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R11658_2025_IMPACT_OF_MICRO-AERATION_ON_FUNGAL_COMMUNITY_FROM_ANAEROBIC_DIGESTION.pdf</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R11658_2025_IMPACT_OF_MICRO-AERATION_ON_FUNGAL_COMMUNITY_FROM_ANAEROBIC_DIGESTION.pdf</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -30189,12 +30229,12 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -30231,7 +30271,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.074330+00:00</t>
+          <t>2026-10-17T08:34:16.521257+00:00</t>
         </is>
       </c>
     </row>
@@ -30331,7 +30371,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.074334+00:00</t>
+          <t>2026-10-17T08:34:16.521360+00:00</t>
         </is>
       </c>
     </row>
@@ -30431,7 +30471,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.074337+00:00</t>
+          <t>2026-10-17T08:34:16.521367+00:00</t>
         </is>
       </c>
     </row>
@@ -30539,7 +30579,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.074884+00:00</t>
+          <t>2026-10-17T08:34:16.522055+00:00</t>
         </is>
       </c>
     </row>
@@ -30639,7 +30679,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.074898+00:00</t>
+          <t>2026-10-17T08:34:16.522094+00:00</t>
         </is>
       </c>
     </row>
@@ -30739,7 +30779,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.074901+00:00</t>
+          <t>2026-10-17T08:34:16.522101+00:00</t>
         </is>
       </c>
     </row>
@@ -30839,7 +30879,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.074904+00:00</t>
+          <t>2026-10-17T08:34:16.522105+00:00</t>
         </is>
       </c>
     </row>
@@ -30939,7 +30979,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.074907+00:00</t>
+          <t>2026-10-17T08:34:16.522109+00:00</t>
         </is>
       </c>
     </row>
@@ -31039,7 +31079,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.074910+00:00</t>
+          <t>2026-10-17T08:34:16.522112+00:00</t>
         </is>
       </c>
     </row>
@@ -31147,7 +31187,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.075334+00:00</t>
+          <t>2026-10-17T08:34:16.522612+00:00</t>
         </is>
       </c>
     </row>
@@ -31255,7 +31295,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.076367+00:00</t>
+          <t>2026-10-17T08:34:16.523733+00:00</t>
         </is>
       </c>
     </row>
@@ -31363,7 +31403,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.079382+00:00</t>
+          <t>2026-10-17T08:34:16.527200+00:00</t>
         </is>
       </c>
     </row>
@@ -31463,7 +31503,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.079407+00:00</t>
+          <t>2026-10-17T08:34:16.527234+00:00</t>
         </is>
       </c>
     </row>
@@ -31571,7 +31611,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.083652+00:00</t>
+          <t>2026-10-17T08:34:16.531897+00:00</t>
         </is>
       </c>
     </row>
@@ -31671,7 +31711,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.083682+00:00</t>
+          <t>2026-10-17T08:34:16.531954+00:00</t>
         </is>
       </c>
     </row>
@@ -31779,7 +31819,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.086002+00:00</t>
+          <t>2026-10-17T08:34:16.534432+00:00</t>
         </is>
       </c>
     </row>
@@ -31887,7 +31927,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.087801+00:00</t>
+          <t>2026-10-17T08:34:16.536238+00:00</t>
         </is>
       </c>
     </row>
@@ -31987,7 +32027,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.087827+00:00</t>
+          <t>2026-10-17T08:34:16.536273+00:00</t>
         </is>
       </c>
     </row>
@@ -32087,7 +32127,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.087831+00:00</t>
+          <t>2026-10-17T08:34:16.536278+00:00</t>
         </is>
       </c>
     </row>
@@ -32187,7 +32227,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.087834+00:00</t>
+          <t>2026-10-17T08:34:16.536282+00:00</t>
         </is>
       </c>
     </row>
@@ -32287,7 +32327,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.087837+00:00</t>
+          <t>2026-10-17T08:34:16.536285+00:00</t>
         </is>
       </c>
     </row>
@@ -32395,7 +32435,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.089025+00:00</t>
+          <t>2026-10-17T08:34:16.537738+00:00</t>
         </is>
       </c>
     </row>
@@ -32495,7 +32535,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.089045+00:00</t>
+          <t>2026-10-17T08:34:16.537765+00:00</t>
         </is>
       </c>
     </row>
@@ -32595,7 +32635,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.089049+00:00</t>
+          <t>2026-10-17T08:34:16.537770+00:00</t>
         </is>
       </c>
     </row>
@@ -32695,7 +32735,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.089052+00:00</t>
+          <t>2026-10-17T08:34:16.537774+00:00</t>
         </is>
       </c>
     </row>
@@ -32791,7 +32831,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.089055+00:00</t>
+          <t>2026-10-17T08:34:16.537777+00:00</t>
         </is>
       </c>
     </row>
@@ -32887,7 +32927,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.089058+00:00</t>
+          <t>2026-10-17T08:34:16.537780+00:00</t>
         </is>
       </c>
     </row>
@@ -32983,7 +33023,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.089062+00:00</t>
+          <t>2026-10-17T08:34:16.537784+00:00</t>
         </is>
       </c>
     </row>
@@ -33079,7 +33119,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.089065+00:00</t>
+          <t>2026-10-17T08:34:16.537787+00:00</t>
         </is>
       </c>
     </row>
@@ -33175,7 +33215,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.089068+00:00</t>
+          <t>2026-10-17T08:34:16.537791+00:00</t>
         </is>
       </c>
     </row>
@@ -33271,7 +33311,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.089070+00:00</t>
+          <t>2026-10-17T08:34:16.537794+00:00</t>
         </is>
       </c>
     </row>
@@ -33367,7 +33407,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.089073+00:00</t>
+          <t>2026-10-17T08:34:16.537798+00:00</t>
         </is>
       </c>
     </row>
@@ -33475,7 +33515,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.089883+00:00</t>
+          <t>2026-10-17T08:34:16.538578+00:00</t>
         </is>
       </c>
     </row>
@@ -33575,7 +33615,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.089951+00:00</t>
+          <t>2026-10-17T08:34:16.538603+00:00</t>
         </is>
       </c>
     </row>
@@ -33683,7 +33723,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.090007+00:00</t>
+          <t>2026-10-17T08:34:16.538656+00:00</t>
         </is>
       </c>
     </row>
@@ -33791,7 +33831,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.090225+00:00</t>
+          <t>2026-10-17T08:34:16.538878+00:00</t>
         </is>
       </c>
     </row>
@@ -33899,7 +33939,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.090363+00:00</t>
+          <t>2026-10-17T08:34:16.539051+00:00</t>
         </is>
       </c>
     </row>
@@ -34011,7 +34051,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.090484+00:00</t>
+          <t>2026-10-17T08:34:16.539186+00:00</t>
         </is>
       </c>
     </row>
@@ -34119,7 +34159,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.090851+00:00</t>
+          <t>2026-10-17T08:34:16.539590+00:00</t>
         </is>
       </c>
     </row>
@@ -34227,7 +34267,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.091031+00:00</t>
+          <t>2026-10-17T08:34:16.539780+00:00</t>
         </is>
       </c>
     </row>
@@ -34339,7 +34379,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.091083+00:00</t>
+          <t>2026-10-17T08:34:16.539837+00:00</t>
         </is>
       </c>
     </row>
@@ -34451,7 +34491,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.091146+00:00</t>
+          <t>2026-10-17T08:34:16.539905+00:00</t>
         </is>
       </c>
     </row>
@@ -34563,7 +34603,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.091302+00:00</t>
+          <t>2026-10-17T08:34:16.540049+00:00</t>
         </is>
       </c>
     </row>
@@ -34675,7 +34715,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.091348+00:00</t>
+          <t>2026-10-17T08:34:16.540094+00:00</t>
         </is>
       </c>
     </row>
@@ -34783,7 +34823,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.091805+00:00</t>
+          <t>2026-10-17T08:34:16.540593+00:00</t>
         </is>
       </c>
     </row>
@@ -34891,7 +34931,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.091851+00:00</t>
+          <t>2026-10-17T08:34:16.540659+00:00</t>
         </is>
       </c>
     </row>
@@ -34991,7 +35031,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.091862+00:00</t>
+          <t>2026-10-17T08:34:16.540669+00:00</t>
         </is>
       </c>
     </row>
@@ -35091,7 +35131,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.091865+00:00</t>
+          <t>2026-10-17T08:34:16.540673+00:00</t>
         </is>
       </c>
     </row>
@@ -35195,7 +35235,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.091869+00:00</t>
+          <t>2026-10-17T08:34:16.540676+00:00</t>
         </is>
       </c>
     </row>
@@ -35295,7 +35335,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.091871+00:00</t>
+          <t>2026-10-17T08:34:16.540680+00:00</t>
         </is>
       </c>
     </row>
@@ -35403,7 +35443,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.092078+00:00</t>
+          <t>2026-10-17T08:34:16.540896+00:00</t>
         </is>
       </c>
     </row>
@@ -35511,7 +35551,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093035+00:00</t>
+          <t>2026-10-17T08:34:16.541960+00:00</t>
         </is>
       </c>
     </row>
@@ -35605,7 +35645,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093051+00:00</t>
+          <t>2026-10-17T08:34:16.541986+00:00</t>
         </is>
       </c>
     </row>
@@ -35699,7 +35739,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093055+00:00</t>
+          <t>2026-10-17T08:34:16.541990+00:00</t>
         </is>
       </c>
     </row>
@@ -35793,7 +35833,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093058+00:00</t>
+          <t>2026-10-17T08:34:16.541994+00:00</t>
         </is>
       </c>
     </row>
@@ -35887,7 +35927,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093061+00:00</t>
+          <t>2026-10-17T08:34:16.541997+00:00</t>
         </is>
       </c>
     </row>
@@ -35981,7 +36021,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093064+00:00</t>
+          <t>2026-10-17T08:34:16.542001+00:00</t>
         </is>
       </c>
     </row>
@@ -36075,7 +36115,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093068+00:00</t>
+          <t>2026-10-17T08:34:16.542004+00:00</t>
         </is>
       </c>
     </row>
@@ -36169,7 +36209,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093071+00:00</t>
+          <t>2026-10-17T08:34:16.542008+00:00</t>
         </is>
       </c>
     </row>
@@ -36263,7 +36303,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093074+00:00</t>
+          <t>2026-10-17T08:34:16.542012+00:00</t>
         </is>
       </c>
     </row>
@@ -36357,7 +36397,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093077+00:00</t>
+          <t>2026-10-17T08:34:16.542015+00:00</t>
         </is>
       </c>
     </row>
@@ -36451,7 +36491,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093081+00:00</t>
+          <t>2026-10-17T08:34:16.542018+00:00</t>
         </is>
       </c>
     </row>
@@ -36545,7 +36585,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093084+00:00</t>
+          <t>2026-10-17T08:34:16.542022+00:00</t>
         </is>
       </c>
     </row>
@@ -36639,7 +36679,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093087+00:00</t>
+          <t>2026-10-17T08:34:16.542026+00:00</t>
         </is>
       </c>
     </row>
@@ -36733,7 +36773,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093090+00:00</t>
+          <t>2026-10-17T08:34:16.542030+00:00</t>
         </is>
       </c>
     </row>
@@ -36827,7 +36867,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093092+00:00</t>
+          <t>2026-10-17T08:34:16.542034+00:00</t>
         </is>
       </c>
     </row>
@@ -36921,7 +36961,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093095+00:00</t>
+          <t>2026-10-17T08:34:16.542037+00:00</t>
         </is>
       </c>
     </row>
@@ -37015,7 +37055,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093098+00:00</t>
+          <t>2026-10-17T08:34:16.542041+00:00</t>
         </is>
       </c>
     </row>
@@ -37109,7 +37149,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093101+00:00</t>
+          <t>2026-10-17T08:34:16.542044+00:00</t>
         </is>
       </c>
     </row>
@@ -37203,7 +37243,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093104+00:00</t>
+          <t>2026-10-17T08:34:16.542048+00:00</t>
         </is>
       </c>
     </row>
@@ -37297,7 +37337,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093107+00:00</t>
+          <t>2026-10-17T08:34:16.542052+00:00</t>
         </is>
       </c>
     </row>
@@ -37391,7 +37431,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093111+00:00</t>
+          <t>2026-10-17T08:34:16.542055+00:00</t>
         </is>
       </c>
     </row>
@@ -37485,7 +37525,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093114+00:00</t>
+          <t>2026-10-17T08:34:16.542058+00:00</t>
         </is>
       </c>
     </row>
@@ -37579,7 +37619,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093116+00:00</t>
+          <t>2026-10-17T08:34:16.542062+00:00</t>
         </is>
       </c>
     </row>
@@ -37673,7 +37713,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093119+00:00</t>
+          <t>2026-10-17T08:34:16.542065+00:00</t>
         </is>
       </c>
     </row>
@@ -37767,7 +37807,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093122+00:00</t>
+          <t>2026-10-17T08:34:16.542069+00:00</t>
         </is>
       </c>
     </row>
@@ -37861,7 +37901,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093126+00:00</t>
+          <t>2026-10-17T08:34:16.542073+00:00</t>
         </is>
       </c>
     </row>
@@ -37955,7 +37995,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093129+00:00</t>
+          <t>2026-10-17T08:34:16.542076+00:00</t>
         </is>
       </c>
     </row>
@@ -38049,7 +38089,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093132+00:00</t>
+          <t>2026-10-17T08:34:16.542079+00:00</t>
         </is>
       </c>
     </row>
@@ -38149,7 +38189,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T08:31:29.093135+00:00</t>
+          <t>2026-10-17T08:34:16.542082+00:00</t>
         </is>
       </c>
     </row>
@@ -38164,7 +38204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38292,12 +38332,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R04700</t>
+          <t>R12483</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R04700.main.40ac0de29f75851c</t>
+          <t>R12483.main.b51428ca89e5bf95</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -38307,20 +38347,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>40ac0de29f75851cab1651e1e339d03329bb7ce0141519329487f0559ebd8297</t>
+          <t>b51428ca89e5bf95c17225fe2e0a08a920379629281ab76f33337561553f3b0f</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2892628</v>
+        <v>1807518</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://repository.tudelft.nl/file/File_d8b73973-6e26-4f66-9162-3212f6b93431</t>
+          <t>https://li01.tci-thaijo.org/index.php/TSAEJ/article/download/269146/181297</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>R04700_2019_Effect_of_aeration_by_micro_-_bubbles_on_methane.pdf</t>
+          <t>R12483_2025_การปรบสภาพชวมวลลกโนเซลลโลสดวยวสดเพาะเหดเหลอทง_แนวทางการเพมมล.pdf</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -38332,12 +38372,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R09568</t>
+          <t>R13819</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R09568.main.393322098ea47587</t>
+          <t>R13819.main.431f5e76781d3cef</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -38347,20 +38387,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>393322098ea4758738b0e338c3e0019bd8618611d25a41cf3535d9542a6c8d16</t>
+          <t>431f5e76781d3cef39588c258c5589b1c9cf01db486c503ba29ab166bc73f14a</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1433947</v>
+        <v>2172752</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://repository.tudelft.nl/file/File_b3a1ee42-17d3-4f7d-82dc-616c91a5a6bf</t>
+          <t>https://epublications.marquette.edu/cgi/viewcontent.cgi?article=1131&amp;context=civengin_fac</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>R09568_2023_The_fate_of_sulfamethoxazole_and_trimethoprim_in_a_micro-aerated.pdf</t>
+          <t>R13819_2015_Bioaugmentation_of_overloaded_anaerobic_digesters_restores_function_and_archaeal.pdf</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -38372,12 +38412,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R10290</t>
+          <t>R13833</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R10290.main.0a63bc6c89e8dff8</t>
+          <t>R13833.main.1a4a4d5f8fd45de9</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -38387,20 +38427,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0a63bc6c89e8dff87ff1b364322ce6738e4fc87f505478ef522e7c73b7db342f</t>
+          <t>1a4a4d5f8fd45de924c78a7be11e1c032c630bd9341431d1d49135c8351cdaf7</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>530753</v>
+        <v>1463714</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://office.nbc-journal.org/index.php/NBC/article/download/2100/955</t>
+          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/234ac4ff-f996-498f-8853-72ba22cb7700/content</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>R10290_2024_Gas_nanobubble_technology_in_wastewater_treatment_and_anaerobic_digestion.pdf</t>
+          <t>R13833_2018_Insight_into_the_Role_of_Facultative_Bacteria_Stimulated_by.pdf</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -38412,12 +38452,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R10724</t>
+          <t>R13861</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R10724.main.cfdc1bcb235acdd7</t>
+          <t>R13861.main.ba6f44b77d79c4a0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -38427,20 +38467,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cfdc1bcb235acdd703e58447b30b31cb8c4e8d53d1c86999ee8ecdafbba1e8aa</t>
+          <t>ba6f44b77d79c4a07ba08602860bcf1bdbb36cb47b4527fa9d1f087825e394d8</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2366242</v>
+        <v>433474</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.ecoeet.com/pdf-181210-105068?filename=Protection-of-the-Purific.pdf</t>
+          <t>https://www.scielo.br/j/esa/a/BD6Bc5rMVrTsbkK7CZz6yVd/?format=pdf&amp;lang=en&amp;ilang=pt_BR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>R10724_2024_Protection_of_the_Purification_Station_Thermal_Engines_Against_the.pdf</t>
+          <t>R13861_2019_Enhanced_removal_of_emerging_micropollutants_by_applying_microaeration_to.pdf</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -38452,12 +38492,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R11658</t>
+          <t>R13871</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R11658.main.83a514a4b04c73a0</t>
+          <t>R13871.main.aeab3126b6e68775</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -38467,20 +38507,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>83a514a4b04c73a09129c21d623d57eb798a3af7c20dc842d47308f889d7695f</t>
+          <t>aeab3126b6e68775b9b316714633bd97c1f184cf9e308d75b404bca6b33be19f</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>458052</v>
+        <v>7983514</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://bsuj.bsu.edu.az/readpdf.php?file=236e3d6763a43f726c9814e7b5de8bc1.pdf</t>
+          <t>https://etheses.whiterose.ac.uk/id/eprint/4094/6/Mahmood_Khazzal_Hummadi_Al-Mashhadani._Reg._No._080243946_%28PhD_thesis%29_2013.pdf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>R11658_2025_IMPACT_OF_MICRO-AERATION_ON_FUNGAL_COMMUNITY_FROM_ANAEROBIC_DIGESTION.pdf</t>
+          <t>R13871_2013_Application_of_Microbubbles_Generated_by_Fluidic_Oscillation_in_the.pdf</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -38492,12 +38532,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R12483</t>
+          <t>R13877</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R12483.main.b51428ca89e5bf95</t>
+          <t>R13877.main.04a76adc76fa9472</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -38507,20 +38547,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>b51428ca89e5bf95c17225fe2e0a08a920379629281ab76f33337561553f3b0f</t>
+          <t>04a76adc76fa947250861c95c93759c590dd3e02d7f80dc23ce0abedccb74510</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1807518</v>
+        <v>522402</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://li01.tci-thaijo.org/index.php/TSAEJ/article/download/269146/181297</t>
+          <t>https://escholarship.org/content/qt5572k7rw/qt5572k7rw.pdf</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>R12483_2025_การปรบสภาพชวมวลลกโนเซลลโลสดวยวสดเพาะเหดเหลอทง_แนวทางการเพมมล.pdf</t>
+          <t>R13877_2018_Microbial_community_response_and_SDS-PAGE_reveal_possible_mechanism_of.pdf</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -38532,12 +38572,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R13819</t>
+          <t>R13862</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R13819.main.431f5e76781d3cef</t>
+          <t>R13862.main.64e03a9beb5813a0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -38547,20 +38587,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>431f5e76781d3cef39588c258c5589b1c9cf01db486c503ba29ab166bc73f14a</t>
+          <t>64e03a9beb5813a0ce6d94272350217f12dac94293420969e3d2d9d7975e96e3</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2172752</v>
+        <v>833659</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://epublications.marquette.edu/cgi/viewcontent.cgi?article=1131&amp;context=civengin_fac</t>
+          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/eb850f96-0570-4e0d-be55-73fcee5f1364/content</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>R13819_2015_Bioaugmentation_of_overloaded_anaerobic_digesters_restores_function_and_archaeal.pdf</t>
+          <t>R13862_2020_Multiple_and_flexible_roles_of_facultative_anaerobic_bacteria_in.pdf</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -38572,12 +38612,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R13833</t>
+          <t>R13900</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R13833.main.1a4a4d5f8fd45de9</t>
+          <t>R13900.main.b2ba7df8c04ab66c</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -38587,20 +38627,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1a4a4d5f8fd45de924c78a7be11e1c032c630bd9341431d1d49135c8351cdaf7</t>
+          <t>b2ba7df8c04ab66c0e548f778e19c5764802c0da8408a3b8499547b3f6ef51b3</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1463714</v>
+        <v>299244</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/234ac4ff-f996-498f-8853-72ba22cb7700/content</t>
+          <t>https://www.research.unipd.it/bitstream/11577/3261852/1/Front.%20Environ.%20Sci.%20Eng%20Dongbei%202018.pdf</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>R13833_2018_Insight_into_the_Role_of_Facultative_Bacteria_Stimulated_by.pdf</t>
+          <t>R13900_2018_Effectiveness_of_aerobic_pretreatment_of_municipal_solid_waste_for.pdf</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -38612,12 +38652,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R13861</t>
+          <t>R13903</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R13861.main.ba6f44b77d79c4a0</t>
+          <t>R13903.main.2cd9e7b409250e7b</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -38627,20 +38667,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ba6f44b77d79c4a07ba08602860bcf1bdbb36cb47b4527fa9d1f087825e394d8</t>
+          <t>2cd9e7b409250e7b104f489e139f57d4daa40d97133c6c57c937184c3ec73b71</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>433474</v>
+        <v>1107675</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.scielo.br/j/esa/a/BD6Bc5rMVrTsbkK7CZz6yVd/?format=pdf&amp;lang=en&amp;ilang=pt_BR</t>
+          <t>https://ijabe.org/index.php/ijabe/article/download/7975/pdf</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>R13861_2019_Enhanced_removal_of_emerging_micropollutants_by_applying_microaeration_to.pdf</t>
+          <t>R13903_2023_Effect_of_vacuum_negative_pressure_aerobic_hydrolysis_pretreatment_on.pdf</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -38652,12 +38692,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R13871</t>
+          <t>R13931</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R13871.main.aeab3126b6e68775</t>
+          <t>R13931.main.6e898a403edac7b3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -38667,20 +38707,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>aeab3126b6e68775b9b316714633bd97c1f184cf9e308d75b404bca6b33be19f</t>
+          <t>6e898a403edac7b3ae15ad88cf75788898cd84ea377b2572f7bab40d9c126f8c</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7983514</v>
+        <v>1324593</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://etheses.whiterose.ac.uk/id/eprint/4094/6/Mahmood_Khazzal_Hummadi_Al-Mashhadani._Reg._No._080243946_%28PhD_thesis%29_2013.pdf</t>
+          <t>https://www.eeer.org/upload/eer-2020-470.pdf</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>R13871_2013_Application_of_Microbubbles_Generated_by_Fluidic_Oscillation_in_the.pdf</t>
+          <t>R13931_2020_Biogas_recovery_from_fresh_landfill_leachates_by_using_a.pdf</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -38692,12 +38732,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R13877</t>
+          <t>R13945</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R13877.main.04a76adc76fa9472</t>
+          <t>R13945.main.67309ea094d2f9bb</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -38707,20 +38747,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>04a76adc76fa947250861c95c93759c590dd3e02d7f80dc23ce0abedccb74510</t>
+          <t>67309ea094d2f9bb088d605746ede869866819a733f53c44dc2d44af934e6be9</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>522402</v>
+        <v>2230958</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://escholarship.org/content/qt5572k7rw/qt5572k7rw.pdf</t>
+          <t>https://epublications.marquette.edu/cgi/viewcontent.cgi?article=1459&amp;context=theses_open</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>R13877_2018_Microbial_community_response_and_SDS-PAGE_reveal_possible_mechanism_of.pdf</t>
+          <t>R13945_2018_Effect_of_Low_Aeration_and_Heat_Drying_on_Anaerobic.pdf</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -38732,12 +38772,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R13862</t>
+          <t>R13950</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R13862.main.64e03a9beb5813a0</t>
+          <t>R13950.main.2bf9b46c448685b9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -38747,20 +38787,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>64e03a9beb5813a0ce6d94272350217f12dac94293420969e3d2d9d7975e96e3</t>
+          <t>2bf9b46c448685b9e66f4064245c5840dc28ded79ee4d613ddd9efeb4805812e</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>833659</v>
+        <v>3508852</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/eb850f96-0570-4e0d-be55-73fcee5f1364/content</t>
+          <t>https://www.research.unipd.it/bitstream/11577/3425227/1/Thesis_Razieh_Rafieenia.pdf</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>R13862_2020_Multiple_and_flexible_roles_of_facultative_anaerobic_bacteria_in.pdf</t>
+          <t>R13950_2019_Enhancement_of_hydrogen_and_methane_production_through_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -38772,12 +38812,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R13900</t>
+          <t>R13944</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R13900.main.b2ba7df8c04ab66c</t>
+          <t>R13944.main.7e22fbfd39ddfed0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -38787,20 +38827,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>b2ba7df8c04ab66c0e548f778e19c5764802c0da8408a3b8499547b3f6ef51b3</t>
+          <t>7e22fbfd39ddfed09b9235fea5c6914cfbe5987d12564fc9cb799bf412ae6779</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>299244</v>
+        <v>12042699</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.research.unipd.it/bitstream/11577/3261852/1/Front.%20Environ.%20Sci.%20Eng%20Dongbei%202018.pdf</t>
+          <t>https://scholarspace.manoa.hawaii.edu/server/api/core/bitstreams/60c88164-f37f-492a-97bc-e34a2f2b1698/content</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>R13900_2018_Effectiveness_of_aerobic_pretreatment_of_municipal_solid_waste_for.pdf</t>
+          <t>R13944_2018_Oxidation-Reduction_Potential-Based_Micro-Aeration_Control_System_for_Anaerobic_Digestion.pdf</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -38812,12 +38852,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R13903</t>
+          <t>R13967</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R13903.main.2cd9e7b409250e7b</t>
+          <t>R13967.main.5e9f84dbaf01dd19</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -38827,20 +38867,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2cd9e7b409250e7b104f489e139f57d4daa40d97133c6c57c937184c3ec73b71</t>
+          <t>5e9f84dbaf01dd19674f09cbce96f338f32fe21a37a883bb9658e49af7072194</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1107675</v>
+        <v>160020</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://ijabe.org/index.php/ijabe/article/download/7975/pdf</t>
+          <t>https://www.aceee.org/wp-content/uploads/proceedings-1980-2020/2012/0193-000342.pdf</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>R13903_2023_Effect_of_vacuum_negative_pressure_aerobic_hydrolysis_pretreatment_on.pdf</t>
+          <t>R13967_2012_An_Improved_Biomass_Waste_Anaerobic_Degradation_Technology_for_Producing.pdf</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -38852,12 +38892,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R13931</t>
+          <t>R13972</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R13931.main.6e898a403edac7b3</t>
+          <t>R13972.main.ff4ee9377a7e227c</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -38867,20 +38907,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6e898a403edac7b3ae15ad88cf75788898cd84ea377b2572f7bab40d9c126f8c</t>
+          <t>ff4ee9377a7e227c48a5bc64d301bfc1a989ee0e709c322eb90f254819d7b391</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1324593</v>
+        <v>1192569</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.eeer.org/upload/eer-2020-470.pdf</t>
+          <t>https://www.osti.gov/servlets/purl/2386939</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>R13931_2020_Biogas_recovery_from_fresh_landfill_leachates_by_using_a.pdf</t>
+          <t>R13972_2022_Enhancing_methane_production_of_anaerobic_digested_sewage_sludge_by.pdf</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -38892,12 +38932,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R13945</t>
+          <t>R13957</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R13945.main.67309ea094d2f9bb</t>
+          <t>R13957.main.3db804dcdefb7608</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -38907,20 +38947,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>67309ea094d2f9bb088d605746ede869866819a733f53c44dc2d44af934e6be9</t>
+          <t>3db804dcdefb7608eefc6bf166b0713cbbec8ac027b1c01831aec97b54253b82</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2230958</v>
+        <v>7806265</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://epublications.marquette.edu/cgi/viewcontent.cgi?article=1459&amp;context=theses_open</t>
+          <t>https://backoffice.biblio.ugent.be/download/8530499/8530500</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>R13945_2018_Effect_of_Low_Aeration_and_Heat_Drying_on_Anaerobic.pdf</t>
+          <t>R13957_2017_Microaeration_for_biogas_desulfurization_experimental_and_simulation_study_of.pdf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -38932,12 +38972,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R13950</t>
+          <t>R04510</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R13950.main.2bf9b46c448685b9</t>
+          <t>R04510.main.c4520ca79e301bb6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -38947,20 +38987,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2bf9b46c448685b9e66f4064245c5840dc28ded79ee4d613ddd9efeb4805812e</t>
+          <t>c4520ca79e301bb606a8ab1fef6cf4af9064c0d85f3c390a4cf31a877238e1c6</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3508852</v>
+        <v>492630</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.research.unipd.it/bitstream/11577/3425227/1/Thesis_Razieh_Rafieenia.pdf</t>
+          <t>https://digital.csic.es/bitstream/10261/196040/5/PostP_2019_JESH_V54_Iss10.pdf</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>R13950_2019_Enhancement_of_hydrogen_and_methane_production_through_anaerobic_digestion.pdf</t>
+          <t>R04510_2019_Anaerobic_digestion_of_wastewater_rich_in_sulfate_and_sulfide_effects_of_metallic_waste_addition_and.pdf</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -38972,12 +39012,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R13944</t>
+          <t>R13889</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R13944.main.7e22fbfd39ddfed0</t>
+          <t>R13889.main.8db0dcdf434e876e</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -38987,20 +39027,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7e22fbfd39ddfed09b9235fea5c6914cfbe5987d12564fc9cb799bf412ae6779</t>
+          <t>8db0dcdf434e876e7cbff3cf342105807bdd41a900f74c0028cb14a6c6e56779</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>12042699</v>
+        <v>514378</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://scholarspace.manoa.hawaii.edu/server/api/core/bitstreams/60c88164-f37f-492a-97bc-e34a2f2b1698/content</t>
+          <t>https://digital.csic.es/bitstream/10261/178890/1/PotP_2018_RE_V123_P541.pdf</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>R13944_2018_Oxidation-Reduction_Potential-Based_Micro-Aeration_Control_System_for_Anaerobic_Digestion.pdf</t>
+          <t>R13889_2018_Increase_in_biogas_production_in_anaerobic_sludge_digestion_by_combining_aerobic_hydrolysis_and_addi.pdf</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -39012,12 +39052,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R13967</t>
+          <t>R02719</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R13967.main.5e9f84dbaf01dd19</t>
+          <t>R02719.main.4bf5e309b2ef3431</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -39027,20 +39067,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5e9f84dbaf01dd19674f09cbce96f338f32fe21a37a883bb9658e49af7072194</t>
+          <t>4bf5e309b2ef343162a9588383a7ae0254118c33cdf2e96bec1a05459fae1523</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>160020</v>
+        <v>583591</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.aceee.org/wp-content/uploads/proceedings-1980-2020/2012/0193-000342.pdf</t>
+          <t>https://digital.csic.es/bitstream/10261/137944/1/Post_2016_JEnvSciHealth_A_BorjaR.pdf</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>R13967_2012_An_Improved_Biomass_Waste_Anaerobic_Degradation_Technology_for_Producing.pdf</t>
+          <t>R02719_2016_Performance_evaluation_of_micro_aerobic_hydrolysis_of_mixed_sludge_Optimum_aeration_and_effect_on_it.pdf</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -39052,12 +39092,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R13972</t>
+          <t>R02282</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R13972.main.ff4ee9377a7e227c</t>
+          <t>R02282.main.e709439b748e7938</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -39067,20 +39107,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ff4ee9377a7e227c48a5bc64d301bfc1a989ee0e709c322eb90f254819d7b391</t>
+          <t>e709439b748e793826102646c009aa10e1e9ac30627ac301fac7dd42276a2047</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1192569</v>
+        <v>1067465</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.osti.gov/servlets/purl/2386939</t>
+          <t>https://digital.csic.es/bitstream/10261/130093/1/Postprint_2016_EnviromRev_V24_P84.pdf</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>R13972_2022_Enhancing_methane_production_of_anaerobic_digested_sewage_sludge_by.pdf</t>
+          <t>R02282_2016_Advances_in_the_biological_removal_of_sulphides_from_aqueous_phase_in_anaerobic_processes_A_review.pdf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -39092,12 +39132,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R13957</t>
+          <t>R13905</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R13957.main.3db804dcdefb7608</t>
+          <t>R13905.main.c75b5084c2545bd9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -39107,20 +39147,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3db804dcdefb7608eefc6bf166b0713cbbec8ac027b1c01831aec97b54253b82</t>
+          <t>c75b5084c2545bd939d3b1928be41fe0072c7302f26c25ba023c4bb6fc8a6970</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>7806265</v>
+        <v>2159708</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://backoffice.biblio.ugent.be/download/8530499/8530500</t>
+          <t>https://ddd.uab.cat/pub/artpub/2017/196242/wasbioval_a2017m7v8n5p1793.pdf</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>R13957_2017_Microaeration_for_biogas_desulfurization_experimental_and_simulation_study_of.pdf</t>
+          <t>R13905_2017_The_Effect_of_a_Short_Term_Aerobic_Pretreatment_Step_on_the_Anaerobic_Co_digestion_of_the_Organic_Fr.pdf</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -39132,12 +39172,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R04510</t>
+          <t>R13932</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R04510.main.c4520ca79e301bb6</t>
+          <t>R13932.main.c15f49a3d617e1be</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -39147,20 +39187,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>c4520ca79e301bb606a8ab1fef6cf4af9064c0d85f3c390a4cf31a877238e1c6</t>
+          <t>c15f49a3d617e1be5e21578ebda1c2d855f8d460c1d66f446ad0d02856a40a13</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>492630</v>
+        <v>1258157</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/196040/5/PostP_2019_JESH_V54_Iss10.pdf</t>
+          <t>https://hal.inrae.fr/hal-02620984/document</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>R04510_2019_Anaerobic_digestion_of_wastewater_rich_in_sulfate_and_sulfide_effects_of_metallic_waste_addition_and.pdf</t>
+          <t>R13932_2018_Comparison_of_pre_and_inter_stage_aerobic_treatment_of_wastewater_sludge_Effects_on_biogas_productio.pdf</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -39172,12 +39212,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R13889</t>
+          <t>R13956</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R13889.main.8db0dcdf434e876e</t>
+          <t>R13956.main.fedaffcdf5be81e2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -39187,20 +39227,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8db0dcdf434e876e7cbff3cf342105807bdd41a900f74c0028cb14a6c6e56779</t>
+          <t>fedaffcdf5be81e2070b7edb0531c332e423578228eeb8c55a6afc4ba8fe1e18</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>514378</v>
+        <v>421626</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/178890/1/PotP_2018_RE_V123_P541.pdf</t>
+          <t>https://www.banglajol.info/index.php/BJSIR/article/download/25579/17152</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>R13889_2018_Increase_in_biogas_production_in_anaerobic_sludge_digestion_by_combining_aerobic_hydrolysis_and_addi.pdf</t>
+          <t>R13956_2015_Anaerobic_digestion_of_mixed_dried_fallen_leaves_by_mixing_with_cow_dung.pdf</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -39212,12 +39252,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>R02719</t>
+          <t>R13955</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R02719.main.4bf5e309b2ef3431</t>
+          <t>R13955.main.7549e1025985363e</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -39227,20 +39267,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4bf5e309b2ef343162a9588383a7ae0254118c33cdf2e96bec1a05459fae1523</t>
+          <t>7549e1025985363e89542bbc1af6eaaa1150bbd62ea43bdd03d2c7b764631f9d</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>583591</v>
+        <v>14662438</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/137944/1/Post_2016_JEnvSciHealth_A_BorjaR.pdf</t>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>R02719_2016_Performance_evaluation_of_micro_aerobic_hydrolysis_of_mixed_sludge_Optimum_aeration_and_effect_on_it.pdf</t>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -39252,35 +39292,35 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>R02282</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R02282.main.e709439b748e7938</t>
+          <t>R07238.supplementary.0b7925ad1ed9c793</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>e709439b748e793826102646c009aa10e1e9ac30627ac301fac7dd42276a2047</t>
+          <t>0b7925ad1ed9c7939a79ba6294d17abc4b23fca77e52ec50df5463d050940d1e</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1067465</v>
+        <v>49526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/130093/1/Postprint_2016_EnviromRev_V24_P84.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>R02282_2016_Advances_in_the_biological_removal_of_sulphides_from_aqueous_phase_in_anaerobic_processes_A_review.pdf</t>
+          <t>mmc1.docx</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -39292,35 +39332,35 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>R13905</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>R13905.main.c75b5084c2545bd9</t>
+          <t>R07238.supplementary.f346f9bdcc964013</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>c75b5084c2545bd939d3b1928be41fe0072c7302f26c25ba023c4bb6fc8a6970</t>
+          <t>f346f9bdcc964013ecb7c4282d6b30f1ab334e035d98adcc653de1447fbe9a9a</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2159708</v>
+        <v>14286928</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://ddd.uab.cat/pub/artpub/2017/196242/wasbioval_a2017m7v8n5p1793.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>R13905_2017_The_Effect_of_a_Short_Term_Aerobic_Pretreatment_Step_on_the_Anaerobic_Co_digestion_of_the_Organic_Fr.pdf</t>
+          <t>mmc2.zip</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -39332,35 +39372,35 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>R13932</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R13932.main.c15f49a3d617e1be</t>
+          <t>R07238.derived.49b84e369d4bb31b</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>c15f49a3d617e1be5e21578ebda1c2d855f8d460c1d66f446ad0d02856a40a13</t>
+          <t>49b84e369d4bb31b4ebdcd25265be3174105c3433e6fbb865f34a445775516a1</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1258157</v>
+        <v>34855493</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://hal.inrae.fr/hal-02620984/document</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>R13932_2018_Comparison_of_pre_and_inter_stage_aerobic_treatment_of_wastewater_sludge_Effects_on_biogas_productio.pdf</t>
+          <t>g a.skp</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -39372,35 +39412,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>R13956</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R13956.main.fedaffcdf5be81e2</t>
+          <t>R08646.supplementary.cfda7e29b12b9784</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>fedaffcdf5be81e2070b7edb0531c332e423578228eeb8c55a6afc4ba8fe1e18</t>
+          <t>cfda7e29b12b97846343963f9f3b64e784bc79644fb1ee1ca31170be78d75327</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>421626</v>
+        <v>42279</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.banglajol.info/index.php/BJSIR/article/download/25579/17152</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>R13956_2015_Anaerobic_digestion_of_mixed_dried_fallen_leaves_by_mixing_with_cow_dung.pdf</t>
+          <t>mmc1.docx</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -39412,35 +39452,35 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>R13955</t>
+          <t>R03161</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R13955.main.7549e1025985363e</t>
+          <t>R03161.evidence_xml.466f3a1e78e8b0f1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7549e1025985363e89542bbc1af6eaaa1150bbd62ea43bdd03d2c7b764631f9d</t>
+          <t>466f3a1e78e8b0f148b1f28f97b61f7134c61488c837c5c5a26ef7316cebc1e9</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>14662438</v>
+        <v>59018</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/fullTextXML</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
+          <t>PMC5627928_fullText.xml</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -39452,35 +39492,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R03161</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R07238.supplementary.0b7925ad1ed9c793</t>
+          <t>R03161.transport_archive.0ef4d4796c84feff</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0b7925ad1ed9c7939a79ba6294d17abc4b23fca77e52ec50df5463d050940d1e</t>
+          <t>0ef4d4796c84fefff7b8450bc56400f8c59f4bdcf074fc51404edff5e4e217f6</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>49526</v>
+        <v>726772</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/supplementaryFiles</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>mmc1.docx</t>
+          <t>PMC5627928_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -39492,35 +39532,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R04092</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>R07238.supplementary.f346f9bdcc964013</t>
+          <t>R04092.evidence_xml.0fb90085e30680fa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>f346f9bdcc964013ecb7c4282d6b30f1ab334e035d98adcc653de1447fbe9a9a</t>
+          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>14286928</v>
+        <v>77995</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>mmc2.zip</t>
+          <t>PMC6288047_fullText.xml</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -39532,35 +39572,35 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R05839</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>R07238.derived.49b84e369d4bb31b</t>
+          <t>R05839.evidence_xml.18ffd43dee955086</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>49b84e369d4bb31b4ebdcd25265be3174105c3433e6fbb865f34a445775516a1</t>
+          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>34855493</v>
+        <v>75205</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>g a.skp</t>
+          <t>PMC7566014_fullText.xml</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -39572,35 +39612,35 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R08877</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R08646.supplementary.cfda7e29b12b9784</t>
+          <t>R08877.evidence_xml.e8712e4198baab4c</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>cfda7e29b12b97846343963f9f3b64e784bc79644fb1ee1ca31170be78d75327</t>
+          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>42279</v>
+        <v>111864</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>mmc1.docx</t>
+          <t>PMC10714394_fullText.xml</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -39612,35 +39652,35 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>R03161</t>
+          <t>R08877</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>R03161.evidence_xml.466f3a1e78e8b0f1</t>
+          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>466f3a1e78e8b0f148b1f28f97b61f7134c61488c837c5c5a26ef7316cebc1e9</t>
+          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>59018</v>
+        <v>704921</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>PMC5627928_fullText.xml</t>
+          <t>PMC10714394_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -39652,35 +39692,35 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>R03161</t>
+          <t>R09236</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R03161.transport_archive.0ef4d4796c84feff</t>
+          <t>R09236.evidence_xml.72064fe9276d8309</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0ef4d4796c84fefff7b8450bc56400f8c59f4bdcf074fc51404edff5e4e217f6</t>
+          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>726772</v>
+        <v>193052</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>PMC5627928_supplementaryFiles.zip</t>
+          <t>PMC10535533_fullText.xml</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -39692,35 +39732,35 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>R04092</t>
+          <t>R09236</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>R04092.evidence_xml.0fb90085e30680fa</t>
+          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
+          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>77995</v>
+        <v>483405</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>PMC6288047_fullText.xml</t>
+          <t>PMC10535533_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -39732,12 +39772,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>R05839</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>R05839.evidence_xml.18ffd43dee955086</t>
+          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -39747,20 +39787,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
+          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>75205</v>
+        <v>118002</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>PMC7566014_fullText.xml</t>
+          <t>PMC10837232_fullText.xml</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -39772,35 +39812,35 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>R08877.evidence_xml.e8712e4198baab4c</t>
+          <t>R10086.transport_archive.4d9eddf454b786ed</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
+          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>111864</v>
+        <v>641038</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>PMC10714394_fullText.xml</t>
+          <t>PMC10837232_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -39812,35 +39852,35 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
+          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
+          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>704921</v>
+        <v>173586</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>PMC10714394_supplementaryFiles.zip</t>
+          <t>PMC12937426_fullText.xml</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -39852,35 +39892,35 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>R09236.evidence_xml.72064fe9276d8309</t>
+          <t>R12985.transport_archive.418d45f1ca296020</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
+          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>193052</v>
+        <v>672244</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>PMC10535533_fullText.xml</t>
+          <t>PMC12937426_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -39892,35 +39932,35 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R05542</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
+          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
+          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>483405</v>
+        <v>100215</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>PMC10535533_supplementaryFiles.zip</t>
+          <t>PMC9056904_fullText.xml</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -39932,12 +39972,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
+          <t>R06325.evidence_xml.645deb707d3790b5</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -39947,20 +39987,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
+          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>118002</v>
+        <v>160509</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>PMC10837232_fullText.xml</t>
+          <t>PMC8290346_fullText.xml</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -39972,12 +40012,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>R10086.transport_archive.4d9eddf454b786ed</t>
+          <t>R06325.transport_archive.6eb4ef126661714a</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -39987,20 +40027,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
+          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>641038</v>
+        <v>1730580</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>PMC10837232_supplementaryFiles.zip</t>
+          <t>PMC8290346_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -40012,12 +40052,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
+          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -40027,20 +40067,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
+          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>173586</v>
+        <v>151458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>PMC12937426_fullText.xml</t>
+          <t>PMC8044681_fullText.xml</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -40052,12 +40092,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>R12985.transport_archive.418d45f1ca296020</t>
+          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -40067,20 +40107,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
+          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>672244</v>
+        <v>14596266</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>PMC12937426_supplementaryFiles.zip</t>
+          <t>PMC8044681_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -40092,12 +40132,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>R05542</t>
+          <t>R03477</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
+          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -40107,20 +40147,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
+          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100215</v>
+        <v>121650</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>PMC9056904_fullText.xml</t>
+          <t>PMC5371168_fullText.xml</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -40132,12 +40172,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>R06325.evidence_xml.645deb707d3790b5</t>
+          <t>R08646.evidence_xml.c7b723e8020f6582</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -40147,20 +40187,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
+          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>160509</v>
+        <v>304277</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>PMC8290346_fullText.xml</t>
+          <t>PMC10559078_fullText.xml</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -40172,12 +40212,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>R06325.transport_archive.6eb4ef126661714a</t>
+          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -40187,20 +40227,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
+          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1730580</v>
+        <v>1539133</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>PMC8290346_supplementaryFiles.zip</t>
+          <t>PMC10559078_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -40212,12 +40252,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R09804</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
+          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -40227,20 +40267,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
+          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>151458</v>
+        <v>211630</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>PMC8044681_fullText.xml</t>
+          <t>PMC11076452_fullText.xml</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -40252,35 +40292,35 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R11503</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
+          <t>R11503.evidence_xml.4002d57be59c215c</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
+          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>14596266</v>
+        <v>258637</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>PMC8044681_supplementaryFiles.zip</t>
+          <t>PMC12561102_fullText.xml</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -40292,12 +40332,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>R03477</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
+          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -40307,20 +40347,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
+          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>121650</v>
+        <v>256247</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>PMC5371168_fullText.xml</t>
+          <t>PMC12125087_fullText.xml</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -40332,35 +40372,35 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>R08646.evidence_xml.c7b723e8020f6582</t>
+          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
+          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>304277</v>
+        <v>521862</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>PMC10559078_fullText.xml</t>
+          <t>PMC12125087_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -40372,35 +40412,35 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
+          <t>R05213.evidence_xml.17894ab410001846</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
+          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1539133</v>
+        <v>130954</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>PMC10559078_supplementaryFiles.zip</t>
+          <t>PMC6858683_fullText.xml</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -40412,35 +40452,35 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
+          <t>R05213.transport_archive.c61c88cf9fd489be</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
+          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>211630</v>
+        <v>1960371</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>PMC11076452_fullText.xml</t>
+          <t>PMC6858683_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -40452,12 +40492,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>R11503</t>
+          <t>R09585</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>R11503.evidence_xml.4002d57be59c215c</t>
+          <t>R09585.evidence_xml.a3430f38fa1652de</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -40467,20 +40507,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
+          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>258637</v>
+        <v>100534</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>PMC12561102_fullText.xml</t>
+          <t>PMC10609292_fullText.xml</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -40492,238 +40532,38 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R11596</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
+          <t>R11596.main.0b2e2d98dffd5449</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
+          <t>0b2e2d98dffd544958b06cc2229d310e4b7d529bd3914c47f20d6a66789a28be</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>256247</v>
+        <v>1659399</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
+          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/7262c516-6b14-4001-a173-517d1187c8d9/content</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>PMC12125087_fullText.xml</t>
+          <t>R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>R11844</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>transport_archive</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>521862</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>PMC12125087_supplementaryFiles.zip</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>R05213</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>R05213.evidence_xml.17894ab410001846</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>evidence_xml</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>130954</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>PMC6858683_fullText.xml</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>R05213</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>R05213.transport_archive.c61c88cf9fd489be</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>transport_archive</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>1960371</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>PMC6858683_supplementaryFiles.zip</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>R09585</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>R09585.evidence_xml.a3430f38fa1652de</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>evidence_xml</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>100534</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>PMC10609292_fullText.xml</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>R11596</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>R11596.main.0b2e2d98dffd5449</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>0b2e2d98dffd544958b06cc2229d310e4b7d529bd3914c47f20d6a66789a28be</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>1659399</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/7262c516-6b14-4001-a173-517d1187c8d9/content</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
         <is>
           <t>历史已获取，当前原件未恢复</t>
         </is>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -16709,7 +16709,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
@@ -18210,7 +18210,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
@@ -19371,7 +19371,7 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
@@ -19797,7 +19797,7 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.423822+00:00</t>
+          <t>2026-10-17T08:35:02.115012+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.424797+00:00</t>
+          <t>2026-10-17T08:35:02.115895+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.424822+00:00</t>
+          <t>2026-10-17T08:35:02.115914+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.425042+00:00</t>
+          <t>2026-10-17T08:35:02.116127+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.426274+00:00</t>
+          <t>2026-10-17T08:35:02.117453+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.426798+00:00</t>
+          <t>2026-10-17T08:35:02.117956+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.434468+00:00</t>
+          <t>2026-10-17T08:35:02.123997+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.437024+00:00</t>
+          <t>2026-10-17T08:35:02.126330+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.438478+00:00</t>
+          <t>2026-10-17T08:35:02.127202+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.438929+00:00</t>
+          <t>2026-10-17T08:35:02.127524+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.439743+00:00</t>
+          <t>2026-10-17T08:35:02.128468+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.440527+00:00</t>
+          <t>2026-10-17T08:35:02.129147+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.441603+00:00</t>
+          <t>2026-10-17T08:35:02.130153+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.441849+00:00</t>
+          <t>2026-10-17T08:35:02.130417+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.442810+00:00</t>
+          <t>2026-10-17T08:35:02.131265+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.451804+00:00</t>
+          <t>2026-10-17T08:35:02.139830+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.452521+00:00</t>
+          <t>2026-10-17T08:35:02.140561+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.453850+00:00</t>
+          <t>2026-10-17T08:35:02.141747+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.456606+00:00</t>
+          <t>2026-10-17T08:35:02.144238+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.457702+00:00</t>
+          <t>2026-10-17T08:35:02.145314+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.458890+00:00</t>
+          <t>2026-10-17T08:35:02.146511+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.463575+00:00</t>
+          <t>2026-10-17T08:35:02.150591+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.466105+00:00</t>
+          <t>2026-10-17T08:35:02.152734+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.468140+00:00</t>
+          <t>2026-10-17T08:35:02.154517+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.468978+00:00</t>
+          <t>2026-10-17T08:35:02.155324+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.469383+00:00</t>
+          <t>2026-10-17T08:35:02.155693+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.471532+00:00</t>
+          <t>2026-10-17T08:35:02.157838+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.472818+00:00</t>
+          <t>2026-10-17T08:35:02.159185+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.475217+00:00</t>
+          <t>2026-10-17T08:35:02.161413+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.477638+00:00</t>
+          <t>2026-10-17T08:35:02.163426+00:00</t>
         </is>
       </c>
     </row>
@@ -27571,7 +27571,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.477668+00:00</t>
+          <t>2026-10-17T08:35:02.163449+00:00</t>
         </is>
       </c>
     </row>
@@ -27679,7 +27679,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.478252+00:00</t>
+          <t>2026-10-17T08:35:02.163989+00:00</t>
         </is>
       </c>
     </row>
@@ -27787,7 +27787,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.479922+00:00</t>
+          <t>2026-10-17T08:35:02.165604+00:00</t>
         </is>
       </c>
     </row>
@@ -27895,7 +27895,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.484056+00:00</t>
+          <t>2026-10-17T08:35:02.168419+00:00</t>
         </is>
       </c>
     </row>
@@ -28003,7 +28003,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.487095+00:00</t>
+          <t>2026-10-17T08:35:02.170502+00:00</t>
         </is>
       </c>
     </row>
@@ -28111,7 +28111,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.488510+00:00</t>
+          <t>2026-10-17T08:35:02.171672+00:00</t>
         </is>
       </c>
     </row>
@@ -28219,7 +28219,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.491590+00:00</t>
+          <t>2026-10-17T08:35:02.174605+00:00</t>
         </is>
       </c>
     </row>
@@ -28327,7 +28327,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.492331+00:00</t>
+          <t>2026-10-17T08:35:02.175380+00:00</t>
         </is>
       </c>
     </row>
@@ -28435,7 +28435,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.494205+00:00</t>
+          <t>2026-10-17T08:35:02.176958+00:00</t>
         </is>
       </c>
     </row>
@@ -28543,7 +28543,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.494494+00:00</t>
+          <t>2026-10-17T08:35:02.177197+00:00</t>
         </is>
       </c>
     </row>
@@ -28651,7 +28651,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.496589+00:00</t>
+          <t>2026-10-17T08:35:02.179271+00:00</t>
         </is>
       </c>
     </row>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.499723+00:00</t>
+          <t>2026-10-17T08:35:02.182269+00:00</t>
         </is>
       </c>
     </row>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.501245+00:00</t>
+          <t>2026-10-17T08:35:02.183582+00:00</t>
         </is>
       </c>
     </row>
@@ -28975,7 +28975,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.501966+00:00</t>
+          <t>2026-10-17T08:35:02.184098+00:00</t>
         </is>
       </c>
     </row>
@@ -29083,7 +29083,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.504601+00:00</t>
+          <t>2026-10-17T08:35:02.186692+00:00</t>
         </is>
       </c>
     </row>
@@ -29191,7 +29191,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.505918+00:00</t>
+          <t>2026-10-17T08:35:02.187948+00:00</t>
         </is>
       </c>
     </row>
@@ -29299,7 +29299,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.510202+00:00</t>
+          <t>2026-10-17T08:35:02.191399+00:00</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.512151+00:00</t>
+          <t>2026-10-17T08:35:02.193019+00:00</t>
         </is>
       </c>
     </row>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.514057+00:00</t>
+          <t>2026-10-17T08:35:02.194843+00:00</t>
         </is>
       </c>
     </row>
@@ -29623,7 +29623,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.515118+00:00</t>
+          <t>2026-10-17T08:35:02.195763+00:00</t>
         </is>
       </c>
     </row>
@@ -29731,7 +29731,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.515655+00:00</t>
+          <t>2026-10-17T08:35:02.196181+00:00</t>
         </is>
       </c>
     </row>
@@ -29839,7 +29839,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.516035+00:00</t>
+          <t>2026-10-17T08:35:02.196552+00:00</t>
         </is>
       </c>
     </row>
@@ -29947,7 +29947,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.517748+00:00</t>
+          <t>2026-10-17T08:35:02.198016+00:00</t>
         </is>
       </c>
     </row>
@@ -30055,7 +30055,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.519122+00:00</t>
+          <t>2026-10-17T08:35:02.199283+00:00</t>
         </is>
       </c>
     </row>
@@ -30163,7 +30163,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.520704+00:00</t>
+          <t>2026-10-17T08:35:02.200761+00:00</t>
         </is>
       </c>
     </row>
@@ -30271,7 +30271,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.521257+00:00</t>
+          <t>2026-10-17T08:35:02.201081+00:00</t>
         </is>
       </c>
     </row>
@@ -30307,13 +30307,21 @@
           <t>papers/R12483/main/b51428ca89e5_R12483_2025_การปรบสภาพชวมวลลกโนเซลลโลสดวยวสดเพาะเหดเหลอทง_แนวทางการเพมมล.pdf</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R12483_2025_การปรบสภาพชวมวลลกโนเซลลโลสดวยวสดเพาะเหดเหลอทง_แนวทางการเพมมล.pdf</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R12483_2025_การปรบสภาพชวมวลลกโนเซลลโลสดวยวสดเพาะเหดเหลอทง_แนวทางการเพมมล.pdf</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R12483_2025_การปรบสภาพชวมวลลกโนเซลลโลสดวยวสดเพาะเหดเหลอทง_แนวทางการเพมมล.pdf</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -30329,12 +30337,12 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -30371,7 +30379,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.521360+00:00</t>
+          <t>2026-10-17T08:35:02.202252+00:00</t>
         </is>
       </c>
     </row>
@@ -30407,13 +30415,21 @@
           <t>papers/R13819/main/431f5e76781d_R13819_2015_Bioaugmentation_of_overloaded_anaerobic_digesters_restores_function_and_archaeal.pdf</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13819_2015_Bioaugmentation_of_overloaded_anaerobic_digesters_restores_function_and_archaeal.pdf</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R13819_2015_Bioaugmentation_of_overloaded_anaerobic_digesters_restores_function_and_archaeal.pdf</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13819_2015_Bioaugmentation_of_overloaded_anaerobic_digesters_restores_function_and_archaeal.pdf</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -30429,12 +30445,12 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -30471,7 +30487,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.521367+00:00</t>
+          <t>2026-10-17T08:35:02.203623+00:00</t>
         </is>
       </c>
     </row>
@@ -30579,7 +30595,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.522055+00:00</t>
+          <t>2026-10-17T08:35:02.204183+00:00</t>
         </is>
       </c>
     </row>
@@ -30615,13 +30631,21 @@
           <t>papers/R13833/main/1a4a4d5f8fd4_R13833_2018_Insight_into_the_Role_of_Facultative_Bacteria_Stimulated_by.pdf</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13833_2018_Insight_into_the_Role_of_Facultative_Bacteria_Stimulated_by.pdf</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R13833_2018_Insight_into_the_Role_of_Facultative_Bacteria_Stimulated_by.pdf</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13833_2018_Insight_into_the_Role_of_Facultative_Bacteria_Stimulated_by.pdf</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -30637,12 +30661,12 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -30679,7 +30703,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.522094+00:00</t>
+          <t>2026-10-17T08:35:02.205113+00:00</t>
         </is>
       </c>
     </row>
@@ -30715,13 +30739,21 @@
           <t>papers/R13861/main/ba6f44b77d79_R13861_2019_Enhanced_removal_of_emerging_micropollutants_by_applying_microaeration_to.pdf</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13861_2019_Enhanced_removal_of_emerging_micropollutants_by_applying_microaeration_to.pdf</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R13861_2019_Enhanced_removal_of_emerging_micropollutants_by_applying_microaeration_to.pdf</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13861_2019_Enhanced_removal_of_emerging_micropollutants_by_applying_microaeration_to.pdf</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -30737,12 +30769,12 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -30779,7 +30811,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.522101+00:00</t>
+          <t>2026-10-17T08:35:02.205432+00:00</t>
         </is>
       </c>
     </row>
@@ -30815,13 +30847,21 @@
           <t>papers/R13871/main/aeab3126b6e6_R13871_2013_Application_of_Microbubbles_Generated_by_Fluidic_Oscillation_in_the.pdf</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13871_2013_Application_of_Microbubbles_Generated_by_Fluidic_Oscillation_in_the.pdf</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R13871_2013_Application_of_Microbubbles_Generated_by_Fluidic_Oscillation_in_the.pdf</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13871_2013_Application_of_Microbubbles_Generated_by_Fluidic_Oscillation_in_the.pdf</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -30837,12 +30877,12 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -30879,7 +30919,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.522105+00:00</t>
+          <t>2026-10-17T08:35:02.210542+00:00</t>
         </is>
       </c>
     </row>
@@ -30979,7 +31019,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.522109+00:00</t>
+          <t>2026-10-17T08:35:02.210568+00:00</t>
         </is>
       </c>
     </row>
@@ -31079,7 +31119,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.522112+00:00</t>
+          <t>2026-10-17T08:35:02.210572+00:00</t>
         </is>
       </c>
     </row>
@@ -31187,7 +31227,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.522612+00:00</t>
+          <t>2026-10-17T08:35:02.210993+00:00</t>
         </is>
       </c>
     </row>
@@ -31295,7 +31335,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.523733+00:00</t>
+          <t>2026-10-17T08:35:02.212033+00:00</t>
         </is>
       </c>
     </row>
@@ -31403,7 +31443,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.527200+00:00</t>
+          <t>2026-10-17T08:35:02.215002+00:00</t>
         </is>
       </c>
     </row>
@@ -31503,7 +31543,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.527234+00:00</t>
+          <t>2026-10-17T08:35:02.215030+00:00</t>
         </is>
       </c>
     </row>
@@ -31611,7 +31651,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.531897+00:00</t>
+          <t>2026-10-17T08:35:02.219349+00:00</t>
         </is>
       </c>
     </row>
@@ -31711,7 +31751,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.531954+00:00</t>
+          <t>2026-10-17T08:35:02.219381+00:00</t>
         </is>
       </c>
     </row>
@@ -31819,7 +31859,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.534432+00:00</t>
+          <t>2026-10-17T08:35:02.221634+00:00</t>
         </is>
       </c>
     </row>
@@ -31927,7 +31967,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.536238+00:00</t>
+          <t>2026-10-17T08:35:02.223373+00:00</t>
         </is>
       </c>
     </row>
@@ -32027,7 +32067,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.536273+00:00</t>
+          <t>2026-10-17T08:35:02.223391+00:00</t>
         </is>
       </c>
     </row>
@@ -32127,7 +32167,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.536278+00:00</t>
+          <t>2026-10-17T08:35:02.223395+00:00</t>
         </is>
       </c>
     </row>
@@ -32227,7 +32267,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.536282+00:00</t>
+          <t>2026-10-17T08:35:02.223398+00:00</t>
         </is>
       </c>
     </row>
@@ -32327,7 +32367,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.536285+00:00</t>
+          <t>2026-10-17T08:35:02.223402+00:00</t>
         </is>
       </c>
     </row>
@@ -32435,7 +32475,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.537738+00:00</t>
+          <t>2026-10-17T08:35:02.224651+00:00</t>
         </is>
       </c>
     </row>
@@ -32535,7 +32575,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.537765+00:00</t>
+          <t>2026-10-17T08:35:02.224672+00:00</t>
         </is>
       </c>
     </row>
@@ -32635,7 +32675,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.537770+00:00</t>
+          <t>2026-10-17T08:35:02.224677+00:00</t>
         </is>
       </c>
     </row>
@@ -32735,7 +32775,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.537774+00:00</t>
+          <t>2026-10-17T08:35:02.224680+00:00</t>
         </is>
       </c>
     </row>
@@ -32831,7 +32871,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.537777+00:00</t>
+          <t>2026-10-17T08:35:02.224683+00:00</t>
         </is>
       </c>
     </row>
@@ -32927,7 +32967,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.537780+00:00</t>
+          <t>2026-10-17T08:35:02.224686+00:00</t>
         </is>
       </c>
     </row>
@@ -33023,7 +33063,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.537784+00:00</t>
+          <t>2026-10-17T08:35:02.224690+00:00</t>
         </is>
       </c>
     </row>
@@ -33119,7 +33159,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.537787+00:00</t>
+          <t>2026-10-17T08:35:02.224692+00:00</t>
         </is>
       </c>
     </row>
@@ -33215,7 +33255,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.537791+00:00</t>
+          <t>2026-10-17T08:35:02.224696+00:00</t>
         </is>
       </c>
     </row>
@@ -33311,7 +33351,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.537794+00:00</t>
+          <t>2026-10-17T08:35:02.224699+00:00</t>
         </is>
       </c>
     </row>
@@ -33407,7 +33447,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.537798+00:00</t>
+          <t>2026-10-17T08:35:02.224703+00:00</t>
         </is>
       </c>
     </row>
@@ -33515,7 +33555,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.538578+00:00</t>
+          <t>2026-10-17T08:35:02.225394+00:00</t>
         </is>
       </c>
     </row>
@@ -33615,7 +33655,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.538603+00:00</t>
+          <t>2026-10-17T08:35:02.225409+00:00</t>
         </is>
       </c>
     </row>
@@ -33723,7 +33763,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.538656+00:00</t>
+          <t>2026-10-17T08:35:02.225453+00:00</t>
         </is>
       </c>
     </row>
@@ -33831,7 +33871,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.538878+00:00</t>
+          <t>2026-10-17T08:35:02.225688+00:00</t>
         </is>
       </c>
     </row>
@@ -33939,7 +33979,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.539051+00:00</t>
+          <t>2026-10-17T08:35:02.225804+00:00</t>
         </is>
       </c>
     </row>
@@ -34051,7 +34091,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.539186+00:00</t>
+          <t>2026-10-17T08:35:02.225916+00:00</t>
         </is>
       </c>
     </row>
@@ -34159,7 +34199,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.539590+00:00</t>
+          <t>2026-10-17T08:35:02.226281+00:00</t>
         </is>
       </c>
     </row>
@@ -34267,7 +34307,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.539780+00:00</t>
+          <t>2026-10-17T08:35:02.226480+00:00</t>
         </is>
       </c>
     </row>
@@ -34379,7 +34419,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.539837+00:00</t>
+          <t>2026-10-17T08:35:02.226528+00:00</t>
         </is>
       </c>
     </row>
@@ -34491,7 +34531,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.539905+00:00</t>
+          <t>2026-10-17T08:35:02.226585+00:00</t>
         </is>
       </c>
     </row>
@@ -34603,7 +34643,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.540049+00:00</t>
+          <t>2026-10-17T08:35:02.226721+00:00</t>
         </is>
       </c>
     </row>
@@ -34715,7 +34755,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.540094+00:00</t>
+          <t>2026-10-17T08:35:02.226764+00:00</t>
         </is>
       </c>
     </row>
@@ -34823,7 +34863,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.540593+00:00</t>
+          <t>2026-10-17T08:35:02.227208+00:00</t>
         </is>
       </c>
     </row>
@@ -34931,7 +34971,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.540659+00:00</t>
+          <t>2026-10-17T08:35:02.227250+00:00</t>
         </is>
       </c>
     </row>
@@ -35031,7 +35071,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.540669+00:00</t>
+          <t>2026-10-17T08:35:02.227260+00:00</t>
         </is>
       </c>
     </row>
@@ -35131,7 +35171,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.540673+00:00</t>
+          <t>2026-10-17T08:35:02.227263+00:00</t>
         </is>
       </c>
     </row>
@@ -35235,7 +35275,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.540676+00:00</t>
+          <t>2026-10-17T08:35:02.227266+00:00</t>
         </is>
       </c>
     </row>
@@ -35335,7 +35375,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.540680+00:00</t>
+          <t>2026-10-17T08:35:02.227269+00:00</t>
         </is>
       </c>
     </row>
@@ -35443,7 +35483,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.540896+00:00</t>
+          <t>2026-10-17T08:35:02.227499+00:00</t>
         </is>
       </c>
     </row>
@@ -35551,7 +35591,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.541960+00:00</t>
+          <t>2026-10-17T08:35:02.228474+00:00</t>
         </is>
       </c>
     </row>
@@ -35645,7 +35685,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.541986+00:00</t>
+          <t>2026-10-17T08:35:02.228488+00:00</t>
         </is>
       </c>
     </row>
@@ -35739,7 +35779,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.541990+00:00</t>
+          <t>2026-10-17T08:35:02.228492+00:00</t>
         </is>
       </c>
     </row>
@@ -35833,7 +35873,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.541994+00:00</t>
+          <t>2026-10-17T08:35:02.228495+00:00</t>
         </is>
       </c>
     </row>
@@ -35927,7 +35967,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.541997+00:00</t>
+          <t>2026-10-17T08:35:02.228499+00:00</t>
         </is>
       </c>
     </row>
@@ -36021,7 +36061,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542001+00:00</t>
+          <t>2026-10-17T08:35:02.228502+00:00</t>
         </is>
       </c>
     </row>
@@ -36115,7 +36155,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542004+00:00</t>
+          <t>2026-10-17T08:35:02.228505+00:00</t>
         </is>
       </c>
     </row>
@@ -36209,7 +36249,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542008+00:00</t>
+          <t>2026-10-17T08:35:02.228507+00:00</t>
         </is>
       </c>
     </row>
@@ -36303,7 +36343,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542012+00:00</t>
+          <t>2026-10-17T08:35:02.228510+00:00</t>
         </is>
       </c>
     </row>
@@ -36397,7 +36437,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542015+00:00</t>
+          <t>2026-10-17T08:35:02.228513+00:00</t>
         </is>
       </c>
     </row>
@@ -36491,7 +36531,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542018+00:00</t>
+          <t>2026-10-17T08:35:02.228516+00:00</t>
         </is>
       </c>
     </row>
@@ -36585,7 +36625,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542022+00:00</t>
+          <t>2026-10-17T08:35:02.228520+00:00</t>
         </is>
       </c>
     </row>
@@ -36679,7 +36719,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542026+00:00</t>
+          <t>2026-10-17T08:35:02.228523+00:00</t>
         </is>
       </c>
     </row>
@@ -36773,7 +36813,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542030+00:00</t>
+          <t>2026-10-17T08:35:02.228526+00:00</t>
         </is>
       </c>
     </row>
@@ -36867,7 +36907,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542034+00:00</t>
+          <t>2026-10-17T08:35:02.228529+00:00</t>
         </is>
       </c>
     </row>
@@ -36961,7 +37001,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542037+00:00</t>
+          <t>2026-10-17T08:35:02.228532+00:00</t>
         </is>
       </c>
     </row>
@@ -37055,7 +37095,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542041+00:00</t>
+          <t>2026-10-17T08:35:02.228535+00:00</t>
         </is>
       </c>
     </row>
@@ -37149,7 +37189,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542044+00:00</t>
+          <t>2026-10-17T08:35:02.228539+00:00</t>
         </is>
       </c>
     </row>
@@ -37243,7 +37283,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542048+00:00</t>
+          <t>2026-10-17T08:35:02.228542+00:00</t>
         </is>
       </c>
     </row>
@@ -37337,7 +37377,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542052+00:00</t>
+          <t>2026-10-17T08:35:02.228545+00:00</t>
         </is>
       </c>
     </row>
@@ -37431,7 +37471,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542055+00:00</t>
+          <t>2026-10-17T08:35:02.228548+00:00</t>
         </is>
       </c>
     </row>
@@ -37525,7 +37565,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542058+00:00</t>
+          <t>2026-10-17T08:35:02.228550+00:00</t>
         </is>
       </c>
     </row>
@@ -37619,7 +37659,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542062+00:00</t>
+          <t>2026-10-17T08:35:02.228553+00:00</t>
         </is>
       </c>
     </row>
@@ -37713,7 +37753,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542065+00:00</t>
+          <t>2026-10-17T08:35:02.228557+00:00</t>
         </is>
       </c>
     </row>
@@ -37807,7 +37847,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542069+00:00</t>
+          <t>2026-10-17T08:35:02.228560+00:00</t>
         </is>
       </c>
     </row>
@@ -37901,7 +37941,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542073+00:00</t>
+          <t>2026-10-17T08:35:02.228563+00:00</t>
         </is>
       </c>
     </row>
@@ -37995,7 +38035,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542076+00:00</t>
+          <t>2026-10-17T08:35:02.228566+00:00</t>
         </is>
       </c>
     </row>
@@ -38089,7 +38129,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542079+00:00</t>
+          <t>2026-10-17T08:35:02.228568+00:00</t>
         </is>
       </c>
     </row>
@@ -38189,7 +38229,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T08:34:16.542082+00:00</t>
+          <t>2026-10-17T08:35:02.228571+00:00</t>
         </is>
       </c>
     </row>
@@ -38204,7 +38244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38332,12 +38372,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R12483</t>
+          <t>R13877</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R12483.main.b51428ca89e5bf95</t>
+          <t>R13877.main.04a76adc76fa9472</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -38347,20 +38387,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>b51428ca89e5bf95c17225fe2e0a08a920379629281ab76f33337561553f3b0f</t>
+          <t>04a76adc76fa947250861c95c93759c590dd3e02d7f80dc23ce0abedccb74510</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1807518</v>
+        <v>522402</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://li01.tci-thaijo.org/index.php/TSAEJ/article/download/269146/181297</t>
+          <t>https://escholarship.org/content/qt5572k7rw/qt5572k7rw.pdf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>R12483_2025_การปรบสภาพชวมวลลกโนเซลลโลสดวยวสดเพาะเหดเหลอทง_แนวทางการเพมมล.pdf</t>
+          <t>R13877_2018_Microbial_community_response_and_SDS-PAGE_reveal_possible_mechanism_of.pdf</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -38372,12 +38412,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R13819</t>
+          <t>R13862</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R13819.main.431f5e76781d3cef</t>
+          <t>R13862.main.64e03a9beb5813a0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -38387,20 +38427,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>431f5e76781d3cef39588c258c5589b1c9cf01db486c503ba29ab166bc73f14a</t>
+          <t>64e03a9beb5813a0ce6d94272350217f12dac94293420969e3d2d9d7975e96e3</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2172752</v>
+        <v>833659</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://epublications.marquette.edu/cgi/viewcontent.cgi?article=1131&amp;context=civengin_fac</t>
+          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/eb850f96-0570-4e0d-be55-73fcee5f1364/content</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>R13819_2015_Bioaugmentation_of_overloaded_anaerobic_digesters_restores_function_and_archaeal.pdf</t>
+          <t>R13862_2020_Multiple_and_flexible_roles_of_facultative_anaerobic_bacteria_in.pdf</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -38412,12 +38452,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R13833</t>
+          <t>R13900</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R13833.main.1a4a4d5f8fd45de9</t>
+          <t>R13900.main.b2ba7df8c04ab66c</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -38427,20 +38467,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1a4a4d5f8fd45de924c78a7be11e1c032c630bd9341431d1d49135c8351cdaf7</t>
+          <t>b2ba7df8c04ab66c0e548f778e19c5764802c0da8408a3b8499547b3f6ef51b3</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1463714</v>
+        <v>299244</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/234ac4ff-f996-498f-8853-72ba22cb7700/content</t>
+          <t>https://www.research.unipd.it/bitstream/11577/3261852/1/Front.%20Environ.%20Sci.%20Eng%20Dongbei%202018.pdf</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>R13833_2018_Insight_into_the_Role_of_Facultative_Bacteria_Stimulated_by.pdf</t>
+          <t>R13900_2018_Effectiveness_of_aerobic_pretreatment_of_municipal_solid_waste_for.pdf</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -38452,12 +38492,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R13861</t>
+          <t>R13903</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R13861.main.ba6f44b77d79c4a0</t>
+          <t>R13903.main.2cd9e7b409250e7b</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -38467,20 +38507,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ba6f44b77d79c4a07ba08602860bcf1bdbb36cb47b4527fa9d1f087825e394d8</t>
+          <t>2cd9e7b409250e7b104f489e139f57d4daa40d97133c6c57c937184c3ec73b71</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>433474</v>
+        <v>1107675</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.scielo.br/j/esa/a/BD6Bc5rMVrTsbkK7CZz6yVd/?format=pdf&amp;lang=en&amp;ilang=pt_BR</t>
+          <t>https://ijabe.org/index.php/ijabe/article/download/7975/pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>R13861_2019_Enhanced_removal_of_emerging_micropollutants_by_applying_microaeration_to.pdf</t>
+          <t>R13903_2023_Effect_of_vacuum_negative_pressure_aerobic_hydrolysis_pretreatment_on.pdf</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -38492,12 +38532,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R13871</t>
+          <t>R13931</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R13871.main.aeab3126b6e68775</t>
+          <t>R13931.main.6e898a403edac7b3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -38507,20 +38547,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>aeab3126b6e68775b9b316714633bd97c1f184cf9e308d75b404bca6b33be19f</t>
+          <t>6e898a403edac7b3ae15ad88cf75788898cd84ea377b2572f7bab40d9c126f8c</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7983514</v>
+        <v>1324593</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://etheses.whiterose.ac.uk/id/eprint/4094/6/Mahmood_Khazzal_Hummadi_Al-Mashhadani._Reg._No._080243946_%28PhD_thesis%29_2013.pdf</t>
+          <t>https://www.eeer.org/upload/eer-2020-470.pdf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>R13871_2013_Application_of_Microbubbles_Generated_by_Fluidic_Oscillation_in_the.pdf</t>
+          <t>R13931_2020_Biogas_recovery_from_fresh_landfill_leachates_by_using_a.pdf</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -38532,12 +38572,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R13877</t>
+          <t>R13945</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R13877.main.04a76adc76fa9472</t>
+          <t>R13945.main.67309ea094d2f9bb</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -38547,20 +38587,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>04a76adc76fa947250861c95c93759c590dd3e02d7f80dc23ce0abedccb74510</t>
+          <t>67309ea094d2f9bb088d605746ede869866819a733f53c44dc2d44af934e6be9</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>522402</v>
+        <v>2230958</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://escholarship.org/content/qt5572k7rw/qt5572k7rw.pdf</t>
+          <t>https://epublications.marquette.edu/cgi/viewcontent.cgi?article=1459&amp;context=theses_open</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>R13877_2018_Microbial_community_response_and_SDS-PAGE_reveal_possible_mechanism_of.pdf</t>
+          <t>R13945_2018_Effect_of_Low_Aeration_and_Heat_Drying_on_Anaerobic.pdf</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -38572,12 +38612,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R13862</t>
+          <t>R13950</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R13862.main.64e03a9beb5813a0</t>
+          <t>R13950.main.2bf9b46c448685b9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -38587,20 +38627,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>64e03a9beb5813a0ce6d94272350217f12dac94293420969e3d2d9d7975e96e3</t>
+          <t>2bf9b46c448685b9e66f4064245c5840dc28ded79ee4d613ddd9efeb4805812e</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>833659</v>
+        <v>3508852</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/eb850f96-0570-4e0d-be55-73fcee5f1364/content</t>
+          <t>https://www.research.unipd.it/bitstream/11577/3425227/1/Thesis_Razieh_Rafieenia.pdf</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>R13862_2020_Multiple_and_flexible_roles_of_facultative_anaerobic_bacteria_in.pdf</t>
+          <t>R13950_2019_Enhancement_of_hydrogen_and_methane_production_through_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -38612,12 +38652,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R13900</t>
+          <t>R13944</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R13900.main.b2ba7df8c04ab66c</t>
+          <t>R13944.main.7e22fbfd39ddfed0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -38627,20 +38667,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>b2ba7df8c04ab66c0e548f778e19c5764802c0da8408a3b8499547b3f6ef51b3</t>
+          <t>7e22fbfd39ddfed09b9235fea5c6914cfbe5987d12564fc9cb799bf412ae6779</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>299244</v>
+        <v>12042699</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.research.unipd.it/bitstream/11577/3261852/1/Front.%20Environ.%20Sci.%20Eng%20Dongbei%202018.pdf</t>
+          <t>https://scholarspace.manoa.hawaii.edu/server/api/core/bitstreams/60c88164-f37f-492a-97bc-e34a2f2b1698/content</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>R13900_2018_Effectiveness_of_aerobic_pretreatment_of_municipal_solid_waste_for.pdf</t>
+          <t>R13944_2018_Oxidation-Reduction_Potential-Based_Micro-Aeration_Control_System_for_Anaerobic_Digestion.pdf</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -38652,12 +38692,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R13903</t>
+          <t>R13967</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R13903.main.2cd9e7b409250e7b</t>
+          <t>R13967.main.5e9f84dbaf01dd19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -38667,20 +38707,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2cd9e7b409250e7b104f489e139f57d4daa40d97133c6c57c937184c3ec73b71</t>
+          <t>5e9f84dbaf01dd19674f09cbce96f338f32fe21a37a883bb9658e49af7072194</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1107675</v>
+        <v>160020</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://ijabe.org/index.php/ijabe/article/download/7975/pdf</t>
+          <t>https://www.aceee.org/wp-content/uploads/proceedings-1980-2020/2012/0193-000342.pdf</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>R13903_2023_Effect_of_vacuum_negative_pressure_aerobic_hydrolysis_pretreatment_on.pdf</t>
+          <t>R13967_2012_An_Improved_Biomass_Waste_Anaerobic_Degradation_Technology_for_Producing.pdf</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -38692,12 +38732,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R13931</t>
+          <t>R13972</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R13931.main.6e898a403edac7b3</t>
+          <t>R13972.main.ff4ee9377a7e227c</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -38707,20 +38747,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6e898a403edac7b3ae15ad88cf75788898cd84ea377b2572f7bab40d9c126f8c</t>
+          <t>ff4ee9377a7e227c48a5bc64d301bfc1a989ee0e709c322eb90f254819d7b391</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1324593</v>
+        <v>1192569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.eeer.org/upload/eer-2020-470.pdf</t>
+          <t>https://www.osti.gov/servlets/purl/2386939</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>R13931_2020_Biogas_recovery_from_fresh_landfill_leachates_by_using_a.pdf</t>
+          <t>R13972_2022_Enhancing_methane_production_of_anaerobic_digested_sewage_sludge_by.pdf</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -38732,12 +38772,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R13945</t>
+          <t>R13957</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R13945.main.67309ea094d2f9bb</t>
+          <t>R13957.main.3db804dcdefb7608</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -38747,20 +38787,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>67309ea094d2f9bb088d605746ede869866819a733f53c44dc2d44af934e6be9</t>
+          <t>3db804dcdefb7608eefc6bf166b0713cbbec8ac027b1c01831aec97b54253b82</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2230958</v>
+        <v>7806265</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://epublications.marquette.edu/cgi/viewcontent.cgi?article=1459&amp;context=theses_open</t>
+          <t>https://backoffice.biblio.ugent.be/download/8530499/8530500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>R13945_2018_Effect_of_Low_Aeration_and_Heat_Drying_on_Anaerobic.pdf</t>
+          <t>R13957_2017_Microaeration_for_biogas_desulfurization_experimental_and_simulation_study_of.pdf</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -38772,12 +38812,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R13950</t>
+          <t>R04510</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R13950.main.2bf9b46c448685b9</t>
+          <t>R04510.main.c4520ca79e301bb6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -38787,20 +38827,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2bf9b46c448685b9e66f4064245c5840dc28ded79ee4d613ddd9efeb4805812e</t>
+          <t>c4520ca79e301bb606a8ab1fef6cf4af9064c0d85f3c390a4cf31a877238e1c6</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3508852</v>
+        <v>492630</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.research.unipd.it/bitstream/11577/3425227/1/Thesis_Razieh_Rafieenia.pdf</t>
+          <t>https://digital.csic.es/bitstream/10261/196040/5/PostP_2019_JESH_V54_Iss10.pdf</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>R13950_2019_Enhancement_of_hydrogen_and_methane_production_through_anaerobic_digestion.pdf</t>
+          <t>R04510_2019_Anaerobic_digestion_of_wastewater_rich_in_sulfate_and_sulfide_effects_of_metallic_waste_addition_and.pdf</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -38812,12 +38852,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R13944</t>
+          <t>R13889</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R13944.main.7e22fbfd39ddfed0</t>
+          <t>R13889.main.8db0dcdf434e876e</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -38827,20 +38867,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7e22fbfd39ddfed09b9235fea5c6914cfbe5987d12564fc9cb799bf412ae6779</t>
+          <t>8db0dcdf434e876e7cbff3cf342105807bdd41a900f74c0028cb14a6c6e56779</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12042699</v>
+        <v>514378</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://scholarspace.manoa.hawaii.edu/server/api/core/bitstreams/60c88164-f37f-492a-97bc-e34a2f2b1698/content</t>
+          <t>https://digital.csic.es/bitstream/10261/178890/1/PotP_2018_RE_V123_P541.pdf</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>R13944_2018_Oxidation-Reduction_Potential-Based_Micro-Aeration_Control_System_for_Anaerobic_Digestion.pdf</t>
+          <t>R13889_2018_Increase_in_biogas_production_in_anaerobic_sludge_digestion_by_combining_aerobic_hydrolysis_and_addi.pdf</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -38852,12 +38892,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R13967</t>
+          <t>R02719</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R13967.main.5e9f84dbaf01dd19</t>
+          <t>R02719.main.4bf5e309b2ef3431</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -38867,20 +38907,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5e9f84dbaf01dd19674f09cbce96f338f32fe21a37a883bb9658e49af7072194</t>
+          <t>4bf5e309b2ef343162a9588383a7ae0254118c33cdf2e96bec1a05459fae1523</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>160020</v>
+        <v>583591</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.aceee.org/wp-content/uploads/proceedings-1980-2020/2012/0193-000342.pdf</t>
+          <t>https://digital.csic.es/bitstream/10261/137944/1/Post_2016_JEnvSciHealth_A_BorjaR.pdf</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>R13967_2012_An_Improved_Biomass_Waste_Anaerobic_Degradation_Technology_for_Producing.pdf</t>
+          <t>R02719_2016_Performance_evaluation_of_micro_aerobic_hydrolysis_of_mixed_sludge_Optimum_aeration_and_effect_on_it.pdf</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -38892,12 +38932,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R13972</t>
+          <t>R02282</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R13972.main.ff4ee9377a7e227c</t>
+          <t>R02282.main.e709439b748e7938</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -38907,20 +38947,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ff4ee9377a7e227c48a5bc64d301bfc1a989ee0e709c322eb90f254819d7b391</t>
+          <t>e709439b748e793826102646c009aa10e1e9ac30627ac301fac7dd42276a2047</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1192569</v>
+        <v>1067465</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.osti.gov/servlets/purl/2386939</t>
+          <t>https://digital.csic.es/bitstream/10261/130093/1/Postprint_2016_EnviromRev_V24_P84.pdf</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>R13972_2022_Enhancing_methane_production_of_anaerobic_digested_sewage_sludge_by.pdf</t>
+          <t>R02282_2016_Advances_in_the_biological_removal_of_sulphides_from_aqueous_phase_in_anaerobic_processes_A_review.pdf</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -38932,12 +38972,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R13957</t>
+          <t>R13905</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R13957.main.3db804dcdefb7608</t>
+          <t>R13905.main.c75b5084c2545bd9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -38947,20 +38987,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3db804dcdefb7608eefc6bf166b0713cbbec8ac027b1c01831aec97b54253b82</t>
+          <t>c75b5084c2545bd939d3b1928be41fe0072c7302f26c25ba023c4bb6fc8a6970</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>7806265</v>
+        <v>2159708</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://backoffice.biblio.ugent.be/download/8530499/8530500</t>
+          <t>https://ddd.uab.cat/pub/artpub/2017/196242/wasbioval_a2017m7v8n5p1793.pdf</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>R13957_2017_Microaeration_for_biogas_desulfurization_experimental_and_simulation_study_of.pdf</t>
+          <t>R13905_2017_The_Effect_of_a_Short_Term_Aerobic_Pretreatment_Step_on_the_Anaerobic_Co_digestion_of_the_Organic_Fr.pdf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -38972,12 +39012,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R04510</t>
+          <t>R13932</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R04510.main.c4520ca79e301bb6</t>
+          <t>R13932.main.c15f49a3d617e1be</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -38987,20 +39027,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>c4520ca79e301bb606a8ab1fef6cf4af9064c0d85f3c390a4cf31a877238e1c6</t>
+          <t>c15f49a3d617e1be5e21578ebda1c2d855f8d460c1d66f446ad0d02856a40a13</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>492630</v>
+        <v>1258157</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/196040/5/PostP_2019_JESH_V54_Iss10.pdf</t>
+          <t>https://hal.inrae.fr/hal-02620984/document</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>R04510_2019_Anaerobic_digestion_of_wastewater_rich_in_sulfate_and_sulfide_effects_of_metallic_waste_addition_and.pdf</t>
+          <t>R13932_2018_Comparison_of_pre_and_inter_stage_aerobic_treatment_of_wastewater_sludge_Effects_on_biogas_productio.pdf</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -39012,12 +39052,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R13889</t>
+          <t>R13956</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R13889.main.8db0dcdf434e876e</t>
+          <t>R13956.main.fedaffcdf5be81e2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -39027,20 +39067,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8db0dcdf434e876e7cbff3cf342105807bdd41a900f74c0028cb14a6c6e56779</t>
+          <t>fedaffcdf5be81e2070b7edb0531c332e423578228eeb8c55a6afc4ba8fe1e18</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>514378</v>
+        <v>421626</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/178890/1/PotP_2018_RE_V123_P541.pdf</t>
+          <t>https://www.banglajol.info/index.php/BJSIR/article/download/25579/17152</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>R13889_2018_Increase_in_biogas_production_in_anaerobic_sludge_digestion_by_combining_aerobic_hydrolysis_and_addi.pdf</t>
+          <t>R13956_2015_Anaerobic_digestion_of_mixed_dried_fallen_leaves_by_mixing_with_cow_dung.pdf</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -39052,12 +39092,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R02719</t>
+          <t>R13955</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R02719.main.4bf5e309b2ef3431</t>
+          <t>R13955.main.7549e1025985363e</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -39067,20 +39107,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4bf5e309b2ef343162a9588383a7ae0254118c33cdf2e96bec1a05459fae1523</t>
+          <t>7549e1025985363e89542bbc1af6eaaa1150bbd62ea43bdd03d2c7b764631f9d</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>583591</v>
+        <v>14662438</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/137944/1/Post_2016_JEnvSciHealth_A_BorjaR.pdf</t>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>R02719_2016_Performance_evaluation_of_micro_aerobic_hydrolysis_of_mixed_sludge_Optimum_aeration_and_effect_on_it.pdf</t>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -39092,35 +39132,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R02282</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R02282.main.e709439b748e7938</t>
+          <t>R07238.supplementary.0b7925ad1ed9c793</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>e709439b748e793826102646c009aa10e1e9ac30627ac301fac7dd42276a2047</t>
+          <t>0b7925ad1ed9c7939a79ba6294d17abc4b23fca77e52ec50df5463d050940d1e</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1067465</v>
+        <v>49526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/130093/1/Postprint_2016_EnviromRev_V24_P84.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>R02282_2016_Advances_in_the_biological_removal_of_sulphides_from_aqueous_phase_in_anaerobic_processes_A_review.pdf</t>
+          <t>mmc1.docx</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -39132,35 +39172,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R13905</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R13905.main.c75b5084c2545bd9</t>
+          <t>R07238.supplementary.f346f9bdcc964013</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>c75b5084c2545bd939d3b1928be41fe0072c7302f26c25ba023c4bb6fc8a6970</t>
+          <t>f346f9bdcc964013ecb7c4282d6b30f1ab334e035d98adcc653de1447fbe9a9a</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2159708</v>
+        <v>14286928</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://ddd.uab.cat/pub/artpub/2017/196242/wasbioval_a2017m7v8n5p1793.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>R13905_2017_The_Effect_of_a_Short_Term_Aerobic_Pretreatment_Step_on_the_Anaerobic_Co_digestion_of_the_Organic_Fr.pdf</t>
+          <t>mmc2.zip</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -39172,35 +39212,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R13932</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R13932.main.c15f49a3d617e1be</t>
+          <t>R07238.derived.49b84e369d4bb31b</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>c15f49a3d617e1be5e21578ebda1c2d855f8d460c1d66f446ad0d02856a40a13</t>
+          <t>49b84e369d4bb31b4ebdcd25265be3174105c3433e6fbb865f34a445775516a1</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1258157</v>
+        <v>34855493</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://hal.inrae.fr/hal-02620984/document</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>R13932_2018_Comparison_of_pre_and_inter_stage_aerobic_treatment_of_wastewater_sludge_Effects_on_biogas_productio.pdf</t>
+          <t>g a.skp</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -39212,35 +39252,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R13956</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R13956.main.fedaffcdf5be81e2</t>
+          <t>R08646.supplementary.cfda7e29b12b9784</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>fedaffcdf5be81e2070b7edb0531c332e423578228eeb8c55a6afc4ba8fe1e18</t>
+          <t>cfda7e29b12b97846343963f9f3b64e784bc79644fb1ee1ca31170be78d75327</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>421626</v>
+        <v>42279</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.banglajol.info/index.php/BJSIR/article/download/25579/17152</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>R13956_2015_Anaerobic_digestion_of_mixed_dried_fallen_leaves_by_mixing_with_cow_dung.pdf</t>
+          <t>mmc1.docx</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -39252,35 +39292,35 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>R13955</t>
+          <t>R03161</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R13955.main.7549e1025985363e</t>
+          <t>R03161.evidence_xml.466f3a1e78e8b0f1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7549e1025985363e89542bbc1af6eaaa1150bbd62ea43bdd03d2c7b764631f9d</t>
+          <t>466f3a1e78e8b0f148b1f28f97b61f7134c61488c837c5c5a26ef7316cebc1e9</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>14662438</v>
+        <v>59018</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/fullTextXML</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
+          <t>PMC5627928_fullText.xml</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -39292,35 +39332,35 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R03161</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R07238.supplementary.0b7925ad1ed9c793</t>
+          <t>R03161.transport_archive.0ef4d4796c84feff</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0b7925ad1ed9c7939a79ba6294d17abc4b23fca77e52ec50df5463d050940d1e</t>
+          <t>0ef4d4796c84fefff7b8450bc56400f8c59f4bdcf074fc51404edff5e4e217f6</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>49526</v>
+        <v>726772</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/supplementaryFiles</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>mmc1.docx</t>
+          <t>PMC5627928_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -39332,35 +39372,35 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R04092</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>R07238.supplementary.f346f9bdcc964013</t>
+          <t>R04092.evidence_xml.0fb90085e30680fa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>f346f9bdcc964013ecb7c4282d6b30f1ab334e035d98adcc653de1447fbe9a9a</t>
+          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>14286928</v>
+        <v>77995</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>mmc2.zip</t>
+          <t>PMC6288047_fullText.xml</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -39372,35 +39412,35 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R05839</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R07238.derived.49b84e369d4bb31b</t>
+          <t>R05839.evidence_xml.18ffd43dee955086</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>49b84e369d4bb31b4ebdcd25265be3174105c3433e6fbb865f34a445775516a1</t>
+          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>34855493</v>
+        <v>75205</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>g a.skp</t>
+          <t>PMC7566014_fullText.xml</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -39412,35 +39452,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R08877</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R08646.supplementary.cfda7e29b12b9784</t>
+          <t>R08877.evidence_xml.e8712e4198baab4c</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>cfda7e29b12b97846343963f9f3b64e784bc79644fb1ee1ca31170be78d75327</t>
+          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>42279</v>
+        <v>111864</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>mmc1.docx</t>
+          <t>PMC10714394_fullText.xml</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -39452,35 +39492,35 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>R03161</t>
+          <t>R08877</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R03161.evidence_xml.466f3a1e78e8b0f1</t>
+          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>466f3a1e78e8b0f148b1f28f97b61f7134c61488c837c5c5a26ef7316cebc1e9</t>
+          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>59018</v>
+        <v>704921</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PMC5627928_fullText.xml</t>
+          <t>PMC10714394_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -39492,35 +39532,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R03161</t>
+          <t>R09236</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R03161.transport_archive.0ef4d4796c84feff</t>
+          <t>R09236.evidence_xml.72064fe9276d8309</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0ef4d4796c84fefff7b8450bc56400f8c59f4bdcf074fc51404edff5e4e217f6</t>
+          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>726772</v>
+        <v>193052</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PMC5627928_supplementaryFiles.zip</t>
+          <t>PMC10535533_fullText.xml</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -39532,35 +39572,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>R04092</t>
+          <t>R09236</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>R04092.evidence_xml.0fb90085e30680fa</t>
+          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
+          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>77995</v>
+        <v>483405</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>PMC6288047_fullText.xml</t>
+          <t>PMC10535533_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -39572,12 +39612,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>R05839</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>R05839.evidence_xml.18ffd43dee955086</t>
+          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -39587,20 +39627,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
+          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>75205</v>
+        <v>118002</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>PMC7566014_fullText.xml</t>
+          <t>PMC10837232_fullText.xml</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -39612,35 +39652,35 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R08877.evidence_xml.e8712e4198baab4c</t>
+          <t>R10086.transport_archive.4d9eddf454b786ed</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
+          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>111864</v>
+        <v>641038</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>PMC10714394_fullText.xml</t>
+          <t>PMC10837232_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -39652,35 +39692,35 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
+          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
+          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>704921</v>
+        <v>173586</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>PMC10714394_supplementaryFiles.zip</t>
+          <t>PMC12937426_fullText.xml</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -39692,35 +39732,35 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R09236.evidence_xml.72064fe9276d8309</t>
+          <t>R12985.transport_archive.418d45f1ca296020</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
+          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>193052</v>
+        <v>672244</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>PMC10535533_fullText.xml</t>
+          <t>PMC12937426_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -39732,35 +39772,35 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R05542</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
+          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
+          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>483405</v>
+        <v>100215</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>PMC10535533_supplementaryFiles.zip</t>
+          <t>PMC9056904_fullText.xml</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -39772,12 +39812,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
+          <t>R06325.evidence_xml.645deb707d3790b5</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -39787,20 +39827,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
+          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>118002</v>
+        <v>160509</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>PMC10837232_fullText.xml</t>
+          <t>PMC8290346_fullText.xml</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -39812,12 +39852,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>R10086.transport_archive.4d9eddf454b786ed</t>
+          <t>R06325.transport_archive.6eb4ef126661714a</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -39827,20 +39867,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
+          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>641038</v>
+        <v>1730580</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>PMC10837232_supplementaryFiles.zip</t>
+          <t>PMC8290346_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -39852,12 +39892,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
+          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -39867,20 +39907,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
+          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>173586</v>
+        <v>151458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>PMC12937426_fullText.xml</t>
+          <t>PMC8044681_fullText.xml</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -39892,12 +39932,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>R12985.transport_archive.418d45f1ca296020</t>
+          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -39907,20 +39947,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
+          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>672244</v>
+        <v>14596266</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>PMC12937426_supplementaryFiles.zip</t>
+          <t>PMC8044681_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -39932,12 +39972,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>R05542</t>
+          <t>R03477</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
+          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -39947,20 +39987,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
+          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100215</v>
+        <v>121650</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>PMC9056904_fullText.xml</t>
+          <t>PMC5371168_fullText.xml</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -39972,12 +40012,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>R06325.evidence_xml.645deb707d3790b5</t>
+          <t>R08646.evidence_xml.c7b723e8020f6582</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -39987,20 +40027,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
+          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>160509</v>
+        <v>304277</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>PMC8290346_fullText.xml</t>
+          <t>PMC10559078_fullText.xml</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -40012,12 +40052,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>R06325.transport_archive.6eb4ef126661714a</t>
+          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -40027,20 +40067,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
+          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1730580</v>
+        <v>1539133</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>PMC8290346_supplementaryFiles.zip</t>
+          <t>PMC10559078_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -40052,12 +40092,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R09804</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
+          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -40067,20 +40107,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
+          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>151458</v>
+        <v>211630</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>PMC8044681_fullText.xml</t>
+          <t>PMC11076452_fullText.xml</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -40092,35 +40132,35 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R11503</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
+          <t>R11503.evidence_xml.4002d57be59c215c</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
+          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>14596266</v>
+        <v>258637</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>PMC8044681_supplementaryFiles.zip</t>
+          <t>PMC12561102_fullText.xml</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -40132,12 +40172,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>R03477</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
+          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -40147,20 +40187,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
+          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>121650</v>
+        <v>256247</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>PMC5371168_fullText.xml</t>
+          <t>PMC12125087_fullText.xml</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -40172,35 +40212,35 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>R08646.evidence_xml.c7b723e8020f6582</t>
+          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
+          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>304277</v>
+        <v>521862</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>PMC10559078_fullText.xml</t>
+          <t>PMC12125087_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -40212,35 +40252,35 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
+          <t>R05213.evidence_xml.17894ab410001846</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
+          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1539133</v>
+        <v>130954</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>PMC10559078_supplementaryFiles.zip</t>
+          <t>PMC6858683_fullText.xml</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -40252,35 +40292,35 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
+          <t>R05213.transport_archive.c61c88cf9fd489be</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
+          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>211630</v>
+        <v>1960371</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>PMC11076452_fullText.xml</t>
+          <t>PMC6858683_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -40292,12 +40332,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>R11503</t>
+          <t>R09585</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>R11503.evidence_xml.4002d57be59c215c</t>
+          <t>R09585.evidence_xml.a3430f38fa1652de</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -40307,20 +40347,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
+          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>258637</v>
+        <v>100534</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>PMC12561102_fullText.xml</t>
+          <t>PMC10609292_fullText.xml</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -40332,238 +40372,38 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R11596</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
+          <t>R11596.main.0b2e2d98dffd5449</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
+          <t>0b2e2d98dffd544958b06cc2229d310e4b7d529bd3914c47f20d6a66789a28be</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>256247</v>
+        <v>1659399</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
+          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/7262c516-6b14-4001-a173-517d1187c8d9/content</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>PMC12125087_fullText.xml</t>
+          <t>R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>R11844</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>transport_archive</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>521862</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>PMC12125087_supplementaryFiles.zip</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>R05213</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>R05213.evidence_xml.17894ab410001846</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>evidence_xml</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>130954</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>PMC6858683_fullText.xml</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>R05213</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>R05213.transport_archive.c61c88cf9fd489be</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>transport_archive</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>1960371</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>PMC6858683_supplementaryFiles.zip</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>R09585</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>R09585.evidence_xml.a3430f38fa1652de</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>evidence_xml</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>100534</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>PMC10609292_fullText.xml</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>R11596</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>R11596.main.0b2e2d98dffd5449</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>0b2e2d98dffd544958b06cc2229d310e4b7d529bd3914c47f20d6a66789a28be</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>1659399</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/7262c516-6b14-4001-a173-517d1187c8d9/content</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
         <is>
           <t>历史已获取，当前原件未恢复</t>
         </is>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -19414,7 +19414,7 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
@@ -21040,7 +21040,7 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
@@ -21169,7 +21169,7 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
@@ -22920,7 +22920,7 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
@@ -23131,7 +23131,7 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.115012+00:00</t>
+          <t>2026-10-17T08:35:55.304906+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.115895+00:00</t>
+          <t>2026-10-17T08:35:55.305829+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.115914+00:00</t>
+          <t>2026-10-17T08:35:55.305850+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.116127+00:00</t>
+          <t>2026-10-17T08:35:55.306085+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.117453+00:00</t>
+          <t>2026-10-17T08:35:55.307196+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.117956+00:00</t>
+          <t>2026-10-17T08:35:55.307749+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.123997+00:00</t>
+          <t>2026-10-17T08:35:55.313697+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.126330+00:00</t>
+          <t>2026-10-17T08:35:55.316024+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.127202+00:00</t>
+          <t>2026-10-17T08:35:55.316986+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.127524+00:00</t>
+          <t>2026-10-17T08:35:55.317336+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.128468+00:00</t>
+          <t>2026-10-17T08:35:55.318229+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.129147+00:00</t>
+          <t>2026-10-17T08:35:55.318966+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.130153+00:00</t>
+          <t>2026-10-17T08:35:55.319879+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.130417+00:00</t>
+          <t>2026-10-17T08:35:55.320125+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.131265+00:00</t>
+          <t>2026-10-17T08:35:55.320981+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.139830+00:00</t>
+          <t>2026-10-17T08:35:55.328703+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.140561+00:00</t>
+          <t>2026-10-17T08:35:55.329497+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.141747+00:00</t>
+          <t>2026-10-17T08:35:55.330758+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.144238+00:00</t>
+          <t>2026-10-17T08:35:55.333211+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.145314+00:00</t>
+          <t>2026-10-17T08:35:55.334314+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.146511+00:00</t>
+          <t>2026-10-17T08:35:55.335504+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.150591+00:00</t>
+          <t>2026-10-17T08:35:55.340048+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.152734+00:00</t>
+          <t>2026-10-17T08:35:55.342226+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.154517+00:00</t>
+          <t>2026-10-17T08:35:55.343993+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.155324+00:00</t>
+          <t>2026-10-17T08:35:55.344655+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.155693+00:00</t>
+          <t>2026-10-17T08:35:55.345140+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.157838+00:00</t>
+          <t>2026-10-17T08:35:55.347224+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.159185+00:00</t>
+          <t>2026-10-17T08:35:55.348554+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.161413+00:00</t>
+          <t>2026-10-17T08:35:55.350770+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.163426+00:00</t>
+          <t>2026-10-17T08:35:55.352799+00:00</t>
         </is>
       </c>
     </row>
@@ -27571,7 +27571,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.163449+00:00</t>
+          <t>2026-10-17T08:35:55.352823+00:00</t>
         </is>
       </c>
     </row>
@@ -27679,7 +27679,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.163989+00:00</t>
+          <t>2026-10-17T08:35:55.353536+00:00</t>
         </is>
       </c>
     </row>
@@ -27787,7 +27787,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.165604+00:00</t>
+          <t>2026-10-17T08:35:55.355343+00:00</t>
         </is>
       </c>
     </row>
@@ -27895,7 +27895,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.168419+00:00</t>
+          <t>2026-10-17T08:35:55.358148+00:00</t>
         </is>
       </c>
     </row>
@@ -28003,7 +28003,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.170502+00:00</t>
+          <t>2026-10-17T08:35:55.360212+00:00</t>
         </is>
       </c>
     </row>
@@ -28111,7 +28111,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.171672+00:00</t>
+          <t>2026-10-17T08:35:55.361404+00:00</t>
         </is>
       </c>
     </row>
@@ -28219,7 +28219,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.174605+00:00</t>
+          <t>2026-10-17T08:35:55.364642+00:00</t>
         </is>
       </c>
     </row>
@@ -28327,7 +28327,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.175380+00:00</t>
+          <t>2026-10-17T08:35:55.365523+00:00</t>
         </is>
       </c>
     </row>
@@ -28435,7 +28435,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.176958+00:00</t>
+          <t>2026-10-17T08:35:55.367105+00:00</t>
         </is>
       </c>
     </row>
@@ -28543,7 +28543,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.177197+00:00</t>
+          <t>2026-10-17T08:35:55.367389+00:00</t>
         </is>
       </c>
     </row>
@@ -28651,7 +28651,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.179271+00:00</t>
+          <t>2026-10-17T08:35:55.369531+00:00</t>
         </is>
       </c>
     </row>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.182269+00:00</t>
+          <t>2026-10-17T08:35:55.372650+00:00</t>
         </is>
       </c>
     </row>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.183582+00:00</t>
+          <t>2026-10-17T08:35:55.373987+00:00</t>
         </is>
       </c>
     </row>
@@ -28975,7 +28975,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.184098+00:00</t>
+          <t>2026-10-17T08:35:55.374591+00:00</t>
         </is>
       </c>
     </row>
@@ -29083,7 +29083,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.186692+00:00</t>
+          <t>2026-10-17T08:35:55.377339+00:00</t>
         </is>
       </c>
     </row>
@@ -29191,7 +29191,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.187948+00:00</t>
+          <t>2026-10-17T08:35:55.378803+00:00</t>
         </is>
       </c>
     </row>
@@ -29299,7 +29299,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.191399+00:00</t>
+          <t>2026-10-17T08:35:55.382279+00:00</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.193019+00:00</t>
+          <t>2026-10-17T08:35:55.383975+00:00</t>
         </is>
       </c>
     </row>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.194843+00:00</t>
+          <t>2026-10-17T08:35:55.385804+00:00</t>
         </is>
       </c>
     </row>
@@ -29623,7 +29623,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.195763+00:00</t>
+          <t>2026-10-17T08:35:55.386732+00:00</t>
         </is>
       </c>
     </row>
@@ -29731,7 +29731,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.196181+00:00</t>
+          <t>2026-10-17T08:35:55.387243+00:00</t>
         </is>
       </c>
     </row>
@@ -29839,7 +29839,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.196552+00:00</t>
+          <t>2026-10-17T08:35:55.387642+00:00</t>
         </is>
       </c>
     </row>
@@ -29947,7 +29947,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.198016+00:00</t>
+          <t>2026-10-17T08:35:55.389128+00:00</t>
         </is>
       </c>
     </row>
@@ -30055,7 +30055,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.199283+00:00</t>
+          <t>2026-10-17T08:35:55.390494+00:00</t>
         </is>
       </c>
     </row>
@@ -30163,7 +30163,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.200761+00:00</t>
+          <t>2026-10-17T08:35:55.391979+00:00</t>
         </is>
       </c>
     </row>
@@ -30271,7 +30271,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.201081+00:00</t>
+          <t>2026-10-17T08:35:55.392314+00:00</t>
         </is>
       </c>
     </row>
@@ -30379,7 +30379,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.202252+00:00</t>
+          <t>2026-10-17T08:35:55.393632+00:00</t>
         </is>
       </c>
     </row>
@@ -30487,7 +30487,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.203623+00:00</t>
+          <t>2026-10-17T08:35:55.395073+00:00</t>
         </is>
       </c>
     </row>
@@ -30595,7 +30595,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.204183+00:00</t>
+          <t>2026-10-17T08:35:55.395665+00:00</t>
         </is>
       </c>
     </row>
@@ -30703,7 +30703,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.205113+00:00</t>
+          <t>2026-10-17T08:35:55.396596+00:00</t>
         </is>
       </c>
     </row>
@@ -30811,7 +30811,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.205432+00:00</t>
+          <t>2026-10-17T08:35:55.396897+00:00</t>
         </is>
       </c>
     </row>
@@ -30919,7 +30919,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.210542+00:00</t>
+          <t>2026-10-17T08:35:55.402458+00:00</t>
         </is>
       </c>
     </row>
@@ -31019,7 +31019,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.210568+00:00</t>
+          <t>2026-10-17T08:35:55.402497+00:00</t>
         </is>
       </c>
     </row>
@@ -31055,13 +31055,21 @@
           <t>papers/R13862/main/64e03a9beb58_R13862_2020_Multiple_and_flexible_roles_of_facultative_anaerobic_bacteria_in.pdf</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13862_2020_Multiple_and_flexible_roles_of_facultative_anaerobic_bacteria_in.pdf</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R13862_2020_Multiple_and_flexible_roles_of_facultative_anaerobic_bacteria_in.pdf</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13862_2020_Multiple_and_flexible_roles_of_facultative_anaerobic_bacteria_in.pdf</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -31077,12 +31085,12 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -31119,7 +31127,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.210572+00:00</t>
+          <t>2026-10-17T08:35:55.403169+00:00</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31235,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.210993+00:00</t>
+          <t>2026-10-17T08:35:55.403693+00:00</t>
         </is>
       </c>
     </row>
@@ -31335,7 +31343,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.212033+00:00</t>
+          <t>2026-10-17T08:35:55.404861+00:00</t>
         </is>
       </c>
     </row>
@@ -31443,7 +31451,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.215002+00:00</t>
+          <t>2026-10-17T08:35:55.407877+00:00</t>
         </is>
       </c>
     </row>
@@ -31479,13 +31487,21 @@
           <t>papers/R13900/main/b2ba7df8c04a_R13900_2018_Effectiveness_of_aerobic_pretreatment_of_municipal_solid_waste_for.pdf</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13900_2018_Effectiveness_of_aerobic_pretreatment_of_municipal_solid_waste_for.pdf</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R13900_2018_Effectiveness_of_aerobic_pretreatment_of_municipal_solid_waste_for.pdf</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13900_2018_Effectiveness_of_aerobic_pretreatment_of_municipal_solid_waste_for.pdf</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -31501,12 +31517,12 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -31543,7 +31559,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.215030+00:00</t>
+          <t>2026-10-17T08:35:55.408136+00:00</t>
         </is>
       </c>
     </row>
@@ -31651,7 +31667,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.219349+00:00</t>
+          <t>2026-10-17T08:35:55.412912+00:00</t>
         </is>
       </c>
     </row>
@@ -31687,13 +31703,21 @@
           <t>papers/R13903/main/2cd9e7b40925_R13903_2023_Effect_of_vacuum_negative_pressure_aerobic_hydrolysis_pretreatment_on.pdf</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13903_2023_Effect_of_vacuum_negative_pressure_aerobic_hydrolysis_pretreatment_on.pdf</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R13903_2023_Effect_of_vacuum_negative_pressure_aerobic_hydrolysis_pretreatment_on.pdf</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13903_2023_Effect_of_vacuum_negative_pressure_aerobic_hydrolysis_pretreatment_on.pdf</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -31709,12 +31733,12 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -31751,7 +31775,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.219381+00:00</t>
+          <t>2026-10-17T08:35:55.413814+00:00</t>
         </is>
       </c>
     </row>
@@ -31859,7 +31883,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.221634+00:00</t>
+          <t>2026-10-17T08:35:55.416482+00:00</t>
         </is>
       </c>
     </row>
@@ -31967,7 +31991,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.223373+00:00</t>
+          <t>2026-10-17T08:35:55.418559+00:00</t>
         </is>
       </c>
     </row>
@@ -32067,7 +32091,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.223391+00:00</t>
+          <t>2026-10-17T08:35:55.418594+00:00</t>
         </is>
       </c>
     </row>
@@ -32103,13 +32127,21 @@
           <t>papers/R13945/main/67309ea094d2_R13945_2018_Effect_of_Low_Aeration_and_Heat_Drying_on_Anaerobic.pdf</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13945_2018_Effect_of_Low_Aeration_and_Heat_Drying_on_Anaerobic.pdf</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R13945_2018_Effect_of_Low_Aeration_and_Heat_Drying_on_Anaerobic.pdf</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13945_2018_Effect_of_Low_Aeration_and_Heat_Drying_on_Anaerobic.pdf</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -32125,12 +32157,12 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -32167,7 +32199,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.223395+00:00</t>
+          <t>2026-10-17T08:35:55.420030+00:00</t>
         </is>
       </c>
     </row>
@@ -32203,13 +32235,21 @@
           <t>papers/R13950/main/2bf9b46c4486_R13950_2019_Enhancement_of_hydrogen_and_methane_production_through_anaerobic_digestion.pdf</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13950_2019_Enhancement_of_hydrogen_and_methane_production_through_anaerobic_digestion.pdf</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R13950_2019_Enhancement_of_hydrogen_and_methane_production_through_anaerobic_digestion.pdf</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13950_2019_Enhancement_of_hydrogen_and_methane_production_through_anaerobic_digestion.pdf</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -32225,12 +32265,12 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -32267,7 +32307,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.223398+00:00</t>
+          <t>2026-10-17T08:35:55.422373+00:00</t>
         </is>
       </c>
     </row>
@@ -32367,7 +32407,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.223402+00:00</t>
+          <t>2026-10-17T08:35:55.422399+00:00</t>
         </is>
       </c>
     </row>
@@ -32475,7 +32515,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.224651+00:00</t>
+          <t>2026-10-17T08:35:55.423633+00:00</t>
         </is>
       </c>
     </row>
@@ -32575,7 +32615,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.224672+00:00</t>
+          <t>2026-10-17T08:35:55.423654+00:00</t>
         </is>
       </c>
     </row>
@@ -32675,7 +32715,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.224677+00:00</t>
+          <t>2026-10-17T08:35:55.423658+00:00</t>
         </is>
       </c>
     </row>
@@ -32775,7 +32815,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.224680+00:00</t>
+          <t>2026-10-17T08:35:55.423660+00:00</t>
         </is>
       </c>
     </row>
@@ -32871,7 +32911,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.224683+00:00</t>
+          <t>2026-10-17T08:35:55.423664+00:00</t>
         </is>
       </c>
     </row>
@@ -32967,7 +33007,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.224686+00:00</t>
+          <t>2026-10-17T08:35:55.423667+00:00</t>
         </is>
       </c>
     </row>
@@ -33063,7 +33103,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.224690+00:00</t>
+          <t>2026-10-17T08:35:55.423671+00:00</t>
         </is>
       </c>
     </row>
@@ -33159,7 +33199,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.224692+00:00</t>
+          <t>2026-10-17T08:35:55.423674+00:00</t>
         </is>
       </c>
     </row>
@@ -33255,7 +33295,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.224696+00:00</t>
+          <t>2026-10-17T08:35:55.423677+00:00</t>
         </is>
       </c>
     </row>
@@ -33351,7 +33391,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.224699+00:00</t>
+          <t>2026-10-17T08:35:55.423680+00:00</t>
         </is>
       </c>
     </row>
@@ -33447,7 +33487,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.224703+00:00</t>
+          <t>2026-10-17T08:35:55.423684+00:00</t>
         </is>
       </c>
     </row>
@@ -33555,7 +33595,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.225394+00:00</t>
+          <t>2026-10-17T08:35:55.424340+00:00</t>
         </is>
       </c>
     </row>
@@ -33655,7 +33695,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.225409+00:00</t>
+          <t>2026-10-17T08:35:55.424355+00:00</t>
         </is>
       </c>
     </row>
@@ -33763,7 +33803,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.225453+00:00</t>
+          <t>2026-10-17T08:35:55.424407+00:00</t>
         </is>
       </c>
     </row>
@@ -33871,7 +33911,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.225688+00:00</t>
+          <t>2026-10-17T08:35:55.424639+00:00</t>
         </is>
       </c>
     </row>
@@ -33979,7 +34019,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.225804+00:00</t>
+          <t>2026-10-17T08:35:55.424756+00:00</t>
         </is>
       </c>
     </row>
@@ -34091,7 +34131,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.225916+00:00</t>
+          <t>2026-10-17T08:35:55.424870+00:00</t>
         </is>
       </c>
     </row>
@@ -34199,7 +34239,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.226281+00:00</t>
+          <t>2026-10-17T08:35:55.425241+00:00</t>
         </is>
       </c>
     </row>
@@ -34307,7 +34347,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.226480+00:00</t>
+          <t>2026-10-17T08:35:55.425439+00:00</t>
         </is>
       </c>
     </row>
@@ -34419,7 +34459,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.226528+00:00</t>
+          <t>2026-10-17T08:35:55.425586+00:00</t>
         </is>
       </c>
     </row>
@@ -34531,7 +34571,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.226585+00:00</t>
+          <t>2026-10-17T08:35:55.425664+00:00</t>
         </is>
       </c>
     </row>
@@ -34643,7 +34683,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.226721+00:00</t>
+          <t>2026-10-17T08:35:55.425817+00:00</t>
         </is>
       </c>
     </row>
@@ -34755,7 +34795,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.226764+00:00</t>
+          <t>2026-10-17T08:35:55.425863+00:00</t>
         </is>
       </c>
     </row>
@@ -34863,7 +34903,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.227208+00:00</t>
+          <t>2026-10-17T08:35:55.426332+00:00</t>
         </is>
       </c>
     </row>
@@ -34971,7 +35011,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.227250+00:00</t>
+          <t>2026-10-17T08:35:55.426414+00:00</t>
         </is>
       </c>
     </row>
@@ -35071,7 +35111,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.227260+00:00</t>
+          <t>2026-10-17T08:35:55.426425+00:00</t>
         </is>
       </c>
     </row>
@@ -35171,7 +35211,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.227263+00:00</t>
+          <t>2026-10-17T08:35:55.426428+00:00</t>
         </is>
       </c>
     </row>
@@ -35275,7 +35315,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.227266+00:00</t>
+          <t>2026-10-17T08:35:55.426432+00:00</t>
         </is>
       </c>
     </row>
@@ -35375,7 +35415,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.227269+00:00</t>
+          <t>2026-10-17T08:35:55.426435+00:00</t>
         </is>
       </c>
     </row>
@@ -35483,7 +35523,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.227499+00:00</t>
+          <t>2026-10-17T08:35:55.426646+00:00</t>
         </is>
       </c>
     </row>
@@ -35591,7 +35631,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228474+00:00</t>
+          <t>2026-10-17T08:35:55.427804+00:00</t>
         </is>
       </c>
     </row>
@@ -35685,7 +35725,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228488+00:00</t>
+          <t>2026-10-17T08:35:55.427831+00:00</t>
         </is>
       </c>
     </row>
@@ -35779,7 +35819,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228492+00:00</t>
+          <t>2026-10-17T08:35:55.427835+00:00</t>
         </is>
       </c>
     </row>
@@ -35873,7 +35913,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228495+00:00</t>
+          <t>2026-10-17T08:35:55.427839+00:00</t>
         </is>
       </c>
     </row>
@@ -35967,7 +36007,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228499+00:00</t>
+          <t>2026-10-17T08:35:55.427841+00:00</t>
         </is>
       </c>
     </row>
@@ -36061,7 +36101,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228502+00:00</t>
+          <t>2026-10-17T08:35:55.427844+00:00</t>
         </is>
       </c>
     </row>
@@ -36155,7 +36195,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228505+00:00</t>
+          <t>2026-10-17T08:35:55.427848+00:00</t>
         </is>
       </c>
     </row>
@@ -36249,7 +36289,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228507+00:00</t>
+          <t>2026-10-17T08:35:55.427851+00:00</t>
         </is>
       </c>
     </row>
@@ -36343,7 +36383,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228510+00:00</t>
+          <t>2026-10-17T08:35:55.427854+00:00</t>
         </is>
       </c>
     </row>
@@ -36437,7 +36477,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228513+00:00</t>
+          <t>2026-10-17T08:35:55.427857+00:00</t>
         </is>
       </c>
     </row>
@@ -36531,7 +36571,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228516+00:00</t>
+          <t>2026-10-17T08:35:55.427859+00:00</t>
         </is>
       </c>
     </row>
@@ -36625,7 +36665,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228520+00:00</t>
+          <t>2026-10-17T08:35:55.427862+00:00</t>
         </is>
       </c>
     </row>
@@ -36719,7 +36759,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228523+00:00</t>
+          <t>2026-10-17T08:35:55.427865+00:00</t>
         </is>
       </c>
     </row>
@@ -36813,7 +36853,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228526+00:00</t>
+          <t>2026-10-17T08:35:55.427868+00:00</t>
         </is>
       </c>
     </row>
@@ -36907,7 +36947,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228529+00:00</t>
+          <t>2026-10-17T08:35:55.427872+00:00</t>
         </is>
       </c>
     </row>
@@ -37001,7 +37041,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228532+00:00</t>
+          <t>2026-10-17T08:35:55.427875+00:00</t>
         </is>
       </c>
     </row>
@@ -37095,7 +37135,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228535+00:00</t>
+          <t>2026-10-17T08:35:55.427877+00:00</t>
         </is>
       </c>
     </row>
@@ -37189,7 +37229,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228539+00:00</t>
+          <t>2026-10-17T08:35:55.427880+00:00</t>
         </is>
       </c>
     </row>
@@ -37283,7 +37323,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228542+00:00</t>
+          <t>2026-10-17T08:35:55.427883+00:00</t>
         </is>
       </c>
     </row>
@@ -37377,7 +37417,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228545+00:00</t>
+          <t>2026-10-17T08:35:55.427886+00:00</t>
         </is>
       </c>
     </row>
@@ -37471,7 +37511,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228548+00:00</t>
+          <t>2026-10-17T08:35:55.427889+00:00</t>
         </is>
       </c>
     </row>
@@ -37565,7 +37605,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228550+00:00</t>
+          <t>2026-10-17T08:35:55.427891+00:00</t>
         </is>
       </c>
     </row>
@@ -37659,7 +37699,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228553+00:00</t>
+          <t>2026-10-17T08:35:55.427895+00:00</t>
         </is>
       </c>
     </row>
@@ -37753,7 +37793,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228557+00:00</t>
+          <t>2026-10-17T08:35:55.427897+00:00</t>
         </is>
       </c>
     </row>
@@ -37847,7 +37887,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228560+00:00</t>
+          <t>2026-10-17T08:35:55.427901+00:00</t>
         </is>
       </c>
     </row>
@@ -37941,7 +37981,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228563+00:00</t>
+          <t>2026-10-17T08:35:55.427904+00:00</t>
         </is>
       </c>
     </row>
@@ -38035,7 +38075,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228566+00:00</t>
+          <t>2026-10-17T08:35:55.427907+00:00</t>
         </is>
       </c>
     </row>
@@ -38129,7 +38169,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228568+00:00</t>
+          <t>2026-10-17T08:35:55.427910+00:00</t>
         </is>
       </c>
     </row>
@@ -38229,7 +38269,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:02.228571+00:00</t>
+          <t>2026-10-17T08:35:55.427912+00:00</t>
         </is>
       </c>
     </row>
@@ -38244,7 +38284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38412,12 +38452,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R13862</t>
+          <t>R13931</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R13862.main.64e03a9beb5813a0</t>
+          <t>R13931.main.6e898a403edac7b3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -38427,20 +38467,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>64e03a9beb5813a0ce6d94272350217f12dac94293420969e3d2d9d7975e96e3</t>
+          <t>6e898a403edac7b3ae15ad88cf75788898cd84ea377b2572f7bab40d9c126f8c</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>833659</v>
+        <v>1324593</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/eb850f96-0570-4e0d-be55-73fcee5f1364/content</t>
+          <t>https://www.eeer.org/upload/eer-2020-470.pdf</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>R13862_2020_Multiple_and_flexible_roles_of_facultative_anaerobic_bacteria_in.pdf</t>
+          <t>R13931_2020_Biogas_recovery_from_fresh_landfill_leachates_by_using_a.pdf</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -38452,12 +38492,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R13900</t>
+          <t>R13944</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R13900.main.b2ba7df8c04ab66c</t>
+          <t>R13944.main.7e22fbfd39ddfed0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -38467,20 +38507,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>b2ba7df8c04ab66c0e548f778e19c5764802c0da8408a3b8499547b3f6ef51b3</t>
+          <t>7e22fbfd39ddfed09b9235fea5c6914cfbe5987d12564fc9cb799bf412ae6779</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>299244</v>
+        <v>12042699</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.research.unipd.it/bitstream/11577/3261852/1/Front.%20Environ.%20Sci.%20Eng%20Dongbei%202018.pdf</t>
+          <t>https://scholarspace.manoa.hawaii.edu/server/api/core/bitstreams/60c88164-f37f-492a-97bc-e34a2f2b1698/content</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>R13900_2018_Effectiveness_of_aerobic_pretreatment_of_municipal_solid_waste_for.pdf</t>
+          <t>R13944_2018_Oxidation-Reduction_Potential-Based_Micro-Aeration_Control_System_for_Anaerobic_Digestion.pdf</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -38492,12 +38532,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R13903</t>
+          <t>R13967</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R13903.main.2cd9e7b409250e7b</t>
+          <t>R13967.main.5e9f84dbaf01dd19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -38507,20 +38547,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2cd9e7b409250e7b104f489e139f57d4daa40d97133c6c57c937184c3ec73b71</t>
+          <t>5e9f84dbaf01dd19674f09cbce96f338f32fe21a37a883bb9658e49af7072194</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1107675</v>
+        <v>160020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://ijabe.org/index.php/ijabe/article/download/7975/pdf</t>
+          <t>https://www.aceee.org/wp-content/uploads/proceedings-1980-2020/2012/0193-000342.pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>R13903_2023_Effect_of_vacuum_negative_pressure_aerobic_hydrolysis_pretreatment_on.pdf</t>
+          <t>R13967_2012_An_Improved_Biomass_Waste_Anaerobic_Degradation_Technology_for_Producing.pdf</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -38532,12 +38572,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R13931</t>
+          <t>R13972</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R13931.main.6e898a403edac7b3</t>
+          <t>R13972.main.ff4ee9377a7e227c</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -38547,20 +38587,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6e898a403edac7b3ae15ad88cf75788898cd84ea377b2572f7bab40d9c126f8c</t>
+          <t>ff4ee9377a7e227c48a5bc64d301bfc1a989ee0e709c322eb90f254819d7b391</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1324593</v>
+        <v>1192569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.eeer.org/upload/eer-2020-470.pdf</t>
+          <t>https://www.osti.gov/servlets/purl/2386939</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>R13931_2020_Biogas_recovery_from_fresh_landfill_leachates_by_using_a.pdf</t>
+          <t>R13972_2022_Enhancing_methane_production_of_anaerobic_digested_sewage_sludge_by.pdf</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -38572,12 +38612,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R13945</t>
+          <t>R13957</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R13945.main.67309ea094d2f9bb</t>
+          <t>R13957.main.3db804dcdefb7608</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -38587,20 +38627,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>67309ea094d2f9bb088d605746ede869866819a733f53c44dc2d44af934e6be9</t>
+          <t>3db804dcdefb7608eefc6bf166b0713cbbec8ac027b1c01831aec97b54253b82</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2230958</v>
+        <v>7806265</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://epublications.marquette.edu/cgi/viewcontent.cgi?article=1459&amp;context=theses_open</t>
+          <t>https://backoffice.biblio.ugent.be/download/8530499/8530500</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>R13945_2018_Effect_of_Low_Aeration_and_Heat_Drying_on_Anaerobic.pdf</t>
+          <t>R13957_2017_Microaeration_for_biogas_desulfurization_experimental_and_simulation_study_of.pdf</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -38612,12 +38652,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R13950</t>
+          <t>R04510</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R13950.main.2bf9b46c448685b9</t>
+          <t>R04510.main.c4520ca79e301bb6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -38627,20 +38667,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2bf9b46c448685b9e66f4064245c5840dc28ded79ee4d613ddd9efeb4805812e</t>
+          <t>c4520ca79e301bb606a8ab1fef6cf4af9064c0d85f3c390a4cf31a877238e1c6</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3508852</v>
+        <v>492630</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.research.unipd.it/bitstream/11577/3425227/1/Thesis_Razieh_Rafieenia.pdf</t>
+          <t>https://digital.csic.es/bitstream/10261/196040/5/PostP_2019_JESH_V54_Iss10.pdf</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>R13950_2019_Enhancement_of_hydrogen_and_methane_production_through_anaerobic_digestion.pdf</t>
+          <t>R04510_2019_Anaerobic_digestion_of_wastewater_rich_in_sulfate_and_sulfide_effects_of_metallic_waste_addition_and.pdf</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -38652,12 +38692,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R13944</t>
+          <t>R13889</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R13944.main.7e22fbfd39ddfed0</t>
+          <t>R13889.main.8db0dcdf434e876e</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -38667,20 +38707,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7e22fbfd39ddfed09b9235fea5c6914cfbe5987d12564fc9cb799bf412ae6779</t>
+          <t>8db0dcdf434e876e7cbff3cf342105807bdd41a900f74c0028cb14a6c6e56779</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12042699</v>
+        <v>514378</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://scholarspace.manoa.hawaii.edu/server/api/core/bitstreams/60c88164-f37f-492a-97bc-e34a2f2b1698/content</t>
+          <t>https://digital.csic.es/bitstream/10261/178890/1/PotP_2018_RE_V123_P541.pdf</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>R13944_2018_Oxidation-Reduction_Potential-Based_Micro-Aeration_Control_System_for_Anaerobic_Digestion.pdf</t>
+          <t>R13889_2018_Increase_in_biogas_production_in_anaerobic_sludge_digestion_by_combining_aerobic_hydrolysis_and_addi.pdf</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -38692,12 +38732,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R13967</t>
+          <t>R02719</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R13967.main.5e9f84dbaf01dd19</t>
+          <t>R02719.main.4bf5e309b2ef3431</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -38707,20 +38747,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5e9f84dbaf01dd19674f09cbce96f338f32fe21a37a883bb9658e49af7072194</t>
+          <t>4bf5e309b2ef343162a9588383a7ae0254118c33cdf2e96bec1a05459fae1523</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>160020</v>
+        <v>583591</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.aceee.org/wp-content/uploads/proceedings-1980-2020/2012/0193-000342.pdf</t>
+          <t>https://digital.csic.es/bitstream/10261/137944/1/Post_2016_JEnvSciHealth_A_BorjaR.pdf</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>R13967_2012_An_Improved_Biomass_Waste_Anaerobic_Degradation_Technology_for_Producing.pdf</t>
+          <t>R02719_2016_Performance_evaluation_of_micro_aerobic_hydrolysis_of_mixed_sludge_Optimum_aeration_and_effect_on_it.pdf</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -38732,12 +38772,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R13972</t>
+          <t>R02282</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R13972.main.ff4ee9377a7e227c</t>
+          <t>R02282.main.e709439b748e7938</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -38747,20 +38787,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ff4ee9377a7e227c48a5bc64d301bfc1a989ee0e709c322eb90f254819d7b391</t>
+          <t>e709439b748e793826102646c009aa10e1e9ac30627ac301fac7dd42276a2047</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1192569</v>
+        <v>1067465</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.osti.gov/servlets/purl/2386939</t>
+          <t>https://digital.csic.es/bitstream/10261/130093/1/Postprint_2016_EnviromRev_V24_P84.pdf</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>R13972_2022_Enhancing_methane_production_of_anaerobic_digested_sewage_sludge_by.pdf</t>
+          <t>R02282_2016_Advances_in_the_biological_removal_of_sulphides_from_aqueous_phase_in_anaerobic_processes_A_review.pdf</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -38772,12 +38812,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R13957</t>
+          <t>R13905</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R13957.main.3db804dcdefb7608</t>
+          <t>R13905.main.c75b5084c2545bd9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -38787,20 +38827,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3db804dcdefb7608eefc6bf166b0713cbbec8ac027b1c01831aec97b54253b82</t>
+          <t>c75b5084c2545bd939d3b1928be41fe0072c7302f26c25ba023c4bb6fc8a6970</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7806265</v>
+        <v>2159708</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://backoffice.biblio.ugent.be/download/8530499/8530500</t>
+          <t>https://ddd.uab.cat/pub/artpub/2017/196242/wasbioval_a2017m7v8n5p1793.pdf</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>R13957_2017_Microaeration_for_biogas_desulfurization_experimental_and_simulation_study_of.pdf</t>
+          <t>R13905_2017_The_Effect_of_a_Short_Term_Aerobic_Pretreatment_Step_on_the_Anaerobic_Co_digestion_of_the_Organic_Fr.pdf</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -38812,12 +38852,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R04510</t>
+          <t>R13932</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R04510.main.c4520ca79e301bb6</t>
+          <t>R13932.main.c15f49a3d617e1be</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -38827,20 +38867,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>c4520ca79e301bb606a8ab1fef6cf4af9064c0d85f3c390a4cf31a877238e1c6</t>
+          <t>c15f49a3d617e1be5e21578ebda1c2d855f8d460c1d66f446ad0d02856a40a13</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>492630</v>
+        <v>1258157</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/196040/5/PostP_2019_JESH_V54_Iss10.pdf</t>
+          <t>https://hal.inrae.fr/hal-02620984/document</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>R04510_2019_Anaerobic_digestion_of_wastewater_rich_in_sulfate_and_sulfide_effects_of_metallic_waste_addition_and.pdf</t>
+          <t>R13932_2018_Comparison_of_pre_and_inter_stage_aerobic_treatment_of_wastewater_sludge_Effects_on_biogas_productio.pdf</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -38852,12 +38892,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R13889</t>
+          <t>R13956</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R13889.main.8db0dcdf434e876e</t>
+          <t>R13956.main.fedaffcdf5be81e2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -38867,20 +38907,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8db0dcdf434e876e7cbff3cf342105807bdd41a900f74c0028cb14a6c6e56779</t>
+          <t>fedaffcdf5be81e2070b7edb0531c332e423578228eeb8c55a6afc4ba8fe1e18</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>514378</v>
+        <v>421626</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/178890/1/PotP_2018_RE_V123_P541.pdf</t>
+          <t>https://www.banglajol.info/index.php/BJSIR/article/download/25579/17152</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>R13889_2018_Increase_in_biogas_production_in_anaerobic_sludge_digestion_by_combining_aerobic_hydrolysis_and_addi.pdf</t>
+          <t>R13956_2015_Anaerobic_digestion_of_mixed_dried_fallen_leaves_by_mixing_with_cow_dung.pdf</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -38892,12 +38932,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R02719</t>
+          <t>R13955</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R02719.main.4bf5e309b2ef3431</t>
+          <t>R13955.main.7549e1025985363e</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -38907,20 +38947,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4bf5e309b2ef343162a9588383a7ae0254118c33cdf2e96bec1a05459fae1523</t>
+          <t>7549e1025985363e89542bbc1af6eaaa1150bbd62ea43bdd03d2c7b764631f9d</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>583591</v>
+        <v>14662438</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/137944/1/Post_2016_JEnvSciHealth_A_BorjaR.pdf</t>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>R02719_2016_Performance_evaluation_of_micro_aerobic_hydrolysis_of_mixed_sludge_Optimum_aeration_and_effect_on_it.pdf</t>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -38932,35 +38972,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R02282</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R02282.main.e709439b748e7938</t>
+          <t>R07238.supplementary.0b7925ad1ed9c793</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>e709439b748e793826102646c009aa10e1e9ac30627ac301fac7dd42276a2047</t>
+          <t>0b7925ad1ed9c7939a79ba6294d17abc4b23fca77e52ec50df5463d050940d1e</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1067465</v>
+        <v>49526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/130093/1/Postprint_2016_EnviromRev_V24_P84.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>R02282_2016_Advances_in_the_biological_removal_of_sulphides_from_aqueous_phase_in_anaerobic_processes_A_review.pdf</t>
+          <t>mmc1.docx</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -38972,35 +39012,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R13905</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R13905.main.c75b5084c2545bd9</t>
+          <t>R07238.supplementary.f346f9bdcc964013</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>c75b5084c2545bd939d3b1928be41fe0072c7302f26c25ba023c4bb6fc8a6970</t>
+          <t>f346f9bdcc964013ecb7c4282d6b30f1ab334e035d98adcc653de1447fbe9a9a</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2159708</v>
+        <v>14286928</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://ddd.uab.cat/pub/artpub/2017/196242/wasbioval_a2017m7v8n5p1793.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>R13905_2017_The_Effect_of_a_Short_Term_Aerobic_Pretreatment_Step_on_the_Anaerobic_Co_digestion_of_the_Organic_Fr.pdf</t>
+          <t>mmc2.zip</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -39012,35 +39052,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R13932</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R13932.main.c15f49a3d617e1be</t>
+          <t>R07238.derived.49b84e369d4bb31b</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>c15f49a3d617e1be5e21578ebda1c2d855f8d460c1d66f446ad0d02856a40a13</t>
+          <t>49b84e369d4bb31b4ebdcd25265be3174105c3433e6fbb865f34a445775516a1</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1258157</v>
+        <v>34855493</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://hal.inrae.fr/hal-02620984/document</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>R13932_2018_Comparison_of_pre_and_inter_stage_aerobic_treatment_of_wastewater_sludge_Effects_on_biogas_productio.pdf</t>
+          <t>g a.skp</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -39052,35 +39092,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R13956</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R13956.main.fedaffcdf5be81e2</t>
+          <t>R08646.supplementary.cfda7e29b12b9784</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>fedaffcdf5be81e2070b7edb0531c332e423578228eeb8c55a6afc4ba8fe1e18</t>
+          <t>cfda7e29b12b97846343963f9f3b64e784bc79644fb1ee1ca31170be78d75327</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>421626</v>
+        <v>42279</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.banglajol.info/index.php/BJSIR/article/download/25579/17152</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>R13956_2015_Anaerobic_digestion_of_mixed_dried_fallen_leaves_by_mixing_with_cow_dung.pdf</t>
+          <t>mmc1.docx</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -39092,35 +39132,35 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R13955</t>
+          <t>R03161</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R13955.main.7549e1025985363e</t>
+          <t>R03161.evidence_xml.466f3a1e78e8b0f1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7549e1025985363e89542bbc1af6eaaa1150bbd62ea43bdd03d2c7b764631f9d</t>
+          <t>466f3a1e78e8b0f148b1f28f97b61f7134c61488c837c5c5a26ef7316cebc1e9</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>14662438</v>
+        <v>59018</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/fullTextXML</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
+          <t>PMC5627928_fullText.xml</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -39132,35 +39172,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R03161</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R07238.supplementary.0b7925ad1ed9c793</t>
+          <t>R03161.transport_archive.0ef4d4796c84feff</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0b7925ad1ed9c7939a79ba6294d17abc4b23fca77e52ec50df5463d050940d1e</t>
+          <t>0ef4d4796c84fefff7b8450bc56400f8c59f4bdcf074fc51404edff5e4e217f6</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>49526</v>
+        <v>726772</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/supplementaryFiles</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>mmc1.docx</t>
+          <t>PMC5627928_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -39172,35 +39212,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R04092</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R07238.supplementary.f346f9bdcc964013</t>
+          <t>R04092.evidence_xml.0fb90085e30680fa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>f346f9bdcc964013ecb7c4282d6b30f1ab334e035d98adcc653de1447fbe9a9a</t>
+          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>14286928</v>
+        <v>77995</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>mmc2.zip</t>
+          <t>PMC6288047_fullText.xml</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -39212,35 +39252,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R05839</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R07238.derived.49b84e369d4bb31b</t>
+          <t>R05839.evidence_xml.18ffd43dee955086</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>49b84e369d4bb31b4ebdcd25265be3174105c3433e6fbb865f34a445775516a1</t>
+          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>34855493</v>
+        <v>75205</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>g a.skp</t>
+          <t>PMC7566014_fullText.xml</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -39252,35 +39292,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R08877</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R08646.supplementary.cfda7e29b12b9784</t>
+          <t>R08877.evidence_xml.e8712e4198baab4c</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>cfda7e29b12b97846343963f9f3b64e784bc79644fb1ee1ca31170be78d75327</t>
+          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>42279</v>
+        <v>111864</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>mmc1.docx</t>
+          <t>PMC10714394_fullText.xml</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -39292,35 +39332,35 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>R03161</t>
+          <t>R08877</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R03161.evidence_xml.466f3a1e78e8b0f1</t>
+          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>466f3a1e78e8b0f148b1f28f97b61f7134c61488c837c5c5a26ef7316cebc1e9</t>
+          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>59018</v>
+        <v>704921</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>PMC5627928_fullText.xml</t>
+          <t>PMC10714394_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -39332,35 +39372,35 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>R03161</t>
+          <t>R09236</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R03161.transport_archive.0ef4d4796c84feff</t>
+          <t>R09236.evidence_xml.72064fe9276d8309</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0ef4d4796c84fefff7b8450bc56400f8c59f4bdcf074fc51404edff5e4e217f6</t>
+          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>726772</v>
+        <v>193052</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>PMC5627928_supplementaryFiles.zip</t>
+          <t>PMC10535533_fullText.xml</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -39372,35 +39412,35 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>R04092</t>
+          <t>R09236</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>R04092.evidence_xml.0fb90085e30680fa</t>
+          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
+          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>77995</v>
+        <v>483405</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PMC6288047_fullText.xml</t>
+          <t>PMC10535533_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -39412,12 +39452,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>R05839</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R05839.evidence_xml.18ffd43dee955086</t>
+          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -39427,20 +39467,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
+          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>75205</v>
+        <v>118002</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PMC7566014_fullText.xml</t>
+          <t>PMC10837232_fullText.xml</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -39452,35 +39492,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R08877.evidence_xml.e8712e4198baab4c</t>
+          <t>R10086.transport_archive.4d9eddf454b786ed</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
+          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>111864</v>
+        <v>641038</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PMC10714394_fullText.xml</t>
+          <t>PMC10837232_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -39492,35 +39532,35 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
+          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
+          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>704921</v>
+        <v>173586</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PMC10714394_supplementaryFiles.zip</t>
+          <t>PMC12937426_fullText.xml</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -39532,35 +39572,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R09236.evidence_xml.72064fe9276d8309</t>
+          <t>R12985.transport_archive.418d45f1ca296020</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
+          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>193052</v>
+        <v>672244</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PMC10535533_fullText.xml</t>
+          <t>PMC12937426_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -39572,35 +39612,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R05542</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
+          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
+          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>483405</v>
+        <v>100215</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>PMC10535533_supplementaryFiles.zip</t>
+          <t>PMC9056904_fullText.xml</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -39612,12 +39652,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
+          <t>R06325.evidence_xml.645deb707d3790b5</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -39627,20 +39667,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
+          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>118002</v>
+        <v>160509</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>PMC10837232_fullText.xml</t>
+          <t>PMC8290346_fullText.xml</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -39652,12 +39692,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R10086.transport_archive.4d9eddf454b786ed</t>
+          <t>R06325.transport_archive.6eb4ef126661714a</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -39667,20 +39707,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
+          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>641038</v>
+        <v>1730580</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>PMC10837232_supplementaryFiles.zip</t>
+          <t>PMC8290346_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -39692,12 +39732,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
+          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -39707,20 +39747,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
+          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>173586</v>
+        <v>151458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>PMC12937426_fullText.xml</t>
+          <t>PMC8044681_fullText.xml</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -39732,12 +39772,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R12985.transport_archive.418d45f1ca296020</t>
+          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -39747,20 +39787,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
+          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>672244</v>
+        <v>14596266</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>PMC12937426_supplementaryFiles.zip</t>
+          <t>PMC8044681_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -39772,12 +39812,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>R05542</t>
+          <t>R03477</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
+          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -39787,20 +39827,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
+          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100215</v>
+        <v>121650</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>PMC9056904_fullText.xml</t>
+          <t>PMC5371168_fullText.xml</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -39812,12 +39852,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>R06325.evidence_xml.645deb707d3790b5</t>
+          <t>R08646.evidence_xml.c7b723e8020f6582</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -39827,20 +39867,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
+          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>160509</v>
+        <v>304277</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>PMC8290346_fullText.xml</t>
+          <t>PMC10559078_fullText.xml</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -39852,12 +39892,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>R06325.transport_archive.6eb4ef126661714a</t>
+          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -39867,20 +39907,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
+          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1730580</v>
+        <v>1539133</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>PMC8290346_supplementaryFiles.zip</t>
+          <t>PMC10559078_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -39892,12 +39932,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R09804</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
+          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -39907,20 +39947,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
+          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>151458</v>
+        <v>211630</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>PMC8044681_fullText.xml</t>
+          <t>PMC11076452_fullText.xml</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -39932,35 +39972,35 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R11503</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
+          <t>R11503.evidence_xml.4002d57be59c215c</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
+          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>14596266</v>
+        <v>258637</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>PMC8044681_supplementaryFiles.zip</t>
+          <t>PMC12561102_fullText.xml</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -39972,12 +40012,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>R03477</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
+          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -39987,20 +40027,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
+          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>121650</v>
+        <v>256247</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>PMC5371168_fullText.xml</t>
+          <t>PMC12125087_fullText.xml</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -40012,35 +40052,35 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>R08646.evidence_xml.c7b723e8020f6582</t>
+          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
+          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>304277</v>
+        <v>521862</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>PMC10559078_fullText.xml</t>
+          <t>PMC12125087_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -40052,35 +40092,35 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
+          <t>R05213.evidence_xml.17894ab410001846</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
+          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1539133</v>
+        <v>130954</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>PMC10559078_supplementaryFiles.zip</t>
+          <t>PMC6858683_fullText.xml</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -40092,35 +40132,35 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
+          <t>R05213.transport_archive.c61c88cf9fd489be</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
+          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>211630</v>
+        <v>1960371</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>PMC11076452_fullText.xml</t>
+          <t>PMC6858683_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -40132,12 +40172,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>R11503</t>
+          <t>R09585</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>R11503.evidence_xml.4002d57be59c215c</t>
+          <t>R09585.evidence_xml.a3430f38fa1652de</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -40147,20 +40187,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
+          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>258637</v>
+        <v>100534</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>PMC12561102_fullText.xml</t>
+          <t>PMC10609292_fullText.xml</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -40172,238 +40212,38 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R11596</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
+          <t>R11596.main.0b2e2d98dffd5449</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
+          <t>0b2e2d98dffd544958b06cc2229d310e4b7d529bd3914c47f20d6a66789a28be</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>256247</v>
+        <v>1659399</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
+          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/7262c516-6b14-4001-a173-517d1187c8d9/content</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>PMC12125087_fullText.xml</t>
+          <t>R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>R11844</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>transport_archive</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>521862</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>PMC12125087_supplementaryFiles.zip</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>R05213</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>R05213.evidence_xml.17894ab410001846</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>evidence_xml</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>130954</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>PMC6858683_fullText.xml</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>R05213</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>R05213.transport_archive.c61c88cf9fd489be</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>transport_archive</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>1960371</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>PMC6858683_supplementaryFiles.zip</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>R09585</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>R09585.evidence_xml.a3430f38fa1652de</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>evidence_xml</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>100534</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>PMC10609292_fullText.xml</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>R11596</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>R11596.main.0b2e2d98dffd5449</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>0b2e2d98dffd544958b06cc2229d310e4b7d529bd3914c47f20d6a66789a28be</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>1659399</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/7262c516-6b14-4001-a173-517d1187c8d9/content</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
         <is>
           <t>历史已获取，当前原件未恢复</t>
         </is>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -1740,7 +1740,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -20567,7 +20567,7 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
@@ -23842,7 +23842,7 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.304906+00:00</t>
+          <t>2026-10-17T08:36:51.266818+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.305829+00:00</t>
+          <t>2026-10-17T08:36:51.267909+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.305850+00:00</t>
+          <t>2026-10-17T08:36:51.267941+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.306085+00:00</t>
+          <t>2026-10-17T08:36:51.268173+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.307196+00:00</t>
+          <t>2026-10-17T08:36:51.269523+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.307749+00:00</t>
+          <t>2026-10-17T08:36:51.270021+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.313697+00:00</t>
+          <t>2026-10-17T08:36:51.276169+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.316024+00:00</t>
+          <t>2026-10-17T08:36:51.279015+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.316986+00:00</t>
+          <t>2026-10-17T08:36:51.279994+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.317336+00:00</t>
+          <t>2026-10-17T08:36:51.280384+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.318229+00:00</t>
+          <t>2026-10-17T08:36:51.281132+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.318966+00:00</t>
+          <t>2026-10-17T08:36:51.281819+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.319879+00:00</t>
+          <t>2026-10-17T08:36:51.282737+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.320125+00:00</t>
+          <t>2026-10-17T08:36:51.282971+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.320981+00:00</t>
+          <t>2026-10-17T08:36:51.283881+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.328703+00:00</t>
+          <t>2026-10-17T08:36:51.291200+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.329497+00:00</t>
+          <t>2026-10-17T08:36:51.292112+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.330758+00:00</t>
+          <t>2026-10-17T08:36:51.293613+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.333211+00:00</t>
+          <t>2026-10-17T08:36:51.296343+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.334314+00:00</t>
+          <t>2026-10-17T08:36:51.297520+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.335504+00:00</t>
+          <t>2026-10-17T08:36:51.298709+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.340048+00:00</t>
+          <t>2026-10-17T08:36:51.302840+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.342226+00:00</t>
+          <t>2026-10-17T08:36:51.305352+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.343993+00:00</t>
+          <t>2026-10-17T08:36:51.307180+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.344655+00:00</t>
+          <t>2026-10-17T08:36:51.307890+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.345140+00:00</t>
+          <t>2026-10-17T08:36:51.308246+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.347224+00:00</t>
+          <t>2026-10-17T08:36:51.310318+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.348554+00:00</t>
+          <t>2026-10-17T08:36:51.311801+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.350770+00:00</t>
+          <t>2026-10-17T08:36:51.313936+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.352799+00:00</t>
+          <t>2026-10-17T08:36:51.316016+00:00</t>
         </is>
       </c>
     </row>
@@ -27571,7 +27571,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.352823+00:00</t>
+          <t>2026-10-17T08:36:51.316038+00:00</t>
         </is>
       </c>
     </row>
@@ -27679,7 +27679,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.353536+00:00</t>
+          <t>2026-10-17T08:36:51.316769+00:00</t>
         </is>
       </c>
     </row>
@@ -27787,7 +27787,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.355343+00:00</t>
+          <t>2026-10-17T08:36:51.318515+00:00</t>
         </is>
       </c>
     </row>
@@ -27895,7 +27895,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.358148+00:00</t>
+          <t>2026-10-17T08:36:51.321365+00:00</t>
         </is>
       </c>
     </row>
@@ -28003,7 +28003,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.360212+00:00</t>
+          <t>2026-10-17T08:36:51.323614+00:00</t>
         </is>
       </c>
     </row>
@@ -28111,7 +28111,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.361404+00:00</t>
+          <t>2026-10-17T08:36:51.324877+00:00</t>
         </is>
       </c>
     </row>
@@ -28219,7 +28219,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.364642+00:00</t>
+          <t>2026-10-17T08:36:51.327767+00:00</t>
         </is>
       </c>
     </row>
@@ -28327,7 +28327,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.365523+00:00</t>
+          <t>2026-10-17T08:36:51.328654+00:00</t>
         </is>
       </c>
     </row>
@@ -28435,7 +28435,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.367105+00:00</t>
+          <t>2026-10-17T08:36:51.330358+00:00</t>
         </is>
       </c>
     </row>
@@ -28543,7 +28543,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.367389+00:00</t>
+          <t>2026-10-17T08:36:51.330624+00:00</t>
         </is>
       </c>
     </row>
@@ -28651,7 +28651,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.369531+00:00</t>
+          <t>2026-10-17T08:36:51.332646+00:00</t>
         </is>
       </c>
     </row>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.372650+00:00</t>
+          <t>2026-10-17T08:36:51.335550+00:00</t>
         </is>
       </c>
     </row>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.373987+00:00</t>
+          <t>2026-10-17T08:36:51.336889+00:00</t>
         </is>
       </c>
     </row>
@@ -28975,7 +28975,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.374591+00:00</t>
+          <t>2026-10-17T08:36:51.337628+00:00</t>
         </is>
       </c>
     </row>
@@ -29083,7 +29083,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.377339+00:00</t>
+          <t>2026-10-17T08:36:51.340321+00:00</t>
         </is>
       </c>
     </row>
@@ -29191,7 +29191,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.378803+00:00</t>
+          <t>2026-10-17T08:36:51.341813+00:00</t>
         </is>
       </c>
     </row>
@@ -29299,7 +29299,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.382279+00:00</t>
+          <t>2026-10-17T08:36:51.345362+00:00</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.383975+00:00</t>
+          <t>2026-10-17T08:36:51.347070+00:00</t>
         </is>
       </c>
     </row>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.385804+00:00</t>
+          <t>2026-10-17T08:36:51.349021+00:00</t>
         </is>
       </c>
     </row>
@@ -29623,7 +29623,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.386732+00:00</t>
+          <t>2026-10-17T08:36:51.349987+00:00</t>
         </is>
       </c>
     </row>
@@ -29731,7 +29731,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.387243+00:00</t>
+          <t>2026-10-17T08:36:51.350477+00:00</t>
         </is>
       </c>
     </row>
@@ -29839,7 +29839,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.387642+00:00</t>
+          <t>2026-10-17T08:36:51.350843+00:00</t>
         </is>
       </c>
     </row>
@@ -29947,7 +29947,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.389128+00:00</t>
+          <t>2026-10-17T08:36:51.352379+00:00</t>
         </is>
       </c>
     </row>
@@ -30055,7 +30055,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.390494+00:00</t>
+          <t>2026-10-17T08:36:51.353829+00:00</t>
         </is>
       </c>
     </row>
@@ -30163,7 +30163,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.391979+00:00</t>
+          <t>2026-10-17T08:36:51.355391+00:00</t>
         </is>
       </c>
     </row>
@@ -30271,7 +30271,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.392314+00:00</t>
+          <t>2026-10-17T08:36:51.355720+00:00</t>
         </is>
       </c>
     </row>
@@ -30379,7 +30379,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.393632+00:00</t>
+          <t>2026-10-17T08:36:51.356897+00:00</t>
         </is>
       </c>
     </row>
@@ -30487,7 +30487,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.395073+00:00</t>
+          <t>2026-10-17T08:36:51.358273+00:00</t>
         </is>
       </c>
     </row>
@@ -30595,7 +30595,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.395665+00:00</t>
+          <t>2026-10-17T08:36:51.358897+00:00</t>
         </is>
       </c>
     </row>
@@ -30703,7 +30703,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.396596+00:00</t>
+          <t>2026-10-17T08:36:51.359840+00:00</t>
         </is>
       </c>
     </row>
@@ -30811,7 +30811,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.396897+00:00</t>
+          <t>2026-10-17T08:36:51.360167+00:00</t>
         </is>
       </c>
     </row>
@@ -30919,7 +30919,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.402458+00:00</t>
+          <t>2026-10-17T08:36:51.365604+00:00</t>
         </is>
       </c>
     </row>
@@ -31019,7 +31019,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.402497+00:00</t>
+          <t>2026-10-17T08:36:51.365667+00:00</t>
         </is>
       </c>
     </row>
@@ -31127,7 +31127,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.403169+00:00</t>
+          <t>2026-10-17T08:36:51.366270+00:00</t>
         </is>
       </c>
     </row>
@@ -31235,7 +31235,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.403693+00:00</t>
+          <t>2026-10-17T08:36:51.366761+00:00</t>
         </is>
       </c>
     </row>
@@ -31343,7 +31343,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.404861+00:00</t>
+          <t>2026-10-17T08:36:51.367849+00:00</t>
         </is>
       </c>
     </row>
@@ -31451,7 +31451,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.407877+00:00</t>
+          <t>2026-10-17T08:36:51.370944+00:00</t>
         </is>
       </c>
     </row>
@@ -31559,7 +31559,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.408136+00:00</t>
+          <t>2026-10-17T08:36:51.371203+00:00</t>
         </is>
       </c>
     </row>
@@ -31667,7 +31667,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.412912+00:00</t>
+          <t>2026-10-17T08:36:51.375673+00:00</t>
         </is>
       </c>
     </row>
@@ -31775,7 +31775,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.413814+00:00</t>
+          <t>2026-10-17T08:36:51.376532+00:00</t>
         </is>
       </c>
     </row>
@@ -31883,7 +31883,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.416482+00:00</t>
+          <t>2026-10-17T08:36:51.378998+00:00</t>
         </is>
       </c>
     </row>
@@ -31991,7 +31991,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.418559+00:00</t>
+          <t>2026-10-17T08:36:51.380783+00:00</t>
         </is>
       </c>
     </row>
@@ -32091,7 +32091,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.418594+00:00</t>
+          <t>2026-10-17T08:36:51.380805+00:00</t>
         </is>
       </c>
     </row>
@@ -32199,7 +32199,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.420030+00:00</t>
+          <t>2026-10-17T08:36:51.382259+00:00</t>
         </is>
       </c>
     </row>
@@ -32307,7 +32307,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.422373+00:00</t>
+          <t>2026-10-17T08:36:51.384505+00:00</t>
         </is>
       </c>
     </row>
@@ -32343,13 +32343,21 @@
           <t>papers/R13944/main/7e22fbfd39dd_R13944_2018_Oxidation-Reduction_Potential-Based_Micro-Aeration_Control_System_for_Anaerobic_Digestion.pdf</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13944_2018_Oxidation-Reduction_Potential-Based_Micro-Aeration_Control_System_for_Anaerobic_Digestion.pdf</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R13944_2018_Oxidation-Reduction_Potential-Based_Micro-Aeration_Control_System_for_Anaerobic_Digestion.pdf</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13944_2018_Oxidation-Reduction_Potential-Based_Micro-Aeration_Control_System_for_Anaerobic_Digestion.pdf</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -32365,12 +32373,12 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -32407,7 +32415,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.422399+00:00</t>
+          <t>2026-10-17T08:36:51.392435+00:00</t>
         </is>
       </c>
     </row>
@@ -32515,7 +32523,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.423633+00:00</t>
+          <t>2026-10-17T08:36:51.393816+00:00</t>
         </is>
       </c>
     </row>
@@ -32551,13 +32559,21 @@
           <t>papers/R13967/main/5e9f84dbaf01_R13967_2012_An_Improved_Biomass_Waste_Anaerobic_Degradation_Technology_for_Producing.pdf</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13967_2012_An_Improved_Biomass_Waste_Anaerobic_Degradation_Technology_for_Producing.pdf</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R13967_2012_An_Improved_Biomass_Waste_Anaerobic_Degradation_Technology_for_Producing.pdf</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13967_2012_An_Improved_Biomass_Waste_Anaerobic_Degradation_Technology_for_Producing.pdf</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -32573,12 +32589,12 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -32615,7 +32631,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.423654+00:00</t>
+          <t>2026-10-17T08:36:51.393974+00:00</t>
         </is>
       </c>
     </row>
@@ -32715,7 +32731,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.423658+00:00</t>
+          <t>2026-10-17T08:36:51.393987+00:00</t>
         </is>
       </c>
     </row>
@@ -32751,13 +32767,21 @@
           <t>papers/R13957/main/3db804dcdefb_R13957_2017_Microaeration_for_biogas_desulfurization_experimental_and_simulation_study_of.pdf</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13957_2017_Microaeration_for_biogas_desulfurization_experimental_and_simulation_study_of.pdf</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R13957_2017_Microaeration_for_biogas_desulfurization_experimental_and_simulation_study_of.pdf</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13957_2017_Microaeration_for_biogas_desulfurization_experimental_and_simulation_study_of.pdf</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -32773,12 +32797,12 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -32815,7 +32839,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.423660+00:00</t>
+          <t>2026-10-17T08:36:51.398940+00:00</t>
         </is>
       </c>
     </row>
@@ -32851,13 +32875,21 @@
           <t>papers/R04510/main/c4520ca79e30_R04510_2019_Anaerobic_digestion_of_wastewater_rich_in_sulfate_and_sulfide_effects_of_metallic_waste_addition_and.pdf</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R04510_2019_Anaerobic_digestion_of_wastewater_rich_in_sulfate_and_sulfide_effects_of_metallic_waste_addition_and.pdf</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R04510_2019_Anaerobic_digestion_of_wastewater_rich_in_sulfate_and_sulfide_effects_of_metallic_waste_addition_and.pdf</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R04510_2019_Anaerobic_digestion_of_wastewater_rich_in_sulfate_and_sulfide_effects_of_metallic_waste_addition_and.pdf</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -32873,12 +32905,12 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -32911,7 +32943,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.423664+00:00</t>
+          <t>2026-10-17T08:36:51.399377+00:00</t>
         </is>
       </c>
     </row>
@@ -32947,13 +32979,21 @@
           <t>papers/R13889/main/8db0dcdf434e_R13889_2018_Increase_in_biogas_production_in_anaerobic_sludge_digestion_by_combining_aerobic_hydrolysis_and_addi.pdf</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13889_2018_Increase_in_biogas_production_in_anaerobic_sludge_digestion_by_combining_aerobic_hydrolysis_and_addi.pdf</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R13889_2018_Increase_in_biogas_production_in_anaerobic_sludge_digestion_by_combining_aerobic_hydrolysis_and_addi.pdf</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13889_2018_Increase_in_biogas_production_in_anaerobic_sludge_digestion_by_combining_aerobic_hydrolysis_and_addi.pdf</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -32969,12 +33009,12 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -33007,7 +33047,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.423667+00:00</t>
+          <t>2026-10-17T08:36:51.399734+00:00</t>
         </is>
       </c>
     </row>
@@ -33103,7 +33143,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.423671+00:00</t>
+          <t>2026-10-17T08:36:51.399748+00:00</t>
         </is>
       </c>
     </row>
@@ -33199,7 +33239,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.423674+00:00</t>
+          <t>2026-10-17T08:36:51.399754+00:00</t>
         </is>
       </c>
     </row>
@@ -33295,7 +33335,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.423677+00:00</t>
+          <t>2026-10-17T08:36:51.399758+00:00</t>
         </is>
       </c>
     </row>
@@ -33391,7 +33431,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.423680+00:00</t>
+          <t>2026-10-17T08:36:51.399761+00:00</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33527,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.423684+00:00</t>
+          <t>2026-10-17T08:36:51.399765+00:00</t>
         </is>
       </c>
     </row>
@@ -33595,7 +33635,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.424340+00:00</t>
+          <t>2026-10-17T08:36:51.400497+00:00</t>
         </is>
       </c>
     </row>
@@ -33695,7 +33735,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.424355+00:00</t>
+          <t>2026-10-17T08:36:51.400516+00:00</t>
         </is>
       </c>
     </row>
@@ -33803,7 +33843,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.424407+00:00</t>
+          <t>2026-10-17T08:36:51.400569+00:00</t>
         </is>
       </c>
     </row>
@@ -33911,7 +33951,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.424639+00:00</t>
+          <t>2026-10-17T08:36:51.400788+00:00</t>
         </is>
       </c>
     </row>
@@ -34019,7 +34059,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.424756+00:00</t>
+          <t>2026-10-17T08:36:51.400910+00:00</t>
         </is>
       </c>
     </row>
@@ -34131,7 +34171,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.424870+00:00</t>
+          <t>2026-10-17T08:36:51.401029+00:00</t>
         </is>
       </c>
     </row>
@@ -34239,7 +34279,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.425241+00:00</t>
+          <t>2026-10-17T08:36:51.401429+00:00</t>
         </is>
       </c>
     </row>
@@ -34347,7 +34387,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.425439+00:00</t>
+          <t>2026-10-17T08:36:51.401642+00:00</t>
         </is>
       </c>
     </row>
@@ -34459,7 +34499,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.425586+00:00</t>
+          <t>2026-10-17T08:36:51.401701+00:00</t>
         </is>
       </c>
     </row>
@@ -34571,7 +34611,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.425664+00:00</t>
+          <t>2026-10-17T08:36:51.401762+00:00</t>
         </is>
       </c>
     </row>
@@ -34683,7 +34723,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.425817+00:00</t>
+          <t>2026-10-17T08:36:51.401909+00:00</t>
         </is>
       </c>
     </row>
@@ -34795,7 +34835,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.425863+00:00</t>
+          <t>2026-10-17T08:36:51.401955+00:00</t>
         </is>
       </c>
     </row>
@@ -34903,7 +34943,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.426332+00:00</t>
+          <t>2026-10-17T08:36:51.402623+00:00</t>
         </is>
       </c>
     </row>
@@ -35011,7 +35051,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.426414+00:00</t>
+          <t>2026-10-17T08:36:51.402720+00:00</t>
         </is>
       </c>
     </row>
@@ -35111,7 +35151,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.426425+00:00</t>
+          <t>2026-10-17T08:36:51.402732+00:00</t>
         </is>
       </c>
     </row>
@@ -35211,7 +35251,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.426428+00:00</t>
+          <t>2026-10-17T08:36:51.402737+00:00</t>
         </is>
       </c>
     </row>
@@ -35315,7 +35355,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.426432+00:00</t>
+          <t>2026-10-17T08:36:51.402740+00:00</t>
         </is>
       </c>
     </row>
@@ -35415,7 +35455,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.426435+00:00</t>
+          <t>2026-10-17T08:36:51.402743+00:00</t>
         </is>
       </c>
     </row>
@@ -35523,7 +35563,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.426646+00:00</t>
+          <t>2026-10-17T08:36:51.402956+00:00</t>
         </is>
       </c>
     </row>
@@ -35631,7 +35671,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427804+00:00</t>
+          <t>2026-10-17T08:36:51.403942+00:00</t>
         </is>
       </c>
     </row>
@@ -35725,7 +35765,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427831+00:00</t>
+          <t>2026-10-17T08:36:51.403962+00:00</t>
         </is>
       </c>
     </row>
@@ -35819,7 +35859,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427835+00:00</t>
+          <t>2026-10-17T08:36:51.403966+00:00</t>
         </is>
       </c>
     </row>
@@ -35913,7 +35953,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427839+00:00</t>
+          <t>2026-10-17T08:36:51.403970+00:00</t>
         </is>
       </c>
     </row>
@@ -36007,7 +36047,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427841+00:00</t>
+          <t>2026-10-17T08:36:51.403973+00:00</t>
         </is>
       </c>
     </row>
@@ -36101,7 +36141,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427844+00:00</t>
+          <t>2026-10-17T08:36:51.403976+00:00</t>
         </is>
       </c>
     </row>
@@ -36195,7 +36235,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427848+00:00</t>
+          <t>2026-10-17T08:36:51.403979+00:00</t>
         </is>
       </c>
     </row>
@@ -36289,7 +36329,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427851+00:00</t>
+          <t>2026-10-17T08:36:51.403982+00:00</t>
         </is>
       </c>
     </row>
@@ -36383,7 +36423,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427854+00:00</t>
+          <t>2026-10-17T08:36:51.403985+00:00</t>
         </is>
       </c>
     </row>
@@ -36477,7 +36517,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427857+00:00</t>
+          <t>2026-10-17T08:36:51.403988+00:00</t>
         </is>
       </c>
     </row>
@@ -36571,7 +36611,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427859+00:00</t>
+          <t>2026-10-17T08:36:51.403991+00:00</t>
         </is>
       </c>
     </row>
@@ -36665,7 +36705,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427862+00:00</t>
+          <t>2026-10-17T08:36:51.403995+00:00</t>
         </is>
       </c>
     </row>
@@ -36759,7 +36799,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427865+00:00</t>
+          <t>2026-10-17T08:36:51.403998+00:00</t>
         </is>
       </c>
     </row>
@@ -36853,7 +36893,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427868+00:00</t>
+          <t>2026-10-17T08:36:51.404001+00:00</t>
         </is>
       </c>
     </row>
@@ -36947,7 +36987,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427872+00:00</t>
+          <t>2026-10-17T08:36:51.404004+00:00</t>
         </is>
       </c>
     </row>
@@ -37041,7 +37081,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427875+00:00</t>
+          <t>2026-10-17T08:36:51.404008+00:00</t>
         </is>
       </c>
     </row>
@@ -37135,7 +37175,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427877+00:00</t>
+          <t>2026-10-17T08:36:51.404011+00:00</t>
         </is>
       </c>
     </row>
@@ -37229,7 +37269,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427880+00:00</t>
+          <t>2026-10-17T08:36:51.404014+00:00</t>
         </is>
       </c>
     </row>
@@ -37323,7 +37363,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427883+00:00</t>
+          <t>2026-10-17T08:36:51.404017+00:00</t>
         </is>
       </c>
     </row>
@@ -37417,7 +37457,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427886+00:00</t>
+          <t>2026-10-17T08:36:51.404021+00:00</t>
         </is>
       </c>
     </row>
@@ -37511,7 +37551,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427889+00:00</t>
+          <t>2026-10-17T08:36:51.404024+00:00</t>
         </is>
       </c>
     </row>
@@ -37605,7 +37645,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427891+00:00</t>
+          <t>2026-10-17T08:36:51.404027+00:00</t>
         </is>
       </c>
     </row>
@@ -37699,7 +37739,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427895+00:00</t>
+          <t>2026-10-17T08:36:51.404032+00:00</t>
         </is>
       </c>
     </row>
@@ -37793,7 +37833,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427897+00:00</t>
+          <t>2026-10-17T08:36:51.404035+00:00</t>
         </is>
       </c>
     </row>
@@ -37887,7 +37927,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427901+00:00</t>
+          <t>2026-10-17T08:36:51.404038+00:00</t>
         </is>
       </c>
     </row>
@@ -37981,7 +38021,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427904+00:00</t>
+          <t>2026-10-17T08:36:51.404042+00:00</t>
         </is>
       </c>
     </row>
@@ -38075,7 +38115,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427907+00:00</t>
+          <t>2026-10-17T08:36:51.404045+00:00</t>
         </is>
       </c>
     </row>
@@ -38169,7 +38209,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427910+00:00</t>
+          <t>2026-10-17T08:36:51.404049+00:00</t>
         </is>
       </c>
     </row>
@@ -38269,7 +38309,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T08:35:55.427912+00:00</t>
+          <t>2026-10-17T08:36:51.404053+00:00</t>
         </is>
       </c>
     </row>
@@ -38284,7 +38324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38492,12 +38532,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R13944</t>
+          <t>R13972</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R13944.main.7e22fbfd39ddfed0</t>
+          <t>R13972.main.ff4ee9377a7e227c</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -38507,20 +38547,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7e22fbfd39ddfed09b9235fea5c6914cfbe5987d12564fc9cb799bf412ae6779</t>
+          <t>ff4ee9377a7e227c48a5bc64d301bfc1a989ee0e709c322eb90f254819d7b391</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12042699</v>
+        <v>1192569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://scholarspace.manoa.hawaii.edu/server/api/core/bitstreams/60c88164-f37f-492a-97bc-e34a2f2b1698/content</t>
+          <t>https://www.osti.gov/servlets/purl/2386939</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>R13944_2018_Oxidation-Reduction_Potential-Based_Micro-Aeration_Control_System_for_Anaerobic_Digestion.pdf</t>
+          <t>R13972_2022_Enhancing_methane_production_of_anaerobic_digested_sewage_sludge_by.pdf</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -38532,12 +38572,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R13967</t>
+          <t>R02719</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R13967.main.5e9f84dbaf01dd19</t>
+          <t>R02719.main.4bf5e309b2ef3431</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -38547,20 +38587,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5e9f84dbaf01dd19674f09cbce96f338f32fe21a37a883bb9658e49af7072194</t>
+          <t>4bf5e309b2ef343162a9588383a7ae0254118c33cdf2e96bec1a05459fae1523</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>160020</v>
+        <v>583591</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.aceee.org/wp-content/uploads/proceedings-1980-2020/2012/0193-000342.pdf</t>
+          <t>https://digital.csic.es/bitstream/10261/137944/1/Post_2016_JEnvSciHealth_A_BorjaR.pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>R13967_2012_An_Improved_Biomass_Waste_Anaerobic_Degradation_Technology_for_Producing.pdf</t>
+          <t>R02719_2016_Performance_evaluation_of_micro_aerobic_hydrolysis_of_mixed_sludge_Optimum_aeration_and_effect_on_it.pdf</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -38572,12 +38612,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R13972</t>
+          <t>R02282</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R13972.main.ff4ee9377a7e227c</t>
+          <t>R02282.main.e709439b748e7938</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -38587,20 +38627,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ff4ee9377a7e227c48a5bc64d301bfc1a989ee0e709c322eb90f254819d7b391</t>
+          <t>e709439b748e793826102646c009aa10e1e9ac30627ac301fac7dd42276a2047</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1192569</v>
+        <v>1067465</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.osti.gov/servlets/purl/2386939</t>
+          <t>https://digital.csic.es/bitstream/10261/130093/1/Postprint_2016_EnviromRev_V24_P84.pdf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>R13972_2022_Enhancing_methane_production_of_anaerobic_digested_sewage_sludge_by.pdf</t>
+          <t>R02282_2016_Advances_in_the_biological_removal_of_sulphides_from_aqueous_phase_in_anaerobic_processes_A_review.pdf</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -38612,12 +38652,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R13957</t>
+          <t>R13905</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R13957.main.3db804dcdefb7608</t>
+          <t>R13905.main.c75b5084c2545bd9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -38627,20 +38667,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3db804dcdefb7608eefc6bf166b0713cbbec8ac027b1c01831aec97b54253b82</t>
+          <t>c75b5084c2545bd939d3b1928be41fe0072c7302f26c25ba023c4bb6fc8a6970</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7806265</v>
+        <v>2159708</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://backoffice.biblio.ugent.be/download/8530499/8530500</t>
+          <t>https://ddd.uab.cat/pub/artpub/2017/196242/wasbioval_a2017m7v8n5p1793.pdf</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>R13957_2017_Microaeration_for_biogas_desulfurization_experimental_and_simulation_study_of.pdf</t>
+          <t>R13905_2017_The_Effect_of_a_Short_Term_Aerobic_Pretreatment_Step_on_the_Anaerobic_Co_digestion_of_the_Organic_Fr.pdf</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -38652,12 +38692,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R04510</t>
+          <t>R13932</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R04510.main.c4520ca79e301bb6</t>
+          <t>R13932.main.c15f49a3d617e1be</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -38667,20 +38707,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>c4520ca79e301bb606a8ab1fef6cf4af9064c0d85f3c390a4cf31a877238e1c6</t>
+          <t>c15f49a3d617e1be5e21578ebda1c2d855f8d460c1d66f446ad0d02856a40a13</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>492630</v>
+        <v>1258157</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/196040/5/PostP_2019_JESH_V54_Iss10.pdf</t>
+          <t>https://hal.inrae.fr/hal-02620984/document</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>R04510_2019_Anaerobic_digestion_of_wastewater_rich_in_sulfate_and_sulfide_effects_of_metallic_waste_addition_and.pdf</t>
+          <t>R13932_2018_Comparison_of_pre_and_inter_stage_aerobic_treatment_of_wastewater_sludge_Effects_on_biogas_productio.pdf</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -38692,12 +38732,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R13889</t>
+          <t>R13956</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R13889.main.8db0dcdf434e876e</t>
+          <t>R13956.main.fedaffcdf5be81e2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -38707,20 +38747,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8db0dcdf434e876e7cbff3cf342105807bdd41a900f74c0028cb14a6c6e56779</t>
+          <t>fedaffcdf5be81e2070b7edb0531c332e423578228eeb8c55a6afc4ba8fe1e18</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>514378</v>
+        <v>421626</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/178890/1/PotP_2018_RE_V123_P541.pdf</t>
+          <t>https://www.banglajol.info/index.php/BJSIR/article/download/25579/17152</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>R13889_2018_Increase_in_biogas_production_in_anaerobic_sludge_digestion_by_combining_aerobic_hydrolysis_and_addi.pdf</t>
+          <t>R13956_2015_Anaerobic_digestion_of_mixed_dried_fallen_leaves_by_mixing_with_cow_dung.pdf</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -38732,12 +38772,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R02719</t>
+          <t>R13955</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R02719.main.4bf5e309b2ef3431</t>
+          <t>R13955.main.7549e1025985363e</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -38747,20 +38787,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4bf5e309b2ef343162a9588383a7ae0254118c33cdf2e96bec1a05459fae1523</t>
+          <t>7549e1025985363e89542bbc1af6eaaa1150bbd62ea43bdd03d2c7b764631f9d</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>583591</v>
+        <v>14662438</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/137944/1/Post_2016_JEnvSciHealth_A_BorjaR.pdf</t>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>R02719_2016_Performance_evaluation_of_micro_aerobic_hydrolysis_of_mixed_sludge_Optimum_aeration_and_effect_on_it.pdf</t>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -38772,35 +38812,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R02282</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R02282.main.e709439b748e7938</t>
+          <t>R07238.supplementary.0b7925ad1ed9c793</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>e709439b748e793826102646c009aa10e1e9ac30627ac301fac7dd42276a2047</t>
+          <t>0b7925ad1ed9c7939a79ba6294d17abc4b23fca77e52ec50df5463d050940d1e</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1067465</v>
+        <v>49526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/130093/1/Postprint_2016_EnviromRev_V24_P84.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>R02282_2016_Advances_in_the_biological_removal_of_sulphides_from_aqueous_phase_in_anaerobic_processes_A_review.pdf</t>
+          <t>mmc1.docx</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -38812,35 +38852,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R13905</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R13905.main.c75b5084c2545bd9</t>
+          <t>R07238.supplementary.f346f9bdcc964013</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>c75b5084c2545bd939d3b1928be41fe0072c7302f26c25ba023c4bb6fc8a6970</t>
+          <t>f346f9bdcc964013ecb7c4282d6b30f1ab334e035d98adcc653de1447fbe9a9a</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2159708</v>
+        <v>14286928</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://ddd.uab.cat/pub/artpub/2017/196242/wasbioval_a2017m7v8n5p1793.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>R13905_2017_The_Effect_of_a_Short_Term_Aerobic_Pretreatment_Step_on_the_Anaerobic_Co_digestion_of_the_Organic_Fr.pdf</t>
+          <t>mmc2.zip</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -38852,35 +38892,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R13932</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R13932.main.c15f49a3d617e1be</t>
+          <t>R07238.derived.49b84e369d4bb31b</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>c15f49a3d617e1be5e21578ebda1c2d855f8d460c1d66f446ad0d02856a40a13</t>
+          <t>49b84e369d4bb31b4ebdcd25265be3174105c3433e6fbb865f34a445775516a1</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1258157</v>
+        <v>34855493</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://hal.inrae.fr/hal-02620984/document</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>R13932_2018_Comparison_of_pre_and_inter_stage_aerobic_treatment_of_wastewater_sludge_Effects_on_biogas_productio.pdf</t>
+          <t>g a.skp</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -38892,35 +38932,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R13956</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R13956.main.fedaffcdf5be81e2</t>
+          <t>R08646.supplementary.cfda7e29b12b9784</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>fedaffcdf5be81e2070b7edb0531c332e423578228eeb8c55a6afc4ba8fe1e18</t>
+          <t>cfda7e29b12b97846343963f9f3b64e784bc79644fb1ee1ca31170be78d75327</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>421626</v>
+        <v>42279</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.banglajol.info/index.php/BJSIR/article/download/25579/17152</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>R13956_2015_Anaerobic_digestion_of_mixed_dried_fallen_leaves_by_mixing_with_cow_dung.pdf</t>
+          <t>mmc1.docx</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -38932,35 +38972,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R13955</t>
+          <t>R03161</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R13955.main.7549e1025985363e</t>
+          <t>R03161.evidence_xml.466f3a1e78e8b0f1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7549e1025985363e89542bbc1af6eaaa1150bbd62ea43bdd03d2c7b764631f9d</t>
+          <t>466f3a1e78e8b0f148b1f28f97b61f7134c61488c837c5c5a26ef7316cebc1e9</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>14662438</v>
+        <v>59018</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/fullTextXML</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
+          <t>PMC5627928_fullText.xml</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -38972,35 +39012,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R03161</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R07238.supplementary.0b7925ad1ed9c793</t>
+          <t>R03161.transport_archive.0ef4d4796c84feff</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0b7925ad1ed9c7939a79ba6294d17abc4b23fca77e52ec50df5463d050940d1e</t>
+          <t>0ef4d4796c84fefff7b8450bc56400f8c59f4bdcf074fc51404edff5e4e217f6</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>49526</v>
+        <v>726772</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/supplementaryFiles</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>mmc1.docx</t>
+          <t>PMC5627928_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -39012,35 +39052,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R04092</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R07238.supplementary.f346f9bdcc964013</t>
+          <t>R04092.evidence_xml.0fb90085e30680fa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>f346f9bdcc964013ecb7c4282d6b30f1ab334e035d98adcc653de1447fbe9a9a</t>
+          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>14286928</v>
+        <v>77995</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>mmc2.zip</t>
+          <t>PMC6288047_fullText.xml</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -39052,35 +39092,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R05839</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R07238.derived.49b84e369d4bb31b</t>
+          <t>R05839.evidence_xml.18ffd43dee955086</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>49b84e369d4bb31b4ebdcd25265be3174105c3433e6fbb865f34a445775516a1</t>
+          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>34855493</v>
+        <v>75205</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>g a.skp</t>
+          <t>PMC7566014_fullText.xml</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -39092,35 +39132,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R08877</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R08646.supplementary.cfda7e29b12b9784</t>
+          <t>R08877.evidence_xml.e8712e4198baab4c</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>cfda7e29b12b97846343963f9f3b64e784bc79644fb1ee1ca31170be78d75327</t>
+          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>42279</v>
+        <v>111864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>mmc1.docx</t>
+          <t>PMC10714394_fullText.xml</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -39132,35 +39172,35 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R03161</t>
+          <t>R08877</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R03161.evidence_xml.466f3a1e78e8b0f1</t>
+          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>466f3a1e78e8b0f148b1f28f97b61f7134c61488c837c5c5a26ef7316cebc1e9</t>
+          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>59018</v>
+        <v>704921</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PMC5627928_fullText.xml</t>
+          <t>PMC10714394_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -39172,35 +39212,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R03161</t>
+          <t>R09236</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R03161.transport_archive.0ef4d4796c84feff</t>
+          <t>R09236.evidence_xml.72064fe9276d8309</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0ef4d4796c84fefff7b8450bc56400f8c59f4bdcf074fc51404edff5e4e217f6</t>
+          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>726772</v>
+        <v>193052</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>PMC5627928_supplementaryFiles.zip</t>
+          <t>PMC10535533_fullText.xml</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -39212,35 +39252,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R04092</t>
+          <t>R09236</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R04092.evidence_xml.0fb90085e30680fa</t>
+          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
+          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>77995</v>
+        <v>483405</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>PMC6288047_fullText.xml</t>
+          <t>PMC10535533_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -39252,12 +39292,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R05839</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R05839.evidence_xml.18ffd43dee955086</t>
+          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -39267,20 +39307,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
+          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>75205</v>
+        <v>118002</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PMC7566014_fullText.xml</t>
+          <t>PMC10837232_fullText.xml</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -39292,35 +39332,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R08877.evidence_xml.e8712e4198baab4c</t>
+          <t>R10086.transport_archive.4d9eddf454b786ed</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
+          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>111864</v>
+        <v>641038</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PMC10714394_fullText.xml</t>
+          <t>PMC10837232_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -39332,35 +39372,35 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
+          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
+          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>704921</v>
+        <v>173586</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>PMC10714394_supplementaryFiles.zip</t>
+          <t>PMC12937426_fullText.xml</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -39372,35 +39412,35 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R09236.evidence_xml.72064fe9276d8309</t>
+          <t>R12985.transport_archive.418d45f1ca296020</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
+          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>193052</v>
+        <v>672244</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>PMC10535533_fullText.xml</t>
+          <t>PMC12937426_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -39412,35 +39452,35 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R05542</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
+          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
+          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>483405</v>
+        <v>100215</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PMC10535533_supplementaryFiles.zip</t>
+          <t>PMC9056904_fullText.xml</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -39452,12 +39492,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
+          <t>R06325.evidence_xml.645deb707d3790b5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -39467,20 +39507,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
+          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>118002</v>
+        <v>160509</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PMC10837232_fullText.xml</t>
+          <t>PMC8290346_fullText.xml</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -39492,12 +39532,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R10086.transport_archive.4d9eddf454b786ed</t>
+          <t>R06325.transport_archive.6eb4ef126661714a</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -39507,20 +39547,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
+          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>641038</v>
+        <v>1730580</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PMC10837232_supplementaryFiles.zip</t>
+          <t>PMC8290346_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -39532,12 +39572,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
+          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -39547,20 +39587,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
+          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>173586</v>
+        <v>151458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PMC12937426_fullText.xml</t>
+          <t>PMC8044681_fullText.xml</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -39572,12 +39612,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R12985.transport_archive.418d45f1ca296020</t>
+          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -39587,20 +39627,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
+          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>672244</v>
+        <v>14596266</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PMC12937426_supplementaryFiles.zip</t>
+          <t>PMC8044681_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -39612,12 +39652,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>R05542</t>
+          <t>R03477</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
+          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -39627,20 +39667,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
+          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100215</v>
+        <v>121650</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>PMC9056904_fullText.xml</t>
+          <t>PMC5371168_fullText.xml</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -39652,12 +39692,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>R06325.evidence_xml.645deb707d3790b5</t>
+          <t>R08646.evidence_xml.c7b723e8020f6582</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -39667,20 +39707,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
+          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>160509</v>
+        <v>304277</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>PMC8290346_fullText.xml</t>
+          <t>PMC10559078_fullText.xml</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -39692,12 +39732,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R06325.transport_archive.6eb4ef126661714a</t>
+          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -39707,20 +39747,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
+          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1730580</v>
+        <v>1539133</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>PMC8290346_supplementaryFiles.zip</t>
+          <t>PMC10559078_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -39732,12 +39772,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R09804</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
+          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -39747,20 +39787,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
+          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>151458</v>
+        <v>211630</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>PMC8044681_fullText.xml</t>
+          <t>PMC11076452_fullText.xml</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -39772,35 +39812,35 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R11503</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
+          <t>R11503.evidence_xml.4002d57be59c215c</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
+          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>14596266</v>
+        <v>258637</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>PMC8044681_supplementaryFiles.zip</t>
+          <t>PMC12561102_fullText.xml</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -39812,12 +39852,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>R03477</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
+          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -39827,20 +39867,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
+          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>121650</v>
+        <v>256247</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>PMC5371168_fullText.xml</t>
+          <t>PMC12125087_fullText.xml</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -39852,35 +39892,35 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>R08646.evidence_xml.c7b723e8020f6582</t>
+          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
+          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>304277</v>
+        <v>521862</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>PMC10559078_fullText.xml</t>
+          <t>PMC12125087_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -39892,35 +39932,35 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
+          <t>R05213.evidence_xml.17894ab410001846</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
+          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1539133</v>
+        <v>130954</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>PMC10559078_supplementaryFiles.zip</t>
+          <t>PMC6858683_fullText.xml</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -39932,35 +39972,35 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
+          <t>R05213.transport_archive.c61c88cf9fd489be</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
+          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>211630</v>
+        <v>1960371</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>PMC11076452_fullText.xml</t>
+          <t>PMC6858683_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -39972,12 +40012,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>R11503</t>
+          <t>R09585</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>R11503.evidence_xml.4002d57be59c215c</t>
+          <t>R09585.evidence_xml.a3430f38fa1652de</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -39987,20 +40027,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
+          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>258637</v>
+        <v>100534</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>PMC12561102_fullText.xml</t>
+          <t>PMC10609292_fullText.xml</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -40012,238 +40052,38 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R11596</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
+          <t>R11596.main.0b2e2d98dffd5449</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
+          <t>0b2e2d98dffd544958b06cc2229d310e4b7d529bd3914c47f20d6a66789a28be</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>256247</v>
+        <v>1659399</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
+          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/7262c516-6b14-4001-a173-517d1187c8d9/content</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>PMC12125087_fullText.xml</t>
+          <t>R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>R11844</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>transport_archive</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>521862</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>PMC12125087_supplementaryFiles.zip</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>R05213</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>R05213.evidence_xml.17894ab410001846</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>evidence_xml</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>130954</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>PMC6858683_fullText.xml</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>R05213</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>R05213.transport_archive.c61c88cf9fd489be</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>transport_archive</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>1960371</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>PMC6858683_supplementaryFiles.zip</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>R09585</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>R09585.evidence_xml.a3430f38fa1652de</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>evidence_xml</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>100534</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>PMC10609292_fullText.xml</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>R11596</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>R11596.main.0b2e2d98dffd5449</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>0b2e2d98dffd544958b06cc2229d310e4b7d529bd3914c47f20d6a66789a28be</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>1659399</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/7262c516-6b14-4001-a173-517d1187c8d9/content</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
         <is>
           <t>历史已获取，当前原件未恢复</t>
         </is>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -4746,7 +4746,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -21255,7 +21255,7 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
@@ -22369,7 +22369,7 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
@@ -23385,7 +23385,7 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.266818+00:00</t>
+          <t>2026-10-17T08:38:06.063474+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.267909+00:00</t>
+          <t>2026-10-17T08:38:06.064520+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.267941+00:00</t>
+          <t>2026-10-17T08:38:06.064547+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.268173+00:00</t>
+          <t>2026-10-17T08:38:06.064855+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.269523+00:00</t>
+          <t>2026-10-17T08:38:06.066256+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.270021+00:00</t>
+          <t>2026-10-17T08:38:06.066787+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.276169+00:00</t>
+          <t>2026-10-17T08:38:06.072610+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.279015+00:00</t>
+          <t>2026-10-17T08:38:06.075260+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.279994+00:00</t>
+          <t>2026-10-17T08:38:06.076350+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.280384+00:00</t>
+          <t>2026-10-17T08:38:06.076686+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.281132+00:00</t>
+          <t>2026-10-17T08:38:06.077674+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.281819+00:00</t>
+          <t>2026-10-17T08:38:06.078358+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.282737+00:00</t>
+          <t>2026-10-17T08:38:06.079359+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.282971+00:00</t>
+          <t>2026-10-17T08:38:06.079614+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.283881+00:00</t>
+          <t>2026-10-17T08:38:06.080474+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.291200+00:00</t>
+          <t>2026-10-17T08:38:06.088624+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.292112+00:00</t>
+          <t>2026-10-17T08:38:06.089384+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.293613+00:00</t>
+          <t>2026-10-17T08:38:06.090592+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.296343+00:00</t>
+          <t>2026-10-17T08:38:06.093199+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.297520+00:00</t>
+          <t>2026-10-17T08:38:06.094323+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.298709+00:00</t>
+          <t>2026-10-17T08:38:06.095591+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.302840+00:00</t>
+          <t>2026-10-17T08:38:06.100766+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.305352+00:00</t>
+          <t>2026-10-17T08:38:06.103231+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.307180+00:00</t>
+          <t>2026-10-17T08:38:06.105032+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.307890+00:00</t>
+          <t>2026-10-17T08:38:06.105721+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.308246+00:00</t>
+          <t>2026-10-17T08:38:06.106094+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.310318+00:00</t>
+          <t>2026-10-17T08:38:06.108162+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.311801+00:00</t>
+          <t>2026-10-17T08:38:06.109513+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.313936+00:00</t>
+          <t>2026-10-17T08:38:06.111550+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.316016+00:00</t>
+          <t>2026-10-17T08:38:06.113562+00:00</t>
         </is>
       </c>
     </row>
@@ -27571,7 +27571,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.316038+00:00</t>
+          <t>2026-10-17T08:38:06.113585+00:00</t>
         </is>
       </c>
     </row>
@@ -27679,7 +27679,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.316769+00:00</t>
+          <t>2026-10-17T08:38:06.114164+00:00</t>
         </is>
       </c>
     </row>
@@ -27787,7 +27787,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.318515+00:00</t>
+          <t>2026-10-17T08:38:06.115802+00:00</t>
         </is>
       </c>
     </row>
@@ -27895,7 +27895,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.321365+00:00</t>
+          <t>2026-10-17T08:38:06.118694+00:00</t>
         </is>
       </c>
     </row>
@@ -28003,7 +28003,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.323614+00:00</t>
+          <t>2026-10-17T08:38:06.121076+00:00</t>
         </is>
       </c>
     </row>
@@ -28111,7 +28111,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.324877+00:00</t>
+          <t>2026-10-17T08:38:06.122437+00:00</t>
         </is>
       </c>
     </row>
@@ -28219,7 +28219,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.327767+00:00</t>
+          <t>2026-10-17T08:38:06.125376+00:00</t>
         </is>
       </c>
     </row>
@@ -28327,7 +28327,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.328654+00:00</t>
+          <t>2026-10-17T08:38:06.126131+00:00</t>
         </is>
       </c>
     </row>
@@ -28435,7 +28435,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.330358+00:00</t>
+          <t>2026-10-17T08:38:06.127706+00:00</t>
         </is>
       </c>
     </row>
@@ -28543,7 +28543,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.330624+00:00</t>
+          <t>2026-10-17T08:38:06.127959+00:00</t>
         </is>
       </c>
     </row>
@@ -28651,7 +28651,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.332646+00:00</t>
+          <t>2026-10-17T08:38:06.130052+00:00</t>
         </is>
       </c>
     </row>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.335550+00:00</t>
+          <t>2026-10-17T08:38:06.133038+00:00</t>
         </is>
       </c>
     </row>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.336889+00:00</t>
+          <t>2026-10-17T08:38:06.135048+00:00</t>
         </is>
       </c>
     </row>
@@ -28975,7 +28975,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.337628+00:00</t>
+          <t>2026-10-17T08:38:06.135888+00:00</t>
         </is>
       </c>
     </row>
@@ -29083,7 +29083,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.340321+00:00</t>
+          <t>2026-10-17T08:38:06.138727+00:00</t>
         </is>
       </c>
     </row>
@@ -29191,7 +29191,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.341813+00:00</t>
+          <t>2026-10-17T08:38:06.140001+00:00</t>
         </is>
       </c>
     </row>
@@ -29299,7 +29299,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.345362+00:00</t>
+          <t>2026-10-17T08:38:06.143888+00:00</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.347070+00:00</t>
+          <t>2026-10-17T08:38:06.145829+00:00</t>
         </is>
       </c>
     </row>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.349021+00:00</t>
+          <t>2026-10-17T08:38:06.148342+00:00</t>
         </is>
       </c>
     </row>
@@ -29623,7 +29623,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.349987+00:00</t>
+          <t>2026-10-17T08:38:06.149670+00:00</t>
         </is>
       </c>
     </row>
@@ -29731,7 +29731,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.350477+00:00</t>
+          <t>2026-10-17T08:38:06.150250+00:00</t>
         </is>
       </c>
     </row>
@@ -29839,7 +29839,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.350843+00:00</t>
+          <t>2026-10-17T08:38:06.150665+00:00</t>
         </is>
       </c>
     </row>
@@ -29947,7 +29947,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.352379+00:00</t>
+          <t>2026-10-17T08:38:06.152240+00:00</t>
         </is>
       </c>
     </row>
@@ -30055,7 +30055,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.353829+00:00</t>
+          <t>2026-10-17T08:38:06.153614+00:00</t>
         </is>
       </c>
     </row>
@@ -30163,7 +30163,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.355391+00:00</t>
+          <t>2026-10-17T08:38:06.155168+00:00</t>
         </is>
       </c>
     </row>
@@ -30271,7 +30271,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.355720+00:00</t>
+          <t>2026-10-17T08:38:06.155522+00:00</t>
         </is>
       </c>
     </row>
@@ -30379,7 +30379,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.356897+00:00</t>
+          <t>2026-10-17T08:38:06.156734+00:00</t>
         </is>
       </c>
     </row>
@@ -30487,7 +30487,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.358273+00:00</t>
+          <t>2026-10-17T08:38:06.158428+00:00</t>
         </is>
       </c>
     </row>
@@ -30595,7 +30595,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.358897+00:00</t>
+          <t>2026-10-17T08:38:06.159050+00:00</t>
         </is>
       </c>
     </row>
@@ -30703,7 +30703,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.359840+00:00</t>
+          <t>2026-10-17T08:38:06.160059+00:00</t>
         </is>
       </c>
     </row>
@@ -30811,7 +30811,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.360167+00:00</t>
+          <t>2026-10-17T08:38:06.160429+00:00</t>
         </is>
       </c>
     </row>
@@ -30919,7 +30919,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.365604+00:00</t>
+          <t>2026-10-17T08:38:06.165936+00:00</t>
         </is>
       </c>
     </row>
@@ -31019,7 +31019,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.365667+00:00</t>
+          <t>2026-10-17T08:38:06.165969+00:00</t>
         </is>
       </c>
     </row>
@@ -31127,7 +31127,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.366270+00:00</t>
+          <t>2026-10-17T08:38:06.166603+00:00</t>
         </is>
       </c>
     </row>
@@ -31235,7 +31235,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.366761+00:00</t>
+          <t>2026-10-17T08:38:06.167125+00:00</t>
         </is>
       </c>
     </row>
@@ -31343,7 +31343,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.367849+00:00</t>
+          <t>2026-10-17T08:38:06.168258+00:00</t>
         </is>
       </c>
     </row>
@@ -31451,7 +31451,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.370944+00:00</t>
+          <t>2026-10-17T08:38:06.171604+00:00</t>
         </is>
       </c>
     </row>
@@ -31559,7 +31559,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.371203+00:00</t>
+          <t>2026-10-17T08:38:06.171873+00:00</t>
         </is>
       </c>
     </row>
@@ -31667,7 +31667,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.375673+00:00</t>
+          <t>2026-10-17T08:38:06.177827+00:00</t>
         </is>
       </c>
     </row>
@@ -31775,7 +31775,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.376532+00:00</t>
+          <t>2026-10-17T08:38:06.178794+00:00</t>
         </is>
       </c>
     </row>
@@ -31883,7 +31883,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.378998+00:00</t>
+          <t>2026-10-17T08:38:06.181058+00:00</t>
         </is>
       </c>
     </row>
@@ -31991,7 +31991,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.380783+00:00</t>
+          <t>2026-10-17T08:38:06.182976+00:00</t>
         </is>
       </c>
     </row>
@@ -32091,7 +32091,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.380805+00:00</t>
+          <t>2026-10-17T08:38:06.183000+00:00</t>
         </is>
       </c>
     </row>
@@ -32199,7 +32199,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.382259+00:00</t>
+          <t>2026-10-17T08:38:06.185032+00:00</t>
         </is>
       </c>
     </row>
@@ -32307,7 +32307,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.384505+00:00</t>
+          <t>2026-10-17T08:38:06.187465+00:00</t>
         </is>
       </c>
     </row>
@@ -32415,7 +32415,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.392435+00:00</t>
+          <t>2026-10-17T08:38:06.196702+00:00</t>
         </is>
       </c>
     </row>
@@ -32523,7 +32523,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.393816+00:00</t>
+          <t>2026-10-17T08:38:06.198462+00:00</t>
         </is>
       </c>
     </row>
@@ -32631,7 +32631,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.393974+00:00</t>
+          <t>2026-10-17T08:38:06.198639+00:00</t>
         </is>
       </c>
     </row>
@@ -32731,7 +32731,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.393987+00:00</t>
+          <t>2026-10-17T08:38:06.198655+00:00</t>
         </is>
       </c>
     </row>
@@ -32839,7 +32839,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.398940+00:00</t>
+          <t>2026-10-17T08:38:06.204636+00:00</t>
         </is>
       </c>
     </row>
@@ -32943,7 +32943,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.399377+00:00</t>
+          <t>2026-10-17T08:38:06.205046+00:00</t>
         </is>
       </c>
     </row>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.399734+00:00</t>
+          <t>2026-10-17T08:38:06.205497+00:00</t>
         </is>
       </c>
     </row>
@@ -33083,13 +33083,21 @@
           <t>papers/R02719/main/4bf5e309b2ef_R02719_2016_Performance_evaluation_of_micro_aerobic_hydrolysis_of_mixed_sludge_Optimum_aeration_and_effect_on_it.pdf</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R02719_2016_Performance_evaluation_of_micro_aerobic_hydrolysis_of_mixed_sludge_Optimum_aeration_and_effect_on_it.pdf</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R02719_2016_Performance_evaluation_of_micro_aerobic_hydrolysis_of_mixed_sludge_Optimum_aeration_and_effect_on_it.pdf</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R02719_2016_Performance_evaluation_of_micro_aerobic_hydrolysis_of_mixed_sludge_Optimum_aeration_and_effect_on_it.pdf</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -33105,12 +33113,12 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -33143,7 +33151,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.399748+00:00</t>
+          <t>2026-10-17T08:38:06.205940+00:00</t>
         </is>
       </c>
     </row>
@@ -33179,13 +33187,21 @@
           <t>papers/R02282/main/e709439b748e_R02282_2016_Advances_in_the_biological_removal_of_sulphides_from_aqueous_phase_in_anaerobic_processes_A_review.pdf</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R02282_2016_Advances_in_the_biological_removal_of_sulphides_from_aqueous_phase_in_anaerobic_processes_A_review.pdf</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R02282_2016_Advances_in_the_biological_removal_of_sulphides_from_aqueous_phase_in_anaerobic_processes_A_review.pdf</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R02282_2016_Advances_in_the_biological_removal_of_sulphides_from_aqueous_phase_in_anaerobic_processes_A_review.pdf</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -33201,12 +33217,12 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -33239,7 +33255,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.399754+00:00</t>
+          <t>2026-10-17T08:38:06.206739+00:00</t>
         </is>
       </c>
     </row>
@@ -33275,13 +33291,21 @@
           <t>papers/R13905/main/c75b5084c254_R13905_2017_The_Effect_of_a_Short_Term_Aerobic_Pretreatment_Step_on_the_Anaerobic_Co_digestion_of_the_Organic_Fr.pdf</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13905_2017_The_Effect_of_a_Short_Term_Aerobic_Pretreatment_Step_on_the_Anaerobic_Co_digestion_of_the_Organic_Fr.pdf</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R13905_2017_The_Effect_of_a_Short_Term_Aerobic_Pretreatment_Step_on_the_Anaerobic_Co_digestion_of_the_Organic_Fr.pdf</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13905_2017_The_Effect_of_a_Short_Term_Aerobic_Pretreatment_Step_on_the_Anaerobic_Co_digestion_of_the_Organic_Fr.pdf</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -33297,12 +33321,12 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -33335,7 +33359,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.399758+00:00</t>
+          <t>2026-10-17T08:38:06.208101+00:00</t>
         </is>
       </c>
     </row>
@@ -33371,13 +33395,21 @@
           <t>papers/R13932/main/c15f49a3d617_R13932_2018_Comparison_of_pre_and_inter_stage_aerobic_treatment_of_wastewater_sludge_Effects_on_biogas_productio.pdf</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13932_2018_Comparison_of_pre_and_inter_stage_aerobic_treatment_of_wastewater_sludge_Effects_on_biogas_productio.pdf</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R13932_2018_Comparison_of_pre_and_inter_stage_aerobic_treatment_of_wastewater_sludge_Effects_on_biogas_productio.pdf</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13932_2018_Comparison_of_pre_and_inter_stage_aerobic_treatment_of_wastewater_sludge_Effects_on_biogas_productio.pdf</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -33393,12 +33425,12 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -33431,7 +33463,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.399761+00:00</t>
+          <t>2026-10-17T08:38:06.208918+00:00</t>
         </is>
       </c>
     </row>
@@ -33467,13 +33499,21 @@
           <t>papers/R13956/main/fedaffcdf5be_R13956_2015_Anaerobic_digestion_of_mixed_dried_fallen_leaves_by_mixing_with_cow_dung.pdf</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13956_2015_Anaerobic_digestion_of_mixed_dried_fallen_leaves_by_mixing_with_cow_dung.pdf</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/candidates/R13956_2015_Anaerobic_digestion_of_mixed_dried_fallen_leaves_by_mixing_with_cow_dung.pdf</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13956_2015_Anaerobic_digestion_of_mixed_dried_fallen_leaves_by_mixing_with_cow_dung.pdf</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -33489,12 +33529,12 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -33527,7 +33567,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.399765+00:00</t>
+          <t>2026-10-17T08:38:06.209217+00:00</t>
         </is>
       </c>
     </row>
@@ -33635,7 +33675,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.400497+00:00</t>
+          <t>2026-10-17T08:38:06.209977+00:00</t>
         </is>
       </c>
     </row>
@@ -33735,7 +33775,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.400516+00:00</t>
+          <t>2026-10-17T08:38:06.210001+00:00</t>
         </is>
       </c>
     </row>
@@ -33843,7 +33883,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.400569+00:00</t>
+          <t>2026-10-17T08:38:06.210062+00:00</t>
         </is>
       </c>
     </row>
@@ -33951,7 +33991,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.400788+00:00</t>
+          <t>2026-10-17T08:38:06.210327+00:00</t>
         </is>
       </c>
     </row>
@@ -34059,7 +34099,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.400910+00:00</t>
+          <t>2026-10-17T08:38:06.210543+00:00</t>
         </is>
       </c>
     </row>
@@ -34171,7 +34211,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.401029+00:00</t>
+          <t>2026-10-17T08:38:06.210684+00:00</t>
         </is>
       </c>
     </row>
@@ -34279,7 +34319,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.401429+00:00</t>
+          <t>2026-10-17T08:38:06.211058+00:00</t>
         </is>
       </c>
     </row>
@@ -34387,7 +34427,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.401642+00:00</t>
+          <t>2026-10-17T08:38:06.211246+00:00</t>
         </is>
       </c>
     </row>
@@ -34499,7 +34539,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.401701+00:00</t>
+          <t>2026-10-17T08:38:06.211380+00:00</t>
         </is>
       </c>
     </row>
@@ -34611,7 +34651,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.401762+00:00</t>
+          <t>2026-10-17T08:38:06.211458+00:00</t>
         </is>
       </c>
     </row>
@@ -34723,7 +34763,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.401909+00:00</t>
+          <t>2026-10-17T08:38:06.211607+00:00</t>
         </is>
       </c>
     </row>
@@ -34835,7 +34875,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.401955+00:00</t>
+          <t>2026-10-17T08:38:06.211653+00:00</t>
         </is>
       </c>
     </row>
@@ -34943,7 +34983,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.402623+00:00</t>
+          <t>2026-10-17T08:38:06.212108+00:00</t>
         </is>
       </c>
     </row>
@@ -35051,7 +35091,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.402720+00:00</t>
+          <t>2026-10-17T08:38:06.212161+00:00</t>
         </is>
       </c>
     </row>
@@ -35151,7 +35191,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.402732+00:00</t>
+          <t>2026-10-17T08:38:06.212171+00:00</t>
         </is>
       </c>
     </row>
@@ -35251,7 +35291,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.402737+00:00</t>
+          <t>2026-10-17T08:38:06.212176+00:00</t>
         </is>
       </c>
     </row>
@@ -35355,7 +35395,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.402740+00:00</t>
+          <t>2026-10-17T08:38:06.212180+00:00</t>
         </is>
       </c>
     </row>
@@ -35455,7 +35495,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.402743+00:00</t>
+          <t>2026-10-17T08:38:06.212184+00:00</t>
         </is>
       </c>
     </row>
@@ -35563,7 +35603,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.402956+00:00</t>
+          <t>2026-10-17T08:38:06.212422+00:00</t>
         </is>
       </c>
     </row>
@@ -35671,7 +35711,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.403942+00:00</t>
+          <t>2026-10-17T08:38:06.213837+00:00</t>
         </is>
       </c>
     </row>
@@ -35765,7 +35805,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.403962+00:00</t>
+          <t>2026-10-17T08:38:06.213865+00:00</t>
         </is>
       </c>
     </row>
@@ -35859,7 +35899,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.403966+00:00</t>
+          <t>2026-10-17T08:38:06.213870+00:00</t>
         </is>
       </c>
     </row>
@@ -35953,7 +35993,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.403970+00:00</t>
+          <t>2026-10-17T08:38:06.213873+00:00</t>
         </is>
       </c>
     </row>
@@ -36047,7 +36087,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.403973+00:00</t>
+          <t>2026-10-17T08:38:06.213876+00:00</t>
         </is>
       </c>
     </row>
@@ -36141,7 +36181,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.403976+00:00</t>
+          <t>2026-10-17T08:38:06.213880+00:00</t>
         </is>
       </c>
     </row>
@@ -36235,7 +36275,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.403979+00:00</t>
+          <t>2026-10-17T08:38:06.213884+00:00</t>
         </is>
       </c>
     </row>
@@ -36329,7 +36369,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.403982+00:00</t>
+          <t>2026-10-17T08:38:06.213887+00:00</t>
         </is>
       </c>
     </row>
@@ -36423,7 +36463,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.403985+00:00</t>
+          <t>2026-10-17T08:38:06.213891+00:00</t>
         </is>
       </c>
     </row>
@@ -36517,7 +36557,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.403988+00:00</t>
+          <t>2026-10-17T08:38:06.213895+00:00</t>
         </is>
       </c>
     </row>
@@ -36611,7 +36651,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.403991+00:00</t>
+          <t>2026-10-17T08:38:06.213898+00:00</t>
         </is>
       </c>
     </row>
@@ -36705,7 +36745,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.403995+00:00</t>
+          <t>2026-10-17T08:38:06.213901+00:00</t>
         </is>
       </c>
     </row>
@@ -36799,7 +36839,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.403998+00:00</t>
+          <t>2026-10-17T08:38:06.213905+00:00</t>
         </is>
       </c>
     </row>
@@ -36893,7 +36933,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.404001+00:00</t>
+          <t>2026-10-17T08:38:06.213908+00:00</t>
         </is>
       </c>
     </row>
@@ -36987,7 +37027,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.404004+00:00</t>
+          <t>2026-10-17T08:38:06.213911+00:00</t>
         </is>
       </c>
     </row>
@@ -37081,7 +37121,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.404008+00:00</t>
+          <t>2026-10-17T08:38:06.213914+00:00</t>
         </is>
       </c>
     </row>
@@ -37175,7 +37215,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.404011+00:00</t>
+          <t>2026-10-17T08:38:06.213918+00:00</t>
         </is>
       </c>
     </row>
@@ -37269,7 +37309,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.404014+00:00</t>
+          <t>2026-10-17T08:38:06.213921+00:00</t>
         </is>
       </c>
     </row>
@@ -37363,7 +37403,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.404017+00:00</t>
+          <t>2026-10-17T08:38:06.213924+00:00</t>
         </is>
       </c>
     </row>
@@ -37457,7 +37497,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.404021+00:00</t>
+          <t>2026-10-17T08:38:06.213927+00:00</t>
         </is>
       </c>
     </row>
@@ -37551,7 +37591,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.404024+00:00</t>
+          <t>2026-10-17T08:38:06.213929+00:00</t>
         </is>
       </c>
     </row>
@@ -37645,7 +37685,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.404027+00:00</t>
+          <t>2026-10-17T08:38:06.213933+00:00</t>
         </is>
       </c>
     </row>
@@ -37739,7 +37779,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.404032+00:00</t>
+          <t>2026-10-17T08:38:06.213936+00:00</t>
         </is>
       </c>
     </row>
@@ -37833,7 +37873,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.404035+00:00</t>
+          <t>2026-10-17T08:38:06.213939+00:00</t>
         </is>
       </c>
     </row>
@@ -37927,7 +37967,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.404038+00:00</t>
+          <t>2026-10-17T08:38:06.213943+00:00</t>
         </is>
       </c>
     </row>
@@ -38021,7 +38061,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.404042+00:00</t>
+          <t>2026-10-17T08:38:06.213946+00:00</t>
         </is>
       </c>
     </row>
@@ -38115,7 +38155,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.404045+00:00</t>
+          <t>2026-10-17T08:38:06.213949+00:00</t>
         </is>
       </c>
     </row>
@@ -38209,7 +38249,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.404049+00:00</t>
+          <t>2026-10-17T08:38:06.213952+00:00</t>
         </is>
       </c>
     </row>
@@ -38309,7 +38349,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T08:36:51.404053+00:00</t>
+          <t>2026-10-17T08:38:06.213955+00:00</t>
         </is>
       </c>
     </row>
@@ -38324,7 +38364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38572,12 +38612,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R02719</t>
+          <t>R13955</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R02719.main.4bf5e309b2ef3431</t>
+          <t>R13955.main.7549e1025985363e</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -38587,20 +38627,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4bf5e309b2ef343162a9588383a7ae0254118c33cdf2e96bec1a05459fae1523</t>
+          <t>7549e1025985363e89542bbc1af6eaaa1150bbd62ea43bdd03d2c7b764631f9d</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>583591</v>
+        <v>14662438</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/137944/1/Post_2016_JEnvSciHealth_A_BorjaR.pdf</t>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>R02719_2016_Performance_evaluation_of_micro_aerobic_hydrolysis_of_mixed_sludge_Optimum_aeration_and_effect_on_it.pdf</t>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -38612,35 +38652,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R02282</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R02282.main.e709439b748e7938</t>
+          <t>R07238.supplementary.0b7925ad1ed9c793</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>e709439b748e793826102646c009aa10e1e9ac30627ac301fac7dd42276a2047</t>
+          <t>0b7925ad1ed9c7939a79ba6294d17abc4b23fca77e52ec50df5463d050940d1e</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1067465</v>
+        <v>49526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://digital.csic.es/bitstream/10261/130093/1/Postprint_2016_EnviromRev_V24_P84.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>R02282_2016_Advances_in_the_biological_removal_of_sulphides_from_aqueous_phase_in_anaerobic_processes_A_review.pdf</t>
+          <t>mmc1.docx</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -38652,35 +38692,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R13905</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R13905.main.c75b5084c2545bd9</t>
+          <t>R07238.supplementary.f346f9bdcc964013</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>c75b5084c2545bd939d3b1928be41fe0072c7302f26c25ba023c4bb6fc8a6970</t>
+          <t>f346f9bdcc964013ecb7c4282d6b30f1ab334e035d98adcc653de1447fbe9a9a</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2159708</v>
+        <v>14286928</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://ddd.uab.cat/pub/artpub/2017/196242/wasbioval_a2017m7v8n5p1793.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>R13905_2017_The_Effect_of_a_Short_Term_Aerobic_Pretreatment_Step_on_the_Anaerobic_Co_digestion_of_the_Organic_Fr.pdf</t>
+          <t>mmc2.zip</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -38692,35 +38732,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R13932</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R13932.main.c15f49a3d617e1be</t>
+          <t>R07238.derived.49b84e369d4bb31b</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>c15f49a3d617e1be5e21578ebda1c2d855f8d460c1d66f446ad0d02856a40a13</t>
+          <t>49b84e369d4bb31b4ebdcd25265be3174105c3433e6fbb865f34a445775516a1</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1258157</v>
+        <v>34855493</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://hal.inrae.fr/hal-02620984/document</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>R13932_2018_Comparison_of_pre_and_inter_stage_aerobic_treatment_of_wastewater_sludge_Effects_on_biogas_productio.pdf</t>
+          <t>g a.skp</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -38732,35 +38772,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R13956</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R13956.main.fedaffcdf5be81e2</t>
+          <t>R08646.supplementary.cfda7e29b12b9784</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>fedaffcdf5be81e2070b7edb0531c332e423578228eeb8c55a6afc4ba8fe1e18</t>
+          <t>cfda7e29b12b97846343963f9f3b64e784bc79644fb1ee1ca31170be78d75327</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>421626</v>
+        <v>42279</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.banglajol.info/index.php/BJSIR/article/download/25579/17152</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>R13956_2015_Anaerobic_digestion_of_mixed_dried_fallen_leaves_by_mixing_with_cow_dung.pdf</t>
+          <t>mmc1.docx</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -38772,35 +38812,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R13955</t>
+          <t>R03161</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R13955.main.7549e1025985363e</t>
+          <t>R03161.evidence_xml.466f3a1e78e8b0f1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7549e1025985363e89542bbc1af6eaaa1150bbd62ea43bdd03d2c7b764631f9d</t>
+          <t>466f3a1e78e8b0f148b1f28f97b61f7134c61488c837c5c5a26ef7316cebc1e9</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>14662438</v>
+        <v>59018</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/fullTextXML</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
+          <t>PMC5627928_fullText.xml</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -38812,35 +38852,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R03161</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R07238.supplementary.0b7925ad1ed9c793</t>
+          <t>R03161.transport_archive.0ef4d4796c84feff</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0b7925ad1ed9c7939a79ba6294d17abc4b23fca77e52ec50df5463d050940d1e</t>
+          <t>0ef4d4796c84fefff7b8450bc56400f8c59f4bdcf074fc51404edff5e4e217f6</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>49526</v>
+        <v>726772</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/supplementaryFiles</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>mmc1.docx</t>
+          <t>PMC5627928_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -38852,35 +38892,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R04092</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R07238.supplementary.f346f9bdcc964013</t>
+          <t>R04092.evidence_xml.0fb90085e30680fa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>f346f9bdcc964013ecb7c4282d6b30f1ab334e035d98adcc653de1447fbe9a9a</t>
+          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>14286928</v>
+        <v>77995</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>mmc2.zip</t>
+          <t>PMC6288047_fullText.xml</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -38892,35 +38932,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R05839</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R07238.derived.49b84e369d4bb31b</t>
+          <t>R05839.evidence_xml.18ffd43dee955086</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>49b84e369d4bb31b4ebdcd25265be3174105c3433e6fbb865f34a445775516a1</t>
+          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>34855493</v>
+        <v>75205</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>g a.skp</t>
+          <t>PMC7566014_fullText.xml</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -38932,35 +38972,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R08877</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R08646.supplementary.cfda7e29b12b9784</t>
+          <t>R08877.evidence_xml.e8712e4198baab4c</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>cfda7e29b12b97846343963f9f3b64e784bc79644fb1ee1ca31170be78d75327</t>
+          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>42279</v>
+        <v>111864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>mmc1.docx</t>
+          <t>PMC10714394_fullText.xml</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -38972,35 +39012,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R03161</t>
+          <t>R08877</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R03161.evidence_xml.466f3a1e78e8b0f1</t>
+          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>466f3a1e78e8b0f148b1f28f97b61f7134c61488c837c5c5a26ef7316cebc1e9</t>
+          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>59018</v>
+        <v>704921</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PMC5627928_fullText.xml</t>
+          <t>PMC10714394_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -39012,35 +39052,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R03161</t>
+          <t>R09236</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R03161.transport_archive.0ef4d4796c84feff</t>
+          <t>R09236.evidence_xml.72064fe9276d8309</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0ef4d4796c84fefff7b8450bc56400f8c59f4bdcf074fc51404edff5e4e217f6</t>
+          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>726772</v>
+        <v>193052</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>PMC5627928_supplementaryFiles.zip</t>
+          <t>PMC10535533_fullText.xml</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -39052,35 +39092,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R04092</t>
+          <t>R09236</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R04092.evidence_xml.0fb90085e30680fa</t>
+          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
+          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>77995</v>
+        <v>483405</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PMC6288047_fullText.xml</t>
+          <t>PMC10535533_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -39092,12 +39132,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R05839</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R05839.evidence_xml.18ffd43dee955086</t>
+          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -39107,20 +39147,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
+          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>75205</v>
+        <v>118002</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>PMC7566014_fullText.xml</t>
+          <t>PMC10837232_fullText.xml</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -39132,35 +39172,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R08877.evidence_xml.e8712e4198baab4c</t>
+          <t>R10086.transport_archive.4d9eddf454b786ed</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
+          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>111864</v>
+        <v>641038</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PMC10714394_fullText.xml</t>
+          <t>PMC10837232_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -39172,35 +39212,35 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
+          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
+          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>704921</v>
+        <v>173586</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PMC10714394_supplementaryFiles.zip</t>
+          <t>PMC12937426_fullText.xml</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -39212,35 +39252,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R09236.evidence_xml.72064fe9276d8309</t>
+          <t>R12985.transport_archive.418d45f1ca296020</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
+          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>193052</v>
+        <v>672244</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>PMC10535533_fullText.xml</t>
+          <t>PMC12937426_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -39252,35 +39292,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R05542</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
+          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
+          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>483405</v>
+        <v>100215</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>PMC10535533_supplementaryFiles.zip</t>
+          <t>PMC9056904_fullText.xml</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -39292,12 +39332,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
+          <t>R06325.evidence_xml.645deb707d3790b5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -39307,20 +39347,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
+          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>118002</v>
+        <v>160509</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PMC10837232_fullText.xml</t>
+          <t>PMC8290346_fullText.xml</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -39332,12 +39372,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R10086.transport_archive.4d9eddf454b786ed</t>
+          <t>R06325.transport_archive.6eb4ef126661714a</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -39347,20 +39387,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
+          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>641038</v>
+        <v>1730580</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PMC10837232_supplementaryFiles.zip</t>
+          <t>PMC8290346_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -39372,12 +39412,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
+          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -39387,20 +39427,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
+          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>173586</v>
+        <v>151458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>PMC12937426_fullText.xml</t>
+          <t>PMC8044681_fullText.xml</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -39412,12 +39452,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R12985.transport_archive.418d45f1ca296020</t>
+          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -39427,20 +39467,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
+          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>672244</v>
+        <v>14596266</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>PMC12937426_supplementaryFiles.zip</t>
+          <t>PMC8044681_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -39452,12 +39492,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>R05542</t>
+          <t>R03477</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
+          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -39467,20 +39507,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
+          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100215</v>
+        <v>121650</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PMC9056904_fullText.xml</t>
+          <t>PMC5371168_fullText.xml</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -39492,12 +39532,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R06325.evidence_xml.645deb707d3790b5</t>
+          <t>R08646.evidence_xml.c7b723e8020f6582</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -39507,20 +39547,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
+          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>160509</v>
+        <v>304277</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PMC8290346_fullText.xml</t>
+          <t>PMC10559078_fullText.xml</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -39532,12 +39572,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R06325.transport_archive.6eb4ef126661714a</t>
+          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -39547,20 +39587,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
+          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1730580</v>
+        <v>1539133</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PMC8290346_supplementaryFiles.zip</t>
+          <t>PMC10559078_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -39572,12 +39612,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R09804</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
+          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -39587,20 +39627,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
+          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>151458</v>
+        <v>211630</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PMC8044681_fullText.xml</t>
+          <t>PMC11076452_fullText.xml</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -39612,35 +39652,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R11503</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
+          <t>R11503.evidence_xml.4002d57be59c215c</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
+          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>14596266</v>
+        <v>258637</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PMC8044681_supplementaryFiles.zip</t>
+          <t>PMC12561102_fullText.xml</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -39652,12 +39692,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>R03477</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
+          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -39667,20 +39707,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
+          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>121650</v>
+        <v>256247</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>PMC5371168_fullText.xml</t>
+          <t>PMC12125087_fullText.xml</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -39692,35 +39732,35 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>R08646.evidence_xml.c7b723e8020f6582</t>
+          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
+          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>304277</v>
+        <v>521862</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>PMC10559078_fullText.xml</t>
+          <t>PMC12125087_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -39732,35 +39772,35 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
+          <t>R05213.evidence_xml.17894ab410001846</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
+          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1539133</v>
+        <v>130954</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>PMC10559078_supplementaryFiles.zip</t>
+          <t>PMC6858683_fullText.xml</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -39772,35 +39812,35 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
+          <t>R05213.transport_archive.c61c88cf9fd489be</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
+          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>211630</v>
+        <v>1960371</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>PMC11076452_fullText.xml</t>
+          <t>PMC6858683_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -39812,12 +39852,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>R11503</t>
+          <t>R09585</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R11503.evidence_xml.4002d57be59c215c</t>
+          <t>R09585.evidence_xml.a3430f38fa1652de</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -39827,20 +39867,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
+          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>258637</v>
+        <v>100534</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>PMC12561102_fullText.xml</t>
+          <t>PMC10609292_fullText.xml</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -39852,238 +39892,38 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R11596</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
+          <t>R11596.main.0b2e2d98dffd5449</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
+          <t>0b2e2d98dffd544958b06cc2229d310e4b7d529bd3914c47f20d6a66789a28be</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>256247</v>
+        <v>1659399</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
+          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/7262c516-6b14-4001-a173-517d1187c8d9/content</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>PMC12125087_fullText.xml</t>
+          <t>R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>R11844</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>transport_archive</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>521862</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>PMC12125087_supplementaryFiles.zip</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>R05213</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>R05213.evidence_xml.17894ab410001846</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>evidence_xml</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>130954</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>PMC6858683_fullText.xml</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>R05213</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>R05213.transport_archive.c61c88cf9fd489be</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>transport_archive</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>1960371</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>PMC6858683_supplementaryFiles.zip</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>R09585</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>R09585.evidence_xml.a3430f38fa1652de</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>evidence_xml</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>100534</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>PMC10609292_fullText.xml</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>R11596</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>R11596.main.0b2e2d98dffd5449</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>0b2e2d98dffd544958b06cc2229d310e4b7d529bd3914c47f20d6a66789a28be</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>1659399</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/7262c516-6b14-4001-a173-517d1187c8d9/content</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
         <is>
           <t>历史已获取，当前原件未恢复</t>
         </is>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -1181,7 +1181,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>not_downloaded</t>
+          <t>historical_acquired_current_original_not_restored</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6471,14 +6471,14 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded</t>
         </is>
       </c>
       <c r="H141" t="b">
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>not_downloaded</t>
+          <t>historical_acquired_current_original_not_restored</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>not_downloaded</t>
+          <t>historical_acquired_current_original_not_restored</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>not_downloaded</t>
+          <t>historical_acquired_current_original_not_restored</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>not_downloaded</t>
+          <t>historical_acquired_current_original_not_restored</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>not_downloaded</t>
+          <t>historical_acquired_current_original_not_restored</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -12097,7 +12097,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>not_downloaded</t>
+          <t>historical_acquired_current_original_not_restored</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -14231,7 +14231,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>not_downloaded</t>
+          <t>historical_acquired_current_original_not_restored</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -20997,7 +20997,7 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>not_downloaded</t>
+          <t>historical_acquired_current_original_not_restored</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
@@ -23342,7 +23342,7 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
@@ -24118,7 +24118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X136"/>
+  <dimension ref="A1:X148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.063474+00:00</t>
+          <t>2026-10-17T08:41:26.347549+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.064520+00:00</t>
+          <t>2026-10-17T08:41:26.348430+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.064547+00:00</t>
+          <t>2026-10-17T08:41:26.348449+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.064855+00:00</t>
+          <t>2026-10-17T08:41:26.348663+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.066256+00:00</t>
+          <t>2026-10-17T08:41:26.349868+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.066787+00:00</t>
+          <t>2026-10-17T08:41:26.350359+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.072610+00:00</t>
+          <t>2026-10-17T08:41:26.355666+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.075260+00:00</t>
+          <t>2026-10-17T08:41:26.357985+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.076350+00:00</t>
+          <t>2026-10-17T08:41:26.359052+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.076686+00:00</t>
+          <t>2026-10-17T08:41:26.359415+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.077674+00:00</t>
+          <t>2026-10-17T08:41:26.360113+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.078358+00:00</t>
+          <t>2026-10-17T08:41:26.360772+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.079359+00:00</t>
+          <t>2026-10-17T08:41:26.361748+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.079614+00:00</t>
+          <t>2026-10-17T08:41:26.362194+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.080474+00:00</t>
+          <t>2026-10-17T08:41:26.363386+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.088624+00:00</t>
+          <t>2026-10-17T08:41:26.372425+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.089384+00:00</t>
+          <t>2026-10-17T08:41:26.373227+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.090592+00:00</t>
+          <t>2026-10-17T08:41:26.374560+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.093199+00:00</t>
+          <t>2026-10-17T08:41:26.377155+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.094323+00:00</t>
+          <t>2026-10-17T08:41:26.378277+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.095591+00:00</t>
+          <t>2026-10-17T08:41:26.379520+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.100766+00:00</t>
+          <t>2026-10-17T08:41:26.383696+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.103231+00:00</t>
+          <t>2026-10-17T08:41:26.385865+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.105032+00:00</t>
+          <t>2026-10-17T08:41:26.387656+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.105721+00:00</t>
+          <t>2026-10-17T08:41:26.388360+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.106094+00:00</t>
+          <t>2026-10-17T08:41:26.388717+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.108162+00:00</t>
+          <t>2026-10-17T08:41:26.390754+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.109513+00:00</t>
+          <t>2026-10-17T08:41:26.391984+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.111550+00:00</t>
+          <t>2026-10-17T08:41:26.394173+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.113562+00:00</t>
+          <t>2026-10-17T08:41:26.396198+00:00</t>
         </is>
       </c>
     </row>
@@ -27571,7 +27571,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.113585+00:00</t>
+          <t>2026-10-17T08:41:26.396223+00:00</t>
         </is>
       </c>
     </row>
@@ -27679,7 +27679,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.114164+00:00</t>
+          <t>2026-10-17T08:41:26.396798+00:00</t>
         </is>
       </c>
     </row>
@@ -27787,7 +27787,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.115802+00:00</t>
+          <t>2026-10-17T08:41:26.398655+00:00</t>
         </is>
       </c>
     </row>
@@ -27895,7 +27895,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.118694+00:00</t>
+          <t>2026-10-17T08:41:26.401497+00:00</t>
         </is>
       </c>
     </row>
@@ -28003,7 +28003,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.121076+00:00</t>
+          <t>2026-10-17T08:41:26.403628+00:00</t>
         </is>
       </c>
     </row>
@@ -28111,7 +28111,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.122437+00:00</t>
+          <t>2026-10-17T08:41:26.404796+00:00</t>
         </is>
       </c>
     </row>
@@ -28219,7 +28219,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.125376+00:00</t>
+          <t>2026-10-17T08:41:26.407614+00:00</t>
         </is>
       </c>
     </row>
@@ -28327,7 +28327,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.126131+00:00</t>
+          <t>2026-10-17T08:41:26.408280+00:00</t>
         </is>
       </c>
     </row>
@@ -28435,7 +28435,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.127706+00:00</t>
+          <t>2026-10-17T08:41:26.409854+00:00</t>
         </is>
       </c>
     </row>
@@ -28543,7 +28543,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.127959+00:00</t>
+          <t>2026-10-17T08:41:26.410087+00:00</t>
         </is>
       </c>
     </row>
@@ -28651,7 +28651,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.130052+00:00</t>
+          <t>2026-10-17T08:41:26.412406+00:00</t>
         </is>
       </c>
     </row>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.133038+00:00</t>
+          <t>2026-10-17T08:41:26.415377+00:00</t>
         </is>
       </c>
     </row>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.135048+00:00</t>
+          <t>2026-10-17T08:41:26.416672+00:00</t>
         </is>
       </c>
     </row>
@@ -28975,7 +28975,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.135888+00:00</t>
+          <t>2026-10-17T08:41:26.417239+00:00</t>
         </is>
       </c>
     </row>
@@ -29083,7 +29083,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.138727+00:00</t>
+          <t>2026-10-17T08:41:26.420095+00:00</t>
         </is>
       </c>
     </row>
@@ -29191,7 +29191,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.140001+00:00</t>
+          <t>2026-10-17T08:41:26.423131+00:00</t>
         </is>
       </c>
     </row>
@@ -29299,7 +29299,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.143888+00:00</t>
+          <t>2026-10-17T08:41:26.427088+00:00</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.145829+00:00</t>
+          <t>2026-10-17T08:41:26.428750+00:00</t>
         </is>
       </c>
     </row>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.148342+00:00</t>
+          <t>2026-10-17T08:41:26.430950+00:00</t>
         </is>
       </c>
     </row>
@@ -29623,7 +29623,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.149670+00:00</t>
+          <t>2026-10-17T08:41:26.432009+00:00</t>
         </is>
       </c>
     </row>
@@ -29731,7 +29731,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.150250+00:00</t>
+          <t>2026-10-17T08:41:26.432842+00:00</t>
         </is>
       </c>
     </row>
@@ -29839,7 +29839,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.150665+00:00</t>
+          <t>2026-10-17T08:41:26.433238+00:00</t>
         </is>
       </c>
     </row>
@@ -29947,7 +29947,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.152240+00:00</t>
+          <t>2026-10-17T08:41:26.434747+00:00</t>
         </is>
       </c>
     </row>
@@ -30055,7 +30055,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.153614+00:00</t>
+          <t>2026-10-17T08:41:26.436053+00:00</t>
         </is>
       </c>
     </row>
@@ -30163,7 +30163,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.155168+00:00</t>
+          <t>2026-10-17T08:41:26.437725+00:00</t>
         </is>
       </c>
     </row>
@@ -30271,7 +30271,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.155522+00:00</t>
+          <t>2026-10-17T08:41:26.438065+00:00</t>
         </is>
       </c>
     </row>
@@ -30379,7 +30379,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.156734+00:00</t>
+          <t>2026-10-17T08:41:26.439341+00:00</t>
         </is>
       </c>
     </row>
@@ -30487,7 +30487,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.158428+00:00</t>
+          <t>2026-10-17T08:41:26.440835+00:00</t>
         </is>
       </c>
     </row>
@@ -30595,7 +30595,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.159050+00:00</t>
+          <t>2026-10-17T08:41:26.441462+00:00</t>
         </is>
       </c>
     </row>
@@ -30703,7 +30703,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.160059+00:00</t>
+          <t>2026-10-17T08:41:26.442440+00:00</t>
         </is>
       </c>
     </row>
@@ -30811,7 +30811,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.160429+00:00</t>
+          <t>2026-10-17T08:41:26.442744+00:00</t>
         </is>
       </c>
     </row>
@@ -30919,7 +30919,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.165936+00:00</t>
+          <t>2026-10-17T08:41:26.447955+00:00</t>
         </is>
       </c>
     </row>
@@ -31019,7 +31019,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.165969+00:00</t>
+          <t>2026-10-17T08:41:26.447997+00:00</t>
         </is>
       </c>
     </row>
@@ -31127,7 +31127,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.166603+00:00</t>
+          <t>2026-10-17T08:41:26.448579+00:00</t>
         </is>
       </c>
     </row>
@@ -31235,7 +31235,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.167125+00:00</t>
+          <t>2026-10-17T08:41:26.449417+00:00</t>
         </is>
       </c>
     </row>
@@ -31343,7 +31343,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.168258+00:00</t>
+          <t>2026-10-17T08:41:26.450583+00:00</t>
         </is>
       </c>
     </row>
@@ -31451,7 +31451,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.171604+00:00</t>
+          <t>2026-10-17T08:41:26.453562+00:00</t>
         </is>
       </c>
     </row>
@@ -31559,7 +31559,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.171873+00:00</t>
+          <t>2026-10-17T08:41:26.453806+00:00</t>
         </is>
       </c>
     </row>
@@ -31667,7 +31667,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.177827+00:00</t>
+          <t>2026-10-17T08:41:26.457976+00:00</t>
         </is>
       </c>
     </row>
@@ -31775,7 +31775,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.178794+00:00</t>
+          <t>2026-10-17T08:41:26.458752+00:00</t>
         </is>
       </c>
     </row>
@@ -31883,7 +31883,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.181058+00:00</t>
+          <t>2026-10-17T08:41:26.461083+00:00</t>
         </is>
       </c>
     </row>
@@ -31991,7 +31991,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.182976+00:00</t>
+          <t>2026-10-17T08:41:26.463378+00:00</t>
         </is>
       </c>
     </row>
@@ -32091,7 +32091,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.183000+00:00</t>
+          <t>2026-10-17T08:41:26.463415+00:00</t>
         </is>
       </c>
     </row>
@@ -32199,7 +32199,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.185032+00:00</t>
+          <t>2026-10-17T08:41:26.465152+00:00</t>
         </is>
       </c>
     </row>
@@ -32307,7 +32307,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.187465+00:00</t>
+          <t>2026-10-17T08:41:26.467911+00:00</t>
         </is>
       </c>
     </row>
@@ -32415,7 +32415,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.196702+00:00</t>
+          <t>2026-10-17T08:41:26.475797+00:00</t>
         </is>
       </c>
     </row>
@@ -32523,7 +32523,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.198462+00:00</t>
+          <t>2026-10-17T08:41:26.477151+00:00</t>
         </is>
       </c>
     </row>
@@ -32631,7 +32631,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.198639+00:00</t>
+          <t>2026-10-17T08:41:26.477342+00:00</t>
         </is>
       </c>
     </row>
@@ -32731,7 +32731,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.198655+00:00</t>
+          <t>2026-10-17T08:41:26.477358+00:00</t>
         </is>
       </c>
     </row>
@@ -32839,7 +32839,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.204636+00:00</t>
+          <t>2026-10-17T08:41:26.482258+00:00</t>
         </is>
       </c>
     </row>
@@ -32943,7 +32943,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.205046+00:00</t>
+          <t>2026-10-17T08:41:26.482661+00:00</t>
         </is>
       </c>
     </row>
@@ -33047,7 +33047,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.205497+00:00</t>
+          <t>2026-10-17T08:41:26.483085+00:00</t>
         </is>
       </c>
     </row>
@@ -33151,7 +33151,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.205940+00:00</t>
+          <t>2026-10-17T08:41:26.483530+00:00</t>
         </is>
       </c>
     </row>
@@ -33255,7 +33255,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.206739+00:00</t>
+          <t>2026-10-17T08:41:26.484216+00:00</t>
         </is>
       </c>
     </row>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.208101+00:00</t>
+          <t>2026-10-17T08:41:26.485608+00:00</t>
         </is>
       </c>
     </row>
@@ -33463,7 +33463,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.208918+00:00</t>
+          <t>2026-10-17T08:41:26.486423+00:00</t>
         </is>
       </c>
     </row>
@@ -33567,7 +33567,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.209217+00:00</t>
+          <t>2026-10-17T08:41:26.486729+00:00</t>
         </is>
       </c>
     </row>
@@ -33675,13 +33675,13 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.209977+00:00</t>
+          <t>2026-10-17T08:41:26.487747+00:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -33775,7 +33775,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.210001+00:00</t>
+          <t>2026-10-17T08:41:26.487778+00:00</t>
         </is>
       </c>
     </row>
@@ -33883,7 +33883,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.210062+00:00</t>
+          <t>2026-10-17T08:41:26.487838+00:00</t>
         </is>
       </c>
     </row>
@@ -33991,7 +33991,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.210327+00:00</t>
+          <t>2026-10-17T08:41:26.488055+00:00</t>
         </is>
       </c>
     </row>
@@ -34099,7 +34099,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.210543+00:00</t>
+          <t>2026-10-17T08:41:26.488170+00:00</t>
         </is>
       </c>
     </row>
@@ -34211,7 +34211,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.210684+00:00</t>
+          <t>2026-10-17T08:41:26.488285+00:00</t>
         </is>
       </c>
     </row>
@@ -34319,7 +34319,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.211058+00:00</t>
+          <t>2026-10-17T08:41:26.488690+00:00</t>
         </is>
       </c>
     </row>
@@ -34427,7 +34427,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.211246+00:00</t>
+          <t>2026-10-17T08:41:26.488874+00:00</t>
         </is>
       </c>
     </row>
@@ -34539,7 +34539,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.211380+00:00</t>
+          <t>2026-10-17T08:41:26.488922+00:00</t>
         </is>
       </c>
     </row>
@@ -34651,7 +34651,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.211458+00:00</t>
+          <t>2026-10-17T08:41:26.488979+00:00</t>
         </is>
       </c>
     </row>
@@ -34763,7 +34763,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.211607+00:00</t>
+          <t>2026-10-17T08:41:26.489115+00:00</t>
         </is>
       </c>
     </row>
@@ -34875,7 +34875,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.211653+00:00</t>
+          <t>2026-10-17T08:41:26.489159+00:00</t>
         </is>
       </c>
     </row>
@@ -34983,7 +34983,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.212108+00:00</t>
+          <t>2026-10-17T08:41:26.489642+00:00</t>
         </is>
       </c>
     </row>
@@ -35091,7 +35091,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.212161+00:00</t>
+          <t>2026-10-17T08:41:26.489690+00:00</t>
         </is>
       </c>
     </row>
@@ -35191,7 +35191,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.212171+00:00</t>
+          <t>2026-10-17T08:41:26.489700+00:00</t>
         </is>
       </c>
     </row>
@@ -35227,13 +35227,21 @@
           <t>papers/R07238/supplementary/f346f9bdcc96_mmc2.zip</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>original_files/supplementary/R07238/mmc2.zip</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-supplements/R07238/official/mmc2.zip</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/supplementary/R07238/mmc2.zip</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>zip</t>
@@ -35249,12 +35257,12 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -35291,7 +35299,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.212176+00:00</t>
+          <t>2026-10-17T08:41:26.499634+00:00</t>
         </is>
       </c>
     </row>
@@ -35395,7 +35403,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.212180+00:00</t>
+          <t>2026-10-17T08:41:26.499697+00:00</t>
         </is>
       </c>
     </row>
@@ -35495,7 +35503,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.212184+00:00</t>
+          <t>2026-10-17T08:41:26.499702+00:00</t>
         </is>
       </c>
     </row>
@@ -35603,7 +35611,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.212422+00:00</t>
+          <t>2026-10-17T08:41:26.499961+00:00</t>
         </is>
       </c>
     </row>
@@ -35711,7 +35719,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213837+00:00</t>
+          <t>2026-10-17T08:41:26.501055+00:00</t>
         </is>
       </c>
     </row>
@@ -35805,7 +35813,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213865+00:00</t>
+          <t>2026-10-17T08:41:26.501080+00:00</t>
         </is>
       </c>
     </row>
@@ -35899,7 +35907,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213870+00:00</t>
+          <t>2026-10-17T08:41:26.501084+00:00</t>
         </is>
       </c>
     </row>
@@ -35993,7 +36001,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213873+00:00</t>
+          <t>2026-10-17T08:41:26.501087+00:00</t>
         </is>
       </c>
     </row>
@@ -36087,7 +36095,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213876+00:00</t>
+          <t>2026-10-17T08:41:26.501090+00:00</t>
         </is>
       </c>
     </row>
@@ -36181,7 +36189,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213880+00:00</t>
+          <t>2026-10-17T08:41:26.501092+00:00</t>
         </is>
       </c>
     </row>
@@ -36275,7 +36283,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213884+00:00</t>
+          <t>2026-10-17T08:41:26.501095+00:00</t>
         </is>
       </c>
     </row>
@@ -36369,7 +36377,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213887+00:00</t>
+          <t>2026-10-17T08:41:26.501097+00:00</t>
         </is>
       </c>
     </row>
@@ -36463,7 +36471,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213891+00:00</t>
+          <t>2026-10-17T08:41:26.501100+00:00</t>
         </is>
       </c>
     </row>
@@ -36557,7 +36565,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213895+00:00</t>
+          <t>2026-10-17T08:41:26.501103+00:00</t>
         </is>
       </c>
     </row>
@@ -36651,7 +36659,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213898+00:00</t>
+          <t>2026-10-17T08:41:26.501106+00:00</t>
         </is>
       </c>
     </row>
@@ -36745,7 +36753,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213901+00:00</t>
+          <t>2026-10-17T08:41:26.501108+00:00</t>
         </is>
       </c>
     </row>
@@ -36839,7 +36847,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213905+00:00</t>
+          <t>2026-10-17T08:41:26.501111+00:00</t>
         </is>
       </c>
     </row>
@@ -36933,7 +36941,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213908+00:00</t>
+          <t>2026-10-17T08:41:26.501113+00:00</t>
         </is>
       </c>
     </row>
@@ -37027,7 +37035,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213911+00:00</t>
+          <t>2026-10-17T08:41:26.501117+00:00</t>
         </is>
       </c>
     </row>
@@ -37121,7 +37129,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213914+00:00</t>
+          <t>2026-10-17T08:41:26.501120+00:00</t>
         </is>
       </c>
     </row>
@@ -37215,7 +37223,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213918+00:00</t>
+          <t>2026-10-17T08:41:26.501123+00:00</t>
         </is>
       </c>
     </row>
@@ -37309,7 +37317,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213921+00:00</t>
+          <t>2026-10-17T08:41:26.501132+00:00</t>
         </is>
       </c>
     </row>
@@ -37403,7 +37411,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213924+00:00</t>
+          <t>2026-10-17T08:41:26.501137+00:00</t>
         </is>
       </c>
     </row>
@@ -37497,7 +37505,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213927+00:00</t>
+          <t>2026-10-17T08:41:26.501140+00:00</t>
         </is>
       </c>
     </row>
@@ -37591,7 +37599,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213929+00:00</t>
+          <t>2026-10-17T08:41:26.501142+00:00</t>
         </is>
       </c>
     </row>
@@ -37685,7 +37693,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213933+00:00</t>
+          <t>2026-10-17T08:41:26.501145+00:00</t>
         </is>
       </c>
     </row>
@@ -37779,7 +37787,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213936+00:00</t>
+          <t>2026-10-17T08:41:26.501148+00:00</t>
         </is>
       </c>
     </row>
@@ -37873,7 +37881,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213939+00:00</t>
+          <t>2026-10-17T08:41:26.501151+00:00</t>
         </is>
       </c>
     </row>
@@ -37967,7 +37975,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213943+00:00</t>
+          <t>2026-10-17T08:41:26.501154+00:00</t>
         </is>
       </c>
     </row>
@@ -38061,7 +38069,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213946+00:00</t>
+          <t>2026-10-17T08:41:26.501157+00:00</t>
         </is>
       </c>
     </row>
@@ -38155,7 +38163,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213949+00:00</t>
+          <t>2026-10-17T08:41:26.501159+00:00</t>
         </is>
       </c>
     </row>
@@ -38249,7 +38257,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213952+00:00</t>
+          <t>2026-10-17T08:41:26.501162+00:00</t>
         </is>
       </c>
     </row>
@@ -38285,13 +38293,21 @@
           <t>papers/R11596/main/0b2e2d98dffd_R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
+        </is>
+      </c>
       <c r="I136" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/candidates/R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr"/>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
+        </is>
+      </c>
       <c r="K136" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -38307,12 +38323,12 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -38349,7 +38365,1095 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T08:38:06.213955+00:00</t>
+          <t>2026-10-17T08:41:26.502323+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="b">
+        <v>1</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>R13955</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>R13955.main.82d3dd4c7af3e63a</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E137" t="b">
+        <v>0</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>14662119</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>82d3dd4c7af3e63a708ab83da8c0b4011affe749fea236491c93f91ec4cd59c9</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>present_sha_verified</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>local_acquired_pending_remote_readback</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>University-published doctoral thesis / publisher PDF (repository cover explicitly states Version of Record)</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>Private authorized research backup; source license not inferred</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr"/>
+      <c r="U137" t="inlineStr"/>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr"/>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>2026-10-17T08:41:26.512014+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="b">
+        <v>1</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>R02274</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>R02274.main.4c7da8384f1f6e3d</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E138" t="b">
+        <v>0</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>R02274_2016_ANAEROBIC_DIGESTION_OF_WASTEWATER_WITH_HIGH_SULFATE_CONCENTRATION_USING.pdf</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>/workspace/library-files/ad-oxygen-fulltexts/R02274_2016_ANAEROBIC_DIGESTION_OF_WASTEWATER_WITH_HIGH_SULFATE_CONCENTRATION_USING.pdf</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>471480</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>4c7da8384f1f6e3d8bd2681eab23bdb95e3057009cf4c7ec7aacc7cdb9eaf43d</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>historical_acquired_current_original_not_restored</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>historical_only_original_missing</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>出版版本（原页出版信息）</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>Historical record; source rights not reassessed</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>4c7da8384f1f6e3d8bd2681eab23bdb95e3057009cf4c7ec7aacc7cdb9eaf43d</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr"/>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>historical_only_current_original_missing</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr"/>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>2026-10-17T08:41:26.512105+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="b">
+        <v>0</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>R10086</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>R10086.main.84777bfb7a2cd42f</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E139" t="b">
+        <v>0</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>R10086_2024_Effect_of_micro-aeration_on_syntrophic_and_methanogenic_activity_in.pdf</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>/workspace/library-files/ad-oxygen-fulltexts/R10086_2024_Effect_of_micro-aeration_on_syntrophic_and_methanogenic_activity_in.pdf</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>984310</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>84777bfb7a2cd42f9696e060fc79d5de3e72d5ad8fa1e222934a7fcdf97dd365</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>historical_acquired_current_original_not_restored</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>historical_only_original_missing</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>出版版本（原页出版信息）</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>Historical record; source rights not reassessed</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>84777bfb7a2cd42f9696e060fc79d5de3e72d5ad8fa1e222934a7fcdf97dd365</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr"/>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>historical_only_current_original_missing</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr"/>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>2026-10-17T08:41:26.512113+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="b">
+        <v>1</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>R03477</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>R03477.main.79583f4a64fb2fbb</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E140" t="b">
+        <v>0</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>R03477_2017_Pretreatment_methods_of_lignocellulosic_biomass_for_anaerobic_digestion.pdf</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>/workspace/library-files/ad-oxygen-fulltexts/R03477_2017_Pretreatment_methods_of_lignocellulosic_biomass_for_anaerobic_digestion.pdf</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>1714874</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>79583f4a64fb2fbb4a1f4f471fe6001b159213acb1f3bbd19d6dc0be5c714fa5</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>historical_acquired_current_original_not_restored</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>historical_only_original_missing</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/content/pdf/10.1186/s13568-017-0375-4.pdf</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>出版版本（原页出版信息）</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>Historical record; source rights not reassessed</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>79583f4a64fb2fbb4a1f4f471fe6001b159213acb1f3bbd19d6dc0be5c714fa5</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr"/>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>historical_only_current_original_missing</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr"/>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>2026-10-17T08:41:26.512116+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="b">
+        <v>1</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>R09804</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>R09804.main.b3cc83d613ad3c36</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E141" t="b">
+        <v>0</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>/workspace/library-files/ad-oxygen-fulltexts/R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>5135812</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>b3cc83d613ad3c36f93b78eace000ebc5a603966523ee71c2e6a0bd85a8ede3e</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>historical_acquired_current_original_not_restored</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>historical_only_original_missing</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/content/pdf/10.1186/s40643-024-00756-6.pdf</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>出版版本（原页出版信息）</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>Historical record; source rights not reassessed</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>b3cc83d613ad3c36f93b78eace000ebc5a603966523ee71c2e6a0bd85a8ede3e</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr"/>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>historical_only_current_original_missing</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr"/>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>2026-10-17T08:41:26.512119+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="b">
+        <v>1</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>R11844</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>R11844.main.c41816bf825167dc</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E142" t="b">
+        <v>0</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>/workspace/library-files/ad-oxygen-fulltexts/R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>1333380</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>c41816bf825167dcb78ff5eb81c8d0dab0d8d8110cd2a23a04cd1109acb34919</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>historical_acquired_current_original_not_restored</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>historical_only_original_missing</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/content/pdf/10.1007/s00253-025-13519-w.pdf</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>出版版本（原页出版信息）</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>Historical record; source rights not reassessed</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>c41816bf825167dcb78ff5eb81c8d0dab0d8d8110cd2a23a04cd1109acb34919</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr"/>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>historical_only_current_original_missing</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr"/>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>2026-10-17T08:41:26.512122+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="b">
+        <v>1</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>R03155</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>R03155.main.2875ce0c137df622</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E143" t="b">
+        <v>0</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>/workspace/library-files/ad-oxygen-fulltexts/R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>5745828</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>historical_acquired_current_original_not_restored</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>historical_only_original_missing</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>https://dspace.lib.ntua.gr/xmlui/bitstream/handle/123456789/44237/Msc.%20Thesis_Aristotle_Vasileiou%20THE.pdf?sequence=1&amp;isAllowed=y</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>学位/机构存档原稿</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Historical record; source rights not reassessed</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr"/>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>historical_only_current_original_missing</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr"/>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>2026-10-17T08:41:26.512126+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="b">
+        <v>1</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>R05213</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>R05213.main.bcab84a15ce93062</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E144" t="b">
+        <v>0</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>/workspace/library-files/ad-oxygen-fulltexts/R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>1022660</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>historical_acquired_current_original_not_restored</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>historical_only_original_missing</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>出版版本（原页出版信息）</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>Historical record; source rights not reassessed</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr"/>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>historical_only_current_original_missing</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr"/>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>2026-10-17T08:41:26.512129+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="b">
+        <v>1</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>R06036</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>R06036.main.0bdc7b19fdb70091</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E145" t="b">
+        <v>0</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>/workspace/library-files/ad-oxygen-fulltexts/R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>927168</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>historical_acquired_current_original_not_restored</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>historical_only_original_missing</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>出版版本（原页出版信息）</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>Historical record; source rights not reassessed</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr"/>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>historical_only_current_original_missing</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr"/>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>2026-10-17T08:41:26.512132+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="b">
+        <v>1</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>R09240</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>R09240.main.da8dbeb874b19b59</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E146" t="b">
+        <v>0</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>/workspace/library-files/ad-oxygen-fulltexts/R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>1315227</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>historical_acquired_current_original_not_restored</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>historical_only_original_missing</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>出版版本（原页出版信息）</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>Historical record; source rights not reassessed</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr"/>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>historical_only_current_original_missing</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr"/>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>2026-10-17T08:41:26.512135+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="b">
+        <v>1</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>R13899</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>R13899.main.19143e56fa77ce99</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E147" t="b">
+        <v>0</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>/workspace/library-files/ad-oxygen-fulltexts/R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>479092</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>historical_acquired_current_original_not_restored</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>historical_only_original_missing</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>出版版本（原页出版信息）</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>Historical record; source rights not reassessed</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr"/>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>historical_only_current_original_missing</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr"/>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>2026-10-17T08:41:26.512149+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="b">
+        <v>0</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>R13955</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>R13955.main.6714f79deccd703d</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E148" t="b">
+        <v>0</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>/workspace/library-files/ad-oxygen-fulltexts/R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>14662119</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>historical_acquired_current_original_not_restored</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>historical_only_original_missing</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>学位/机构存档原稿</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>Historical record; source rights not reassessed</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr"/>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>historical_only_current_original_missing</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr"/>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>2026-10-17T08:41:26.512152+00:00</t>
         </is>
       </c>
     </row>
@@ -38364,7 +39468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38697,21 +39801,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R07238.supplementary.f346f9bdcc964013</t>
+          <t>R07238.derived.49b84e369d4bb31b</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>f346f9bdcc964013ecb7c4282d6b30f1ab334e035d98adcc653de1447fbe9a9a</t>
+          <t>49b84e369d4bb31b4ebdcd25265be3174105c3433e6fbb865f34a445775516a1</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>14286928</v>
+        <v>34855493</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -38720,7 +39824,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>mmc2.zip</t>
+          <t>g a.skp</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -38732,35 +39836,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R07238.derived.49b84e369d4bb31b</t>
+          <t>R08646.supplementary.cfda7e29b12b9784</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>49b84e369d4bb31b4ebdcd25265be3174105c3433e6fbb865f34a445775516a1</t>
+          <t>cfda7e29b12b97846343963f9f3b64e784bc79644fb1ee1ca31170be78d75327</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>34855493</v>
+        <v>42279</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>g a.skp</t>
+          <t>mmc1.docx</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -38772,35 +39876,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R03161</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R08646.supplementary.cfda7e29b12b9784</t>
+          <t>R03161.evidence_xml.466f3a1e78e8b0f1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>cfda7e29b12b97846343963f9f3b64e784bc79644fb1ee1ca31170be78d75327</t>
+          <t>466f3a1e78e8b0f148b1f28f97b61f7134c61488c837c5c5a26ef7316cebc1e9</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>42279</v>
+        <v>59018</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/fullTextXML</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>mmc1.docx</t>
+          <t>PMC5627928_fullText.xml</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -38817,30 +39921,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R03161.evidence_xml.466f3a1e78e8b0f1</t>
+          <t>R03161.transport_archive.0ef4d4796c84feff</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>466f3a1e78e8b0f148b1f28f97b61f7134c61488c837c5c5a26ef7316cebc1e9</t>
+          <t>0ef4d4796c84fefff7b8450bc56400f8c59f4bdcf074fc51404edff5e4e217f6</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>59018</v>
+        <v>726772</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/supplementaryFiles</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>PMC5627928_fullText.xml</t>
+          <t>PMC5627928_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -38852,35 +39956,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R03161</t>
+          <t>R04092</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R03161.transport_archive.0ef4d4796c84feff</t>
+          <t>R04092.evidence_xml.0fb90085e30680fa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0ef4d4796c84fefff7b8450bc56400f8c59f4bdcf074fc51404edff5e4e217f6</t>
+          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>726772</v>
+        <v>77995</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>PMC5627928_supplementaryFiles.zip</t>
+          <t>PMC6288047_fullText.xml</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -38892,12 +39996,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R04092</t>
+          <t>R05839</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R04092.evidence_xml.0fb90085e30680fa</t>
+          <t>R05839.evidence_xml.18ffd43dee955086</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -38907,20 +40011,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
+          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>77995</v>
+        <v>75205</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>PMC6288047_fullText.xml</t>
+          <t>PMC7566014_fullText.xml</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -38932,12 +40036,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R05839</t>
+          <t>R08877</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R05839.evidence_xml.18ffd43dee955086</t>
+          <t>R08877.evidence_xml.e8712e4198baab4c</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -38947,20 +40051,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
+          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>75205</v>
+        <v>111864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>PMC7566014_fullText.xml</t>
+          <t>PMC10714394_fullText.xml</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -38977,30 +40081,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R08877.evidence_xml.e8712e4198baab4c</t>
+          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
+          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>111864</v>
+        <v>704921</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>PMC10714394_fullText.xml</t>
+          <t>PMC10714394_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -39012,35 +40116,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R09236</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
+          <t>R09236.evidence_xml.72064fe9276d8309</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
+          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>704921</v>
+        <v>193052</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PMC10714394_supplementaryFiles.zip</t>
+          <t>PMC10535533_fullText.xml</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -39057,30 +40161,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R09236.evidence_xml.72064fe9276d8309</t>
+          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
+          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>193052</v>
+        <v>483405</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>PMC10535533_fullText.xml</t>
+          <t>PMC10535533_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -39092,35 +40196,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
+          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
+          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>483405</v>
+        <v>118002</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PMC10535533_supplementaryFiles.zip</t>
+          <t>PMC10837232_fullText.xml</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -39137,30 +40241,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
+          <t>R10086.transport_archive.4d9eddf454b786ed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
+          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>118002</v>
+        <v>641038</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>PMC10837232_fullText.xml</t>
+          <t>PMC10837232_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -39172,35 +40276,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R10086.transport_archive.4d9eddf454b786ed</t>
+          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
+          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>641038</v>
+        <v>173586</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PMC10837232_supplementaryFiles.zip</t>
+          <t>PMC12937426_fullText.xml</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -39217,30 +40321,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
+          <t>R12985.transport_archive.418d45f1ca296020</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
+          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>173586</v>
+        <v>672244</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PMC12937426_fullText.xml</t>
+          <t>PMC12937426_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -39252,35 +40356,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R05542</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R12985.transport_archive.418d45f1ca296020</t>
+          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
+          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>672244</v>
+        <v>100215</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>PMC12937426_supplementaryFiles.zip</t>
+          <t>PMC9056904_fullText.xml</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -39292,12 +40396,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R05542</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
+          <t>R06325.evidence_xml.645deb707d3790b5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -39307,20 +40411,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
+          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100215</v>
+        <v>160509</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>PMC9056904_fullText.xml</t>
+          <t>PMC8290346_fullText.xml</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -39337,30 +40441,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R06325.evidence_xml.645deb707d3790b5</t>
+          <t>R06325.transport_archive.6eb4ef126661714a</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
+          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>160509</v>
+        <v>1730580</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PMC8290346_fullText.xml</t>
+          <t>PMC8290346_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -39372,35 +40476,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R06325.transport_archive.6eb4ef126661714a</t>
+          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
+          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1730580</v>
+        <v>151458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PMC8290346_supplementaryFiles.zip</t>
+          <t>PMC8044681_fullText.xml</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -39417,30 +40521,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
+          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
+          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>151458</v>
+        <v>14596266</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>PMC8044681_fullText.xml</t>
+          <t>PMC8044681_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -39452,35 +40556,35 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R03477</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
+          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
+          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>14596266</v>
+        <v>121650</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>PMC8044681_supplementaryFiles.zip</t>
+          <t>PMC5371168_fullText.xml</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -39492,12 +40596,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>R03477</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
+          <t>R08646.evidence_xml.c7b723e8020f6582</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -39507,20 +40611,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
+          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>121650</v>
+        <v>304277</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PMC5371168_fullText.xml</t>
+          <t>PMC10559078_fullText.xml</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -39537,30 +40641,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R08646.evidence_xml.c7b723e8020f6582</t>
+          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
+          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>304277</v>
+        <v>1539133</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PMC10559078_fullText.xml</t>
+          <t>PMC10559078_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -39572,35 +40676,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R09804</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
+          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
+          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1539133</v>
+        <v>211630</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PMC10559078_supplementaryFiles.zip</t>
+          <t>PMC11076452_fullText.xml</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -39612,12 +40716,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R11503</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
+          <t>R11503.evidence_xml.4002d57be59c215c</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -39627,20 +40731,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
+          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>211630</v>
+        <v>258637</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PMC11076452_fullText.xml</t>
+          <t>PMC12561102_fullText.xml</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -39652,12 +40756,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R11503</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R11503.evidence_xml.4002d57be59c215c</t>
+          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -39667,20 +40771,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
+          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>258637</v>
+        <v>256247</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PMC12561102_fullText.xml</t>
+          <t>PMC12125087_fullText.xml</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -39697,30 +40801,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
+          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
+          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>256247</v>
+        <v>521862</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>PMC12125087_fullText.xml</t>
+          <t>PMC12125087_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -39732,35 +40836,35 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
+          <t>R05213.evidence_xml.17894ab410001846</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
+          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>521862</v>
+        <v>130954</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>PMC12125087_supplementaryFiles.zip</t>
+          <t>PMC6858683_fullText.xml</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -39777,30 +40881,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R05213.evidence_xml.17894ab410001846</t>
+          <t>R05213.transport_archive.c61c88cf9fd489be</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
+          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>130954</v>
+        <v>1960371</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>PMC6858683_fullText.xml</t>
+          <t>PMC6858683_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -39812,35 +40916,35 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>R05213</t>
+          <t>R09585</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>R05213.transport_archive.c61c88cf9fd489be</t>
+          <t>R09585.evidence_xml.a3430f38fa1652de</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
+          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1960371</v>
+        <v>100534</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>PMC6858683_supplementaryFiles.zip</t>
+          <t>PMC10609292_fullText.xml</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -39852,35 +40956,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>R09585</t>
+          <t>R02274</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R09585.evidence_xml.a3430f38fa1652de</t>
+          <t>R02274.main.4c7da8384f1f6e3d</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
+          <t>4c7da8384f1f6e3d8bd2681eab23bdb95e3057009cf4c7ec7aacc7cdb9eaf43d</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100534</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
-        </is>
-      </c>
+        <v>471480</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>PMC10609292_fullText.xml</t>
+          <t>R02274_2016_ANAEROBIC_DIGESTION_OF_WASTEWATER_WITH_HIGH_SULFATE_CONCENTRATION_USING.pdf</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -39892,12 +40992,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>R11596</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>R11596.main.0b2e2d98dffd5449</t>
+          <t>R10086.main.84777bfb7a2cd42f</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -39907,23 +41007,371 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0b2e2d98dffd544958b06cc2229d310e4b7d529bd3914c47f20d6a66789a28be</t>
+          <t>84777bfb7a2cd42f9696e060fc79d5de3e72d5ad8fa1e222934a7fcdf97dd365</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1659399</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>https://repositorium.uminho.pt/server/api/core/bitstreams/7262c516-6b14-4001-a173-517d1187c8d9/content</t>
-        </is>
-      </c>
+        <v>984310</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>R11596_2025_Facultative_anaerobic_bacteria_enable_syntrophic_fatty_acids_degradation_under_0b2e2d98dffd.pdf</t>
+          <t>R10086_2024_Effect_of_micro-aeration_on_syntrophic_and_methanogenic_activity_in.pdf</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
+        <is>
+          <t>历史已获取，当前原件未恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>R03477</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>R03477.main.79583f4a64fb2fbb</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>79583f4a64fb2fbb4a1f4f471fe6001b159213acb1f3bbd19d6dc0be5c714fa5</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1714874</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/content/pdf/10.1186/s13568-017-0375-4.pdf</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>R03477_2017_Pretreatment_methods_of_lignocellulosic_biomass_for_anaerobic_digestion.pdf</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>历史已获取，当前原件未恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>R09804</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>R09804.main.b3cc83d613ad3c36</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>b3cc83d613ad3c36f93b78eace000ebc5a603966523ee71c2e6a0bd85a8ede3e</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5135812</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/content/pdf/10.1186/s40643-024-00756-6.pdf</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>历史已获取，当前原件未恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>R11844</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>R11844.main.c41816bf825167dc</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>c41816bf825167dcb78ff5eb81c8d0dab0d8d8110cd2a23a04cd1109acb34919</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1333380</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/content/pdf/10.1007/s00253-025-13519-w.pdf</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>历史已获取，当前原件未恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>R03155</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>R03155.main.2875ce0c137df622</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>5745828</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://dspace.lib.ntua.gr/xmlui/bitstream/handle/123456789/44237/Msc.%20Thesis_Aristotle_Vasileiou%20THE.pdf?sequence=1&amp;isAllowed=y</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>历史已获取，当前原件未恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>R05213</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>R05213.main.bcab84a15ce93062</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1022660</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>历史已获取，当前原件未恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>R06036</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>R06036.main.0bdc7b19fdb70091</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>927168</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>历史已获取，当前原件未恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>R09240</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>R09240.main.da8dbeb874b19b59</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1315227</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>历史已获取，当前原件未恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>R13899</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>R13899.main.19143e56fa77ce99</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>479092</v>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>历史已获取，当前原件未恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>R13955</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>R13955.main.6714f79deccd703d</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>14662119</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>历史已获取，当前原件未恢复</t>
         </is>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -5649,7 +5649,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -7288,14 +7288,14 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded</t>
         </is>
       </c>
       <c r="H160" t="b">
         <v>0</v>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -20051,7 +20051,7 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.347549+00:00</t>
+          <t>2026-10-17T08:44:41.730556+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.348430+00:00</t>
+          <t>2026-10-17T08:44:41.731588+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.348449+00:00</t>
+          <t>2026-10-17T08:44:41.731617+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.348663+00:00</t>
+          <t>2026-10-17T08:44:41.731853+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.349868+00:00</t>
+          <t>2026-10-17T08:44:41.732933+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.350359+00:00</t>
+          <t>2026-10-17T08:44:41.733428+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.355666+00:00</t>
+          <t>2026-10-17T08:44:41.739170+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.357985+00:00</t>
+          <t>2026-10-17T08:44:41.741468+00:00</t>
         </is>
       </c>
     </row>
@@ -25166,7 +25166,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.359052+00:00</t>
+          <t>2026-10-17T08:44:41.742431+00:00</t>
         </is>
       </c>
     </row>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.359415+00:00</t>
+          <t>2026-10-17T08:44:41.742754+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.360113+00:00</t>
+          <t>2026-10-17T08:44:41.743465+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.360772+00:00</t>
+          <t>2026-10-17T08:44:41.744100+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.361748+00:00</t>
+          <t>2026-10-17T08:44:41.745125+00:00</t>
         </is>
       </c>
     </row>
@@ -25706,7 +25706,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.362194+00:00</t>
+          <t>2026-10-17T08:44:41.745439+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.363386+00:00</t>
+          <t>2026-10-17T08:44:41.746420+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.372425+00:00</t>
+          <t>2026-10-17T08:44:41.754576+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.373227+00:00</t>
+          <t>2026-10-17T08:44:41.755257+00:00</t>
         </is>
       </c>
     </row>
@@ -26138,7 +26138,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.374560+00:00</t>
+          <t>2026-10-17T08:44:41.756539+00:00</t>
         </is>
       </c>
     </row>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.377155+00:00</t>
+          <t>2026-10-17T08:44:41.759178+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.378277+00:00</t>
+          <t>2026-10-17T08:44:41.760543+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.379520+00:00</t>
+          <t>2026-10-17T08:44:41.762572+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.383696+00:00</t>
+          <t>2026-10-17T08:44:41.767197+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.385865+00:00</t>
+          <t>2026-10-17T08:44:41.769776+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.387656+00:00</t>
+          <t>2026-10-17T08:44:41.771654+00:00</t>
         </is>
       </c>
     </row>
@@ -26894,7 +26894,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.388360+00:00</t>
+          <t>2026-10-17T08:44:41.772319+00:00</t>
         </is>
       </c>
     </row>
@@ -27002,7 +27002,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.388717+00:00</t>
+          <t>2026-10-17T08:44:41.772667+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.390754+00:00</t>
+          <t>2026-10-17T08:44:41.775189+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.391984+00:00</t>
+          <t>2026-10-17T08:44:41.776759+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.394173+00:00</t>
+          <t>2026-10-17T08:44:41.778936+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.396198+00:00</t>
+          <t>2026-10-17T08:44:41.781210+00:00</t>
         </is>
       </c>
     </row>
@@ -27507,13 +27507,21 @@
           <t>papers/R01212/main/ef235fcb491d_R01212_2014_Effects_of_Pre-aeration_on_the_Anaerobic_Digestion_of_Sewage.pdf</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R01212_2014_Effects_of_Pre-aeration_on_the_Anaerobic_Digestion_of_Sewage.pdf</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R01212_2014_Effects_of_Pre-aeration_on_the_Anaerobic_Digestion_of_Sewage.pdf</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R01212_2014_Effects_of_Pre-aeration_on_the_Anaerobic_Digestion_of_Sewage.pdf</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -27529,12 +27537,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -27571,7 +27579,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.396223+00:00</t>
+          <t>2026-10-17T08:44:41.781800+00:00</t>
         </is>
       </c>
     </row>
@@ -27642,7 +27650,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -27679,7 +27687,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.396798+00:00</t>
+          <t>2026-10-17T08:44:41.782463+00:00</t>
         </is>
       </c>
     </row>
@@ -27787,7 +27795,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.398655+00:00</t>
+          <t>2026-10-17T08:44:41.784054+00:00</t>
         </is>
       </c>
     </row>
@@ -27895,7 +27903,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.401497+00:00</t>
+          <t>2026-10-17T08:44:41.786804+00:00</t>
         </is>
       </c>
     </row>
@@ -27966,7 +27974,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -28003,7 +28011,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.403628+00:00</t>
+          <t>2026-10-17T08:44:41.788848+00:00</t>
         </is>
       </c>
     </row>
@@ -28111,7 +28119,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.404796+00:00</t>
+          <t>2026-10-17T08:44:41.790018+00:00</t>
         </is>
       </c>
     </row>
@@ -28182,7 +28190,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -28219,7 +28227,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.407614+00:00</t>
+          <t>2026-10-17T08:44:41.793045+00:00</t>
         </is>
       </c>
     </row>
@@ -28327,7 +28335,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.408280+00:00</t>
+          <t>2026-10-17T08:44:41.793818+00:00</t>
         </is>
       </c>
     </row>
@@ -28435,7 +28443,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.409854+00:00</t>
+          <t>2026-10-17T08:44:41.795558+00:00</t>
         </is>
       </c>
     </row>
@@ -28543,7 +28551,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.410087+00:00</t>
+          <t>2026-10-17T08:44:41.795830+00:00</t>
         </is>
       </c>
     </row>
@@ -28614,7 +28622,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -28651,7 +28659,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.412406+00:00</t>
+          <t>2026-10-17T08:44:41.797966+00:00</t>
         </is>
       </c>
     </row>
@@ -28759,7 +28767,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.415377+00:00</t>
+          <t>2026-10-17T08:44:41.800878+00:00</t>
         </is>
       </c>
     </row>
@@ -28830,7 +28838,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -28867,7 +28875,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.416672+00:00</t>
+          <t>2026-10-17T08:44:41.802283+00:00</t>
         </is>
       </c>
     </row>
@@ -28975,7 +28983,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.417239+00:00</t>
+          <t>2026-10-17T08:44:41.802839+00:00</t>
         </is>
       </c>
     </row>
@@ -29046,7 +29054,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -29083,7 +29091,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.420095+00:00</t>
+          <t>2026-10-17T08:44:41.805384+00:00</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29162,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -29191,7 +29199,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.423131+00:00</t>
+          <t>2026-10-17T08:44:41.806656+00:00</t>
         </is>
       </c>
     </row>
@@ -29262,7 +29270,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -29299,7 +29307,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.427088+00:00</t>
+          <t>2026-10-17T08:44:41.810585+00:00</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29415,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.428750+00:00</t>
+          <t>2026-10-17T08:44:41.812338+00:00</t>
         </is>
       </c>
     </row>
@@ -29478,7 +29486,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -29515,7 +29523,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.430950+00:00</t>
+          <t>2026-10-17T08:44:41.814149+00:00</t>
         </is>
       </c>
     </row>
@@ -29586,7 +29594,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -29623,7 +29631,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.432009+00:00</t>
+          <t>2026-10-17T08:44:41.815199+00:00</t>
         </is>
       </c>
     </row>
@@ -29731,7 +29739,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.432842+00:00</t>
+          <t>2026-10-17T08:44:41.815661+00:00</t>
         </is>
       </c>
     </row>
@@ -29802,7 +29810,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -29839,7 +29847,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.433238+00:00</t>
+          <t>2026-10-17T08:44:41.816019+00:00</t>
         </is>
       </c>
     </row>
@@ -29947,7 +29955,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.434747+00:00</t>
+          <t>2026-10-17T08:44:41.817610+00:00</t>
         </is>
       </c>
     </row>
@@ -30055,7 +30063,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.436053+00:00</t>
+          <t>2026-10-17T08:44:41.818934+00:00</t>
         </is>
       </c>
     </row>
@@ -30126,7 +30134,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -30163,7 +30171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.437725+00:00</t>
+          <t>2026-10-17T08:44:41.820807+00:00</t>
         </is>
       </c>
     </row>
@@ -30234,7 +30242,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -30271,7 +30279,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.438065+00:00</t>
+          <t>2026-10-17T08:44:41.821149+00:00</t>
         </is>
       </c>
     </row>
@@ -30342,7 +30350,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -30379,7 +30387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.439341+00:00</t>
+          <t>2026-10-17T08:44:41.822617+00:00</t>
         </is>
       </c>
     </row>
@@ -30450,7 +30458,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -30487,7 +30495,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.440835+00:00</t>
+          <t>2026-10-17T08:44:41.824045+00:00</t>
         </is>
       </c>
     </row>
@@ -30595,7 +30603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.441462+00:00</t>
+          <t>2026-10-17T08:44:41.824696+00:00</t>
         </is>
       </c>
     </row>
@@ -30666,7 +30674,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -30703,7 +30711,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.442440+00:00</t>
+          <t>2026-10-17T08:44:41.825735+00:00</t>
         </is>
       </c>
     </row>
@@ -30774,7 +30782,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -30811,7 +30819,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.442744+00:00</t>
+          <t>2026-10-17T08:44:41.826064+00:00</t>
         </is>
       </c>
     </row>
@@ -30882,7 +30890,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -30919,7 +30927,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.447955+00:00</t>
+          <t>2026-10-17T08:44:41.831767+00:00</t>
         </is>
       </c>
     </row>
@@ -30955,13 +30963,21 @@
           <t>papers/R13877/main/04a76adc76fa_R13877_2018_Microbial_community_response_and_SDS-PAGE_reveal_possible_mechanism_of.pdf</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13877_2018_Microbial_community_response_and_SDS-PAGE_reveal_possible_mechanism_of.pdf</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R13877_2018_Microbial_community_response_and_SDS-PAGE_reveal_possible_mechanism_of.pdf</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13877_2018_Microbial_community_response_and_SDS-PAGE_reveal_possible_mechanism_of.pdf</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -30977,12 +30993,12 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -31019,7 +31035,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.447997+00:00</t>
+          <t>2026-10-17T08:44:41.832175+00:00</t>
         </is>
       </c>
     </row>
@@ -31090,7 +31106,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -31127,7 +31143,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.448579+00:00</t>
+          <t>2026-10-17T08:44:41.832815+00:00</t>
         </is>
       </c>
     </row>
@@ -31235,7 +31251,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.449417+00:00</t>
+          <t>2026-10-17T08:44:41.833250+00:00</t>
         </is>
       </c>
     </row>
@@ -31343,7 +31359,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.450583+00:00</t>
+          <t>2026-10-17T08:44:41.834560+00:00</t>
         </is>
       </c>
     </row>
@@ -31451,7 +31467,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.453562+00:00</t>
+          <t>2026-10-17T08:44:41.837720+00:00</t>
         </is>
       </c>
     </row>
@@ -31522,7 +31538,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -31559,7 +31575,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.453806+00:00</t>
+          <t>2026-10-17T08:44:41.837978+00:00</t>
         </is>
       </c>
     </row>
@@ -31667,7 +31683,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.457976+00:00</t>
+          <t>2026-10-17T08:44:41.842979+00:00</t>
         </is>
       </c>
     </row>
@@ -31738,7 +31754,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -31775,7 +31791,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.458752+00:00</t>
+          <t>2026-10-17T08:44:41.843795+00:00</t>
         </is>
       </c>
     </row>
@@ -31883,7 +31899,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.461083+00:00</t>
+          <t>2026-10-17T08:44:41.846083+00:00</t>
         </is>
       </c>
     </row>
@@ -31991,7 +32007,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.463378+00:00</t>
+          <t>2026-10-17T08:44:41.848507+00:00</t>
         </is>
       </c>
     </row>
@@ -32027,13 +32043,21 @@
           <t>papers/R13931/main/6e898a403eda_R13931_2020_Biogas_recovery_from_fresh_landfill_leachates_by_using_a.pdf</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13931_2020_Biogas_recovery_from_fresh_landfill_leachates_by_using_a.pdf</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-current-run/fulltexts/R13931_2020_Biogas_recovery_from_fresh_landfill_leachates_by_using_a.pdf</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13931_2020_Biogas_recovery_from_fresh_landfill_leachates_by_using_a.pdf</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -32049,12 +32073,12 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -32091,7 +32115,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.463415+00:00</t>
+          <t>2026-10-17T08:44:41.849473+00:00</t>
         </is>
       </c>
     </row>
@@ -32162,7 +32186,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -32199,7 +32223,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.465152+00:00</t>
+          <t>2026-10-17T08:44:41.850892+00:00</t>
         </is>
       </c>
     </row>
@@ -32270,7 +32294,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -32307,7 +32331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.467911+00:00</t>
+          <t>2026-10-17T08:44:41.853570+00:00</t>
         </is>
       </c>
     </row>
@@ -32378,7 +32402,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -32415,7 +32439,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.475797+00:00</t>
+          <t>2026-10-17T08:44:41.866001+00:00</t>
         </is>
       </c>
     </row>
@@ -32523,7 +32547,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.477151+00:00</t>
+          <t>2026-10-17T08:44:41.867376+00:00</t>
         </is>
       </c>
     </row>
@@ -32594,7 +32618,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -32631,7 +32655,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.477342+00:00</t>
+          <t>2026-10-17T08:44:41.867528+00:00</t>
         </is>
       </c>
     </row>
@@ -32731,7 +32755,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.477358+00:00</t>
+          <t>2026-10-17T08:44:41.867542+00:00</t>
         </is>
       </c>
     </row>
@@ -32802,7 +32826,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -32839,7 +32863,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.482258+00:00</t>
+          <t>2026-10-17T08:44:41.873568+00:00</t>
         </is>
       </c>
     </row>
@@ -32910,7 +32934,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -32943,7 +32967,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.482661+00:00</t>
+          <t>2026-10-17T08:44:41.873974+00:00</t>
         </is>
       </c>
     </row>
@@ -33014,7 +33038,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -33047,7 +33071,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.483085+00:00</t>
+          <t>2026-10-17T08:44:41.874457+00:00</t>
         </is>
       </c>
     </row>
@@ -33118,7 +33142,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -33151,7 +33175,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.483530+00:00</t>
+          <t>2026-10-17T08:44:41.874923+00:00</t>
         </is>
       </c>
     </row>
@@ -33222,7 +33246,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -33255,7 +33279,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.484216+00:00</t>
+          <t>2026-10-17T08:44:41.875736+00:00</t>
         </is>
       </c>
     </row>
@@ -33326,7 +33350,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -33359,7 +33383,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.485608+00:00</t>
+          <t>2026-10-17T08:44:41.877105+00:00</t>
         </is>
       </c>
     </row>
@@ -33430,7 +33454,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -33463,7 +33487,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.486423+00:00</t>
+          <t>2026-10-17T08:44:41.877936+00:00</t>
         </is>
       </c>
     </row>
@@ -33534,7 +33558,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -33567,7 +33591,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.486729+00:00</t>
+          <t>2026-10-17T08:44:41.878253+00:00</t>
         </is>
       </c>
     </row>
@@ -33675,7 +33699,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.487747+00:00</t>
+          <t>2026-10-17T08:44:41.878900+00:00</t>
         </is>
       </c>
     </row>
@@ -33775,7 +33799,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.487778+00:00</t>
+          <t>2026-10-17T08:44:41.878915+00:00</t>
         </is>
       </c>
     </row>
@@ -33883,7 +33907,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.487838+00:00</t>
+          <t>2026-10-17T08:44:41.878965+00:00</t>
         </is>
       </c>
     </row>
@@ -33991,7 +34015,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.488055+00:00</t>
+          <t>2026-10-17T08:44:41.879436+00:00</t>
         </is>
       </c>
     </row>
@@ -34099,7 +34123,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.488170+00:00</t>
+          <t>2026-10-17T08:44:41.879579+00:00</t>
         </is>
       </c>
     </row>
@@ -34211,7 +34235,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.488285+00:00</t>
+          <t>2026-10-17T08:44:41.879699+00:00</t>
         </is>
       </c>
     </row>
@@ -34319,7 +34343,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.488690+00:00</t>
+          <t>2026-10-17T08:44:41.880065+00:00</t>
         </is>
       </c>
     </row>
@@ -34427,7 +34451,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.488874+00:00</t>
+          <t>2026-10-17T08:44:41.880252+00:00</t>
         </is>
       </c>
     </row>
@@ -34539,7 +34563,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.488922+00:00</t>
+          <t>2026-10-17T08:44:41.880330+00:00</t>
         </is>
       </c>
     </row>
@@ -34651,7 +34675,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.488979+00:00</t>
+          <t>2026-10-17T08:44:41.880398+00:00</t>
         </is>
       </c>
     </row>
@@ -34763,7 +34787,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.489115+00:00</t>
+          <t>2026-10-17T08:44:41.880536+00:00</t>
         </is>
       </c>
     </row>
@@ -34875,7 +34899,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.489159+00:00</t>
+          <t>2026-10-17T08:44:41.880582+00:00</t>
         </is>
       </c>
     </row>
@@ -34983,7 +35007,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.489642+00:00</t>
+          <t>2026-10-17T08:44:41.881024+00:00</t>
         </is>
       </c>
     </row>
@@ -35091,7 +35115,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.489690+00:00</t>
+          <t>2026-10-17T08:44:41.881070+00:00</t>
         </is>
       </c>
     </row>
@@ -35191,7 +35215,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.489700+00:00</t>
+          <t>2026-10-17T08:44:41.881080+00:00</t>
         </is>
       </c>
     </row>
@@ -35262,7 +35286,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -35299,7 +35323,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.499634+00:00</t>
+          <t>2026-10-17T08:44:41.892338+00:00</t>
         </is>
       </c>
     </row>
@@ -35403,7 +35427,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.499697+00:00</t>
+          <t>2026-10-17T08:44:41.892420+00:00</t>
         </is>
       </c>
     </row>
@@ -35439,13 +35463,21 @@
           <t>papers/R08646/supplementary/cfda7e29b12b_mmc1.docx</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>original_files/supplementary/R08646/mmc1.docx</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-supplements/R08646/official/mmc1.docx</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/supplementary/R08646/mmc1.docx</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
           <t>docx</t>
@@ -35461,12 +35493,12 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -35503,7 +35535,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.499702+00:00</t>
+          <t>2026-10-17T08:44:41.892546+00:00</t>
         </is>
       </c>
     </row>
@@ -35611,7 +35643,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.499961+00:00</t>
+          <t>2026-10-17T08:44:41.892789+00:00</t>
         </is>
       </c>
     </row>
@@ -35719,7 +35751,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501055+00:00</t>
+          <t>2026-10-17T08:44:41.893903+00:00</t>
         </is>
       </c>
     </row>
@@ -35753,13 +35785,21 @@
           <t>papers/R03161/evidence/466f3a1e78e8_PMC5627928_fullText.xml</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R03161/PMC5627928_fullText.xml</t>
+        </is>
+      </c>
       <c r="I109" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-supplements/R03161/evidence/PMC5627928_fullText.xml</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/source_evidence/R03161/PMC5627928_fullText.xml</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>xml</t>
@@ -35775,12 +35815,12 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -35813,7 +35853,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501080+00:00</t>
+          <t>2026-10-17T08:44:41.894006+00:00</t>
         </is>
       </c>
     </row>
@@ -35907,7 +35947,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501084+00:00</t>
+          <t>2026-10-17T08:44:41.894019+00:00</t>
         </is>
       </c>
     </row>
@@ -36001,7 +36041,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501087+00:00</t>
+          <t>2026-10-17T08:44:41.894022+00:00</t>
         </is>
       </c>
     </row>
@@ -36095,7 +36135,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501090+00:00</t>
+          <t>2026-10-17T08:44:41.894025+00:00</t>
         </is>
       </c>
     </row>
@@ -36189,7 +36229,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501092+00:00</t>
+          <t>2026-10-17T08:44:41.894028+00:00</t>
         </is>
       </c>
     </row>
@@ -36283,7 +36323,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501095+00:00</t>
+          <t>2026-10-17T08:44:41.894031+00:00</t>
         </is>
       </c>
     </row>
@@ -36377,7 +36417,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501097+00:00</t>
+          <t>2026-10-17T08:44:41.894034+00:00</t>
         </is>
       </c>
     </row>
@@ -36471,7 +36511,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501100+00:00</t>
+          <t>2026-10-17T08:44:41.894043+00:00</t>
         </is>
       </c>
     </row>
@@ -36565,7 +36605,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501103+00:00</t>
+          <t>2026-10-17T08:44:41.894046+00:00</t>
         </is>
       </c>
     </row>
@@ -36659,7 +36699,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501106+00:00</t>
+          <t>2026-10-17T08:44:41.894049+00:00</t>
         </is>
       </c>
     </row>
@@ -36753,7 +36793,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501108+00:00</t>
+          <t>2026-10-17T08:44:41.894052+00:00</t>
         </is>
       </c>
     </row>
@@ -36847,7 +36887,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501111+00:00</t>
+          <t>2026-10-17T08:44:41.894055+00:00</t>
         </is>
       </c>
     </row>
@@ -36941,7 +36981,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501113+00:00</t>
+          <t>2026-10-17T08:44:41.894058+00:00</t>
         </is>
       </c>
     </row>
@@ -37035,7 +37075,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501117+00:00</t>
+          <t>2026-10-17T08:44:41.894060+00:00</t>
         </is>
       </c>
     </row>
@@ -37129,7 +37169,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501120+00:00</t>
+          <t>2026-10-17T08:44:41.894063+00:00</t>
         </is>
       </c>
     </row>
@@ -37223,7 +37263,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501123+00:00</t>
+          <t>2026-10-17T08:44:41.894066+00:00</t>
         </is>
       </c>
     </row>
@@ -37317,7 +37357,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501132+00:00</t>
+          <t>2026-10-17T08:44:41.894069+00:00</t>
         </is>
       </c>
     </row>
@@ -37411,7 +37451,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501137+00:00</t>
+          <t>2026-10-17T08:44:41.894071+00:00</t>
         </is>
       </c>
     </row>
@@ -37505,7 +37545,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501140+00:00</t>
+          <t>2026-10-17T08:44:41.894074+00:00</t>
         </is>
       </c>
     </row>
@@ -37599,7 +37639,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501142+00:00</t>
+          <t>2026-10-17T08:44:41.894077+00:00</t>
         </is>
       </c>
     </row>
@@ -37693,7 +37733,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501145+00:00</t>
+          <t>2026-10-17T08:44:41.894080+00:00</t>
         </is>
       </c>
     </row>
@@ -37787,7 +37827,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501148+00:00</t>
+          <t>2026-10-17T08:44:41.894084+00:00</t>
         </is>
       </c>
     </row>
@@ -37881,7 +37921,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501151+00:00</t>
+          <t>2026-10-17T08:44:41.894086+00:00</t>
         </is>
       </c>
     </row>
@@ -37975,7 +38015,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501154+00:00</t>
+          <t>2026-10-17T08:44:41.894089+00:00</t>
         </is>
       </c>
     </row>
@@ -38069,7 +38109,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501157+00:00</t>
+          <t>2026-10-17T08:44:41.894091+00:00</t>
         </is>
       </c>
     </row>
@@ -38163,7 +38203,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501159+00:00</t>
+          <t>2026-10-17T08:44:41.894094+00:00</t>
         </is>
       </c>
     </row>
@@ -38257,7 +38297,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.501162+00:00</t>
+          <t>2026-10-17T08:44:41.894096+00:00</t>
         </is>
       </c>
     </row>
@@ -38328,7 +38368,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -38365,7 +38405,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.502323+00:00</t>
+          <t>2026-10-17T08:44:41.895445+00:00</t>
         </is>
       </c>
     </row>
@@ -38428,7 +38468,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -38457,7 +38497,7 @@
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.512014+00:00</t>
+          <t>2026-10-17T08:44:41.906626+00:00</t>
         </is>
       </c>
     </row>
@@ -38545,7 +38585,7 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.512105+00:00</t>
+          <t>2026-10-17T08:44:41.906695+00:00</t>
         </is>
       </c>
     </row>
@@ -38633,7 +38673,7 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.512113+00:00</t>
+          <t>2026-10-17T08:44:41.906701+00:00</t>
         </is>
       </c>
     </row>
@@ -38725,7 +38765,7 @@
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.512116+00:00</t>
+          <t>2026-10-17T08:44:41.906705+00:00</t>
         </is>
       </c>
     </row>
@@ -38817,7 +38857,7 @@
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.512119+00:00</t>
+          <t>2026-10-17T08:44:41.906708+00:00</t>
         </is>
       </c>
     </row>
@@ -38909,7 +38949,7 @@
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.512122+00:00</t>
+          <t>2026-10-17T08:44:41.906710+00:00</t>
         </is>
       </c>
     </row>
@@ -39001,7 +39041,7 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.512126+00:00</t>
+          <t>2026-10-17T08:44:41.906713+00:00</t>
         </is>
       </c>
     </row>
@@ -39089,7 +39129,7 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.512129+00:00</t>
+          <t>2026-10-17T08:44:41.906715+00:00</t>
         </is>
       </c>
     </row>
@@ -39181,7 +39221,7 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.512132+00:00</t>
+          <t>2026-10-17T08:44:41.906718+00:00</t>
         </is>
       </c>
     </row>
@@ -39273,7 +39313,7 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.512135+00:00</t>
+          <t>2026-10-17T08:44:41.906721+00:00</t>
         </is>
       </c>
     </row>
@@ -39361,7 +39401,7 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.512149+00:00</t>
+          <t>2026-10-17T08:44:41.906724+00:00</t>
         </is>
       </c>
     </row>
@@ -39453,7 +39493,7 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-10-17T08:41:26.512152+00:00</t>
+          <t>2026-10-17T08:44:41.906726+00:00</t>
         </is>
       </c>
     </row>
@@ -39468,7 +39508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39556,12 +39596,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R01212</t>
+          <t>R13972</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R01212.main.ef235fcb491d4749</t>
+          <t>R13972.main.ff4ee9377a7e227c</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -39571,20 +39611,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ef235fcb491d474970838cf59cfd36efaf9a37c84ddd225c06788beb77d497e3</t>
+          <t>ff4ee9377a7e227c48a5bc64d301bfc1a989ee0e709c322eb90f254819d7b391</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>773976</v>
+        <v>1192569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.eeer.org/upload/eer-19-1-59-9.pdf</t>
+          <t>https://www.osti.gov/servlets/purl/2386939</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>R01212_2014_Effects_of_Pre-aeration_on_the_Anaerobic_Digestion_of_Sewage.pdf</t>
+          <t>R13972_2022_Enhancing_methane_production_of_anaerobic_digested_sewage_sludge_by.pdf</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -39596,12 +39636,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R13877</t>
+          <t>R13955</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R13877.main.04a76adc76fa9472</t>
+          <t>R13955.main.7549e1025985363e</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -39611,20 +39651,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>04a76adc76fa947250861c95c93759c590dd3e02d7f80dc23ce0abedccb74510</t>
+          <t>7549e1025985363e89542bbc1af6eaaa1150bbd62ea43bdd03d2c7b764631f9d</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>522402</v>
+        <v>14662438</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://escholarship.org/content/qt5572k7rw/qt5572k7rw.pdf</t>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>R13877_2018_Microbial_community_response_and_SDS-PAGE_reveal_possible_mechanism_of.pdf</t>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -39636,35 +39676,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R13931</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R13931.main.6e898a403edac7b3</t>
+          <t>R07238.supplementary.0b7925ad1ed9c793</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>supplementary</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6e898a403edac7b3ae15ad88cf75788898cd84ea377b2572f7bab40d9c126f8c</t>
+          <t>0b7925ad1ed9c7939a79ba6294d17abc4b23fca77e52ec50df5463d050940d1e</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1324593</v>
+        <v>49526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.eeer.org/upload/eer-2020-470.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>R13931_2020_Biogas_recovery_from_fresh_landfill_leachates_by_using_a.pdf</t>
+          <t>mmc1.docx</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -39676,35 +39716,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R13972</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R13972.main.ff4ee9377a7e227c</t>
+          <t>R07238.derived.49b84e369d4bb31b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ff4ee9377a7e227c48a5bc64d301bfc1a989ee0e709c322eb90f254819d7b391</t>
+          <t>49b84e369d4bb31b4ebdcd25265be3174105c3433e6fbb865f34a445775516a1</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1192569</v>
+        <v>34855493</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.osti.gov/servlets/purl/2386939</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>R13972_2022_Enhancing_methane_production_of_anaerobic_digested_sewage_sludge_by.pdf</t>
+          <t>g a.skp</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -39716,35 +39756,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R13955</t>
+          <t>R03161</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R13955.main.7549e1025985363e</t>
+          <t>R03161.transport_archive.0ef4d4796c84feff</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7549e1025985363e89542bbc1af6eaaa1150bbd62ea43bdd03d2c7b764631f9d</t>
+          <t>0ef4d4796c84fefff7b8450bc56400f8c59f4bdcf074fc51404edff5e4e217f6</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14662438</v>
+        <v>726772</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/supplementaryFiles</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion_7549e1025985.pdf</t>
+          <t>PMC5627928_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -39756,35 +39796,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R04092</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R07238.supplementary.0b7925ad1ed9c793</t>
+          <t>R04092.evidence_xml.0fb90085e30680fa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0b7925ad1ed9c7939a79ba6294d17abc4b23fca77e52ec50df5463d050940d1e</t>
+          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>49526</v>
+        <v>77995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>mmc1.docx</t>
+          <t>PMC6288047_fullText.xml</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -39796,35 +39836,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R05839</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R07238.derived.49b84e369d4bb31b</t>
+          <t>R05839.evidence_xml.18ffd43dee955086</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>49b84e369d4bb31b4ebdcd25265be3174105c3433e6fbb865f34a445775516a1</t>
+          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>34855493</v>
+        <v>75205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>g a.skp</t>
+          <t>PMC7566014_fullText.xml</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -39836,35 +39876,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R08877</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R08646.supplementary.cfda7e29b12b9784</t>
+          <t>R08877.evidence_xml.e8712e4198baab4c</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>supplementary</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>cfda7e29b12b97846343963f9f3b64e784bc79644fb1ee1ca31170be78d75327</t>
+          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>42279</v>
+        <v>111864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>mmc1.docx</t>
+          <t>PMC10714394_fullText.xml</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -39876,35 +39916,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R03161</t>
+          <t>R08877</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R03161.evidence_xml.466f3a1e78e8b0f1</t>
+          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>466f3a1e78e8b0f148b1f28f97b61f7134c61488c837c5c5a26ef7316cebc1e9</t>
+          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>59018</v>
+        <v>704921</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PMC5627928_fullText.xml</t>
+          <t>PMC10714394_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -39916,35 +39956,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R03161</t>
+          <t>R09236</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R03161.transport_archive.0ef4d4796c84feff</t>
+          <t>R09236.evidence_xml.72064fe9276d8309</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0ef4d4796c84fefff7b8450bc56400f8c59f4bdcf074fc51404edff5e4e217f6</t>
+          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>726772</v>
+        <v>193052</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5627928/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>PMC5627928_supplementaryFiles.zip</t>
+          <t>PMC10535533_fullText.xml</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -39956,35 +39996,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R04092</t>
+          <t>R09236</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R04092.evidence_xml.0fb90085e30680fa</t>
+          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
+          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>77995</v>
+        <v>483405</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>PMC6288047_fullText.xml</t>
+          <t>PMC10535533_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -39996,12 +40036,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R05839</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R05839.evidence_xml.18ffd43dee955086</t>
+          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -40011,20 +40051,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
+          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>75205</v>
+        <v>118002</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>PMC7566014_fullText.xml</t>
+          <t>PMC10837232_fullText.xml</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -40036,35 +40076,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R08877.evidence_xml.e8712e4198baab4c</t>
+          <t>R10086.transport_archive.4d9eddf454b786ed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
+          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>111864</v>
+        <v>641038</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>PMC10714394_fullText.xml</t>
+          <t>PMC10837232_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -40076,35 +40116,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
+          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
+          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>704921</v>
+        <v>173586</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>PMC10714394_supplementaryFiles.zip</t>
+          <t>PMC12937426_fullText.xml</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -40116,35 +40156,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R09236.evidence_xml.72064fe9276d8309</t>
+          <t>R12985.transport_archive.418d45f1ca296020</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
+          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>193052</v>
+        <v>672244</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PMC10535533_fullText.xml</t>
+          <t>PMC12937426_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -40156,35 +40196,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R05542</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
+          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
+          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>483405</v>
+        <v>100215</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>PMC10535533_supplementaryFiles.zip</t>
+          <t>PMC9056904_fullText.xml</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -40196,12 +40236,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
+          <t>R06325.evidence_xml.645deb707d3790b5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -40211,20 +40251,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
+          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>118002</v>
+        <v>160509</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PMC10837232_fullText.xml</t>
+          <t>PMC8290346_fullText.xml</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -40236,12 +40276,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R10086.transport_archive.4d9eddf454b786ed</t>
+          <t>R06325.transport_archive.6eb4ef126661714a</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -40251,20 +40291,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
+          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>641038</v>
+        <v>1730580</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>PMC10837232_supplementaryFiles.zip</t>
+          <t>PMC8290346_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -40276,12 +40316,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
+          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -40291,20 +40331,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
+          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>173586</v>
+        <v>151458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PMC12937426_fullText.xml</t>
+          <t>PMC8044681_fullText.xml</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -40316,12 +40356,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R12985.transport_archive.418d45f1ca296020</t>
+          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -40331,20 +40371,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
+          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>672244</v>
+        <v>14596266</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PMC12937426_supplementaryFiles.zip</t>
+          <t>PMC8044681_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -40356,12 +40396,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R05542</t>
+          <t>R03477</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
+          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -40371,20 +40411,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
+          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100215</v>
+        <v>121650</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>PMC9056904_fullText.xml</t>
+          <t>PMC5371168_fullText.xml</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -40396,12 +40436,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R06325.evidence_xml.645deb707d3790b5</t>
+          <t>R08646.evidence_xml.c7b723e8020f6582</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -40411,20 +40451,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
+          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>160509</v>
+        <v>304277</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>PMC8290346_fullText.xml</t>
+          <t>PMC10559078_fullText.xml</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -40436,12 +40476,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R06325.transport_archive.6eb4ef126661714a</t>
+          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -40451,20 +40491,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
+          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1730580</v>
+        <v>1539133</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PMC8290346_supplementaryFiles.zip</t>
+          <t>PMC10559078_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -40476,12 +40516,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R09804</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
+          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -40491,20 +40531,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
+          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>151458</v>
+        <v>211630</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PMC8044681_fullText.xml</t>
+          <t>PMC11076452_fullText.xml</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -40516,35 +40556,35 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R11503</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
+          <t>R11503.evidence_xml.4002d57be59c215c</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
+          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>14596266</v>
+        <v>258637</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>PMC8044681_supplementaryFiles.zip</t>
+          <t>PMC12561102_fullText.xml</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -40556,12 +40596,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>R03477</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
+          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -40571,20 +40611,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
+          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>121650</v>
+        <v>256247</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>PMC5371168_fullText.xml</t>
+          <t>PMC12125087_fullText.xml</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -40596,35 +40636,35 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>R08646.evidence_xml.c7b723e8020f6582</t>
+          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
+          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>304277</v>
+        <v>521862</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PMC10559078_fullText.xml</t>
+          <t>PMC12125087_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -40636,35 +40676,35 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
+          <t>R05213.evidence_xml.17894ab410001846</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
+          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1539133</v>
+        <v>130954</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PMC10559078_supplementaryFiles.zip</t>
+          <t>PMC6858683_fullText.xml</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -40676,35 +40716,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
+          <t>R05213.transport_archive.c61c88cf9fd489be</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
+          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>211630</v>
+        <v>1960371</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PMC11076452_fullText.xml</t>
+          <t>PMC6858683_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -40716,12 +40756,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>R11503</t>
+          <t>R09585</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R11503.evidence_xml.4002d57be59c215c</t>
+          <t>R09585.evidence_xml.a3430f38fa1652de</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -40731,20 +40771,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
+          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>258637</v>
+        <v>100534</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PMC12561102_fullText.xml</t>
+          <t>PMC10609292_fullText.xml</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -40756,35 +40796,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R02274</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
+          <t>R02274.main.4c7da8384f1f6e3d</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
+          <t>4c7da8384f1f6e3d8bd2681eab23bdb95e3057009cf4c7ec7aacc7cdb9eaf43d</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>256247</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
-        </is>
-      </c>
+        <v>471480</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PMC12125087_fullText.xml</t>
+          <t>R02274_2016_ANAEROBIC_DIGESTION_OF_WASTEWATER_WITH_HIGH_SULFATE_CONCENTRATION_USING.pdf</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -40796,35 +40832,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
+          <t>R10086.main.84777bfb7a2cd42f</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
+          <t>84777bfb7a2cd42f9696e060fc79d5de3e72d5ad8fa1e222934a7fcdf97dd365</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>521862</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
-        </is>
-      </c>
+        <v>984310</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>PMC12125087_supplementaryFiles.zip</t>
+          <t>R10086_2024_Effect_of_micro-aeration_on_syntrophic_and_methanogenic_activity_in.pdf</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -40836,35 +40868,35 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>R05213</t>
+          <t>R03477</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>R05213.evidence_xml.17894ab410001846</t>
+          <t>R03477.main.79583f4a64fb2fbb</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
+          <t>79583f4a64fb2fbb4a1f4f471fe6001b159213acb1f3bbd19d6dc0be5c714fa5</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>130954</v>
+        <v>1714874</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
+          <t>https://link.springer.com/content/pdf/10.1186/s13568-017-0375-4.pdf</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>PMC6858683_fullText.xml</t>
+          <t>R03477_2017_Pretreatment_methods_of_lignocellulosic_biomass_for_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -40876,35 +40908,35 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>R05213</t>
+          <t>R09804</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R05213.transport_archive.c61c88cf9fd489be</t>
+          <t>R09804.main.b3cc83d613ad3c36</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
+          <t>b3cc83d613ad3c36f93b78eace000ebc5a603966523ee71c2e6a0bd85a8ede3e</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1960371</v>
+        <v>5135812</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
+          <t>https://link.springer.com/content/pdf/10.1186/s40643-024-00756-6.pdf</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>PMC6858683_supplementaryFiles.zip</t>
+          <t>R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -40916,35 +40948,35 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>R09585</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>R09585.evidence_xml.a3430f38fa1652de</t>
+          <t>R11844.main.c41816bf825167dc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
+          <t>c41816bf825167dcb78ff5eb81c8d0dab0d8d8110cd2a23a04cd1109acb34919</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100534</v>
+        <v>1333380</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
+          <t>https://link.springer.com/content/pdf/10.1007/s00253-025-13519-w.pdf</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>PMC10609292_fullText.xml</t>
+          <t>R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -40956,12 +40988,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>R02274</t>
+          <t>R03155</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R02274.main.4c7da8384f1f6e3d</t>
+          <t>R03155.main.2875ce0c137df622</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -40971,16 +41003,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4c7da8384f1f6e3d8bd2681eab23bdb95e3057009cf4c7ec7aacc7cdb9eaf43d</t>
+          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>471480</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
+        <v>5745828</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://dspace.lib.ntua.gr/xmlui/bitstream/handle/123456789/44237/Msc.%20Thesis_Aristotle_Vasileiou%20THE.pdf?sequence=1&amp;isAllowed=y</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>R02274_2016_ANAEROBIC_DIGESTION_OF_WASTEWATER_WITH_HIGH_SULFATE_CONCENTRATION_USING.pdf</t>
+          <t>R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -40992,12 +41028,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>R10086.main.84777bfb7a2cd42f</t>
+          <t>R05213.main.bcab84a15ce93062</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -41007,16 +41043,16 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>84777bfb7a2cd42f9696e060fc79d5de3e72d5ad8fa1e222934a7fcdf97dd365</t>
+          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>984310</v>
+        <v>1022660</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>R10086_2024_Effect_of_micro-aeration_on_syntrophic_and_methanogenic_activity_in.pdf</t>
+          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -41028,12 +41064,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>R03477</t>
+          <t>R06036</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>R03477.main.79583f4a64fb2fbb</t>
+          <t>R06036.main.0bdc7b19fdb70091</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -41043,20 +41079,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>79583f4a64fb2fbb4a1f4f471fe6001b159213acb1f3bbd19d6dc0be5c714fa5</t>
+          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1714874</v>
+        <v>927168</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1186/s13568-017-0375-4.pdf</t>
+          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>R03477_2017_Pretreatment_methods_of_lignocellulosic_biomass_for_anaerobic_digestion.pdf</t>
+          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -41068,12 +41104,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R09240</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>R09804.main.b3cc83d613ad3c36</t>
+          <t>R09240.main.da8dbeb874b19b59</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -41083,20 +41119,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>b3cc83d613ad3c36f93b78eace000ebc5a603966523ee71c2e6a0bd85a8ede3e</t>
+          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5135812</v>
+        <v>1315227</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1186/s40643-024-00756-6.pdf</t>
+          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
+          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -41108,12 +41144,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R13899</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>R11844.main.c41816bf825167dc</t>
+          <t>R13899.main.19143e56fa77ce99</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -41123,20 +41159,16 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>c41816bf825167dcb78ff5eb81c8d0dab0d8d8110cd2a23a04cd1109acb34919</t>
+          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1333380</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>https://link.springer.com/content/pdf/10.1007/s00253-025-13519-w.pdf</t>
-        </is>
-      </c>
+        <v>479092</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
+          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -41148,12 +41180,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>R03155</t>
+          <t>R13955</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>R03155.main.2875ce0c137df622</t>
+          <t>R13955.main.6714f79deccd703d</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -41163,215 +41195,23 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
+          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5745828</v>
+        <v>14662119</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://dspace.lib.ntua.gr/xmlui/bitstream/handle/123456789/44237/Msc.%20Thesis_Aristotle_Vasileiou%20THE.pdf?sequence=1&amp;isAllowed=y</t>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>R05213</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>R05213.main.bcab84a15ce93062</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>1022660</v>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>R06036</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>R06036.main.0bdc7b19fdb70091</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>927168</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>R09240</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>R09240.main.da8dbeb874b19b59</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>1315227</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>R13899</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>R13899.main.19143e56fa77ce99</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>479092</v>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>R13955</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>R13955.main.6714f79deccd703d</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>14662119</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
         <is>
           <t>历史已获取，当前原件未恢复</t>
         </is>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.730556+00:00</t>
+          <t>2026-10-17T08:45:50.702022+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.731588+00:00</t>
+          <t>2026-10-17T08:45:50.702957+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.731617+00:00</t>
+          <t>2026-10-17T08:45:50.702978+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.731853+00:00</t>
+          <t>2026-10-17T08:45:50.703200+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.732933+00:00</t>
+          <t>2026-10-17T08:45:50.704421+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.733428+00:00</t>
+          <t>2026-10-17T08:45:50.704894+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.739170+00:00</t>
+          <t>2026-10-17T08:45:50.711996+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.741468+00:00</t>
+          <t>2026-10-17T08:45:50.714498+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.742431+00:00</t>
+          <t>2026-10-17T08:45:50.715434+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.742754+00:00</t>
+          <t>2026-10-17T08:45:50.715772+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.743465+00:00</t>
+          <t>2026-10-17T08:45:50.716538+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.744100+00:00</t>
+          <t>2026-10-17T08:45:50.717210+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.745125+00:00</t>
+          <t>2026-10-17T08:45:50.718195+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.745439+00:00</t>
+          <t>2026-10-17T08:45:50.718455+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.746420+00:00</t>
+          <t>2026-10-17T08:45:50.719320+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.754576+00:00</t>
+          <t>2026-10-17T08:45:50.726800+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.755257+00:00</t>
+          <t>2026-10-17T08:45:50.727501+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.756539+00:00</t>
+          <t>2026-10-17T08:45:50.728737+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.759178+00:00</t>
+          <t>2026-10-17T08:45:50.731286+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.760543+00:00</t>
+          <t>2026-10-17T08:45:50.732488+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.762572+00:00</t>
+          <t>2026-10-17T08:45:50.733708+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.767197+00:00</t>
+          <t>2026-10-17T08:45:50.738763+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.769776+00:00</t>
+          <t>2026-10-17T08:45:50.741376+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.771654+00:00</t>
+          <t>2026-10-17T08:45:50.743244+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.772319+00:00</t>
+          <t>2026-10-17T08:45:50.743931+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.772667+00:00</t>
+          <t>2026-10-17T08:45:50.744331+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.775189+00:00</t>
+          <t>2026-10-17T08:45:50.746504+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.776759+00:00</t>
+          <t>2026-10-17T08:45:50.748111+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.778936+00:00</t>
+          <t>2026-10-17T08:45:50.750283+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.781210+00:00</t>
+          <t>2026-10-17T08:45:50.752255+00:00</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.781800+00:00</t>
+          <t>2026-10-17T08:45:50.752945+00:00</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.782463+00:00</t>
+          <t>2026-10-17T08:45:50.753817+00:00</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.784054+00:00</t>
+          <t>2026-10-17T08:45:50.755642+00:00</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.786804+00:00</t>
+          <t>2026-10-17T08:45:50.758463+00:00</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.788848+00:00</t>
+          <t>2026-10-17T08:45:50.760538+00:00</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.790018+00:00</t>
+          <t>2026-10-17T08:45:50.761745+00:00</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.793045+00:00</t>
+          <t>2026-10-17T08:45:50.764637+00:00</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.793818+00:00</t>
+          <t>2026-10-17T08:45:50.765370+00:00</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.795558+00:00</t>
+          <t>2026-10-17T08:45:50.767036+00:00</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.795830+00:00</t>
+          <t>2026-10-17T08:45:50.767341+00:00</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.797966+00:00</t>
+          <t>2026-10-17T08:45:50.769200+00:00</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.800878+00:00</t>
+          <t>2026-10-17T08:45:50.772284+00:00</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.802283+00:00</t>
+          <t>2026-10-17T08:45:50.773816+00:00</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.802839+00:00</t>
+          <t>2026-10-17T08:45:50.774418+00:00</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.805384+00:00</t>
+          <t>2026-10-17T08:45:50.777090+00:00</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.806656+00:00</t>
+          <t>2026-10-17T08:45:50.778216+00:00</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.810585+00:00</t>
+          <t>2026-10-17T08:45:50.781891+00:00</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.812338+00:00</t>
+          <t>2026-10-17T08:45:50.783716+00:00</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.814149+00:00</t>
+          <t>2026-10-17T08:45:50.785752+00:00</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.815199+00:00</t>
+          <t>2026-10-17T08:45:50.786786+00:00</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.815661+00:00</t>
+          <t>2026-10-17T08:45:50.787222+00:00</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.816019+00:00</t>
+          <t>2026-10-17T08:45:50.787607+00:00</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.817610+00:00</t>
+          <t>2026-10-17T08:45:50.789100+00:00</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.818934+00:00</t>
+          <t>2026-10-17T08:45:50.790404+00:00</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.820807+00:00</t>
+          <t>2026-10-17T08:45:50.791990+00:00</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.821149+00:00</t>
+          <t>2026-10-17T08:45:50.792459+00:00</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.822617+00:00</t>
+          <t>2026-10-17T08:45:50.793940+00:00</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.824045+00:00</t>
+          <t>2026-10-17T08:45:50.795386+00:00</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.824696+00:00</t>
+          <t>2026-10-17T08:45:50.795970+00:00</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.825735+00:00</t>
+          <t>2026-10-17T08:45:50.796985+00:00</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.826064+00:00</t>
+          <t>2026-10-17T08:45:50.797449+00:00</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.831767+00:00</t>
+          <t>2026-10-17T08:45:50.803050+00:00</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.832175+00:00</t>
+          <t>2026-10-17T08:45:50.803598+00:00</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.832815+00:00</t>
+          <t>2026-10-17T08:45:50.804168+00:00</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.833250+00:00</t>
+          <t>2026-10-17T08:45:50.804627+00:00</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.834560+00:00</t>
+          <t>2026-10-17T08:45:50.805761+00:00</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.837720+00:00</t>
+          <t>2026-10-17T08:45:50.809030+00:00</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.837978+00:00</t>
+          <t>2026-10-17T08:45:50.809313+00:00</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.842979+00:00</t>
+          <t>2026-10-17T08:45:50.813952+00:00</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.843795+00:00</t>
+          <t>2026-10-17T08:45:50.814780+00:00</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.846083+00:00</t>
+          <t>2026-10-17T08:45:50.817045+00:00</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.848507+00:00</t>
+          <t>2026-10-17T08:45:50.818899+00:00</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.849473+00:00</t>
+          <t>2026-10-17T08:45:50.819801+00:00</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.850892+00:00</t>
+          <t>2026-10-17T08:45:50.821225+00:00</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.853570+00:00</t>
+          <t>2026-10-17T08:45:50.823515+00:00</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.866001+00:00</t>
+          <t>2026-10-17T08:45:50.831579+00:00</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.867376+00:00</t>
+          <t>2026-10-17T08:45:50.832994+00:00</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.867528+00:00</t>
+          <t>2026-10-17T08:45:50.833160+00:00</t>
         </is>
       </c>
     </row>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.867542+00:00</t>
+          <t>2026-10-17T08:45:50.833173+00:00</t>
         </is>
       </c>
     </row>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.873568+00:00</t>
+          <t>2026-10-17T08:45:50.838402+00:00</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.873974+00:00</t>
+          <t>2026-10-17T08:45:50.838888+00:00</t>
         </is>
       </c>
     </row>
@@ -33071,7 +33071,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.874457+00:00</t>
+          <t>2026-10-17T08:45:50.839252+00:00</t>
         </is>
       </c>
     </row>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.874923+00:00</t>
+          <t>2026-10-17T08:45:50.839703+00:00</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.875736+00:00</t>
+          <t>2026-10-17T08:45:50.840450+00:00</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33383,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.877105+00:00</t>
+          <t>2026-10-17T08:45:50.842227+00:00</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.877936+00:00</t>
+          <t>2026-10-17T08:45:50.843094+00:00</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.878253+00:00</t>
+          <t>2026-10-17T08:45:50.843428+00:00</t>
         </is>
       </c>
     </row>
@@ -33699,7 +33699,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.878900+00:00</t>
+          <t>2026-10-17T08:45:50.844082+00:00</t>
         </is>
       </c>
     </row>
@@ -33799,7 +33799,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.878915+00:00</t>
+          <t>2026-10-17T08:45:50.844097+00:00</t>
         </is>
       </c>
     </row>
@@ -33907,7 +33907,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.878965+00:00</t>
+          <t>2026-10-17T08:45:50.844149+00:00</t>
         </is>
       </c>
     </row>
@@ -34015,7 +34015,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.879436+00:00</t>
+          <t>2026-10-17T08:45:50.844387+00:00</t>
         </is>
       </c>
     </row>
@@ -34123,7 +34123,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.879579+00:00</t>
+          <t>2026-10-17T08:45:50.844509+00:00</t>
         </is>
       </c>
     </row>
@@ -34235,7 +34235,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.879699+00:00</t>
+          <t>2026-10-17T08:45:50.844629+00:00</t>
         </is>
       </c>
     </row>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.880065+00:00</t>
+          <t>2026-10-17T08:45:50.845020+00:00</t>
         </is>
       </c>
     </row>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.880252+00:00</t>
+          <t>2026-10-17T08:45:50.845271+00:00</t>
         </is>
       </c>
     </row>
@@ -34563,7 +34563,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.880330+00:00</t>
+          <t>2026-10-17T08:45:50.845372+00:00</t>
         </is>
       </c>
     </row>
@@ -34675,7 +34675,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.880398+00:00</t>
+          <t>2026-10-17T08:45:50.845438+00:00</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.880536+00:00</t>
+          <t>2026-10-17T08:45:50.845607+00:00</t>
         </is>
       </c>
     </row>
@@ -34899,7 +34899,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.880582+00:00</t>
+          <t>2026-10-17T08:45:50.845658+00:00</t>
         </is>
       </c>
     </row>
@@ -35007,7 +35007,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.881024+00:00</t>
+          <t>2026-10-17T08:45:50.846115+00:00</t>
         </is>
       </c>
     </row>
@@ -35115,7 +35115,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.881070+00:00</t>
+          <t>2026-10-17T08:45:50.846164+00:00</t>
         </is>
       </c>
     </row>
@@ -35215,7 +35215,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.881080+00:00</t>
+          <t>2026-10-17T08:45:50.846174+00:00</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.892338+00:00</t>
+          <t>2026-10-17T08:45:50.856211+00:00</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.892420+00:00</t>
+          <t>2026-10-17T08:45:50.856338+00:00</t>
         </is>
       </c>
     </row>
@@ -35535,7 +35535,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.892546+00:00</t>
+          <t>2026-10-17T08:45:50.856487+00:00</t>
         </is>
       </c>
     </row>
@@ -35643,7 +35643,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.892789+00:00</t>
+          <t>2026-10-17T08:45:50.856740+00:00</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.893903+00:00</t>
+          <t>2026-10-17T08:45:50.857858+00:00</t>
         </is>
       </c>
     </row>
@@ -35853,7 +35853,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894006+00:00</t>
+          <t>2026-10-17T08:45:50.857945+00:00</t>
         </is>
       </c>
     </row>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894019+00:00</t>
+          <t>2026-10-17T08:45:50.857957+00:00</t>
         </is>
       </c>
     </row>
@@ -35981,13 +35981,21 @@
           <t>papers/R04092/evidence/0fb90085e306_PMC6288047_fullText.xml</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R04092/PMC6288047_fullText.xml</t>
+        </is>
+      </c>
       <c r="I111" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-supplements/R04092/evidence/PMC6288047_fullText.xml</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/source_evidence/R04092/PMC6288047_fullText.xml</t>
+        </is>
+      </c>
       <c r="K111" t="inlineStr">
         <is>
           <t>xml</t>
@@ -36003,12 +36011,12 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -36041,7 +36049,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894022+00:00</t>
+          <t>2026-10-17T08:45:50.858044+00:00</t>
         </is>
       </c>
     </row>
@@ -36075,13 +36083,21 @@
           <t>papers/R05839/evidence/18ffd43dee95_PMC7566014_fullText.xml</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R05839/PMC7566014_fullText.xml</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-supplements/R05839/evidence/PMC7566014_fullText.xml</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/source_evidence/R05839/PMC7566014_fullText.xml</t>
+        </is>
+      </c>
       <c r="K112" t="inlineStr">
         <is>
           <t>xml</t>
@@ -36097,12 +36113,12 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -36135,7 +36151,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894025+00:00</t>
+          <t>2026-10-17T08:45:50.858124+00:00</t>
         </is>
       </c>
     </row>
@@ -36169,13 +36185,21 @@
           <t>papers/R08877/evidence/e8712e4198ba_PMC10714394_fullText.xml</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R08877/PMC10714394_fullText.xml</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-supplements/R08877/evidence/PMC10714394_fullText.xml</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/source_evidence/R08877/PMC10714394_fullText.xml</t>
+        </is>
+      </c>
       <c r="K113" t="inlineStr">
         <is>
           <t>xml</t>
@@ -36191,12 +36215,12 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -36229,7 +36253,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894028+00:00</t>
+          <t>2026-10-17T08:45:50.858232+00:00</t>
         </is>
       </c>
     </row>
@@ -36323,7 +36347,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894031+00:00</t>
+          <t>2026-10-17T08:45:50.858243+00:00</t>
         </is>
       </c>
     </row>
@@ -36357,13 +36381,21 @@
           <t>papers/R09236/evidence/72064fe9276d_PMC10535533_fullText.xml</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R09236/PMC10535533_fullText.xml</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-supplements/R09236/evidence/PMC10535533_fullText.xml</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/source_evidence/R09236/PMC10535533_fullText.xml</t>
+        </is>
+      </c>
       <c r="K115" t="inlineStr">
         <is>
           <t>xml</t>
@@ -36379,12 +36411,12 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -36417,7 +36449,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894034+00:00</t>
+          <t>2026-10-17T08:45:50.858436+00:00</t>
         </is>
       </c>
     </row>
@@ -36511,7 +36543,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894043+00:00</t>
+          <t>2026-10-17T08:45:50.858451+00:00</t>
         </is>
       </c>
     </row>
@@ -36545,13 +36577,21 @@
           <t>papers/R10086/evidence/074f3cb8a393_PMC10837232_fullText.xml</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R10086/PMC10837232_fullText.xml</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-supplements/R10086/evidence/PMC10837232_fullText.xml</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/source_evidence/R10086/PMC10837232_fullText.xml</t>
+        </is>
+      </c>
       <c r="K117" t="inlineStr">
         <is>
           <t>xml</t>
@@ -36567,12 +36607,12 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -36605,7 +36645,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894046+00:00</t>
+          <t>2026-10-17T08:45:50.858554+00:00</t>
         </is>
       </c>
     </row>
@@ -36699,7 +36739,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894049+00:00</t>
+          <t>2026-10-17T08:45:50.858566+00:00</t>
         </is>
       </c>
     </row>
@@ -36793,7 +36833,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894052+00:00</t>
+          <t>2026-10-17T08:45:50.858570+00:00</t>
         </is>
       </c>
     </row>
@@ -36887,7 +36927,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894055+00:00</t>
+          <t>2026-10-17T08:45:50.858573+00:00</t>
         </is>
       </c>
     </row>
@@ -36981,7 +37021,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894058+00:00</t>
+          <t>2026-10-17T08:45:50.858576+00:00</t>
         </is>
       </c>
     </row>
@@ -37075,7 +37115,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894060+00:00</t>
+          <t>2026-10-17T08:45:50.858579+00:00</t>
         </is>
       </c>
     </row>
@@ -37169,7 +37209,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894063+00:00</t>
+          <t>2026-10-17T08:45:50.858583+00:00</t>
         </is>
       </c>
     </row>
@@ -37263,7 +37303,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894066+00:00</t>
+          <t>2026-10-17T08:45:50.858587+00:00</t>
         </is>
       </c>
     </row>
@@ -37357,7 +37397,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894069+00:00</t>
+          <t>2026-10-17T08:45:50.858590+00:00</t>
         </is>
       </c>
     </row>
@@ -37451,7 +37491,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894071+00:00</t>
+          <t>2026-10-17T08:45:50.858594+00:00</t>
         </is>
       </c>
     </row>
@@ -37545,7 +37585,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894074+00:00</t>
+          <t>2026-10-17T08:45:50.858597+00:00</t>
         </is>
       </c>
     </row>
@@ -37639,7 +37679,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894077+00:00</t>
+          <t>2026-10-17T08:45:50.858601+00:00</t>
         </is>
       </c>
     </row>
@@ -37733,7 +37773,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894080+00:00</t>
+          <t>2026-10-17T08:45:50.858604+00:00</t>
         </is>
       </c>
     </row>
@@ -37827,7 +37867,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894084+00:00</t>
+          <t>2026-10-17T08:45:50.858607+00:00</t>
         </is>
       </c>
     </row>
@@ -37921,7 +37961,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894086+00:00</t>
+          <t>2026-10-17T08:45:50.858611+00:00</t>
         </is>
       </c>
     </row>
@@ -38015,7 +38055,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894089+00:00</t>
+          <t>2026-10-17T08:45:50.858614+00:00</t>
         </is>
       </c>
     </row>
@@ -38109,7 +38149,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894091+00:00</t>
+          <t>2026-10-17T08:45:50.858617+00:00</t>
         </is>
       </c>
     </row>
@@ -38203,7 +38243,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894094+00:00</t>
+          <t>2026-10-17T08:45:50.858621+00:00</t>
         </is>
       </c>
     </row>
@@ -38297,7 +38337,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.894096+00:00</t>
+          <t>2026-10-17T08:45:50.858625+00:00</t>
         </is>
       </c>
     </row>
@@ -38405,7 +38445,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.895445+00:00</t>
+          <t>2026-10-17T08:45:50.859850+00:00</t>
         </is>
       </c>
     </row>
@@ -38497,7 +38537,7 @@
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.906626+00:00</t>
+          <t>2026-10-17T08:45:50.869749+00:00</t>
         </is>
       </c>
     </row>
@@ -38585,7 +38625,7 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.906695+00:00</t>
+          <t>2026-10-17T08:45:50.869818+00:00</t>
         </is>
       </c>
     </row>
@@ -38673,7 +38713,7 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.906701+00:00</t>
+          <t>2026-10-17T08:45:50.869825+00:00</t>
         </is>
       </c>
     </row>
@@ -38765,7 +38805,7 @@
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.906705+00:00</t>
+          <t>2026-10-17T08:45:50.869829+00:00</t>
         </is>
       </c>
     </row>
@@ -38857,7 +38897,7 @@
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.906708+00:00</t>
+          <t>2026-10-17T08:45:50.869832+00:00</t>
         </is>
       </c>
     </row>
@@ -38949,7 +38989,7 @@
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.906710+00:00</t>
+          <t>2026-10-17T08:45:50.869835+00:00</t>
         </is>
       </c>
     </row>
@@ -39041,7 +39081,7 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.906713+00:00</t>
+          <t>2026-10-17T08:45:50.869839+00:00</t>
         </is>
       </c>
     </row>
@@ -39129,7 +39169,7 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.906715+00:00</t>
+          <t>2026-10-17T08:45:50.869842+00:00</t>
         </is>
       </c>
     </row>
@@ -39221,7 +39261,7 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.906718+00:00</t>
+          <t>2026-10-17T08:45:50.869846+00:00</t>
         </is>
       </c>
     </row>
@@ -39313,7 +39353,7 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.906721+00:00</t>
+          <t>2026-10-17T08:45:50.869850+00:00</t>
         </is>
       </c>
     </row>
@@ -39401,7 +39441,7 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.906724+00:00</t>
+          <t>2026-10-17T08:45:50.869854+00:00</t>
         </is>
       </c>
     </row>
@@ -39493,7 +39533,7 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-10-17T08:44:41.906726+00:00</t>
+          <t>2026-10-17T08:45:50.869858+00:00</t>
         </is>
       </c>
     </row>
@@ -39508,7 +39548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39796,35 +39836,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R04092</t>
+          <t>R08877</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R04092.evidence_xml.0fb90085e30680fa</t>
+          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0fb90085e30680fa8a9896b80afb9da4f9466ba0051ea2ffb89a13e06a5013a3</t>
+          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>77995</v>
+        <v>704921</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6288047/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>PMC6288047_fullText.xml</t>
+          <t>PMC10714394_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -39836,35 +39876,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R05839</t>
+          <t>R09236</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R05839.evidence_xml.18ffd43dee955086</t>
+          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18ffd43dee955086eae0947027dc85e1d765e181357143650e9fef0b0dfbef74</t>
+          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>75205</v>
+        <v>483405</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC7566014/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>PMC7566014_fullText.xml</t>
+          <t>PMC10535533_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -39876,35 +39916,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R08877.evidence_xml.e8712e4198baab4c</t>
+          <t>R10086.transport_archive.4d9eddf454b786ed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>e8712e4198baab4c79ee53c54ea30b4d96721e2d47e08b657a6b19b4bf41891a</t>
+          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>111864</v>
+        <v>641038</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>PMC10714394_fullText.xml</t>
+          <t>PMC10837232_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -39916,35 +39956,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R08877</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R08877.transport_archive.ed8e864a3225e9c4</t>
+          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ed8e864a3225e9c4cecf84e5f4670c985de4c6d453d0b7b459ad5870e6627f97</t>
+          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>704921</v>
+        <v>173586</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10714394/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PMC10714394_supplementaryFiles.zip</t>
+          <t>PMC12937426_fullText.xml</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -39956,35 +39996,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R12985</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R09236.evidence_xml.72064fe9276d8309</t>
+          <t>R12985.transport_archive.418d45f1ca296020</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>72064fe9276d830984364e82e4567877578408565c650d856c531204a17ded89</t>
+          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>193052</v>
+        <v>672244</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>PMC10535533_fullText.xml</t>
+          <t>PMC12937426_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -39996,35 +40036,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R09236</t>
+          <t>R05542</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R09236.transport_archive.f3c6856282b7e8d6</t>
+          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>f3c6856282b7e8d694d35a87eae016d8e66aa902189c7c3311a1153ea24752e0</t>
+          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>483405</v>
+        <v>100215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10535533/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>PMC10535533_supplementaryFiles.zip</t>
+          <t>PMC9056904_fullText.xml</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -40036,12 +40076,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R10086.evidence_xml.074f3cb8a39355a5</t>
+          <t>R06325.evidence_xml.645deb707d3790b5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -40051,20 +40091,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>074f3cb8a39355a5d7cfb8af0139c674b72aec8e5d08bcd20b8f0e46d0d88fbe</t>
+          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>118002</v>
+        <v>160509</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>PMC10837232_fullText.xml</t>
+          <t>PMC8290346_fullText.xml</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -40076,12 +40116,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R10086.transport_archive.4d9eddf454b786ed</t>
+          <t>R06325.transport_archive.6eb4ef126661714a</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -40091,20 +40131,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4d9eddf454b786eddece423a320b28d7f96959a935334ddc7c7e2fe32d39bc9b</t>
+          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>641038</v>
+        <v>1730580</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10837232/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>PMC10837232_supplementaryFiles.zip</t>
+          <t>PMC8290346_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -40116,12 +40156,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
+          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -40131,20 +40171,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
+          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>173586</v>
+        <v>151458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>PMC12937426_fullText.xml</t>
+          <t>PMC8044681_fullText.xml</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -40156,12 +40196,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R12985.transport_archive.418d45f1ca296020</t>
+          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -40171,20 +40211,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
+          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>672244</v>
+        <v>14596266</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PMC12937426_supplementaryFiles.zip</t>
+          <t>PMC8044681_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -40196,12 +40236,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R05542</t>
+          <t>R03477</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
+          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -40211,20 +40251,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
+          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100215</v>
+        <v>121650</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>PMC9056904_fullText.xml</t>
+          <t>PMC5371168_fullText.xml</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -40236,12 +40276,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R06325.evidence_xml.645deb707d3790b5</t>
+          <t>R08646.evidence_xml.c7b723e8020f6582</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -40251,20 +40291,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
+          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>160509</v>
+        <v>304277</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PMC8290346_fullText.xml</t>
+          <t>PMC10559078_fullText.xml</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -40276,12 +40316,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R06325.transport_archive.6eb4ef126661714a</t>
+          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -40291,20 +40331,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
+          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1730580</v>
+        <v>1539133</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>PMC8290346_supplementaryFiles.zip</t>
+          <t>PMC10559078_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -40316,12 +40356,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R09804</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
+          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -40331,20 +40371,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
+          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>151458</v>
+        <v>211630</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PMC8044681_fullText.xml</t>
+          <t>PMC11076452_fullText.xml</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -40356,35 +40396,35 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R11503</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
+          <t>R11503.evidence_xml.4002d57be59c215c</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
+          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>14596266</v>
+        <v>258637</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PMC8044681_supplementaryFiles.zip</t>
+          <t>PMC12561102_fullText.xml</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -40396,12 +40436,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R03477</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
+          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -40411,20 +40451,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
+          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>121650</v>
+        <v>256247</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>PMC5371168_fullText.xml</t>
+          <t>PMC12125087_fullText.xml</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -40436,35 +40476,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R08646.evidence_xml.c7b723e8020f6582</t>
+          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
+          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>304277</v>
+        <v>521862</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>PMC10559078_fullText.xml</t>
+          <t>PMC12125087_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -40476,35 +40516,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
+          <t>R05213.evidence_xml.17894ab410001846</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
+          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1539133</v>
+        <v>130954</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PMC10559078_supplementaryFiles.zip</t>
+          <t>PMC6858683_fullText.xml</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -40516,35 +40556,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
+          <t>R05213.transport_archive.c61c88cf9fd489be</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
+          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>211630</v>
+        <v>1960371</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PMC11076452_fullText.xml</t>
+          <t>PMC6858683_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -40556,12 +40596,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>R11503</t>
+          <t>R09585</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R11503.evidence_xml.4002d57be59c215c</t>
+          <t>R09585.evidence_xml.a3430f38fa1652de</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -40571,20 +40611,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
+          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>258637</v>
+        <v>100534</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>PMC12561102_fullText.xml</t>
+          <t>PMC10609292_fullText.xml</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -40596,35 +40636,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R02274</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
+          <t>R02274.main.4c7da8384f1f6e3d</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
+          <t>4c7da8384f1f6e3d8bd2681eab23bdb95e3057009cf4c7ec7aacc7cdb9eaf43d</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>256247</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
-        </is>
-      </c>
+        <v>471480</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>PMC12125087_fullText.xml</t>
+          <t>R02274_2016_ANAEROBIC_DIGESTION_OF_WASTEWATER_WITH_HIGH_SULFATE_CONCENTRATION_USING.pdf</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -40636,35 +40672,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
+          <t>R10086.main.84777bfb7a2cd42f</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
+          <t>84777bfb7a2cd42f9696e060fc79d5de3e72d5ad8fa1e222934a7fcdf97dd365</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>521862</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
-        </is>
-      </c>
+        <v>984310</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PMC12125087_supplementaryFiles.zip</t>
+          <t>R10086_2024_Effect_of_micro-aeration_on_syntrophic_and_methanogenic_activity_in.pdf</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -40676,35 +40708,35 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>R05213</t>
+          <t>R03477</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R05213.evidence_xml.17894ab410001846</t>
+          <t>R03477.main.79583f4a64fb2fbb</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
+          <t>79583f4a64fb2fbb4a1f4f471fe6001b159213acb1f3bbd19d6dc0be5c714fa5</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>130954</v>
+        <v>1714874</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
+          <t>https://link.springer.com/content/pdf/10.1186/s13568-017-0375-4.pdf</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PMC6858683_fullText.xml</t>
+          <t>R03477_2017_Pretreatment_methods_of_lignocellulosic_biomass_for_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -40716,35 +40748,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>R05213</t>
+          <t>R09804</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R05213.transport_archive.c61c88cf9fd489be</t>
+          <t>R09804.main.b3cc83d613ad3c36</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
+          <t>b3cc83d613ad3c36f93b78eace000ebc5a603966523ee71c2e6a0bd85a8ede3e</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1960371</v>
+        <v>5135812</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
+          <t>https://link.springer.com/content/pdf/10.1186/s40643-024-00756-6.pdf</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PMC6858683_supplementaryFiles.zip</t>
+          <t>R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -40756,35 +40788,35 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>R09585</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R09585.evidence_xml.a3430f38fa1652de</t>
+          <t>R11844.main.c41816bf825167dc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
+          <t>c41816bf825167dcb78ff5eb81c8d0dab0d8d8110cd2a23a04cd1109acb34919</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100534</v>
+        <v>1333380</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
+          <t>https://link.springer.com/content/pdf/10.1007/s00253-025-13519-w.pdf</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PMC10609292_fullText.xml</t>
+          <t>R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -40796,12 +40828,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R02274</t>
+          <t>R03155</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R02274.main.4c7da8384f1f6e3d</t>
+          <t>R03155.main.2875ce0c137df622</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -40811,16 +40843,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4c7da8384f1f6e3d8bd2681eab23bdb95e3057009cf4c7ec7aacc7cdb9eaf43d</t>
+          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>471480</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
+        <v>5745828</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://dspace.lib.ntua.gr/xmlui/bitstream/handle/123456789/44237/Msc.%20Thesis_Aristotle_Vasileiou%20THE.pdf?sequence=1&amp;isAllowed=y</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>R02274_2016_ANAEROBIC_DIGESTION_OF_WASTEWATER_WITH_HIGH_SULFATE_CONCENTRATION_USING.pdf</t>
+          <t>R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -40832,12 +40868,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>R10086.main.84777bfb7a2cd42f</t>
+          <t>R05213.main.bcab84a15ce93062</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -40847,16 +40883,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>84777bfb7a2cd42f9696e060fc79d5de3e72d5ad8fa1e222934a7fcdf97dd365</t>
+          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>984310</v>
+        <v>1022660</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>R10086_2024_Effect_of_micro-aeration_on_syntrophic_and_methanogenic_activity_in.pdf</t>
+          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -40868,12 +40904,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>R03477</t>
+          <t>R06036</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>R03477.main.79583f4a64fb2fbb</t>
+          <t>R06036.main.0bdc7b19fdb70091</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -40883,20 +40919,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>79583f4a64fb2fbb4a1f4f471fe6001b159213acb1f3bbd19d6dc0be5c714fa5</t>
+          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1714874</v>
+        <v>927168</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1186/s13568-017-0375-4.pdf</t>
+          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>R03477_2017_Pretreatment_methods_of_lignocellulosic_biomass_for_anaerobic_digestion.pdf</t>
+          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -40908,12 +40944,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R09240</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R09804.main.b3cc83d613ad3c36</t>
+          <t>R09240.main.da8dbeb874b19b59</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -40923,20 +40959,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>b3cc83d613ad3c36f93b78eace000ebc5a603966523ee71c2e6a0bd85a8ede3e</t>
+          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5135812</v>
+        <v>1315227</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1186/s40643-024-00756-6.pdf</t>
+          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
+          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -40948,12 +40984,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R13899</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>R11844.main.c41816bf825167dc</t>
+          <t>R13899.main.19143e56fa77ce99</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -40963,20 +40999,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>c41816bf825167dcb78ff5eb81c8d0dab0d8d8110cd2a23a04cd1109acb34919</t>
+          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1333380</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>https://link.springer.com/content/pdf/10.1007/s00253-025-13519-w.pdf</t>
-        </is>
-      </c>
+        <v>479092</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
+          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -40988,12 +41020,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>R03155</t>
+          <t>R13955</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R03155.main.2875ce0c137df622</t>
+          <t>R13955.main.6714f79deccd703d</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -41003,215 +41035,23 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
+          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5745828</v>
+        <v>14662119</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://dspace.lib.ntua.gr/xmlui/bitstream/handle/123456789/44237/Msc.%20Thesis_Aristotle_Vasileiou%20THE.pdf?sequence=1&amp;isAllowed=y</t>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>R05213</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>R05213.main.bcab84a15ce93062</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>1022660</v>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>R06036</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>R06036.main.0bdc7b19fdb70091</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>927168</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>R09240</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>R09240.main.da8dbeb874b19b59</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>1315227</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>R13899</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>R13899.main.19143e56fa77ce99</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>479092</v>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>R13955</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>R13955.main.6714f79deccd703d</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>14662119</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
         <is>
           <t>历史已获取，当前原件未恢复</t>
         </is>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.702022+00:00</t>
+          <t>2026-10-17T08:46:53.263460+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.702957+00:00</t>
+          <t>2026-10-17T08:46:53.264440+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.702978+00:00</t>
+          <t>2026-10-17T08:46:53.264466+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.703200+00:00</t>
+          <t>2026-10-17T08:46:53.264689+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.704421+00:00</t>
+          <t>2026-10-17T08:46:53.266554+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.704894+00:00</t>
+          <t>2026-10-17T08:46:53.267038+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.711996+00:00</t>
+          <t>2026-10-17T08:46:53.272936+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.714498+00:00</t>
+          <t>2026-10-17T08:46:53.275352+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.715434+00:00</t>
+          <t>2026-10-17T08:46:53.276229+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.715772+00:00</t>
+          <t>2026-10-17T08:46:53.276579+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.716538+00:00</t>
+          <t>2026-10-17T08:46:53.277354+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.717210+00:00</t>
+          <t>2026-10-17T08:46:53.278024+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.718195+00:00</t>
+          <t>2026-10-17T08:46:53.278920+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.718455+00:00</t>
+          <t>2026-10-17T08:46:53.279160+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.719320+00:00</t>
+          <t>2026-10-17T08:46:53.280015+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.726800+00:00</t>
+          <t>2026-10-17T08:46:53.291564+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.727501+00:00</t>
+          <t>2026-10-17T08:46:53.292346+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.728737+00:00</t>
+          <t>2026-10-17T08:46:53.293622+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.731286+00:00</t>
+          <t>2026-10-17T08:46:53.298220+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.732488+00:00</t>
+          <t>2026-10-17T08:46:53.301384+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.733708+00:00</t>
+          <t>2026-10-17T08:46:53.302635+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.738763+00:00</t>
+          <t>2026-10-17T08:46:53.308945+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.741376+00:00</t>
+          <t>2026-10-17T08:46:53.312070+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.743244+00:00</t>
+          <t>2026-10-17T08:46:53.314750+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.743931+00:00</t>
+          <t>2026-10-17T08:46:53.315471+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.744331+00:00</t>
+          <t>2026-10-17T08:46:53.315852+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.746504+00:00</t>
+          <t>2026-10-17T08:46:53.318434+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.748111+00:00</t>
+          <t>2026-10-17T08:46:53.320099+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.750283+00:00</t>
+          <t>2026-10-17T08:46:53.322521+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.752255+00:00</t>
+          <t>2026-10-17T08:46:53.324802+00:00</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.752945+00:00</t>
+          <t>2026-10-17T08:46:53.325449+00:00</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.753817+00:00</t>
+          <t>2026-10-17T08:46:53.326088+00:00</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.755642+00:00</t>
+          <t>2026-10-17T08:46:53.328576+00:00</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.758463+00:00</t>
+          <t>2026-10-17T08:46:53.332358+00:00</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.760538+00:00</t>
+          <t>2026-10-17T08:46:53.334767+00:00</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.761745+00:00</t>
+          <t>2026-10-17T08:46:53.336120+00:00</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.764637+00:00</t>
+          <t>2026-10-17T08:46:53.339862+00:00</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.765370+00:00</t>
+          <t>2026-10-17T08:46:53.340720+00:00</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.767036+00:00</t>
+          <t>2026-10-17T08:46:53.342687+00:00</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.767341+00:00</t>
+          <t>2026-10-17T08:46:53.342979+00:00</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.769200+00:00</t>
+          <t>2026-10-17T08:46:53.344990+00:00</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.772284+00:00</t>
+          <t>2026-10-17T08:46:53.348730+00:00</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.773816+00:00</t>
+          <t>2026-10-17T08:46:53.350177+00:00</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.774418+00:00</t>
+          <t>2026-10-17T08:46:53.350829+00:00</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.777090+00:00</t>
+          <t>2026-10-17T08:46:53.354082+00:00</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.778216+00:00</t>
+          <t>2026-10-17T08:46:53.355377+00:00</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.781891+00:00</t>
+          <t>2026-10-17T08:46:53.359476+00:00</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.783716+00:00</t>
+          <t>2026-10-17T08:46:53.361780+00:00</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.785752+00:00</t>
+          <t>2026-10-17T08:46:53.364059+00:00</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.786786+00:00</t>
+          <t>2026-10-17T08:46:53.365555+00:00</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.787222+00:00</t>
+          <t>2026-10-17T08:46:53.366025+00:00</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.787607+00:00</t>
+          <t>2026-10-17T08:46:53.366546+00:00</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.789100+00:00</t>
+          <t>2026-10-17T08:46:53.368171+00:00</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.790404+00:00</t>
+          <t>2026-10-17T08:46:53.369665+00:00</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.791990+00:00</t>
+          <t>2026-10-17T08:46:53.371212+00:00</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.792459+00:00</t>
+          <t>2026-10-17T08:46:53.371627+00:00</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.793940+00:00</t>
+          <t>2026-10-17T08:46:53.372854+00:00</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.795386+00:00</t>
+          <t>2026-10-17T08:46:53.374225+00:00</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.795970+00:00</t>
+          <t>2026-10-17T08:46:53.375026+00:00</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.796985+00:00</t>
+          <t>2026-10-17T08:46:53.376090+00:00</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.797449+00:00</t>
+          <t>2026-10-17T08:46:53.376492+00:00</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.803050+00:00</t>
+          <t>2026-10-17T08:46:53.382317+00:00</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.803598+00:00</t>
+          <t>2026-10-17T08:46:53.382744+00:00</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.804168+00:00</t>
+          <t>2026-10-17T08:46:53.383315+00:00</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.804627+00:00</t>
+          <t>2026-10-17T08:46:53.383749+00:00</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.805761+00:00</t>
+          <t>2026-10-17T08:46:53.384890+00:00</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.809030+00:00</t>
+          <t>2026-10-17T08:46:53.388444+00:00</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.809313+00:00</t>
+          <t>2026-10-17T08:46:53.388718+00:00</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.813952+00:00</t>
+          <t>2026-10-17T08:46:53.393454+00:00</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.814780+00:00</t>
+          <t>2026-10-17T08:46:53.394373+00:00</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.817045+00:00</t>
+          <t>2026-10-17T08:46:53.396605+00:00</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.818899+00:00</t>
+          <t>2026-10-17T08:46:53.398474+00:00</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.819801+00:00</t>
+          <t>2026-10-17T08:46:53.399377+00:00</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.821225+00:00</t>
+          <t>2026-10-17T08:46:53.400957+00:00</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.823515+00:00</t>
+          <t>2026-10-17T08:46:53.404354+00:00</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.831579+00:00</t>
+          <t>2026-10-17T08:46:53.414817+00:00</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.832994+00:00</t>
+          <t>2026-10-17T08:46:53.416380+00:00</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.833160+00:00</t>
+          <t>2026-10-17T08:46:53.416555+00:00</t>
         </is>
       </c>
     </row>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.833173+00:00</t>
+          <t>2026-10-17T08:46:53.416569+00:00</t>
         </is>
       </c>
     </row>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.838402+00:00</t>
+          <t>2026-10-17T08:46:53.422145+00:00</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.838888+00:00</t>
+          <t>2026-10-17T08:46:53.422651+00:00</t>
         </is>
       </c>
     </row>
@@ -33071,7 +33071,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.839252+00:00</t>
+          <t>2026-10-17T08:46:53.423013+00:00</t>
         </is>
       </c>
     </row>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.839703+00:00</t>
+          <t>2026-10-17T08:46:53.423427+00:00</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.840450+00:00</t>
+          <t>2026-10-17T08:46:53.424126+00:00</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33383,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.842227+00:00</t>
+          <t>2026-10-17T08:46:53.425686+00:00</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.843094+00:00</t>
+          <t>2026-10-17T08:46:53.426539+00:00</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.843428+00:00</t>
+          <t>2026-10-17T08:46:53.426847+00:00</t>
         </is>
       </c>
     </row>
@@ -33699,7 +33699,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.844082+00:00</t>
+          <t>2026-10-17T08:46:53.427508+00:00</t>
         </is>
       </c>
     </row>
@@ -33799,7 +33799,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.844097+00:00</t>
+          <t>2026-10-17T08:46:53.427522+00:00</t>
         </is>
       </c>
     </row>
@@ -33907,7 +33907,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.844149+00:00</t>
+          <t>2026-10-17T08:46:53.427576+00:00</t>
         </is>
       </c>
     </row>
@@ -34015,7 +34015,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.844387+00:00</t>
+          <t>2026-10-17T08:46:53.427805+00:00</t>
         </is>
       </c>
     </row>
@@ -34123,7 +34123,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.844509+00:00</t>
+          <t>2026-10-17T08:46:53.427922+00:00</t>
         </is>
       </c>
     </row>
@@ -34235,7 +34235,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.844629+00:00</t>
+          <t>2026-10-17T08:46:53.428035+00:00</t>
         </is>
       </c>
     </row>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.845020+00:00</t>
+          <t>2026-10-17T08:46:53.428437+00:00</t>
         </is>
       </c>
     </row>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.845271+00:00</t>
+          <t>2026-10-17T08:46:53.428705+00:00</t>
         </is>
       </c>
     </row>
@@ -34563,7 +34563,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.845372+00:00</t>
+          <t>2026-10-17T08:46:53.428779+00:00</t>
         </is>
       </c>
     </row>
@@ -34675,7 +34675,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.845438+00:00</t>
+          <t>2026-10-17T08:46:53.428844+00:00</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.845607+00:00</t>
+          <t>2026-10-17T08:46:53.428986+00:00</t>
         </is>
       </c>
     </row>
@@ -34899,7 +34899,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.845658+00:00</t>
+          <t>2026-10-17T08:46:53.429032+00:00</t>
         </is>
       </c>
     </row>
@@ -35007,7 +35007,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.846115+00:00</t>
+          <t>2026-10-17T08:46:53.429673+00:00</t>
         </is>
       </c>
     </row>
@@ -35115,7 +35115,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.846164+00:00</t>
+          <t>2026-10-17T08:46:53.429754+00:00</t>
         </is>
       </c>
     </row>
@@ -35215,7 +35215,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.846174+00:00</t>
+          <t>2026-10-17T08:46:53.429766+00:00</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.856211+00:00</t>
+          <t>2026-10-17T08:46:53.439990+00:00</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.856338+00:00</t>
+          <t>2026-10-17T08:46:53.440064+00:00</t>
         </is>
       </c>
     </row>
@@ -35535,7 +35535,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.856487+00:00</t>
+          <t>2026-10-17T08:46:53.440174+00:00</t>
         </is>
       </c>
     </row>
@@ -35643,7 +35643,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.856740+00:00</t>
+          <t>2026-10-17T08:46:53.440466+00:00</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.857858+00:00</t>
+          <t>2026-10-17T08:46:53.441649+00:00</t>
         </is>
       </c>
     </row>
@@ -35853,7 +35853,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.857945+00:00</t>
+          <t>2026-10-17T08:46:53.441756+00:00</t>
         </is>
       </c>
     </row>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.857957+00:00</t>
+          <t>2026-10-17T08:46:53.441769+00:00</t>
         </is>
       </c>
     </row>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858044+00:00</t>
+          <t>2026-10-17T08:46:53.441852+00:00</t>
         </is>
       </c>
     </row>
@@ -36151,7 +36151,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858124+00:00</t>
+          <t>2026-10-17T08:46:53.441934+00:00</t>
         </is>
       </c>
     </row>
@@ -36253,7 +36253,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858232+00:00</t>
+          <t>2026-10-17T08:46:53.442042+00:00</t>
         </is>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858243+00:00</t>
+          <t>2026-10-17T08:46:53.442053+00:00</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858436+00:00</t>
+          <t>2026-10-17T08:46:53.442273+00:00</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858451+00:00</t>
+          <t>2026-10-17T08:46:53.442315+00:00</t>
         </is>
       </c>
     </row>
@@ -36645,7 +36645,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858554+00:00</t>
+          <t>2026-10-17T08:46:53.442429+00:00</t>
         </is>
       </c>
     </row>
@@ -36739,7 +36739,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858566+00:00</t>
+          <t>2026-10-17T08:46:53.442442+00:00</t>
         </is>
       </c>
     </row>
@@ -36773,13 +36773,21 @@
           <t>papers/R12985/evidence/f1a80564a8a1_PMC12937426_fullText.xml</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R12985/PMC12937426_fullText.xml</t>
+        </is>
+      </c>
       <c r="I119" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-supplements/R12985/evidence/PMC12937426_fullText.xml</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr"/>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/source_evidence/R12985/PMC12937426_fullText.xml</t>
+        </is>
+      </c>
       <c r="K119" t="inlineStr">
         <is>
           <t>xml</t>
@@ -36795,12 +36803,12 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -36833,7 +36841,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858570+00:00</t>
+          <t>2026-10-17T08:46:53.442620+00:00</t>
         </is>
       </c>
     </row>
@@ -36927,7 +36935,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858573+00:00</t>
+          <t>2026-10-17T08:46:53.442638+00:00</t>
         </is>
       </c>
     </row>
@@ -36961,13 +36969,21 @@
           <t>papers/R05542/evidence/9ee6c9217e7c_PMC9056904_fullText.xml</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R05542/PMC9056904_fullText.xml</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-supplements/R05542/evidence/PMC9056904_fullText.xml</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr"/>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/source_evidence/R05542/PMC9056904_fullText.xml</t>
+        </is>
+      </c>
       <c r="K121" t="inlineStr">
         <is>
           <t>xml</t>
@@ -36983,12 +36999,12 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -37021,7 +37037,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858576+00:00</t>
+          <t>2026-10-17T08:46:53.442736+00:00</t>
         </is>
       </c>
     </row>
@@ -37055,13 +37071,21 @@
           <t>papers/R06325/evidence/645deb707d37_PMC8290346_fullText.xml</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R06325/PMC8290346_fullText.xml</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-supplements/R06325/evidence/PMC8290346_fullText.xml</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr"/>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/source_evidence/R06325/PMC8290346_fullText.xml</t>
+        </is>
+      </c>
       <c r="K122" t="inlineStr">
         <is>
           <t>xml</t>
@@ -37077,12 +37101,12 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -37115,7 +37139,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858579+00:00</t>
+          <t>2026-10-17T08:46:53.442868+00:00</t>
         </is>
       </c>
     </row>
@@ -37209,7 +37233,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858583+00:00</t>
+          <t>2026-10-17T08:46:53.442879+00:00</t>
         </is>
       </c>
     </row>
@@ -37243,13 +37267,21 @@
           <t>papers/R07238/evidence/6c93b117d7bd_PMC8044681_fullText.xml</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R07238/PMC8044681_fullText.xml</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-supplements/R07238/evidence/PMC8044681_fullText.xml</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr"/>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/source_evidence/R07238/PMC8044681_fullText.xml</t>
+        </is>
+      </c>
       <c r="K124" t="inlineStr">
         <is>
           <t>xml</t>
@@ -37265,12 +37297,12 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -37303,7 +37335,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858587+00:00</t>
+          <t>2026-10-17T08:46:53.442999+00:00</t>
         </is>
       </c>
     </row>
@@ -37397,7 +37429,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858590+00:00</t>
+          <t>2026-10-17T08:46:53.443009+00:00</t>
         </is>
       </c>
     </row>
@@ -37431,13 +37463,21 @@
           <t>papers/R03477/evidence/c127b68ddfdc_PMC5371168_fullText.xml</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R03477/PMC5371168_fullText.xml</t>
+        </is>
+      </c>
       <c r="I126" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-supplements/R03477/evidence/PMC5371168_fullText.xml</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr"/>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/source_evidence/R03477/PMC5371168_fullText.xml</t>
+        </is>
+      </c>
       <c r="K126" t="inlineStr">
         <is>
           <t>xml</t>
@@ -37453,12 +37493,12 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -37491,7 +37531,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858594+00:00</t>
+          <t>2026-10-17T08:46:53.443112+00:00</t>
         </is>
       </c>
     </row>
@@ -37585,7 +37625,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858597+00:00</t>
+          <t>2026-10-17T08:46:53.443123+00:00</t>
         </is>
       </c>
     </row>
@@ -37679,7 +37719,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858601+00:00</t>
+          <t>2026-10-17T08:46:53.443127+00:00</t>
         </is>
       </c>
     </row>
@@ -37773,7 +37813,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858604+00:00</t>
+          <t>2026-10-17T08:46:53.443131+00:00</t>
         </is>
       </c>
     </row>
@@ -37867,7 +37907,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858607+00:00</t>
+          <t>2026-10-17T08:46:53.443134+00:00</t>
         </is>
       </c>
     </row>
@@ -37961,7 +38001,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858611+00:00</t>
+          <t>2026-10-17T08:46:53.443138+00:00</t>
         </is>
       </c>
     </row>
@@ -38055,7 +38095,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858614+00:00</t>
+          <t>2026-10-17T08:46:53.443142+00:00</t>
         </is>
       </c>
     </row>
@@ -38149,7 +38189,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858617+00:00</t>
+          <t>2026-10-17T08:46:53.443146+00:00</t>
         </is>
       </c>
     </row>
@@ -38243,7 +38283,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858621+00:00</t>
+          <t>2026-10-17T08:46:53.443149+00:00</t>
         </is>
       </c>
     </row>
@@ -38337,7 +38377,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.858625+00:00</t>
+          <t>2026-10-17T08:46:53.443152+00:00</t>
         </is>
       </c>
     </row>
@@ -38445,7 +38485,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.859850+00:00</t>
+          <t>2026-10-17T08:46:53.444269+00:00</t>
         </is>
       </c>
     </row>
@@ -38537,7 +38577,7 @@
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.869749+00:00</t>
+          <t>2026-10-17T08:46:53.455436+00:00</t>
         </is>
       </c>
     </row>
@@ -38625,7 +38665,7 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.869818+00:00</t>
+          <t>2026-10-17T08:46:53.455513+00:00</t>
         </is>
       </c>
     </row>
@@ -38713,7 +38753,7 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.869825+00:00</t>
+          <t>2026-10-17T08:46:53.455520+00:00</t>
         </is>
       </c>
     </row>
@@ -38805,7 +38845,7 @@
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.869829+00:00</t>
+          <t>2026-10-17T08:46:53.455523+00:00</t>
         </is>
       </c>
     </row>
@@ -38897,7 +38937,7 @@
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.869832+00:00</t>
+          <t>2026-10-17T08:46:53.455527+00:00</t>
         </is>
       </c>
     </row>
@@ -38989,7 +39029,7 @@
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.869835+00:00</t>
+          <t>2026-10-17T08:46:53.455531+00:00</t>
         </is>
       </c>
     </row>
@@ -39081,7 +39121,7 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.869839+00:00</t>
+          <t>2026-10-17T08:46:53.455535+00:00</t>
         </is>
       </c>
     </row>
@@ -39169,7 +39209,7 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.869842+00:00</t>
+          <t>2026-10-17T08:46:53.455538+00:00</t>
         </is>
       </c>
     </row>
@@ -39261,7 +39301,7 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.869846+00:00</t>
+          <t>2026-10-17T08:46:53.455542+00:00</t>
         </is>
       </c>
     </row>
@@ -39353,7 +39393,7 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.869850+00:00</t>
+          <t>2026-10-17T08:46:53.455545+00:00</t>
         </is>
       </c>
     </row>
@@ -39441,7 +39481,7 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.869854+00:00</t>
+          <t>2026-10-17T08:46:53.455548+00:00</t>
         </is>
       </c>
     </row>
@@ -39533,7 +39573,7 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-10-17T08:45:50.869858+00:00</t>
+          <t>2026-10-17T08:46:53.455551+00:00</t>
         </is>
       </c>
     </row>
@@ -39548,7 +39588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39961,30 +40001,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R12985.evidence_xml.f1a80564a8a1fa4b</t>
+          <t>R12985.transport_archive.418d45f1ca296020</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>f1a80564a8a1fa4b638bb6097c75cb3709b4c7487b6c8012474fd4e1865576cc</t>
+          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>173586</v>
+        <v>672244</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>PMC12937426_fullText.xml</t>
+          <t>PMC12937426_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -39996,12 +40036,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R12985</t>
+          <t>R06325</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R12985.transport_archive.418d45f1ca296020</t>
+          <t>R06325.transport_archive.6eb4ef126661714a</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -40011,20 +40051,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>418d45f1ca2960209df0bfc1c3d44069413edc213239570a3d71d08d01f3e3e0</t>
+          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>672244</v>
+        <v>1730580</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12937426/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>PMC12937426_supplementaryFiles.zip</t>
+          <t>PMC8290346_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -40036,35 +40076,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R05542</t>
+          <t>R07238</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R05542.evidence_xml.9ee6c9217e7c01e1</t>
+          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>9ee6c9217e7c01e1604e3170e0041677e5b9d0f14b59ee1e9717c1082d9d193a</t>
+          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100215</v>
+        <v>14596266</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC9056904/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>PMC9056904_fullText.xml</t>
+          <t>PMC8044681_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -40076,12 +40116,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R06325.evidence_xml.645deb707d3790b5</t>
+          <t>R08646.evidence_xml.c7b723e8020f6582</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -40091,20 +40131,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>645deb707d3790b518690b7413885823461bb57a3dfa5bb587202d8f16dda296</t>
+          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>160509</v>
+        <v>304277</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>PMC8290346_fullText.xml</t>
+          <t>PMC10559078_fullText.xml</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -40116,12 +40156,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R06325</t>
+          <t>R08646</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R06325.transport_archive.6eb4ef126661714a</t>
+          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -40131,20 +40171,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6eb4ef126661714ae89bde97acdddac2c2a582864ca26ff9af569cfe609a4226</t>
+          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1730580</v>
+        <v>1539133</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8290346/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>PMC8290346_supplementaryFiles.zip</t>
+          <t>PMC10559078_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -40156,12 +40196,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R09804</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R07238.evidence_xml.6c93b117d7bd5886</t>
+          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -40171,20 +40211,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6c93b117d7bd588658aabfd8b7ec679110899d8f556eb6b90b071e6057ddd2cd</t>
+          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>151458</v>
+        <v>211630</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>PMC8044681_fullText.xml</t>
+          <t>PMC11076452_fullText.xml</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -40196,35 +40236,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R07238</t>
+          <t>R11503</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R07238.transport_archive.3785c23cb2f4ab50</t>
+          <t>R11503.evidence_xml.4002d57be59c215c</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3785c23cb2f4ab50f5b2b5cbb581da63ced9f8d1e69a91e6faca839b6b57587d</t>
+          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>14596266</v>
+        <v>258637</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC8044681/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PMC8044681_supplementaryFiles.zip</t>
+          <t>PMC12561102_fullText.xml</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -40236,12 +40276,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R03477</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R03477.evidence_xml.c127b68ddfdcfec8</t>
+          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -40251,20 +40291,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>c127b68ddfdcfec8d98508723d4d7a4b250ec3f82c4c75756cb539406519a8f7</t>
+          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>121650</v>
+        <v>256247</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC5371168/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>PMC5371168_fullText.xml</t>
+          <t>PMC12125087_fullText.xml</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -40276,35 +40316,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R08646.evidence_xml.c7b723e8020f6582</t>
+          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
+          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>304277</v>
+        <v>521862</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PMC10559078_fullText.xml</t>
+          <t>PMC12125087_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -40316,35 +40356,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
+          <t>R05213.evidence_xml.17894ab410001846</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>evidence_xml</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
+          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1539133</v>
+        <v>130954</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>PMC10559078_supplementaryFiles.zip</t>
+          <t>PMC6858683_fullText.xml</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -40356,35 +40396,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
+          <t>R05213.transport_archive.c61c88cf9fd489be</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
+          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>211630</v>
+        <v>1960371</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PMC11076452_fullText.xml</t>
+          <t>PMC6858683_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -40396,12 +40436,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R11503</t>
+          <t>R09585</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R11503.evidence_xml.4002d57be59c215c</t>
+          <t>R09585.evidence_xml.a3430f38fa1652de</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -40411,20 +40451,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
+          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>258637</v>
+        <v>100534</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PMC12561102_fullText.xml</t>
+          <t>PMC10609292_fullText.xml</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -40436,35 +40476,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R02274</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
+          <t>R02274.main.4c7da8384f1f6e3d</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
+          <t>4c7da8384f1f6e3d8bd2681eab23bdb95e3057009cf4c7ec7aacc7cdb9eaf43d</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>256247</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
-        </is>
-      </c>
+        <v>471480</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>PMC12125087_fullText.xml</t>
+          <t>R02274_2016_ANAEROBIC_DIGESTION_OF_WASTEWATER_WITH_HIGH_SULFATE_CONCENTRATION_USING.pdf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -40476,35 +40512,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
+          <t>R10086.main.84777bfb7a2cd42f</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
+          <t>84777bfb7a2cd42f9696e060fc79d5de3e72d5ad8fa1e222934a7fcdf97dd365</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>521862</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
-        </is>
-      </c>
+        <v>984310</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>PMC12125087_supplementaryFiles.zip</t>
+          <t>R10086_2024_Effect_of_micro-aeration_on_syntrophic_and_methanogenic_activity_in.pdf</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -40516,35 +40548,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R05213</t>
+          <t>R03477</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R05213.evidence_xml.17894ab410001846</t>
+          <t>R03477.main.79583f4a64fb2fbb</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
+          <t>79583f4a64fb2fbb4a1f4f471fe6001b159213acb1f3bbd19d6dc0be5c714fa5</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>130954</v>
+        <v>1714874</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
+          <t>https://link.springer.com/content/pdf/10.1186/s13568-017-0375-4.pdf</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PMC6858683_fullText.xml</t>
+          <t>R03477_2017_Pretreatment_methods_of_lignocellulosic_biomass_for_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -40556,35 +40588,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R05213</t>
+          <t>R09804</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R05213.transport_archive.c61c88cf9fd489be</t>
+          <t>R09804.main.b3cc83d613ad3c36</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
+          <t>b3cc83d613ad3c36f93b78eace000ebc5a603966523ee71c2e6a0bd85a8ede3e</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1960371</v>
+        <v>5135812</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
+          <t>https://link.springer.com/content/pdf/10.1186/s40643-024-00756-6.pdf</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PMC6858683_supplementaryFiles.zip</t>
+          <t>R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -40596,35 +40628,35 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>R09585</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R09585.evidence_xml.a3430f38fa1652de</t>
+          <t>R11844.main.c41816bf825167dc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
+          <t>c41816bf825167dcb78ff5eb81c8d0dab0d8d8110cd2a23a04cd1109acb34919</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100534</v>
+        <v>1333380</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
+          <t>https://link.springer.com/content/pdf/10.1007/s00253-025-13519-w.pdf</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>PMC10609292_fullText.xml</t>
+          <t>R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -40636,12 +40668,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>R02274</t>
+          <t>R03155</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R02274.main.4c7da8384f1f6e3d</t>
+          <t>R03155.main.2875ce0c137df622</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -40651,16 +40683,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4c7da8384f1f6e3d8bd2681eab23bdb95e3057009cf4c7ec7aacc7cdb9eaf43d</t>
+          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>471480</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
+        <v>5745828</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://dspace.lib.ntua.gr/xmlui/bitstream/handle/123456789/44237/Msc.%20Thesis_Aristotle_Vasileiou%20THE.pdf?sequence=1&amp;isAllowed=y</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>R02274_2016_ANAEROBIC_DIGESTION_OF_WASTEWATER_WITH_HIGH_SULFATE_CONCENTRATION_USING.pdf</t>
+          <t>R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -40672,12 +40708,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>R10086.main.84777bfb7a2cd42f</t>
+          <t>R05213.main.bcab84a15ce93062</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -40687,16 +40723,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>84777bfb7a2cd42f9696e060fc79d5de3e72d5ad8fa1e222934a7fcdf97dd365</t>
+          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>984310</v>
+        <v>1022660</v>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>R10086_2024_Effect_of_micro-aeration_on_syntrophic_and_methanogenic_activity_in.pdf</t>
+          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -40708,12 +40744,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>R03477</t>
+          <t>R06036</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>R03477.main.79583f4a64fb2fbb</t>
+          <t>R06036.main.0bdc7b19fdb70091</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -40723,20 +40759,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>79583f4a64fb2fbb4a1f4f471fe6001b159213acb1f3bbd19d6dc0be5c714fa5</t>
+          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1714874</v>
+        <v>927168</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1186/s13568-017-0375-4.pdf</t>
+          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>R03477_2017_Pretreatment_methods_of_lignocellulosic_biomass_for_anaerobic_digestion.pdf</t>
+          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -40748,12 +40784,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R09240</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R09804.main.b3cc83d613ad3c36</t>
+          <t>R09240.main.da8dbeb874b19b59</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -40763,20 +40799,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>b3cc83d613ad3c36f93b78eace000ebc5a603966523ee71c2e6a0bd85a8ede3e</t>
+          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5135812</v>
+        <v>1315227</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1186/s40643-024-00756-6.pdf</t>
+          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
+          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -40788,12 +40824,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R13899</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R11844.main.c41816bf825167dc</t>
+          <t>R13899.main.19143e56fa77ce99</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -40803,20 +40839,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>c41816bf825167dcb78ff5eb81c8d0dab0d8d8110cd2a23a04cd1109acb34919</t>
+          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1333380</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>https://link.springer.com/content/pdf/10.1007/s00253-025-13519-w.pdf</t>
-        </is>
-      </c>
+        <v>479092</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
+          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -40828,12 +40860,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R03155</t>
+          <t>R13955</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R03155.main.2875ce0c137df622</t>
+          <t>R13955.main.6714f79deccd703d</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -40843,215 +40875,23 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
+          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5745828</v>
+        <v>14662119</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://dspace.lib.ntua.gr/xmlui/bitstream/handle/123456789/44237/Msc.%20Thesis_Aristotle_Vasileiou%20THE.pdf?sequence=1&amp;isAllowed=y</t>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>R05213</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>R05213.main.bcab84a15ce93062</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>1022660</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>R06036</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>R06036.main.0bdc7b19fdb70091</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>927168</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>R09240</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>R09240.main.da8dbeb874b19b59</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>1315227</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>R13899</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>R13899.main.19143e56fa77ce99</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>479092</v>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>R13955</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>R13955.main.6714f79deccd703d</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>14662119</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
         <is>
           <t>历史已获取，当前原件未恢复</t>
         </is>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.263460+00:00</t>
+          <t>2026-10-17T08:47:55.904273+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.264440+00:00</t>
+          <t>2026-10-17T08:47:55.905189+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.264466+00:00</t>
+          <t>2026-10-17T08:47:55.905206+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.264689+00:00</t>
+          <t>2026-10-17T08:47:55.905435+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.266554+00:00</t>
+          <t>2026-10-17T08:47:55.906557+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.267038+00:00</t>
+          <t>2026-10-17T08:47:55.907155+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.272936+00:00</t>
+          <t>2026-10-17T08:47:55.912766+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.275352+00:00</t>
+          <t>2026-10-17T08:47:55.915129+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.276229+00:00</t>
+          <t>2026-10-17T08:47:55.916063+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.276579+00:00</t>
+          <t>2026-10-17T08:47:55.916401+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.277354+00:00</t>
+          <t>2026-10-17T08:47:55.917160+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.278024+00:00</t>
+          <t>2026-10-17T08:47:55.917831+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.278920+00:00</t>
+          <t>2026-10-17T08:47:55.918829+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.279160+00:00</t>
+          <t>2026-10-17T08:47:55.919137+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.280015+00:00</t>
+          <t>2026-10-17T08:47:55.920004+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.291564+00:00</t>
+          <t>2026-10-17T08:47:55.927635+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.292346+00:00</t>
+          <t>2026-10-17T08:47:55.928369+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.293622+00:00</t>
+          <t>2026-10-17T08:47:55.929842+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.298220+00:00</t>
+          <t>2026-10-17T08:47:55.932436+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.301384+00:00</t>
+          <t>2026-10-17T08:47:55.933531+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.302635+00:00</t>
+          <t>2026-10-17T08:47:55.934703+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.308945+00:00</t>
+          <t>2026-10-17T08:47:55.939437+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.312070+00:00</t>
+          <t>2026-10-17T08:47:55.941604+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.314750+00:00</t>
+          <t>2026-10-17T08:47:55.943391+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.315471+00:00</t>
+          <t>2026-10-17T08:47:55.944061+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.315852+00:00</t>
+          <t>2026-10-17T08:47:55.944434+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.318434+00:00</t>
+          <t>2026-10-17T08:47:55.946420+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.320099+00:00</t>
+          <t>2026-10-17T08:47:55.947791+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.322521+00:00</t>
+          <t>2026-10-17T08:47:55.949851+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.324802+00:00</t>
+          <t>2026-10-17T08:47:55.951799+00:00</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.325449+00:00</t>
+          <t>2026-10-17T08:47:55.952358+00:00</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.326088+00:00</t>
+          <t>2026-10-17T08:47:55.952900+00:00</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.328576+00:00</t>
+          <t>2026-10-17T08:47:55.954641+00:00</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.332358+00:00</t>
+          <t>2026-10-17T08:47:55.957651+00:00</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.334767+00:00</t>
+          <t>2026-10-17T08:47:55.959806+00:00</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.336120+00:00</t>
+          <t>2026-10-17T08:47:55.960997+00:00</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.339862+00:00</t>
+          <t>2026-10-17T08:47:55.963934+00:00</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.340720+00:00</t>
+          <t>2026-10-17T08:47:55.964748+00:00</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.342687+00:00</t>
+          <t>2026-10-17T08:47:55.966479+00:00</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.342979+00:00</t>
+          <t>2026-10-17T08:47:55.966802+00:00</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.344990+00:00</t>
+          <t>2026-10-17T08:47:55.968728+00:00</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.348730+00:00</t>
+          <t>2026-10-17T08:47:55.971648+00:00</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.350177+00:00</t>
+          <t>2026-10-17T08:47:55.972944+00:00</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.350829+00:00</t>
+          <t>2026-10-17T08:47:55.973514+00:00</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.354082+00:00</t>
+          <t>2026-10-17T08:47:55.976168+00:00</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.355377+00:00</t>
+          <t>2026-10-17T08:47:55.977366+00:00</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.359476+00:00</t>
+          <t>2026-10-17T08:47:55.981029+00:00</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.361780+00:00</t>
+          <t>2026-10-17T08:47:55.982778+00:00</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.364059+00:00</t>
+          <t>2026-10-17T08:47:55.984771+00:00</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.365555+00:00</t>
+          <t>2026-10-17T08:47:55.985843+00:00</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.366025+00:00</t>
+          <t>2026-10-17T08:47:55.986284+00:00</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.366546+00:00</t>
+          <t>2026-10-17T08:47:55.986664+00:00</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.368171+00:00</t>
+          <t>2026-10-17T08:47:55.988158+00:00</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.369665+00:00</t>
+          <t>2026-10-17T08:47:55.989444+00:00</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.371212+00:00</t>
+          <t>2026-10-17T08:47:55.990928+00:00</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.371627+00:00</t>
+          <t>2026-10-17T08:47:55.991256+00:00</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.372854+00:00</t>
+          <t>2026-10-17T08:47:55.992500+00:00</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.374225+00:00</t>
+          <t>2026-10-17T08:47:55.993959+00:00</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.375026+00:00</t>
+          <t>2026-10-17T08:47:55.994589+00:00</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.376090+00:00</t>
+          <t>2026-10-17T08:47:55.995547+00:00</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.376492+00:00</t>
+          <t>2026-10-17T08:47:55.995849+00:00</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.382317+00:00</t>
+          <t>2026-10-17T08:47:56.001013+00:00</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.382744+00:00</t>
+          <t>2026-10-17T08:47:56.001406+00:00</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.383315+00:00</t>
+          <t>2026-10-17T08:47:56.001994+00:00</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.383749+00:00</t>
+          <t>2026-10-17T08:47:56.002443+00:00</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.384890+00:00</t>
+          <t>2026-10-17T08:47:56.003493+00:00</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.388444+00:00</t>
+          <t>2026-10-17T08:47:56.006401+00:00</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.388718+00:00</t>
+          <t>2026-10-17T08:47:56.006633+00:00</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.393454+00:00</t>
+          <t>2026-10-17T08:47:56.010697+00:00</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.394373+00:00</t>
+          <t>2026-10-17T08:47:56.011473+00:00</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.396605+00:00</t>
+          <t>2026-10-17T08:47:56.013531+00:00</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.398474+00:00</t>
+          <t>2026-10-17T08:47:56.015354+00:00</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.399377+00:00</t>
+          <t>2026-10-17T08:47:56.016245+00:00</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.400957+00:00</t>
+          <t>2026-10-17T08:47:56.017666+00:00</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.404354+00:00</t>
+          <t>2026-10-17T08:47:56.019949+00:00</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.414817+00:00</t>
+          <t>2026-10-17T08:47:56.027962+00:00</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.416380+00:00</t>
+          <t>2026-10-17T08:47:56.029286+00:00</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.416555+00:00</t>
+          <t>2026-10-17T08:47:56.029496+00:00</t>
         </is>
       </c>
     </row>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.416569+00:00</t>
+          <t>2026-10-17T08:47:56.029513+00:00</t>
         </is>
       </c>
     </row>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.422145+00:00</t>
+          <t>2026-10-17T08:47:56.034484+00:00</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.422651+00:00</t>
+          <t>2026-10-17T08:47:56.035055+00:00</t>
         </is>
       </c>
     </row>
@@ -33071,7 +33071,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.423013+00:00</t>
+          <t>2026-10-17T08:47:56.035512+00:00</t>
         </is>
       </c>
     </row>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.423427+00:00</t>
+          <t>2026-10-17T08:47:56.035944+00:00</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.424126+00:00</t>
+          <t>2026-10-17T08:47:56.038194+00:00</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33383,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.425686+00:00</t>
+          <t>2026-10-17T08:47:56.039618+00:00</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.426539+00:00</t>
+          <t>2026-10-17T08:47:56.040679+00:00</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.426847+00:00</t>
+          <t>2026-10-17T08:47:56.041019+00:00</t>
         </is>
       </c>
     </row>
@@ -33699,7 +33699,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.427508+00:00</t>
+          <t>2026-10-17T08:47:56.042397+00:00</t>
         </is>
       </c>
     </row>
@@ -33799,7 +33799,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.427522+00:00</t>
+          <t>2026-10-17T08:47:56.042428+00:00</t>
         </is>
       </c>
     </row>
@@ -33907,7 +33907,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.427576+00:00</t>
+          <t>2026-10-17T08:47:56.042502+00:00</t>
         </is>
       </c>
     </row>
@@ -34015,7 +34015,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.427805+00:00</t>
+          <t>2026-10-17T08:47:56.042728+00:00</t>
         </is>
       </c>
     </row>
@@ -34123,7 +34123,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.427922+00:00</t>
+          <t>2026-10-17T08:47:56.042851+00:00</t>
         </is>
       </c>
     </row>
@@ -34235,7 +34235,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.428035+00:00</t>
+          <t>2026-10-17T08:47:56.043169+00:00</t>
         </is>
       </c>
     </row>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.428437+00:00</t>
+          <t>2026-10-17T08:47:56.043604+00:00</t>
         </is>
       </c>
     </row>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.428705+00:00</t>
+          <t>2026-10-17T08:47:56.043810+00:00</t>
         </is>
       </c>
     </row>
@@ -34563,7 +34563,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.428779+00:00</t>
+          <t>2026-10-17T08:47:56.043867+00:00</t>
         </is>
       </c>
     </row>
@@ -34675,7 +34675,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.428844+00:00</t>
+          <t>2026-10-17T08:47:56.043928+00:00</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.428986+00:00</t>
+          <t>2026-10-17T08:47:56.044068+00:00</t>
         </is>
       </c>
     </row>
@@ -34899,7 +34899,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.429032+00:00</t>
+          <t>2026-10-17T08:47:56.044115+00:00</t>
         </is>
       </c>
     </row>
@@ -35007,7 +35007,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.429673+00:00</t>
+          <t>2026-10-17T08:47:56.044617+00:00</t>
         </is>
       </c>
     </row>
@@ -35115,7 +35115,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.429754+00:00</t>
+          <t>2026-10-17T08:47:56.044676+00:00</t>
         </is>
       </c>
     </row>
@@ -35215,7 +35215,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.429766+00:00</t>
+          <t>2026-10-17T08:47:56.044687+00:00</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.439990+00:00</t>
+          <t>2026-10-17T08:47:56.058032+00:00</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.440064+00:00</t>
+          <t>2026-10-17T08:47:56.058127+00:00</t>
         </is>
       </c>
     </row>
@@ -35535,7 +35535,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.440174+00:00</t>
+          <t>2026-10-17T08:47:56.058434+00:00</t>
         </is>
       </c>
     </row>
@@ -35643,7 +35643,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.440466+00:00</t>
+          <t>2026-10-17T08:47:56.058709+00:00</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.441649+00:00</t>
+          <t>2026-10-17T08:47:56.060089+00:00</t>
         </is>
       </c>
     </row>
@@ -35853,7 +35853,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.441756+00:00</t>
+          <t>2026-10-17T08:47:56.060207+00:00</t>
         </is>
       </c>
     </row>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.441769+00:00</t>
+          <t>2026-10-17T08:47:56.060222+00:00</t>
         </is>
       </c>
     </row>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.441852+00:00</t>
+          <t>2026-10-17T08:47:56.060308+00:00</t>
         </is>
       </c>
     </row>
@@ -36151,7 +36151,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.441934+00:00</t>
+          <t>2026-10-17T08:47:56.060430+00:00</t>
         </is>
       </c>
     </row>
@@ -36253,7 +36253,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.442042+00:00</t>
+          <t>2026-10-17T08:47:56.060544+00:00</t>
         </is>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.442053+00:00</t>
+          <t>2026-10-17T08:47:56.060555+00:00</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.442273+00:00</t>
+          <t>2026-10-17T08:47:56.060706+00:00</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.442315+00:00</t>
+          <t>2026-10-17T08:47:56.060717+00:00</t>
         </is>
       </c>
     </row>
@@ -36645,7 +36645,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.442429+00:00</t>
+          <t>2026-10-17T08:47:56.060820+00:00</t>
         </is>
       </c>
     </row>
@@ -36739,7 +36739,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.442442+00:00</t>
+          <t>2026-10-17T08:47:56.060831+00:00</t>
         </is>
       </c>
     </row>
@@ -36841,7 +36841,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.442620+00:00</t>
+          <t>2026-10-17T08:47:56.060968+00:00</t>
         </is>
       </c>
     </row>
@@ -36935,7 +36935,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.442638+00:00</t>
+          <t>2026-10-17T08:47:56.060982+00:00</t>
         </is>
       </c>
     </row>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.442736+00:00</t>
+          <t>2026-10-17T08:47:56.061074+00:00</t>
         </is>
       </c>
     </row>
@@ -37139,7 +37139,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.442868+00:00</t>
+          <t>2026-10-17T08:47:56.061217+00:00</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.442879+00:00</t>
+          <t>2026-10-17T08:47:56.061230+00:00</t>
         </is>
       </c>
     </row>
@@ -37335,7 +37335,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.442999+00:00</t>
+          <t>2026-10-17T08:47:56.061444+00:00</t>
         </is>
       </c>
     </row>
@@ -37429,7 +37429,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.443009+00:00</t>
+          <t>2026-10-17T08:47:56.061462+00:00</t>
         </is>
       </c>
     </row>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.443112+00:00</t>
+          <t>2026-10-17T08:47:56.061629+00:00</t>
         </is>
       </c>
     </row>
@@ -37565,13 +37565,21 @@
           <t>papers/R08646/evidence/c7b723e8020f_PMC10559078_fullText.xml</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R08646/PMC10559078_fullText.xml</t>
+        </is>
+      </c>
       <c r="I127" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-supplements/R08646/evidence/PMC10559078_fullText.xml</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr"/>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/source_evidence/R08646/PMC10559078_fullText.xml</t>
+        </is>
+      </c>
       <c r="K127" t="inlineStr">
         <is>
           <t>xml</t>
@@ -37587,12 +37595,12 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -37625,7 +37633,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.443123+00:00</t>
+          <t>2026-10-17T08:47:56.061873+00:00</t>
         </is>
       </c>
     </row>
@@ -37719,7 +37727,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.443127+00:00</t>
+          <t>2026-10-17T08:47:56.061886+00:00</t>
         </is>
       </c>
     </row>
@@ -37753,13 +37761,21 @@
           <t>papers/R09804/evidence/2ca7af24c486_PMC11076452_fullText.xml</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R09804/PMC11076452_fullText.xml</t>
+        </is>
+      </c>
       <c r="I129" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-supplements/R09804/evidence/PMC11076452_fullText.xml</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr"/>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/source_evidence/R09804/PMC11076452_fullText.xml</t>
+        </is>
+      </c>
       <c r="K129" t="inlineStr">
         <is>
           <t>xml</t>
@@ -37775,12 +37791,12 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -37813,7 +37829,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.443131+00:00</t>
+          <t>2026-10-17T08:47:56.062047+00:00</t>
         </is>
       </c>
     </row>
@@ -37847,13 +37863,21 @@
           <t>papers/R11503/evidence/4002d57be59c_PMC12561102_fullText.xml</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R11503/PMC12561102_fullText.xml</t>
+        </is>
+      </c>
       <c r="I130" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-supplements/R11503/evidence/PMC12561102_fullText.xml</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr"/>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/source_evidence/R11503/PMC12561102_fullText.xml</t>
+        </is>
+      </c>
       <c r="K130" t="inlineStr">
         <is>
           <t>xml</t>
@@ -37869,12 +37893,12 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -37907,7 +37931,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.443134+00:00</t>
+          <t>2026-10-17T08:47:56.062307+00:00</t>
         </is>
       </c>
     </row>
@@ -37941,13 +37965,21 @@
           <t>papers/R11844/evidence/9c39d5f64ac0_PMC12125087_fullText.xml</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R11844/PMC12125087_fullText.xml</t>
+        </is>
+      </c>
       <c r="I131" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-supplements/R11844/evidence/PMC12125087_fullText.xml</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr"/>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/source_evidence/R11844/PMC12125087_fullText.xml</t>
+        </is>
+      </c>
       <c r="K131" t="inlineStr">
         <is>
           <t>xml</t>
@@ -37963,12 +37995,12 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -38001,7 +38033,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.443138+00:00</t>
+          <t>2026-10-17T08:47:56.062564+00:00</t>
         </is>
       </c>
     </row>
@@ -38095,7 +38127,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.443142+00:00</t>
+          <t>2026-10-17T08:47:56.062577+00:00</t>
         </is>
       </c>
     </row>
@@ -38129,13 +38161,21 @@
           <t>papers/R05213/evidence/17894ab41000_PMC6858683_fullText.xml</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R05213/PMC6858683_fullText.xml</t>
+        </is>
+      </c>
       <c r="I133" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-supplements/R05213/evidence/PMC6858683_fullText.xml</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr"/>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/source_evidence/R05213/PMC6858683_fullText.xml</t>
+        </is>
+      </c>
       <c r="K133" t="inlineStr">
         <is>
           <t>xml</t>
@@ -38151,12 +38191,12 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -38189,7 +38229,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.443146+00:00</t>
+          <t>2026-10-17T08:47:56.062688+00:00</t>
         </is>
       </c>
     </row>
@@ -38283,7 +38323,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.443149+00:00</t>
+          <t>2026-10-17T08:47:56.062699+00:00</t>
         </is>
       </c>
     </row>
@@ -38377,7 +38417,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.443152+00:00</t>
+          <t>2026-10-17T08:47:56.062704+00:00</t>
         </is>
       </c>
     </row>
@@ -38485,7 +38525,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.444269+00:00</t>
+          <t>2026-10-17T08:47:56.063910+00:00</t>
         </is>
       </c>
     </row>
@@ -38577,7 +38617,7 @@
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.455436+00:00</t>
+          <t>2026-10-17T08:47:56.075431+00:00</t>
         </is>
       </c>
     </row>
@@ -38665,7 +38705,7 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.455513+00:00</t>
+          <t>2026-10-17T08:47:56.075521+00:00</t>
         </is>
       </c>
     </row>
@@ -38753,7 +38793,7 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.455520+00:00</t>
+          <t>2026-10-17T08:47:56.075529+00:00</t>
         </is>
       </c>
     </row>
@@ -38845,7 +38885,7 @@
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.455523+00:00</t>
+          <t>2026-10-17T08:47:56.075533+00:00</t>
         </is>
       </c>
     </row>
@@ -38937,7 +38977,7 @@
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.455527+00:00</t>
+          <t>2026-10-17T08:47:56.075536+00:00</t>
         </is>
       </c>
     </row>
@@ -39029,7 +39069,7 @@
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.455531+00:00</t>
+          <t>2026-10-17T08:47:56.075540+00:00</t>
         </is>
       </c>
     </row>
@@ -39121,7 +39161,7 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.455535+00:00</t>
+          <t>2026-10-17T08:47:56.075544+00:00</t>
         </is>
       </c>
     </row>
@@ -39209,7 +39249,7 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.455538+00:00</t>
+          <t>2026-10-17T08:47:56.075548+00:00</t>
         </is>
       </c>
     </row>
@@ -39301,7 +39341,7 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.455542+00:00</t>
+          <t>2026-10-17T08:47:56.075552+00:00</t>
         </is>
       </c>
     </row>
@@ -39393,7 +39433,7 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.455545+00:00</t>
+          <t>2026-10-17T08:47:56.075555+00:00</t>
         </is>
       </c>
     </row>
@@ -39481,7 +39521,7 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.455548+00:00</t>
+          <t>2026-10-17T08:47:56.075559+00:00</t>
         </is>
       </c>
     </row>
@@ -39573,7 +39613,7 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-10-17T08:46:53.455551+00:00</t>
+          <t>2026-10-17T08:47:56.075562+00:00</t>
         </is>
       </c>
     </row>
@@ -39588,7 +39628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40121,30 +40161,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R08646.evidence_xml.c7b723e8020f6582</t>
+          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>c7b723e8020f65823eaf8b08c6b56c36aab85784bbef3b10c9a85a820b960d3a</t>
+          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>304277</v>
+        <v>1539133</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>PMC10559078_fullText.xml</t>
+          <t>PMC10559078_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -40156,12 +40196,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R08646</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R08646.transport_archive.ecda9ea461a3deb3</t>
+          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -40171,20 +40211,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ecda9ea461a3deb361931eb51186e88488c4d6ae284899e1feb1d611de42550a</t>
+          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1539133</v>
+        <v>521862</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10559078/supplementaryFiles</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>PMC10559078_supplementaryFiles.zip</t>
+          <t>PMC12125087_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -40196,35 +40236,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R09804.evidence_xml.2ca7af24c486ae9e</t>
+          <t>R05213.transport_archive.c61c88cf9fd489be</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>transport_archive</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2ca7af24c486ae9eb9c65682356964011c985b22a4a36f4ee07ea3a705c38951</t>
+          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>211630</v>
+        <v>1960371</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC11076452/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>PMC11076452_fullText.xml</t>
+          <t>PMC6858683_supplementaryFiles.zip</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -40236,12 +40276,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R11503</t>
+          <t>R09585</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R11503.evidence_xml.4002d57be59c215c</t>
+          <t>R09585.evidence_xml.a3430f38fa1652de</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -40251,20 +40291,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4002d57be59c215cea8477a4b667f20f9ffb09680e70af377a81ffae74b99801</t>
+          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>258637</v>
+        <v>100534</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12561102/fullTextXML</t>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PMC12561102_fullText.xml</t>
+          <t>PMC10609292_fullText.xml</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -40276,35 +40316,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R02274</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R11844.evidence_xml.9c39d5f64ac01253</t>
+          <t>R02274.main.4c7da8384f1f6e3d</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9c39d5f64ac01253c8bb4866ce3974997765b2d47e37641f3717e99e0d7f1f61</t>
+          <t>4c7da8384f1f6e3d8bd2681eab23bdb95e3057009cf4c7ec7aacc7cdb9eaf43d</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>256247</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/fullTextXML</t>
-        </is>
-      </c>
+        <v>471480</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>PMC12125087_fullText.xml</t>
+          <t>R02274_2016_ANAEROBIC_DIGESTION_OF_WASTEWATER_WITH_HIGH_SULFATE_CONCENTRATION_USING.pdf</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -40316,35 +40352,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R11844.transport_archive.60ef29cf0a557bf4</t>
+          <t>R10086.main.84777bfb7a2cd42f</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>60ef29cf0a557bf44838f4a3f45e2dbf1b1a2001547f5c0b976b48cc64c1b6d9</t>
+          <t>84777bfb7a2cd42f9696e060fc79d5de3e72d5ad8fa1e222934a7fcdf97dd365</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>521862</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12125087/supplementaryFiles</t>
-        </is>
-      </c>
+        <v>984310</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PMC12125087_supplementaryFiles.zip</t>
+          <t>R10086_2024_Effect_of_micro-aeration_on_syntrophic_and_methanogenic_activity_in.pdf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -40356,35 +40388,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R05213</t>
+          <t>R03477</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R05213.evidence_xml.17894ab410001846</t>
+          <t>R03477.main.79583f4a64fb2fbb</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>17894ab41000184655d2f9f9a0daa796981ab3658678c6b123eb9f3deb1bf45a</t>
+          <t>79583f4a64fb2fbb4a1f4f471fe6001b159213acb1f3bbd19d6dc0be5c714fa5</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>130954</v>
+        <v>1714874</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/fullTextXML</t>
+          <t>https://link.springer.com/content/pdf/10.1186/s13568-017-0375-4.pdf</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>PMC6858683_fullText.xml</t>
+          <t>R03477_2017_Pretreatment_methods_of_lignocellulosic_biomass_for_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -40396,35 +40428,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R05213</t>
+          <t>R09804</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R05213.transport_archive.c61c88cf9fd489be</t>
+          <t>R09804.main.b3cc83d613ad3c36</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>transport_archive</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>c61c88cf9fd489beab88c1b72bbfe5f13167f32c984b6dba6e48ba97c6136b7b</t>
+          <t>b3cc83d613ad3c36f93b78eace000ebc5a603966523ee71c2e6a0bd85a8ede3e</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1960371</v>
+        <v>5135812</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC6858683/supplementaryFiles</t>
+          <t>https://link.springer.com/content/pdf/10.1186/s40643-024-00756-6.pdf</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PMC6858683_supplementaryFiles.zip</t>
+          <t>R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -40436,35 +40468,35 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R09585</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R09585.evidence_xml.a3430f38fa1652de</t>
+          <t>R11844.main.c41816bf825167dc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
+          <t>c41816bf825167dcb78ff5eb81c8d0dab0d8d8110cd2a23a04cd1109acb34919</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100534</v>
+        <v>1333380</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
+          <t>https://link.springer.com/content/pdf/10.1007/s00253-025-13519-w.pdf</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PMC10609292_fullText.xml</t>
+          <t>R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -40476,12 +40508,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R02274</t>
+          <t>R03155</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R02274.main.4c7da8384f1f6e3d</t>
+          <t>R03155.main.2875ce0c137df622</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -40491,16 +40523,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4c7da8384f1f6e3d8bd2681eab23bdb95e3057009cf4c7ec7aacc7cdb9eaf43d</t>
+          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>471480</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
+        <v>5745828</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://dspace.lib.ntua.gr/xmlui/bitstream/handle/123456789/44237/Msc.%20Thesis_Aristotle_Vasileiou%20THE.pdf?sequence=1&amp;isAllowed=y</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>R02274_2016_ANAEROBIC_DIGESTION_OF_WASTEWATER_WITH_HIGH_SULFATE_CONCENTRATION_USING.pdf</t>
+          <t>R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -40512,12 +40548,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R10086.main.84777bfb7a2cd42f</t>
+          <t>R05213.main.bcab84a15ce93062</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -40527,16 +40563,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>84777bfb7a2cd42f9696e060fc79d5de3e72d5ad8fa1e222934a7fcdf97dd365</t>
+          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>984310</v>
+        <v>1022660</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>R10086_2024_Effect_of_micro-aeration_on_syntrophic_and_methanogenic_activity_in.pdf</t>
+          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -40548,12 +40584,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R03477</t>
+          <t>R06036</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R03477.main.79583f4a64fb2fbb</t>
+          <t>R06036.main.0bdc7b19fdb70091</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -40563,20 +40599,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>79583f4a64fb2fbb4a1f4f471fe6001b159213acb1f3bbd19d6dc0be5c714fa5</t>
+          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1714874</v>
+        <v>927168</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1186/s13568-017-0375-4.pdf</t>
+          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>R03477_2017_Pretreatment_methods_of_lignocellulosic_biomass_for_anaerobic_digestion.pdf</t>
+          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -40588,12 +40624,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R09240</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R09804.main.b3cc83d613ad3c36</t>
+          <t>R09240.main.da8dbeb874b19b59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -40603,20 +40639,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>b3cc83d613ad3c36f93b78eace000ebc5a603966523ee71c2e6a0bd85a8ede3e</t>
+          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5135812</v>
+        <v>1315227</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1186/s40643-024-00756-6.pdf</t>
+          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
+          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -40628,12 +40664,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R13899</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R11844.main.c41816bf825167dc</t>
+          <t>R13899.main.19143e56fa77ce99</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -40643,20 +40679,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>c41816bf825167dcb78ff5eb81c8d0dab0d8d8110cd2a23a04cd1109acb34919</t>
+          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1333380</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>https://link.springer.com/content/pdf/10.1007/s00253-025-13519-w.pdf</t>
-        </is>
-      </c>
+        <v>479092</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
+          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -40668,12 +40700,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>R03155</t>
+          <t>R13955</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R03155.main.2875ce0c137df622</t>
+          <t>R13955.main.6714f79deccd703d</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -40683,215 +40715,23 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
+          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5745828</v>
+        <v>14662119</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://dspace.lib.ntua.gr/xmlui/bitstream/handle/123456789/44237/Msc.%20Thesis_Aristotle_Vasileiou%20THE.pdf?sequence=1&amp;isAllowed=y</t>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>R05213</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>R05213.main.bcab84a15ce93062</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>1022660</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>R06036</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>R06036.main.0bdc7b19fdb70091</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>927168</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>R09240</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>R09240.main.da8dbeb874b19b59</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>1315227</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>R13899</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>R13899.main.19143e56fa77ce99</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>479092</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>R13955</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>R13955.main.6714f79deccd703d</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>14662119</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
         <is>
           <t>历史已获取，当前原件未恢复</t>
         </is>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.904273+00:00</t>
+          <t>2026-10-17T08:48:34.414866+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.905189+00:00</t>
+          <t>2026-10-17T08:48:34.415826+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.905206+00:00</t>
+          <t>2026-10-17T08:48:34.415848+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.905435+00:00</t>
+          <t>2026-10-17T08:48:34.416068+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.906557+00:00</t>
+          <t>2026-10-17T08:48:34.417185+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.907155+00:00</t>
+          <t>2026-10-17T08:48:34.417701+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.912766+00:00</t>
+          <t>2026-10-17T08:48:34.423229+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.915129+00:00</t>
+          <t>2026-10-17T08:48:34.425700+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.916063+00:00</t>
+          <t>2026-10-17T08:48:34.426638+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.916401+00:00</t>
+          <t>2026-10-17T08:48:34.426969+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.917160+00:00</t>
+          <t>2026-10-17T08:48:34.427726+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.917831+00:00</t>
+          <t>2026-10-17T08:48:34.428415+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.918829+00:00</t>
+          <t>2026-10-17T08:48:34.429377+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.919137+00:00</t>
+          <t>2026-10-17T08:48:34.429633+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.920004+00:00</t>
+          <t>2026-10-17T08:48:34.430500+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.927635+00:00</t>
+          <t>2026-10-17T08:48:34.438320+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.928369+00:00</t>
+          <t>2026-10-17T08:48:34.439036+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.929842+00:00</t>
+          <t>2026-10-17T08:48:34.440353+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.932436+00:00</t>
+          <t>2026-10-17T08:48:34.442916+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.933531+00:00</t>
+          <t>2026-10-17T08:48:34.444073+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.934703+00:00</t>
+          <t>2026-10-17T08:48:34.445378+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.939437+00:00</t>
+          <t>2026-10-17T08:48:34.449469+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.941604+00:00</t>
+          <t>2026-10-17T08:48:34.451649+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.943391+00:00</t>
+          <t>2026-10-17T08:48:34.453524+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.944061+00:00</t>
+          <t>2026-10-17T08:48:34.454218+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.944434+00:00</t>
+          <t>2026-10-17T08:48:34.454627+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.946420+00:00</t>
+          <t>2026-10-17T08:48:34.456619+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.947791+00:00</t>
+          <t>2026-10-17T08:48:34.457877+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.949851+00:00</t>
+          <t>2026-10-17T08:48:34.460092+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.951799+00:00</t>
+          <t>2026-10-17T08:48:34.462188+00:00</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.952358+00:00</t>
+          <t>2026-10-17T08:48:34.462778+00:00</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.952900+00:00</t>
+          <t>2026-10-17T08:48:34.463360+00:00</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.954641+00:00</t>
+          <t>2026-10-17T08:48:34.464957+00:00</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.957651+00:00</t>
+          <t>2026-10-17T08:48:34.467972+00:00</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.959806+00:00</t>
+          <t>2026-10-17T08:48:34.470166+00:00</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.960997+00:00</t>
+          <t>2026-10-17T08:48:34.471690+00:00</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.963934+00:00</t>
+          <t>2026-10-17T08:48:34.474676+00:00</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.964748+00:00</t>
+          <t>2026-10-17T08:48:34.475380+00:00</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.966479+00:00</t>
+          <t>2026-10-17T08:48:34.477020+00:00</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.966802+00:00</t>
+          <t>2026-10-17T08:48:34.477279+00:00</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.968728+00:00</t>
+          <t>2026-10-17T08:48:34.479228+00:00</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.971648+00:00</t>
+          <t>2026-10-17T08:48:34.482113+00:00</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.972944+00:00</t>
+          <t>2026-10-17T08:48:34.483686+00:00</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.973514+00:00</t>
+          <t>2026-10-17T08:48:34.484226+00:00</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.976168+00:00</t>
+          <t>2026-10-17T08:48:34.486927+00:00</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.977366+00:00</t>
+          <t>2026-10-17T08:48:34.488074+00:00</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.981029+00:00</t>
+          <t>2026-10-17T08:48:34.491491+00:00</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.982778+00:00</t>
+          <t>2026-10-17T08:48:34.493124+00:00</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.984771+00:00</t>
+          <t>2026-10-17T08:48:34.494971+00:00</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.985843+00:00</t>
+          <t>2026-10-17T08:48:34.496068+00:00</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.986284+00:00</t>
+          <t>2026-10-17T08:48:34.496533+00:00</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.986664+00:00</t>
+          <t>2026-10-17T08:48:34.498029+00:00</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.988158+00:00</t>
+          <t>2026-10-17T08:48:34.499591+00:00</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.989444+00:00</t>
+          <t>2026-10-17T08:48:34.500972+00:00</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.990928+00:00</t>
+          <t>2026-10-17T08:48:34.502676+00:00</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.991256+00:00</t>
+          <t>2026-10-17T08:48:34.503027+00:00</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.992500+00:00</t>
+          <t>2026-10-17T08:48:34.504169+00:00</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.993959+00:00</t>
+          <t>2026-10-17T08:48:34.505592+00:00</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.994589+00:00</t>
+          <t>2026-10-17T08:48:34.506246+00:00</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.995547+00:00</t>
+          <t>2026-10-17T08:48:34.507262+00:00</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:55.995849+00:00</t>
+          <t>2026-10-17T08:48:34.507614+00:00</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.001013+00:00</t>
+          <t>2026-10-17T08:48:34.512772+00:00</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.001406+00:00</t>
+          <t>2026-10-17T08:48:34.513182+00:00</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.001994+00:00</t>
+          <t>2026-10-17T08:48:34.513808+00:00</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.002443+00:00</t>
+          <t>2026-10-17T08:48:34.514255+00:00</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.003493+00:00</t>
+          <t>2026-10-17T08:48:34.515453+00:00</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.006401+00:00</t>
+          <t>2026-10-17T08:48:34.518479+00:00</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.006633+00:00</t>
+          <t>2026-10-17T08:48:34.518729+00:00</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.010697+00:00</t>
+          <t>2026-10-17T08:48:34.523058+00:00</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.011473+00:00</t>
+          <t>2026-10-17T08:48:34.523855+00:00</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.013531+00:00</t>
+          <t>2026-10-17T08:48:34.526042+00:00</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.015354+00:00</t>
+          <t>2026-10-17T08:48:34.528362+00:00</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.016245+00:00</t>
+          <t>2026-10-17T08:48:34.529282+00:00</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.017666+00:00</t>
+          <t>2026-10-17T08:48:34.530725+00:00</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.019949+00:00</t>
+          <t>2026-10-17T08:48:34.533011+00:00</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.027962+00:00</t>
+          <t>2026-10-17T08:48:34.540949+00:00</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.029286+00:00</t>
+          <t>2026-10-17T08:48:34.542264+00:00</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.029496+00:00</t>
+          <t>2026-10-17T08:48:34.542426+00:00</t>
         </is>
       </c>
     </row>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.029513+00:00</t>
+          <t>2026-10-17T08:48:34.542439+00:00</t>
         </is>
       </c>
     </row>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.034484+00:00</t>
+          <t>2026-10-17T08:48:34.547286+00:00</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.035055+00:00</t>
+          <t>2026-10-17T08:48:34.547660+00:00</t>
         </is>
       </c>
     </row>
@@ -33071,7 +33071,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.035512+00:00</t>
+          <t>2026-10-17T08:48:34.548019+00:00</t>
         </is>
       </c>
     </row>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.035944+00:00</t>
+          <t>2026-10-17T08:48:34.548447+00:00</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.038194+00:00</t>
+          <t>2026-10-17T08:48:34.549132+00:00</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33383,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.039618+00:00</t>
+          <t>2026-10-17T08:48:34.550533+00:00</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.040679+00:00</t>
+          <t>2026-10-17T08:48:34.551393+00:00</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.041019+00:00</t>
+          <t>2026-10-17T08:48:34.551702+00:00</t>
         </is>
       </c>
     </row>
@@ -33699,7 +33699,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.042397+00:00</t>
+          <t>2026-10-17T08:48:34.552347+00:00</t>
         </is>
       </c>
     </row>
@@ -33799,7 +33799,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.042428+00:00</t>
+          <t>2026-10-17T08:48:34.552361+00:00</t>
         </is>
       </c>
     </row>
@@ -33907,7 +33907,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.042502+00:00</t>
+          <t>2026-10-17T08:48:34.552413+00:00</t>
         </is>
       </c>
     </row>
@@ -34015,7 +34015,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.042728+00:00</t>
+          <t>2026-10-17T08:48:34.552629+00:00</t>
         </is>
       </c>
     </row>
@@ -34123,7 +34123,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.042851+00:00</t>
+          <t>2026-10-17T08:48:34.552744+00:00</t>
         </is>
       </c>
     </row>
@@ -34235,7 +34235,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.043169+00:00</t>
+          <t>2026-10-17T08:48:34.552857+00:00</t>
         </is>
       </c>
     </row>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.043604+00:00</t>
+          <t>2026-10-17T08:48:34.553234+00:00</t>
         </is>
       </c>
     </row>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.043810+00:00</t>
+          <t>2026-10-17T08:48:34.553446+00:00</t>
         </is>
       </c>
     </row>
@@ -34563,7 +34563,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.043867+00:00</t>
+          <t>2026-10-17T08:48:34.553532+00:00</t>
         </is>
       </c>
     </row>
@@ -34675,7 +34675,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.043928+00:00</t>
+          <t>2026-10-17T08:48:34.553595+00:00</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.044068+00:00</t>
+          <t>2026-10-17T08:48:34.553741+00:00</t>
         </is>
       </c>
     </row>
@@ -34899,7 +34899,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.044115+00:00</t>
+          <t>2026-10-17T08:48:34.553791+00:00</t>
         </is>
       </c>
     </row>
@@ -35007,7 +35007,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.044617+00:00</t>
+          <t>2026-10-17T08:48:34.554245+00:00</t>
         </is>
       </c>
     </row>
@@ -35115,7 +35115,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.044676+00:00</t>
+          <t>2026-10-17T08:48:34.554329+00:00</t>
         </is>
       </c>
     </row>
@@ -35215,7 +35215,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.044687+00:00</t>
+          <t>2026-10-17T08:48:34.554341+00:00</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.058032+00:00</t>
+          <t>2026-10-17T08:48:34.564175+00:00</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.058127+00:00</t>
+          <t>2026-10-17T08:48:34.564239+00:00</t>
         </is>
       </c>
     </row>
@@ -35535,7 +35535,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.058434+00:00</t>
+          <t>2026-10-17T08:48:34.564367+00:00</t>
         </is>
       </c>
     </row>
@@ -35643,7 +35643,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.058709+00:00</t>
+          <t>2026-10-17T08:48:34.564600+00:00</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.060089+00:00</t>
+          <t>2026-10-17T08:48:34.565688+00:00</t>
         </is>
       </c>
     </row>
@@ -35853,7 +35853,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.060207+00:00</t>
+          <t>2026-10-17T08:48:34.565772+00:00</t>
         </is>
       </c>
     </row>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.060222+00:00</t>
+          <t>2026-10-17T08:48:34.565783+00:00</t>
         </is>
       </c>
     </row>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.060308+00:00</t>
+          <t>2026-10-17T08:48:34.565861+00:00</t>
         </is>
       </c>
     </row>
@@ -36151,7 +36151,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.060430+00:00</t>
+          <t>2026-10-17T08:48:34.565943+00:00</t>
         </is>
       </c>
     </row>
@@ -36253,7 +36253,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.060544+00:00</t>
+          <t>2026-10-17T08:48:34.566050+00:00</t>
         </is>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.060555+00:00</t>
+          <t>2026-10-17T08:48:34.566061+00:00</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.060706+00:00</t>
+          <t>2026-10-17T08:48:34.566213+00:00</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.060717+00:00</t>
+          <t>2026-10-17T08:48:34.566224+00:00</t>
         </is>
       </c>
     </row>
@@ -36645,7 +36645,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.060820+00:00</t>
+          <t>2026-10-17T08:48:34.566346+00:00</t>
         </is>
       </c>
     </row>
@@ -36739,7 +36739,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.060831+00:00</t>
+          <t>2026-10-17T08:48:34.566358+00:00</t>
         </is>
       </c>
     </row>
@@ -36841,7 +36841,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.060968+00:00</t>
+          <t>2026-10-17T08:48:34.566495+00:00</t>
         </is>
       </c>
     </row>
@@ -36935,7 +36935,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.060982+00:00</t>
+          <t>2026-10-17T08:48:34.566507+00:00</t>
         </is>
       </c>
     </row>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.061074+00:00</t>
+          <t>2026-10-17T08:48:34.566598+00:00</t>
         </is>
       </c>
     </row>
@@ -37139,7 +37139,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.061217+00:00</t>
+          <t>2026-10-17T08:48:34.566735+00:00</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.061230+00:00</t>
+          <t>2026-10-17T08:48:34.566747+00:00</t>
         </is>
       </c>
     </row>
@@ -37335,7 +37335,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.061444+00:00</t>
+          <t>2026-10-17T08:48:34.566871+00:00</t>
         </is>
       </c>
     </row>
@@ -37429,7 +37429,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.061462+00:00</t>
+          <t>2026-10-17T08:48:34.566882+00:00</t>
         </is>
       </c>
     </row>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.061629+00:00</t>
+          <t>2026-10-17T08:48:34.566983+00:00</t>
         </is>
       </c>
     </row>
@@ -37633,7 +37633,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.061873+00:00</t>
+          <t>2026-10-17T08:48:34.567221+00:00</t>
         </is>
       </c>
     </row>
@@ -37727,7 +37727,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.061886+00:00</t>
+          <t>2026-10-17T08:48:34.567233+00:00</t>
         </is>
       </c>
     </row>
@@ -37829,7 +37829,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.062047+00:00</t>
+          <t>2026-10-17T08:48:34.567413+00:00</t>
         </is>
       </c>
     </row>
@@ -37931,7 +37931,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.062307+00:00</t>
+          <t>2026-10-17T08:48:34.567618+00:00</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38033,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.062564+00:00</t>
+          <t>2026-10-17T08:48:34.567809+00:00</t>
         </is>
       </c>
     </row>
@@ -38127,7 +38127,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.062577+00:00</t>
+          <t>2026-10-17T08:48:34.567820+00:00</t>
         </is>
       </c>
     </row>
@@ -38229,7 +38229,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.062688+00:00</t>
+          <t>2026-10-17T08:48:34.567928+00:00</t>
         </is>
       </c>
     </row>
@@ -38323,7 +38323,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.062699+00:00</t>
+          <t>2026-10-17T08:48:34.567938+00:00</t>
         </is>
       </c>
     </row>
@@ -38357,13 +38357,21 @@
           <t>papers/R09585/evidence/a3430f38fa16_PMC10609292_fullText.xml</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R09585/PMC10609292_fullText.xml</t>
+        </is>
+      </c>
       <c r="I135" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-supplements/R09585/evidence/PMC10609292_fullText.xml</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr"/>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/source_evidence/R09585/PMC10609292_fullText.xml</t>
+        </is>
+      </c>
       <c r="K135" t="inlineStr">
         <is>
           <t>xml</t>
@@ -38379,12 +38387,12 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -38417,7 +38425,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.062704+00:00</t>
+          <t>2026-10-17T08:48:34.568038+00:00</t>
         </is>
       </c>
     </row>
@@ -38525,7 +38533,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.063910+00:00</t>
+          <t>2026-10-17T08:48:34.569082+00:00</t>
         </is>
       </c>
     </row>
@@ -38617,7 +38625,7 @@
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.075431+00:00</t>
+          <t>2026-10-17T08:48:34.578938+00:00</t>
         </is>
       </c>
     </row>
@@ -38705,7 +38713,7 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.075521+00:00</t>
+          <t>2026-10-17T08:48:34.579000+00:00</t>
         </is>
       </c>
     </row>
@@ -38793,7 +38801,7 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.075529+00:00</t>
+          <t>2026-10-17T08:48:34.579006+00:00</t>
         </is>
       </c>
     </row>
@@ -38885,7 +38893,7 @@
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.075533+00:00</t>
+          <t>2026-10-17T08:48:34.579011+00:00</t>
         </is>
       </c>
     </row>
@@ -38977,7 +38985,7 @@
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.075536+00:00</t>
+          <t>2026-10-17T08:48:34.579014+00:00</t>
         </is>
       </c>
     </row>
@@ -39069,7 +39077,7 @@
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.075540+00:00</t>
+          <t>2026-10-17T08:48:34.579018+00:00</t>
         </is>
       </c>
     </row>
@@ -39161,7 +39169,7 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.075544+00:00</t>
+          <t>2026-10-17T08:48:34.579022+00:00</t>
         </is>
       </c>
     </row>
@@ -39249,7 +39257,7 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.075548+00:00</t>
+          <t>2026-10-17T08:48:34.579025+00:00</t>
         </is>
       </c>
     </row>
@@ -39341,7 +39349,7 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.075552+00:00</t>
+          <t>2026-10-17T08:48:34.579029+00:00</t>
         </is>
       </c>
     </row>
@@ -39433,7 +39441,7 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.075555+00:00</t>
+          <t>2026-10-17T08:48:34.579033+00:00</t>
         </is>
       </c>
     </row>
@@ -39521,7 +39529,7 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.075559+00:00</t>
+          <t>2026-10-17T08:48:34.579036+00:00</t>
         </is>
       </c>
     </row>
@@ -39613,7 +39621,7 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-10-17T08:47:56.075562+00:00</t>
+          <t>2026-10-17T08:48:34.579041+00:00</t>
         </is>
       </c>
     </row>
@@ -39628,7 +39636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40276,35 +40284,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R09585</t>
+          <t>R02274</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R09585.evidence_xml.a3430f38fa1652de</t>
+          <t>R02274.main.4c7da8384f1f6e3d</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>evidence_xml</t>
+          <t>main</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>a3430f38fa1652de3145ffc47f0da514ee41e12ef8e95acc30330d6b3a01efd2</t>
+          <t>4c7da8384f1f6e3d8bd2681eab23bdb95e3057009cf4c7ec7aacc7cdb9eaf43d</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100534</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC10609292/fullTextXML</t>
-        </is>
-      </c>
+        <v>471480</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>PMC10609292_fullText.xml</t>
+          <t>R02274_2016_ANAEROBIC_DIGESTION_OF_WASTEWATER_WITH_HIGH_SULFATE_CONCENTRATION_USING.pdf</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -40316,12 +40320,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R02274</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R02274.main.4c7da8384f1f6e3d</t>
+          <t>R10086.main.84777bfb7a2cd42f</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -40331,16 +40335,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4c7da8384f1f6e3d8bd2681eab23bdb95e3057009cf4c7ec7aacc7cdb9eaf43d</t>
+          <t>84777bfb7a2cd42f9696e060fc79d5de3e72d5ad8fa1e222934a7fcdf97dd365</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>471480</v>
+        <v>984310</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>R02274_2016_ANAEROBIC_DIGESTION_OF_WASTEWATER_WITH_HIGH_SULFATE_CONCENTRATION_USING.pdf</t>
+          <t>R10086_2024_Effect_of_micro-aeration_on_syntrophic_and_methanogenic_activity_in.pdf</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -40352,12 +40356,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R03477</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R10086.main.84777bfb7a2cd42f</t>
+          <t>R03477.main.79583f4a64fb2fbb</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -40367,16 +40371,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>84777bfb7a2cd42f9696e060fc79d5de3e72d5ad8fa1e222934a7fcdf97dd365</t>
+          <t>79583f4a64fb2fbb4a1f4f471fe6001b159213acb1f3bbd19d6dc0be5c714fa5</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>984310</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
+        <v>1714874</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/content/pdf/10.1186/s13568-017-0375-4.pdf</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>R10086_2024_Effect_of_micro-aeration_on_syntrophic_and_methanogenic_activity_in.pdf</t>
+          <t>R03477_2017_Pretreatment_methods_of_lignocellulosic_biomass_for_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -40388,12 +40396,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R03477</t>
+          <t>R09804</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R03477.main.79583f4a64fb2fbb</t>
+          <t>R09804.main.b3cc83d613ad3c36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -40403,20 +40411,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>79583f4a64fb2fbb4a1f4f471fe6001b159213acb1f3bbd19d6dc0be5c714fa5</t>
+          <t>b3cc83d613ad3c36f93b78eace000ebc5a603966523ee71c2e6a0bd85a8ede3e</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1714874</v>
+        <v>5135812</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1186/s13568-017-0375-4.pdf</t>
+          <t>https://link.springer.com/content/pdf/10.1186/s40643-024-00756-6.pdf</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>R03477_2017_Pretreatment_methods_of_lignocellulosic_biomass_for_anaerobic_digestion.pdf</t>
+          <t>R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -40428,12 +40436,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R09804.main.b3cc83d613ad3c36</t>
+          <t>R11844.main.c41816bf825167dc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -40443,20 +40451,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>b3cc83d613ad3c36f93b78eace000ebc5a603966523ee71c2e6a0bd85a8ede3e</t>
+          <t>c41816bf825167dcb78ff5eb81c8d0dab0d8d8110cd2a23a04cd1109acb34919</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5135812</v>
+        <v>1333380</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1186/s40643-024-00756-6.pdf</t>
+          <t>https://link.springer.com/content/pdf/10.1007/s00253-025-13519-w.pdf</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
+          <t>R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -40468,12 +40476,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R03155</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R11844.main.c41816bf825167dc</t>
+          <t>R03155.main.2875ce0c137df622</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -40483,20 +40491,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>c41816bf825167dcb78ff5eb81c8d0dab0d8d8110cd2a23a04cd1109acb34919</t>
+          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1333380</v>
+        <v>5745828</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1007/s00253-025-13519-w.pdf</t>
+          <t>https://dspace.lib.ntua.gr/xmlui/bitstream/handle/123456789/44237/Msc.%20Thesis_Aristotle_Vasileiou%20THE.pdf?sequence=1&amp;isAllowed=y</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
+          <t>R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -40508,12 +40516,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R03155</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R03155.main.2875ce0c137df622</t>
+          <t>R05213.main.bcab84a15ce93062</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -40523,20 +40531,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
+          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5745828</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>https://dspace.lib.ntua.gr/xmlui/bitstream/handle/123456789/44237/Msc.%20Thesis_Aristotle_Vasileiou%20THE.pdf?sequence=1&amp;isAllowed=y</t>
-        </is>
-      </c>
+        <v>1022660</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
+          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -40548,12 +40552,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R05213</t>
+          <t>R06036</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R05213.main.bcab84a15ce93062</t>
+          <t>R06036.main.0bdc7b19fdb70091</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -40563,16 +40567,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
+          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1022660</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
+        <v>927168</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
+          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -40584,12 +40592,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R06036</t>
+          <t>R09240</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R06036.main.0bdc7b19fdb70091</t>
+          <t>R09240.main.da8dbeb874b19b59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -40599,20 +40607,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
+          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>927168</v>
+        <v>1315227</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
+          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
+          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -40624,12 +40632,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R09240</t>
+          <t>R13899</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R09240.main.da8dbeb874b19b59</t>
+          <t>R13899.main.19143e56fa77ce99</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -40639,20 +40647,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
+          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1315227</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
-        </is>
-      </c>
+        <v>479092</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
+          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -40664,12 +40668,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>R13899</t>
+          <t>R13955</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R13899.main.19143e56fa77ce99</t>
+          <t>R13955.main.6714f79deccd703d</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -40679,59 +40683,23 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
+          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>479092</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
+        <v>14662119</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>R13955</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>R13955.main.6714f79deccd703d</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>14662119</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
         <is>
           <t>历史已获取，当前原件未恢复</t>
         </is>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="H22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -1616,11 +1616,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>explicit_no_attachments_in_complete_JATS</t>
         </is>
       </c>
       <c r="H28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2218,11 +2218,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>explicit_no_attachments_in_complete_JATS</t>
         </is>
       </c>
       <c r="H42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="H61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
         <v>1</v>
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="H64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
         <v>1</v>
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.414866+00:00</t>
+          <t>2026-10-17T08:49:38.773058+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.415826+00:00</t>
+          <t>2026-10-17T08:49:38.773987+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.415848+00:00</t>
+          <t>2026-10-17T08:49:38.774012+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.416068+00:00</t>
+          <t>2026-10-17T08:49:38.774282+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.417185+00:00</t>
+          <t>2026-10-17T08:49:38.775405+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.417701+00:00</t>
+          <t>2026-10-17T08:49:38.775847+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.423229+00:00</t>
+          <t>2026-10-17T08:49:38.780860+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.425700+00:00</t>
+          <t>2026-10-17T08:49:38.783071+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.426638+00:00</t>
+          <t>2026-10-17T08:49:38.783936+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.426969+00:00</t>
+          <t>2026-10-17T08:49:38.784244+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.427726+00:00</t>
+          <t>2026-10-17T08:49:38.785018+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.428415+00:00</t>
+          <t>2026-10-17T08:49:38.785738+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.429377+00:00</t>
+          <t>2026-10-17T08:49:38.786652+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.429633+00:00</t>
+          <t>2026-10-17T08:49:38.786886+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.430500+00:00</t>
+          <t>2026-10-17T08:49:38.787746+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.438320+00:00</t>
+          <t>2026-10-17T08:49:38.795817+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.439036+00:00</t>
+          <t>2026-10-17T08:49:38.796540+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.440353+00:00</t>
+          <t>2026-10-17T08:49:38.797745+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.442916+00:00</t>
+          <t>2026-10-17T08:49:38.800301+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.444073+00:00</t>
+          <t>2026-10-17T08:49:38.801379+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.445378+00:00</t>
+          <t>2026-10-17T08:49:38.802577+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.449469+00:00</t>
+          <t>2026-10-17T08:49:38.806712+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.451649+00:00</t>
+          <t>2026-10-17T08:49:38.808860+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.453524+00:00</t>
+          <t>2026-10-17T08:49:38.810686+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.454218+00:00</t>
+          <t>2026-10-17T08:49:38.811335+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.454627+00:00</t>
+          <t>2026-10-17T08:49:38.811683+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.456619+00:00</t>
+          <t>2026-10-17T08:49:38.813757+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.457877+00:00</t>
+          <t>2026-10-17T08:49:38.814984+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.460092+00:00</t>
+          <t>2026-10-17T08:49:38.817017+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.462188+00:00</t>
+          <t>2026-10-17T08:49:38.818973+00:00</t>
         </is>
       </c>
     </row>
@@ -27542,7 +27542,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -27579,7 +27579,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.462778+00:00</t>
+          <t>2026-10-17T08:49:38.819681+00:00</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.463360+00:00</t>
+          <t>2026-10-17T08:49:38.820250+00:00</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.464957+00:00</t>
+          <t>2026-10-17T08:49:38.821884+00:00</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.467972+00:00</t>
+          <t>2026-10-17T08:49:38.824676+00:00</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.470166+00:00</t>
+          <t>2026-10-17T08:49:38.826766+00:00</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.471690+00:00</t>
+          <t>2026-10-17T08:49:38.827952+00:00</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.474676+00:00</t>
+          <t>2026-10-17T08:49:38.830825+00:00</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.475380+00:00</t>
+          <t>2026-10-17T08:49:38.831526+00:00</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.477020+00:00</t>
+          <t>2026-10-17T08:49:38.833417+00:00</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.477279+00:00</t>
+          <t>2026-10-17T08:49:38.833701+00:00</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.479228+00:00</t>
+          <t>2026-10-17T08:49:38.835570+00:00</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.482113+00:00</t>
+          <t>2026-10-17T08:49:38.838376+00:00</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.483686+00:00</t>
+          <t>2026-10-17T08:49:38.839805+00:00</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.484226+00:00</t>
+          <t>2026-10-17T08:49:38.840363+00:00</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.486927+00:00</t>
+          <t>2026-10-17T08:49:38.843205+00:00</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.488074+00:00</t>
+          <t>2026-10-17T08:49:38.844425+00:00</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.491491+00:00</t>
+          <t>2026-10-17T08:49:38.847816+00:00</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.493124+00:00</t>
+          <t>2026-10-17T08:49:38.849521+00:00</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.494971+00:00</t>
+          <t>2026-10-17T08:49:38.851333+00:00</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.496068+00:00</t>
+          <t>2026-10-17T08:49:38.852320+00:00</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.496533+00:00</t>
+          <t>2026-10-17T08:49:38.852755+00:00</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.498029+00:00</t>
+          <t>2026-10-17T08:49:38.853110+00:00</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.499591+00:00</t>
+          <t>2026-10-17T08:49:38.854589+00:00</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.500972+00:00</t>
+          <t>2026-10-17T08:49:38.856074+00:00</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.502676+00:00</t>
+          <t>2026-10-17T08:49:38.857795+00:00</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.503027+00:00</t>
+          <t>2026-10-17T08:49:38.858149+00:00</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.504169+00:00</t>
+          <t>2026-10-17T08:49:38.859628+00:00</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.505592+00:00</t>
+          <t>2026-10-17T08:49:38.861002+00:00</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.506246+00:00</t>
+          <t>2026-10-17T08:49:38.861595+00:00</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.507262+00:00</t>
+          <t>2026-10-17T08:49:38.862579+00:00</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.507614+00:00</t>
+          <t>2026-10-17T08:49:38.862894+00:00</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.512772+00:00</t>
+          <t>2026-10-17T08:49:38.868252+00:00</t>
         </is>
       </c>
     </row>
@@ -30998,7 +30998,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -31035,7 +31035,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.513182+00:00</t>
+          <t>2026-10-17T08:49:38.868680+00:00</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.513808+00:00</t>
+          <t>2026-10-17T08:49:38.869227+00:00</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.514255+00:00</t>
+          <t>2026-10-17T08:49:38.869752+00:00</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.515453+00:00</t>
+          <t>2026-10-17T08:49:38.870837+00:00</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.518479+00:00</t>
+          <t>2026-10-17T08:49:38.873844+00:00</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.518729+00:00</t>
+          <t>2026-10-17T08:49:38.874092+00:00</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.523058+00:00</t>
+          <t>2026-10-17T08:49:38.878273+00:00</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.523855+00:00</t>
+          <t>2026-10-17T08:49:38.879027+00:00</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.526042+00:00</t>
+          <t>2026-10-17T08:49:38.881082+00:00</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.528362+00:00</t>
+          <t>2026-10-17T08:49:38.883006+00:00</t>
         </is>
       </c>
     </row>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -32115,7 +32115,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.529282+00:00</t>
+          <t>2026-10-17T08:49:38.883883+00:00</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.530725+00:00</t>
+          <t>2026-10-17T08:49:38.885610+00:00</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.533011+00:00</t>
+          <t>2026-10-17T08:49:38.887841+00:00</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.540949+00:00</t>
+          <t>2026-10-17T08:49:38.897928+00:00</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.542264+00:00</t>
+          <t>2026-10-17T08:49:38.899277+00:00</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.542426+00:00</t>
+          <t>2026-10-17T08:49:38.899467+00:00</t>
         </is>
       </c>
     </row>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.542439+00:00</t>
+          <t>2026-10-17T08:49:38.899483+00:00</t>
         </is>
       </c>
     </row>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.547286+00:00</t>
+          <t>2026-10-17T08:49:38.904401+00:00</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.547660+00:00</t>
+          <t>2026-10-17T08:49:38.904782+00:00</t>
         </is>
       </c>
     </row>
@@ -33071,7 +33071,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.548019+00:00</t>
+          <t>2026-10-17T08:49:38.905566+00:00</t>
         </is>
       </c>
     </row>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.548447+00:00</t>
+          <t>2026-10-17T08:49:38.905986+00:00</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.549132+00:00</t>
+          <t>2026-10-17T08:49:38.906686+00:00</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33383,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.550533+00:00</t>
+          <t>2026-10-17T08:49:38.908042+00:00</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.551393+00:00</t>
+          <t>2026-10-17T08:49:38.908853+00:00</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.551702+00:00</t>
+          <t>2026-10-17T08:49:38.909146+00:00</t>
         </is>
       </c>
     </row>
@@ -33699,7 +33699,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.552347+00:00</t>
+          <t>2026-10-17T08:49:38.909819+00:00</t>
         </is>
       </c>
     </row>
@@ -33799,7 +33799,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.552361+00:00</t>
+          <t>2026-10-17T08:49:38.909835+00:00</t>
         </is>
       </c>
     </row>
@@ -33907,7 +33907,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.552413+00:00</t>
+          <t>2026-10-17T08:49:38.909881+00:00</t>
         </is>
       </c>
     </row>
@@ -34015,7 +34015,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.552629+00:00</t>
+          <t>2026-10-17T08:49:38.910096+00:00</t>
         </is>
       </c>
     </row>
@@ -34123,7 +34123,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.552744+00:00</t>
+          <t>2026-10-17T08:49:38.910210+00:00</t>
         </is>
       </c>
     </row>
@@ -34235,7 +34235,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.552857+00:00</t>
+          <t>2026-10-17T08:49:38.910338+00:00</t>
         </is>
       </c>
     </row>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.553234+00:00</t>
+          <t>2026-10-17T08:49:38.910707+00:00</t>
         </is>
       </c>
     </row>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.553446+00:00</t>
+          <t>2026-10-17T08:49:38.910889+00:00</t>
         </is>
       </c>
     </row>
@@ -34563,7 +34563,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.553532+00:00</t>
+          <t>2026-10-17T08:49:38.910940+00:00</t>
         </is>
       </c>
     </row>
@@ -34675,7 +34675,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.553595+00:00</t>
+          <t>2026-10-17T08:49:38.910998+00:00</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.553741+00:00</t>
+          <t>2026-10-17T08:49:38.911137+00:00</t>
         </is>
       </c>
     </row>
@@ -34899,7 +34899,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.553791+00:00</t>
+          <t>2026-10-17T08:49:38.911182+00:00</t>
         </is>
       </c>
     </row>
@@ -35007,7 +35007,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.554245+00:00</t>
+          <t>2026-10-17T08:49:38.911644+00:00</t>
         </is>
       </c>
     </row>
@@ -35115,7 +35115,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.554329+00:00</t>
+          <t>2026-10-17T08:49:38.911690+00:00</t>
         </is>
       </c>
     </row>
@@ -35215,7 +35215,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.554341+00:00</t>
+          <t>2026-10-17T08:49:38.911700+00:00</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.564175+00:00</t>
+          <t>2026-10-17T08:49:38.921260+00:00</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.564239+00:00</t>
+          <t>2026-10-17T08:49:38.921333+00:00</t>
         </is>
       </c>
     </row>
@@ -35498,7 +35498,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -35535,7 +35535,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.564367+00:00</t>
+          <t>2026-10-17T08:49:38.921429+00:00</t>
         </is>
       </c>
     </row>
@@ -35643,7 +35643,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.564600+00:00</t>
+          <t>2026-10-17T08:49:38.921688+00:00</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.565688+00:00</t>
+          <t>2026-10-17T08:49:38.922660+00:00</t>
         </is>
       </c>
     </row>
@@ -35820,7 +35820,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -35853,7 +35853,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.565772+00:00</t>
+          <t>2026-10-17T08:49:38.922741+00:00</t>
         </is>
       </c>
     </row>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.565783+00:00</t>
+          <t>2026-10-17T08:49:38.922752+00:00</t>
         </is>
       </c>
     </row>
@@ -36016,7 +36016,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -36049,7 +36049,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.565861+00:00</t>
+          <t>2026-10-17T08:49:38.922829+00:00</t>
         </is>
       </c>
     </row>
@@ -36118,7 +36118,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -36151,7 +36151,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.565943+00:00</t>
+          <t>2026-10-17T08:49:38.922907+00:00</t>
         </is>
       </c>
     </row>
@@ -36220,7 +36220,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -36253,7 +36253,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.566050+00:00</t>
+          <t>2026-10-17T08:49:38.923010+00:00</t>
         </is>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.566061+00:00</t>
+          <t>2026-10-17T08:49:38.923021+00:00</t>
         </is>
       </c>
     </row>
@@ -36416,7 +36416,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -36449,7 +36449,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.566213+00:00</t>
+          <t>2026-10-17T08:49:38.923166+00:00</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.566224+00:00</t>
+          <t>2026-10-17T08:49:38.923177+00:00</t>
         </is>
       </c>
     </row>
@@ -36612,7 +36612,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -36645,7 +36645,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.566346+00:00</t>
+          <t>2026-10-17T08:49:38.923274+00:00</t>
         </is>
       </c>
     </row>
@@ -36739,7 +36739,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.566358+00:00</t>
+          <t>2026-10-17T08:49:38.923285+00:00</t>
         </is>
       </c>
     </row>
@@ -36808,7 +36808,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -36841,7 +36841,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.566495+00:00</t>
+          <t>2026-10-17T08:49:38.923434+00:00</t>
         </is>
       </c>
     </row>
@@ -36935,7 +36935,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.566507+00:00</t>
+          <t>2026-10-17T08:49:38.923445+00:00</t>
         </is>
       </c>
     </row>
@@ -37004,7 +37004,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -37037,7 +37037,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.566598+00:00</t>
+          <t>2026-10-17T08:49:38.923531+00:00</t>
         </is>
       </c>
     </row>
@@ -37106,7 +37106,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -37139,7 +37139,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.566735+00:00</t>
+          <t>2026-10-17T08:49:38.923659+00:00</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.566747+00:00</t>
+          <t>2026-10-17T08:49:38.923670+00:00</t>
         </is>
       </c>
     </row>
@@ -37302,7 +37302,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -37335,7 +37335,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.566871+00:00</t>
+          <t>2026-10-17T08:49:38.923787+00:00</t>
         </is>
       </c>
     </row>
@@ -37429,7 +37429,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.566882+00:00</t>
+          <t>2026-10-17T08:49:38.923796+00:00</t>
         </is>
       </c>
     </row>
@@ -37498,7 +37498,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -37531,7 +37531,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.566983+00:00</t>
+          <t>2026-10-17T08:49:38.923913+00:00</t>
         </is>
       </c>
     </row>
@@ -37600,7 +37600,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -37633,7 +37633,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.567221+00:00</t>
+          <t>2026-10-17T08:49:38.924129+00:00</t>
         </is>
       </c>
     </row>
@@ -37727,7 +37727,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.567233+00:00</t>
+          <t>2026-10-17T08:49:38.924140+00:00</t>
         </is>
       </c>
     </row>
@@ -37796,7 +37796,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -37829,7 +37829,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.567413+00:00</t>
+          <t>2026-10-17T08:49:38.924310+00:00</t>
         </is>
       </c>
     </row>
@@ -37898,7 +37898,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -37931,7 +37931,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.567618+00:00</t>
+          <t>2026-10-17T08:49:38.924503+00:00</t>
         </is>
       </c>
     </row>
@@ -38000,7 +38000,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -38033,7 +38033,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.567809+00:00</t>
+          <t>2026-10-17T08:49:38.924694+00:00</t>
         </is>
       </c>
     </row>
@@ -38127,7 +38127,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.567820+00:00</t>
+          <t>2026-10-17T08:49:38.924705+00:00</t>
         </is>
       </c>
     </row>
@@ -38196,7 +38196,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -38229,7 +38229,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.567928+00:00</t>
+          <t>2026-10-17T08:49:38.924813+00:00</t>
         </is>
       </c>
     </row>
@@ -38323,7 +38323,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.567938+00:00</t>
+          <t>2026-10-17T08:49:38.924824+00:00</t>
         </is>
       </c>
     </row>
@@ -38392,7 +38392,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -38425,7 +38425,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.568038+00:00</t>
+          <t>2026-10-17T08:49:38.924911+00:00</t>
         </is>
       </c>
     </row>
@@ -38533,7 +38533,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.569082+00:00</t>
+          <t>2026-10-17T08:49:38.925981+00:00</t>
         </is>
       </c>
     </row>
@@ -38625,7 +38625,7 @@
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.578938+00:00</t>
+          <t>2026-10-17T08:49:38.935211+00:00</t>
         </is>
       </c>
     </row>
@@ -38713,7 +38713,7 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.579000+00:00</t>
+          <t>2026-10-17T08:49:38.935268+00:00</t>
         </is>
       </c>
     </row>
@@ -38801,7 +38801,7 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.579006+00:00</t>
+          <t>2026-10-17T08:49:38.935274+00:00</t>
         </is>
       </c>
     </row>
@@ -38893,7 +38893,7 @@
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.579011+00:00</t>
+          <t>2026-10-17T08:49:38.935278+00:00</t>
         </is>
       </c>
     </row>
@@ -38985,7 +38985,7 @@
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.579014+00:00</t>
+          <t>2026-10-17T08:49:38.935281+00:00</t>
         </is>
       </c>
     </row>
@@ -39077,7 +39077,7 @@
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.579018+00:00</t>
+          <t>2026-10-17T08:49:38.935284+00:00</t>
         </is>
       </c>
     </row>
@@ -39169,7 +39169,7 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.579022+00:00</t>
+          <t>2026-10-17T08:49:38.935300+00:00</t>
         </is>
       </c>
     </row>
@@ -39257,7 +39257,7 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.579025+00:00</t>
+          <t>2026-10-17T08:49:38.935303+00:00</t>
         </is>
       </c>
     </row>
@@ -39349,7 +39349,7 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.579029+00:00</t>
+          <t>2026-10-17T08:49:38.935306+00:00</t>
         </is>
       </c>
     </row>
@@ -39441,7 +39441,7 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.579033+00:00</t>
+          <t>2026-10-17T08:49:38.935309+00:00</t>
         </is>
       </c>
     </row>
@@ -39529,7 +39529,7 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.579036+00:00</t>
+          <t>2026-10-17T08:49:38.935313+00:00</t>
         </is>
       </c>
     </row>
@@ -39621,7 +39621,7 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-10-17T08:48:34.579041+00:00</t>
+          <t>2026-10-17T08:49:38.935317+00:00</t>
         </is>
       </c>
     </row>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="H66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="n">
         <v>1</v>
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="H84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
         <v>1</v>
@@ -6213,11 +6213,11 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>explicit_no_attachments_in_complete_JATS</t>
         </is>
       </c>
       <c r="H135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I135" t="n">
         <v>0</v>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="H137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I137" t="n">
         <v>2</v>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>downloaded</t>
+          <t>partial_or_access_failed</t>
         </is>
       </c>
       <c r="H141" t="b">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.773058+00:00</t>
+          <t>2026-10-17T08:51:35.214112+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.773987+00:00</t>
+          <t>2026-10-17T08:51:35.215317+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.774012+00:00</t>
+          <t>2026-10-17T08:51:35.215347+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.774282+00:00</t>
+          <t>2026-10-17T08:51:35.215664+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.775405+00:00</t>
+          <t>2026-10-17T08:51:35.217226+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.775847+00:00</t>
+          <t>2026-10-17T08:51:35.217838+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.780860+00:00</t>
+          <t>2026-10-17T08:51:35.226345+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.783071+00:00</t>
+          <t>2026-10-17T08:51:35.231165+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.783936+00:00</t>
+          <t>2026-10-17T08:51:35.232419+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.784244+00:00</t>
+          <t>2026-10-17T08:51:35.232769+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.785018+00:00</t>
+          <t>2026-10-17T08:51:35.233726+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.785738+00:00</t>
+          <t>2026-10-17T08:51:35.234469+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.786652+00:00</t>
+          <t>2026-10-17T08:51:35.235381+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.786886+00:00</t>
+          <t>2026-10-17T08:51:35.235617+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.787746+00:00</t>
+          <t>2026-10-17T08:51:35.236624+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.795817+00:00</t>
+          <t>2026-10-17T08:51:35.244486+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.796540+00:00</t>
+          <t>2026-10-17T08:51:35.245235+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.797745+00:00</t>
+          <t>2026-10-17T08:51:35.246468+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.800301+00:00</t>
+          <t>2026-10-17T08:51:35.249004+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.801379+00:00</t>
+          <t>2026-10-17T08:51:35.250259+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.802577+00:00</t>
+          <t>2026-10-17T08:51:35.251654+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.806712+00:00</t>
+          <t>2026-10-17T08:51:35.256062+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.808860+00:00</t>
+          <t>2026-10-17T08:51:35.258691+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.810686+00:00</t>
+          <t>2026-10-17T08:51:35.260617+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.811335+00:00</t>
+          <t>2026-10-17T08:51:35.261383+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.811683+00:00</t>
+          <t>2026-10-17T08:51:35.261772+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.813757+00:00</t>
+          <t>2026-10-17T08:51:35.264115+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.814984+00:00</t>
+          <t>2026-10-17T08:51:35.265538+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.817017+00:00</t>
+          <t>2026-10-17T08:51:35.267722+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.818973+00:00</t>
+          <t>2026-10-17T08:51:35.269855+00:00</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.819681+00:00</t>
+          <t>2026-10-17T08:51:35.270661+00:00</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.820250+00:00</t>
+          <t>2026-10-17T08:51:35.271219+00:00</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.821884+00:00</t>
+          <t>2026-10-17T08:51:35.272979+00:00</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.824676+00:00</t>
+          <t>2026-10-17T08:51:35.276277+00:00</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.826766+00:00</t>
+          <t>2026-10-17T08:51:35.278849+00:00</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.827952+00:00</t>
+          <t>2026-10-17T08:51:35.280076+00:00</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.830825+00:00</t>
+          <t>2026-10-17T08:51:35.283340+00:00</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.831526+00:00</t>
+          <t>2026-10-17T08:51:35.284082+00:00</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.833417+00:00</t>
+          <t>2026-10-17T08:51:35.285685+00:00</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.833701+00:00</t>
+          <t>2026-10-17T08:51:35.285933+00:00</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.835570+00:00</t>
+          <t>2026-10-17T08:51:35.287961+00:00</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.838376+00:00</t>
+          <t>2026-10-17T08:51:35.291047+00:00</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.839805+00:00</t>
+          <t>2026-10-17T08:51:35.292523+00:00</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.840363+00:00</t>
+          <t>2026-10-17T08:51:35.293180+00:00</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.843205+00:00</t>
+          <t>2026-10-17T08:51:35.295977+00:00</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.844425+00:00</t>
+          <t>2026-10-17T08:51:35.297253+00:00</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.847816+00:00</t>
+          <t>2026-10-17T08:51:35.300934+00:00</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.849521+00:00</t>
+          <t>2026-10-17T08:51:35.302941+00:00</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.851333+00:00</t>
+          <t>2026-10-17T08:51:35.304970+00:00</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.852320+00:00</t>
+          <t>2026-10-17T08:51:35.306051+00:00</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.852755+00:00</t>
+          <t>2026-10-17T08:51:35.306621+00:00</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.853110+00:00</t>
+          <t>2026-10-17T08:51:35.307117+00:00</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.854589+00:00</t>
+          <t>2026-10-17T08:51:35.309120+00:00</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.856074+00:00</t>
+          <t>2026-10-17T08:51:35.310820+00:00</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.857795+00:00</t>
+          <t>2026-10-17T08:51:35.312574+00:00</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.858149+00:00</t>
+          <t>2026-10-17T08:51:35.312927+00:00</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.859628+00:00</t>
+          <t>2026-10-17T08:51:35.314144+00:00</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.861002+00:00</t>
+          <t>2026-10-17T08:51:35.315977+00:00</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.861595+00:00</t>
+          <t>2026-10-17T08:51:35.316848+00:00</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.862579+00:00</t>
+          <t>2026-10-17T08:51:35.318137+00:00</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.862894+00:00</t>
+          <t>2026-10-17T08:51:35.318630+00:00</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.868252+00:00</t>
+          <t>2026-10-17T08:51:35.324401+00:00</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.868680+00:00</t>
+          <t>2026-10-17T08:51:35.324887+00:00</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.869227+00:00</t>
+          <t>2026-10-17T08:51:35.325585+00:00</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.869752+00:00</t>
+          <t>2026-10-17T08:51:35.326046+00:00</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.870837+00:00</t>
+          <t>2026-10-17T08:51:35.328122+00:00</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.873844+00:00</t>
+          <t>2026-10-17T08:51:35.331443+00:00</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.874092+00:00</t>
+          <t>2026-10-17T08:51:35.331706+00:00</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.878273+00:00</t>
+          <t>2026-10-17T08:51:35.336215+00:00</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.879027+00:00</t>
+          <t>2026-10-17T08:51:35.337147+00:00</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.881082+00:00</t>
+          <t>2026-10-17T08:51:35.339688+00:00</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.883006+00:00</t>
+          <t>2026-10-17T08:51:35.341620+00:00</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.883883+00:00</t>
+          <t>2026-10-17T08:51:35.342649+00:00</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.885610+00:00</t>
+          <t>2026-10-17T08:51:35.344132+00:00</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.887841+00:00</t>
+          <t>2026-10-17T08:51:35.346392+00:00</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.897928+00:00</t>
+          <t>2026-10-17T08:51:35.354620+00:00</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.899277+00:00</t>
+          <t>2026-10-17T08:51:35.356032+00:00</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.899467+00:00</t>
+          <t>2026-10-17T08:51:35.356194+00:00</t>
         </is>
       </c>
     </row>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.899483+00:00</t>
+          <t>2026-10-17T08:51:35.356208+00:00</t>
         </is>
       </c>
     </row>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.904401+00:00</t>
+          <t>2026-10-17T08:51:35.361822+00:00</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.904782+00:00</t>
+          <t>2026-10-17T08:51:35.362337+00:00</t>
         </is>
       </c>
     </row>
@@ -33071,7 +33071,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.905566+00:00</t>
+          <t>2026-10-17T08:51:35.362707+00:00</t>
         </is>
       </c>
     </row>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.905986+00:00</t>
+          <t>2026-10-17T08:51:35.363151+00:00</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.906686+00:00</t>
+          <t>2026-10-17T08:51:35.364012+00:00</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33383,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.908042+00:00</t>
+          <t>2026-10-17T08:51:35.365625+00:00</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.908853+00:00</t>
+          <t>2026-10-17T08:51:35.366471+00:00</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.909146+00:00</t>
+          <t>2026-10-17T08:51:35.366862+00:00</t>
         </is>
       </c>
     </row>
@@ -33699,7 +33699,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.909819+00:00</t>
+          <t>2026-10-17T08:51:35.367563+00:00</t>
         </is>
       </c>
     </row>
@@ -33799,7 +33799,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.909835+00:00</t>
+          <t>2026-10-17T08:51:35.367580+00:00</t>
         </is>
       </c>
     </row>
@@ -33907,7 +33907,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.909881+00:00</t>
+          <t>2026-10-17T08:51:35.367629+00:00</t>
         </is>
       </c>
     </row>
@@ -34015,7 +34015,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.910096+00:00</t>
+          <t>2026-10-17T08:51:35.367897+00:00</t>
         </is>
       </c>
     </row>
@@ -34123,7 +34123,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.910210+00:00</t>
+          <t>2026-10-17T08:51:35.368038+00:00</t>
         </is>
       </c>
     </row>
@@ -34235,7 +34235,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.910338+00:00</t>
+          <t>2026-10-17T08:51:35.368156+00:00</t>
         </is>
       </c>
     </row>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.910707+00:00</t>
+          <t>2026-10-17T08:51:35.368553+00:00</t>
         </is>
       </c>
     </row>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.910889+00:00</t>
+          <t>2026-10-17T08:51:35.368756+00:00</t>
         </is>
       </c>
     </row>
@@ -34563,7 +34563,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.910940+00:00</t>
+          <t>2026-10-17T08:51:35.368809+00:00</t>
         </is>
       </c>
     </row>
@@ -34675,7 +34675,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.910998+00:00</t>
+          <t>2026-10-17T08:51:35.368874+00:00</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.911137+00:00</t>
+          <t>2026-10-17T08:51:35.369121+00:00</t>
         </is>
       </c>
     </row>
@@ -34899,7 +34899,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.911182+00:00</t>
+          <t>2026-10-17T08:51:35.369174+00:00</t>
         </is>
       </c>
     </row>
@@ -35007,7 +35007,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.911644+00:00</t>
+          <t>2026-10-17T08:51:35.369746+00:00</t>
         </is>
       </c>
     </row>
@@ -35115,7 +35115,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.911690+00:00</t>
+          <t>2026-10-17T08:51:35.369815+00:00</t>
         </is>
       </c>
     </row>
@@ -35215,7 +35215,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.911700+00:00</t>
+          <t>2026-10-17T08:51:35.369826+00:00</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.921260+00:00</t>
+          <t>2026-10-17T08:51:35.380712+00:00</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.921333+00:00</t>
+          <t>2026-10-17T08:51:35.380794+00:00</t>
         </is>
       </c>
     </row>
@@ -35535,7 +35535,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.921429+00:00</t>
+          <t>2026-10-17T08:51:35.380912+00:00</t>
         </is>
       </c>
     </row>
@@ -35643,7 +35643,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.921688+00:00</t>
+          <t>2026-10-17T08:51:35.381152+00:00</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.922660+00:00</t>
+          <t>2026-10-17T08:51:35.382347+00:00</t>
         </is>
       </c>
     </row>
@@ -35853,7 +35853,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.922741+00:00</t>
+          <t>2026-10-17T08:51:35.382460+00:00</t>
         </is>
       </c>
     </row>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.922752+00:00</t>
+          <t>2026-10-17T08:51:35.382473+00:00</t>
         </is>
       </c>
     </row>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.922829+00:00</t>
+          <t>2026-10-17T08:51:35.382558+00:00</t>
         </is>
       </c>
     </row>
@@ -36151,7 +36151,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.922907+00:00</t>
+          <t>2026-10-17T08:51:35.382646+00:00</t>
         </is>
       </c>
     </row>
@@ -36253,7 +36253,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.923010+00:00</t>
+          <t>2026-10-17T08:51:35.382754+00:00</t>
         </is>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.923021+00:00</t>
+          <t>2026-10-17T08:51:35.382766+00:00</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.923166+00:00</t>
+          <t>2026-10-17T08:51:35.382924+00:00</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.923177+00:00</t>
+          <t>2026-10-17T08:51:35.382935+00:00</t>
         </is>
       </c>
     </row>
@@ -36645,7 +36645,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.923274+00:00</t>
+          <t>2026-10-17T08:51:35.383040+00:00</t>
         </is>
       </c>
     </row>
@@ -36739,7 +36739,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.923285+00:00</t>
+          <t>2026-10-17T08:51:35.383052+00:00</t>
         </is>
       </c>
     </row>
@@ -36841,7 +36841,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.923434+00:00</t>
+          <t>2026-10-17T08:51:35.383268+00:00</t>
         </is>
       </c>
     </row>
@@ -36935,7 +36935,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.923445+00:00</t>
+          <t>2026-10-17T08:51:35.383344+00:00</t>
         </is>
       </c>
     </row>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.923531+00:00</t>
+          <t>2026-10-17T08:51:35.383445+00:00</t>
         </is>
       </c>
     </row>
@@ -37139,7 +37139,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.923659+00:00</t>
+          <t>2026-10-17T08:51:35.383580+00:00</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.923670+00:00</t>
+          <t>2026-10-17T08:51:35.383591+00:00</t>
         </is>
       </c>
     </row>
@@ -37335,7 +37335,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.923787+00:00</t>
+          <t>2026-10-17T08:51:35.383718+00:00</t>
         </is>
       </c>
     </row>
@@ -37429,7 +37429,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.923796+00:00</t>
+          <t>2026-10-17T08:51:35.383729+00:00</t>
         </is>
       </c>
     </row>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.923913+00:00</t>
+          <t>2026-10-17T08:51:35.383834+00:00</t>
         </is>
       </c>
     </row>
@@ -37633,7 +37633,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.924129+00:00</t>
+          <t>2026-10-17T08:51:35.384053+00:00</t>
         </is>
       </c>
     </row>
@@ -37727,7 +37727,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.924140+00:00</t>
+          <t>2026-10-17T08:51:35.384065+00:00</t>
         </is>
       </c>
     </row>
@@ -37829,7 +37829,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.924310+00:00</t>
+          <t>2026-10-17T08:51:35.384223+00:00</t>
         </is>
       </c>
     </row>
@@ -37931,7 +37931,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.924503+00:00</t>
+          <t>2026-10-17T08:51:35.384446+00:00</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38033,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.924694+00:00</t>
+          <t>2026-10-17T08:51:35.384645+00:00</t>
         </is>
       </c>
     </row>
@@ -38127,7 +38127,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.924705+00:00</t>
+          <t>2026-10-17T08:51:35.384657+00:00</t>
         </is>
       </c>
     </row>
@@ -38229,7 +38229,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.924813+00:00</t>
+          <t>2026-10-17T08:51:35.384765+00:00</t>
         </is>
       </c>
     </row>
@@ -38323,7 +38323,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.924824+00:00</t>
+          <t>2026-10-17T08:51:35.384776+00:00</t>
         </is>
       </c>
     </row>
@@ -38425,7 +38425,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.924911+00:00</t>
+          <t>2026-10-17T08:51:35.384863+00:00</t>
         </is>
       </c>
     </row>
@@ -38533,7 +38533,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.925981+00:00</t>
+          <t>2026-10-17T08:51:35.386060+00:00</t>
         </is>
       </c>
     </row>
@@ -38625,7 +38625,7 @@
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.935211+00:00</t>
+          <t>2026-10-17T08:51:35.395683+00:00</t>
         </is>
       </c>
     </row>
@@ -38713,7 +38713,7 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.935268+00:00</t>
+          <t>2026-10-17T08:51:35.395759+00:00</t>
         </is>
       </c>
     </row>
@@ -38801,7 +38801,7 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.935274+00:00</t>
+          <t>2026-10-17T08:51:35.395765+00:00</t>
         </is>
       </c>
     </row>
@@ -38893,7 +38893,7 @@
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.935278+00:00</t>
+          <t>2026-10-17T08:51:35.395768+00:00</t>
         </is>
       </c>
     </row>
@@ -38985,7 +38985,7 @@
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.935281+00:00</t>
+          <t>2026-10-17T08:51:35.395771+00:00</t>
         </is>
       </c>
     </row>
@@ -39077,7 +39077,7 @@
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.935284+00:00</t>
+          <t>2026-10-17T08:51:35.395775+00:00</t>
         </is>
       </c>
     </row>
@@ -39169,7 +39169,7 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.935300+00:00</t>
+          <t>2026-10-17T08:51:35.395778+00:00</t>
         </is>
       </c>
     </row>
@@ -39257,7 +39257,7 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.935303+00:00</t>
+          <t>2026-10-17T08:51:35.395780+00:00</t>
         </is>
       </c>
     </row>
@@ -39349,7 +39349,7 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.935306+00:00</t>
+          <t>2026-10-17T08:51:35.395783+00:00</t>
         </is>
       </c>
     </row>
@@ -39441,7 +39441,7 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.935309+00:00</t>
+          <t>2026-10-17T08:51:35.395787+00:00</t>
         </is>
       </c>
     </row>
@@ -39529,7 +39529,7 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.935313+00:00</t>
+          <t>2026-10-17T08:51:35.395790+00:00</t>
         </is>
       </c>
     </row>
@@ -39621,7 +39621,7 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-10-17T08:49:38.935317+00:00</t>
+          <t>2026-10-17T08:51:35.395793+00:00</t>
         </is>
       </c>
     </row>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -6858,11 +6858,11 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>explicit_no_attachments_in_complete_JATS</t>
         </is>
       </c>
       <c r="H150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I150" t="n">
         <v>0</v>
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="H160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I160" t="n">
         <v>1</v>
@@ -7460,11 +7460,11 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>explicit_no_attachments_in_complete_JATS</t>
         </is>
       </c>
       <c r="H164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I164" t="n">
         <v>0</v>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H170" t="b">
@@ -7804,11 +7804,11 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>explicit_no_attachments_in_complete_JATS</t>
         </is>
       </c>
       <c r="H172" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I172" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="H173" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I173" t="n">
         <v>1</v>
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.214112+00:00</t>
+          <t>2026-10-17T08:52:38.716531+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.215317+00:00</t>
+          <t>2026-10-17T08:52:38.717428+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.215347+00:00</t>
+          <t>2026-10-17T08:52:38.717445+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.215664+00:00</t>
+          <t>2026-10-17T08:52:38.717694+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.217226+00:00</t>
+          <t>2026-10-17T08:52:38.718864+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.217838+00:00</t>
+          <t>2026-10-17T08:52:38.719488+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.226345+00:00</t>
+          <t>2026-10-17T08:52:38.724821+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.231165+00:00</t>
+          <t>2026-10-17T08:52:38.727114+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.232419+00:00</t>
+          <t>2026-10-17T08:52:38.728141+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.232769+00:00</t>
+          <t>2026-10-17T08:52:38.728645+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.233726+00:00</t>
+          <t>2026-10-17T08:52:38.729402+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.234469+00:00</t>
+          <t>2026-10-17T08:52:38.730074+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.235381+00:00</t>
+          <t>2026-10-17T08:52:38.730983+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.235617+00:00</t>
+          <t>2026-10-17T08:52:38.731230+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.236624+00:00</t>
+          <t>2026-10-17T08:52:38.732088+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.244486+00:00</t>
+          <t>2026-10-17T08:52:38.739642+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.245235+00:00</t>
+          <t>2026-10-17T08:52:38.740488+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.246468+00:00</t>
+          <t>2026-10-17T08:52:38.741731+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.249004+00:00</t>
+          <t>2026-10-17T08:52:38.744380+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.250259+00:00</t>
+          <t>2026-10-17T08:52:38.745493+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.251654+00:00</t>
+          <t>2026-10-17T08:52:38.746674+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.256062+00:00</t>
+          <t>2026-10-17T08:52:38.750938+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.258691+00:00</t>
+          <t>2026-10-17T08:52:38.753168+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.260617+00:00</t>
+          <t>2026-10-17T08:52:38.755033+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.261383+00:00</t>
+          <t>2026-10-17T08:52:38.755897+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.261772+00:00</t>
+          <t>2026-10-17T08:52:38.756269+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.264115+00:00</t>
+          <t>2026-10-17T08:52:38.758424+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.265538+00:00</t>
+          <t>2026-10-17T08:52:38.759661+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.267722+00:00</t>
+          <t>2026-10-17T08:52:38.761699+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.269855+00:00</t>
+          <t>2026-10-17T08:52:38.763645+00:00</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.270661+00:00</t>
+          <t>2026-10-17T08:52:38.764185+00:00</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.271219+00:00</t>
+          <t>2026-10-17T08:52:38.764747+00:00</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.272979+00:00</t>
+          <t>2026-10-17T08:52:38.766385+00:00</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.276277+00:00</t>
+          <t>2026-10-17T08:52:38.769143+00:00</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.278849+00:00</t>
+          <t>2026-10-17T08:52:38.771471+00:00</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.280076+00:00</t>
+          <t>2026-10-17T08:52:38.772773+00:00</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.283340+00:00</t>
+          <t>2026-10-17T08:52:38.775623+00:00</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.284082+00:00</t>
+          <t>2026-10-17T08:52:38.776326+00:00</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.285685+00:00</t>
+          <t>2026-10-17T08:52:38.777944+00:00</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.285933+00:00</t>
+          <t>2026-10-17T08:52:38.778215+00:00</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.287961+00:00</t>
+          <t>2026-10-17T08:52:38.780202+00:00</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.291047+00:00</t>
+          <t>2026-10-17T08:52:38.783148+00:00</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.292523+00:00</t>
+          <t>2026-10-17T08:52:38.784471+00:00</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.293180+00:00</t>
+          <t>2026-10-17T08:52:38.785085+00:00</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.295977+00:00</t>
+          <t>2026-10-17T08:52:38.787687+00:00</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.297253+00:00</t>
+          <t>2026-10-17T08:52:38.788870+00:00</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.300934+00:00</t>
+          <t>2026-10-17T08:52:38.792431+00:00</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.302941+00:00</t>
+          <t>2026-10-17T08:52:38.794232+00:00</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.304970+00:00</t>
+          <t>2026-10-17T08:52:38.796072+00:00</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.306051+00:00</t>
+          <t>2026-10-17T08:52:38.797127+00:00</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.306621+00:00</t>
+          <t>2026-10-17T08:52:38.797623+00:00</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.307117+00:00</t>
+          <t>2026-10-17T08:52:38.797987+00:00</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.309120+00:00</t>
+          <t>2026-10-17T08:52:38.799620+00:00</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.310820+00:00</t>
+          <t>2026-10-17T08:52:38.800955+00:00</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.312574+00:00</t>
+          <t>2026-10-17T08:52:38.802602+00:00</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.312927+00:00</t>
+          <t>2026-10-17T08:52:38.802958+00:00</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.314144+00:00</t>
+          <t>2026-10-17T08:52:38.804236+00:00</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.315977+00:00</t>
+          <t>2026-10-17T08:52:38.805661+00:00</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.316848+00:00</t>
+          <t>2026-10-17T08:52:38.806286+00:00</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.318137+00:00</t>
+          <t>2026-10-17T08:52:38.807260+00:00</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.318630+00:00</t>
+          <t>2026-10-17T08:52:38.807700+00:00</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.324401+00:00</t>
+          <t>2026-10-17T08:52:38.812888+00:00</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.324887+00:00</t>
+          <t>2026-10-17T08:52:38.813323+00:00</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.325585+00:00</t>
+          <t>2026-10-17T08:52:38.813908+00:00</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.326046+00:00</t>
+          <t>2026-10-17T08:52:38.814372+00:00</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.328122+00:00</t>
+          <t>2026-10-17T08:52:38.815422+00:00</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.331443+00:00</t>
+          <t>2026-10-17T08:52:38.818309+00:00</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.331706+00:00</t>
+          <t>2026-10-17T08:52:38.818553+00:00</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.336215+00:00</t>
+          <t>2026-10-17T08:52:38.823036+00:00</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.337147+00:00</t>
+          <t>2026-10-17T08:52:38.823888+00:00</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.339688+00:00</t>
+          <t>2026-10-17T08:52:38.826458+00:00</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.341620+00:00</t>
+          <t>2026-10-17T08:52:38.828338+00:00</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.342649+00:00</t>
+          <t>2026-10-17T08:52:38.829330+00:00</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.344132+00:00</t>
+          <t>2026-10-17T08:52:38.830879+00:00</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.346392+00:00</t>
+          <t>2026-10-17T08:52:38.833145+00:00</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.354620+00:00</t>
+          <t>2026-10-17T08:52:38.840888+00:00</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.356032+00:00</t>
+          <t>2026-10-17T08:52:38.842290+00:00</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.356194+00:00</t>
+          <t>2026-10-17T08:52:38.842484+00:00</t>
         </is>
       </c>
     </row>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.356208+00:00</t>
+          <t>2026-10-17T08:52:38.842497+00:00</t>
         </is>
       </c>
     </row>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.361822+00:00</t>
+          <t>2026-10-17T08:52:38.847593+00:00</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.362337+00:00</t>
+          <t>2026-10-17T08:52:38.847978+00:00</t>
         </is>
       </c>
     </row>
@@ -33071,7 +33071,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.362707+00:00</t>
+          <t>2026-10-17T08:52:38.848408+00:00</t>
         </is>
       </c>
     </row>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.363151+00:00</t>
+          <t>2026-10-17T08:52:38.848814+00:00</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.364012+00:00</t>
+          <t>2026-10-17T08:52:38.849601+00:00</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33383,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.365625+00:00</t>
+          <t>2026-10-17T08:52:38.850997+00:00</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.366471+00:00</t>
+          <t>2026-10-17T08:52:38.851871+00:00</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.366862+00:00</t>
+          <t>2026-10-17T08:52:38.852181+00:00</t>
         </is>
       </c>
     </row>
@@ -33699,7 +33699,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.367563+00:00</t>
+          <t>2026-10-17T08:52:38.852828+00:00</t>
         </is>
       </c>
     </row>
@@ -33799,7 +33799,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.367580+00:00</t>
+          <t>2026-10-17T08:52:38.852842+00:00</t>
         </is>
       </c>
     </row>
@@ -33907,7 +33907,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.367629+00:00</t>
+          <t>2026-10-17T08:52:38.852892+00:00</t>
         </is>
       </c>
     </row>
@@ -34015,7 +34015,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.367897+00:00</t>
+          <t>2026-10-17T08:52:38.853127+00:00</t>
         </is>
       </c>
     </row>
@@ -34123,7 +34123,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.368038+00:00</t>
+          <t>2026-10-17T08:52:38.853247+00:00</t>
         </is>
       </c>
     </row>
@@ -34235,7 +34235,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.368156+00:00</t>
+          <t>2026-10-17T08:52:38.853376+00:00</t>
         </is>
       </c>
     </row>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.368553+00:00</t>
+          <t>2026-10-17T08:52:38.853765+00:00</t>
         </is>
       </c>
     </row>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.368756+00:00</t>
+          <t>2026-10-17T08:52:38.853948+00:00</t>
         </is>
       </c>
     </row>
@@ -34563,7 +34563,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.368809+00:00</t>
+          <t>2026-10-17T08:52:38.854002+00:00</t>
         </is>
       </c>
     </row>
@@ -34675,7 +34675,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.368874+00:00</t>
+          <t>2026-10-17T08:52:38.854065+00:00</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.369121+00:00</t>
+          <t>2026-10-17T08:52:38.854214+00:00</t>
         </is>
       </c>
     </row>
@@ -34899,7 +34899,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.369174+00:00</t>
+          <t>2026-10-17T08:52:38.854261+00:00</t>
         </is>
       </c>
     </row>
@@ -35007,7 +35007,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.369746+00:00</t>
+          <t>2026-10-17T08:52:38.854757+00:00</t>
         </is>
       </c>
     </row>
@@ -35115,7 +35115,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.369815+00:00</t>
+          <t>2026-10-17T08:52:38.854814+00:00</t>
         </is>
       </c>
     </row>
@@ -35215,7 +35215,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.369826+00:00</t>
+          <t>2026-10-17T08:52:38.854824+00:00</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.380712+00:00</t>
+          <t>2026-10-17T08:52:38.863783+00:00</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.380794+00:00</t>
+          <t>2026-10-17T08:52:38.863830+00:00</t>
         </is>
       </c>
     </row>
@@ -35535,7 +35535,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.380912+00:00</t>
+          <t>2026-10-17T08:52:38.863917+00:00</t>
         </is>
       </c>
     </row>
@@ -35643,7 +35643,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.381152+00:00</t>
+          <t>2026-10-17T08:52:38.864147+00:00</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.382347+00:00</t>
+          <t>2026-10-17T08:52:38.865250+00:00</t>
         </is>
       </c>
     </row>
@@ -35853,7 +35853,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.382460+00:00</t>
+          <t>2026-10-17T08:52:38.865368+00:00</t>
         </is>
       </c>
     </row>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.382473+00:00</t>
+          <t>2026-10-17T08:52:38.865381+00:00</t>
         </is>
       </c>
     </row>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.382558+00:00</t>
+          <t>2026-10-17T08:52:38.865464+00:00</t>
         </is>
       </c>
     </row>
@@ -36151,7 +36151,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.382646+00:00</t>
+          <t>2026-10-17T08:52:38.865566+00:00</t>
         </is>
       </c>
     </row>
@@ -36253,7 +36253,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.382754+00:00</t>
+          <t>2026-10-17T08:52:38.865674+00:00</t>
         </is>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.382766+00:00</t>
+          <t>2026-10-17T08:52:38.865685+00:00</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.382924+00:00</t>
+          <t>2026-10-17T08:52:38.865837+00:00</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.382935+00:00</t>
+          <t>2026-10-17T08:52:38.865849+00:00</t>
         </is>
       </c>
     </row>
@@ -36645,7 +36645,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.383040+00:00</t>
+          <t>2026-10-17T08:52:38.865946+00:00</t>
         </is>
       </c>
     </row>
@@ -36739,7 +36739,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.383052+00:00</t>
+          <t>2026-10-17T08:52:38.865957+00:00</t>
         </is>
       </c>
     </row>
@@ -36841,7 +36841,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.383268+00:00</t>
+          <t>2026-10-17T08:52:38.866089+00:00</t>
         </is>
       </c>
     </row>
@@ -36935,7 +36935,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.383344+00:00</t>
+          <t>2026-10-17T08:52:38.866101+00:00</t>
         </is>
       </c>
     </row>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.383445+00:00</t>
+          <t>2026-10-17T08:52:38.866190+00:00</t>
         </is>
       </c>
     </row>
@@ -37139,7 +37139,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.383580+00:00</t>
+          <t>2026-10-17T08:52:38.866349+00:00</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.383591+00:00</t>
+          <t>2026-10-17T08:52:38.866361+00:00</t>
         </is>
       </c>
     </row>
@@ -37335,7 +37335,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.383718+00:00</t>
+          <t>2026-10-17T08:52:38.866480+00:00</t>
         </is>
       </c>
     </row>
@@ -37429,7 +37429,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.383729+00:00</t>
+          <t>2026-10-17T08:52:38.866492+00:00</t>
         </is>
       </c>
     </row>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.383834+00:00</t>
+          <t>2026-10-17T08:52:38.866594+00:00</t>
         </is>
       </c>
     </row>
@@ -37633,7 +37633,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.384053+00:00</t>
+          <t>2026-10-17T08:52:38.866813+00:00</t>
         </is>
       </c>
     </row>
@@ -37727,7 +37727,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.384065+00:00</t>
+          <t>2026-10-17T08:52:38.866824+00:00</t>
         </is>
       </c>
     </row>
@@ -37829,7 +37829,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.384223+00:00</t>
+          <t>2026-10-17T08:52:38.866982+00:00</t>
         </is>
       </c>
     </row>
@@ -37931,7 +37931,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.384446+00:00</t>
+          <t>2026-10-17T08:52:38.867192+00:00</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38033,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.384645+00:00</t>
+          <t>2026-10-17T08:52:38.867408+00:00</t>
         </is>
       </c>
     </row>
@@ -38127,7 +38127,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.384657+00:00</t>
+          <t>2026-10-17T08:52:38.867421+00:00</t>
         </is>
       </c>
     </row>
@@ -38229,7 +38229,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.384765+00:00</t>
+          <t>2026-10-17T08:52:38.867528+00:00</t>
         </is>
       </c>
     </row>
@@ -38323,7 +38323,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.384776+00:00</t>
+          <t>2026-10-17T08:52:38.867538+00:00</t>
         </is>
       </c>
     </row>
@@ -38425,7 +38425,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.384863+00:00</t>
+          <t>2026-10-17T08:52:38.867625+00:00</t>
         </is>
       </c>
     </row>
@@ -38533,7 +38533,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.386060+00:00</t>
+          <t>2026-10-17T08:52:38.868698+00:00</t>
         </is>
       </c>
     </row>
@@ -38625,7 +38625,7 @@
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.395683+00:00</t>
+          <t>2026-10-17T08:52:38.877931+00:00</t>
         </is>
       </c>
     </row>
@@ -38713,7 +38713,7 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.395759+00:00</t>
+          <t>2026-10-17T08:52:38.877985+00:00</t>
         </is>
       </c>
     </row>
@@ -38801,7 +38801,7 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.395765+00:00</t>
+          <t>2026-10-17T08:52:38.877990+00:00</t>
         </is>
       </c>
     </row>
@@ -38893,7 +38893,7 @@
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.395768+00:00</t>
+          <t>2026-10-17T08:52:38.877994+00:00</t>
         </is>
       </c>
     </row>
@@ -38985,7 +38985,7 @@
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.395771+00:00</t>
+          <t>2026-10-17T08:52:38.877997+00:00</t>
         </is>
       </c>
     </row>
@@ -39077,7 +39077,7 @@
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.395775+00:00</t>
+          <t>2026-10-17T08:52:38.878000+00:00</t>
         </is>
       </c>
     </row>
@@ -39169,7 +39169,7 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.395778+00:00</t>
+          <t>2026-10-17T08:52:38.878003+00:00</t>
         </is>
       </c>
     </row>
@@ -39257,7 +39257,7 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.395780+00:00</t>
+          <t>2026-10-17T08:52:38.878007+00:00</t>
         </is>
       </c>
     </row>
@@ -39349,7 +39349,7 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.395783+00:00</t>
+          <t>2026-10-17T08:52:38.878010+00:00</t>
         </is>
       </c>
     </row>
@@ -39441,7 +39441,7 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.395787+00:00</t>
+          <t>2026-10-17T08:52:38.878013+00:00</t>
         </is>
       </c>
     </row>
@@ -39529,7 +39529,7 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.395790+00:00</t>
+          <t>2026-10-17T08:52:38.878016+00:00</t>
         </is>
       </c>
     </row>
@@ -39621,7 +39621,7 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-10-17T08:51:35.395793+00:00</t>
+          <t>2026-10-17T08:52:38.878020+00:00</t>
         </is>
       </c>
     </row>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -10613,7 +10613,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H239" t="b">
@@ -11508,7 +11508,7 @@
         </is>
       </c>
       <c r="H260" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I260" t="n">
         <v>1</v>
@@ -14490,11 +14490,11 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>explicit_no_attachments_in_complete_JATS</t>
         </is>
       </c>
       <c r="H330" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I330" t="n">
         <v>0</v>
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.716531+00:00</t>
+          <t>2026-10-17T08:53:27.689130+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.717428+00:00</t>
+          <t>2026-10-17T08:53:27.690136+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.717445+00:00</t>
+          <t>2026-10-17T08:53:27.690161+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.717694+00:00</t>
+          <t>2026-10-17T08:53:27.690440+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.718864+00:00</t>
+          <t>2026-10-17T08:53:27.691576+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.719488+00:00</t>
+          <t>2026-10-17T08:53:27.692049+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.724821+00:00</t>
+          <t>2026-10-17T08:53:27.697241+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.727114+00:00</t>
+          <t>2026-10-17T08:53:27.699490+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.728141+00:00</t>
+          <t>2026-10-17T08:53:27.700845+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.728645+00:00</t>
+          <t>2026-10-17T08:53:27.701576+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.729402+00:00</t>
+          <t>2026-10-17T08:53:27.702459+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.730074+00:00</t>
+          <t>2026-10-17T08:53:27.703113+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.730983+00:00</t>
+          <t>2026-10-17T08:53:27.704007+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.731230+00:00</t>
+          <t>2026-10-17T08:53:27.704240+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.732088+00:00</t>
+          <t>2026-10-17T08:53:27.705409+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.739642+00:00</t>
+          <t>2026-10-17T08:53:27.713660+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.740488+00:00</t>
+          <t>2026-10-17T08:53:27.714537+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.741731+00:00</t>
+          <t>2026-10-17T08:53:27.716095+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.744380+00:00</t>
+          <t>2026-10-17T08:53:27.719570+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.745493+00:00</t>
+          <t>2026-10-17T08:53:27.720771+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.746674+00:00</t>
+          <t>2026-10-17T08:53:27.722433+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.750938+00:00</t>
+          <t>2026-10-17T08:53:27.727375+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.753168+00:00</t>
+          <t>2026-10-17T08:53:27.729978+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.755033+00:00</t>
+          <t>2026-10-17T08:53:27.732186+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.755897+00:00</t>
+          <t>2026-10-17T08:53:27.733155+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.756269+00:00</t>
+          <t>2026-10-17T08:53:27.733633+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.758424+00:00</t>
+          <t>2026-10-17T08:53:27.735711+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.759661+00:00</t>
+          <t>2026-10-17T08:53:27.737380+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.761699+00:00</t>
+          <t>2026-10-17T08:53:27.740520+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.763645+00:00</t>
+          <t>2026-10-17T08:53:27.743134+00:00</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.764185+00:00</t>
+          <t>2026-10-17T08:53:27.743970+00:00</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.764747+00:00</t>
+          <t>2026-10-17T08:53:27.744940+00:00</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.766385+00:00</t>
+          <t>2026-10-17T08:53:27.746646+00:00</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.769143+00:00</t>
+          <t>2026-10-17T08:53:27.749667+00:00</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.771471+00:00</t>
+          <t>2026-10-17T08:53:27.752446+00:00</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.772773+00:00</t>
+          <t>2026-10-17T08:53:27.754560+00:00</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.775623+00:00</t>
+          <t>2026-10-17T08:53:27.758372+00:00</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.776326+00:00</t>
+          <t>2026-10-17T08:53:27.759134+00:00</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.777944+00:00</t>
+          <t>2026-10-17T08:53:27.760848+00:00</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.778215+00:00</t>
+          <t>2026-10-17T08:53:27.761116+00:00</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.780202+00:00</t>
+          <t>2026-10-17T08:53:27.763255+00:00</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.783148+00:00</t>
+          <t>2026-10-17T08:53:27.767281+00:00</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.784471+00:00</t>
+          <t>2026-10-17T08:53:27.768794+00:00</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.785085+00:00</t>
+          <t>2026-10-17T08:53:27.769872+00:00</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.787687+00:00</t>
+          <t>2026-10-17T08:53:27.772880+00:00</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.788870+00:00</t>
+          <t>2026-10-17T08:53:27.774339+00:00</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.792431+00:00</t>
+          <t>2026-10-17T08:53:27.777843+00:00</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.794232+00:00</t>
+          <t>2026-10-17T08:53:27.779569+00:00</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.796072+00:00</t>
+          <t>2026-10-17T08:53:27.781387+00:00</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.797127+00:00</t>
+          <t>2026-10-17T08:53:27.782356+00:00</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.797623+00:00</t>
+          <t>2026-10-17T08:53:27.782820+00:00</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.797987+00:00</t>
+          <t>2026-10-17T08:53:27.783193+00:00</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.799620+00:00</t>
+          <t>2026-10-17T08:53:27.784814+00:00</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.800955+00:00</t>
+          <t>2026-10-17T08:53:27.786369+00:00</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.802602+00:00</t>
+          <t>2026-10-17T08:53:27.787860+00:00</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.802958+00:00</t>
+          <t>2026-10-17T08:53:27.788189+00:00</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.804236+00:00</t>
+          <t>2026-10-17T08:53:27.789506+00:00</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.805661+00:00</t>
+          <t>2026-10-17T08:53:27.790976+00:00</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.806286+00:00</t>
+          <t>2026-10-17T08:53:27.791627+00:00</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.807260+00:00</t>
+          <t>2026-10-17T08:53:27.792595+00:00</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.807700+00:00</t>
+          <t>2026-10-17T08:53:27.792978+00:00</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.812888+00:00</t>
+          <t>2026-10-17T08:53:27.799128+00:00</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.813323+00:00</t>
+          <t>2026-10-17T08:53:27.800097+00:00</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.813908+00:00</t>
+          <t>2026-10-17T08:53:27.800904+00:00</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.814372+00:00</t>
+          <t>2026-10-17T08:53:27.801406+00:00</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.815422+00:00</t>
+          <t>2026-10-17T08:53:27.802611+00:00</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.818309+00:00</t>
+          <t>2026-10-17T08:53:27.806184+00:00</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.818553+00:00</t>
+          <t>2026-10-17T08:53:27.806504+00:00</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.823036+00:00</t>
+          <t>2026-10-17T08:53:27.811210+00:00</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.823888+00:00</t>
+          <t>2026-10-17T08:53:27.812067+00:00</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.826458+00:00</t>
+          <t>2026-10-17T08:53:27.814429+00:00</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.828338+00:00</t>
+          <t>2026-10-17T08:53:27.816266+00:00</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.829330+00:00</t>
+          <t>2026-10-17T08:53:27.817224+00:00</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.830879+00:00</t>
+          <t>2026-10-17T08:53:27.818682+00:00</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.833145+00:00</t>
+          <t>2026-10-17T08:53:27.821071+00:00</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.840888+00:00</t>
+          <t>2026-10-17T08:53:27.830303+00:00</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.842290+00:00</t>
+          <t>2026-10-17T08:53:27.831875+00:00</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.842484+00:00</t>
+          <t>2026-10-17T08:53:27.832061+00:00</t>
         </is>
       </c>
     </row>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.842497+00:00</t>
+          <t>2026-10-17T08:53:27.832077+00:00</t>
         </is>
       </c>
     </row>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.847593+00:00</t>
+          <t>2026-10-17T08:53:27.837404+00:00</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.847978+00:00</t>
+          <t>2026-10-17T08:53:27.837841+00:00</t>
         </is>
       </c>
     </row>
@@ -33071,7 +33071,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.848408+00:00</t>
+          <t>2026-10-17T08:53:27.838198+00:00</t>
         </is>
       </c>
     </row>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.848814+00:00</t>
+          <t>2026-10-17T08:53:27.838625+00:00</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.849601+00:00</t>
+          <t>2026-10-17T08:53:27.839559+00:00</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33383,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.850997+00:00</t>
+          <t>2026-10-17T08:53:27.840999+00:00</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.851871+00:00</t>
+          <t>2026-10-17T08:53:27.841857+00:00</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.852181+00:00</t>
+          <t>2026-10-17T08:53:27.842175+00:00</t>
         </is>
       </c>
     </row>
@@ -33699,7 +33699,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.852828+00:00</t>
+          <t>2026-10-17T08:53:27.842938+00:00</t>
         </is>
       </c>
     </row>
@@ -33799,7 +33799,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.852842+00:00</t>
+          <t>2026-10-17T08:53:27.842961+00:00</t>
         </is>
       </c>
     </row>
@@ -33907,7 +33907,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.852892+00:00</t>
+          <t>2026-10-17T08:53:27.843016+00:00</t>
         </is>
       </c>
     </row>
@@ -34015,7 +34015,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.853127+00:00</t>
+          <t>2026-10-17T08:53:27.843250+00:00</t>
         </is>
       </c>
     </row>
@@ -34123,7 +34123,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.853247+00:00</t>
+          <t>2026-10-17T08:53:27.843423+00:00</t>
         </is>
       </c>
     </row>
@@ -34235,7 +34235,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.853376+00:00</t>
+          <t>2026-10-17T08:53:27.843543+00:00</t>
         </is>
       </c>
     </row>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.853765+00:00</t>
+          <t>2026-10-17T08:53:27.843923+00:00</t>
         </is>
       </c>
     </row>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.853948+00:00</t>
+          <t>2026-10-17T08:53:27.844121+00:00</t>
         </is>
       </c>
     </row>
@@ -34563,7 +34563,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.854002+00:00</t>
+          <t>2026-10-17T08:53:27.844179+00:00</t>
         </is>
       </c>
     </row>
@@ -34675,7 +34675,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.854065+00:00</t>
+          <t>2026-10-17T08:53:27.844243+00:00</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.854214+00:00</t>
+          <t>2026-10-17T08:53:27.844407+00:00</t>
         </is>
       </c>
     </row>
@@ -34899,7 +34899,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.854261+00:00</t>
+          <t>2026-10-17T08:53:27.844457+00:00</t>
         </is>
       </c>
     </row>
@@ -35007,7 +35007,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.854757+00:00</t>
+          <t>2026-10-17T08:53:27.845103+00:00</t>
         </is>
       </c>
     </row>
@@ -35115,7 +35115,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.854814+00:00</t>
+          <t>2026-10-17T08:53:27.845188+00:00</t>
         </is>
       </c>
     </row>
@@ -35215,7 +35215,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.854824+00:00</t>
+          <t>2026-10-17T08:53:27.845200+00:00</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.863783+00:00</t>
+          <t>2026-10-17T08:53:27.855402+00:00</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.863830+00:00</t>
+          <t>2026-10-17T08:53:27.855478+00:00</t>
         </is>
       </c>
     </row>
@@ -35535,7 +35535,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.863917+00:00</t>
+          <t>2026-10-17T08:53:27.855598+00:00</t>
         </is>
       </c>
     </row>
@@ -35643,7 +35643,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.864147+00:00</t>
+          <t>2026-10-17T08:53:27.855895+00:00</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.865250+00:00</t>
+          <t>2026-10-17T08:53:27.857171+00:00</t>
         </is>
       </c>
     </row>
@@ -35853,7 +35853,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.865368+00:00</t>
+          <t>2026-10-17T08:53:27.857282+00:00</t>
         </is>
       </c>
     </row>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.865381+00:00</t>
+          <t>2026-10-17T08:53:27.857325+00:00</t>
         </is>
       </c>
     </row>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.865464+00:00</t>
+          <t>2026-10-17T08:53:27.857507+00:00</t>
         </is>
       </c>
     </row>
@@ -36151,7 +36151,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.865566+00:00</t>
+          <t>2026-10-17T08:53:27.857875+00:00</t>
         </is>
       </c>
     </row>
@@ -36253,7 +36253,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.865674+00:00</t>
+          <t>2026-10-17T08:53:27.858003+00:00</t>
         </is>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.865685+00:00</t>
+          <t>2026-10-17T08:53:27.858016+00:00</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.865837+00:00</t>
+          <t>2026-10-17T08:53:27.858172+00:00</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.865849+00:00</t>
+          <t>2026-10-17T08:53:27.858184+00:00</t>
         </is>
       </c>
     </row>
@@ -36645,7 +36645,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.865946+00:00</t>
+          <t>2026-10-17T08:53:27.858285+00:00</t>
         </is>
       </c>
     </row>
@@ -36739,7 +36739,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.865957+00:00</t>
+          <t>2026-10-17T08:53:27.858325+00:00</t>
         </is>
       </c>
     </row>
@@ -36841,7 +36841,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.866089+00:00</t>
+          <t>2026-10-17T08:53:27.858465+00:00</t>
         </is>
       </c>
     </row>
@@ -36935,7 +36935,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.866101+00:00</t>
+          <t>2026-10-17T08:53:27.858478+00:00</t>
         </is>
       </c>
     </row>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.866190+00:00</t>
+          <t>2026-10-17T08:53:27.858570+00:00</t>
         </is>
       </c>
     </row>
@@ -37139,7 +37139,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.866349+00:00</t>
+          <t>2026-10-17T08:53:27.858702+00:00</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.866361+00:00</t>
+          <t>2026-10-17T08:53:27.858713+00:00</t>
         </is>
       </c>
     </row>
@@ -37335,7 +37335,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.866480+00:00</t>
+          <t>2026-10-17T08:53:27.858928+00:00</t>
         </is>
       </c>
     </row>
@@ -37429,7 +37429,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.866492+00:00</t>
+          <t>2026-10-17T08:53:27.859016+00:00</t>
         </is>
       </c>
     </row>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.866594+00:00</t>
+          <t>2026-10-17T08:53:27.859132+00:00</t>
         </is>
       </c>
     </row>
@@ -37633,7 +37633,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.866813+00:00</t>
+          <t>2026-10-17T08:53:27.859386+00:00</t>
         </is>
       </c>
     </row>
@@ -37727,7 +37727,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.866824+00:00</t>
+          <t>2026-10-17T08:53:27.859402+00:00</t>
         </is>
       </c>
     </row>
@@ -37829,7 +37829,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.866982+00:00</t>
+          <t>2026-10-17T08:53:27.859570+00:00</t>
         </is>
       </c>
     </row>
@@ -37931,7 +37931,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.867192+00:00</t>
+          <t>2026-10-17T08:53:27.859858+00:00</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38033,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.867408+00:00</t>
+          <t>2026-10-17T08:53:27.860078+00:00</t>
         </is>
       </c>
     </row>
@@ -38127,7 +38127,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.867421+00:00</t>
+          <t>2026-10-17T08:53:27.860092+00:00</t>
         </is>
       </c>
     </row>
@@ -38229,7 +38229,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.867528+00:00</t>
+          <t>2026-10-17T08:53:27.860200+00:00</t>
         </is>
       </c>
     </row>
@@ -38323,7 +38323,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.867538+00:00</t>
+          <t>2026-10-17T08:53:27.860212+00:00</t>
         </is>
       </c>
     </row>
@@ -38425,7 +38425,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.867625+00:00</t>
+          <t>2026-10-17T08:53:27.860324+00:00</t>
         </is>
       </c>
     </row>
@@ -38533,7 +38533,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.868698+00:00</t>
+          <t>2026-10-17T08:53:27.861550+00:00</t>
         </is>
       </c>
     </row>
@@ -38625,7 +38625,7 @@
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.877931+00:00</t>
+          <t>2026-10-17T08:53:27.871932+00:00</t>
         </is>
       </c>
     </row>
@@ -38713,7 +38713,7 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.877985+00:00</t>
+          <t>2026-10-17T08:53:27.872016+00:00</t>
         </is>
       </c>
     </row>
@@ -38801,7 +38801,7 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.877990+00:00</t>
+          <t>2026-10-17T08:53:27.872024+00:00</t>
         </is>
       </c>
     </row>
@@ -38893,7 +38893,7 @@
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.877994+00:00</t>
+          <t>2026-10-17T08:53:27.872028+00:00</t>
         </is>
       </c>
     </row>
@@ -38985,7 +38985,7 @@
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.877997+00:00</t>
+          <t>2026-10-17T08:53:27.872032+00:00</t>
         </is>
       </c>
     </row>
@@ -39077,7 +39077,7 @@
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.878000+00:00</t>
+          <t>2026-10-17T08:53:27.872036+00:00</t>
         </is>
       </c>
     </row>
@@ -39169,7 +39169,7 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.878003+00:00</t>
+          <t>2026-10-17T08:53:27.872038+00:00</t>
         </is>
       </c>
     </row>
@@ -39257,7 +39257,7 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.878007+00:00</t>
+          <t>2026-10-17T08:53:27.872042+00:00</t>
         </is>
       </c>
     </row>
@@ -39349,7 +39349,7 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.878010+00:00</t>
+          <t>2026-10-17T08:53:27.872045+00:00</t>
         </is>
       </c>
     </row>
@@ -39441,7 +39441,7 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.878013+00:00</t>
+          <t>2026-10-17T08:53:27.872048+00:00</t>
         </is>
       </c>
     </row>
@@ -39529,7 +39529,7 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.878016+00:00</t>
+          <t>2026-10-17T08:53:27.872052+00:00</t>
         </is>
       </c>
     </row>
@@ -39621,7 +39621,7 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-10-17T08:52:38.878020+00:00</t>
+          <t>2026-10-17T08:53:27.872056+00:00</t>
         </is>
       </c>
     </row>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -1181,7 +1181,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.689130+00:00</t>
+          <t>2026-10-17T08:56:30.799244+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.690136+00:00</t>
+          <t>2026-10-17T08:56:30.800160+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.690161+00:00</t>
+          <t>2026-10-17T08:56:30.800178+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.690440+00:00</t>
+          <t>2026-10-17T08:56:30.800416+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.691576+00:00</t>
+          <t>2026-10-17T08:56:30.801602+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.692049+00:00</t>
+          <t>2026-10-17T08:56:30.802059+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.697241+00:00</t>
+          <t>2026-10-17T08:56:30.807348+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.699490+00:00</t>
+          <t>2026-10-17T08:56:30.809749+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.700845+00:00</t>
+          <t>2026-10-17T08:56:30.810691+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.701576+00:00</t>
+          <t>2026-10-17T08:56:30.811017+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.702459+00:00</t>
+          <t>2026-10-17T08:56:30.811723+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.703113+00:00</t>
+          <t>2026-10-17T08:56:30.812445+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.704007+00:00</t>
+          <t>2026-10-17T08:56:30.813349+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.704240+00:00</t>
+          <t>2026-10-17T08:56:30.813638+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.705409+00:00</t>
+          <t>2026-10-17T08:56:30.814495+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.713660+00:00</t>
+          <t>2026-10-17T08:56:30.821922+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.714537+00:00</t>
+          <t>2026-10-17T08:56:30.822928+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.716095+00:00</t>
+          <t>2026-10-17T08:56:30.824223+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.719570+00:00</t>
+          <t>2026-10-17T08:56:30.826907+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.720771+00:00</t>
+          <t>2026-10-17T08:56:30.828064+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.722433+00:00</t>
+          <t>2026-10-17T08:56:30.829681+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.727375+00:00</t>
+          <t>2026-10-17T08:56:30.834250+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.729978+00:00</t>
+          <t>2026-10-17T08:56:30.836758+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.732186+00:00</t>
+          <t>2026-10-17T08:56:30.838828+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.733155+00:00</t>
+          <t>2026-10-17T08:56:30.839621+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.733633+00:00</t>
+          <t>2026-10-17T08:56:30.839984+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.735711+00:00</t>
+          <t>2026-10-17T08:56:30.842205+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.737380+00:00</t>
+          <t>2026-10-17T08:56:30.843576+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.740520+00:00</t>
+          <t>2026-10-17T08:56:30.846174+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.743134+00:00</t>
+          <t>2026-10-17T08:56:30.848229+00:00</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.743970+00:00</t>
+          <t>2026-10-17T08:56:30.848812+00:00</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.744940+00:00</t>
+          <t>2026-10-17T08:56:30.849376+00:00</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.746646+00:00</t>
+          <t>2026-10-17T08:56:30.851004+00:00</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.749667+00:00</t>
+          <t>2026-10-17T08:56:30.853754+00:00</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.752446+00:00</t>
+          <t>2026-10-17T08:56:30.855843+00:00</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.754560+00:00</t>
+          <t>2026-10-17T08:56:30.857273+00:00</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.758372+00:00</t>
+          <t>2026-10-17T08:56:30.860558+00:00</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.759134+00:00</t>
+          <t>2026-10-17T08:56:30.861685+00:00</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.760848+00:00</t>
+          <t>2026-10-17T08:56:30.863542+00:00</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.761116+00:00</t>
+          <t>2026-10-17T08:56:30.863831+00:00</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.763255+00:00</t>
+          <t>2026-10-17T08:56:30.865744+00:00</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.767281+00:00</t>
+          <t>2026-10-17T08:56:30.869036+00:00</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.768794+00:00</t>
+          <t>2026-10-17T08:56:30.870479+00:00</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.769872+00:00</t>
+          <t>2026-10-17T08:56:30.871035+00:00</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.772880+00:00</t>
+          <t>2026-10-17T08:56:30.873770+00:00</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.774339+00:00</t>
+          <t>2026-10-17T08:56:30.874954+00:00</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.777843+00:00</t>
+          <t>2026-10-17T08:56:30.878589+00:00</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.779569+00:00</t>
+          <t>2026-10-17T08:56:30.880216+00:00</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.781387+00:00</t>
+          <t>2026-10-17T08:56:30.882129+00:00</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.782356+00:00</t>
+          <t>2026-10-17T08:56:30.883090+00:00</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.782820+00:00</t>
+          <t>2026-10-17T08:56:30.883575+00:00</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.783193+00:00</t>
+          <t>2026-10-17T08:56:30.883957+00:00</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.784814+00:00</t>
+          <t>2026-10-17T08:56:30.885569+00:00</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.786369+00:00</t>
+          <t>2026-10-17T08:56:30.887246+00:00</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.787860+00:00</t>
+          <t>2026-10-17T08:56:30.888775+00:00</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.788189+00:00</t>
+          <t>2026-10-17T08:56:30.889115+00:00</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.789506+00:00</t>
+          <t>2026-10-17T08:56:30.890618+00:00</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.790976+00:00</t>
+          <t>2026-10-17T08:56:30.893276+00:00</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.791627+00:00</t>
+          <t>2026-10-17T08:56:30.894536+00:00</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.792595+00:00</t>
+          <t>2026-10-17T08:56:30.895991+00:00</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.792978+00:00</t>
+          <t>2026-10-17T08:56:30.896469+00:00</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.799128+00:00</t>
+          <t>2026-10-17T08:56:30.902352+00:00</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.800097+00:00</t>
+          <t>2026-10-17T08:56:30.903092+00:00</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.800904+00:00</t>
+          <t>2026-10-17T08:56:30.903810+00:00</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.801406+00:00</t>
+          <t>2026-10-17T08:56:30.904742+00:00</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.802611+00:00</t>
+          <t>2026-10-17T08:56:30.906926+00:00</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.806184+00:00</t>
+          <t>2026-10-17T08:56:30.911982+00:00</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.806504+00:00</t>
+          <t>2026-10-17T08:56:30.912517+00:00</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.811210+00:00</t>
+          <t>2026-10-17T08:56:30.917042+00:00</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.812067+00:00</t>
+          <t>2026-10-17T08:56:30.918118+00:00</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.814429+00:00</t>
+          <t>2026-10-17T08:56:30.920324+00:00</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.816266+00:00</t>
+          <t>2026-10-17T08:56:30.922193+00:00</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.817224+00:00</t>
+          <t>2026-10-17T08:56:30.923487+00:00</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.818682+00:00</t>
+          <t>2026-10-17T08:56:30.925228+00:00</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.821071+00:00</t>
+          <t>2026-10-17T08:56:30.927813+00:00</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.830303+00:00</t>
+          <t>2026-10-17T08:56:30.936077+00:00</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.831875+00:00</t>
+          <t>2026-10-17T08:56:30.937459+00:00</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.832061+00:00</t>
+          <t>2026-10-17T08:56:30.937638+00:00</t>
         </is>
       </c>
     </row>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.832077+00:00</t>
+          <t>2026-10-17T08:56:30.937652+00:00</t>
         </is>
       </c>
     </row>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.837404+00:00</t>
+          <t>2026-10-17T08:56:30.943248+00:00</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.837841+00:00</t>
+          <t>2026-10-17T08:56:30.943744+00:00</t>
         </is>
       </c>
     </row>
@@ -33071,7 +33071,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.838198+00:00</t>
+          <t>2026-10-17T08:56:30.944104+00:00</t>
         </is>
       </c>
     </row>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.838625+00:00</t>
+          <t>2026-10-17T08:56:30.944517+00:00</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.839559+00:00</t>
+          <t>2026-10-17T08:56:30.945366+00:00</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33383,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.840999+00:00</t>
+          <t>2026-10-17T08:56:30.947281+00:00</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.841857+00:00</t>
+          <t>2026-10-17T08:56:30.948208+00:00</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.842175+00:00</t>
+          <t>2026-10-17T08:56:30.948540+00:00</t>
         </is>
       </c>
     </row>
@@ -33699,7 +33699,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.842938+00:00</t>
+          <t>2026-10-17T08:56:30.949180+00:00</t>
         </is>
       </c>
     </row>
@@ -33799,7 +33799,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.842961+00:00</t>
+          <t>2026-10-17T08:56:30.949195+00:00</t>
         </is>
       </c>
     </row>
@@ -33907,7 +33907,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.843016+00:00</t>
+          <t>2026-10-17T08:56:30.949242+00:00</t>
         </is>
       </c>
     </row>
@@ -34015,7 +34015,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.843250+00:00</t>
+          <t>2026-10-17T08:56:30.949514+00:00</t>
         </is>
       </c>
     </row>
@@ -34123,7 +34123,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.843423+00:00</t>
+          <t>2026-10-17T08:56:30.949641+00:00</t>
         </is>
       </c>
     </row>
@@ -34235,7 +34235,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.843543+00:00</t>
+          <t>2026-10-17T08:56:30.949839+00:00</t>
         </is>
       </c>
     </row>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.843923+00:00</t>
+          <t>2026-10-17T08:56:30.950228+00:00</t>
         </is>
       </c>
     </row>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.844121+00:00</t>
+          <t>2026-10-17T08:56:30.950449+00:00</t>
         </is>
       </c>
     </row>
@@ -34563,7 +34563,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.844179+00:00</t>
+          <t>2026-10-17T08:56:30.950512+00:00</t>
         </is>
       </c>
     </row>
@@ -34675,7 +34675,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.844243+00:00</t>
+          <t>2026-10-17T08:56:30.950575+00:00</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.844407+00:00</t>
+          <t>2026-10-17T08:56:30.950719+00:00</t>
         </is>
       </c>
     </row>
@@ -34899,7 +34899,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.844457+00:00</t>
+          <t>2026-10-17T08:56:30.950848+00:00</t>
         </is>
       </c>
     </row>
@@ -35007,7 +35007,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.845103+00:00</t>
+          <t>2026-10-17T08:56:30.951327+00:00</t>
         </is>
       </c>
     </row>
@@ -35115,7 +35115,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.845188+00:00</t>
+          <t>2026-10-17T08:56:30.951384+00:00</t>
         </is>
       </c>
     </row>
@@ -35215,7 +35215,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.845200+00:00</t>
+          <t>2026-10-17T08:56:30.951395+00:00</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.855402+00:00</t>
+          <t>2026-10-17T08:56:30.961746+00:00</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.855478+00:00</t>
+          <t>2026-10-17T08:56:30.961828+00:00</t>
         </is>
       </c>
     </row>
@@ -35535,7 +35535,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.855598+00:00</t>
+          <t>2026-10-17T08:56:30.961948+00:00</t>
         </is>
       </c>
     </row>
@@ -35643,7 +35643,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.855895+00:00</t>
+          <t>2026-10-17T08:56:30.962190+00:00</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.857171+00:00</t>
+          <t>2026-10-17T08:56:30.963316+00:00</t>
         </is>
       </c>
     </row>
@@ -35853,7 +35853,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.857282+00:00</t>
+          <t>2026-10-17T08:56:30.963424+00:00</t>
         </is>
       </c>
     </row>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.857325+00:00</t>
+          <t>2026-10-17T08:56:30.963437+00:00</t>
         </is>
       </c>
     </row>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.857507+00:00</t>
+          <t>2026-10-17T08:56:30.963516+00:00</t>
         </is>
       </c>
     </row>
@@ -36151,7 +36151,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.857875+00:00</t>
+          <t>2026-10-17T08:56:30.963597+00:00</t>
         </is>
       </c>
     </row>
@@ -36253,7 +36253,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.858003+00:00</t>
+          <t>2026-10-17T08:56:30.963706+00:00</t>
         </is>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.858016+00:00</t>
+          <t>2026-10-17T08:56:30.963718+00:00</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.858172+00:00</t>
+          <t>2026-10-17T08:56:30.963872+00:00</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.858184+00:00</t>
+          <t>2026-10-17T08:56:30.963884+00:00</t>
         </is>
       </c>
     </row>
@@ -36645,7 +36645,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.858285+00:00</t>
+          <t>2026-10-17T08:56:30.963984+00:00</t>
         </is>
       </c>
     </row>
@@ -36739,7 +36739,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.858325+00:00</t>
+          <t>2026-10-17T08:56:30.963994+00:00</t>
         </is>
       </c>
     </row>
@@ -36841,7 +36841,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.858465+00:00</t>
+          <t>2026-10-17T08:56:30.964125+00:00</t>
         </is>
       </c>
     </row>
@@ -36935,7 +36935,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.858478+00:00</t>
+          <t>2026-10-17T08:56:30.964136+00:00</t>
         </is>
       </c>
     </row>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.858570+00:00</t>
+          <t>2026-10-17T08:56:30.964224+00:00</t>
         </is>
       </c>
     </row>
@@ -37139,7 +37139,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.858702+00:00</t>
+          <t>2026-10-17T08:56:30.964371+00:00</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.858713+00:00</t>
+          <t>2026-10-17T08:56:30.964385+00:00</t>
         </is>
       </c>
     </row>
@@ -37335,7 +37335,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.858928+00:00</t>
+          <t>2026-10-17T08:56:30.964503+00:00</t>
         </is>
       </c>
     </row>
@@ -37429,7 +37429,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.859016+00:00</t>
+          <t>2026-10-17T08:56:30.964514+00:00</t>
         </is>
       </c>
     </row>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.859132+00:00</t>
+          <t>2026-10-17T08:56:30.964615+00:00</t>
         </is>
       </c>
     </row>
@@ -37633,7 +37633,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.859386+00:00</t>
+          <t>2026-10-17T08:56:30.964838+00:00</t>
         </is>
       </c>
     </row>
@@ -37727,7 +37727,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.859402+00:00</t>
+          <t>2026-10-17T08:56:30.964849+00:00</t>
         </is>
       </c>
     </row>
@@ -37829,7 +37829,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.859570+00:00</t>
+          <t>2026-10-17T08:56:30.965006+00:00</t>
         </is>
       </c>
     </row>
@@ -37931,7 +37931,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.859858+00:00</t>
+          <t>2026-10-17T08:56:30.965196+00:00</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38033,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.860078+00:00</t>
+          <t>2026-10-17T08:56:30.965458+00:00</t>
         </is>
       </c>
     </row>
@@ -38127,7 +38127,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.860092+00:00</t>
+          <t>2026-10-17T08:56:30.965500+00:00</t>
         </is>
       </c>
     </row>
@@ -38229,7 +38229,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.860200+00:00</t>
+          <t>2026-10-17T08:56:30.965632+00:00</t>
         </is>
       </c>
     </row>
@@ -38323,7 +38323,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.860212+00:00</t>
+          <t>2026-10-17T08:56:30.965644+00:00</t>
         </is>
       </c>
     </row>
@@ -38425,7 +38425,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.860324+00:00</t>
+          <t>2026-10-17T08:56:30.965732+00:00</t>
         </is>
       </c>
     </row>
@@ -38533,7 +38533,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.861550+00:00</t>
+          <t>2026-10-17T08:56:30.966804+00:00</t>
         </is>
       </c>
     </row>
@@ -38625,7 +38625,7 @@
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.871932+00:00</t>
+          <t>2026-10-17T08:56:30.976947+00:00</t>
         </is>
       </c>
     </row>
@@ -38657,13 +38657,21 @@
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R02274_2016_ANAEROBIC_DIGESTION_OF_WASTEWATER_WITH_HIGH_SULFATE_CONCENTRATION_USING.pdf</t>
+        </is>
+      </c>
       <c r="I138" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-fulltexts/R02274_2016_ANAEROBIC_DIGESTION_OF_WASTEWATER_WITH_HIGH_SULFATE_CONCENTRATION_USING.pdf</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr"/>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R02274_2016_ANAEROBIC_DIGESTION_OF_WASTEWATER_WITH_HIGH_SULFATE_CONCENTRATION_USING.pdf</t>
+        </is>
+      </c>
       <c r="K138" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -38679,15 +38687,19 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
-        </is>
-      </c>
-      <c r="P138" t="inlineStr"/>
+          <t>local_acquired_pending_remote_readback</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>https://www.scielo.br/j/bjce/a/Fsb5BG69HCqpVRTqkxS4stm/?lang=en&amp;format=pdf</t>
+        </is>
+      </c>
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr">
         <is>
@@ -38713,7 +38725,7 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.872016+00:00</t>
+          <t>2026-10-17T08:56:30.977437+00:00</t>
         </is>
       </c>
     </row>
@@ -38801,7 +38813,7 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.872024+00:00</t>
+          <t>2026-10-17T08:56:30.977455+00:00</t>
         </is>
       </c>
     </row>
@@ -38893,7 +38905,7 @@
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.872028+00:00</t>
+          <t>2026-10-17T08:56:30.977459+00:00</t>
         </is>
       </c>
     </row>
@@ -38985,7 +38997,7 @@
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.872032+00:00</t>
+          <t>2026-10-17T08:56:30.977463+00:00</t>
         </is>
       </c>
     </row>
@@ -39077,7 +39089,7 @@
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.872036+00:00</t>
+          <t>2026-10-17T08:56:30.977466+00:00</t>
         </is>
       </c>
     </row>
@@ -39169,7 +39181,7 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.872038+00:00</t>
+          <t>2026-10-17T08:56:30.977469+00:00</t>
         </is>
       </c>
     </row>
@@ -39257,7 +39269,7 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.872042+00:00</t>
+          <t>2026-10-17T08:56:30.977472+00:00</t>
         </is>
       </c>
     </row>
@@ -39349,7 +39361,7 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.872045+00:00</t>
+          <t>2026-10-17T08:56:30.977495+00:00</t>
         </is>
       </c>
     </row>
@@ -39441,7 +39453,7 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.872048+00:00</t>
+          <t>2026-10-17T08:56:30.977498+00:00</t>
         </is>
       </c>
     </row>
@@ -39529,7 +39541,7 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.872052+00:00</t>
+          <t>2026-10-17T08:56:30.977502+00:00</t>
         </is>
       </c>
     </row>
@@ -39621,7 +39633,7 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-10-17T08:53:27.872056+00:00</t>
+          <t>2026-10-17T08:56:30.977505+00:00</t>
         </is>
       </c>
     </row>
@@ -39636,7 +39648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40284,12 +40296,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R02274</t>
+          <t>R10086</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R02274.main.4c7da8384f1f6e3d</t>
+          <t>R10086.main.84777bfb7a2cd42f</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -40299,16 +40311,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4c7da8384f1f6e3d8bd2681eab23bdb95e3057009cf4c7ec7aacc7cdb9eaf43d</t>
+          <t>84777bfb7a2cd42f9696e060fc79d5de3e72d5ad8fa1e222934a7fcdf97dd365</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>471480</v>
+        <v>984310</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>R02274_2016_ANAEROBIC_DIGESTION_OF_WASTEWATER_WITH_HIGH_SULFATE_CONCENTRATION_USING.pdf</t>
+          <t>R10086_2024_Effect_of_micro-aeration_on_syntrophic_and_methanogenic_activity_in.pdf</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -40320,12 +40332,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R10086</t>
+          <t>R03477</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R10086.main.84777bfb7a2cd42f</t>
+          <t>R03477.main.79583f4a64fb2fbb</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -40335,16 +40347,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>84777bfb7a2cd42f9696e060fc79d5de3e72d5ad8fa1e222934a7fcdf97dd365</t>
+          <t>79583f4a64fb2fbb4a1f4f471fe6001b159213acb1f3bbd19d6dc0be5c714fa5</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>984310</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
+        <v>1714874</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/content/pdf/10.1186/s13568-017-0375-4.pdf</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>R10086_2024_Effect_of_micro-aeration_on_syntrophic_and_methanogenic_activity_in.pdf</t>
+          <t>R03477_2017_Pretreatment_methods_of_lignocellulosic_biomass_for_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -40356,12 +40372,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R03477</t>
+          <t>R09804</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R03477.main.79583f4a64fb2fbb</t>
+          <t>R09804.main.b3cc83d613ad3c36</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -40371,20 +40387,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>79583f4a64fb2fbb4a1f4f471fe6001b159213acb1f3bbd19d6dc0be5c714fa5</t>
+          <t>b3cc83d613ad3c36f93b78eace000ebc5a603966523ee71c2e6a0bd85a8ede3e</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1714874</v>
+        <v>5135812</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1186/s13568-017-0375-4.pdf</t>
+          <t>https://link.springer.com/content/pdf/10.1186/s40643-024-00756-6.pdf</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>R03477_2017_Pretreatment_methods_of_lignocellulosic_biomass_for_anaerobic_digestion.pdf</t>
+          <t>R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -40396,12 +40412,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R09804.main.b3cc83d613ad3c36</t>
+          <t>R11844.main.c41816bf825167dc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -40411,20 +40427,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>b3cc83d613ad3c36f93b78eace000ebc5a603966523ee71c2e6a0bd85a8ede3e</t>
+          <t>c41816bf825167dcb78ff5eb81c8d0dab0d8d8110cd2a23a04cd1109acb34919</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5135812</v>
+        <v>1333380</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1186/s40643-024-00756-6.pdf</t>
+          <t>https://link.springer.com/content/pdf/10.1007/s00253-025-13519-w.pdf</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
+          <t>R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -40436,12 +40452,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R03155</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R11844.main.c41816bf825167dc</t>
+          <t>R03155.main.2875ce0c137df622</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -40451,20 +40467,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>c41816bf825167dcb78ff5eb81c8d0dab0d8d8110cd2a23a04cd1109acb34919</t>
+          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1333380</v>
+        <v>5745828</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1007/s00253-025-13519-w.pdf</t>
+          <t>https://dspace.lib.ntua.gr/xmlui/bitstream/handle/123456789/44237/Msc.%20Thesis_Aristotle_Vasileiou%20THE.pdf?sequence=1&amp;isAllowed=y</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
+          <t>R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -40476,12 +40492,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R03155</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R03155.main.2875ce0c137df622</t>
+          <t>R05213.main.bcab84a15ce93062</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -40491,20 +40507,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
+          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5745828</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>https://dspace.lib.ntua.gr/xmlui/bitstream/handle/123456789/44237/Msc.%20Thesis_Aristotle_Vasileiou%20THE.pdf?sequence=1&amp;isAllowed=y</t>
-        </is>
-      </c>
+        <v>1022660</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
+          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -40516,12 +40528,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R05213</t>
+          <t>R06036</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R05213.main.bcab84a15ce93062</t>
+          <t>R06036.main.0bdc7b19fdb70091</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -40531,16 +40543,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
+          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1022660</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
+        <v>927168</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
+          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -40552,12 +40568,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R06036</t>
+          <t>R09240</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R06036.main.0bdc7b19fdb70091</t>
+          <t>R09240.main.da8dbeb874b19b59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -40567,20 +40583,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
+          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>927168</v>
+        <v>1315227</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
+          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
+          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -40592,12 +40608,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R09240</t>
+          <t>R13899</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R09240.main.da8dbeb874b19b59</t>
+          <t>R13899.main.19143e56fa77ce99</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -40607,20 +40623,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
+          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1315227</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
-        </is>
-      </c>
+        <v>479092</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
+          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -40632,12 +40644,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R13899</t>
+          <t>R13955</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R13899.main.19143e56fa77ce99</t>
+          <t>R13955.main.6714f79deccd703d</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -40647,59 +40659,23 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
+          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>479092</v>
-      </c>
-      <c r="F26" t="inlineStr"/>
+        <v>14662119</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>R13955</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>R13955.main.6714f79deccd703d</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>14662119</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
         <is>
           <t>历史已获取，当前原件未恢复</t>
         </is>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -6853,7 +6853,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.799244+00:00</t>
+          <t>2026-10-17T09:05:12.138303+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.800160+00:00</t>
+          <t>2026-10-17T09:05:12.139160+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.800178+00:00</t>
+          <t>2026-10-17T09:05:12.139178+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.800416+00:00</t>
+          <t>2026-10-17T09:05:12.139416+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.801602+00:00</t>
+          <t>2026-10-17T09:05:12.140506+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.802059+00:00</t>
+          <t>2026-10-17T09:05:12.140974+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.807348+00:00</t>
+          <t>2026-10-17T09:05:12.146217+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.809749+00:00</t>
+          <t>2026-10-17T09:05:12.148521+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.810691+00:00</t>
+          <t>2026-10-17T09:05:12.149661+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.811017+00:00</t>
+          <t>2026-10-17T09:05:12.150022+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.811723+00:00</t>
+          <t>2026-10-17T09:05:12.150740+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.812445+00:00</t>
+          <t>2026-10-17T09:05:12.151400+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.813349+00:00</t>
+          <t>2026-10-17T09:05:12.152463+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.813638+00:00</t>
+          <t>2026-10-17T09:05:12.152724+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.814495+00:00</t>
+          <t>2026-10-17T09:05:12.153614+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.821922+00:00</t>
+          <t>2026-10-17T09:05:12.162220+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.822928+00:00</t>
+          <t>2026-10-17T09:05:12.163044+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.824223+00:00</t>
+          <t>2026-10-17T09:05:12.164343+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.826907+00:00</t>
+          <t>2026-10-17T09:05:12.166919+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.828064+00:00</t>
+          <t>2026-10-17T09:05:12.168114+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.829681+00:00</t>
+          <t>2026-10-17T09:05:12.169498+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.834250+00:00</t>
+          <t>2026-10-17T09:05:12.173980+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.836758+00:00</t>
+          <t>2026-10-17T09:05:12.176337+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.838828+00:00</t>
+          <t>2026-10-17T09:05:12.178413+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.839621+00:00</t>
+          <t>2026-10-17T09:05:12.179373+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.839984+00:00</t>
+          <t>2026-10-17T09:05:12.179764+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.842205+00:00</t>
+          <t>2026-10-17T09:05:12.181880+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.843576+00:00</t>
+          <t>2026-10-17T09:05:12.183179+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.846174+00:00</t>
+          <t>2026-10-17T09:05:12.185461+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.848229+00:00</t>
+          <t>2026-10-17T09:05:12.187564+00:00</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.848812+00:00</t>
+          <t>2026-10-17T09:05:12.188202+00:00</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.849376+00:00</t>
+          <t>2026-10-17T09:05:12.188866+00:00</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.851004+00:00</t>
+          <t>2026-10-17T09:05:12.190607+00:00</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.853754+00:00</t>
+          <t>2026-10-17T09:05:12.193399+00:00</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.855843+00:00</t>
+          <t>2026-10-17T09:05:12.195501+00:00</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.857273+00:00</t>
+          <t>2026-10-17T09:05:12.196677+00:00</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.860558+00:00</t>
+          <t>2026-10-17T09:05:12.199628+00:00</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.861685+00:00</t>
+          <t>2026-10-17T09:05:12.200443+00:00</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.863542+00:00</t>
+          <t>2026-10-17T09:05:12.202034+00:00</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.863831+00:00</t>
+          <t>2026-10-17T09:05:12.202281+00:00</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.865744+00:00</t>
+          <t>2026-10-17T09:05:12.204160+00:00</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.869036+00:00</t>
+          <t>2026-10-17T09:05:12.207112+00:00</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.870479+00:00</t>
+          <t>2026-10-17T09:05:12.208623+00:00</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.871035+00:00</t>
+          <t>2026-10-17T09:05:12.209262+00:00</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.873770+00:00</t>
+          <t>2026-10-17T09:05:12.211966+00:00</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.874954+00:00</t>
+          <t>2026-10-17T09:05:12.213076+00:00</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.878589+00:00</t>
+          <t>2026-10-17T09:05:12.216448+00:00</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.880216+00:00</t>
+          <t>2026-10-17T09:05:12.218077+00:00</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.882129+00:00</t>
+          <t>2026-10-17T09:05:12.219884+00:00</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.883090+00:00</t>
+          <t>2026-10-17T09:05:12.220820+00:00</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.883575+00:00</t>
+          <t>2026-10-17T09:05:12.221253+00:00</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.883957+00:00</t>
+          <t>2026-10-17T09:05:12.221647+00:00</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.885569+00:00</t>
+          <t>2026-10-17T09:05:12.223104+00:00</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.887246+00:00</t>
+          <t>2026-10-17T09:05:12.224454+00:00</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.888775+00:00</t>
+          <t>2026-10-17T09:05:12.226017+00:00</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.889115+00:00</t>
+          <t>2026-10-17T09:05:12.226372+00:00</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.890618+00:00</t>
+          <t>2026-10-17T09:05:12.227567+00:00</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.893276+00:00</t>
+          <t>2026-10-17T09:05:12.228920+00:00</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.894536+00:00</t>
+          <t>2026-10-17T09:05:12.229528+00:00</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.895991+00:00</t>
+          <t>2026-10-17T09:05:12.230460+00:00</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.896469+00:00</t>
+          <t>2026-10-17T09:05:12.230788+00:00</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.902352+00:00</t>
+          <t>2026-10-17T09:05:12.237787+00:00</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.903092+00:00</t>
+          <t>2026-10-17T09:05:12.238262+00:00</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.903810+00:00</t>
+          <t>2026-10-17T09:05:12.238857+00:00</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.904742+00:00</t>
+          <t>2026-10-17T09:05:12.239313+00:00</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.906926+00:00</t>
+          <t>2026-10-17T09:05:12.240420+00:00</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.911982+00:00</t>
+          <t>2026-10-17T09:05:12.243507+00:00</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.912517+00:00</t>
+          <t>2026-10-17T09:05:12.243756+00:00</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.917042+00:00</t>
+          <t>2026-10-17T09:05:12.248046+00:00</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.918118+00:00</t>
+          <t>2026-10-17T09:05:12.248797+00:00</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.920324+00:00</t>
+          <t>2026-10-17T09:05:12.251190+00:00</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.922193+00:00</t>
+          <t>2026-10-17T09:05:12.253136+00:00</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.923487+00:00</t>
+          <t>2026-10-17T09:05:12.254113+00:00</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.925228+00:00</t>
+          <t>2026-10-17T09:05:12.255796+00:00</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.927813+00:00</t>
+          <t>2026-10-17T09:05:12.258026+00:00</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.936077+00:00</t>
+          <t>2026-10-17T09:05:12.266015+00:00</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.937459+00:00</t>
+          <t>2026-10-17T09:05:12.267361+00:00</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.937638+00:00</t>
+          <t>2026-10-17T09:05:12.267514+00:00</t>
         </is>
       </c>
     </row>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.937652+00:00</t>
+          <t>2026-10-17T09:05:12.267527+00:00</t>
         </is>
       </c>
     </row>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.943248+00:00</t>
+          <t>2026-10-17T09:05:12.272793+00:00</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.943744+00:00</t>
+          <t>2026-10-17T09:05:12.273207+00:00</t>
         </is>
       </c>
     </row>
@@ -33071,7 +33071,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.944104+00:00</t>
+          <t>2026-10-17T09:05:12.273603+00:00</t>
         </is>
       </c>
     </row>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.944517+00:00</t>
+          <t>2026-10-17T09:05:12.274002+00:00</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.945366+00:00</t>
+          <t>2026-10-17T09:05:12.274740+00:00</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33383,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.947281+00:00</t>
+          <t>2026-10-17T09:05:12.276449+00:00</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.948208+00:00</t>
+          <t>2026-10-17T09:05:12.277497+00:00</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.948540+00:00</t>
+          <t>2026-10-17T09:05:12.277908+00:00</t>
         </is>
       </c>
     </row>
@@ -33699,7 +33699,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.949180+00:00</t>
+          <t>2026-10-17T09:05:12.278579+00:00</t>
         </is>
       </c>
     </row>
@@ -33799,7 +33799,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.949195+00:00</t>
+          <t>2026-10-17T09:05:12.278595+00:00</t>
         </is>
       </c>
     </row>
@@ -33907,7 +33907,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.949242+00:00</t>
+          <t>2026-10-17T09:05:12.278645+00:00</t>
         </is>
       </c>
     </row>
@@ -34015,7 +34015,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.949514+00:00</t>
+          <t>2026-10-17T09:05:12.278863+00:00</t>
         </is>
       </c>
     </row>
@@ -34123,7 +34123,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.949641+00:00</t>
+          <t>2026-10-17T09:05:12.278984+00:00</t>
         </is>
       </c>
     </row>
@@ -34235,7 +34235,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.949839+00:00</t>
+          <t>2026-10-17T09:05:12.279100+00:00</t>
         </is>
       </c>
     </row>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.950228+00:00</t>
+          <t>2026-10-17T09:05:12.279556+00:00</t>
         </is>
       </c>
     </row>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.950449+00:00</t>
+          <t>2026-10-17T09:05:12.279760+00:00</t>
         </is>
       </c>
     </row>
@@ -34563,7 +34563,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.950512+00:00</t>
+          <t>2026-10-17T09:05:12.279815+00:00</t>
         </is>
       </c>
     </row>
@@ -34675,7 +34675,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.950575+00:00</t>
+          <t>2026-10-17T09:05:12.279893+00:00</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.950719+00:00</t>
+          <t>2026-10-17T09:05:12.280042+00:00</t>
         </is>
       </c>
     </row>
@@ -34899,7 +34899,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.950848+00:00</t>
+          <t>2026-10-17T09:05:12.280087+00:00</t>
         </is>
       </c>
     </row>
@@ -35007,7 +35007,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.951327+00:00</t>
+          <t>2026-10-17T09:05:12.280564+00:00</t>
         </is>
       </c>
     </row>
@@ -35115,7 +35115,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.951384+00:00</t>
+          <t>2026-10-17T09:05:12.280623+00:00</t>
         </is>
       </c>
     </row>
@@ -35215,7 +35215,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.951395+00:00</t>
+          <t>2026-10-17T09:05:12.280633+00:00</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.961746+00:00</t>
+          <t>2026-10-17T09:05:12.290317+00:00</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.961828+00:00</t>
+          <t>2026-10-17T09:05:12.290392+00:00</t>
         </is>
       </c>
     </row>
@@ -35535,7 +35535,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.961948+00:00</t>
+          <t>2026-10-17T09:05:12.290513+00:00</t>
         </is>
       </c>
     </row>
@@ -35643,7 +35643,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.962190+00:00</t>
+          <t>2026-10-17T09:05:12.290749+00:00</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.963316+00:00</t>
+          <t>2026-10-17T09:05:12.291795+00:00</t>
         </is>
       </c>
     </row>
@@ -35853,7 +35853,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.963424+00:00</t>
+          <t>2026-10-17T09:05:12.291880+00:00</t>
         </is>
       </c>
     </row>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.963437+00:00</t>
+          <t>2026-10-17T09:05:12.291891+00:00</t>
         </is>
       </c>
     </row>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.963516+00:00</t>
+          <t>2026-10-17T09:05:12.291974+00:00</t>
         </is>
       </c>
     </row>
@@ -36151,7 +36151,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.963597+00:00</t>
+          <t>2026-10-17T09:05:12.292056+00:00</t>
         </is>
       </c>
     </row>
@@ -36253,7 +36253,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.963706+00:00</t>
+          <t>2026-10-17T09:05:12.292162+00:00</t>
         </is>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.963718+00:00</t>
+          <t>2026-10-17T09:05:12.292172+00:00</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.963872+00:00</t>
+          <t>2026-10-17T09:05:12.292341+00:00</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.963884+00:00</t>
+          <t>2026-10-17T09:05:12.292353+00:00</t>
         </is>
       </c>
     </row>
@@ -36645,7 +36645,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.963984+00:00</t>
+          <t>2026-10-17T09:05:12.292455+00:00</t>
         </is>
       </c>
     </row>
@@ -36739,7 +36739,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.963994+00:00</t>
+          <t>2026-10-17T09:05:12.292466+00:00</t>
         </is>
       </c>
     </row>
@@ -36841,7 +36841,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.964125+00:00</t>
+          <t>2026-10-17T09:05:12.292609+00:00</t>
         </is>
       </c>
     </row>
@@ -36935,7 +36935,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.964136+00:00</t>
+          <t>2026-10-17T09:05:12.292621+00:00</t>
         </is>
       </c>
     </row>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.964224+00:00</t>
+          <t>2026-10-17T09:05:12.292714+00:00</t>
         </is>
       </c>
     </row>
@@ -37139,7 +37139,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.964371+00:00</t>
+          <t>2026-10-17T09:05:12.292852+00:00</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.964385+00:00</t>
+          <t>2026-10-17T09:05:12.292863+00:00</t>
         </is>
       </c>
     </row>
@@ -37335,7 +37335,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.964503+00:00</t>
+          <t>2026-10-17T09:05:12.292985+00:00</t>
         </is>
       </c>
     </row>
@@ -37429,7 +37429,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.964514+00:00</t>
+          <t>2026-10-17T09:05:12.292996+00:00</t>
         </is>
       </c>
     </row>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.964615+00:00</t>
+          <t>2026-10-17T09:05:12.293105+00:00</t>
         </is>
       </c>
     </row>
@@ -37633,7 +37633,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.964838+00:00</t>
+          <t>2026-10-17T09:05:12.293345+00:00</t>
         </is>
       </c>
     </row>
@@ -37727,7 +37727,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.964849+00:00</t>
+          <t>2026-10-17T09:05:12.293358+00:00</t>
         </is>
       </c>
     </row>
@@ -37829,7 +37829,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.965006+00:00</t>
+          <t>2026-10-17T09:05:12.293573+00:00</t>
         </is>
       </c>
     </row>
@@ -37931,7 +37931,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.965196+00:00</t>
+          <t>2026-10-17T09:05:12.293777+00:00</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38033,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.965458+00:00</t>
+          <t>2026-10-17T09:05:12.293970+00:00</t>
         </is>
       </c>
     </row>
@@ -38127,7 +38127,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.965500+00:00</t>
+          <t>2026-10-17T09:05:12.293982+00:00</t>
         </is>
       </c>
     </row>
@@ -38229,7 +38229,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.965632+00:00</t>
+          <t>2026-10-17T09:05:12.294092+00:00</t>
         </is>
       </c>
     </row>
@@ -38323,7 +38323,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.965644+00:00</t>
+          <t>2026-10-17T09:05:12.294103+00:00</t>
         </is>
       </c>
     </row>
@@ -38425,7 +38425,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.965732+00:00</t>
+          <t>2026-10-17T09:05:12.294191+00:00</t>
         </is>
       </c>
     </row>
@@ -38533,7 +38533,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.966804+00:00</t>
+          <t>2026-10-17T09:05:12.295257+00:00</t>
         </is>
       </c>
     </row>
@@ -38625,7 +38625,7 @@
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.976947+00:00</t>
+          <t>2026-10-17T09:05:12.305378+00:00</t>
         </is>
       </c>
     </row>
@@ -38692,7 +38692,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -38725,7 +38725,7 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.977437+00:00</t>
+          <t>2026-10-17T09:05:12.306047+00:00</t>
         </is>
       </c>
     </row>
@@ -38813,7 +38813,7 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.977455+00:00</t>
+          <t>2026-10-17T09:05:12.306074+00:00</t>
         </is>
       </c>
     </row>
@@ -38845,13 +38845,21 @@
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R03477_2017_Pretreatment_methods_of_lignocellulosic_biomass_for_anaerobic_digestion.pdf</t>
+        </is>
+      </c>
       <c r="I140" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-fulltexts/R03477_2017_Pretreatment_methods_of_lignocellulosic_biomass_for_anaerobic_digestion.pdf</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr"/>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R03477_2017_Pretreatment_methods_of_lignocellulosic_biomass_for_anaerobic_digestion.pdf</t>
+        </is>
+      </c>
       <c r="K140" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -38867,17 +38875,17 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1186/s13568-017-0375-4.pdf</t>
+          <t>https://europepmc.org/api/getPdf?pmcid=PMC5371168</t>
         </is>
       </c>
       <c r="Q140" t="inlineStr"/>
@@ -38905,7 +38913,7 @@
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.977459+00:00</t>
+          <t>2026-10-17T09:05:12.307247+00:00</t>
         </is>
       </c>
     </row>
@@ -38997,7 +39005,7 @@
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.977463+00:00</t>
+          <t>2026-10-17T09:05:12.307264+00:00</t>
         </is>
       </c>
     </row>
@@ -39089,7 +39097,7 @@
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.977466+00:00</t>
+          <t>2026-10-17T09:05:12.307268+00:00</t>
         </is>
       </c>
     </row>
@@ -39181,7 +39189,7 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.977469+00:00</t>
+          <t>2026-10-17T09:05:12.307272+00:00</t>
         </is>
       </c>
     </row>
@@ -39269,7 +39277,7 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.977472+00:00</t>
+          <t>2026-10-17T09:05:12.307275+00:00</t>
         </is>
       </c>
     </row>
@@ -39361,7 +39369,7 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.977495+00:00</t>
+          <t>2026-10-17T09:05:12.307278+00:00</t>
         </is>
       </c>
     </row>
@@ -39453,7 +39461,7 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.977498+00:00</t>
+          <t>2026-10-17T09:05:12.307282+00:00</t>
         </is>
       </c>
     </row>
@@ -39541,7 +39549,7 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.977502+00:00</t>
+          <t>2026-10-17T09:05:12.307285+00:00</t>
         </is>
       </c>
     </row>
@@ -39633,7 +39641,7 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-10-17T08:56:30.977505+00:00</t>
+          <t>2026-10-17T09:05:12.307318+00:00</t>
         </is>
       </c>
     </row>
@@ -39648,7 +39656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40332,12 +40340,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R03477</t>
+          <t>R09804</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R03477.main.79583f4a64fb2fbb</t>
+          <t>R09804.main.b3cc83d613ad3c36</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -40347,20 +40355,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>79583f4a64fb2fbb4a1f4f471fe6001b159213acb1f3bbd19d6dc0be5c714fa5</t>
+          <t>b3cc83d613ad3c36f93b78eace000ebc5a603966523ee71c2e6a0bd85a8ede3e</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1714874</v>
+        <v>5135812</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1186/s13568-017-0375-4.pdf</t>
+          <t>https://link.springer.com/content/pdf/10.1186/s40643-024-00756-6.pdf</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>R03477_2017_Pretreatment_methods_of_lignocellulosic_biomass_for_anaerobic_digestion.pdf</t>
+          <t>R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -40372,12 +40380,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R09804.main.b3cc83d613ad3c36</t>
+          <t>R11844.main.c41816bf825167dc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -40387,20 +40395,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>b3cc83d613ad3c36f93b78eace000ebc5a603966523ee71c2e6a0bd85a8ede3e</t>
+          <t>c41816bf825167dcb78ff5eb81c8d0dab0d8d8110cd2a23a04cd1109acb34919</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5135812</v>
+        <v>1333380</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1186/s40643-024-00756-6.pdf</t>
+          <t>https://link.springer.com/content/pdf/10.1007/s00253-025-13519-w.pdf</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
+          <t>R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -40412,12 +40420,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R03155</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R11844.main.c41816bf825167dc</t>
+          <t>R03155.main.2875ce0c137df622</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -40427,20 +40435,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>c41816bf825167dcb78ff5eb81c8d0dab0d8d8110cd2a23a04cd1109acb34919</t>
+          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1333380</v>
+        <v>5745828</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1007/s00253-025-13519-w.pdf</t>
+          <t>https://dspace.lib.ntua.gr/xmlui/bitstream/handle/123456789/44237/Msc.%20Thesis_Aristotle_Vasileiou%20THE.pdf?sequence=1&amp;isAllowed=y</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
+          <t>R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -40452,12 +40460,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R03155</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R03155.main.2875ce0c137df622</t>
+          <t>R05213.main.bcab84a15ce93062</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -40467,20 +40475,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
+          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5745828</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>https://dspace.lib.ntua.gr/xmlui/bitstream/handle/123456789/44237/Msc.%20Thesis_Aristotle_Vasileiou%20THE.pdf?sequence=1&amp;isAllowed=y</t>
-        </is>
-      </c>
+        <v>1022660</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
+          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -40492,12 +40496,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R05213</t>
+          <t>R06036</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R05213.main.bcab84a15ce93062</t>
+          <t>R06036.main.0bdc7b19fdb70091</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -40507,16 +40511,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
+          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1022660</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
+        <v>927168</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
+          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -40528,12 +40536,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R06036</t>
+          <t>R09240</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R06036.main.0bdc7b19fdb70091</t>
+          <t>R09240.main.da8dbeb874b19b59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -40543,20 +40551,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
+          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>927168</v>
+        <v>1315227</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
+          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
+          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -40568,12 +40576,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R09240</t>
+          <t>R13899</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R09240.main.da8dbeb874b19b59</t>
+          <t>R13899.main.19143e56fa77ce99</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -40583,20 +40591,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
+          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1315227</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
-        </is>
-      </c>
+        <v>479092</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
+          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -40608,12 +40612,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R13899</t>
+          <t>R13955</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R13899.main.19143e56fa77ce99</t>
+          <t>R13955.main.6714f79deccd703d</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -40623,59 +40627,23 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
+          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>479092</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
+        <v>14662119</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>R13955</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>R13955.main.6714f79deccd703d</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>14662119</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
         <is>
           <t>历史已获取，当前原件未恢复</t>
         </is>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -7455,7 +7455,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.138303+00:00</t>
+          <t>2026-10-17T09:05:46.979782+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.139160+00:00</t>
+          <t>2026-10-17T09:05:46.980712+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.139178+00:00</t>
+          <t>2026-10-17T09:05:46.980733+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.139416+00:00</t>
+          <t>2026-10-17T09:05:46.980955+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.140506+00:00</t>
+          <t>2026-10-17T09:05:46.982168+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.140974+00:00</t>
+          <t>2026-10-17T09:05:46.982659+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.146217+00:00</t>
+          <t>2026-10-17T09:05:46.987898+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.148521+00:00</t>
+          <t>2026-10-17T09:05:46.990340+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.149661+00:00</t>
+          <t>2026-10-17T09:05:46.991266+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.150022+00:00</t>
+          <t>2026-10-17T09:05:46.991604+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.150740+00:00</t>
+          <t>2026-10-17T09:05:46.992675+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.151400+00:00</t>
+          <t>2026-10-17T09:05:46.993350+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.152463+00:00</t>
+          <t>2026-10-17T09:05:46.994254+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.152724+00:00</t>
+          <t>2026-10-17T09:05:46.994524+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.153614+00:00</t>
+          <t>2026-10-17T09:05:46.995396+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.162220+00:00</t>
+          <t>2026-10-17T09:05:47.002594+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.163044+00:00</t>
+          <t>2026-10-17T09:05:47.003264+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.164343+00:00</t>
+          <t>2026-10-17T09:05:47.005651+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.166919+00:00</t>
+          <t>2026-10-17T09:05:47.008349+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.168114+00:00</t>
+          <t>2026-10-17T09:05:47.009455+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.169498+00:00</t>
+          <t>2026-10-17T09:05:47.010863+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.173980+00:00</t>
+          <t>2026-10-17T09:05:47.016057+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.176337+00:00</t>
+          <t>2026-10-17T09:05:47.018587+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.178413+00:00</t>
+          <t>2026-10-17T09:05:47.020401+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.179373+00:00</t>
+          <t>2026-10-17T09:05:47.021089+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.179764+00:00</t>
+          <t>2026-10-17T09:05:47.021466+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.181880+00:00</t>
+          <t>2026-10-17T09:05:47.023489+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.183179+00:00</t>
+          <t>2026-10-17T09:05:47.024805+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.185461+00:00</t>
+          <t>2026-10-17T09:05:47.026856+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.187564+00:00</t>
+          <t>2026-10-17T09:05:47.028803+00:00</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.188202+00:00</t>
+          <t>2026-10-17T09:05:47.029346+00:00</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.188866+00:00</t>
+          <t>2026-10-17T09:05:47.029913+00:00</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.190607+00:00</t>
+          <t>2026-10-17T09:05:47.031547+00:00</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.193399+00:00</t>
+          <t>2026-10-17T09:05:47.034478+00:00</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.195501+00:00</t>
+          <t>2026-10-17T09:05:47.036625+00:00</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.196677+00:00</t>
+          <t>2026-10-17T09:05:47.037941+00:00</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.199628+00:00</t>
+          <t>2026-10-17T09:05:47.040938+00:00</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.200443+00:00</t>
+          <t>2026-10-17T09:05:47.041785+00:00</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.202034+00:00</t>
+          <t>2026-10-17T09:05:47.043504+00:00</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.202281+00:00</t>
+          <t>2026-10-17T09:05:47.043761+00:00</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.204160+00:00</t>
+          <t>2026-10-17T09:05:47.045856+00:00</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.207112+00:00</t>
+          <t>2026-10-17T09:05:47.048755+00:00</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.208623+00:00</t>
+          <t>2026-10-17T09:05:47.050255+00:00</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.209262+00:00</t>
+          <t>2026-10-17T09:05:47.050889+00:00</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.211966+00:00</t>
+          <t>2026-10-17T09:05:47.053499+00:00</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.213076+00:00</t>
+          <t>2026-10-17T09:05:47.054714+00:00</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.216448+00:00</t>
+          <t>2026-10-17T09:05:47.058170+00:00</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.218077+00:00</t>
+          <t>2026-10-17T09:05:47.059935+00:00</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.219884+00:00</t>
+          <t>2026-10-17T09:05:47.062007+00:00</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.220820+00:00</t>
+          <t>2026-10-17T09:05:47.062974+00:00</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.221253+00:00</t>
+          <t>2026-10-17T09:05:47.063431+00:00</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.221647+00:00</t>
+          <t>2026-10-17T09:05:47.063807+00:00</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.223104+00:00</t>
+          <t>2026-10-17T09:05:47.065305+00:00</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.224454+00:00</t>
+          <t>2026-10-17T09:05:47.066656+00:00</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.226017+00:00</t>
+          <t>2026-10-17T09:05:47.068159+00:00</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.226372+00:00</t>
+          <t>2026-10-17T09:05:47.068504+00:00</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.227567+00:00</t>
+          <t>2026-10-17T09:05:47.069785+00:00</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.228920+00:00</t>
+          <t>2026-10-17T09:05:47.071140+00:00</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.229528+00:00</t>
+          <t>2026-10-17T09:05:47.071727+00:00</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.230460+00:00</t>
+          <t>2026-10-17T09:05:47.072671+00:00</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.230788+00:00</t>
+          <t>2026-10-17T09:05:47.072979+00:00</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.237787+00:00</t>
+          <t>2026-10-17T09:05:47.078397+00:00</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.238262+00:00</t>
+          <t>2026-10-17T09:05:47.078831+00:00</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.238857+00:00</t>
+          <t>2026-10-17T09:05:47.079399+00:00</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.239313+00:00</t>
+          <t>2026-10-17T09:05:47.079848+00:00</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.240420+00:00</t>
+          <t>2026-10-17T09:05:47.080981+00:00</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.243507+00:00</t>
+          <t>2026-10-17T09:05:47.083978+00:00</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.243756+00:00</t>
+          <t>2026-10-17T09:05:47.084231+00:00</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.248046+00:00</t>
+          <t>2026-10-17T09:05:47.088547+00:00</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.248797+00:00</t>
+          <t>2026-10-17T09:05:47.089410+00:00</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.251190+00:00</t>
+          <t>2026-10-17T09:05:47.091821+00:00</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.253136+00:00</t>
+          <t>2026-10-17T09:05:47.093602+00:00</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.254113+00:00</t>
+          <t>2026-10-17T09:05:47.094502+00:00</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.255796+00:00</t>
+          <t>2026-10-17T09:05:47.096115+00:00</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.258026+00:00</t>
+          <t>2026-10-17T09:05:47.098550+00:00</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.266015+00:00</t>
+          <t>2026-10-17T09:05:47.106871+00:00</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.267361+00:00</t>
+          <t>2026-10-17T09:05:47.108432+00:00</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.267514+00:00</t>
+          <t>2026-10-17T09:05:47.108610+00:00</t>
         </is>
       </c>
     </row>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.267527+00:00</t>
+          <t>2026-10-17T09:05:47.108626+00:00</t>
         </is>
       </c>
     </row>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.272793+00:00</t>
+          <t>2026-10-17T09:05:47.114579+00:00</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.273207+00:00</t>
+          <t>2026-10-17T09:05:47.114984+00:00</t>
         </is>
       </c>
     </row>
@@ -33071,7 +33071,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.273603+00:00</t>
+          <t>2026-10-17T09:05:47.115399+00:00</t>
         </is>
       </c>
     </row>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.274002+00:00</t>
+          <t>2026-10-17T09:05:47.115862+00:00</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.274740+00:00</t>
+          <t>2026-10-17T09:05:47.116645+00:00</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33383,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.276449+00:00</t>
+          <t>2026-10-17T09:05:47.118146+00:00</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.277497+00:00</t>
+          <t>2026-10-17T09:05:47.119005+00:00</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.277908+00:00</t>
+          <t>2026-10-17T09:05:47.119353+00:00</t>
         </is>
       </c>
     </row>
@@ -33699,7 +33699,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.278579+00:00</t>
+          <t>2026-10-17T09:05:47.119988+00:00</t>
         </is>
       </c>
     </row>
@@ -33799,7 +33799,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.278595+00:00</t>
+          <t>2026-10-17T09:05:47.120002+00:00</t>
         </is>
       </c>
     </row>
@@ -33907,7 +33907,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.278645+00:00</t>
+          <t>2026-10-17T09:05:47.120053+00:00</t>
         </is>
       </c>
     </row>
@@ -34015,7 +34015,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.278863+00:00</t>
+          <t>2026-10-17T09:05:47.120276+00:00</t>
         </is>
       </c>
     </row>
@@ -34123,7 +34123,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.278984+00:00</t>
+          <t>2026-10-17T09:05:47.120439+00:00</t>
         </is>
       </c>
     </row>
@@ -34235,7 +34235,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.279100+00:00</t>
+          <t>2026-10-17T09:05:47.120559+00:00</t>
         </is>
       </c>
     </row>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.279556+00:00</t>
+          <t>2026-10-17T09:05:47.120930+00:00</t>
         </is>
       </c>
     </row>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.279760+00:00</t>
+          <t>2026-10-17T09:05:47.121122+00:00</t>
         </is>
       </c>
     </row>
@@ -34563,7 +34563,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.279815+00:00</t>
+          <t>2026-10-17T09:05:47.121176+00:00</t>
         </is>
       </c>
     </row>
@@ -34675,7 +34675,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.279893+00:00</t>
+          <t>2026-10-17T09:05:47.121239+00:00</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.280042+00:00</t>
+          <t>2026-10-17T09:05:47.121441+00:00</t>
         </is>
       </c>
     </row>
@@ -34899,7 +34899,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.280087+00:00</t>
+          <t>2026-10-17T09:05:47.121513+00:00</t>
         </is>
       </c>
     </row>
@@ -35007,7 +35007,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.280564+00:00</t>
+          <t>2026-10-17T09:05:47.121990+00:00</t>
         </is>
       </c>
     </row>
@@ -35115,7 +35115,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.280623+00:00</t>
+          <t>2026-10-17T09:05:47.122041+00:00</t>
         </is>
       </c>
     </row>
@@ -35215,7 +35215,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.280633+00:00</t>
+          <t>2026-10-17T09:05:47.122051+00:00</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.290317+00:00</t>
+          <t>2026-10-17T09:05:47.131357+00:00</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.290392+00:00</t>
+          <t>2026-10-17T09:05:47.131405+00:00</t>
         </is>
       </c>
     </row>
@@ -35535,7 +35535,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.290513+00:00</t>
+          <t>2026-10-17T09:05:47.131498+00:00</t>
         </is>
       </c>
     </row>
@@ -35643,7 +35643,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.290749+00:00</t>
+          <t>2026-10-17T09:05:47.131850+00:00</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.291795+00:00</t>
+          <t>2026-10-17T09:05:47.132949+00:00</t>
         </is>
       </c>
     </row>
@@ -35853,7 +35853,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.291880+00:00</t>
+          <t>2026-10-17T09:05:47.133050+00:00</t>
         </is>
       </c>
     </row>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.291891+00:00</t>
+          <t>2026-10-17T09:05:47.133061+00:00</t>
         </is>
       </c>
     </row>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.291974+00:00</t>
+          <t>2026-10-17T09:05:47.133145+00:00</t>
         </is>
       </c>
     </row>
@@ -36151,7 +36151,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.292056+00:00</t>
+          <t>2026-10-17T09:05:47.133229+00:00</t>
         </is>
       </c>
     </row>
@@ -36253,7 +36253,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.292162+00:00</t>
+          <t>2026-10-17T09:05:47.133391+00:00</t>
         </is>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.292172+00:00</t>
+          <t>2026-10-17T09:05:47.133406+00:00</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.292341+00:00</t>
+          <t>2026-10-17T09:05:47.133587+00:00</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.292353+00:00</t>
+          <t>2026-10-17T09:05:47.133601+00:00</t>
         </is>
       </c>
     </row>
@@ -36645,7 +36645,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.292455+00:00</t>
+          <t>2026-10-17T09:05:47.133704+00:00</t>
         </is>
       </c>
     </row>
@@ -36739,7 +36739,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.292466+00:00</t>
+          <t>2026-10-17T09:05:47.133715+00:00</t>
         </is>
       </c>
     </row>
@@ -36841,7 +36841,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.292609+00:00</t>
+          <t>2026-10-17T09:05:47.133855+00:00</t>
         </is>
       </c>
     </row>
@@ -36935,7 +36935,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.292621+00:00</t>
+          <t>2026-10-17T09:05:47.133866+00:00</t>
         </is>
       </c>
     </row>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.292714+00:00</t>
+          <t>2026-10-17T09:05:47.133957+00:00</t>
         </is>
       </c>
     </row>
@@ -37139,7 +37139,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.292852+00:00</t>
+          <t>2026-10-17T09:05:47.134145+00:00</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.292863+00:00</t>
+          <t>2026-10-17T09:05:47.134165+00:00</t>
         </is>
       </c>
     </row>
@@ -37335,7 +37335,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.292985+00:00</t>
+          <t>2026-10-17T09:05:47.134337+00:00</t>
         </is>
       </c>
     </row>
@@ -37429,7 +37429,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.292996+00:00</t>
+          <t>2026-10-17T09:05:47.134350+00:00</t>
         </is>
       </c>
     </row>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.293105+00:00</t>
+          <t>2026-10-17T09:05:47.134458+00:00</t>
         </is>
       </c>
     </row>
@@ -37633,7 +37633,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.293345+00:00</t>
+          <t>2026-10-17T09:05:47.134677+00:00</t>
         </is>
       </c>
     </row>
@@ -37727,7 +37727,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.293358+00:00</t>
+          <t>2026-10-17T09:05:47.134690+00:00</t>
         </is>
       </c>
     </row>
@@ -37829,7 +37829,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.293573+00:00</t>
+          <t>2026-10-17T09:05:47.134850+00:00</t>
         </is>
       </c>
     </row>
@@ -37931,7 +37931,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.293777+00:00</t>
+          <t>2026-10-17T09:05:47.135047+00:00</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38033,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.293970+00:00</t>
+          <t>2026-10-17T09:05:47.135238+00:00</t>
         </is>
       </c>
     </row>
@@ -38127,7 +38127,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.293982+00:00</t>
+          <t>2026-10-17T09:05:47.135249+00:00</t>
         </is>
       </c>
     </row>
@@ -38229,7 +38229,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.294092+00:00</t>
+          <t>2026-10-17T09:05:47.135410+00:00</t>
         </is>
       </c>
     </row>
@@ -38323,7 +38323,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.294103+00:00</t>
+          <t>2026-10-17T09:05:47.135428+00:00</t>
         </is>
       </c>
     </row>
@@ -38425,7 +38425,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.294191+00:00</t>
+          <t>2026-10-17T09:05:47.135524+00:00</t>
         </is>
       </c>
     </row>
@@ -38533,7 +38533,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.295257+00:00</t>
+          <t>2026-10-17T09:05:47.136743+00:00</t>
         </is>
       </c>
     </row>
@@ -38625,7 +38625,7 @@
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.305378+00:00</t>
+          <t>2026-10-17T09:05:47.146164+00:00</t>
         </is>
       </c>
     </row>
@@ -38725,7 +38725,7 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.306047+00:00</t>
+          <t>2026-10-17T09:05:47.146638+00:00</t>
         </is>
       </c>
     </row>
@@ -38813,7 +38813,7 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.306074+00:00</t>
+          <t>2026-10-17T09:05:47.146655+00:00</t>
         </is>
       </c>
     </row>
@@ -38880,7 +38880,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -38913,7 +38913,7 @@
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.307247+00:00</t>
+          <t>2026-10-17T09:05:47.147890+00:00</t>
         </is>
       </c>
     </row>
@@ -38945,13 +38945,21 @@
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
+        </is>
+      </c>
       <c r="I141" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-fulltexts/R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr"/>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
+        </is>
+      </c>
       <c r="K141" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -38967,17 +38975,17 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1186/s40643-024-00756-6.pdf</t>
+          <t>https://europepmc.org/api/getPdf?pmcid=PMC11076452</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr"/>
@@ -39005,7 +39013,7 @@
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.307264+00:00</t>
+          <t>2026-10-17T09:05:47.151370+00:00</t>
         </is>
       </c>
     </row>
@@ -39097,7 +39105,7 @@
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.307268+00:00</t>
+          <t>2026-10-17T09:05:47.151401+00:00</t>
         </is>
       </c>
     </row>
@@ -39189,7 +39197,7 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.307272+00:00</t>
+          <t>2026-10-17T09:05:47.151406+00:00</t>
         </is>
       </c>
     </row>
@@ -39277,7 +39285,7 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.307275+00:00</t>
+          <t>2026-10-17T09:05:47.151409+00:00</t>
         </is>
       </c>
     </row>
@@ -39369,7 +39377,7 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.307278+00:00</t>
+          <t>2026-10-17T09:05:47.151412+00:00</t>
         </is>
       </c>
     </row>
@@ -39461,7 +39469,7 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.307282+00:00</t>
+          <t>2026-10-17T09:05:47.151415+00:00</t>
         </is>
       </c>
     </row>
@@ -39549,7 +39557,7 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.307285+00:00</t>
+          <t>2026-10-17T09:05:47.151419+00:00</t>
         </is>
       </c>
     </row>
@@ -39641,7 +39649,7 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:12.307318+00:00</t>
+          <t>2026-10-17T09:05:47.151423+00:00</t>
         </is>
       </c>
     </row>
@@ -39656,7 +39664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40340,12 +40348,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R09804</t>
+          <t>R11844</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R09804.main.b3cc83d613ad3c36</t>
+          <t>R11844.main.c41816bf825167dc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -40355,20 +40363,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>b3cc83d613ad3c36f93b78eace000ebc5a603966523ee71c2e6a0bd85a8ede3e</t>
+          <t>c41816bf825167dcb78ff5eb81c8d0dab0d8d8110cd2a23a04cd1109acb34919</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5135812</v>
+        <v>1333380</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1186/s40643-024-00756-6.pdf</t>
+          <t>https://link.springer.com/content/pdf/10.1007/s00253-025-13519-w.pdf</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>R09804_2024_Anaerobic_digestion_of_process_water_from_hydrothermal_treatment_processes.pdf</t>
+          <t>R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -40380,12 +40388,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R03155</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R11844.main.c41816bf825167dc</t>
+          <t>R03155.main.2875ce0c137df622</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -40395,20 +40403,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>c41816bf825167dcb78ff5eb81c8d0dab0d8d8110cd2a23a04cd1109acb34919</t>
+          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1333380</v>
+        <v>5745828</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1007/s00253-025-13519-w.pdf</t>
+          <t>https://dspace.lib.ntua.gr/xmlui/bitstream/handle/123456789/44237/Msc.%20Thesis_Aristotle_Vasileiou%20THE.pdf?sequence=1&amp;isAllowed=y</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
+          <t>R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -40420,12 +40428,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R03155</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R03155.main.2875ce0c137df622</t>
+          <t>R05213.main.bcab84a15ce93062</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -40435,20 +40443,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
+          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5745828</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>https://dspace.lib.ntua.gr/xmlui/bitstream/handle/123456789/44237/Msc.%20Thesis_Aristotle_Vasileiou%20THE.pdf?sequence=1&amp;isAllowed=y</t>
-        </is>
-      </c>
+        <v>1022660</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
+          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -40460,12 +40464,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R05213</t>
+          <t>R06036</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R05213.main.bcab84a15ce93062</t>
+          <t>R06036.main.0bdc7b19fdb70091</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -40475,16 +40479,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
+          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1022660</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
+        <v>927168</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
+          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -40496,12 +40504,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R06036</t>
+          <t>R09240</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R06036.main.0bdc7b19fdb70091</t>
+          <t>R09240.main.da8dbeb874b19b59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -40511,20 +40519,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
+          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>927168</v>
+        <v>1315227</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
+          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
+          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -40536,12 +40544,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R09240</t>
+          <t>R13899</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R09240.main.da8dbeb874b19b59</t>
+          <t>R13899.main.19143e56fa77ce99</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -40551,20 +40559,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
+          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1315227</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
-        </is>
-      </c>
+        <v>479092</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
+          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -40576,12 +40580,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R13899</t>
+          <t>R13955</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R13899.main.19143e56fa77ce99</t>
+          <t>R13955.main.6714f79deccd703d</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -40591,59 +40595,23 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
+          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>479092</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
+        <v>14662119</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>R13955</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>R13955.main.6714f79deccd703d</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>14662119</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
         <is>
           <t>历史已获取，当前原件未恢复</t>
         </is>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -7842,7 +7842,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:46.979782+00:00</t>
+          <t>2026-10-17T09:06:13.729392+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:46.980712+00:00</t>
+          <t>2026-10-17T09:06:13.730373+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:46.980733+00:00</t>
+          <t>2026-10-17T09:06:13.730397+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:46.980955+00:00</t>
+          <t>2026-10-17T09:06:13.730623+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:46.982168+00:00</t>
+          <t>2026-10-17T09:06:13.731724+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:46.982659+00:00</t>
+          <t>2026-10-17T09:06:13.732200+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:46.987898+00:00</t>
+          <t>2026-10-17T09:06:13.738129+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:46.990340+00:00</t>
+          <t>2026-10-17T09:06:13.740927+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:46.991266+00:00</t>
+          <t>2026-10-17T09:06:13.742074+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:46.991604+00:00</t>
+          <t>2026-10-17T09:06:13.742472+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:46.992675+00:00</t>
+          <t>2026-10-17T09:06:13.743267+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:46.993350+00:00</t>
+          <t>2026-10-17T09:06:13.744044+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:46.994254+00:00</t>
+          <t>2026-10-17T09:06:13.745077+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:46.994524+00:00</t>
+          <t>2026-10-17T09:06:13.745353+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:46.995396+00:00</t>
+          <t>2026-10-17T09:06:13.746226+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.002594+00:00</t>
+          <t>2026-10-17T09:06:13.754943+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.003264+00:00</t>
+          <t>2026-10-17T09:06:13.755964+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.005651+00:00</t>
+          <t>2026-10-17T09:06:13.757328+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.008349+00:00</t>
+          <t>2026-10-17T09:06:13.760571+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.009455+00:00</t>
+          <t>2026-10-17T09:06:13.761915+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.010863+00:00</t>
+          <t>2026-10-17T09:06:13.763180+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.016057+00:00</t>
+          <t>2026-10-17T09:06:13.767962+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.018587+00:00</t>
+          <t>2026-10-17T09:06:13.770474+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.020401+00:00</t>
+          <t>2026-10-17T09:06:13.772436+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.021089+00:00</t>
+          <t>2026-10-17T09:06:13.773158+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.021466+00:00</t>
+          <t>2026-10-17T09:06:13.773591+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.023489+00:00</t>
+          <t>2026-10-17T09:06:13.775777+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.024805+00:00</t>
+          <t>2026-10-17T09:06:13.777401+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.026856+00:00</t>
+          <t>2026-10-17T09:06:13.779624+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.028803+00:00</t>
+          <t>2026-10-17T09:06:13.781716+00:00</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.029346+00:00</t>
+          <t>2026-10-17T09:06:13.782533+00:00</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.029913+00:00</t>
+          <t>2026-10-17T09:06:13.783183+00:00</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.031547+00:00</t>
+          <t>2026-10-17T09:06:13.784889+00:00</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.034478+00:00</t>
+          <t>2026-10-17T09:06:13.788329+00:00</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.036625+00:00</t>
+          <t>2026-10-17T09:06:13.790461+00:00</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.037941+00:00</t>
+          <t>2026-10-17T09:06:13.791959+00:00</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.040938+00:00</t>
+          <t>2026-10-17T09:06:13.795022+00:00</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.041785+00:00</t>
+          <t>2026-10-17T09:06:13.796122+00:00</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.043504+00:00</t>
+          <t>2026-10-17T09:06:13.797870+00:00</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.043761+00:00</t>
+          <t>2026-10-17T09:06:13.798131+00:00</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.045856+00:00</t>
+          <t>2026-10-17T09:06:13.800383+00:00</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.048755+00:00</t>
+          <t>2026-10-17T09:06:13.803392+00:00</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.050255+00:00</t>
+          <t>2026-10-17T09:06:13.804949+00:00</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.050889+00:00</t>
+          <t>2026-10-17T09:06:13.805685+00:00</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.053499+00:00</t>
+          <t>2026-10-17T09:06:13.808383+00:00</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.054714+00:00</t>
+          <t>2026-10-17T09:06:13.809775+00:00</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.058170+00:00</t>
+          <t>2026-10-17T09:06:13.813512+00:00</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.059935+00:00</t>
+          <t>2026-10-17T09:06:13.815451+00:00</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.062007+00:00</t>
+          <t>2026-10-17T09:06:13.817564+00:00</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.062974+00:00</t>
+          <t>2026-10-17T09:06:13.818581+00:00</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.063431+00:00</t>
+          <t>2026-10-17T09:06:13.819048+00:00</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.063807+00:00</t>
+          <t>2026-10-17T09:06:13.819432+00:00</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.065305+00:00</t>
+          <t>2026-10-17T09:06:13.821281+00:00</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.066656+00:00</t>
+          <t>2026-10-17T09:06:13.822853+00:00</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.068159+00:00</t>
+          <t>2026-10-17T09:06:13.824491+00:00</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.068504+00:00</t>
+          <t>2026-10-17T09:06:13.824839+00:00</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.069785+00:00</t>
+          <t>2026-10-17T09:06:13.826211+00:00</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.071140+00:00</t>
+          <t>2026-10-17T09:06:13.827712+00:00</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.071727+00:00</t>
+          <t>2026-10-17T09:06:13.828325+00:00</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.072671+00:00</t>
+          <t>2026-10-17T09:06:13.829258+00:00</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.072979+00:00</t>
+          <t>2026-10-17T09:06:13.829634+00:00</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.078397+00:00</t>
+          <t>2026-10-17T09:06:13.835324+00:00</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.078831+00:00</t>
+          <t>2026-10-17T09:06:13.835900+00:00</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.079399+00:00</t>
+          <t>2026-10-17T09:06:13.836618+00:00</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.079848+00:00</t>
+          <t>2026-10-17T09:06:13.837065+00:00</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.080981+00:00</t>
+          <t>2026-10-17T09:06:13.840455+00:00</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.083978+00:00</t>
+          <t>2026-10-17T09:06:13.845599+00:00</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.084231+00:00</t>
+          <t>2026-10-17T09:06:13.845910+00:00</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.088547+00:00</t>
+          <t>2026-10-17T09:06:13.851230+00:00</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.089410+00:00</t>
+          <t>2026-10-17T09:06:13.852135+00:00</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.091821+00:00</t>
+          <t>2026-10-17T09:06:13.854319+00:00</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.093602+00:00</t>
+          <t>2026-10-17T09:06:13.856080+00:00</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.094502+00:00</t>
+          <t>2026-10-17T09:06:13.856974+00:00</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.096115+00:00</t>
+          <t>2026-10-17T09:06:13.858512+00:00</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.098550+00:00</t>
+          <t>2026-10-17T09:06:13.861459+00:00</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.106871+00:00</t>
+          <t>2026-10-17T09:06:13.869909+00:00</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.108432+00:00</t>
+          <t>2026-10-17T09:06:13.871540+00:00</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.108610+00:00</t>
+          <t>2026-10-17T09:06:13.871721+00:00</t>
         </is>
       </c>
     </row>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.108626+00:00</t>
+          <t>2026-10-17T09:06:13.871737+00:00</t>
         </is>
       </c>
     </row>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.114579+00:00</t>
+          <t>2026-10-17T09:06:13.877140+00:00</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.114984+00:00</t>
+          <t>2026-10-17T09:06:13.877640+00:00</t>
         </is>
       </c>
     </row>
@@ -33071,7 +33071,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.115399+00:00</t>
+          <t>2026-10-17T09:06:13.878088+00:00</t>
         </is>
       </c>
     </row>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.115862+00:00</t>
+          <t>2026-10-17T09:06:13.878868+00:00</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.116645+00:00</t>
+          <t>2026-10-17T09:06:13.879994+00:00</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33383,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.118146+00:00</t>
+          <t>2026-10-17T09:06:13.881857+00:00</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.119005+00:00</t>
+          <t>2026-10-17T09:06:13.882772+00:00</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.119353+00:00</t>
+          <t>2026-10-17T09:06:13.883356+00:00</t>
         </is>
       </c>
     </row>
@@ -33699,7 +33699,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.119988+00:00</t>
+          <t>2026-10-17T09:06:13.884011+00:00</t>
         </is>
       </c>
     </row>
@@ -33799,7 +33799,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.120002+00:00</t>
+          <t>2026-10-17T09:06:13.884027+00:00</t>
         </is>
       </c>
     </row>
@@ -33907,7 +33907,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.120053+00:00</t>
+          <t>2026-10-17T09:06:13.884083+00:00</t>
         </is>
       </c>
     </row>
@@ -34015,7 +34015,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.120276+00:00</t>
+          <t>2026-10-17T09:06:13.884320+00:00</t>
         </is>
       </c>
     </row>
@@ -34123,7 +34123,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.120439+00:00</t>
+          <t>2026-10-17T09:06:13.884440+00:00</t>
         </is>
       </c>
     </row>
@@ -34235,7 +34235,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.120559+00:00</t>
+          <t>2026-10-17T09:06:13.884555+00:00</t>
         </is>
       </c>
     </row>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.120930+00:00</t>
+          <t>2026-10-17T09:06:13.884940+00:00</t>
         </is>
       </c>
     </row>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.121122+00:00</t>
+          <t>2026-10-17T09:06:13.885223+00:00</t>
         </is>
       </c>
     </row>
@@ -34563,7 +34563,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.121176+00:00</t>
+          <t>2026-10-17T09:06:13.885309+00:00</t>
         </is>
       </c>
     </row>
@@ -34675,7 +34675,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.121239+00:00</t>
+          <t>2026-10-17T09:06:13.885387+00:00</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.121441+00:00</t>
+          <t>2026-10-17T09:06:13.885559+00:00</t>
         </is>
       </c>
     </row>
@@ -34899,7 +34899,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.121513+00:00</t>
+          <t>2026-10-17T09:06:13.885608+00:00</t>
         </is>
       </c>
     </row>
@@ -35007,7 +35007,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.121990+00:00</t>
+          <t>2026-10-17T09:06:13.886183+00:00</t>
         </is>
       </c>
     </row>
@@ -35115,7 +35115,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.122041+00:00</t>
+          <t>2026-10-17T09:06:13.886255+00:00</t>
         </is>
       </c>
     </row>
@@ -35215,7 +35215,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.122051+00:00</t>
+          <t>2026-10-17T09:06:13.886267+00:00</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.131357+00:00</t>
+          <t>2026-10-17T09:06:13.896632+00:00</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.131405+00:00</t>
+          <t>2026-10-17T09:06:13.896725+00:00</t>
         </is>
       </c>
     </row>
@@ -35535,7 +35535,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.131498+00:00</t>
+          <t>2026-10-17T09:06:13.896856+00:00</t>
         </is>
       </c>
     </row>
@@ -35643,7 +35643,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.131850+00:00</t>
+          <t>2026-10-17T09:06:13.897099+00:00</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.132949+00:00</t>
+          <t>2026-10-17T09:06:13.898332+00:00</t>
         </is>
       </c>
     </row>
@@ -35853,7 +35853,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.133050+00:00</t>
+          <t>2026-10-17T09:06:13.898457+00:00</t>
         </is>
       </c>
     </row>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.133061+00:00</t>
+          <t>2026-10-17T09:06:13.898472+00:00</t>
         </is>
       </c>
     </row>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.133145+00:00</t>
+          <t>2026-10-17T09:06:13.898574+00:00</t>
         </is>
       </c>
     </row>
@@ -36151,7 +36151,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.133229+00:00</t>
+          <t>2026-10-17T09:06:13.898704+00:00</t>
         </is>
       </c>
     </row>
@@ -36253,7 +36253,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.133391+00:00</t>
+          <t>2026-10-17T09:06:13.898818+00:00</t>
         </is>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.133406+00:00</t>
+          <t>2026-10-17T09:06:13.898830+00:00</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.133587+00:00</t>
+          <t>2026-10-17T09:06:13.898988+00:00</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.133601+00:00</t>
+          <t>2026-10-17T09:06:13.898999+00:00</t>
         </is>
       </c>
     </row>
@@ -36645,7 +36645,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.133704+00:00</t>
+          <t>2026-10-17T09:06:13.899101+00:00</t>
         </is>
       </c>
     </row>
@@ -36739,7 +36739,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.133715+00:00</t>
+          <t>2026-10-17T09:06:13.899113+00:00</t>
         </is>
       </c>
     </row>
@@ -36841,7 +36841,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.133855+00:00</t>
+          <t>2026-10-17T09:06:13.899300+00:00</t>
         </is>
       </c>
     </row>
@@ -36935,7 +36935,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.133866+00:00</t>
+          <t>2026-10-17T09:06:13.899324+00:00</t>
         </is>
       </c>
     </row>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.133957+00:00</t>
+          <t>2026-10-17T09:06:13.899430+00:00</t>
         </is>
       </c>
     </row>
@@ -37139,7 +37139,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.134145+00:00</t>
+          <t>2026-10-17T09:06:13.899817+00:00</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.134165+00:00</t>
+          <t>2026-10-17T09:06:13.899834+00:00</t>
         </is>
       </c>
     </row>
@@ -37335,7 +37335,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.134337+00:00</t>
+          <t>2026-10-17T09:06:13.899958+00:00</t>
         </is>
       </c>
     </row>
@@ -37429,7 +37429,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.134350+00:00</t>
+          <t>2026-10-17T09:06:13.899970+00:00</t>
         </is>
       </c>
     </row>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.134458+00:00</t>
+          <t>2026-10-17T09:06:13.900074+00:00</t>
         </is>
       </c>
     </row>
@@ -37633,7 +37633,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.134677+00:00</t>
+          <t>2026-10-17T09:06:13.900324+00:00</t>
         </is>
       </c>
     </row>
@@ -37727,7 +37727,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.134690+00:00</t>
+          <t>2026-10-17T09:06:13.900340+00:00</t>
         </is>
       </c>
     </row>
@@ -37829,7 +37829,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.134850+00:00</t>
+          <t>2026-10-17T09:06:13.900509+00:00</t>
         </is>
       </c>
     </row>
@@ -37931,7 +37931,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.135047+00:00</t>
+          <t>2026-10-17T09:06:13.900962+00:00</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38033,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.135238+00:00</t>
+          <t>2026-10-17T09:06:13.901260+00:00</t>
         </is>
       </c>
     </row>
@@ -38127,7 +38127,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.135249+00:00</t>
+          <t>2026-10-17T09:06:13.901279+00:00</t>
         </is>
       </c>
     </row>
@@ -38229,7 +38229,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.135410+00:00</t>
+          <t>2026-10-17T09:06:13.901426+00:00</t>
         </is>
       </c>
     </row>
@@ -38323,7 +38323,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.135428+00:00</t>
+          <t>2026-10-17T09:06:13.901438+00:00</t>
         </is>
       </c>
     </row>
@@ -38425,7 +38425,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.135524+00:00</t>
+          <t>2026-10-17T09:06:13.901553+00:00</t>
         </is>
       </c>
     </row>
@@ -38533,7 +38533,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.136743+00:00</t>
+          <t>2026-10-17T09:06:13.902643+00:00</t>
         </is>
       </c>
     </row>
@@ -38625,7 +38625,7 @@
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.146164+00:00</t>
+          <t>2026-10-17T09:06:13.914016+00:00</t>
         </is>
       </c>
     </row>
@@ -38725,7 +38725,7 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.146638+00:00</t>
+          <t>2026-10-17T09:06:13.914866+00:00</t>
         </is>
       </c>
     </row>
@@ -38813,7 +38813,7 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.146655+00:00</t>
+          <t>2026-10-17T09:06:13.914888+00:00</t>
         </is>
       </c>
     </row>
@@ -38913,7 +38913,7 @@
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.147890+00:00</t>
+          <t>2026-10-17T09:06:13.916029+00:00</t>
         </is>
       </c>
     </row>
@@ -38980,7 +38980,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -39013,7 +39013,7 @@
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.151370+00:00</t>
+          <t>2026-10-17T09:06:13.919850+00:00</t>
         </is>
       </c>
     </row>
@@ -39045,13 +39045,21 @@
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
+        </is>
+      </c>
       <c r="I142" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-fulltexts/R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr"/>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
+        </is>
+      </c>
       <c r="K142" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -39067,17 +39075,17 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
+          <t>local_acquired_pending_remote_readback</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1007/s00253-025-13519-w.pdf</t>
+          <t>https://europepmc.org/api/getPdf?pmcid=PMC12125087</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr"/>
@@ -39105,7 +39113,7 @@
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.151401+00:00</t>
+          <t>2026-10-17T09:06:13.920889+00:00</t>
         </is>
       </c>
     </row>
@@ -39197,7 +39205,7 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.151406+00:00</t>
+          <t>2026-10-17T09:06:13.920912+00:00</t>
         </is>
       </c>
     </row>
@@ -39285,7 +39293,7 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.151409+00:00</t>
+          <t>2026-10-17T09:06:13.920918+00:00</t>
         </is>
       </c>
     </row>
@@ -39377,7 +39385,7 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.151412+00:00</t>
+          <t>2026-10-17T09:06:13.920922+00:00</t>
         </is>
       </c>
     </row>
@@ -39469,7 +39477,7 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.151415+00:00</t>
+          <t>2026-10-17T09:06:13.920925+00:00</t>
         </is>
       </c>
     </row>
@@ -39557,7 +39565,7 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.151419+00:00</t>
+          <t>2026-10-17T09:06:13.920929+00:00</t>
         </is>
       </c>
     </row>
@@ -39649,7 +39657,7 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-10-17T09:05:47.151423+00:00</t>
+          <t>2026-10-17T09:06:13.920932+00:00</t>
         </is>
       </c>
     </row>
@@ -39664,7 +39672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40348,12 +40356,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R11844</t>
+          <t>R03155</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R11844.main.c41816bf825167dc</t>
+          <t>R03155.main.2875ce0c137df622</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -40363,20 +40371,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>c41816bf825167dcb78ff5eb81c8d0dab0d8d8110cd2a23a04cd1109acb34919</t>
+          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1333380</v>
+        <v>5745828</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1007/s00253-025-13519-w.pdf</t>
+          <t>https://dspace.lib.ntua.gr/xmlui/bitstream/handle/123456789/44237/Msc.%20Thesis_Aristotle_Vasileiou%20THE.pdf?sequence=1&amp;isAllowed=y</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>R11844_2025_Micro-aeration_for_improving_anaerobic_treatment_and_biogas_production_from.pdf</t>
+          <t>R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -40388,12 +40396,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R03155</t>
+          <t>R05213</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R03155.main.2875ce0c137df622</t>
+          <t>R05213.main.bcab84a15ce93062</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -40403,20 +40411,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2875ce0c137df622bdafd5e5f4cf9be69518057654dadfcaa55a2b7c46e8625c</t>
+          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5745828</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>https://dspace.lib.ntua.gr/xmlui/bitstream/handle/123456789/44237/Msc.%20Thesis_Aristotle_Vasileiou%20THE.pdf?sequence=1&amp;isAllowed=y</t>
-        </is>
-      </c>
+        <v>1022660</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>R03155_2016_Effect_of_bioaugmentation_with_hydrolytic_bacteria_and_micro_aeration.pdf</t>
+          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -40428,12 +40432,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R05213</t>
+          <t>R06036</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R05213.main.bcab84a15ce93062</t>
+          <t>R06036.main.0bdc7b19fdb70091</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -40443,16 +40447,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
+          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1022660</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
+        <v>927168</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
+          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -40464,12 +40472,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R06036</t>
+          <t>R09240</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R06036.main.0bdc7b19fdb70091</t>
+          <t>R09240.main.da8dbeb874b19b59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -40479,20 +40487,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
+          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>927168</v>
+        <v>1315227</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
+          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
+          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -40504,12 +40512,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R09240</t>
+          <t>R13899</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R09240.main.da8dbeb874b19b59</t>
+          <t>R13899.main.19143e56fa77ce99</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -40519,20 +40527,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
+          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1315227</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
-        </is>
-      </c>
+        <v>479092</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
+          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -40544,12 +40548,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R13899</t>
+          <t>R13955</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R13899.main.19143e56fa77ce99</t>
+          <t>R13955.main.6714f79deccd703d</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -40559,59 +40563,23 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
+          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>479092</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
+        <v>14662119</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>R13955</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>R13955.main.6714f79deccd703d</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>14662119</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
         <is>
           <t>历史已获取，当前原件未恢复</t>
         </is>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -11499,7 +11499,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.729392+00:00</t>
+          <t>2026-10-17T09:09:29.397990+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.730373+00:00</t>
+          <t>2026-10-17T09:09:29.398928+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.730397+00:00</t>
+          <t>2026-10-17T09:09:29.398946+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.730623+00:00</t>
+          <t>2026-10-17T09:09:29.399165+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.731724+00:00</t>
+          <t>2026-10-17T09:09:29.400322+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.732200+00:00</t>
+          <t>2026-10-17T09:09:29.400788+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.738129+00:00</t>
+          <t>2026-10-17T09:09:29.405740+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.740927+00:00</t>
+          <t>2026-10-17T09:09:29.408011+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.742074+00:00</t>
+          <t>2026-10-17T09:09:29.408983+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.742472+00:00</t>
+          <t>2026-10-17T09:09:29.409344+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.743267+00:00</t>
+          <t>2026-10-17T09:09:29.410087+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.744044+00:00</t>
+          <t>2026-10-17T09:09:29.410793+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.745077+00:00</t>
+          <t>2026-10-17T09:09:29.411771+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.745353+00:00</t>
+          <t>2026-10-17T09:09:29.412008+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.746226+00:00</t>
+          <t>2026-10-17T09:09:29.412923+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.754943+00:00</t>
+          <t>2026-10-17T09:09:29.420701+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.755964+00:00</t>
+          <t>2026-10-17T09:09:29.421469+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.757328+00:00</t>
+          <t>2026-10-17T09:09:29.422725+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.760571+00:00</t>
+          <t>2026-10-17T09:09:29.425155+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.761915+00:00</t>
+          <t>2026-10-17T09:09:29.426397+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.763180+00:00</t>
+          <t>2026-10-17T09:09:29.427604+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.767962+00:00</t>
+          <t>2026-10-17T09:09:29.431773+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.770474+00:00</t>
+          <t>2026-10-17T09:09:29.434006+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.772436+00:00</t>
+          <t>2026-10-17T09:09:29.435857+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.773158+00:00</t>
+          <t>2026-10-17T09:09:29.436585+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.773591+00:00</t>
+          <t>2026-10-17T09:09:29.436962+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.775777+00:00</t>
+          <t>2026-10-17T09:09:29.439020+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.777401+00:00</t>
+          <t>2026-10-17T09:09:29.440276+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.779624+00:00</t>
+          <t>2026-10-17T09:09:29.442335+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.781716+00:00</t>
+          <t>2026-10-17T09:09:29.444563+00:00</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.782533+00:00</t>
+          <t>2026-10-17T09:09:29.445134+00:00</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.783183+00:00</t>
+          <t>2026-10-17T09:09:29.445745+00:00</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.784889+00:00</t>
+          <t>2026-10-17T09:09:29.447361+00:00</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.788329+00:00</t>
+          <t>2026-10-17T09:09:29.450499+00:00</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.790461+00:00</t>
+          <t>2026-10-17T09:09:29.452702+00:00</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.791959+00:00</t>
+          <t>2026-10-17T09:09:29.454237+00:00</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.795022+00:00</t>
+          <t>2026-10-17T09:09:29.457383+00:00</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.796122+00:00</t>
+          <t>2026-10-17T09:09:29.458212+00:00</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.797870+00:00</t>
+          <t>2026-10-17T09:09:29.459932+00:00</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.798131+00:00</t>
+          <t>2026-10-17T09:09:29.460193+00:00</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.800383+00:00</t>
+          <t>2026-10-17T09:09:29.462100+00:00</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.803392+00:00</t>
+          <t>2026-10-17T09:09:29.464912+00:00</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.804949+00:00</t>
+          <t>2026-10-17T09:09:29.466239+00:00</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.805685+00:00</t>
+          <t>2026-10-17T09:09:29.466805+00:00</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.808383+00:00</t>
+          <t>2026-10-17T09:09:29.469366+00:00</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.809775+00:00</t>
+          <t>2026-10-17T09:09:29.470556+00:00</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.813512+00:00</t>
+          <t>2026-10-17T09:09:29.474195+00:00</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.815451+00:00</t>
+          <t>2026-10-17T09:09:29.476001+00:00</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.817564+00:00</t>
+          <t>2026-10-17T09:09:29.478136+00:00</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.818581+00:00</t>
+          <t>2026-10-17T09:09:29.479178+00:00</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.819048+00:00</t>
+          <t>2026-10-17T09:09:29.479647+00:00</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.819432+00:00</t>
+          <t>2026-10-17T09:09:29.480032+00:00</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.821281+00:00</t>
+          <t>2026-10-17T09:09:29.481515+00:00</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.822853+00:00</t>
+          <t>2026-10-17T09:09:29.482780+00:00</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.824491+00:00</t>
+          <t>2026-10-17T09:09:29.484329+00:00</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.824839+00:00</t>
+          <t>2026-10-17T09:09:29.484676+00:00</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.826211+00:00</t>
+          <t>2026-10-17T09:09:29.486184+00:00</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.827712+00:00</t>
+          <t>2026-10-17T09:09:29.487589+00:00</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.828325+00:00</t>
+          <t>2026-10-17T09:09:29.488190+00:00</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.829258+00:00</t>
+          <t>2026-10-17T09:09:29.489160+00:00</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.829634+00:00</t>
+          <t>2026-10-17T09:09:29.489506+00:00</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.835324+00:00</t>
+          <t>2026-10-17T09:09:29.494459+00:00</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.835900+00:00</t>
+          <t>2026-10-17T09:09:29.494848+00:00</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.836618+00:00</t>
+          <t>2026-10-17T09:09:29.495477+00:00</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.837065+00:00</t>
+          <t>2026-10-17T09:09:29.495935+00:00</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.840455+00:00</t>
+          <t>2026-10-17T09:09:29.497029+00:00</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.845599+00:00</t>
+          <t>2026-10-17T09:09:29.500034+00:00</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.845910+00:00</t>
+          <t>2026-10-17T09:09:29.500313+00:00</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.851230+00:00</t>
+          <t>2026-10-17T09:09:29.504480+00:00</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.852135+00:00</t>
+          <t>2026-10-17T09:09:29.505361+00:00</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.854319+00:00</t>
+          <t>2026-10-17T09:09:29.507744+00:00</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.856080+00:00</t>
+          <t>2026-10-17T09:09:29.509557+00:00</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.856974+00:00</t>
+          <t>2026-10-17T09:09:29.510485+00:00</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.858512+00:00</t>
+          <t>2026-10-17T09:09:29.511881+00:00</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.861459+00:00</t>
+          <t>2026-10-17T09:09:29.514082+00:00</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.869909+00:00</t>
+          <t>2026-10-17T09:09:29.522272+00:00</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.871540+00:00</t>
+          <t>2026-10-17T09:09:29.523881+00:00</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.871721+00:00</t>
+          <t>2026-10-17T09:09:29.524056+00:00</t>
         </is>
       </c>
     </row>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.871737+00:00</t>
+          <t>2026-10-17T09:09:29.524069+00:00</t>
         </is>
       </c>
     </row>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.877140+00:00</t>
+          <t>2026-10-17T09:09:29.529202+00:00</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.877640+00:00</t>
+          <t>2026-10-17T09:09:29.529732+00:00</t>
         </is>
       </c>
     </row>
@@ -33071,7 +33071,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.878088+00:00</t>
+          <t>2026-10-17T09:09:29.530106+00:00</t>
         </is>
       </c>
     </row>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.878868+00:00</t>
+          <t>2026-10-17T09:09:29.530548+00:00</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.879994+00:00</t>
+          <t>2026-10-17T09:09:29.531514+00:00</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33383,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.881857+00:00</t>
+          <t>2026-10-17T09:09:29.532936+00:00</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.882772+00:00</t>
+          <t>2026-10-17T09:09:29.533848+00:00</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.883356+00:00</t>
+          <t>2026-10-17T09:09:29.534151+00:00</t>
         </is>
       </c>
     </row>
@@ -33699,7 +33699,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.884011+00:00</t>
+          <t>2026-10-17T09:09:29.534842+00:00</t>
         </is>
       </c>
     </row>
@@ -33799,7 +33799,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.884027+00:00</t>
+          <t>2026-10-17T09:09:29.534856+00:00</t>
         </is>
       </c>
     </row>
@@ -33907,7 +33907,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.884083+00:00</t>
+          <t>2026-10-17T09:09:29.534909+00:00</t>
         </is>
       </c>
     </row>
@@ -34015,7 +34015,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.884320+00:00</t>
+          <t>2026-10-17T09:09:29.535129+00:00</t>
         </is>
       </c>
     </row>
@@ -34123,7 +34123,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.884440+00:00</t>
+          <t>2026-10-17T09:09:29.535250+00:00</t>
         </is>
       </c>
     </row>
@@ -34235,7 +34235,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.884555+00:00</t>
+          <t>2026-10-17T09:09:29.535381+00:00</t>
         </is>
       </c>
     </row>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.884940+00:00</t>
+          <t>2026-10-17T09:09:29.535758+00:00</t>
         </is>
       </c>
     </row>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.885223+00:00</t>
+          <t>2026-10-17T09:09:29.535954+00:00</t>
         </is>
       </c>
     </row>
@@ -34563,7 +34563,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.885309+00:00</t>
+          <t>2026-10-17T09:09:29.536010+00:00</t>
         </is>
       </c>
     </row>
@@ -34675,7 +34675,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.885387+00:00</t>
+          <t>2026-10-17T09:09:29.536071+00:00</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.885559+00:00</t>
+          <t>2026-10-17T09:09:29.536211+00:00</t>
         </is>
       </c>
     </row>
@@ -34899,7 +34899,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.885608+00:00</t>
+          <t>2026-10-17T09:09:29.536255+00:00</t>
         </is>
       </c>
     </row>
@@ -35007,7 +35007,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.886183+00:00</t>
+          <t>2026-10-17T09:09:29.536742+00:00</t>
         </is>
       </c>
     </row>
@@ -35115,7 +35115,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.886255+00:00</t>
+          <t>2026-10-17T09:09:29.536803+00:00</t>
         </is>
       </c>
     </row>
@@ -35215,7 +35215,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.886267+00:00</t>
+          <t>2026-10-17T09:09:29.536814+00:00</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.896632+00:00</t>
+          <t>2026-10-17T09:09:29.546506+00:00</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.896725+00:00</t>
+          <t>2026-10-17T09:09:29.546569+00:00</t>
         </is>
       </c>
     </row>
@@ -35535,7 +35535,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.896856+00:00</t>
+          <t>2026-10-17T09:09:29.546672+00:00</t>
         </is>
       </c>
     </row>
@@ -35643,7 +35643,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.897099+00:00</t>
+          <t>2026-10-17T09:09:29.546907+00:00</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.898332+00:00</t>
+          <t>2026-10-17T09:09:29.547910+00:00</t>
         </is>
       </c>
     </row>
@@ -35853,7 +35853,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.898457+00:00</t>
+          <t>2026-10-17T09:09:29.548129+00:00</t>
         </is>
       </c>
     </row>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.898472+00:00</t>
+          <t>2026-10-17T09:09:29.548152+00:00</t>
         </is>
       </c>
     </row>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.898574+00:00</t>
+          <t>2026-10-17T09:09:29.548246+00:00</t>
         </is>
       </c>
     </row>
@@ -36151,7 +36151,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.898704+00:00</t>
+          <t>2026-10-17T09:09:29.548355+00:00</t>
         </is>
       </c>
     </row>
@@ -36253,7 +36253,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.898818+00:00</t>
+          <t>2026-10-17T09:09:29.548469+00:00</t>
         </is>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.898830+00:00</t>
+          <t>2026-10-17T09:09:29.548481+00:00</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.898988+00:00</t>
+          <t>2026-10-17T09:09:29.548637+00:00</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.898999+00:00</t>
+          <t>2026-10-17T09:09:29.548648+00:00</t>
         </is>
       </c>
     </row>
@@ -36645,7 +36645,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.899101+00:00</t>
+          <t>2026-10-17T09:09:29.548748+00:00</t>
         </is>
       </c>
     </row>
@@ -36739,7 +36739,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.899113+00:00</t>
+          <t>2026-10-17T09:09:29.548759+00:00</t>
         </is>
       </c>
     </row>
@@ -36841,7 +36841,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.899300+00:00</t>
+          <t>2026-10-17T09:09:29.548900+00:00</t>
         </is>
       </c>
     </row>
@@ -36935,7 +36935,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.899324+00:00</t>
+          <t>2026-10-17T09:09:29.548911+00:00</t>
         </is>
       </c>
     </row>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.899430+00:00</t>
+          <t>2026-10-17T09:09:29.549000+00:00</t>
         </is>
       </c>
     </row>
@@ -37139,7 +37139,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.899817+00:00</t>
+          <t>2026-10-17T09:09:29.549131+00:00</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.899834+00:00</t>
+          <t>2026-10-17T09:09:29.549143+00:00</t>
         </is>
       </c>
     </row>
@@ -37335,7 +37335,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.899958+00:00</t>
+          <t>2026-10-17T09:09:29.549262+00:00</t>
         </is>
       </c>
     </row>
@@ -37429,7 +37429,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.899970+00:00</t>
+          <t>2026-10-17T09:09:29.549273+00:00</t>
         </is>
       </c>
     </row>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.900074+00:00</t>
+          <t>2026-10-17T09:09:29.549393+00:00</t>
         </is>
       </c>
     </row>
@@ -37633,7 +37633,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.900324+00:00</t>
+          <t>2026-10-17T09:09:29.549645+00:00</t>
         </is>
       </c>
     </row>
@@ -37727,7 +37727,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.900340+00:00</t>
+          <t>2026-10-17T09:09:29.549661+00:00</t>
         </is>
       </c>
     </row>
@@ -37829,7 +37829,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.900509+00:00</t>
+          <t>2026-10-17T09:09:29.549970+00:00</t>
         </is>
       </c>
     </row>
@@ -37931,7 +37931,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.900962+00:00</t>
+          <t>2026-10-17T09:09:29.550184+00:00</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38033,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.901260+00:00</t>
+          <t>2026-10-17T09:09:29.550411+00:00</t>
         </is>
       </c>
     </row>
@@ -38127,7 +38127,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.901279+00:00</t>
+          <t>2026-10-17T09:09:29.550425+00:00</t>
         </is>
       </c>
     </row>
@@ -38229,7 +38229,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.901426+00:00</t>
+          <t>2026-10-17T09:09:29.550538+00:00</t>
         </is>
       </c>
     </row>
@@ -38323,7 +38323,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.901438+00:00</t>
+          <t>2026-10-17T09:09:29.550549+00:00</t>
         </is>
       </c>
     </row>
@@ -38425,7 +38425,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.901553+00:00</t>
+          <t>2026-10-17T09:09:29.550637+00:00</t>
         </is>
       </c>
     </row>
@@ -38533,7 +38533,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.902643+00:00</t>
+          <t>2026-10-17T09:09:29.551804+00:00</t>
         </is>
       </c>
     </row>
@@ -38625,7 +38625,7 @@
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.914016+00:00</t>
+          <t>2026-10-17T09:09:29.561397+00:00</t>
         </is>
       </c>
     </row>
@@ -38725,7 +38725,7 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.914866+00:00</t>
+          <t>2026-10-17T09:09:29.561907+00:00</t>
         </is>
       </c>
     </row>
@@ -38813,7 +38813,7 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.914888+00:00</t>
+          <t>2026-10-17T09:09:29.561923+00:00</t>
         </is>
       </c>
     </row>
@@ -38913,7 +38913,7 @@
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.916029+00:00</t>
+          <t>2026-10-17T09:09:29.563075+00:00</t>
         </is>
       </c>
     </row>
@@ -39013,7 +39013,7 @@
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.919850+00:00</t>
+          <t>2026-10-17T09:09:29.566559+00:00</t>
         </is>
       </c>
     </row>
@@ -39080,7 +39080,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -39113,7 +39113,7 @@
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.920889+00:00</t>
+          <t>2026-10-17T09:09:29.567542+00:00</t>
         </is>
       </c>
     </row>
@@ -39205,7 +39205,7 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.920912+00:00</t>
+          <t>2026-10-17T09:09:29.567560+00:00</t>
         </is>
       </c>
     </row>
@@ -39237,13 +39237,21 @@
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
+        </is>
+      </c>
       <c r="I144" t="inlineStr">
         <is>
           <t>/workspace/library-files/ad-oxygen-fulltexts/R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
         </is>
       </c>
-      <c r="J144" t="inlineStr"/>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
+        </is>
+      </c>
       <c r="K144" t="inlineStr">
         <is>
           <t>pdf</t>
@@ -39259,15 +39267,19 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>historical_acquired_current_original_not_restored</t>
+          <t>present_sha_verified</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>historical_only_original_missing</t>
-        </is>
-      </c>
-      <c r="P144" t="inlineStr"/>
+          <t>local_acquired_pending_remote_readback</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>https://europepmc.org/api/getPdf?pmcid=PMC6858683</t>
+        </is>
+      </c>
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr">
         <is>
@@ -39293,7 +39305,7 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.920918+00:00</t>
+          <t>2026-10-17T09:09:29.568262+00:00</t>
         </is>
       </c>
     </row>
@@ -39385,7 +39397,7 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.920922+00:00</t>
+          <t>2026-10-17T09:09:29.568276+00:00</t>
         </is>
       </c>
     </row>
@@ -39477,7 +39489,7 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.920925+00:00</t>
+          <t>2026-10-17T09:09:29.568280+00:00</t>
         </is>
       </c>
     </row>
@@ -39565,7 +39577,7 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.920929+00:00</t>
+          <t>2026-10-17T09:09:29.568284+00:00</t>
         </is>
       </c>
     </row>
@@ -39657,7 +39669,7 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-10-17T09:06:13.920932+00:00</t>
+          <t>2026-10-17T09:09:29.568302+00:00</t>
         </is>
       </c>
     </row>
@@ -39672,7 +39684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40396,12 +40408,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R05213</t>
+          <t>R06036</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R05213.main.bcab84a15ce93062</t>
+          <t>R06036.main.0bdc7b19fdb70091</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -40411,16 +40423,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>bcab84a15ce930626c5a8f88083f5a7bb857b403c5e0ba13af2f6aaed379f051</t>
+          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1022660</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
+        <v>927168</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>R05213_2019_The_use_of_lytic_polysaccharide_monooxygenases_in_anaerobic_digestion.pdf</t>
+          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -40432,12 +40448,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R06036</t>
+          <t>R09240</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R06036.main.0bdc7b19fdb70091</t>
+          <t>R09240.main.da8dbeb874b19b59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -40447,20 +40463,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0bdc7b19fdb700910361bf68b9c874d8a5c51772418f9d267f9163e360dc4b27</t>
+          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>927168</v>
+        <v>1315227</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://link.springer.com/content/pdf/10.1007/s42452-020-03247-3.pdf</t>
+          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>R06036_2020_Rapid_hydrogen_generation_from_cotton_wastes_by_mean_of.pdf</t>
+          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -40472,12 +40488,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R09240</t>
+          <t>R13899</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R09240.main.da8dbeb874b19b59</t>
+          <t>R13899.main.19143e56fa77ce99</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -40487,20 +40503,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>da8dbeb874b19b59dbea53c11766a209aaa0b0bc319e2128c94340ae78cecfaf</t>
+          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1315227</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>https://technology.matthey.com/docserver/fulltext/jmtr/67/4/Zimmerman_16a_Imp.pdf?expires=1791804248&amp;id=id&amp;accname=guest&amp;checksum=934385598F9DDA2349B917F1B50C4858</t>
-        </is>
-      </c>
+        <v>479092</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>R09240_2023_Microbubble_Intensification_of_Bioprocessing.pdf</t>
+          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -40512,12 +40524,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R13899</t>
+          <t>R13955</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R13899.main.19143e56fa77ce99</t>
+          <t>R13955.main.6714f79deccd703d</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -40527,59 +40539,23 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>19143e56fa77ce99639f652b53bde1b70f61a67b18f24b9686fc371215092714</t>
+          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>479092</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
+        <v>14662119</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>R13899_2013_Effect_of_aerobic_pretreatment_of_waste_on_the_rate.pdf</t>
+          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
-        <is>
-          <t>历史已获取，当前原件未恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>R13955</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>R13955.main.6714f79deccd703d</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>6714f79deccd703d9c74784b27ea4770f9095bfad44e0579a4f5de2990ae711f</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>14662119</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>R13955_2017_Biogas_Production_from_Lignocellulosic_Biomass_Impact_of_pre-treatment_co-digestion.pdf</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
         <is>
           <t>历史已获取，当前原件未恢复</t>
         </is>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H2" t="b">
@@ -541,7 +541,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H3" t="b">
@@ -584,7 +584,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H4" t="b">
@@ -627,7 +627,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H5" t="b">
@@ -670,7 +670,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>checked_no_file_links_found_coverage_unconfirmed</t>
         </is>
       </c>
       <c r="H6" t="b">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>not_downloaded</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>not_downloaded</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>not_downloaded</t>
+          <t>downloaded_verified</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -24118,7 +24118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X148"/>
+  <dimension ref="A1:X153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.397990+00:00</t>
+          <t>2026-10-17T09:22:30.796820+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.398928+00:00</t>
+          <t>2026-10-17T09:22:30.797808+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.398946+00:00</t>
+          <t>2026-10-17T09:22:30.797834+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.399165+00:00</t>
+          <t>2026-10-17T09:22:30.798075+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.400322+00:00</t>
+          <t>2026-10-17T09:22:30.799161+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.400788+00:00</t>
+          <t>2026-10-17T09:22:30.799657+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.405740+00:00</t>
+          <t>2026-10-17T09:22:30.806684+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.408011+00:00</t>
+          <t>2026-10-17T09:22:30.809068+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.408983+00:00</t>
+          <t>2026-10-17T09:22:30.810077+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.409344+00:00</t>
+          <t>2026-10-17T09:22:30.810447+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.410087+00:00</t>
+          <t>2026-10-17T09:22:30.811231+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.410793+00:00</t>
+          <t>2026-10-17T09:22:30.811895+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.411771+00:00</t>
+          <t>2026-10-17T09:22:30.813125+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.412008+00:00</t>
+          <t>2026-10-17T09:22:30.813546+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.412923+00:00</t>
+          <t>2026-10-17T09:22:30.815065+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.420701+00:00</t>
+          <t>2026-10-17T09:22:30.827603+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.421469+00:00</t>
+          <t>2026-10-17T09:22:30.828480+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.422725+00:00</t>
+          <t>2026-10-17T09:22:30.829715+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.425155+00:00</t>
+          <t>2026-10-17T09:22:30.832179+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.426397+00:00</t>
+          <t>2026-10-17T09:22:30.833261+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.427604+00:00</t>
+          <t>2026-10-17T09:22:30.836519+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.431773+00:00</t>
+          <t>2026-10-17T09:22:30.840897+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.434006+00:00</t>
+          <t>2026-10-17T09:22:30.843206+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.435857+00:00</t>
+          <t>2026-10-17T09:22:30.845025+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.436585+00:00</t>
+          <t>2026-10-17T09:22:30.845844+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.436962+00:00</t>
+          <t>2026-10-17T09:22:30.846404+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.439020+00:00</t>
+          <t>2026-10-17T09:22:30.849761+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.440276+00:00</t>
+          <t>2026-10-17T09:22:30.851231+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.442335+00:00</t>
+          <t>2026-10-17T09:22:30.853569+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.444563+00:00</t>
+          <t>2026-10-17T09:22:30.855568+00:00</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.445134+00:00</t>
+          <t>2026-10-17T09:22:30.856223+00:00</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.445745+00:00</t>
+          <t>2026-10-17T09:22:30.857027+00:00</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.447361+00:00</t>
+          <t>2026-10-17T09:22:30.858685+00:00</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.450499+00:00</t>
+          <t>2026-10-17T09:22:30.861565+00:00</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.452702+00:00</t>
+          <t>2026-10-17T09:22:30.863686+00:00</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.454237+00:00</t>
+          <t>2026-10-17T09:22:30.864982+00:00</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.457383+00:00</t>
+          <t>2026-10-17T09:22:30.868329+00:00</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.458212+00:00</t>
+          <t>2026-10-17T09:22:30.869095+00:00</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.459932+00:00</t>
+          <t>2026-10-17T09:22:30.870786+00:00</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.460193+00:00</t>
+          <t>2026-10-17T09:22:30.871077+00:00</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.462100+00:00</t>
+          <t>2026-10-17T09:22:30.873193+00:00</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.464912+00:00</t>
+          <t>2026-10-17T09:22:30.876224+00:00</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.466239+00:00</t>
+          <t>2026-10-17T09:22:30.877886+00:00</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.466805+00:00</t>
+          <t>2026-10-17T09:22:30.878568+00:00</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.469366+00:00</t>
+          <t>2026-10-17T09:22:30.881156+00:00</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.470556+00:00</t>
+          <t>2026-10-17T09:22:30.882410+00:00</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.474195+00:00</t>
+          <t>2026-10-17T09:22:30.885911+00:00</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.476001+00:00</t>
+          <t>2026-10-17T09:22:30.887548+00:00</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.478136+00:00</t>
+          <t>2026-10-17T09:22:30.889373+00:00</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.479178+00:00</t>
+          <t>2026-10-17T09:22:30.890430+00:00</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.479647+00:00</t>
+          <t>2026-10-17T09:22:30.890895+00:00</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.480032+00:00</t>
+          <t>2026-10-17T09:22:30.891311+00:00</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.481515+00:00</t>
+          <t>2026-10-17T09:22:30.892760+00:00</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.482780+00:00</t>
+          <t>2026-10-17T09:22:30.894044+00:00</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.484329+00:00</t>
+          <t>2026-10-17T09:22:30.895535+00:00</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.484676+00:00</t>
+          <t>2026-10-17T09:22:30.895879+00:00</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.486184+00:00</t>
+          <t>2026-10-17T09:22:30.897140+00:00</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.487589+00:00</t>
+          <t>2026-10-17T09:22:30.898728+00:00</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.488190+00:00</t>
+          <t>2026-10-17T09:22:30.899486+00:00</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.489160+00:00</t>
+          <t>2026-10-17T09:22:30.900846+00:00</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.489506+00:00</t>
+          <t>2026-10-17T09:22:30.901456+00:00</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.494459+00:00</t>
+          <t>2026-10-17T09:22:30.909196+00:00</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.494848+00:00</t>
+          <t>2026-10-17T09:22:30.909830+00:00</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.495477+00:00</t>
+          <t>2026-10-17T09:22:30.910534+00:00</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.495935+00:00</t>
+          <t>2026-10-17T09:22:30.911314+00:00</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.497029+00:00</t>
+          <t>2026-10-17T09:22:30.913496+00:00</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.500034+00:00</t>
+          <t>2026-10-17T09:22:30.919978+00:00</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.500313+00:00</t>
+          <t>2026-10-17T09:22:30.920430+00:00</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.504480+00:00</t>
+          <t>2026-10-17T09:22:30.925021+00:00</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.505361+00:00</t>
+          <t>2026-10-17T09:22:30.926206+00:00</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.507744+00:00</t>
+          <t>2026-10-17T09:22:30.929279+00:00</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.509557+00:00</t>
+          <t>2026-10-17T09:22:30.931353+00:00</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.510485+00:00</t>
+          <t>2026-10-17T09:22:30.932351+00:00</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.511881+00:00</t>
+          <t>2026-10-17T09:22:30.933806+00:00</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.514082+00:00</t>
+          <t>2026-10-17T09:22:30.936305+00:00</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.522272+00:00</t>
+          <t>2026-10-17T09:22:30.946091+00:00</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.523881+00:00</t>
+          <t>2026-10-17T09:22:30.947882+00:00</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.524056+00:00</t>
+          <t>2026-10-17T09:22:30.948160+00:00</t>
         </is>
       </c>
     </row>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.524069+00:00</t>
+          <t>2026-10-17T09:22:30.948183+00:00</t>
         </is>
       </c>
     </row>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.529202+00:00</t>
+          <t>2026-10-17T09:22:30.953807+00:00</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.529732+00:00</t>
+          <t>2026-10-17T09:22:30.954420+00:00</t>
         </is>
       </c>
     </row>
@@ -33071,7 +33071,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.530106+00:00</t>
+          <t>2026-10-17T09:22:30.954933+00:00</t>
         </is>
       </c>
     </row>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.530548+00:00</t>
+          <t>2026-10-17T09:22:30.955388+00:00</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.531514+00:00</t>
+          <t>2026-10-17T09:22:30.956198+00:00</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33383,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.532936+00:00</t>
+          <t>2026-10-17T09:22:30.957844+00:00</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.533848+00:00</t>
+          <t>2026-10-17T09:22:30.959001+00:00</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.534151+00:00</t>
+          <t>2026-10-17T09:22:30.959548+00:00</t>
         </is>
       </c>
     </row>
@@ -33699,7 +33699,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.534842+00:00</t>
+          <t>2026-10-17T09:22:30.960282+00:00</t>
         </is>
       </c>
     </row>
@@ -33799,7 +33799,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.534856+00:00</t>
+          <t>2026-10-17T09:22:30.960325+00:00</t>
         </is>
       </c>
     </row>
@@ -33907,7 +33907,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.534909+00:00</t>
+          <t>2026-10-17T09:22:30.960392+00:00</t>
         </is>
       </c>
     </row>
@@ -34015,7 +34015,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.535129+00:00</t>
+          <t>2026-10-17T09:22:30.960629+00:00</t>
         </is>
       </c>
     </row>
@@ -34123,7 +34123,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.535250+00:00</t>
+          <t>2026-10-17T09:22:30.960751+00:00</t>
         </is>
       </c>
     </row>
@@ -34235,7 +34235,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.535381+00:00</t>
+          <t>2026-10-17T09:22:30.960998+00:00</t>
         </is>
       </c>
     </row>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.535758+00:00</t>
+          <t>2026-10-17T09:22:30.961531+00:00</t>
         </is>
       </c>
     </row>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.535954+00:00</t>
+          <t>2026-10-17T09:22:30.961830+00:00</t>
         </is>
       </c>
     </row>
@@ -34563,7 +34563,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.536010+00:00</t>
+          <t>2026-10-17T09:22:30.961902+00:00</t>
         </is>
       </c>
     </row>
@@ -34675,7 +34675,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.536071+00:00</t>
+          <t>2026-10-17T09:22:30.961966+00:00</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.536211+00:00</t>
+          <t>2026-10-17T09:22:30.962108+00:00</t>
         </is>
       </c>
     </row>
@@ -34899,7 +34899,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.536255+00:00</t>
+          <t>2026-10-17T09:22:30.962153+00:00</t>
         </is>
       </c>
     </row>
@@ -35007,7 +35007,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.536742+00:00</t>
+          <t>2026-10-17T09:22:30.962836+00:00</t>
         </is>
       </c>
     </row>
@@ -35115,7 +35115,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.536803+00:00</t>
+          <t>2026-10-17T09:22:30.962910+00:00</t>
         </is>
       </c>
     </row>
@@ -35215,7 +35215,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.536814+00:00</t>
+          <t>2026-10-17T09:22:30.962922+00:00</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.546506+00:00</t>
+          <t>2026-10-17T09:22:30.974519+00:00</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.546569+00:00</t>
+          <t>2026-10-17T09:22:30.974611+00:00</t>
         </is>
       </c>
     </row>
@@ -35535,7 +35535,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.546672+00:00</t>
+          <t>2026-10-17T09:22:30.974739+00:00</t>
         </is>
       </c>
     </row>
@@ -35643,7 +35643,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.546907+00:00</t>
+          <t>2026-10-17T09:22:30.974998+00:00</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.547910+00:00</t>
+          <t>2026-10-17T09:22:30.976314+00:00</t>
         </is>
       </c>
     </row>
@@ -35853,7 +35853,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.548129+00:00</t>
+          <t>2026-10-17T09:22:30.976449+00:00</t>
         </is>
       </c>
     </row>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.548152+00:00</t>
+          <t>2026-10-17T09:22:30.976464+00:00</t>
         </is>
       </c>
     </row>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.548246+00:00</t>
+          <t>2026-10-17T09:22:30.976553+00:00</t>
         </is>
       </c>
     </row>
@@ -36151,7 +36151,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.548355+00:00</t>
+          <t>2026-10-17T09:22:30.976641+00:00</t>
         </is>
       </c>
     </row>
@@ -36253,7 +36253,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.548469+00:00</t>
+          <t>2026-10-17T09:22:30.976751+00:00</t>
         </is>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.548481+00:00</t>
+          <t>2026-10-17T09:22:30.976763+00:00</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.548637+00:00</t>
+          <t>2026-10-17T09:22:30.976944+00:00</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.548648+00:00</t>
+          <t>2026-10-17T09:22:30.976957+00:00</t>
         </is>
       </c>
     </row>
@@ -36645,7 +36645,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.548748+00:00</t>
+          <t>2026-10-17T09:22:30.977067+00:00</t>
         </is>
       </c>
     </row>
@@ -36739,7 +36739,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.548759+00:00</t>
+          <t>2026-10-17T09:22:30.977077+00:00</t>
         </is>
       </c>
     </row>
@@ -36841,7 +36841,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.548900+00:00</t>
+          <t>2026-10-17T09:22:30.977214+00:00</t>
         </is>
       </c>
     </row>
@@ -36935,7 +36935,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.548911+00:00</t>
+          <t>2026-10-17T09:22:30.977225+00:00</t>
         </is>
       </c>
     </row>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.549000+00:00</t>
+          <t>2026-10-17T09:22:30.977336+00:00</t>
         </is>
       </c>
     </row>
@@ -37139,7 +37139,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.549131+00:00</t>
+          <t>2026-10-17T09:22:30.977471+00:00</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.549143+00:00</t>
+          <t>2026-10-17T09:22:30.977504+00:00</t>
         </is>
       </c>
     </row>
@@ -37335,7 +37335,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.549262+00:00</t>
+          <t>2026-10-17T09:22:30.977626+00:00</t>
         </is>
       </c>
     </row>
@@ -37429,7 +37429,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.549273+00:00</t>
+          <t>2026-10-17T09:22:30.977636+00:00</t>
         </is>
       </c>
     </row>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.549393+00:00</t>
+          <t>2026-10-17T09:22:30.977743+00:00</t>
         </is>
       </c>
     </row>
@@ -37633,7 +37633,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.549645+00:00</t>
+          <t>2026-10-17T09:22:30.977967+00:00</t>
         </is>
       </c>
     </row>
@@ -37727,7 +37727,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.549661+00:00</t>
+          <t>2026-10-17T09:22:30.977979+00:00</t>
         </is>
       </c>
     </row>
@@ -37829,7 +37829,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.549970+00:00</t>
+          <t>2026-10-17T09:22:30.978141+00:00</t>
         </is>
       </c>
     </row>
@@ -37931,7 +37931,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.550184+00:00</t>
+          <t>2026-10-17T09:22:30.978372+00:00</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38033,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.550411+00:00</t>
+          <t>2026-10-17T09:22:30.978571+00:00</t>
         </is>
       </c>
     </row>
@@ -38127,7 +38127,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.550425+00:00</t>
+          <t>2026-10-17T09:22:30.978583+00:00</t>
         </is>
       </c>
     </row>
@@ -38229,7 +38229,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.550538+00:00</t>
+          <t>2026-10-17T09:22:30.978693+00:00</t>
         </is>
       </c>
     </row>
@@ -38323,7 +38323,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.550549+00:00</t>
+          <t>2026-10-17T09:22:30.978704+00:00</t>
         </is>
       </c>
     </row>
@@ -38425,7 +38425,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.550637+00:00</t>
+          <t>2026-10-17T09:22:30.978794+00:00</t>
         </is>
       </c>
     </row>
@@ -38533,13 +38533,13 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.551804+00:00</t>
+          <t>2026-10-17T09:22:30.979941+00:00</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -38625,7 +38625,7 @@
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.561397+00:00</t>
+          <t>2026-10-17T09:22:30.989797+00:00</t>
         </is>
       </c>
     </row>
@@ -38725,7 +38725,7 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.561907+00:00</t>
+          <t>2026-10-17T09:22:30.990309+00:00</t>
         </is>
       </c>
     </row>
@@ -38813,7 +38813,7 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.561923+00:00</t>
+          <t>2026-10-17T09:22:30.990325+00:00</t>
         </is>
       </c>
     </row>
@@ -38913,7 +38913,7 @@
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.563075+00:00</t>
+          <t>2026-10-17T09:22:30.991480+00:00</t>
         </is>
       </c>
     </row>
@@ -39013,7 +39013,7 @@
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.566559+00:00</t>
+          <t>2026-10-17T09:22:30.994900+00:00</t>
         </is>
       </c>
     </row>
@@ -39113,7 +39113,7 @@
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.567542+00:00</t>
+          <t>2026-10-17T09:22:30.995850+00:00</t>
         </is>
       </c>
     </row>
@@ -39205,7 +39205,7 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.567560+00:00</t>
+          <t>2026-10-17T09:22:30.995866+00:00</t>
         </is>
       </c>
     </row>
@@ -39272,7 +39272,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -39305,7 +39305,7 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.568262+00:00</t>
+          <t>2026-10-17T09:22:30.996571+00:00</t>
         </is>
       </c>
     </row>
@@ -39397,7 +39397,7 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.568276+00:00</t>
+          <t>2026-10-17T09:22:30.996586+00:00</t>
         </is>
       </c>
     </row>
@@ -39489,7 +39489,7 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.568280+00:00</t>
+          <t>2026-10-17T09:22:30.996589+00:00</t>
         </is>
       </c>
     </row>
@@ -39577,7 +39577,7 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.568284+00:00</t>
+          <t>2026-10-17T09:22:30.996592+00:00</t>
         </is>
       </c>
     </row>
@@ -39669,7 +39669,487 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-10-17T09:09:29.568302+00:00</t>
+          <t>2026-10-17T09:22:30.996595+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="b">
+        <v>1</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>R06588</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>R06588.main.a69e903d7886bcd0</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E149" t="b">
+        <v>0</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>R06588_2021_Effect_of_Rotten_Butter_Shock_Load_on_Anaerobic_Digestion_of_Chicken_Manure_a69e903d7886.pdf</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R06588_2021_Effect_of_Rotten_Butter_Shock_Load_on_Anaerobic_Digestion_of_Chicken_Manure_a69e903d7886.pdf</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R06588_2021_Effect_of_Rotten_Butter_Shock_Load_on_Anaerobic_Digestion_of_Chicken_Manure_a69e903d7886.pdf</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R06588_2021_Effect_of_Rotten_Butter_Shock_Load_on_Anaerobic_Digestion_of_Chicken_Manure_a69e903d7886.pdf</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>1226404</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>a69e903d7886bcd01cf3b4d34bb10798d152945594161598f6eb01c877a7c074</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>present_sha_verified</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>local_acquired_pending_remote_readback</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>https://journal.ugm.ac.id/agritech/article/download/56792/32685</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>出版版（agriTECH 41(4),2021,362–375；自身题名作者及DOI页首核验）</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>Private authorized research backup; source license not inferred</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr"/>
+      <c r="U149" t="inlineStr"/>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr"/>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>2026-10-17T09:22:30.997493+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="b">
+        <v>1</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>R10492</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>R10492.main.3e5bb123d9d9d4ad</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E150" t="b">
+        <v>0</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>R10492_2024_Metagenomic_analysis_reveals_metabolic_mechanism_of_enhancing_lignocellulosic_anaerobic_digestion_me_3e5bb123d9d9.pdf</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R10492_2024_Metagenomic_analysis_reveals_metabolic_mechanism_of_enhancing_lignocellulosic_anaerobic_digestion_me_3e5bb123d9d9.pdf</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R10492_2024_Metagenomic_analysis_reveals_metabolic_mechanism_of_enhancing_lignocellulosic_anaerobic_digestion_me_3e5bb123d9d9.pdf</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R10492_2024_Metagenomic_analysis_reveals_metabolic_mechanism_of_enhancing_lignocellulosic_anaerobic_digestion_me_3e5bb123d9d9.pdf</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>1587578</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>3e5bb123d9d9d4add19c728f272d23055ccb980cf99cb60f516f7c2567ccee11</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>present_sha_verified</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>local_acquired_pending_remote_readback</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>https://dspace.lib.cranfield.ac.uk/server/api/core/bitstreams/6052bc57-8e4b-48b8-aca7-00399ad7eace/content</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>作者接受稿（PDF第一页明确Author Accepted Manuscript及正式DOI；不是预印本）</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Private authorized research backup; source license not inferred</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr"/>
+      <c r="U150" t="inlineStr"/>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr"/>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>2026-10-17T09:22:30.998716+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="b">
+        <v>1</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>R04928</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>R04928.main.9d47028c02204ac0</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E151" t="b">
+        <v>0</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>R04928_2019_MATHEMATICAL_MODEL_FOR_QUANTITATIVE_ANALYSIS_OF_ACIDOGENIC_PERFORMANCE_UNDER_MICROAERATION_CONDITION_9d47028c0220.pdf</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R04928_2019_MATHEMATICAL_MODEL_FOR_QUANTITATIVE_ANALYSIS_OF_ACIDOGENIC_PERFORMANCE_UNDER_MICROAERATION_CONDITION_9d47028c0220.pdf</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R04928_2019_MATHEMATICAL_MODEL_FOR_QUANTITATIVE_ANALYSIS_OF_ACIDOGENIC_PERFORMANCE_UNDER_MICROAERATION_CONDITION_9d47028c0220.pdf</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R04928_2019_MATHEMATICAL_MODEL_FOR_QUANTITATIVE_ANALYSIS_OF_ACIDOGENIC_PERFORMANCE_UNDER_MICROAERATION_CONDITION_9d47028c0220.pdf</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>614108</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>9d47028c02204ac08f73849bdf73af55c1e235aa3593b2b281d139b85d58607f</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>present_sha_verified</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>local_acquired_pending_remote_readback</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>https://jrtppi.id/index.php/jrtppi/article/download/31/24</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>期刊正式文章页提供的出版PDF（10(1):12–21）；PDF DOI栏为占位符，DOI由同一期刊文章页的citation_doi独立核对</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Private authorized research backup; source license not inferred</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr"/>
+      <c r="U151" t="inlineStr"/>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr"/>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>2026-10-17T09:22:30.999166+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="b">
+        <v>1</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>R13955</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>R13955.main.536763265cdc087f</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E152" t="b">
+        <v>0</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>R13955_2017_Biogas_Production_Thesis__20261017_variant_536763265cdc.pdf</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13955_2017_Biogas_Production_Thesis__20261017_variant_536763265cdc.pdf</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>original_files/fulltext/R13955_2017_Biogas_Production_Thesis__20261017_variant_536763265cdc.pdf</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/fulltext/R13955_2017_Biogas_Production_Thesis__20261017_variant_536763265cdc.pdf</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>14662119</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>536763265cdc087f2b0941e5305f33d2b98cc70ec29c58af4e238d1801b5fdce</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>present_sha_verified</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>local_acquired_pending_remote_readback</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>https://lup.lub.lu.se/search/files/30364253/Thesis_Chao_Li_150_dpi.pdf</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>大学出版学位论文/仓储明确标注Publisher PDF；本轮另一字节副本，143页提取文字与已核验副本逐页相同</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>Private authorized research backup; source license not inferred</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr"/>
+      <c r="U152" t="inlineStr"/>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr"/>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>2026-10-17T09:22:31.008715+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="b">
+        <v>0</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>R00735</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>R00735.evidence_html.fbe84942b58dfb81</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>evidence_html</t>
+        </is>
+      </c>
+      <c r="E153" t="b">
+        <v>0</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>publisher_article_page_20261017.html</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R00735/publisher_article_page_20261017.html</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R00735/publisher_article_page_20261017.html</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/source_evidence/R00735/publisher_article_page_20261017.html</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>18604</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>fbe84942b58dfb81b99138bd5095557649cf00b707c88f4a366d3346941335db</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>present_sha_verified</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>local_acquired_pending_remote_readback</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>https://elibrary.asabe.org/abstract.asp?aid=44112&amp;t=3&amp;dabs=Y&amp;redir=&amp;redirType=</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Article HTML with anonymous server session identifiers removed</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>Private authorized research backup; source license not inferred</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr"/>
+      <c r="U153" t="inlineStr"/>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr"/>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>2026-10-17T09:22:31.008898+00:00</t>
         </is>
       </c>
     </row>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -713,7 +713,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H7" t="b">
@@ -756,7 +756,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H8" t="b">
@@ -799,7 +799,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H9" t="b">
@@ -842,7 +842,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H10" t="b">
@@ -885,7 +885,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H11" t="b">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.796820+00:00</t>
+          <t>2026-10-17T09:22:55.491665+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.797808+00:00</t>
+          <t>2026-10-17T09:22:55.492560+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.797834+00:00</t>
+          <t>2026-10-17T09:22:55.492579+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.798075+00:00</t>
+          <t>2026-10-17T09:22:55.492803+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.799161+00:00</t>
+          <t>2026-10-17T09:22:55.493938+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.799657+00:00</t>
+          <t>2026-10-17T09:22:55.494623+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.806684+00:00</t>
+          <t>2026-10-17T09:22:55.500382+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.809068+00:00</t>
+          <t>2026-10-17T09:22:55.502876+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.810077+00:00</t>
+          <t>2026-10-17T09:22:55.503886+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.810447+00:00</t>
+          <t>2026-10-17T09:22:55.504223+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.811231+00:00</t>
+          <t>2026-10-17T09:22:55.505269+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.811895+00:00</t>
+          <t>2026-10-17T09:22:55.506062+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.813125+00:00</t>
+          <t>2026-10-17T09:22:55.507179+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.813546+00:00</t>
+          <t>2026-10-17T09:22:55.507545+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.815065+00:00</t>
+          <t>2026-10-17T09:22:55.508437+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.827603+00:00</t>
+          <t>2026-10-17T09:22:55.516537+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.828480+00:00</t>
+          <t>2026-10-17T09:22:55.517353+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.829715+00:00</t>
+          <t>2026-10-17T09:22:55.518564+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.832179+00:00</t>
+          <t>2026-10-17T09:22:55.521169+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.833261+00:00</t>
+          <t>2026-10-17T09:22:55.522324+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.836519+00:00</t>
+          <t>2026-10-17T09:22:55.523632+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.840897+00:00</t>
+          <t>2026-10-17T09:22:55.527736+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.843206+00:00</t>
+          <t>2026-10-17T09:22:55.529894+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.845025+00:00</t>
+          <t>2026-10-17T09:22:55.531734+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.845844+00:00</t>
+          <t>2026-10-17T09:22:55.532409+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.846404+00:00</t>
+          <t>2026-10-17T09:22:55.532767+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.849761+00:00</t>
+          <t>2026-10-17T09:22:55.534756+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.851231+00:00</t>
+          <t>2026-10-17T09:22:55.535977+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.853569+00:00</t>
+          <t>2026-10-17T09:22:55.538005+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.855568+00:00</t>
+          <t>2026-10-17T09:22:55.539939+00:00</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.856223+00:00</t>
+          <t>2026-10-17T09:22:55.540514+00:00</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.857027+00:00</t>
+          <t>2026-10-17T09:22:55.541083+00:00</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.858685+00:00</t>
+          <t>2026-10-17T09:22:55.542708+00:00</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.861565+00:00</t>
+          <t>2026-10-17T09:22:55.545412+00:00</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.863686+00:00</t>
+          <t>2026-10-17T09:22:55.547775+00:00</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.864982+00:00</t>
+          <t>2026-10-17T09:22:55.549011+00:00</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.868329+00:00</t>
+          <t>2026-10-17T09:22:55.551904+00:00</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.869095+00:00</t>
+          <t>2026-10-17T09:22:55.552669+00:00</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.870786+00:00</t>
+          <t>2026-10-17T09:22:55.554422+00:00</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.871077+00:00</t>
+          <t>2026-10-17T09:22:55.555042+00:00</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.873193+00:00</t>
+          <t>2026-10-17T09:22:55.556947+00:00</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.876224+00:00</t>
+          <t>2026-10-17T09:22:55.559824+00:00</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.877886+00:00</t>
+          <t>2026-10-17T09:22:55.561115+00:00</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.878568+00:00</t>
+          <t>2026-10-17T09:22:55.561697+00:00</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.881156+00:00</t>
+          <t>2026-10-17T09:22:55.564334+00:00</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.882410+00:00</t>
+          <t>2026-10-17T09:22:55.565542+00:00</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.885911+00:00</t>
+          <t>2026-10-17T09:22:55.568946+00:00</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.887548+00:00</t>
+          <t>2026-10-17T09:22:55.571047+00:00</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.889373+00:00</t>
+          <t>2026-10-17T09:22:55.573112+00:00</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.890430+00:00</t>
+          <t>2026-10-17T09:22:55.574280+00:00</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.890895+00:00</t>
+          <t>2026-10-17T09:22:55.574775+00:00</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.891311+00:00</t>
+          <t>2026-10-17T09:22:55.575216+00:00</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.892760+00:00</t>
+          <t>2026-10-17T09:22:55.576862+00:00</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.894044+00:00</t>
+          <t>2026-10-17T09:22:55.579476+00:00</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.895535+00:00</t>
+          <t>2026-10-17T09:22:55.581258+00:00</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.895879+00:00</t>
+          <t>2026-10-17T09:22:55.581671+00:00</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.897140+00:00</t>
+          <t>2026-10-17T09:22:55.583850+00:00</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.898728+00:00</t>
+          <t>2026-10-17T09:22:55.585339+00:00</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.899486+00:00</t>
+          <t>2026-10-17T09:22:55.586135+00:00</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.900846+00:00</t>
+          <t>2026-10-17T09:22:55.587161+00:00</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.901456+00:00</t>
+          <t>2026-10-17T09:22:55.587529+00:00</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.909196+00:00</t>
+          <t>2026-10-17T09:22:55.593057+00:00</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.909830+00:00</t>
+          <t>2026-10-17T09:22:55.593599+00:00</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.910534+00:00</t>
+          <t>2026-10-17T09:22:55.594187+00:00</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.911314+00:00</t>
+          <t>2026-10-17T09:22:55.594776+00:00</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.913496+00:00</t>
+          <t>2026-10-17T09:22:55.595911+00:00</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.919978+00:00</t>
+          <t>2026-10-17T09:22:55.599310+00:00</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.920430+00:00</t>
+          <t>2026-10-17T09:22:55.599601+00:00</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.925021+00:00</t>
+          <t>2026-10-17T09:22:55.603932+00:00</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.926206+00:00</t>
+          <t>2026-10-17T09:22:55.604908+00:00</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.929279+00:00</t>
+          <t>2026-10-17T09:22:55.607352+00:00</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.931353+00:00</t>
+          <t>2026-10-17T09:22:55.609330+00:00</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.932351+00:00</t>
+          <t>2026-10-17T09:22:55.610231+00:00</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.933806+00:00</t>
+          <t>2026-10-17T09:22:55.611691+00:00</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.936305+00:00</t>
+          <t>2026-10-17T09:22:55.614367+00:00</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.946091+00:00</t>
+          <t>2026-10-17T09:22:55.622171+00:00</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.947882+00:00</t>
+          <t>2026-10-17T09:22:55.623429+00:00</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.948160+00:00</t>
+          <t>2026-10-17T09:22:55.623585+00:00</t>
         </is>
       </c>
     </row>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.948183+00:00</t>
+          <t>2026-10-17T09:22:55.623598+00:00</t>
         </is>
       </c>
     </row>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.953807+00:00</t>
+          <t>2026-10-17T09:22:55.628787+00:00</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.954420+00:00</t>
+          <t>2026-10-17T09:22:55.629264+00:00</t>
         </is>
       </c>
     </row>
@@ -33071,7 +33071,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.954933+00:00</t>
+          <t>2026-10-17T09:22:55.629691+00:00</t>
         </is>
       </c>
     </row>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.955388+00:00</t>
+          <t>2026-10-17T09:22:55.630098+00:00</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.956198+00:00</t>
+          <t>2026-10-17T09:22:55.630844+00:00</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33383,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.957844+00:00</t>
+          <t>2026-10-17T09:22:55.632196+00:00</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.959001+00:00</t>
+          <t>2026-10-17T09:22:55.633095+00:00</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.959548+00:00</t>
+          <t>2026-10-17T09:22:55.633440+00:00</t>
         </is>
       </c>
     </row>
@@ -33699,7 +33699,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.960282+00:00</t>
+          <t>2026-10-17T09:22:55.634114+00:00</t>
         </is>
       </c>
     </row>
@@ -33799,7 +33799,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.960325+00:00</t>
+          <t>2026-10-17T09:22:55.634130+00:00</t>
         </is>
       </c>
     </row>
@@ -33907,7 +33907,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.960392+00:00</t>
+          <t>2026-10-17T09:22:55.634181+00:00</t>
         </is>
       </c>
     </row>
@@ -34015,7 +34015,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.960629+00:00</t>
+          <t>2026-10-17T09:22:55.634425+00:00</t>
         </is>
       </c>
     </row>
@@ -34123,7 +34123,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.960751+00:00</t>
+          <t>2026-10-17T09:22:55.634550+00:00</t>
         </is>
       </c>
     </row>
@@ -34235,7 +34235,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.960998+00:00</t>
+          <t>2026-10-17T09:22:55.634759+00:00</t>
         </is>
       </c>
     </row>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.961531+00:00</t>
+          <t>2026-10-17T09:22:55.635404+00:00</t>
         </is>
       </c>
     </row>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.961830+00:00</t>
+          <t>2026-10-17T09:22:55.635627+00:00</t>
         </is>
       </c>
     </row>
@@ -34563,7 +34563,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.961902+00:00</t>
+          <t>2026-10-17T09:22:55.635687+00:00</t>
         </is>
       </c>
     </row>
@@ -34675,7 +34675,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.961966+00:00</t>
+          <t>2026-10-17T09:22:55.635755+00:00</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.962108+00:00</t>
+          <t>2026-10-17T09:22:55.635908+00:00</t>
         </is>
       </c>
     </row>
@@ -34899,7 +34899,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.962153+00:00</t>
+          <t>2026-10-17T09:22:55.635955+00:00</t>
         </is>
       </c>
     </row>
@@ -35007,7 +35007,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.962836+00:00</t>
+          <t>2026-10-17T09:22:55.636518+00:00</t>
         </is>
       </c>
     </row>
@@ -35115,7 +35115,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.962910+00:00</t>
+          <t>2026-10-17T09:22:55.636599+00:00</t>
         </is>
       </c>
     </row>
@@ -35215,7 +35215,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.962922+00:00</t>
+          <t>2026-10-17T09:22:55.636612+00:00</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.974519+00:00</t>
+          <t>2026-10-17T09:22:55.645829+00:00</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.974611+00:00</t>
+          <t>2026-10-17T09:22:55.645911+00:00</t>
         </is>
       </c>
     </row>
@@ -35535,7 +35535,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.974739+00:00</t>
+          <t>2026-10-17T09:22:55.646027+00:00</t>
         </is>
       </c>
     </row>
@@ -35643,7 +35643,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.974998+00:00</t>
+          <t>2026-10-17T09:22:55.646272+00:00</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.976314+00:00</t>
+          <t>2026-10-17T09:22:55.647379+00:00</t>
         </is>
       </c>
     </row>
@@ -35853,7 +35853,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.976449+00:00</t>
+          <t>2026-10-17T09:22:55.647488+00:00</t>
         </is>
       </c>
     </row>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.976464+00:00</t>
+          <t>2026-10-17T09:22:55.647500+00:00</t>
         </is>
       </c>
     </row>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.976553+00:00</t>
+          <t>2026-10-17T09:22:55.647590+00:00</t>
         </is>
       </c>
     </row>
@@ -36151,7 +36151,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.976641+00:00</t>
+          <t>2026-10-17T09:22:55.647679+00:00</t>
         </is>
       </c>
     </row>
@@ -36253,7 +36253,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.976751+00:00</t>
+          <t>2026-10-17T09:22:55.647785+00:00</t>
         </is>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.976763+00:00</t>
+          <t>2026-10-17T09:22:55.647795+00:00</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.976944+00:00</t>
+          <t>2026-10-17T09:22:55.647953+00:00</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.976957+00:00</t>
+          <t>2026-10-17T09:22:55.647966+00:00</t>
         </is>
       </c>
     </row>
@@ -36645,7 +36645,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.977067+00:00</t>
+          <t>2026-10-17T09:22:55.648068+00:00</t>
         </is>
       </c>
     </row>
@@ -36739,7 +36739,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.977077+00:00</t>
+          <t>2026-10-17T09:22:55.648079+00:00</t>
         </is>
       </c>
     </row>
@@ -36841,7 +36841,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.977214+00:00</t>
+          <t>2026-10-17T09:22:55.648213+00:00</t>
         </is>
       </c>
     </row>
@@ -36935,7 +36935,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.977225+00:00</t>
+          <t>2026-10-17T09:22:55.648224+00:00</t>
         </is>
       </c>
     </row>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.977336+00:00</t>
+          <t>2026-10-17T09:22:55.648397+00:00</t>
         </is>
       </c>
     </row>
@@ -37139,7 +37139,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.977471+00:00</t>
+          <t>2026-10-17T09:22:55.648562+00:00</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.977504+00:00</t>
+          <t>2026-10-17T09:22:55.648578+00:00</t>
         </is>
       </c>
     </row>
@@ -37335,7 +37335,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.977626+00:00</t>
+          <t>2026-10-17T09:22:55.648701+00:00</t>
         </is>
       </c>
     </row>
@@ -37429,7 +37429,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.977636+00:00</t>
+          <t>2026-10-17T09:22:55.648712+00:00</t>
         </is>
       </c>
     </row>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.977743+00:00</t>
+          <t>2026-10-17T09:22:55.648824+00:00</t>
         </is>
       </c>
     </row>
@@ -37633,7 +37633,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.977967+00:00</t>
+          <t>2026-10-17T09:22:55.649044+00:00</t>
         </is>
       </c>
     </row>
@@ -37727,7 +37727,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.977979+00:00</t>
+          <t>2026-10-17T09:22:55.649056+00:00</t>
         </is>
       </c>
     </row>
@@ -37829,7 +37829,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.978141+00:00</t>
+          <t>2026-10-17T09:22:55.649218+00:00</t>
         </is>
       </c>
     </row>
@@ -37931,7 +37931,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.978372+00:00</t>
+          <t>2026-10-17T09:22:55.649443+00:00</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38033,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.978571+00:00</t>
+          <t>2026-10-17T09:22:55.649682+00:00</t>
         </is>
       </c>
     </row>
@@ -38127,7 +38127,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.978583+00:00</t>
+          <t>2026-10-17T09:22:55.649697+00:00</t>
         </is>
       </c>
     </row>
@@ -38229,7 +38229,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.978693+00:00</t>
+          <t>2026-10-17T09:22:55.649813+00:00</t>
         </is>
       </c>
     </row>
@@ -38323,7 +38323,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.978704+00:00</t>
+          <t>2026-10-17T09:22:55.649825+00:00</t>
         </is>
       </c>
     </row>
@@ -38425,7 +38425,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.978794+00:00</t>
+          <t>2026-10-17T09:22:55.649915+00:00</t>
         </is>
       </c>
     </row>
@@ -38533,7 +38533,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.979941+00:00</t>
+          <t>2026-10-17T09:22:55.650968+00:00</t>
         </is>
       </c>
     </row>
@@ -38625,7 +38625,7 @@
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.989797+00:00</t>
+          <t>2026-10-17T09:22:55.660634+00:00</t>
         </is>
       </c>
     </row>
@@ -38725,7 +38725,7 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.990309+00:00</t>
+          <t>2026-10-17T09:22:55.661080+00:00</t>
         </is>
       </c>
     </row>
@@ -38813,7 +38813,7 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.990325+00:00</t>
+          <t>2026-10-17T09:22:55.661103+00:00</t>
         </is>
       </c>
     </row>
@@ -38913,7 +38913,7 @@
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.991480+00:00</t>
+          <t>2026-10-17T09:22:55.662418+00:00</t>
         </is>
       </c>
     </row>
@@ -39013,7 +39013,7 @@
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.994900+00:00</t>
+          <t>2026-10-17T09:22:55.665937+00:00</t>
         </is>
       </c>
     </row>
@@ -39113,7 +39113,7 @@
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.995850+00:00</t>
+          <t>2026-10-17T09:22:55.666848+00:00</t>
         </is>
       </c>
     </row>
@@ -39205,7 +39205,7 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.995866+00:00</t>
+          <t>2026-10-17T09:22:55.666867+00:00</t>
         </is>
       </c>
     </row>
@@ -39305,7 +39305,7 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.996571+00:00</t>
+          <t>2026-10-17T09:22:55.667653+00:00</t>
         </is>
       </c>
     </row>
@@ -39397,7 +39397,7 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.996586+00:00</t>
+          <t>2026-10-17T09:22:55.667676+00:00</t>
         </is>
       </c>
     </row>
@@ -39489,7 +39489,7 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.996589+00:00</t>
+          <t>2026-10-17T09:22:55.667681+00:00</t>
         </is>
       </c>
     </row>
@@ -39577,7 +39577,7 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.996592+00:00</t>
+          <t>2026-10-17T09:22:55.667685+00:00</t>
         </is>
       </c>
     </row>
@@ -39669,7 +39669,7 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.996595+00:00</t>
+          <t>2026-10-17T09:22:55.667688+00:00</t>
         </is>
       </c>
     </row>
@@ -39736,7 +39736,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -39765,7 +39765,7 @@
       <c r="W149" t="inlineStr"/>
       <c r="X149" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.997493+00:00</t>
+          <t>2026-10-17T09:22:55.668486+00:00</t>
         </is>
       </c>
     </row>
@@ -39832,7 +39832,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -39861,7 +39861,7 @@
       <c r="W150" t="inlineStr"/>
       <c r="X150" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.998716+00:00</t>
+          <t>2026-10-17T09:22:55.669521+00:00</t>
         </is>
       </c>
     </row>
@@ -39928,7 +39928,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -39957,7 +39957,7 @@
       <c r="W151" t="inlineStr"/>
       <c r="X151" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:30.999166+00:00</t>
+          <t>2026-10-17T09:22:55.669959+00:00</t>
         </is>
       </c>
     </row>
@@ -40024,7 +40024,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -40053,7 +40053,7 @@
       <c r="W152" t="inlineStr"/>
       <c r="X152" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:31.008715+00:00</t>
+          <t>2026-10-17T09:22:55.679646+00:00</t>
         </is>
       </c>
     </row>
@@ -40120,7 +40120,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -40149,7 +40149,7 @@
       <c r="W153" t="inlineStr"/>
       <c r="X153" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:31.008898+00:00</t>
+          <t>2026-10-17T09:22:55.679818+00:00</t>
         </is>
       </c>
     </row>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -928,7 +928,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H12" t="b">
@@ -971,7 +971,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H13" t="b">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H14" t="b">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H15" t="b">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H16" t="b">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.491665+00:00</t>
+          <t>2026-10-17T09:23:15.771160+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.492560+00:00</t>
+          <t>2026-10-17T09:23:15.772068+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.492579+00:00</t>
+          <t>2026-10-17T09:23:15.772085+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.492803+00:00</t>
+          <t>2026-10-17T09:23:15.772325+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.493938+00:00</t>
+          <t>2026-10-17T09:23:15.773426+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.494623+00:00</t>
+          <t>2026-10-17T09:23:15.773932+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.500382+00:00</t>
+          <t>2026-10-17T09:23:15.779019+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.502876+00:00</t>
+          <t>2026-10-17T09:23:15.781267+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.503886+00:00</t>
+          <t>2026-10-17T09:23:15.782213+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.504223+00:00</t>
+          <t>2026-10-17T09:23:15.782654+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.505269+00:00</t>
+          <t>2026-10-17T09:23:15.783453+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.506062+00:00</t>
+          <t>2026-10-17T09:23:15.784140+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.507179+00:00</t>
+          <t>2026-10-17T09:23:15.785058+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.507545+00:00</t>
+          <t>2026-10-17T09:23:15.785316+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.508437+00:00</t>
+          <t>2026-10-17T09:23:15.786196+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.516537+00:00</t>
+          <t>2026-10-17T09:23:15.793340+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.517353+00:00</t>
+          <t>2026-10-17T09:23:15.794065+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.518564+00:00</t>
+          <t>2026-10-17T09:23:15.795331+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.521169+00:00</t>
+          <t>2026-10-17T09:23:15.797910+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.522324+00:00</t>
+          <t>2026-10-17T09:23:15.799015+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.523632+00:00</t>
+          <t>2026-10-17T09:23:15.800196+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.527736+00:00</t>
+          <t>2026-10-17T09:23:15.804301+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.529894+00:00</t>
+          <t>2026-10-17T09:23:15.806494+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.531734+00:00</t>
+          <t>2026-10-17T09:23:15.808391+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.532409+00:00</t>
+          <t>2026-10-17T09:23:15.809151+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.532767+00:00</t>
+          <t>2026-10-17T09:23:15.809614+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.534756+00:00</t>
+          <t>2026-10-17T09:23:15.811653+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.535977+00:00</t>
+          <t>2026-10-17T09:23:15.813158+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.538005+00:00</t>
+          <t>2026-10-17T09:23:15.815305+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.539939+00:00</t>
+          <t>2026-10-17T09:23:15.817260+00:00</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.540514+00:00</t>
+          <t>2026-10-17T09:23:15.817902+00:00</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.541083+00:00</t>
+          <t>2026-10-17T09:23:15.818511+00:00</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.542708+00:00</t>
+          <t>2026-10-17T09:23:15.820111+00:00</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.545412+00:00</t>
+          <t>2026-10-17T09:23:15.822852+00:00</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.547775+00:00</t>
+          <t>2026-10-17T09:23:15.824929+00:00</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.549011+00:00</t>
+          <t>2026-10-17T09:23:15.826219+00:00</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.551904+00:00</t>
+          <t>2026-10-17T09:23:15.829309+00:00</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.552669+00:00</t>
+          <t>2026-10-17T09:23:15.830078+00:00</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.554422+00:00</t>
+          <t>2026-10-17T09:23:15.831651+00:00</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.555042+00:00</t>
+          <t>2026-10-17T09:23:15.831914+00:00</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.556947+00:00</t>
+          <t>2026-10-17T09:23:15.833970+00:00</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.559824+00:00</t>
+          <t>2026-10-17T09:23:15.837145+00:00</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.561115+00:00</t>
+          <t>2026-10-17T09:23:15.838610+00:00</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.561697+00:00</t>
+          <t>2026-10-17T09:23:15.839236+00:00</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.564334+00:00</t>
+          <t>2026-10-17T09:23:15.841849+00:00</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.565542+00:00</t>
+          <t>2026-10-17T09:23:15.842972+00:00</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.568946+00:00</t>
+          <t>2026-10-17T09:23:15.846325+00:00</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.571047+00:00</t>
+          <t>2026-10-17T09:23:15.847929+00:00</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.573112+00:00</t>
+          <t>2026-10-17T09:23:15.849741+00:00</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.574280+00:00</t>
+          <t>2026-10-17T09:23:15.850673+00:00</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.574775+00:00</t>
+          <t>2026-10-17T09:23:15.851141+00:00</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.575216+00:00</t>
+          <t>2026-10-17T09:23:15.851558+00:00</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.576862+00:00</t>
+          <t>2026-10-17T09:23:15.853001+00:00</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.579476+00:00</t>
+          <t>2026-10-17T09:23:15.854376+00:00</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.581258+00:00</t>
+          <t>2026-10-17T09:23:15.855872+00:00</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.581671+00:00</t>
+          <t>2026-10-17T09:23:15.856214+00:00</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.583850+00:00</t>
+          <t>2026-10-17T09:23:15.857379+00:00</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.585339+00:00</t>
+          <t>2026-10-17T09:23:15.858887+00:00</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.586135+00:00</t>
+          <t>2026-10-17T09:23:15.859540+00:00</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.587161+00:00</t>
+          <t>2026-10-17T09:23:15.860556+00:00</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.587529+00:00</t>
+          <t>2026-10-17T09:23:15.860900+00:00</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.593057+00:00</t>
+          <t>2026-10-17T09:23:15.865921+00:00</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.593599+00:00</t>
+          <t>2026-10-17T09:23:15.866365+00:00</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.594187+00:00</t>
+          <t>2026-10-17T09:23:15.866931+00:00</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.594776+00:00</t>
+          <t>2026-10-17T09:23:15.867424+00:00</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.595911+00:00</t>
+          <t>2026-10-17T09:23:15.868478+00:00</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.599310+00:00</t>
+          <t>2026-10-17T09:23:15.871397+00:00</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.599601+00:00</t>
+          <t>2026-10-17T09:23:15.871649+00:00</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.603932+00:00</t>
+          <t>2026-10-17T09:23:15.875735+00:00</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.604908+00:00</t>
+          <t>2026-10-17T09:23:15.876535+00:00</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.607352+00:00</t>
+          <t>2026-10-17T09:23:15.878632+00:00</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.609330+00:00</t>
+          <t>2026-10-17T09:23:15.880346+00:00</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.610231+00:00</t>
+          <t>2026-10-17T09:23:15.881227+00:00</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.611691+00:00</t>
+          <t>2026-10-17T09:23:15.882646+00:00</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.614367+00:00</t>
+          <t>2026-10-17T09:23:15.884820+00:00</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.622171+00:00</t>
+          <t>2026-10-17T09:23:15.892806+00:00</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.623429+00:00</t>
+          <t>2026-10-17T09:23:15.894166+00:00</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.623585+00:00</t>
+          <t>2026-10-17T09:23:15.894330+00:00</t>
         </is>
       </c>
     </row>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.623598+00:00</t>
+          <t>2026-10-17T09:23:15.894343+00:00</t>
         </is>
       </c>
     </row>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.628787+00:00</t>
+          <t>2026-10-17T09:23:15.899450+00:00</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.629264+00:00</t>
+          <t>2026-10-17T09:23:15.899902+00:00</t>
         </is>
       </c>
     </row>
@@ -33071,7 +33071,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.629691+00:00</t>
+          <t>2026-10-17T09:23:15.900258+00:00</t>
         </is>
       </c>
     </row>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.630098+00:00</t>
+          <t>2026-10-17T09:23:15.900709+00:00</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.630844+00:00</t>
+          <t>2026-10-17T09:23:15.901453+00:00</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33383,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.632196+00:00</t>
+          <t>2026-10-17T09:23:15.902836+00:00</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.633095+00:00</t>
+          <t>2026-10-17T09:23:15.903661+00:00</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.633440+00:00</t>
+          <t>2026-10-17T09:23:15.903980+00:00</t>
         </is>
       </c>
     </row>
@@ -33699,7 +33699,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.634114+00:00</t>
+          <t>2026-10-17T09:23:15.904718+00:00</t>
         </is>
       </c>
     </row>
@@ -33799,7 +33799,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.634130+00:00</t>
+          <t>2026-10-17T09:23:15.904741+00:00</t>
         </is>
       </c>
     </row>
@@ -33907,7 +33907,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.634181+00:00</t>
+          <t>2026-10-17T09:23:15.904804+00:00</t>
         </is>
       </c>
     </row>
@@ -34015,7 +34015,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.634425+00:00</t>
+          <t>2026-10-17T09:23:15.905034+00:00</t>
         </is>
       </c>
     </row>
@@ -34123,7 +34123,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.634550+00:00</t>
+          <t>2026-10-17T09:23:15.905157+00:00</t>
         </is>
       </c>
     </row>
@@ -34235,7 +34235,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.634759+00:00</t>
+          <t>2026-10-17T09:23:15.905276+00:00</t>
         </is>
       </c>
     </row>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.635404+00:00</t>
+          <t>2026-10-17T09:23:15.905812+00:00</t>
         </is>
       </c>
     </row>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.635627+00:00</t>
+          <t>2026-10-17T09:23:15.906026+00:00</t>
         </is>
       </c>
     </row>
@@ -34563,7 +34563,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.635687+00:00</t>
+          <t>2026-10-17T09:23:15.906087+00:00</t>
         </is>
       </c>
     </row>
@@ -34675,7 +34675,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.635755+00:00</t>
+          <t>2026-10-17T09:23:15.906154+00:00</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.635908+00:00</t>
+          <t>2026-10-17T09:23:15.906346+00:00</t>
         </is>
       </c>
     </row>
@@ -34899,7 +34899,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.635955+00:00</t>
+          <t>2026-10-17T09:23:15.906405+00:00</t>
         </is>
       </c>
     </row>
@@ -35007,7 +35007,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.636518+00:00</t>
+          <t>2026-10-17T09:23:15.906876+00:00</t>
         </is>
       </c>
     </row>
@@ -35115,7 +35115,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.636599+00:00</t>
+          <t>2026-10-17T09:23:15.906938+00:00</t>
         </is>
       </c>
     </row>
@@ -35215,7 +35215,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.636612+00:00</t>
+          <t>2026-10-17T09:23:15.906949+00:00</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.645829+00:00</t>
+          <t>2026-10-17T09:23:15.916757+00:00</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.645911+00:00</t>
+          <t>2026-10-17T09:23:15.916833+00:00</t>
         </is>
       </c>
     </row>
@@ -35535,7 +35535,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.646027+00:00</t>
+          <t>2026-10-17T09:23:15.916947+00:00</t>
         </is>
       </c>
     </row>
@@ -35643,7 +35643,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.646272+00:00</t>
+          <t>2026-10-17T09:23:15.917186+00:00</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.647379+00:00</t>
+          <t>2026-10-17T09:23:15.918273+00:00</t>
         </is>
       </c>
     </row>
@@ -35853,7 +35853,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.647488+00:00</t>
+          <t>2026-10-17T09:23:15.918411+00:00</t>
         </is>
       </c>
     </row>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.647500+00:00</t>
+          <t>2026-10-17T09:23:15.918425+00:00</t>
         </is>
       </c>
     </row>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.647590+00:00</t>
+          <t>2026-10-17T09:23:15.918508+00:00</t>
         </is>
       </c>
     </row>
@@ -36151,7 +36151,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.647679+00:00</t>
+          <t>2026-10-17T09:23:15.918597+00:00</t>
         </is>
       </c>
     </row>
@@ -36253,7 +36253,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.647785+00:00</t>
+          <t>2026-10-17T09:23:15.918707+00:00</t>
         </is>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.647795+00:00</t>
+          <t>2026-10-17T09:23:15.918720+00:00</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.647953+00:00</t>
+          <t>2026-10-17T09:23:15.918877+00:00</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.647966+00:00</t>
+          <t>2026-10-17T09:23:15.918888+00:00</t>
         </is>
       </c>
     </row>
@@ -36645,7 +36645,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.648068+00:00</t>
+          <t>2026-10-17T09:23:15.918995+00:00</t>
         </is>
       </c>
     </row>
@@ -36739,7 +36739,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.648079+00:00</t>
+          <t>2026-10-17T09:23:15.919006+00:00</t>
         </is>
       </c>
     </row>
@@ -36841,7 +36841,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.648213+00:00</t>
+          <t>2026-10-17T09:23:15.919149+00:00</t>
         </is>
       </c>
     </row>
@@ -36935,7 +36935,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.648224+00:00</t>
+          <t>2026-10-17T09:23:15.919160+00:00</t>
         </is>
       </c>
     </row>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.648397+00:00</t>
+          <t>2026-10-17T09:23:15.919252+00:00</t>
         </is>
       </c>
     </row>
@@ -37139,7 +37139,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.648562+00:00</t>
+          <t>2026-10-17T09:23:15.919409+00:00</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.648578+00:00</t>
+          <t>2026-10-17T09:23:15.919422+00:00</t>
         </is>
       </c>
     </row>
@@ -37335,7 +37335,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.648701+00:00</t>
+          <t>2026-10-17T09:23:15.919550+00:00</t>
         </is>
       </c>
     </row>
@@ -37429,7 +37429,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.648712+00:00</t>
+          <t>2026-10-17T09:23:15.919561+00:00</t>
         </is>
       </c>
     </row>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.648824+00:00</t>
+          <t>2026-10-17T09:23:15.919670+00:00</t>
         </is>
       </c>
     </row>
@@ -37633,7 +37633,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.649044+00:00</t>
+          <t>2026-10-17T09:23:15.919901+00:00</t>
         </is>
       </c>
     </row>
@@ -37727,7 +37727,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.649056+00:00</t>
+          <t>2026-10-17T09:23:15.919913+00:00</t>
         </is>
       </c>
     </row>
@@ -37829,7 +37829,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.649218+00:00</t>
+          <t>2026-10-17T09:23:15.920079+00:00</t>
         </is>
       </c>
     </row>
@@ -37931,7 +37931,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.649443+00:00</t>
+          <t>2026-10-17T09:23:15.920308+00:00</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38033,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.649682+00:00</t>
+          <t>2026-10-17T09:23:15.920510+00:00</t>
         </is>
       </c>
     </row>
@@ -38127,7 +38127,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.649697+00:00</t>
+          <t>2026-10-17T09:23:15.920521+00:00</t>
         </is>
       </c>
     </row>
@@ -38229,7 +38229,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.649813+00:00</t>
+          <t>2026-10-17T09:23:15.920636+00:00</t>
         </is>
       </c>
     </row>
@@ -38323,7 +38323,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.649825+00:00</t>
+          <t>2026-10-17T09:23:15.920647+00:00</t>
         </is>
       </c>
     </row>
@@ -38425,7 +38425,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.649915+00:00</t>
+          <t>2026-10-17T09:23:15.920737+00:00</t>
         </is>
       </c>
     </row>
@@ -38533,7 +38533,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.650968+00:00</t>
+          <t>2026-10-17T09:23:15.921852+00:00</t>
         </is>
       </c>
     </row>
@@ -38625,7 +38625,7 @@
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.660634+00:00</t>
+          <t>2026-10-17T09:23:15.931564+00:00</t>
         </is>
       </c>
     </row>
@@ -38725,7 +38725,7 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.661080+00:00</t>
+          <t>2026-10-17T09:23:15.931988+00:00</t>
         </is>
       </c>
     </row>
@@ -38813,7 +38813,7 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.661103+00:00</t>
+          <t>2026-10-17T09:23:15.932002+00:00</t>
         </is>
       </c>
     </row>
@@ -38913,7 +38913,7 @@
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.662418+00:00</t>
+          <t>2026-10-17T09:23:15.933092+00:00</t>
         </is>
       </c>
     </row>
@@ -39013,7 +39013,7 @@
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.665937+00:00</t>
+          <t>2026-10-17T09:23:15.936424+00:00</t>
         </is>
       </c>
     </row>
@@ -39113,7 +39113,7 @@
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.666848+00:00</t>
+          <t>2026-10-17T09:23:15.937380+00:00</t>
         </is>
       </c>
     </row>
@@ -39205,7 +39205,7 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.666867+00:00</t>
+          <t>2026-10-17T09:23:15.937396+00:00</t>
         </is>
       </c>
     </row>
@@ -39305,7 +39305,7 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.667653+00:00</t>
+          <t>2026-10-17T09:23:15.938108+00:00</t>
         </is>
       </c>
     </row>
@@ -39397,7 +39397,7 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.667676+00:00</t>
+          <t>2026-10-17T09:23:15.938123+00:00</t>
         </is>
       </c>
     </row>
@@ -39489,7 +39489,7 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.667681+00:00</t>
+          <t>2026-10-17T09:23:15.938127+00:00</t>
         </is>
       </c>
     </row>
@@ -39577,7 +39577,7 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.667685+00:00</t>
+          <t>2026-10-17T09:23:15.938132+00:00</t>
         </is>
       </c>
     </row>
@@ -39669,7 +39669,7 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.667688+00:00</t>
+          <t>2026-10-17T09:23:15.938135+00:00</t>
         </is>
       </c>
     </row>
@@ -39765,7 +39765,7 @@
       <c r="W149" t="inlineStr"/>
       <c r="X149" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.668486+00:00</t>
+          <t>2026-10-17T09:23:15.938925+00:00</t>
         </is>
       </c>
     </row>
@@ -39861,7 +39861,7 @@
       <c r="W150" t="inlineStr"/>
       <c r="X150" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.669521+00:00</t>
+          <t>2026-10-17T09:23:15.939953+00:00</t>
         </is>
       </c>
     </row>
@@ -39957,7 +39957,7 @@
       <c r="W151" t="inlineStr"/>
       <c r="X151" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.669959+00:00</t>
+          <t>2026-10-17T09:23:15.940432+00:00</t>
         </is>
       </c>
     </row>
@@ -40053,7 +40053,7 @@
       <c r="W152" t="inlineStr"/>
       <c r="X152" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.679646+00:00</t>
+          <t>2026-10-17T09:23:15.950638+00:00</t>
         </is>
       </c>
     </row>
@@ -40149,7 +40149,7 @@
       <c r="W153" t="inlineStr"/>
       <c r="X153" t="inlineStr">
         <is>
-          <t>2026-10-17T09:22:55.679818+00:00</t>
+          <t>2026-10-17T09:23:15.950792+00:00</t>
         </is>
       </c>
     </row>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -1143,7 +1143,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H17" t="b">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>checked_no_file_links_found_coverage_unconfirmed</t>
         </is>
       </c>
       <c r="H18" t="b">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H19" t="b">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H20" t="b">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H21" t="b">
@@ -24118,7 +24118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X153"/>
+  <dimension ref="A1:X154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.771160+00:00</t>
+          <t>2026-10-17T09:23:39.564664+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.772068+00:00</t>
+          <t>2026-10-17T09:23:39.565594+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.772085+00:00</t>
+          <t>2026-10-17T09:23:39.565617+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.772325+00:00</t>
+          <t>2026-10-17T09:23:39.565854+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.773426+00:00</t>
+          <t>2026-10-17T09:23:39.567004+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.773932+00:00</t>
+          <t>2026-10-17T09:23:39.567470+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.779019+00:00</t>
+          <t>2026-10-17T09:23:39.572726+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.781267+00:00</t>
+          <t>2026-10-17T09:23:39.574990+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.782213+00:00</t>
+          <t>2026-10-17T09:23:39.575893+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.782654+00:00</t>
+          <t>2026-10-17T09:23:39.576376+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.783453+00:00</t>
+          <t>2026-10-17T09:23:39.577146+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.784140+00:00</t>
+          <t>2026-10-17T09:23:39.577941+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.785058+00:00</t>
+          <t>2026-10-17T09:23:39.578918+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.785316+00:00</t>
+          <t>2026-10-17T09:23:39.579240+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.786196+00:00</t>
+          <t>2026-10-17T09:23:39.580131+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.793340+00:00</t>
+          <t>2026-10-17T09:23:39.588903+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.794065+00:00</t>
+          <t>2026-10-17T09:23:39.591388+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.795331+00:00</t>
+          <t>2026-10-17T09:23:39.592681+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.797910+00:00</t>
+          <t>2026-10-17T09:23:39.597250+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.799015+00:00</t>
+          <t>2026-10-17T09:23:39.600624+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.800196+00:00</t>
+          <t>2026-10-17T09:23:39.601968+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.804301+00:00</t>
+          <t>2026-10-17T09:23:39.606878+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.806494+00:00</t>
+          <t>2026-10-17T09:23:39.609199+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.808391+00:00</t>
+          <t>2026-10-17T09:23:39.611466+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.809151+00:00</t>
+          <t>2026-10-17T09:23:39.612539+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.809614+00:00</t>
+          <t>2026-10-17T09:23:39.613015+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.811653+00:00</t>
+          <t>2026-10-17T09:23:39.615136+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.813158+00:00</t>
+          <t>2026-10-17T09:23:39.616503+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.815305+00:00</t>
+          <t>2026-10-17T09:23:39.618737+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.817260+00:00</t>
+          <t>2026-10-17T09:23:39.620761+00:00</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.817902+00:00</t>
+          <t>2026-10-17T09:23:39.621346+00:00</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.818511+00:00</t>
+          <t>2026-10-17T09:23:39.621932+00:00</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.820111+00:00</t>
+          <t>2026-10-17T09:23:39.623878+00:00</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.822852+00:00</t>
+          <t>2026-10-17T09:23:39.626869+00:00</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.824929+00:00</t>
+          <t>2026-10-17T09:23:39.629428+00:00</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.826219+00:00</t>
+          <t>2026-10-17T09:23:39.630784+00:00</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.829309+00:00</t>
+          <t>2026-10-17T09:23:39.633906+00:00</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.830078+00:00</t>
+          <t>2026-10-17T09:23:39.636488+00:00</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.831651+00:00</t>
+          <t>2026-10-17T09:23:39.638159+00:00</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.831914+00:00</t>
+          <t>2026-10-17T09:23:39.641943+00:00</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.833970+00:00</t>
+          <t>2026-10-17T09:23:39.644205+00:00</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.837145+00:00</t>
+          <t>2026-10-17T09:23:39.647535+00:00</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.838610+00:00</t>
+          <t>2026-10-17T09:23:39.649138+00:00</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.839236+00:00</t>
+          <t>2026-10-17T09:23:39.649856+00:00</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.841849+00:00</t>
+          <t>2026-10-17T09:23:39.652737+00:00</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.842972+00:00</t>
+          <t>2026-10-17T09:23:39.653896+00:00</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.846325+00:00</t>
+          <t>2026-10-17T09:23:39.657899+00:00</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.847929+00:00</t>
+          <t>2026-10-17T09:23:39.659770+00:00</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.849741+00:00</t>
+          <t>2026-10-17T09:23:39.661734+00:00</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.850673+00:00</t>
+          <t>2026-10-17T09:23:39.662739+00:00</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.851141+00:00</t>
+          <t>2026-10-17T09:23:39.663177+00:00</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.851558+00:00</t>
+          <t>2026-10-17T09:23:39.663570+00:00</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.853001+00:00</t>
+          <t>2026-10-17T09:23:39.665092+00:00</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.854376+00:00</t>
+          <t>2026-10-17T09:23:39.666550+00:00</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.855872+00:00</t>
+          <t>2026-10-17T09:23:39.668318+00:00</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.856214+00:00</t>
+          <t>2026-10-17T09:23:39.668685+00:00</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.857379+00:00</t>
+          <t>2026-10-17T09:23:39.670169+00:00</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.858887+00:00</t>
+          <t>2026-10-17T09:23:39.671628+00:00</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.859540+00:00</t>
+          <t>2026-10-17T09:23:39.672231+00:00</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.860556+00:00</t>
+          <t>2026-10-17T09:23:39.673159+00:00</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.860900+00:00</t>
+          <t>2026-10-17T09:23:39.673571+00:00</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.865921+00:00</t>
+          <t>2026-10-17T09:23:39.679438+00:00</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.866365+00:00</t>
+          <t>2026-10-17T09:23:39.679900+00:00</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.866931+00:00</t>
+          <t>2026-10-17T09:23:39.680489+00:00</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.867424+00:00</t>
+          <t>2026-10-17T09:23:39.680930+00:00</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.868478+00:00</t>
+          <t>2026-10-17T09:23:39.682222+00:00</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.871397+00:00</t>
+          <t>2026-10-17T09:23:39.686082+00:00</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.871649+00:00</t>
+          <t>2026-10-17T09:23:39.686399+00:00</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.875735+00:00</t>
+          <t>2026-10-17T09:23:39.691349+00:00</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.876535+00:00</t>
+          <t>2026-10-17T09:23:39.692241+00:00</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.878632+00:00</t>
+          <t>2026-10-17T09:23:39.694557+00:00</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.880346+00:00</t>
+          <t>2026-10-17T09:23:39.696399+00:00</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.881227+00:00</t>
+          <t>2026-10-17T09:23:39.697367+00:00</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.882646+00:00</t>
+          <t>2026-10-17T09:23:39.699151+00:00</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.884820+00:00</t>
+          <t>2026-10-17T09:23:39.701421+00:00</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.892806+00:00</t>
+          <t>2026-10-17T09:23:39.710257+00:00</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.894166+00:00</t>
+          <t>2026-10-17T09:23:39.711607+00:00</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.894330+00:00</t>
+          <t>2026-10-17T09:23:39.711767+00:00</t>
         </is>
       </c>
     </row>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.894343+00:00</t>
+          <t>2026-10-17T09:23:39.711780+00:00</t>
         </is>
       </c>
     </row>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.899450+00:00</t>
+          <t>2026-10-17T09:23:39.717179+00:00</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.899902+00:00</t>
+          <t>2026-10-17T09:23:39.718181+00:00</t>
         </is>
       </c>
     </row>
@@ -33071,7 +33071,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.900258+00:00</t>
+          <t>2026-10-17T09:23:39.718659+00:00</t>
         </is>
       </c>
     </row>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.900709+00:00</t>
+          <t>2026-10-17T09:23:39.719078+00:00</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.901453+00:00</t>
+          <t>2026-10-17T09:23:39.719898+00:00</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33383,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.902836+00:00</t>
+          <t>2026-10-17T09:23:39.721327+00:00</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.903661+00:00</t>
+          <t>2026-10-17T09:23:39.722368+00:00</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.903980+00:00</t>
+          <t>2026-10-17T09:23:39.722755+00:00</t>
         </is>
       </c>
     </row>
@@ -33699,7 +33699,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.904718+00:00</t>
+          <t>2026-10-17T09:23:39.723422+00:00</t>
         </is>
       </c>
     </row>
@@ -33799,7 +33799,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.904741+00:00</t>
+          <t>2026-10-17T09:23:39.723441+00:00</t>
         </is>
       </c>
     </row>
@@ -33907,7 +33907,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.904804+00:00</t>
+          <t>2026-10-17T09:23:39.723498+00:00</t>
         </is>
       </c>
     </row>
@@ -34015,7 +34015,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.905034+00:00</t>
+          <t>2026-10-17T09:23:39.723742+00:00</t>
         </is>
       </c>
     </row>
@@ -34123,7 +34123,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.905157+00:00</t>
+          <t>2026-10-17T09:23:39.723874+00:00</t>
         </is>
       </c>
     </row>
@@ -34235,7 +34235,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.905276+00:00</t>
+          <t>2026-10-17T09:23:39.723994+00:00</t>
         </is>
       </c>
     </row>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.905812+00:00</t>
+          <t>2026-10-17T09:23:39.724379+00:00</t>
         </is>
       </c>
     </row>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.906026+00:00</t>
+          <t>2026-10-17T09:23:39.724589+00:00</t>
         </is>
       </c>
     </row>
@@ -34563,7 +34563,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.906087+00:00</t>
+          <t>2026-10-17T09:23:39.724647+00:00</t>
         </is>
       </c>
     </row>
@@ -34675,7 +34675,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.906154+00:00</t>
+          <t>2026-10-17T09:23:39.724710+00:00</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.906346+00:00</t>
+          <t>2026-10-17T09:23:39.724939+00:00</t>
         </is>
       </c>
     </row>
@@ -34899,7 +34899,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.906405+00:00</t>
+          <t>2026-10-17T09:23:39.725010+00:00</t>
         </is>
       </c>
     </row>
@@ -35007,7 +35007,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.906876+00:00</t>
+          <t>2026-10-17T09:23:39.725502+00:00</t>
         </is>
       </c>
     </row>
@@ -35115,7 +35115,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.906938+00:00</t>
+          <t>2026-10-17T09:23:39.725572+00:00</t>
         </is>
       </c>
     </row>
@@ -35215,7 +35215,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.906949+00:00</t>
+          <t>2026-10-17T09:23:39.725583+00:00</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.916757+00:00</t>
+          <t>2026-10-17T09:23:39.736894+00:00</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.916833+00:00</t>
+          <t>2026-10-17T09:23:39.736989+00:00</t>
         </is>
       </c>
     </row>
@@ -35535,7 +35535,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.916947+00:00</t>
+          <t>2026-10-17T09:23:39.737119+00:00</t>
         </is>
       </c>
     </row>
@@ -35643,7 +35643,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.917186+00:00</t>
+          <t>2026-10-17T09:23:39.737452+00:00</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.918273+00:00</t>
+          <t>2026-10-17T09:23:39.738759+00:00</t>
         </is>
       </c>
     </row>
@@ -35853,7 +35853,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.918411+00:00</t>
+          <t>2026-10-17T09:23:39.739073+00:00</t>
         </is>
       </c>
     </row>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.918425+00:00</t>
+          <t>2026-10-17T09:23:39.739098+00:00</t>
         </is>
       </c>
     </row>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.918508+00:00</t>
+          <t>2026-10-17T09:23:39.739197+00:00</t>
         </is>
       </c>
     </row>
@@ -36151,7 +36151,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.918597+00:00</t>
+          <t>2026-10-17T09:23:39.739309+00:00</t>
         </is>
       </c>
     </row>
@@ -36253,7 +36253,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.918707+00:00</t>
+          <t>2026-10-17T09:23:39.739431+00:00</t>
         </is>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.918720+00:00</t>
+          <t>2026-10-17T09:23:39.739444+00:00</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.918877+00:00</t>
+          <t>2026-10-17T09:23:39.739604+00:00</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.918888+00:00</t>
+          <t>2026-10-17T09:23:39.739615+00:00</t>
         </is>
       </c>
     </row>
@@ -36645,7 +36645,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.918995+00:00</t>
+          <t>2026-10-17T09:23:39.739726+00:00</t>
         </is>
       </c>
     </row>
@@ -36739,7 +36739,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.919006+00:00</t>
+          <t>2026-10-17T09:23:39.739736+00:00</t>
         </is>
       </c>
     </row>
@@ -36841,7 +36841,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.919149+00:00</t>
+          <t>2026-10-17T09:23:39.739877+00:00</t>
         </is>
       </c>
     </row>
@@ -36935,7 +36935,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.919160+00:00</t>
+          <t>2026-10-17T09:23:39.739889+00:00</t>
         </is>
       </c>
     </row>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.919252+00:00</t>
+          <t>2026-10-17T09:23:39.739980+00:00</t>
         </is>
       </c>
     </row>
@@ -37139,7 +37139,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.919409+00:00</t>
+          <t>2026-10-17T09:23:39.740116+00:00</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.919422+00:00</t>
+          <t>2026-10-17T09:23:39.740127+00:00</t>
         </is>
       </c>
     </row>
@@ -37335,7 +37335,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.919550+00:00</t>
+          <t>2026-10-17T09:23:39.740245+00:00</t>
         </is>
       </c>
     </row>
@@ -37429,7 +37429,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.919561+00:00</t>
+          <t>2026-10-17T09:23:39.740256+00:00</t>
         </is>
       </c>
     </row>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.919670+00:00</t>
+          <t>2026-10-17T09:23:39.740383+00:00</t>
         </is>
       </c>
     </row>
@@ -37633,7 +37633,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.919901+00:00</t>
+          <t>2026-10-17T09:23:39.740609+00:00</t>
         </is>
       </c>
     </row>
@@ -37727,7 +37727,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.919913+00:00</t>
+          <t>2026-10-17T09:23:39.740621+00:00</t>
         </is>
       </c>
     </row>
@@ -37829,7 +37829,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.920079+00:00</t>
+          <t>2026-10-17T09:23:39.740782+00:00</t>
         </is>
       </c>
     </row>
@@ -37931,7 +37931,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.920308+00:00</t>
+          <t>2026-10-17T09:23:39.740994+00:00</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38033,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.920510+00:00</t>
+          <t>2026-10-17T09:23:39.741189+00:00</t>
         </is>
       </c>
     </row>
@@ -38127,7 +38127,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.920521+00:00</t>
+          <t>2026-10-17T09:23:39.741200+00:00</t>
         </is>
       </c>
     </row>
@@ -38229,7 +38229,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.920636+00:00</t>
+          <t>2026-10-17T09:23:39.741329+00:00</t>
         </is>
       </c>
     </row>
@@ -38323,7 +38323,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.920647+00:00</t>
+          <t>2026-10-17T09:23:39.741341+00:00</t>
         </is>
       </c>
     </row>
@@ -38425,7 +38425,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.920737+00:00</t>
+          <t>2026-10-17T09:23:39.741431+00:00</t>
         </is>
       </c>
     </row>
@@ -38533,7 +38533,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.921852+00:00</t>
+          <t>2026-10-17T09:23:39.742852+00:00</t>
         </is>
       </c>
     </row>
@@ -38625,7 +38625,7 @@
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.931564+00:00</t>
+          <t>2026-10-17T09:23:39.753075+00:00</t>
         </is>
       </c>
     </row>
@@ -38725,7 +38725,7 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.931988+00:00</t>
+          <t>2026-10-17T09:23:39.753556+00:00</t>
         </is>
       </c>
     </row>
@@ -38813,7 +38813,7 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.932002+00:00</t>
+          <t>2026-10-17T09:23:39.753576+00:00</t>
         </is>
       </c>
     </row>
@@ -38913,7 +38913,7 @@
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.933092+00:00</t>
+          <t>2026-10-17T09:23:39.755014+00:00</t>
         </is>
       </c>
     </row>
@@ -39013,7 +39013,7 @@
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.936424+00:00</t>
+          <t>2026-10-17T09:23:39.759408+00:00</t>
         </is>
       </c>
     </row>
@@ -39113,7 +39113,7 @@
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.937380+00:00</t>
+          <t>2026-10-17T09:23:39.760430+00:00</t>
         </is>
       </c>
     </row>
@@ -39205,7 +39205,7 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.937396+00:00</t>
+          <t>2026-10-17T09:23:39.760453+00:00</t>
         </is>
       </c>
     </row>
@@ -39305,7 +39305,7 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.938108+00:00</t>
+          <t>2026-10-17T09:23:39.761161+00:00</t>
         </is>
       </c>
     </row>
@@ -39397,7 +39397,7 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.938123+00:00</t>
+          <t>2026-10-17T09:23:39.761178+00:00</t>
         </is>
       </c>
     </row>
@@ -39489,7 +39489,7 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.938127+00:00</t>
+          <t>2026-10-17T09:23:39.761182+00:00</t>
         </is>
       </c>
     </row>
@@ -39577,7 +39577,7 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.938132+00:00</t>
+          <t>2026-10-17T09:23:39.761185+00:00</t>
         </is>
       </c>
     </row>
@@ -39669,7 +39669,7 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.938135+00:00</t>
+          <t>2026-10-17T09:23:39.761189+00:00</t>
         </is>
       </c>
     </row>
@@ -39765,7 +39765,7 @@
       <c r="W149" t="inlineStr"/>
       <c r="X149" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.938925+00:00</t>
+          <t>2026-10-17T09:23:39.762908+00:00</t>
         </is>
       </c>
     </row>
@@ -39861,7 +39861,7 @@
       <c r="W150" t="inlineStr"/>
       <c r="X150" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.939953+00:00</t>
+          <t>2026-10-17T09:23:39.763970+00:00</t>
         </is>
       </c>
     </row>
@@ -39957,7 +39957,7 @@
       <c r="W151" t="inlineStr"/>
       <c r="X151" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.940432+00:00</t>
+          <t>2026-10-17T09:23:39.764538+00:00</t>
         </is>
       </c>
     </row>
@@ -40053,7 +40053,7 @@
       <c r="W152" t="inlineStr"/>
       <c r="X152" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.950638+00:00</t>
+          <t>2026-10-17T09:23:39.774110+00:00</t>
         </is>
       </c>
     </row>
@@ -40149,7 +40149,103 @@
       <c r="W153" t="inlineStr"/>
       <c r="X153" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:15.950792+00:00</t>
+          <t>2026-10-17T09:23:39.774262+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="b">
+        <v>0</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>R02274</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>R02274.evidence_html.635d598c2639050d</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>evidence_html</t>
+        </is>
+      </c>
+      <c r="E154" t="b">
+        <v>0</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>publisher_article_page_20261017.html</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R02274/publisher_article_page_20261017.html</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R02274/publisher_article_page_20261017.html</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/source_evidence/R02274/publisher_article_page_20261017.html</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>196847</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>635d598c2639050d4522f3ef58cf92a3779f03833561ca384b83cf19a01a5ead</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>present_sha_verified</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>local_acquired_pending_remote_readback</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>http://www.scielo.br/j/bjce/a/Fsb5BG69HCqpVRTqkxS4stm/?lang=en</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>Article HTML with anonymous server session identifiers removed</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>Private authorized research backup; source license not inferred</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr"/>
+      <c r="U154" t="inlineStr"/>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr"/>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>2026-10-17T09:23:39.774467+00:00</t>
         </is>
       </c>
     </row>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -1401,7 +1401,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H23" t="b">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H24" t="b">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H25" t="b">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>checked_no_file_links_found_coverage_unconfirmed</t>
         </is>
       </c>
       <c r="H26" t="b">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H27" t="b">
@@ -24118,7 +24118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X154"/>
+  <dimension ref="A1:X155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.564664+00:00</t>
+          <t>2026-10-17T09:24:03.862081+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.565594+00:00</t>
+          <t>2026-10-17T09:24:03.862969+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.565617+00:00</t>
+          <t>2026-10-17T09:24:03.862987+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.565854+00:00</t>
+          <t>2026-10-17T09:24:03.863216+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.567004+00:00</t>
+          <t>2026-10-17T09:24:03.864363+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.567470+00:00</t>
+          <t>2026-10-17T09:24:03.865311+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.572726+00:00</t>
+          <t>2026-10-17T09:24:03.870597+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.574990+00:00</t>
+          <t>2026-10-17T09:24:03.873018+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.575893+00:00</t>
+          <t>2026-10-17T09:24:03.873944+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.576376+00:00</t>
+          <t>2026-10-17T09:24:03.874282+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.577146+00:00</t>
+          <t>2026-10-17T09:24:03.875064+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.577941+00:00</t>
+          <t>2026-10-17T09:24:03.875781+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.578918+00:00</t>
+          <t>2026-10-17T09:24:03.876678+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.579240+00:00</t>
+          <t>2026-10-17T09:24:03.876921+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.580131+00:00</t>
+          <t>2026-10-17T09:24:03.877802+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.588903+00:00</t>
+          <t>2026-10-17T09:24:03.885179+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.591388+00:00</t>
+          <t>2026-10-17T09:24:03.885952+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.592681+00:00</t>
+          <t>2026-10-17T09:24:03.887145+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.597250+00:00</t>
+          <t>2026-10-17T09:24:03.889780+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.600624+00:00</t>
+          <t>2026-10-17T09:24:03.890879+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.601968+00:00</t>
+          <t>2026-10-17T09:24:03.892060+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.606878+00:00</t>
+          <t>2026-10-17T09:24:03.896400+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.609199+00:00</t>
+          <t>2026-10-17T09:24:03.898735+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.611466+00:00</t>
+          <t>2026-10-17T09:24:03.900631+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.612539+00:00</t>
+          <t>2026-10-17T09:24:03.901354+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.613015+00:00</t>
+          <t>2026-10-17T09:24:03.901775+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.615136+00:00</t>
+          <t>2026-10-17T09:24:03.903767+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.616503+00:00</t>
+          <t>2026-10-17T09:24:03.905006+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.618737+00:00</t>
+          <t>2026-10-17T09:24:03.907064+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.620761+00:00</t>
+          <t>2026-10-17T09:24:03.909001+00:00</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.621346+00:00</t>
+          <t>2026-10-17T09:24:03.909610+00:00</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.621932+00:00</t>
+          <t>2026-10-17T09:24:03.910183+00:00</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.623878+00:00</t>
+          <t>2026-10-17T09:24:03.911907+00:00</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.626869+00:00</t>
+          <t>2026-10-17T09:24:03.914688+00:00</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.629428+00:00</t>
+          <t>2026-10-17T09:24:03.917282+00:00</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.630784+00:00</t>
+          <t>2026-10-17T09:24:03.918565+00:00</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.633906+00:00</t>
+          <t>2026-10-17T09:24:03.921510+00:00</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.636488+00:00</t>
+          <t>2026-10-17T09:24:03.922277+00:00</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.638159+00:00</t>
+          <t>2026-10-17T09:24:03.923954+00:00</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.641943+00:00</t>
+          <t>2026-10-17T09:24:03.924216+00:00</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.644205+00:00</t>
+          <t>2026-10-17T09:24:03.926252+00:00</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.647535+00:00</t>
+          <t>2026-10-17T09:24:03.929066+00:00</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.649138+00:00</t>
+          <t>2026-10-17T09:24:03.930429+00:00</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.649856+00:00</t>
+          <t>2026-10-17T09:24:03.930991+00:00</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.652737+00:00</t>
+          <t>2026-10-17T09:24:03.933706+00:00</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.653896+00:00</t>
+          <t>2026-10-17T09:24:03.934893+00:00</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.657899+00:00</t>
+          <t>2026-10-17T09:24:03.938490+00:00</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.659770+00:00</t>
+          <t>2026-10-17T09:24:03.940230+00:00</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.661734+00:00</t>
+          <t>2026-10-17T09:24:03.942318+00:00</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.662739+00:00</t>
+          <t>2026-10-17T09:24:03.943274+00:00</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.663177+00:00</t>
+          <t>2026-10-17T09:24:03.943832+00:00</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.663570+00:00</t>
+          <t>2026-10-17T09:24:03.944227+00:00</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.665092+00:00</t>
+          <t>2026-10-17T09:24:03.945769+00:00</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.666550+00:00</t>
+          <t>2026-10-17T09:24:03.947169+00:00</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.668318+00:00</t>
+          <t>2026-10-17T09:24:03.948687+00:00</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.668685+00:00</t>
+          <t>2026-10-17T09:24:03.949029+00:00</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.670169+00:00</t>
+          <t>2026-10-17T09:24:03.950204+00:00</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.671628+00:00</t>
+          <t>2026-10-17T09:24:03.951570+00:00</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.672231+00:00</t>
+          <t>2026-10-17T09:24:03.952156+00:00</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.673159+00:00</t>
+          <t>2026-10-17T09:24:03.953114+00:00</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.673571+00:00</t>
+          <t>2026-10-17T09:24:03.953438+00:00</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.679438+00:00</t>
+          <t>2026-10-17T09:24:03.958532+00:00</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.679900+00:00</t>
+          <t>2026-10-17T09:24:03.959030+00:00</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.680489+00:00</t>
+          <t>2026-10-17T09:24:03.959630+00:00</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.680930+00:00</t>
+          <t>2026-10-17T09:24:03.960098+00:00</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.682222+00:00</t>
+          <t>2026-10-17T09:24:03.961156+00:00</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.686082+00:00</t>
+          <t>2026-10-17T09:24:03.964116+00:00</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.686399+00:00</t>
+          <t>2026-10-17T09:24:03.964388+00:00</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.691349+00:00</t>
+          <t>2026-10-17T09:24:03.968767+00:00</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.692241+00:00</t>
+          <t>2026-10-17T09:24:03.969643+00:00</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.694557+00:00</t>
+          <t>2026-10-17T09:24:03.971919+00:00</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.696399+00:00</t>
+          <t>2026-10-17T09:24:03.973814+00:00</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.697367+00:00</t>
+          <t>2026-10-17T09:24:03.974691+00:00</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.699151+00:00</t>
+          <t>2026-10-17T09:24:03.976235+00:00</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.701421+00:00</t>
+          <t>2026-10-17T09:24:03.978591+00:00</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.710257+00:00</t>
+          <t>2026-10-17T09:24:03.986529+00:00</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.711607+00:00</t>
+          <t>2026-10-17T09:24:03.987817+00:00</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.711767+00:00</t>
+          <t>2026-10-17T09:24:03.987973+00:00</t>
         </is>
       </c>
     </row>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.711780+00:00</t>
+          <t>2026-10-17T09:24:03.987985+00:00</t>
         </is>
       </c>
     </row>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.717179+00:00</t>
+          <t>2026-10-17T09:24:03.992849+00:00</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.718181+00:00</t>
+          <t>2026-10-17T09:24:03.993267+00:00</t>
         </is>
       </c>
     </row>
@@ -33071,7 +33071,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.718659+00:00</t>
+          <t>2026-10-17T09:24:03.993660+00:00</t>
         </is>
       </c>
     </row>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.719078+00:00</t>
+          <t>2026-10-17T09:24:03.994066+00:00</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.719898+00:00</t>
+          <t>2026-10-17T09:24:03.994832+00:00</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33383,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.721327+00:00</t>
+          <t>2026-10-17T09:24:03.996812+00:00</t>
         </is>
       </c>
     </row>
@@ -33487,7 +33487,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.722368+00:00</t>
+          <t>2026-10-17T09:24:03.997710+00:00</t>
         </is>
       </c>
     </row>
@@ -33591,7 +33591,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.722755+00:00</t>
+          <t>2026-10-17T09:24:03.998033+00:00</t>
         </is>
       </c>
     </row>
@@ -33699,7 +33699,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.723422+00:00</t>
+          <t>2026-10-17T09:24:03.998747+00:00</t>
         </is>
       </c>
     </row>
@@ -33799,7 +33799,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.723441+00:00</t>
+          <t>2026-10-17T09:24:03.998767+00:00</t>
         </is>
       </c>
     </row>
@@ -33907,7 +33907,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.723498+00:00</t>
+          <t>2026-10-17T09:24:03.998919+00:00</t>
         </is>
       </c>
     </row>
@@ -34015,7 +34015,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.723742+00:00</t>
+          <t>2026-10-17T09:24:03.999163+00:00</t>
         </is>
       </c>
     </row>
@@ -34123,7 +34123,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.723874+00:00</t>
+          <t>2026-10-17T09:24:03.999341+00:00</t>
         </is>
       </c>
     </row>
@@ -34235,7 +34235,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.723994+00:00</t>
+          <t>2026-10-17T09:24:03.999481+00:00</t>
         </is>
       </c>
     </row>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.724379+00:00</t>
+          <t>2026-10-17T09:24:03.999856+00:00</t>
         </is>
       </c>
     </row>
@@ -34451,7 +34451,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.724589+00:00</t>
+          <t>2026-10-17T09:24:04.000051+00:00</t>
         </is>
       </c>
     </row>
@@ -34563,7 +34563,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.724647+00:00</t>
+          <t>2026-10-17T09:24:04.000107+00:00</t>
         </is>
       </c>
     </row>
@@ -34675,7 +34675,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.724710+00:00</t>
+          <t>2026-10-17T09:24:04.000175+00:00</t>
         </is>
       </c>
     </row>
@@ -34787,7 +34787,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.724939+00:00</t>
+          <t>2026-10-17T09:24:04.000354+00:00</t>
         </is>
       </c>
     </row>
@@ -34899,7 +34899,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.725010+00:00</t>
+          <t>2026-10-17T09:24:04.000403+00:00</t>
         </is>
       </c>
     </row>
@@ -35007,7 +35007,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.725502+00:00</t>
+          <t>2026-10-17T09:24:04.000896+00:00</t>
         </is>
       </c>
     </row>
@@ -35115,7 +35115,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.725572+00:00</t>
+          <t>2026-10-17T09:24:04.000955+00:00</t>
         </is>
       </c>
     </row>
@@ -35215,7 +35215,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.725583+00:00</t>
+          <t>2026-10-17T09:24:04.000965+00:00</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.736894+00:00</t>
+          <t>2026-10-17T09:24:04.010582+00:00</t>
         </is>
       </c>
     </row>
@@ -35427,7 +35427,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.736989+00:00</t>
+          <t>2026-10-17T09:24:04.010645+00:00</t>
         </is>
       </c>
     </row>
@@ -35535,7 +35535,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.737119+00:00</t>
+          <t>2026-10-17T09:24:04.010748+00:00</t>
         </is>
       </c>
     </row>
@@ -35643,7 +35643,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.737452+00:00</t>
+          <t>2026-10-17T09:24:04.010998+00:00</t>
         </is>
       </c>
     </row>
@@ -35751,7 +35751,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.738759+00:00</t>
+          <t>2026-10-17T09:24:04.012002+00:00</t>
         </is>
       </c>
     </row>
@@ -35853,7 +35853,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.739073+00:00</t>
+          <t>2026-10-17T09:24:04.012091+00:00</t>
         </is>
       </c>
     </row>
@@ -35947,7 +35947,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.739098+00:00</t>
+          <t>2026-10-17T09:24:04.012102+00:00</t>
         </is>
       </c>
     </row>
@@ -36049,7 +36049,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.739197+00:00</t>
+          <t>2026-10-17T09:24:04.012189+00:00</t>
         </is>
       </c>
     </row>
@@ -36151,7 +36151,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.739309+00:00</t>
+          <t>2026-10-17T09:24:04.012279+00:00</t>
         </is>
       </c>
     </row>
@@ -36253,7 +36253,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.739431+00:00</t>
+          <t>2026-10-17T09:24:04.012408+00:00</t>
         </is>
       </c>
     </row>
@@ -36347,7 +36347,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.739444+00:00</t>
+          <t>2026-10-17T09:24:04.012419+00:00</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.739604+00:00</t>
+          <t>2026-10-17T09:24:04.012573+00:00</t>
         </is>
       </c>
     </row>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.739615+00:00</t>
+          <t>2026-10-17T09:24:04.012583+00:00</t>
         </is>
       </c>
     </row>
@@ -36645,7 +36645,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.739726+00:00</t>
+          <t>2026-10-17T09:24:04.012687+00:00</t>
         </is>
       </c>
     </row>
@@ -36739,7 +36739,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.739736+00:00</t>
+          <t>2026-10-17T09:24:04.012697+00:00</t>
         </is>
       </c>
     </row>
@@ -36841,7 +36841,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.739877+00:00</t>
+          <t>2026-10-17T09:24:04.012836+00:00</t>
         </is>
       </c>
     </row>
@@ -36935,7 +36935,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.739889+00:00</t>
+          <t>2026-10-17T09:24:04.012847+00:00</t>
         </is>
       </c>
     </row>
@@ -37037,7 +37037,7 @@
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.739980+00:00</t>
+          <t>2026-10-17T09:24:04.012939+00:00</t>
         </is>
       </c>
     </row>
@@ -37139,7 +37139,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.740116+00:00</t>
+          <t>2026-10-17T09:24:04.013081+00:00</t>
         </is>
       </c>
     </row>
@@ -37233,7 +37233,7 @@
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.740127+00:00</t>
+          <t>2026-10-17T09:24:04.013095+00:00</t>
         </is>
       </c>
     </row>
@@ -37335,7 +37335,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.740245+00:00</t>
+          <t>2026-10-17T09:24:04.013219+00:00</t>
         </is>
       </c>
     </row>
@@ -37429,7 +37429,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.740256+00:00</t>
+          <t>2026-10-17T09:24:04.013231+00:00</t>
         </is>
       </c>
     </row>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.740383+00:00</t>
+          <t>2026-10-17T09:24:04.013350+00:00</t>
         </is>
       </c>
     </row>
@@ -37633,7 +37633,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.740609+00:00</t>
+          <t>2026-10-17T09:24:04.013590+00:00</t>
         </is>
       </c>
     </row>
@@ -37727,7 +37727,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.740621+00:00</t>
+          <t>2026-10-17T09:24:04.013605+00:00</t>
         </is>
       </c>
     </row>
@@ -37829,7 +37829,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.740782+00:00</t>
+          <t>2026-10-17T09:24:04.013784+00:00</t>
         </is>
       </c>
     </row>
@@ -37931,7 +37931,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.740994+00:00</t>
+          <t>2026-10-17T09:24:04.013987+00:00</t>
         </is>
       </c>
     </row>
@@ -38033,7 +38033,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.741189+00:00</t>
+          <t>2026-10-17T09:24:04.014181+00:00</t>
         </is>
       </c>
     </row>
@@ -38127,7 +38127,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.741200+00:00</t>
+          <t>2026-10-17T09:24:04.014192+00:00</t>
         </is>
       </c>
     </row>
@@ -38229,7 +38229,7 @@
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.741329+00:00</t>
+          <t>2026-10-17T09:24:04.014324+00:00</t>
         </is>
       </c>
     </row>
@@ -38323,7 +38323,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.741341+00:00</t>
+          <t>2026-10-17T09:24:04.014336+00:00</t>
         </is>
       </c>
     </row>
@@ -38425,7 +38425,7 @@
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.741431+00:00</t>
+          <t>2026-10-17T09:24:04.014426+00:00</t>
         </is>
       </c>
     </row>
@@ -38533,7 +38533,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.742852+00:00</t>
+          <t>2026-10-17T09:24:04.016475+00:00</t>
         </is>
       </c>
     </row>
@@ -38625,7 +38625,7 @@
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.753075+00:00</t>
+          <t>2026-10-17T09:24:04.026104+00:00</t>
         </is>
       </c>
     </row>
@@ -38725,7 +38725,7 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.753556+00:00</t>
+          <t>2026-10-17T09:24:04.026542+00:00</t>
         </is>
       </c>
     </row>
@@ -38813,7 +38813,7 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.753576+00:00</t>
+          <t>2026-10-17T09:24:04.026559+00:00</t>
         </is>
       </c>
     </row>
@@ -38913,7 +38913,7 @@
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.755014+00:00</t>
+          <t>2026-10-17T09:24:04.027684+00:00</t>
         </is>
       </c>
     </row>
@@ -39013,7 +39013,7 @@
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.759408+00:00</t>
+          <t>2026-10-17T09:24:04.031057+00:00</t>
         </is>
       </c>
     </row>
@@ -39113,7 +39113,7 @@
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.760430+00:00</t>
+          <t>2026-10-17T09:24:04.031964+00:00</t>
         </is>
       </c>
     </row>
@@ -39205,7 +39205,7 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.760453+00:00</t>
+          <t>2026-10-17T09:24:04.031981+00:00</t>
         </is>
       </c>
     </row>
@@ -39305,7 +39305,7 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.761161+00:00</t>
+          <t>2026-10-17T09:24:04.032710+00:00</t>
         </is>
       </c>
     </row>
@@ -39397,7 +39397,7 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.761178+00:00</t>
+          <t>2026-10-17T09:24:04.032724+00:00</t>
         </is>
       </c>
     </row>
@@ -39489,7 +39489,7 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.761182+00:00</t>
+          <t>2026-10-17T09:24:04.032728+00:00</t>
         </is>
       </c>
     </row>
@@ -39577,7 +39577,7 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.761185+00:00</t>
+          <t>2026-10-17T09:24:04.032732+00:00</t>
         </is>
       </c>
     </row>
@@ -39669,7 +39669,7 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.761189+00:00</t>
+          <t>2026-10-17T09:24:04.032735+00:00</t>
         </is>
       </c>
     </row>
@@ -39765,7 +39765,7 @@
       <c r="W149" t="inlineStr"/>
       <c r="X149" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.762908+00:00</t>
+          <t>2026-10-17T09:24:04.033535+00:00</t>
         </is>
       </c>
     </row>
@@ -39861,7 +39861,7 @@
       <c r="W150" t="inlineStr"/>
       <c r="X150" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.763970+00:00</t>
+          <t>2026-10-17T09:24:04.034571+00:00</t>
         </is>
       </c>
     </row>
@@ -39957,7 +39957,7 @@
       <c r="W151" t="inlineStr"/>
       <c r="X151" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.764538+00:00</t>
+          <t>2026-10-17T09:24:04.035016+00:00</t>
         </is>
       </c>
     </row>
@@ -40053,7 +40053,7 @@
       <c r="W152" t="inlineStr"/>
       <c r="X152" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.774110+00:00</t>
+          <t>2026-10-17T09:24:04.044789+00:00</t>
         </is>
       </c>
     </row>
@@ -40149,7 +40149,7 @@
       <c r="W153" t="inlineStr"/>
       <c r="X153" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.774262+00:00</t>
+          <t>2026-10-17T09:24:04.044940+00:00</t>
         </is>
       </c>
     </row>
@@ -40216,7 +40216,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>local_acquired_pending_remote_readback</t>
+          <t>git_remote_verified_20261017</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -40245,7 +40245,103 @@
       <c r="W154" t="inlineStr"/>
       <c r="X154" t="inlineStr">
         <is>
-          <t>2026-10-17T09:23:39.774467+00:00</t>
+          <t>2026-10-17T09:24:04.045112+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="b">
+        <v>0</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>R03564</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>R03564.evidence_html.e3a69b5338325eab</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>evidence_html</t>
+        </is>
+      </c>
+      <c r="E155" t="b">
+        <v>0</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>publisher_article_page_20261017.html</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R03564/publisher_article_page_20261017.html</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>original_files/source_evidence/R03564/publisher_article_page_20261017.html</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>/workspace/FirstCodex/results/ad-oxygen-literature-20261006/original_files/source_evidence/R03564/publisher_article_page_20261017.html</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
+        <v>634641</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>e3a69b5338325eabc9b744f1964752b926b8ab65022180d7e93fa512e1dc9e23</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>present_sha_verified</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>local_acquired_pending_remote_readback</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>https://www.mdpi.com/1996-1073/10/2/258</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>Article HTML with anonymous server session identifiers removed</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>Private authorized research backup; source license not inferred</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr"/>
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr"/>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>2026-10-17T09:24:04.045623+00:00</t>
         </is>
       </c>
     </row>

--- a/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
+++ b/results/ad-oxygen-literature-20261006/inventory/unified_library_inventory.xlsx
@@ -1659,7 +1659,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H29" t="b">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>checked_no_file_links_found_coverage_unconfirmed</t>
         </is>
       </c>
       <c r="H30" t="b">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H31" t="b">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H32" t="b">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>not_checked</t>
+          <t>access_failed</t>
         </is>
       </c>
       <c r="H33" t="b">
@@ -24118,7 +24118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X155"/>
+  <dimension ref="A1:X156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.862081+00:00</t>
+          <t>2026-10-17T09:24:30.133533+00:00</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.862969+00:00</t>
+          <t>2026-10-17T09:24:30.134627+00:00</t>
         </is>
       </c>
     </row>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.862987+00:00</t>
+          <t>2026-10-17T09:24:30.134656+00:00</t>
         </is>
       </c>
     </row>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.863216+00:00</t>
+          <t>2026-10-17T09:24:30.134889+00:00</t>
         </is>
       </c>
     </row>
@@ -24771,7 +24771,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.864363+00:00</t>
+          <t>2026-10-17T09:24:30.136090+00:00</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.865311+00:00</t>
+          <t>2026-10-17T09:24:30.136770+00:00</t>
         </is>
       </c>
     </row>
@@ -24987,7 +24987,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.870597+00:00</t>
+          <t>2026-10-17T09:24:30.143005+00:00</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.873018+00:00</t>
+          <t>2026-10-17T09:24:30.146101+00:00</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.873944+00:00</t>
+          <t>2026-10-17T09:24:30.147317+00:00</t>
         </is>
       </c>
     </row>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.874282+00:00</t>
+          <t>2026-10-17T09:24:30.147763+00:00</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.875064+00:00</t>
+          <t>2026-10-17T09:24:30.148567+00:00</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.875781+00:00</t>
+          <t>2026-10-17T09:24:30.149221+00:00</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.876678+00:00</t>
+          <t>2026-10-17T09:24:30.150191+00:00</t>
         </is>
       </c>
     </row>
@@ -25743,7 +25743,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.876921+00:00</t>
+          <t>2026-10-17T09:24:30.150472+00:00</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.877802+00:00</t>
+          <t>2026-10-17T09:24:30.151582+00:00</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.885179+00:00</t>
+          <t>2026-10-17T09:24:30.159776+00:00</t>
         </is>
       </c>
     </row>
@@ -26067,7 +26067,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.885952+00:00</t>
+          <t>2026-10-17T09:24:30.160791+00:00</t>
         </is>
       </c>
     </row>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.887145+00:00</t>
+          <t>2026-10-17T09:24:30.162563+00:00</t>
         </is>
       </c>
     </row>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.889780+00:00</t>
+          <t>2026-10-17T09:24:30.165687+00:00</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.890879+00:00</t>
+          <t>2026-10-17T09:24:30.166939+00:00</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.892060+00:00</t>
+          <t>2026-10-17T09:24:30.168191+00:00</t>
         </is>
       </c>
     </row>
@@ -26607,7 +26607,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.896400+00:00</t>
+          <t>2026-10-17T09:24:30.172676+00:00</t>
         </is>
       </c>
     </row>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.898735+00:00</t>
+          <t>2026-10-17T09:24:30.175250+00:00</t>
         </is>
       </c>
     </row>
@@ -26823,7 +26823,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.900631+00:00</t>
+          <t>2026-10-17T09:24:30.177577+00:00</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.901354+00:00</t>
+          <t>2026-10-17T09:24:30.178284+00:00</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.901775+00:00</t>
+          <t>2026-10-17T09:24:30.178712+00:00</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.903767+00:00</t>
+          <t>2026-10-17T09:24:30.180914+00:00</t>
         </is>
       </c>
     </row>
@@ -27255,7 +27255,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.905006+00:00</t>
+          <t>2026-10-17T09:24:30.182597+00:00</t>
         </is>
       </c>
     </row>
@@ -27363,7 +27363,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.907064+00:00</t>
+          <t>2026-10-17T09:24:30.185063+00:00</t>
         </is>
       </c>
     </row>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.909001+00:00</t>
+          <t>2026-10-17T09:24:30.187365+00:00</t>
         </is>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.909610+00:00</t>
+          <t>2026-10-17T09:24:30.188032+00:00</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27687,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.910183+00:00</t>
+          <t>2026-10-17T09:24:30.188838+00:00</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.911907+00:00</t>
+          <t>2026-10-17T09:24:30.190971+00:00</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27903,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.914688+00:00</t>
+          <t>2026-10-17T09:24:30.194253+00:00</t>
         </is>
       </c>
     </row>
@@ -28011,7 +28011,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.917282+00:00</t>
+          <t>2026-10-17T09:24:30.196892+00:00</t>
         </is>
       </c>
     </row>
@@ -28119,7 +28119,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.918565+00:00</t>
+          <t>2026-10-17T09:24:30.198337+00:00</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.921510+00:00</t>
+          <t>2026-10-17T09:24:30.201853+00:00</t>
         </is>
       </c>
     </row>
@@ -28335,7 +28335,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.922277+00:00</t>
+          <t>2026-10-17T09:24:30.202674+00:00</t>
         </is>
       </c>
     </row>
@@ -28443,7 +28443,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.923954+00:00</t>
+          <t>2026-10-17T09:24:30.204415+00:00</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.924216+00:00</t>
+          <t>2026-10-17T09:24:30.204702+00:00</t>
         </is>
       </c>
     </row>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.926252+00:00</t>
+          <t>2026-10-17T09:24:30.206776+00:00</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.929066+00:00</t>
+          <t>2026-10-17T09:24:30.210447+00:00</t>
         </is>
       </c>
     </row>
@@ -28875,7 +28875,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.930429+00:00</t>
+          <t>2026-10-17T09:24:30.211826+00:00</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.930991+00:00</t>
+          <t>2026-10-17T09:24:30.212395+00:00</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.933706+00:00</t>
+          <t>2026-10-17T09:24:30.215338+00:00</t>
         </is>
       </c>
     </row>
@@ -29199,7 +29199,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.934893+00:00</t>
+          <t>2026-10-17T09:24:30.216599+00:00</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.938490+00:00</t>
+          <t>2026-10-17T09:24:30.220412+00:00</t>
         </is>
       </c>
     </row>
@@ -29415,7 +29415,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.940230+00:00</t>
+          <t>2026-10-17T09:24:30.222288+00:00</t>
         </is>
       </c>
     </row>
@@ -29523,7 +29523,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.942318+00:00</t>
+          <t>2026-10-17T09:24:30.224404+00:00</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.943274+00:00</t>
+          <t>2026-10-17T09:24:30.225751+00:00</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.943832+00:00</t>
+          <t>2026-10-17T09:24:30.226229+00:00</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.944227+00:00</t>
+          <t>2026-10-17T09:24:30.226649+00:00</t>
         </is>
       </c>
     </row>
@@ -29955,7 +29955,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.945769+00:00</t>
+          <t>2026-10-17T09:24:30.228091+00:00</t>
         </is>
       </c>
     </row>
@@ -30063,7 +30063,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.947169+00:00</t>
+          <t>2026-10-17T09:24:30.229442+00:00</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30171,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.948687+00:00</t>
+          <t>2026-10-17T09:24:30.231196+00:00</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.949029+00:00</t>
+          <t>2026-10-17T09:24:30.231597+00:00</t>
         </is>
       </c>
     </row>
@@ -30387,7 +30387,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.950204+00:00</t>
+          <t>2026-10-17T09:24:30.233234+00:00</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.951570+00:00</t>
+          <t>2026-10-17T09:24:30.234811+00:00</t>
         </is>
       </c>
     </row>
@@ -30603,7 +30603,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.952156+00:00</t>
+          <t>2026-10-17T09:24:30.235526+00:00</t>
         </is>
       </c>
     </row>
@@ -30711,7 +30711,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.953114+00:00</t>
+          <t>2026-10-17T09:24:30.236631+00:00</t>
         </is>
       </c>
     </row>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.953438+00:00</t>
+          <t>2026-10-17T09:24:30.237199+00:00</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.958532+00:00</t>
+          <t>2026-10-17T09:24:30.243453+00:00</t>
         </is>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.959030+00:00</t>
+          <t>2026-10-17T09:24:30.243887+00:00</t>
         </is>
       </c>
     </row>
@@ -31143,7 +31143,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.959630+00:00</t>
+          <t>2026-10-17T09:24:30.244682+00:00</t>
         </is>
       </c>
     </row>
@@ -31251,7 +31251,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.960098+00:00</t>
+          <t>2026-10-17T09:24:30.245409+00:00</t>
         </is>
       </c>
     </row>
@@ -31359,7 +31359,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.961156+00:00</t>
+          <t>2026-10-17T09:24:30.246694+00:00</t>
         </is>
       </c>
     </row>
@@ -31467,7 +31467,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.964116+00:00</t>
+          <t>2026-10-17T09:24:30.250194+00:00</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.964388+00:00</t>
+          <t>2026-10-17T09:24:30.250549+00:00</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.968767+00:00</t>
+          <t>2026-10-17T09:24:30.254851+00:00</t>
         </is>
       </c>
     </row>
@@ -31791,7 +31791,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.969643+00:00</t>
+          <t>2026-10-17T09:24:30.255806+00:00</t>
         </is>
       </c>
     </row>
@@ -31899,7 +31899,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.971919+00:00</t>
+          <t>2026-10-17T09:24:30.258079+00:00</t>
         </is>
       </c>
     </row>
@@ -32007,7 +32007,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.973814+00:00</t>
+          <t>2026-10-17T09:24:30.259932+00:00</t>
         </is>
       </c>
     </row>
@@ -32115,7 +32115,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.974691+00:00</t>
+          <t>2026-10-17T09:24:30.260967+00:00</t>
         </is>
       </c>
     </row>
@@ -32223,7 +32223,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.976235+00:00</t>
+          <t>2026-10-17T09:24:30.262735+00:00</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32331,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.978591+00:00</t>
+          <t>2026-10-17T09:24:30.264980+00:00</t>
         </is>
       </c>
     </row>
@@ -32439,7 +32439,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.986529+00:00</t>
+          <t>2026-10-17T09:24:30.273997+00:00</t>
         </is>
       </c>
     </row>
@@ -32547,7 +32547,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.987817+00:00</t>
+          <t>2026-10-17T09:24:30.275359+00:00</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.987973+00:00</t>
+          <t>2026-10-17T09:24:30.275579+00:00</t>
         </is>
       </c>
     </row>
@@ -32755,7 +32755,7 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.987985+00:00</t>
+          <t>2026-10-17T09:24:30.275600+00:00</t>
         </is>
       </c>
     </row>
@@ -32863,7 +32863,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.992849+00:00</t>
+          <t>2026-10-17T09:24:30.281239+00:00</t>
         </is>
       </c>
     </row>
@@ -32967,7 +32967,7 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.993267+00:00</t>
+          <t>2026-10-17T09:24:30.281903+00:00</t>
         </is>
       </c>
     </row>
@@ -33071,7 +33071,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.993660+00:00</t>
+          <t>2026-10-17T09:24:30.282269+00:00</t>
         </is>
       </c>
     </row>
@@ -33175,7 +33175,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.994066+00:00</t>
+          <t>2026-10-17T09:24:30.282785+00:00</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-10-17T09:24:03.994832+00:00</t>
+          <t>2026-10-17T09:24:30.283668+00:00</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33383,7 @@
       </c>
       